--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Indicators" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Daily Log" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Methodology" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Indicators" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily Log" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-06-28  -  generated 2026-06-28 17:17 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-06-28  -  generated 2026-06-28 17:50 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1430,7 @@
         </is>
       </c>
       <c r="D3" s="7" t="n">
-        <v>66.79000000000001</v>
+        <v>96</v>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O3" s="8" t="inlineStr">
@@ -1534,7 +1534,7 @@
       </c>
       <c r="N4" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O4" s="8" t="inlineStr">
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>161.685</v>
+        <v>156</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O5" s="8" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O6" s="8" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O7" s="8" t="inlineStr"/>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O9" s="8" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="N10" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O10" s="8" t="inlineStr"/>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O13" s="8" t="inlineStr"/>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="N14" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O14" s="8" t="inlineStr"/>
@@ -2190,7 +2190,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>6.7897</v>
+        <v>7.2</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O15" s="8" t="inlineStr"/>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="N16" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O16" s="8" t="inlineStr"/>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O17" s="8" t="inlineStr"/>
@@ -2412,7 +2412,7 @@
       </c>
       <c r="N18" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O18" s="8" t="inlineStr"/>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O19" s="8" t="inlineStr"/>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="N20" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O20" s="8" t="inlineStr">
@@ -2599,7 +2599,7 @@
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O21" s="8" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="N22" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O22" s="8" t="inlineStr"/>
@@ -2790,7 +2790,7 @@
       </c>
       <c r="N24" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O24" s="8" t="inlineStr"/>
@@ -2851,7 +2851,7 @@
       </c>
       <c r="N25" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O25" s="8" t="inlineStr"/>
@@ -2912,7 +2912,7 @@
       </c>
       <c r="N26" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O26" s="8" t="inlineStr">
@@ -2977,7 +2977,7 @@
       </c>
       <c r="N27" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O27" s="8" t="inlineStr"/>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="N29" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O29" s="8" t="inlineStr"/>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="N30" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O30" s="8" t="inlineStr"/>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="N31" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O31" s="8" t="inlineStr"/>
@@ -3351,7 +3351,7 @@
       </c>
       <c r="N33" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O33" s="8" t="inlineStr"/>
@@ -3373,7 +3373,7 @@
         </is>
       </c>
       <c r="D34" s="7" t="n">
-        <v>4096.2998</v>
+        <v>4300</v>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
       </c>
       <c r="N34" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O34" s="8" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="N35" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O35" s="8" t="inlineStr"/>
@@ -3538,7 +3538,7 @@
       </c>
       <c r="N36" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O36" s="8" t="inlineStr"/>
@@ -3599,7 +3599,7 @@
       </c>
       <c r="N37" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O37" s="8" t="inlineStr"/>
@@ -3721,7 +3721,7 @@
       </c>
       <c r="N39" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O39" s="8" t="inlineStr"/>
@@ -3782,7 +3782,7 @@
       </c>
       <c r="N40" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O40" s="8" t="inlineStr"/>
@@ -3843,7 +3843,7 @@
       </c>
       <c r="N41" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O41" s="8" t="inlineStr"/>
@@ -3904,7 +3904,7 @@
       </c>
       <c r="N42" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O42" s="8" t="inlineStr"/>
@@ -3965,7 +3965,7 @@
       </c>
       <c r="N43" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O43" s="8" t="inlineStr">
@@ -4030,7 +4030,7 @@
       </c>
       <c r="N44" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O44" s="8" t="inlineStr"/>
@@ -4091,7 +4091,7 @@
       </c>
       <c r="N45" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O45" s="8" t="inlineStr">
@@ -4117,7 +4117,7 @@
         </is>
       </c>
       <c r="D46" s="7" t="n">
-        <v>6.207</v>
+        <v>5.4</v>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
       </c>
       <c r="N46" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O46" s="8" t="inlineStr">
@@ -4221,7 +4221,7 @@
       </c>
       <c r="N47" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O47" s="8" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="N48" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O48" s="8" t="inlineStr"/>
@@ -4347,7 +4347,7 @@
       </c>
       <c r="N49" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O49" s="8" t="inlineStr"/>
@@ -4408,7 +4408,7 @@
       </c>
       <c r="N50" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O50" s="8" t="inlineStr"/>
@@ -4469,7 +4469,7 @@
       </c>
       <c r="N51" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O51" s="8" t="inlineStr"/>
@@ -4530,7 +4530,7 @@
       </c>
       <c r="N52" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O52" s="8" t="inlineStr"/>
@@ -4591,7 +4591,7 @@
       </c>
       <c r="N53" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O53" s="8" t="inlineStr">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="N54" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O54" s="8" t="inlineStr"/>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="N55" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O55" s="8" t="inlineStr"/>
@@ -4778,7 +4778,7 @@
       </c>
       <c r="N56" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O56" s="8" t="inlineStr"/>
@@ -4839,7 +4839,7 @@
       </c>
       <c r="N57" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O57" s="8" t="inlineStr"/>
@@ -4900,7 +4900,7 @@
       </c>
       <c r="N58" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O58" s="8" t="inlineStr">
@@ -4926,7 +4926,7 @@
         </is>
       </c>
       <c r="D59" s="7" t="n">
-        <v>69.23</v>
+        <v>95</v>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
@@ -4965,7 +4965,7 @@
       </c>
       <c r="N59" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O59" s="8" t="inlineStr"/>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="N60" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O60" s="8" t="inlineStr"/>
@@ -5048,7 +5048,7 @@
         </is>
       </c>
       <c r="D61" s="7" t="n">
-        <v>18.41</v>
+        <v>17</v>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="N61" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O61" s="8" t="inlineStr"/>
@@ -5109,7 +5109,7 @@
         </is>
       </c>
       <c r="D62" s="7" t="n">
-        <v>66.79000000000001</v>
+        <v>96</v>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="N62" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O62" s="8" t="inlineStr"/>
@@ -5209,7 +5209,7 @@
       </c>
       <c r="N63" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O63" s="8" t="inlineStr"/>
@@ -5225,7 +5225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6051,783 +6051,6 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B23" s="9" t="inlineStr">
-        <is>
-          <t>s1_basis_trade</t>
-        </is>
-      </c>
-      <c r="C23" s="9" t="inlineStr">
-        <is>
-          <t>Treasury basis trade (hidden leverage)</t>
-        </is>
-      </c>
-      <c r="D23" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E23" s="9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F23" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G23" s="9" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B24" s="9" t="inlineStr">
-        <is>
-          <t>s2_japan</t>
-        </is>
-      </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>Japan fiscal / JGB / carry trade</t>
-        </is>
-      </c>
-      <c r="D24" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E24" s="9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F24" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G24" s="9" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B25" s="9" t="inlineStr">
-        <is>
-          <t>s3_private_credit</t>
-        </is>
-      </c>
-      <c r="C25" s="9" t="inlineStr">
-        <is>
-          <t>Private credit's opaque expansion</t>
-        </is>
-      </c>
-      <c r="D25" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E25" s="9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F25" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G25" s="9" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B26" s="9" t="inlineStr">
-        <is>
-          <t>s4_dev_debt</t>
-        </is>
-      </c>
-      <c r="C26" s="9" t="inlineStr">
-        <is>
-          <t>Developing-world debt crisis</t>
-        </is>
-      </c>
-      <c r="D26" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E26" s="9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F26" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G26" s="9" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B27" s="9" t="inlineStr">
-        <is>
-          <t>s5_china_deflation</t>
-        </is>
-      </c>
-      <c r="C27" s="9" t="inlineStr">
-        <is>
-          <t>China's exported deflation</t>
-        </is>
-      </c>
-      <c r="D27" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E27" s="9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F27" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G27" s="9" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B28" s="9" t="inlineStr">
-        <is>
-          <t>s6_rare_earths</t>
-        </is>
-      </c>
-      <c r="C28" s="9" t="inlineStr">
-        <is>
-          <t>Critical minerals as a weapon</t>
-        </is>
-      </c>
-      <c r="D28" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E28" s="9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F28" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G28" s="9" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B29" s="9" t="inlineStr">
-        <is>
-          <t>s7_stablecoins</t>
-        </is>
-      </c>
-      <c r="C29" s="9" t="inlineStr">
-        <is>
-          <t>Stablecoins &amp; Treasury demand</t>
-        </is>
-      </c>
-      <c r="D29" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E29" s="9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F29" s="9" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="G29" s="9" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B30" s="9" t="inlineStr">
-        <is>
-          <t>s8_ai_capex</t>
-        </is>
-      </c>
-      <c r="C30" s="9" t="inlineStr">
-        <is>
-          <t>AI build-out circular financing</t>
-        </is>
-      </c>
-      <c r="D30" s="9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E30" s="9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F30" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G30" s="9" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B31" s="9" t="inlineStr">
-        <is>
-          <t>s9_cre</t>
-        </is>
-      </c>
-      <c r="C31" s="9" t="inlineStr">
-        <is>
-          <t>CRE maturity wall / regional banks</t>
-        </is>
-      </c>
-      <c r="D31" s="9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E31" s="9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F31" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G31" s="9" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B32" s="9" t="inlineStr">
-        <is>
-          <t>s10_france</t>
-        </is>
-      </c>
-      <c r="C32" s="9" t="inlineStr">
-        <is>
-          <t>France / eurozone fragility</t>
-        </is>
-      </c>
-      <c r="D32" s="9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E32" s="9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F32" s="9" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="G32" s="9" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B33" s="9" t="inlineStr">
-        <is>
-          <t>s11_consumer_debt</t>
-        </is>
-      </c>
-      <c r="C33" s="9" t="inlineStr">
-        <is>
-          <t>Hidden consumer debt</t>
-        </is>
-      </c>
-      <c r="D33" s="9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E33" s="9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F33" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G33" s="9" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B34" s="9" t="inlineStr">
-        <is>
-          <t>s12_gold_dedollar</t>
-        </is>
-      </c>
-      <c r="C34" s="9" t="inlineStr">
-        <is>
-          <t>Gold / de-dollarization</t>
-        </is>
-      </c>
-      <c r="D34" s="9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E34" s="9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F34" s="9" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="G34" s="9" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B35" s="9" t="inlineStr">
-        <is>
-          <t>s13_insurance</t>
-        </is>
-      </c>
-      <c r="C35" s="9" t="inlineStr">
-        <is>
-          <t>Insurance retreat</t>
-        </is>
-      </c>
-      <c r="D35" s="9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E35" s="9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F35" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G35" s="9" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B36" s="9" t="inlineStr">
-        <is>
-          <t>s14_pensions</t>
-        </is>
-      </c>
-      <c r="C36" s="9" t="inlineStr">
-        <is>
-          <t>Pensions / demographics</t>
-        </is>
-      </c>
-      <c r="D36" s="9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E36" s="9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F36" s="9" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="G36" s="9" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B37" s="9" t="inlineStr">
-        <is>
-          <t>s15_ai_power</t>
-        </is>
-      </c>
-      <c r="C37" s="9" t="inlineStr">
-        <is>
-          <t>AI power &amp; the grid bottleneck</t>
-        </is>
-      </c>
-      <c r="D37" s="9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E37" s="9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F37" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G37" s="9" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B38" s="9" t="inlineStr">
-        <is>
-          <t>s16_copper</t>
-        </is>
-      </c>
-      <c r="C38" s="9" t="inlineStr">
-        <is>
-          <t>Copper &amp; the electrification deficit</t>
-        </is>
-      </c>
-      <c r="D38" s="9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E38" s="9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F38" s="9" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="G38" s="9" t="inlineStr">
-        <is>
-          <t>4.25</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B39" s="9" t="inlineStr">
-        <is>
-          <t>s17_water</t>
-        </is>
-      </c>
-      <c r="C39" s="9" t="inlineStr">
-        <is>
-          <t>Water - the underpriced input</t>
-        </is>
-      </c>
-      <c r="D39" s="9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E39" s="9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F39" s="9" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="G39" s="9" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B40" s="9" t="inlineStr">
-        <is>
-          <t>s18_food_fertilizer</t>
-        </is>
-      </c>
-      <c r="C40" s="9" t="inlineStr">
-        <is>
-          <t>Food &amp; fertilizer fragility</t>
-        </is>
-      </c>
-      <c r="D40" s="9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E40" s="9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F40" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G40" s="9" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B41" s="9" t="inlineStr">
-        <is>
-          <t>s19_lithography</t>
-        </is>
-      </c>
-      <c r="C41" s="9" t="inlineStr">
-        <is>
-          <t>The lithography (ASML) chokepoint</t>
-        </is>
-      </c>
-      <c r="D41" s="9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E41" s="9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F41" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G41" s="9" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B42" s="9" t="inlineStr">
-        <is>
-          <t>s20_sea_lanes</t>
-        </is>
-      </c>
-      <c r="C42" s="9" t="inlineStr">
-        <is>
-          <t>Sea lanes &amp; undersea cables</t>
-        </is>
-      </c>
-      <c r="D42" s="9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E42" s="9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F42" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G42" s="9" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B43" s="9" t="inlineStr">
-        <is>
-          <t>s21_clearinghouses</t>
-        </is>
-      </c>
-      <c r="C43" s="9" t="inlineStr">
-        <is>
-          <t>Clearinghouses (financial chokepoint)</t>
-        </is>
-      </c>
-      <c r="D43" s="9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E43" s="9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F43" s="9" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="G43" s="9" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6839,7 +6062,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A24"/>
+  <dimension ref="A1:A15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -6927,61 +6150,14 @@
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t># EOD Macro-Risk Brief | 28 June 2026</t>
+          <t>As of 2026-06-28: overall risk 5.0/10 (Set 1 5.3/10, Set 2 4.6/10, Set 3 5.1/10).</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>**Headline:** Macro risk stable at 5.0/10 with 14 elevated stories and one de-escalation.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="12" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
-          <t>**Level Changes:**</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>• **Sea lanes &amp; undersea cables** (7→6, Elevated): WTI crude fell 50¢ to $69.23/bbl, reducing energy-driven geopolitical pressure on maritime routes and critical infrastructure.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="12" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>**Elevated Stories to Monitor (14 total):**</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t>Nine financial-system risks span Treasury basis trades, Japan's JGB/carry exposure, opaque private credit, developing-world debt, CRE maturity walls, and hidden consumer leverage. Six supply-chain and structural risks include China's export deflation, critical minerals weaponization, AI financing circularity, lithography chokepoints, power-grid bottlenecks, and food-fertilizer fragility. Insurance retreat compounds tail-risk exposure.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="12" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="12" t="inlineStr">
-        <is>
-          <t>**Watch:** Japan fiscal/JGB/carry trade (level 6) remains the highest-risk trigger for rapid deleveraging across global markets.</t>
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>No story changed level versus the previous run. Daily market indicators moved within their current bands.</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Indicators" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily Log" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Indicators" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Daily Log" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Methodology" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-06-28  -  generated 2026-06-28 17:50 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-06-28  -  generated 2026-06-28 18:09 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1430,7 @@
         </is>
       </c>
       <c r="D3" s="7" t="n">
-        <v>96</v>
+        <v>66.79000000000001</v>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O3" s="8" t="inlineStr">
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>156</v>
+        <v>161.685</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O5" s="8" t="inlineStr">
@@ -2190,7 +2190,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>7.2</v>
+        <v>6.7975</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O15" s="8" t="inlineStr"/>
@@ -3373,7 +3373,7 @@
         </is>
       </c>
       <c r="D34" s="7" t="n">
-        <v>4300</v>
+        <v>4096.2998</v>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
       </c>
       <c r="N34" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O34" s="8" t="inlineStr">
@@ -4117,7 +4117,7 @@
         </is>
       </c>
       <c r="D46" s="7" t="n">
-        <v>5.4</v>
+        <v>6.207</v>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
       </c>
       <c r="N46" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O46" s="8" t="inlineStr">
@@ -4926,7 +4926,7 @@
         </is>
       </c>
       <c r="D59" s="7" t="n">
-        <v>95</v>
+        <v>69.23</v>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
@@ -4965,7 +4965,7 @@
       </c>
       <c r="N59" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O59" s="8" t="inlineStr"/>
@@ -5048,7 +5048,7 @@
         </is>
       </c>
       <c r="D61" s="7" t="n">
-        <v>17</v>
+        <v>18.41</v>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="N61" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O61" s="8" t="inlineStr"/>
@@ -5109,7 +5109,7 @@
         </is>
       </c>
       <c r="D62" s="7" t="n">
-        <v>96</v>
+        <v>66.79000000000001</v>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="N62" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O62" s="8" t="inlineStr"/>
@@ -5225,7 +5225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6051,6 +6051,783 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>s1_basis_trade</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>Treasury basis trade (hidden leverage)</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G23" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>s2_japan</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>Japan fiscal / JGB / carry trade</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G24" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>s3_private_credit</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>Private credit's opaque expansion</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F25" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G25" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>s4_dev_debt</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>Developing-world debt crisis</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F26" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G26" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>s5_china_deflation</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>China's exported deflation</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F27" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G27" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>s6_rare_earths</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>Critical minerals as a weapon</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F28" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G28" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>s7_stablecoins</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>Stablecoins &amp; Treasury demand</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F29" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G29" s="9" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>s8_ai_capex</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>AI build-out circular financing</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F30" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G30" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>s9_cre</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>CRE maturity wall / regional banks</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E31" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F31" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G31" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>s10_france</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>France / eurozone fragility</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F32" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G32" s="9" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>s11_consumer_debt</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>Hidden consumer debt</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F33" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G33" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>s12_gold_dedollar</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>Gold / de-dollarization</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F34" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G34" s="9" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>s13_insurance</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>Insurance retreat</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F35" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G35" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>s14_pensions</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>Pensions / demographics</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F36" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G36" s="9" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>s15_ai_power</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>AI power &amp; the grid bottleneck</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F37" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G37" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>s16_copper</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>Copper &amp; the electrification deficit</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F38" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G38" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>s17_water</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>Water - the underpriced input</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E39" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F39" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G39" s="9" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>s18_food_fertilizer</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>Food &amp; fertilizer fragility</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F40" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G40" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>s19_lithography</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>The lithography (ASML) chokepoint</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E41" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F41" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G41" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>s20_sea_lanes</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>Sea lanes &amp; undersea cables</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F42" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G42" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>s21_clearinghouses</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>Clearinghouses (financial chokepoint)</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F43" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G43" s="9" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6062,7 +6839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -6150,14 +6927,65 @@
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>As of 2026-06-28: overall risk 5.0/10 (Set 1 5.3/10, Set 2 4.6/10, Set 3 5.1/10).</t>
+          <t>**HEADLINE**</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>No story changed level versus the previous run. Daily market indicators moved within their current bands.</t>
+          <t>Macro risk stable at 5.0/10, with 14 stories in Elevated band; one infrastructure risk eased.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>**LEVEL CHANGES**</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>• **Sea lanes &amp; undersea cables** (7→6): WTI crude fell 50¢ to $69.23/bbl, reducing energy-transit pressure but leaving critical chokepoint risk material.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>**ELEVATED RISKS TO MONITOR**</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>Japan fiscal/JGB/carry trade, China's exported deflation, critical minerals weaponization, AI build-out financing, and food/fertilizer fragility all at level 6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>**WATCH**</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>Japan fiscal/JGB/carry trade (level 6) remains the highest-risk story given interlinkage with global funding conditions.</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Indicators" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Daily Log" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Methodology" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Indicators" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily Log" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-06-28  -  generated 2026-06-28 18:09 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-06-28  -  generated 2026-06-28 18:06 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1430,7 @@
         </is>
       </c>
       <c r="D3" s="7" t="n">
-        <v>66.79000000000001</v>
+        <v>96</v>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O3" s="8" t="inlineStr">
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>161.685</v>
+        <v>156</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O5" s="8" t="inlineStr">
@@ -2190,7 +2190,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>6.7975</v>
+        <v>7.2</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O15" s="8" t="inlineStr"/>
@@ -3373,7 +3373,7 @@
         </is>
       </c>
       <c r="D34" s="7" t="n">
-        <v>4096.2998</v>
+        <v>4300</v>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
       </c>
       <c r="N34" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O34" s="8" t="inlineStr">
@@ -4117,7 +4117,7 @@
         </is>
       </c>
       <c r="D46" s="7" t="n">
-        <v>6.207</v>
+        <v>5.4</v>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
       </c>
       <c r="N46" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O46" s="8" t="inlineStr">
@@ -4926,7 +4926,7 @@
         </is>
       </c>
       <c r="D59" s="7" t="n">
-        <v>69.23</v>
+        <v>95</v>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
@@ -4965,7 +4965,7 @@
       </c>
       <c r="N59" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O59" s="8" t="inlineStr"/>
@@ -5048,7 +5048,7 @@
         </is>
       </c>
       <c r="D61" s="7" t="n">
-        <v>18.41</v>
+        <v>17</v>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="N61" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O61" s="8" t="inlineStr"/>
@@ -5109,7 +5109,7 @@
         </is>
       </c>
       <c r="D62" s="7" t="n">
-        <v>66.79000000000001</v>
+        <v>96</v>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="N62" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O62" s="8" t="inlineStr"/>
@@ -5225,7 +5225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6051,783 +6051,6 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B23" s="9" t="inlineStr">
-        <is>
-          <t>s1_basis_trade</t>
-        </is>
-      </c>
-      <c r="C23" s="9" t="inlineStr">
-        <is>
-          <t>Treasury basis trade (hidden leverage)</t>
-        </is>
-      </c>
-      <c r="D23" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E23" s="9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F23" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G23" s="9" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B24" s="9" t="inlineStr">
-        <is>
-          <t>s2_japan</t>
-        </is>
-      </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>Japan fiscal / JGB / carry trade</t>
-        </is>
-      </c>
-      <c r="D24" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E24" s="9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F24" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G24" s="9" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B25" s="9" t="inlineStr">
-        <is>
-          <t>s3_private_credit</t>
-        </is>
-      </c>
-      <c r="C25" s="9" t="inlineStr">
-        <is>
-          <t>Private credit's opaque expansion</t>
-        </is>
-      </c>
-      <c r="D25" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E25" s="9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F25" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G25" s="9" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B26" s="9" t="inlineStr">
-        <is>
-          <t>s4_dev_debt</t>
-        </is>
-      </c>
-      <c r="C26" s="9" t="inlineStr">
-        <is>
-          <t>Developing-world debt crisis</t>
-        </is>
-      </c>
-      <c r="D26" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E26" s="9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F26" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G26" s="9" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B27" s="9" t="inlineStr">
-        <is>
-          <t>s5_china_deflation</t>
-        </is>
-      </c>
-      <c r="C27" s="9" t="inlineStr">
-        <is>
-          <t>China's exported deflation</t>
-        </is>
-      </c>
-      <c r="D27" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E27" s="9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F27" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G27" s="9" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B28" s="9" t="inlineStr">
-        <is>
-          <t>s6_rare_earths</t>
-        </is>
-      </c>
-      <c r="C28" s="9" t="inlineStr">
-        <is>
-          <t>Critical minerals as a weapon</t>
-        </is>
-      </c>
-      <c r="D28" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E28" s="9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F28" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G28" s="9" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B29" s="9" t="inlineStr">
-        <is>
-          <t>s7_stablecoins</t>
-        </is>
-      </c>
-      <c r="C29" s="9" t="inlineStr">
-        <is>
-          <t>Stablecoins &amp; Treasury demand</t>
-        </is>
-      </c>
-      <c r="D29" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E29" s="9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F29" s="9" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="G29" s="9" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B30" s="9" t="inlineStr">
-        <is>
-          <t>s8_ai_capex</t>
-        </is>
-      </c>
-      <c r="C30" s="9" t="inlineStr">
-        <is>
-          <t>AI build-out circular financing</t>
-        </is>
-      </c>
-      <c r="D30" s="9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E30" s="9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F30" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G30" s="9" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B31" s="9" t="inlineStr">
-        <is>
-          <t>s9_cre</t>
-        </is>
-      </c>
-      <c r="C31" s="9" t="inlineStr">
-        <is>
-          <t>CRE maturity wall / regional banks</t>
-        </is>
-      </c>
-      <c r="D31" s="9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E31" s="9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F31" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G31" s="9" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B32" s="9" t="inlineStr">
-        <is>
-          <t>s10_france</t>
-        </is>
-      </c>
-      <c r="C32" s="9" t="inlineStr">
-        <is>
-          <t>France / eurozone fragility</t>
-        </is>
-      </c>
-      <c r="D32" s="9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E32" s="9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F32" s="9" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="G32" s="9" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B33" s="9" t="inlineStr">
-        <is>
-          <t>s11_consumer_debt</t>
-        </is>
-      </c>
-      <c r="C33" s="9" t="inlineStr">
-        <is>
-          <t>Hidden consumer debt</t>
-        </is>
-      </c>
-      <c r="D33" s="9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E33" s="9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F33" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G33" s="9" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B34" s="9" t="inlineStr">
-        <is>
-          <t>s12_gold_dedollar</t>
-        </is>
-      </c>
-      <c r="C34" s="9" t="inlineStr">
-        <is>
-          <t>Gold / de-dollarization</t>
-        </is>
-      </c>
-      <c r="D34" s="9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E34" s="9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F34" s="9" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="G34" s="9" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B35" s="9" t="inlineStr">
-        <is>
-          <t>s13_insurance</t>
-        </is>
-      </c>
-      <c r="C35" s="9" t="inlineStr">
-        <is>
-          <t>Insurance retreat</t>
-        </is>
-      </c>
-      <c r="D35" s="9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E35" s="9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F35" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G35" s="9" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B36" s="9" t="inlineStr">
-        <is>
-          <t>s14_pensions</t>
-        </is>
-      </c>
-      <c r="C36" s="9" t="inlineStr">
-        <is>
-          <t>Pensions / demographics</t>
-        </is>
-      </c>
-      <c r="D36" s="9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E36" s="9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F36" s="9" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="G36" s="9" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B37" s="9" t="inlineStr">
-        <is>
-          <t>s15_ai_power</t>
-        </is>
-      </c>
-      <c r="C37" s="9" t="inlineStr">
-        <is>
-          <t>AI power &amp; the grid bottleneck</t>
-        </is>
-      </c>
-      <c r="D37" s="9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E37" s="9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F37" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G37" s="9" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B38" s="9" t="inlineStr">
-        <is>
-          <t>s16_copper</t>
-        </is>
-      </c>
-      <c r="C38" s="9" t="inlineStr">
-        <is>
-          <t>Copper &amp; the electrification deficit</t>
-        </is>
-      </c>
-      <c r="D38" s="9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E38" s="9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F38" s="9" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="G38" s="9" t="inlineStr">
-        <is>
-          <t>4.25</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B39" s="9" t="inlineStr">
-        <is>
-          <t>s17_water</t>
-        </is>
-      </c>
-      <c r="C39" s="9" t="inlineStr">
-        <is>
-          <t>Water - the underpriced input</t>
-        </is>
-      </c>
-      <c r="D39" s="9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E39" s="9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F39" s="9" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="G39" s="9" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B40" s="9" t="inlineStr">
-        <is>
-          <t>s18_food_fertilizer</t>
-        </is>
-      </c>
-      <c r="C40" s="9" t="inlineStr">
-        <is>
-          <t>Food &amp; fertilizer fragility</t>
-        </is>
-      </c>
-      <c r="D40" s="9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E40" s="9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F40" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G40" s="9" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B41" s="9" t="inlineStr">
-        <is>
-          <t>s19_lithography</t>
-        </is>
-      </c>
-      <c r="C41" s="9" t="inlineStr">
-        <is>
-          <t>The lithography (ASML) chokepoint</t>
-        </is>
-      </c>
-      <c r="D41" s="9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E41" s="9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F41" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G41" s="9" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B42" s="9" t="inlineStr">
-        <is>
-          <t>s20_sea_lanes</t>
-        </is>
-      </c>
-      <c r="C42" s="9" t="inlineStr">
-        <is>
-          <t>Sea lanes &amp; undersea cables</t>
-        </is>
-      </c>
-      <c r="D42" s="9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E42" s="9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F42" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G42" s="9" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B43" s="9" t="inlineStr">
-        <is>
-          <t>s21_clearinghouses</t>
-        </is>
-      </c>
-      <c r="C43" s="9" t="inlineStr">
-        <is>
-          <t>Clearinghouses (financial chokepoint)</t>
-        </is>
-      </c>
-      <c r="D43" s="9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E43" s="9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F43" s="9" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="G43" s="9" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6839,7 +6062,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A24"/>
+  <dimension ref="A1:A15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -6927,65 +6150,14 @@
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>**HEADLINE**</t>
+          <t>As of 2026-06-28: overall risk 5.0/10 (Set 1 5.3/10, Set 2 4.6/10, Set 3 5.1/10).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>Macro risk stable at 5.0/10, with 14 stories in Elevated band; one infrastructure risk eased.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="12" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>**LEVEL CHANGES**</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
-          <t>• **Sea lanes &amp; undersea cables** (7→6): WTI crude fell 50¢ to $69.23/bbl, reducing energy-transit pressure but leaving critical chokepoint risk material.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="12" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
-          <t>**ELEVATED RISKS TO MONITOR**</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>Japan fiscal/JGB/carry trade, China's exported deflation, critical minerals weaponization, AI build-out financing, and food/fertilizer fragility all at level 6.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="12" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>**WATCH**</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="12" t="inlineStr">
-        <is>
-          <t>Japan fiscal/JGB/carry trade (level 6) remains the highest-risk story given interlinkage with global funding conditions.</t>
+          <t>No story changed level versus the previous run. Daily market indicators moved within their current bands.</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Indicators" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily Log" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Indicators" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Daily Log" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Methodology" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-06-28  -  generated 2026-06-28 18:06 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-06-28  -  generated 2026-06-28 18:16 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1430,7 @@
         </is>
       </c>
       <c r="D3" s="7" t="n">
-        <v>96</v>
+        <v>66.79000000000001</v>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O3" s="8" t="inlineStr">
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>156</v>
+        <v>161.685</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O5" s="8" t="inlineStr">
@@ -2190,7 +2190,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>7.2</v>
+        <v>6.7975</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O15" s="8" t="inlineStr"/>
@@ -3373,7 +3373,7 @@
         </is>
       </c>
       <c r="D34" s="7" t="n">
-        <v>4300</v>
+        <v>4096.2998</v>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
       </c>
       <c r="N34" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O34" s="8" t="inlineStr">
@@ -4117,7 +4117,7 @@
         </is>
       </c>
       <c r="D46" s="7" t="n">
-        <v>5.4</v>
+        <v>6.207</v>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
       </c>
       <c r="N46" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O46" s="8" t="inlineStr">
@@ -4926,7 +4926,7 @@
         </is>
       </c>
       <c r="D59" s="7" t="n">
-        <v>95</v>
+        <v>69.23</v>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
@@ -4965,7 +4965,7 @@
       </c>
       <c r="N59" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O59" s="8" t="inlineStr"/>
@@ -5048,7 +5048,7 @@
         </is>
       </c>
       <c r="D61" s="7" t="n">
-        <v>17</v>
+        <v>18.41</v>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="N61" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O61" s="8" t="inlineStr"/>
@@ -5109,7 +5109,7 @@
         </is>
       </c>
       <c r="D62" s="7" t="n">
-        <v>96</v>
+        <v>66.79000000000001</v>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="N62" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O62" s="8" t="inlineStr"/>
@@ -5225,7 +5225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6051,6 +6051,783 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>s1_basis_trade</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>Treasury basis trade (hidden leverage)</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G23" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>s2_japan</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>Japan fiscal / JGB / carry trade</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G24" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>s3_private_credit</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>Private credit's opaque expansion</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F25" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G25" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>s4_dev_debt</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>Developing-world debt crisis</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F26" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G26" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>s5_china_deflation</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>China's exported deflation</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F27" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G27" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>s6_rare_earths</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>Critical minerals as a weapon</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F28" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G28" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>s7_stablecoins</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>Stablecoins &amp; Treasury demand</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F29" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G29" s="9" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>s8_ai_capex</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>AI build-out circular financing</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F30" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G30" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>s9_cre</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>CRE maturity wall / regional banks</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E31" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F31" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G31" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>s10_france</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>France / eurozone fragility</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F32" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G32" s="9" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>s11_consumer_debt</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>Hidden consumer debt</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F33" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G33" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>s12_gold_dedollar</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>Gold / de-dollarization</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F34" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G34" s="9" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>s13_insurance</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>Insurance retreat</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F35" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G35" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>s14_pensions</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>Pensions / demographics</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F36" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G36" s="9" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>s15_ai_power</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>AI power &amp; the grid bottleneck</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F37" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G37" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>s16_copper</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>Copper &amp; the electrification deficit</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F38" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G38" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>s17_water</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>Water - the underpriced input</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E39" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F39" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G39" s="9" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>s18_food_fertilizer</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>Food &amp; fertilizer fragility</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F40" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G40" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>s19_lithography</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>The lithography (ASML) chokepoint</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E41" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F41" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G41" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>s20_sea_lanes</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>Sea lanes &amp; undersea cables</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F42" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G42" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>s21_clearinghouses</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>Clearinghouses (financial chokepoint)</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F43" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G43" s="9" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6062,7 +6839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -6150,14 +6927,65 @@
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>As of 2026-06-28: overall risk 5.0/10 (Set 1 5.3/10, Set 2 4.6/10, Set 3 5.1/10).</t>
+          <t>**HEADLINE**</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>No story changed level versus the previous run. Daily market indicators moved within their current bands.</t>
+          <t>Overall macro risk stable at 5.0, with 14 elevated or higher risks persisting across financial, supply chain, and geopolitical domains.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>**LEVEL CHANGES**</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>• **Sea lanes &amp; undersea cables** (7→6, Elevated): WTI crude fell 50 cents to $69.23/bbl, reducing energy-driven shipping pressure but infrastructure vulnerability remains amid geopolitical tensions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>**ELEVATED RISKS TO MONITOR**</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>Fourteen stories remain at Elevated or higher: Japan's carry-trade exposure (6), China's deflationary exports (6), critical minerals weaponization (6), AI circular financing (6), grid bottleneck (6), food fragility (6); plus Treasury basis leverage, private credit opacity, developing-world debt, CRE maturity wall, hidden consumer debt, insurance retreat, and lithography chokepoints (all 5).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>**WATCH CLOSEST**</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>Japan fiscal/JGB/carry trade (6): largest single tail risk for sudden deleveraging shock.</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Indicators" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Daily Log" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Methodology" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Indicators" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily Log" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-06-28  -  generated 2026-06-28 18:16 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-06-28  -  generated 2026-06-28 18:36 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1430,7 @@
         </is>
       </c>
       <c r="D3" s="7" t="n">
-        <v>66.79000000000001</v>
+        <v>96</v>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O3" s="8" t="inlineStr">
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>161.685</v>
+        <v>156</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O5" s="8" t="inlineStr">
@@ -2190,7 +2190,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>6.7975</v>
+        <v>7.2</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O15" s="8" t="inlineStr"/>
@@ -3373,7 +3373,7 @@
         </is>
       </c>
       <c r="D34" s="7" t="n">
-        <v>4096.2998</v>
+        <v>4300</v>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
       </c>
       <c r="N34" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O34" s="8" t="inlineStr">
@@ -4117,7 +4117,7 @@
         </is>
       </c>
       <c r="D46" s="7" t="n">
-        <v>6.207</v>
+        <v>5.4</v>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
       </c>
       <c r="N46" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O46" s="8" t="inlineStr">
@@ -4926,7 +4926,7 @@
         </is>
       </c>
       <c r="D59" s="7" t="n">
-        <v>69.23</v>
+        <v>95</v>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
@@ -4965,7 +4965,7 @@
       </c>
       <c r="N59" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O59" s="8" t="inlineStr"/>
@@ -5048,7 +5048,7 @@
         </is>
       </c>
       <c r="D61" s="7" t="n">
-        <v>18.41</v>
+        <v>17</v>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="N61" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O61" s="8" t="inlineStr"/>
@@ -5109,7 +5109,7 @@
         </is>
       </c>
       <c r="D62" s="7" t="n">
-        <v>66.79000000000001</v>
+        <v>96</v>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="N62" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O62" s="8" t="inlineStr"/>
@@ -5225,7 +5225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6051,783 +6051,6 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B23" s="9" t="inlineStr">
-        <is>
-          <t>s1_basis_trade</t>
-        </is>
-      </c>
-      <c r="C23" s="9" t="inlineStr">
-        <is>
-          <t>Treasury basis trade (hidden leverage)</t>
-        </is>
-      </c>
-      <c r="D23" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E23" s="9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F23" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G23" s="9" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B24" s="9" t="inlineStr">
-        <is>
-          <t>s2_japan</t>
-        </is>
-      </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>Japan fiscal / JGB / carry trade</t>
-        </is>
-      </c>
-      <c r="D24" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E24" s="9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F24" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G24" s="9" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B25" s="9" t="inlineStr">
-        <is>
-          <t>s3_private_credit</t>
-        </is>
-      </c>
-      <c r="C25" s="9" t="inlineStr">
-        <is>
-          <t>Private credit's opaque expansion</t>
-        </is>
-      </c>
-      <c r="D25" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E25" s="9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F25" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G25" s="9" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B26" s="9" t="inlineStr">
-        <is>
-          <t>s4_dev_debt</t>
-        </is>
-      </c>
-      <c r="C26" s="9" t="inlineStr">
-        <is>
-          <t>Developing-world debt crisis</t>
-        </is>
-      </c>
-      <c r="D26" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E26" s="9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F26" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G26" s="9" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B27" s="9" t="inlineStr">
-        <is>
-          <t>s5_china_deflation</t>
-        </is>
-      </c>
-      <c r="C27" s="9" t="inlineStr">
-        <is>
-          <t>China's exported deflation</t>
-        </is>
-      </c>
-      <c r="D27" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E27" s="9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F27" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G27" s="9" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B28" s="9" t="inlineStr">
-        <is>
-          <t>s6_rare_earths</t>
-        </is>
-      </c>
-      <c r="C28" s="9" t="inlineStr">
-        <is>
-          <t>Critical minerals as a weapon</t>
-        </is>
-      </c>
-      <c r="D28" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E28" s="9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F28" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G28" s="9" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B29" s="9" t="inlineStr">
-        <is>
-          <t>s7_stablecoins</t>
-        </is>
-      </c>
-      <c r="C29" s="9" t="inlineStr">
-        <is>
-          <t>Stablecoins &amp; Treasury demand</t>
-        </is>
-      </c>
-      <c r="D29" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E29" s="9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F29" s="9" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="G29" s="9" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B30" s="9" t="inlineStr">
-        <is>
-          <t>s8_ai_capex</t>
-        </is>
-      </c>
-      <c r="C30" s="9" t="inlineStr">
-        <is>
-          <t>AI build-out circular financing</t>
-        </is>
-      </c>
-      <c r="D30" s="9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E30" s="9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F30" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G30" s="9" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B31" s="9" t="inlineStr">
-        <is>
-          <t>s9_cre</t>
-        </is>
-      </c>
-      <c r="C31" s="9" t="inlineStr">
-        <is>
-          <t>CRE maturity wall / regional banks</t>
-        </is>
-      </c>
-      <c r="D31" s="9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E31" s="9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F31" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G31" s="9" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B32" s="9" t="inlineStr">
-        <is>
-          <t>s10_france</t>
-        </is>
-      </c>
-      <c r="C32" s="9" t="inlineStr">
-        <is>
-          <t>France / eurozone fragility</t>
-        </is>
-      </c>
-      <c r="D32" s="9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E32" s="9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F32" s="9" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="G32" s="9" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B33" s="9" t="inlineStr">
-        <is>
-          <t>s11_consumer_debt</t>
-        </is>
-      </c>
-      <c r="C33" s="9" t="inlineStr">
-        <is>
-          <t>Hidden consumer debt</t>
-        </is>
-      </c>
-      <c r="D33" s="9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E33" s="9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F33" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G33" s="9" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B34" s="9" t="inlineStr">
-        <is>
-          <t>s12_gold_dedollar</t>
-        </is>
-      </c>
-      <c r="C34" s="9" t="inlineStr">
-        <is>
-          <t>Gold / de-dollarization</t>
-        </is>
-      </c>
-      <c r="D34" s="9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E34" s="9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F34" s="9" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="G34" s="9" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B35" s="9" t="inlineStr">
-        <is>
-          <t>s13_insurance</t>
-        </is>
-      </c>
-      <c r="C35" s="9" t="inlineStr">
-        <is>
-          <t>Insurance retreat</t>
-        </is>
-      </c>
-      <c r="D35" s="9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E35" s="9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F35" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G35" s="9" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B36" s="9" t="inlineStr">
-        <is>
-          <t>s14_pensions</t>
-        </is>
-      </c>
-      <c r="C36" s="9" t="inlineStr">
-        <is>
-          <t>Pensions / demographics</t>
-        </is>
-      </c>
-      <c r="D36" s="9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E36" s="9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F36" s="9" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="G36" s="9" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B37" s="9" t="inlineStr">
-        <is>
-          <t>s15_ai_power</t>
-        </is>
-      </c>
-      <c r="C37" s="9" t="inlineStr">
-        <is>
-          <t>AI power &amp; the grid bottleneck</t>
-        </is>
-      </c>
-      <c r="D37" s="9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E37" s="9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F37" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G37" s="9" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B38" s="9" t="inlineStr">
-        <is>
-          <t>s16_copper</t>
-        </is>
-      </c>
-      <c r="C38" s="9" t="inlineStr">
-        <is>
-          <t>Copper &amp; the electrification deficit</t>
-        </is>
-      </c>
-      <c r="D38" s="9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E38" s="9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F38" s="9" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="G38" s="9" t="inlineStr">
-        <is>
-          <t>4.25</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B39" s="9" t="inlineStr">
-        <is>
-          <t>s17_water</t>
-        </is>
-      </c>
-      <c r="C39" s="9" t="inlineStr">
-        <is>
-          <t>Water - the underpriced input</t>
-        </is>
-      </c>
-      <c r="D39" s="9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E39" s="9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F39" s="9" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="G39" s="9" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B40" s="9" t="inlineStr">
-        <is>
-          <t>s18_food_fertilizer</t>
-        </is>
-      </c>
-      <c r="C40" s="9" t="inlineStr">
-        <is>
-          <t>Food &amp; fertilizer fragility</t>
-        </is>
-      </c>
-      <c r="D40" s="9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E40" s="9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F40" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G40" s="9" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B41" s="9" t="inlineStr">
-        <is>
-          <t>s19_lithography</t>
-        </is>
-      </c>
-      <c r="C41" s="9" t="inlineStr">
-        <is>
-          <t>The lithography (ASML) chokepoint</t>
-        </is>
-      </c>
-      <c r="D41" s="9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E41" s="9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F41" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G41" s="9" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B42" s="9" t="inlineStr">
-        <is>
-          <t>s20_sea_lanes</t>
-        </is>
-      </c>
-      <c r="C42" s="9" t="inlineStr">
-        <is>
-          <t>Sea lanes &amp; undersea cables</t>
-        </is>
-      </c>
-      <c r="D42" s="9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E42" s="9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F42" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G42" s="9" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B43" s="9" t="inlineStr">
-        <is>
-          <t>s21_clearinghouses</t>
-        </is>
-      </c>
-      <c r="C43" s="9" t="inlineStr">
-        <is>
-          <t>Clearinghouses (financial chokepoint)</t>
-        </is>
-      </c>
-      <c r="D43" s="9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E43" s="9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F43" s="9" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="G43" s="9" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6839,7 +6062,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A24"/>
+  <dimension ref="A1:A15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -6927,65 +6150,14 @@
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>**HEADLINE**</t>
+          <t>As of 2026-06-28: overall risk 5.0/10 (Set 1 5.3/10, Set 2 4.6/10, Set 3 5.1/10).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>Overall macro risk stable at 5.0, with 14 elevated or higher risks persisting across financial, supply chain, and geopolitical domains.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="12" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>**LEVEL CHANGES**</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
-          <t>• **Sea lanes &amp; undersea cables** (7→6, Elevated): WTI crude fell 50 cents to $69.23/bbl, reducing energy-driven shipping pressure but infrastructure vulnerability remains amid geopolitical tensions.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="12" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
-          <t>**ELEVATED RISKS TO MONITOR**</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>Fourteen stories remain at Elevated or higher: Japan's carry-trade exposure (6), China's deflationary exports (6), critical minerals weaponization (6), AI circular financing (6), grid bottleneck (6), food fragility (6); plus Treasury basis leverage, private credit opacity, developing-world debt, CRE maturity wall, hidden consumer debt, insurance retreat, and lithography chokepoints (all 5).</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="12" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>**WATCH CLOSEST**</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="12" t="inlineStr">
-        <is>
-          <t>Japan fiscal/JGB/carry trade (6): largest single tail risk for sudden deleveraging shock.</t>
+          <t>No story changed level versus the previous run. Daily market indicators moved within their current bands.</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Indicators" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily Log" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Indicators" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Daily Log" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Methodology" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-06-28  -  generated 2026-06-28 18:36 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-06-28  -  generated 2026-06-28 18:46 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1430,7 @@
         </is>
       </c>
       <c r="D3" s="7" t="n">
-        <v>96</v>
+        <v>66.79000000000001</v>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O3" s="8" t="inlineStr">
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>156</v>
+        <v>161.685</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O5" s="8" t="inlineStr">
@@ -2190,7 +2190,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>7.2</v>
+        <v>6.7975</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O15" s="8" t="inlineStr"/>
@@ -3373,7 +3373,7 @@
         </is>
       </c>
       <c r="D34" s="7" t="n">
-        <v>4300</v>
+        <v>4096.2998</v>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
       </c>
       <c r="N34" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O34" s="8" t="inlineStr">
@@ -4117,7 +4117,7 @@
         </is>
       </c>
       <c r="D46" s="7" t="n">
-        <v>5.4</v>
+        <v>6.207</v>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
       </c>
       <c r="N46" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O46" s="8" t="inlineStr">
@@ -4926,7 +4926,7 @@
         </is>
       </c>
       <c r="D59" s="7" t="n">
-        <v>95</v>
+        <v>69.23</v>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
@@ -4965,7 +4965,7 @@
       </c>
       <c r="N59" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O59" s="8" t="inlineStr"/>
@@ -5048,7 +5048,7 @@
         </is>
       </c>
       <c r="D61" s="7" t="n">
-        <v>17</v>
+        <v>18.41</v>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="N61" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O61" s="8" t="inlineStr"/>
@@ -5109,7 +5109,7 @@
         </is>
       </c>
       <c r="D62" s="7" t="n">
-        <v>96</v>
+        <v>66.79000000000001</v>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="N62" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O62" s="8" t="inlineStr"/>
@@ -5225,7 +5225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6051,6 +6051,783 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>s1_basis_trade</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>Treasury basis trade (hidden leverage)</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G23" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>s2_japan</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>Japan fiscal / JGB / carry trade</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G24" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>s3_private_credit</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>Private credit's opaque expansion</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F25" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G25" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>s4_dev_debt</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>Developing-world debt crisis</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F26" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G26" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>s5_china_deflation</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>China's exported deflation</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F27" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G27" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>s6_rare_earths</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>Critical minerals as a weapon</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F28" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G28" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>s7_stablecoins</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>Stablecoins &amp; Treasury demand</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F29" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G29" s="9" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>s8_ai_capex</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>AI build-out circular financing</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F30" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G30" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>s9_cre</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>CRE maturity wall / regional banks</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E31" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F31" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G31" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>s10_france</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>France / eurozone fragility</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F32" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G32" s="9" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>s11_consumer_debt</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>Hidden consumer debt</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F33" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G33" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>s12_gold_dedollar</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>Gold / de-dollarization</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F34" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G34" s="9" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>s13_insurance</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>Insurance retreat</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F35" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G35" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>s14_pensions</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>Pensions / demographics</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F36" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G36" s="9" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>s15_ai_power</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>AI power &amp; the grid bottleneck</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F37" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G37" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>s16_copper</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>Copper &amp; the electrification deficit</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F38" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G38" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>s17_water</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>Water - the underpriced input</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E39" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F39" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G39" s="9" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>s18_food_fertilizer</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>Food &amp; fertilizer fragility</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F40" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G40" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>s19_lithography</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>The lithography (ASML) chokepoint</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E41" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F41" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G41" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>s20_sea_lanes</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>Sea lanes &amp; undersea cables</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F42" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G42" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>s21_clearinghouses</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>Clearinghouses (financial chokepoint)</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F43" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G43" s="9" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6062,7 +6839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -6150,14 +6927,65 @@
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>As of 2026-06-28: overall risk 5.0/10 (Set 1 5.3/10, Set 2 4.6/10, Set 3 5.1/10).</t>
+          <t>**HEADLINE**</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>No story changed level versus the previous run. Daily market indicators moved within their current bands.</t>
+          <t>Macro risk stable at 5.0 overall; sea-lane vulnerability eased but 14 elevated risks remain concentrated in financial leverage, supply-chain chokepoints, and geopolitical leverage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>**LEVEL CHANGES**</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>• **Sea lanes &amp; undersea cables** (7→6): WTI crude fell to $69.23/bbl, reducing energy-security urgency and shipping-cost pressure; cables remain exposed to interdiction and sabotage during tension.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>**ELEVATED RISKS (14 active)**</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>Nine risks hold at level 5–6 across financial (Treasury basis trades, JGB carry, private credit opacity, CRE maturity wall, hidden consumer debt, insurance retreat), supply (lithography, critical minerals, food &amp; fertilizer), and structural (China deflation, AI circular financing, AI power grid strain, developing-world debt).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>**WATCH**</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>Japan fiscal/JGB/carry trade (6) and China exported deflation (6) remain highest-risk due to structural leverage and deflationary feedback loops.</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Indicators" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Daily Log" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Methodology" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Indicators" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily Log" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-06-28  -  generated 2026-06-28 18:46 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-06-29  -  generated 2026-06-29 09:20 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1430,7 @@
         </is>
       </c>
       <c r="D3" s="7" t="n">
-        <v>66.79000000000001</v>
+        <v>96</v>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O3" s="8" t="inlineStr">
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>161.685</v>
+        <v>156</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O5" s="8" t="inlineStr">
@@ -2190,7 +2190,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>6.7975</v>
+        <v>7.2</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O15" s="8" t="inlineStr"/>
@@ -3373,7 +3373,7 @@
         </is>
       </c>
       <c r="D34" s="7" t="n">
-        <v>4096.2998</v>
+        <v>4300</v>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
       </c>
       <c r="N34" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O34" s="8" t="inlineStr">
@@ -4117,7 +4117,7 @@
         </is>
       </c>
       <c r="D46" s="7" t="n">
-        <v>6.207</v>
+        <v>5.4</v>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
       </c>
       <c r="N46" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O46" s="8" t="inlineStr">
@@ -4926,7 +4926,7 @@
         </is>
       </c>
       <c r="D59" s="7" t="n">
-        <v>69.23</v>
+        <v>95</v>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
@@ -4965,7 +4965,7 @@
       </c>
       <c r="N59" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O59" s="8" t="inlineStr"/>
@@ -5048,7 +5048,7 @@
         </is>
       </c>
       <c r="D61" s="7" t="n">
-        <v>18.41</v>
+        <v>17</v>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="N61" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O61" s="8" t="inlineStr"/>
@@ -5109,7 +5109,7 @@
         </is>
       </c>
       <c r="D62" s="7" t="n">
-        <v>66.79000000000001</v>
+        <v>96</v>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="N62" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O62" s="8" t="inlineStr"/>
@@ -5225,7 +5225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5277,7 +5277,7 @@
     <row r="2">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B2" s="9" t="inlineStr">
@@ -5314,7 +5314,7 @@
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B3" s="9" t="inlineStr">
@@ -5351,7 +5351,7 @@
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B4" s="9" t="inlineStr">
@@ -5388,7 +5388,7 @@
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B5" s="9" t="inlineStr">
@@ -5425,7 +5425,7 @@
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
@@ -5462,7 +5462,7 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
@@ -5499,7 +5499,7 @@
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
@@ -5536,7 +5536,7 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
@@ -5573,7 +5573,7 @@
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
@@ -5610,7 +5610,7 @@
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
@@ -5647,7 +5647,7 @@
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
@@ -5684,7 +5684,7 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B13" s="9" t="inlineStr">
@@ -5721,7 +5721,7 @@
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
@@ -5758,7 +5758,7 @@
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B15" s="9" t="inlineStr">
@@ -5795,7 +5795,7 @@
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
@@ -5832,7 +5832,7 @@
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
@@ -5869,7 +5869,7 @@
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
@@ -5906,7 +5906,7 @@
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
@@ -5943,7 +5943,7 @@
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
@@ -5980,7 +5980,7 @@
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
@@ -6017,7 +6017,7 @@
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B22" s="9" t="inlineStr">
@@ -6046,783 +6046,6 @@
         </is>
       </c>
       <c r="G22" s="9" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B23" s="9" t="inlineStr">
-        <is>
-          <t>s1_basis_trade</t>
-        </is>
-      </c>
-      <c r="C23" s="9" t="inlineStr">
-        <is>
-          <t>Treasury basis trade (hidden leverage)</t>
-        </is>
-      </c>
-      <c r="D23" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E23" s="9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F23" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G23" s="9" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B24" s="9" t="inlineStr">
-        <is>
-          <t>s2_japan</t>
-        </is>
-      </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>Japan fiscal / JGB / carry trade</t>
-        </is>
-      </c>
-      <c r="D24" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E24" s="9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F24" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G24" s="9" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B25" s="9" t="inlineStr">
-        <is>
-          <t>s3_private_credit</t>
-        </is>
-      </c>
-      <c r="C25" s="9" t="inlineStr">
-        <is>
-          <t>Private credit's opaque expansion</t>
-        </is>
-      </c>
-      <c r="D25" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E25" s="9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F25" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G25" s="9" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B26" s="9" t="inlineStr">
-        <is>
-          <t>s4_dev_debt</t>
-        </is>
-      </c>
-      <c r="C26" s="9" t="inlineStr">
-        <is>
-          <t>Developing-world debt crisis</t>
-        </is>
-      </c>
-      <c r="D26" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E26" s="9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F26" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G26" s="9" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B27" s="9" t="inlineStr">
-        <is>
-          <t>s5_china_deflation</t>
-        </is>
-      </c>
-      <c r="C27" s="9" t="inlineStr">
-        <is>
-          <t>China's exported deflation</t>
-        </is>
-      </c>
-      <c r="D27" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E27" s="9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F27" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G27" s="9" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B28" s="9" t="inlineStr">
-        <is>
-          <t>s6_rare_earths</t>
-        </is>
-      </c>
-      <c r="C28" s="9" t="inlineStr">
-        <is>
-          <t>Critical minerals as a weapon</t>
-        </is>
-      </c>
-      <c r="D28" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E28" s="9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F28" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G28" s="9" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B29" s="9" t="inlineStr">
-        <is>
-          <t>s7_stablecoins</t>
-        </is>
-      </c>
-      <c r="C29" s="9" t="inlineStr">
-        <is>
-          <t>Stablecoins &amp; Treasury demand</t>
-        </is>
-      </c>
-      <c r="D29" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E29" s="9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F29" s="9" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="G29" s="9" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B30" s="9" t="inlineStr">
-        <is>
-          <t>s8_ai_capex</t>
-        </is>
-      </c>
-      <c r="C30" s="9" t="inlineStr">
-        <is>
-          <t>AI build-out circular financing</t>
-        </is>
-      </c>
-      <c r="D30" s="9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E30" s="9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F30" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G30" s="9" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B31" s="9" t="inlineStr">
-        <is>
-          <t>s9_cre</t>
-        </is>
-      </c>
-      <c r="C31" s="9" t="inlineStr">
-        <is>
-          <t>CRE maturity wall / regional banks</t>
-        </is>
-      </c>
-      <c r="D31" s="9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E31" s="9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F31" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G31" s="9" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B32" s="9" t="inlineStr">
-        <is>
-          <t>s10_france</t>
-        </is>
-      </c>
-      <c r="C32" s="9" t="inlineStr">
-        <is>
-          <t>France / eurozone fragility</t>
-        </is>
-      </c>
-      <c r="D32" s="9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E32" s="9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F32" s="9" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="G32" s="9" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B33" s="9" t="inlineStr">
-        <is>
-          <t>s11_consumer_debt</t>
-        </is>
-      </c>
-      <c r="C33" s="9" t="inlineStr">
-        <is>
-          <t>Hidden consumer debt</t>
-        </is>
-      </c>
-      <c r="D33" s="9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E33" s="9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F33" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G33" s="9" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B34" s="9" t="inlineStr">
-        <is>
-          <t>s12_gold_dedollar</t>
-        </is>
-      </c>
-      <c r="C34" s="9" t="inlineStr">
-        <is>
-          <t>Gold / de-dollarization</t>
-        </is>
-      </c>
-      <c r="D34" s="9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E34" s="9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F34" s="9" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="G34" s="9" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B35" s="9" t="inlineStr">
-        <is>
-          <t>s13_insurance</t>
-        </is>
-      </c>
-      <c r="C35" s="9" t="inlineStr">
-        <is>
-          <t>Insurance retreat</t>
-        </is>
-      </c>
-      <c r="D35" s="9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E35" s="9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F35" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G35" s="9" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B36" s="9" t="inlineStr">
-        <is>
-          <t>s14_pensions</t>
-        </is>
-      </c>
-      <c r="C36" s="9" t="inlineStr">
-        <is>
-          <t>Pensions / demographics</t>
-        </is>
-      </c>
-      <c r="D36" s="9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E36" s="9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F36" s="9" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="G36" s="9" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B37" s="9" t="inlineStr">
-        <is>
-          <t>s15_ai_power</t>
-        </is>
-      </c>
-      <c r="C37" s="9" t="inlineStr">
-        <is>
-          <t>AI power &amp; the grid bottleneck</t>
-        </is>
-      </c>
-      <c r="D37" s="9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E37" s="9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F37" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G37" s="9" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B38" s="9" t="inlineStr">
-        <is>
-          <t>s16_copper</t>
-        </is>
-      </c>
-      <c r="C38" s="9" t="inlineStr">
-        <is>
-          <t>Copper &amp; the electrification deficit</t>
-        </is>
-      </c>
-      <c r="D38" s="9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E38" s="9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F38" s="9" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="G38" s="9" t="inlineStr">
-        <is>
-          <t>4.25</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B39" s="9" t="inlineStr">
-        <is>
-          <t>s17_water</t>
-        </is>
-      </c>
-      <c r="C39" s="9" t="inlineStr">
-        <is>
-          <t>Water - the underpriced input</t>
-        </is>
-      </c>
-      <c r="D39" s="9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E39" s="9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F39" s="9" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="G39" s="9" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B40" s="9" t="inlineStr">
-        <is>
-          <t>s18_food_fertilizer</t>
-        </is>
-      </c>
-      <c r="C40" s="9" t="inlineStr">
-        <is>
-          <t>Food &amp; fertilizer fragility</t>
-        </is>
-      </c>
-      <c r="D40" s="9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E40" s="9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F40" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G40" s="9" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B41" s="9" t="inlineStr">
-        <is>
-          <t>s19_lithography</t>
-        </is>
-      </c>
-      <c r="C41" s="9" t="inlineStr">
-        <is>
-          <t>The lithography (ASML) chokepoint</t>
-        </is>
-      </c>
-      <c r="D41" s="9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E41" s="9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F41" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G41" s="9" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B42" s="9" t="inlineStr">
-        <is>
-          <t>s20_sea_lanes</t>
-        </is>
-      </c>
-      <c r="C42" s="9" t="inlineStr">
-        <is>
-          <t>Sea lanes &amp; undersea cables</t>
-        </is>
-      </c>
-      <c r="D42" s="9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E42" s="9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F42" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G42" s="9" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B43" s="9" t="inlineStr">
-        <is>
-          <t>s21_clearinghouses</t>
-        </is>
-      </c>
-      <c r="C43" s="9" t="inlineStr">
-        <is>
-          <t>Clearinghouses (financial chokepoint)</t>
-        </is>
-      </c>
-      <c r="D43" s="9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E43" s="9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F43" s="9" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="G43" s="9" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
@@ -6839,7 +6062,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A24"/>
+  <dimension ref="A1:A15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -6920,72 +6143,21 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>--- Daily narrative (2026-06-28) ---</t>
+          <t>--- Daily narrative (2026-06-29) ---</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>**HEADLINE**</t>
+          <t>As of 2026-06-29: overall risk 5.0/10 (Set 1 5.3/10, Set 2 4.6/10, Set 3 5.1/10).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>Macro risk stable at 5.0 overall; sea-lane vulnerability eased but 14 elevated risks remain concentrated in financial leverage, supply-chain chokepoints, and geopolitical leverage.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="12" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>**LEVEL CHANGES**</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
-          <t>• **Sea lanes &amp; undersea cables** (7→6): WTI crude fell to $69.23/bbl, reducing energy-security urgency and shipping-cost pressure; cables remain exposed to interdiction and sabotage during tension.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="12" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
-          <t>**ELEVATED RISKS (14 active)**</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>Nine risks hold at level 5–6 across financial (Treasury basis trades, JGB carry, private credit opacity, CRE maturity wall, hidden consumer debt, insurance retreat), supply (lithography, critical minerals, food &amp; fertilizer), and structural (China deflation, AI circular financing, AI power grid strain, developing-world debt).</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="12" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>**WATCH**</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="12" t="inlineStr">
-        <is>
-          <t>Japan fiscal/JGB/carry trade (6) and China exported deflation (6) remain highest-risk due to structural leverage and deflationary feedback loops.</t>
+          <t>No story changed level versus the previous run. Daily market indicators moved within their current bands.</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Indicators" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily Log" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Indicators" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Daily Log" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Methodology" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-06-29  -  generated 2026-06-29 09:20 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-06-29  -  generated 2026-06-29 09:27 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1430,7 @@
         </is>
       </c>
       <c r="D3" s="7" t="n">
-        <v>96</v>
+        <v>66.79000000000001</v>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O3" s="8" t="inlineStr">
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>156</v>
+        <v>161.87</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O5" s="8" t="inlineStr">
@@ -2190,7 +2190,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>7.2</v>
+        <v>6.7928</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O15" s="8" t="inlineStr"/>
@@ -3373,7 +3373,7 @@
         </is>
       </c>
       <c r="D34" s="7" t="n">
-        <v>4300</v>
+        <v>4064.3999</v>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
       </c>
       <c r="N34" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O34" s="8" t="inlineStr">
@@ -4117,7 +4117,7 @@
         </is>
       </c>
       <c r="D46" s="7" t="n">
-        <v>5.4</v>
+        <v>6.18</v>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
       </c>
       <c r="N46" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O46" s="8" t="inlineStr">
@@ -4926,7 +4926,7 @@
         </is>
       </c>
       <c r="D59" s="7" t="n">
-        <v>95</v>
+        <v>69.95999999999999</v>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
@@ -4965,7 +4965,7 @@
       </c>
       <c r="N59" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O59" s="8" t="inlineStr"/>
@@ -5048,7 +5048,7 @@
         </is>
       </c>
       <c r="D61" s="7" t="n">
-        <v>17</v>
+        <v>18.46</v>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="N61" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O61" s="8" t="inlineStr"/>
@@ -5109,7 +5109,7 @@
         </is>
       </c>
       <c r="D62" s="7" t="n">
-        <v>96</v>
+        <v>66.79000000000001</v>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="N62" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O62" s="8" t="inlineStr"/>
@@ -5225,7 +5225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6051,6 +6051,783 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>s1_basis_trade</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>Treasury basis trade (hidden leverage)</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G23" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>s2_japan</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>Japan fiscal / JGB / carry trade</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G24" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>s3_private_credit</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>Private credit's opaque expansion</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F25" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G25" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>s4_dev_debt</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>Developing-world debt crisis</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F26" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G26" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>s5_china_deflation</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>China's exported deflation</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F27" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G27" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>s6_rare_earths</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>Critical minerals as a weapon</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F28" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G28" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>s7_stablecoins</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>Stablecoins &amp; Treasury demand</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F29" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G29" s="9" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>s8_ai_capex</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>AI build-out circular financing</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F30" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G30" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>s9_cre</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>CRE maturity wall / regional banks</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E31" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F31" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G31" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>s10_france</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>France / eurozone fragility</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F32" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G32" s="9" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>s11_consumer_debt</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>Hidden consumer debt</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F33" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G33" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>s12_gold_dedollar</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>Gold / de-dollarization</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F34" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G34" s="9" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>s13_insurance</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>Insurance retreat</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F35" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G35" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>s14_pensions</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>Pensions / demographics</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F36" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G36" s="9" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>s15_ai_power</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>AI power &amp; the grid bottleneck</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F37" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G37" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>s16_copper</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>Copper &amp; the electrification deficit</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F38" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G38" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>s17_water</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>Water - the underpriced input</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E39" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F39" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G39" s="9" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>s18_food_fertilizer</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>Food &amp; fertilizer fragility</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F40" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G40" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>s19_lithography</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>The lithography (ASML) chokepoint</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E41" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F41" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G41" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>s20_sea_lanes</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>Sea lanes &amp; undersea cables</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F42" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G42" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>s21_clearinghouses</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>Clearinghouses (financial chokepoint)</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F43" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G43" s="9" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6062,7 +6839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -6150,14 +6927,37 @@
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>As of 2026-06-29: overall risk 5.0/10 (Set 1 5.3/10, Set 2 4.6/10, Set 3 5.1/10).</t>
+          <t># EOD MACRO-RISK BRIEF | 29 JUN 2026</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>No story changed level versus the previous run. Daily market indicators moved within their current bands.</t>
+      <c r="A15" s="12" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>**Overall risk stable at 5.0, but 14 Elevated-level stories remain embedded across financial, commodity, and infrastructure domains.**</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>• **Sea lanes &amp; undersea cables** declined from 7 to 6 (Elevated) on WTI crude falling to $69.96/bbl, easing shipping-cost pressure but leaving geopolitical infrastructure vulnerability intact.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>**Highest priority:** Japan fiscal/JGB/carry trade and China's exported deflation both at level 6—synchronized deflationary export pressure and BoJ policy constraints pose correlated shock risk to global rates and FX stability.</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Indicators" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Daily Log" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Methodology" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Indicators" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily Log" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-06-29  -  generated 2026-06-29 09:27 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-06-29  -  generated 2026-06-29 10:10 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1430,7 @@
         </is>
       </c>
       <c r="D3" s="7" t="n">
-        <v>66.79000000000001</v>
+        <v>96</v>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O3" s="8" t="inlineStr">
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>161.87</v>
+        <v>156</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O5" s="8" t="inlineStr">
@@ -2190,7 +2190,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>6.7928</v>
+        <v>7.2</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O15" s="8" t="inlineStr"/>
@@ -3373,7 +3373,7 @@
         </is>
       </c>
       <c r="D34" s="7" t="n">
-        <v>4064.3999</v>
+        <v>4300</v>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
       </c>
       <c r="N34" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O34" s="8" t="inlineStr">
@@ -4117,7 +4117,7 @@
         </is>
       </c>
       <c r="D46" s="7" t="n">
-        <v>6.18</v>
+        <v>5.4</v>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
       </c>
       <c r="N46" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O46" s="8" t="inlineStr">
@@ -4926,7 +4926,7 @@
         </is>
       </c>
       <c r="D59" s="7" t="n">
-        <v>69.95999999999999</v>
+        <v>95</v>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
@@ -4965,7 +4965,7 @@
       </c>
       <c r="N59" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O59" s="8" t="inlineStr"/>
@@ -5048,7 +5048,7 @@
         </is>
       </c>
       <c r="D61" s="7" t="n">
-        <v>18.46</v>
+        <v>17</v>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="N61" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O61" s="8" t="inlineStr"/>
@@ -5109,7 +5109,7 @@
         </is>
       </c>
       <c r="D62" s="7" t="n">
-        <v>66.79000000000001</v>
+        <v>96</v>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="N62" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O62" s="8" t="inlineStr"/>
@@ -5225,7 +5225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6051,783 +6051,6 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="B23" s="9" t="inlineStr">
-        <is>
-          <t>s1_basis_trade</t>
-        </is>
-      </c>
-      <c r="C23" s="9" t="inlineStr">
-        <is>
-          <t>Treasury basis trade (hidden leverage)</t>
-        </is>
-      </c>
-      <c r="D23" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E23" s="9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F23" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G23" s="9" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="B24" s="9" t="inlineStr">
-        <is>
-          <t>s2_japan</t>
-        </is>
-      </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>Japan fiscal / JGB / carry trade</t>
-        </is>
-      </c>
-      <c r="D24" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E24" s="9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F24" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G24" s="9" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="B25" s="9" t="inlineStr">
-        <is>
-          <t>s3_private_credit</t>
-        </is>
-      </c>
-      <c r="C25" s="9" t="inlineStr">
-        <is>
-          <t>Private credit's opaque expansion</t>
-        </is>
-      </c>
-      <c r="D25" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E25" s="9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F25" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G25" s="9" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="B26" s="9" t="inlineStr">
-        <is>
-          <t>s4_dev_debt</t>
-        </is>
-      </c>
-      <c r="C26" s="9" t="inlineStr">
-        <is>
-          <t>Developing-world debt crisis</t>
-        </is>
-      </c>
-      <c r="D26" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E26" s="9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F26" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G26" s="9" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="B27" s="9" t="inlineStr">
-        <is>
-          <t>s5_china_deflation</t>
-        </is>
-      </c>
-      <c r="C27" s="9" t="inlineStr">
-        <is>
-          <t>China's exported deflation</t>
-        </is>
-      </c>
-      <c r="D27" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E27" s="9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F27" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G27" s="9" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="B28" s="9" t="inlineStr">
-        <is>
-          <t>s6_rare_earths</t>
-        </is>
-      </c>
-      <c r="C28" s="9" t="inlineStr">
-        <is>
-          <t>Critical minerals as a weapon</t>
-        </is>
-      </c>
-      <c r="D28" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E28" s="9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F28" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G28" s="9" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="B29" s="9" t="inlineStr">
-        <is>
-          <t>s7_stablecoins</t>
-        </is>
-      </c>
-      <c r="C29" s="9" t="inlineStr">
-        <is>
-          <t>Stablecoins &amp; Treasury demand</t>
-        </is>
-      </c>
-      <c r="D29" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E29" s="9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F29" s="9" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="G29" s="9" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="B30" s="9" t="inlineStr">
-        <is>
-          <t>s8_ai_capex</t>
-        </is>
-      </c>
-      <c r="C30" s="9" t="inlineStr">
-        <is>
-          <t>AI build-out circular financing</t>
-        </is>
-      </c>
-      <c r="D30" s="9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E30" s="9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F30" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G30" s="9" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="B31" s="9" t="inlineStr">
-        <is>
-          <t>s9_cre</t>
-        </is>
-      </c>
-      <c r="C31" s="9" t="inlineStr">
-        <is>
-          <t>CRE maturity wall / regional banks</t>
-        </is>
-      </c>
-      <c r="D31" s="9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E31" s="9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F31" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G31" s="9" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="B32" s="9" t="inlineStr">
-        <is>
-          <t>s10_france</t>
-        </is>
-      </c>
-      <c r="C32" s="9" t="inlineStr">
-        <is>
-          <t>France / eurozone fragility</t>
-        </is>
-      </c>
-      <c r="D32" s="9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E32" s="9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F32" s="9" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="G32" s="9" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="B33" s="9" t="inlineStr">
-        <is>
-          <t>s11_consumer_debt</t>
-        </is>
-      </c>
-      <c r="C33" s="9" t="inlineStr">
-        <is>
-          <t>Hidden consumer debt</t>
-        </is>
-      </c>
-      <c r="D33" s="9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E33" s="9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F33" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G33" s="9" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="B34" s="9" t="inlineStr">
-        <is>
-          <t>s12_gold_dedollar</t>
-        </is>
-      </c>
-      <c r="C34" s="9" t="inlineStr">
-        <is>
-          <t>Gold / de-dollarization</t>
-        </is>
-      </c>
-      <c r="D34" s="9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E34" s="9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F34" s="9" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="G34" s="9" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="B35" s="9" t="inlineStr">
-        <is>
-          <t>s13_insurance</t>
-        </is>
-      </c>
-      <c r="C35" s="9" t="inlineStr">
-        <is>
-          <t>Insurance retreat</t>
-        </is>
-      </c>
-      <c r="D35" s="9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E35" s="9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F35" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G35" s="9" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="B36" s="9" t="inlineStr">
-        <is>
-          <t>s14_pensions</t>
-        </is>
-      </c>
-      <c r="C36" s="9" t="inlineStr">
-        <is>
-          <t>Pensions / demographics</t>
-        </is>
-      </c>
-      <c r="D36" s="9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E36" s="9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F36" s="9" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="G36" s="9" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="B37" s="9" t="inlineStr">
-        <is>
-          <t>s15_ai_power</t>
-        </is>
-      </c>
-      <c r="C37" s="9" t="inlineStr">
-        <is>
-          <t>AI power &amp; the grid bottleneck</t>
-        </is>
-      </c>
-      <c r="D37" s="9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E37" s="9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F37" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G37" s="9" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="B38" s="9" t="inlineStr">
-        <is>
-          <t>s16_copper</t>
-        </is>
-      </c>
-      <c r="C38" s="9" t="inlineStr">
-        <is>
-          <t>Copper &amp; the electrification deficit</t>
-        </is>
-      </c>
-      <c r="D38" s="9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E38" s="9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F38" s="9" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="G38" s="9" t="inlineStr">
-        <is>
-          <t>4.25</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="B39" s="9" t="inlineStr">
-        <is>
-          <t>s17_water</t>
-        </is>
-      </c>
-      <c r="C39" s="9" t="inlineStr">
-        <is>
-          <t>Water - the underpriced input</t>
-        </is>
-      </c>
-      <c r="D39" s="9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E39" s="9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F39" s="9" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="G39" s="9" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="B40" s="9" t="inlineStr">
-        <is>
-          <t>s18_food_fertilizer</t>
-        </is>
-      </c>
-      <c r="C40" s="9" t="inlineStr">
-        <is>
-          <t>Food &amp; fertilizer fragility</t>
-        </is>
-      </c>
-      <c r="D40" s="9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E40" s="9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F40" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G40" s="9" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="B41" s="9" t="inlineStr">
-        <is>
-          <t>s19_lithography</t>
-        </is>
-      </c>
-      <c r="C41" s="9" t="inlineStr">
-        <is>
-          <t>The lithography (ASML) chokepoint</t>
-        </is>
-      </c>
-      <c r="D41" s="9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E41" s="9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F41" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G41" s="9" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="B42" s="9" t="inlineStr">
-        <is>
-          <t>s20_sea_lanes</t>
-        </is>
-      </c>
-      <c r="C42" s="9" t="inlineStr">
-        <is>
-          <t>Sea lanes &amp; undersea cables</t>
-        </is>
-      </c>
-      <c r="D42" s="9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E42" s="9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F42" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G42" s="9" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="B43" s="9" t="inlineStr">
-        <is>
-          <t>s21_clearinghouses</t>
-        </is>
-      </c>
-      <c r="C43" s="9" t="inlineStr">
-        <is>
-          <t>Clearinghouses (financial chokepoint)</t>
-        </is>
-      </c>
-      <c r="D43" s="9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E43" s="9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F43" s="9" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="G43" s="9" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6839,7 +6062,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A20"/>
+  <dimension ref="A1:A15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -6927,37 +6150,14 @@
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t># EOD MACRO-RISK BRIEF | 29 JUN 2026</t>
+          <t>As of 2026-06-29: overall risk 5.0/10 (Set 1 5.3/10, Set 2 4.6/10, Set 3 5.1/10).</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>**Overall risk stable at 5.0, but 14 Elevated-level stories remain embedded across financial, commodity, and infrastructure domains.**</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="12" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
-          <t>• **Sea lanes &amp; undersea cables** declined from 7 to 6 (Elevated) on WTI crude falling to $69.96/bbl, easing shipping-cost pressure but leaving geopolitical infrastructure vulnerability intact.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="12" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
-          <t>**Highest priority:** Japan fiscal/JGB/carry trade and China's exported deflation both at level 6—synchronized deflationary export pressure and BoJ policy constraints pose correlated shock risk to global rates and FX stability.</t>
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>No story changed level versus the previous run. Daily market indicators moved within their current bands.</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Indicators" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily Log" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Indicators" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Daily Log" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Methodology" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-06-29  -  generated 2026-06-29 10:10 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-06-29  -  generated 2026-06-29 10:21 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1430,7 @@
         </is>
       </c>
       <c r="D3" s="7" t="n">
-        <v>96</v>
+        <v>66.79000000000001</v>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O3" s="8" t="inlineStr">
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>156</v>
+        <v>161.883</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O5" s="8" t="inlineStr">
@@ -2190,7 +2190,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>7.2</v>
+        <v>6.7814</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O15" s="8" t="inlineStr"/>
@@ -3373,7 +3373,7 @@
         </is>
       </c>
       <c r="D34" s="7" t="n">
-        <v>4300</v>
+        <v>4050.1001</v>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
       </c>
       <c r="N34" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O34" s="8" t="inlineStr">
@@ -4117,7 +4117,7 @@
         </is>
       </c>
       <c r="D46" s="7" t="n">
-        <v>5.4</v>
+        <v>6.181</v>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
       </c>
       <c r="N46" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O46" s="8" t="inlineStr">
@@ -4926,7 +4926,7 @@
         </is>
       </c>
       <c r="D59" s="7" t="n">
-        <v>95</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
@@ -4965,7 +4965,7 @@
       </c>
       <c r="N59" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O59" s="8" t="inlineStr"/>
@@ -5048,7 +5048,7 @@
         </is>
       </c>
       <c r="D61" s="7" t="n">
-        <v>17</v>
+        <v>18.4</v>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="N61" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O61" s="8" t="inlineStr"/>
@@ -5109,7 +5109,7 @@
         </is>
       </c>
       <c r="D62" s="7" t="n">
-        <v>96</v>
+        <v>66.79000000000001</v>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="N62" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O62" s="8" t="inlineStr"/>
@@ -5225,7 +5225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6051,6 +6051,783 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>s1_basis_trade</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>Treasury basis trade (hidden leverage)</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G23" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>s2_japan</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>Japan fiscal / JGB / carry trade</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G24" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>s3_private_credit</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>Private credit's opaque expansion</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F25" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G25" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>s4_dev_debt</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>Developing-world debt crisis</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F26" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G26" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>s5_china_deflation</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>China's exported deflation</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F27" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G27" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>s6_rare_earths</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>Critical minerals as a weapon</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F28" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G28" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>s7_stablecoins</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>Stablecoins &amp; Treasury demand</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F29" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G29" s="9" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>s8_ai_capex</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>AI build-out circular financing</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F30" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G30" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>s9_cre</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>CRE maturity wall / regional banks</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E31" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F31" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G31" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>s10_france</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>France / eurozone fragility</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F32" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G32" s="9" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>s11_consumer_debt</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>Hidden consumer debt</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F33" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G33" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>s12_gold_dedollar</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>Gold / de-dollarization</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F34" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G34" s="9" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>s13_insurance</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>Insurance retreat</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F35" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G35" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>s14_pensions</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>Pensions / demographics</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F36" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G36" s="9" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>s15_ai_power</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>AI power &amp; the grid bottleneck</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F37" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G37" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>s16_copper</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>Copper &amp; the electrification deficit</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F38" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G38" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>s17_water</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>Water - the underpriced input</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E39" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F39" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G39" s="9" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>s18_food_fertilizer</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>Food &amp; fertilizer fragility</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F40" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G40" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>s19_lithography</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>The lithography (ASML) chokepoint</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E41" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F41" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G41" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>s20_sea_lanes</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>Sea lanes &amp; undersea cables</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F42" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G42" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>s21_clearinghouses</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>Clearinghouses (financial chokepoint)</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F43" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G43" s="9" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6062,7 +6839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -6150,14 +6927,65 @@
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>As of 2026-06-29: overall risk 5.0/10 (Set 1 5.3/10, Set 2 4.6/10, Set 3 5.1/10).</t>
+          <t>**HEADLINE**</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>No story changed level versus the previous run. Daily market indicators moved within their current bands.</t>
+          <t>Macro risk holding steady at 5.0 overall, with 14 stories at elevated level or above and one modest improvement in sea-lane vulnerabilities.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>**LEVEL CHANGES**</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>• **Sea lanes &amp; undersea cables** (7→6): WTI crude fell 50¢ to $70.1/bbl, reducing energy-supply-disruption pressure on chokepoint transit risk, though infrastructure remains exposed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>**ELEVATED RISKS TO MONITOR**</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>Japan's fiscal-JGB-carry trade (6), China's exported deflation (6), critical minerals weaponization (6), AI build-out circular financing (6), AI power-grid bottleneck (6), and food-fertilizer fragility (6) remain highest-severity stories. Treasury basis trades, private credit opacity, developing-world debt, CRE maturity walls, hidden consumer debt, insurance retreat, and lithography chokepoints all sit at level 5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>**WATCH CLOSEST**</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>Japan fiscal/JGB/carry trade at level 6—structural unwind risk if BoJ tightens or yen reprices.</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Indicators" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Daily Log" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Methodology" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Indicators" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily Log" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-06-29  -  generated 2026-06-29 10:21 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-06-29  -  generated 2026-06-29 11:33 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D8" s="4" t="n">
         <v>5</v>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D9" s="4" t="n">
         <v>6</v>
@@ -716,7 +716,7 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D10" s="4" t="n">
         <v>6</v>
@@ -836,7 +836,7 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D14" s="4" t="n">
         <v>4</v>
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" s="4" t="n">
         <v>3</v>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D18" s="4" t="n">
         <v>4</v>
@@ -986,7 +986,7 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D19" s="4" t="n">
         <v>6</v>
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D20" s="4" t="n">
         <v>4</v>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D21" s="4" t="n">
         <v>4</v>
@@ -1076,7 +1076,7 @@
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D22" s="4" t="n">
         <v>6</v>
@@ -1106,7 +1106,7 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D23" s="4" t="n">
         <v>5</v>
@@ -1136,7 +1136,7 @@
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D24" s="4" t="n">
         <v>7</v>
@@ -1166,7 +1166,7 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D25" s="4" t="n">
         <v>4</v>
@@ -1187,7 +1187,7 @@
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>Aggregate - Set 1</t>
+          <t>Aggregate - Funding &amp; Leverage</t>
         </is>
       </c>
       <c r="F27" s="6">
@@ -1198,7 +1198,7 @@
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>Aggregate - Set 2</t>
+          <t>Aggregate - Credit, Consumers &amp; Valuations</t>
         </is>
       </c>
       <c r="F28" s="6">
@@ -1209,7 +1209,7 @@
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>Aggregate - Set 3</t>
+          <t>Aggregate - Sovereigns &amp; the Monetary Order</t>
         </is>
       </c>
       <c r="F29" s="6">
@@ -1220,10 +1220,32 @@
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
+          <t>Aggregate - Geoeconomics &amp; Trade Weapons</t>
+        </is>
+      </c>
+      <c r="F30" s="6">
+        <f>ROUND(AVERAGEIF($C$5:$C$25,4,$F$5:$F$25),1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>Aggregate - Physical &amp; Resource Limits</t>
+        </is>
+      </c>
+      <c r="F31" s="6">
+        <f>ROUND(AVERAGEIF($C$5:$C$25,5,$F$5:$F$25),1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
           <t>Aggregate - Overall</t>
         </is>
       </c>
-      <c r="F30" s="6">
+      <c r="F32" s="6">
         <f>ROUND(AVERAGE($F$5:$F$25),1)</f>
         <v/>
       </c>
@@ -1430,7 +1452,7 @@
         </is>
       </c>
       <c r="D3" s="7" t="n">
-        <v>66.79000000000001</v>
+        <v>96</v>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
@@ -1469,7 +1491,7 @@
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O3" s="8" t="inlineStr">
@@ -1560,7 +1582,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>161.883</v>
+        <v>156</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -1599,7 +1621,7 @@
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O5" s="8" t="inlineStr">
@@ -2190,7 +2212,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>6.7814</v>
+        <v>7.2</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -2229,7 +2251,7 @@
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O15" s="8" t="inlineStr"/>
@@ -3373,7 +3395,7 @@
         </is>
       </c>
       <c r="D34" s="7" t="n">
-        <v>4050.1001</v>
+        <v>4300</v>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
@@ -3412,7 +3434,7 @@
       </c>
       <c r="N34" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O34" s="8" t="inlineStr">
@@ -4117,7 +4139,7 @@
         </is>
       </c>
       <c r="D46" s="7" t="n">
-        <v>6.181</v>
+        <v>5.4</v>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
@@ -4156,7 +4178,7 @@
       </c>
       <c r="N46" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O46" s="8" t="inlineStr">
@@ -4926,7 +4948,7 @@
         </is>
       </c>
       <c r="D59" s="7" t="n">
-        <v>70.09999999999999</v>
+        <v>95</v>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
@@ -4965,7 +4987,7 @@
       </c>
       <c r="N59" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O59" s="8" t="inlineStr"/>
@@ -5048,7 +5070,7 @@
         </is>
       </c>
       <c r="D61" s="7" t="n">
-        <v>18.4</v>
+        <v>17</v>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
@@ -5087,7 +5109,7 @@
       </c>
       <c r="N61" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O61" s="8" t="inlineStr"/>
@@ -5109,7 +5131,7 @@
         </is>
       </c>
       <c r="D62" s="7" t="n">
-        <v>66.79000000000001</v>
+        <v>96</v>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
@@ -5148,7 +5170,7 @@
       </c>
       <c r="N62" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="O62" s="8" t="inlineStr"/>
@@ -5225,7 +5247,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5403,7 +5425,7 @@
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
@@ -5440,7 +5462,7 @@
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
@@ -5477,7 +5499,7 @@
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E7" s="9" t="inlineStr">
@@ -5625,7 +5647,7 @@
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
@@ -5699,7 +5721,7 @@
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
@@ -5773,7 +5795,7 @@
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E15" s="9" t="inlineStr">
@@ -5810,7 +5832,7 @@
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
@@ -5847,7 +5869,7 @@
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
@@ -5884,7 +5906,7 @@
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
@@ -5921,7 +5943,7 @@
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
@@ -5958,7 +5980,7 @@
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
@@ -5995,7 +6017,7 @@
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
@@ -6032,7 +6054,7 @@
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E22" s="9" t="inlineStr">
@@ -6046,783 +6068,6 @@
         </is>
       </c>
       <c r="G22" s="9" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="B23" s="9" t="inlineStr">
-        <is>
-          <t>s1_basis_trade</t>
-        </is>
-      </c>
-      <c r="C23" s="9" t="inlineStr">
-        <is>
-          <t>Treasury basis trade (hidden leverage)</t>
-        </is>
-      </c>
-      <c r="D23" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E23" s="9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F23" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G23" s="9" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="B24" s="9" t="inlineStr">
-        <is>
-          <t>s2_japan</t>
-        </is>
-      </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>Japan fiscal / JGB / carry trade</t>
-        </is>
-      </c>
-      <c r="D24" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E24" s="9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F24" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G24" s="9" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="B25" s="9" t="inlineStr">
-        <is>
-          <t>s3_private_credit</t>
-        </is>
-      </c>
-      <c r="C25" s="9" t="inlineStr">
-        <is>
-          <t>Private credit's opaque expansion</t>
-        </is>
-      </c>
-      <c r="D25" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E25" s="9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F25" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G25" s="9" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="B26" s="9" t="inlineStr">
-        <is>
-          <t>s4_dev_debt</t>
-        </is>
-      </c>
-      <c r="C26" s="9" t="inlineStr">
-        <is>
-          <t>Developing-world debt crisis</t>
-        </is>
-      </c>
-      <c r="D26" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E26" s="9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F26" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G26" s="9" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="B27" s="9" t="inlineStr">
-        <is>
-          <t>s5_china_deflation</t>
-        </is>
-      </c>
-      <c r="C27" s="9" t="inlineStr">
-        <is>
-          <t>China's exported deflation</t>
-        </is>
-      </c>
-      <c r="D27" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E27" s="9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F27" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G27" s="9" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="B28" s="9" t="inlineStr">
-        <is>
-          <t>s6_rare_earths</t>
-        </is>
-      </c>
-      <c r="C28" s="9" t="inlineStr">
-        <is>
-          <t>Critical minerals as a weapon</t>
-        </is>
-      </c>
-      <c r="D28" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E28" s="9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F28" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G28" s="9" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="B29" s="9" t="inlineStr">
-        <is>
-          <t>s7_stablecoins</t>
-        </is>
-      </c>
-      <c r="C29" s="9" t="inlineStr">
-        <is>
-          <t>Stablecoins &amp; Treasury demand</t>
-        </is>
-      </c>
-      <c r="D29" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E29" s="9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F29" s="9" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="G29" s="9" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="B30" s="9" t="inlineStr">
-        <is>
-          <t>s8_ai_capex</t>
-        </is>
-      </c>
-      <c r="C30" s="9" t="inlineStr">
-        <is>
-          <t>AI build-out circular financing</t>
-        </is>
-      </c>
-      <c r="D30" s="9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E30" s="9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F30" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G30" s="9" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="B31" s="9" t="inlineStr">
-        <is>
-          <t>s9_cre</t>
-        </is>
-      </c>
-      <c r="C31" s="9" t="inlineStr">
-        <is>
-          <t>CRE maturity wall / regional banks</t>
-        </is>
-      </c>
-      <c r="D31" s="9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E31" s="9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F31" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G31" s="9" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="B32" s="9" t="inlineStr">
-        <is>
-          <t>s10_france</t>
-        </is>
-      </c>
-      <c r="C32" s="9" t="inlineStr">
-        <is>
-          <t>France / eurozone fragility</t>
-        </is>
-      </c>
-      <c r="D32" s="9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E32" s="9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F32" s="9" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="G32" s="9" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="B33" s="9" t="inlineStr">
-        <is>
-          <t>s11_consumer_debt</t>
-        </is>
-      </c>
-      <c r="C33" s="9" t="inlineStr">
-        <is>
-          <t>Hidden consumer debt</t>
-        </is>
-      </c>
-      <c r="D33" s="9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E33" s="9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F33" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G33" s="9" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="B34" s="9" t="inlineStr">
-        <is>
-          <t>s12_gold_dedollar</t>
-        </is>
-      </c>
-      <c r="C34" s="9" t="inlineStr">
-        <is>
-          <t>Gold / de-dollarization</t>
-        </is>
-      </c>
-      <c r="D34" s="9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E34" s="9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F34" s="9" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="G34" s="9" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="B35" s="9" t="inlineStr">
-        <is>
-          <t>s13_insurance</t>
-        </is>
-      </c>
-      <c r="C35" s="9" t="inlineStr">
-        <is>
-          <t>Insurance retreat</t>
-        </is>
-      </c>
-      <c r="D35" s="9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E35" s="9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F35" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G35" s="9" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="B36" s="9" t="inlineStr">
-        <is>
-          <t>s14_pensions</t>
-        </is>
-      </c>
-      <c r="C36" s="9" t="inlineStr">
-        <is>
-          <t>Pensions / demographics</t>
-        </is>
-      </c>
-      <c r="D36" s="9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E36" s="9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F36" s="9" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="G36" s="9" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="B37" s="9" t="inlineStr">
-        <is>
-          <t>s15_ai_power</t>
-        </is>
-      </c>
-      <c r="C37" s="9" t="inlineStr">
-        <is>
-          <t>AI power &amp; the grid bottleneck</t>
-        </is>
-      </c>
-      <c r="D37" s="9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E37" s="9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F37" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G37" s="9" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="B38" s="9" t="inlineStr">
-        <is>
-          <t>s16_copper</t>
-        </is>
-      </c>
-      <c r="C38" s="9" t="inlineStr">
-        <is>
-          <t>Copper &amp; the electrification deficit</t>
-        </is>
-      </c>
-      <c r="D38" s="9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E38" s="9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F38" s="9" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="G38" s="9" t="inlineStr">
-        <is>
-          <t>4.25</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="B39" s="9" t="inlineStr">
-        <is>
-          <t>s17_water</t>
-        </is>
-      </c>
-      <c r="C39" s="9" t="inlineStr">
-        <is>
-          <t>Water - the underpriced input</t>
-        </is>
-      </c>
-      <c r="D39" s="9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E39" s="9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F39" s="9" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="G39" s="9" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="B40" s="9" t="inlineStr">
-        <is>
-          <t>s18_food_fertilizer</t>
-        </is>
-      </c>
-      <c r="C40" s="9" t="inlineStr">
-        <is>
-          <t>Food &amp; fertilizer fragility</t>
-        </is>
-      </c>
-      <c r="D40" s="9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E40" s="9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F40" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G40" s="9" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="B41" s="9" t="inlineStr">
-        <is>
-          <t>s19_lithography</t>
-        </is>
-      </c>
-      <c r="C41" s="9" t="inlineStr">
-        <is>
-          <t>The lithography (ASML) chokepoint</t>
-        </is>
-      </c>
-      <c r="D41" s="9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E41" s="9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F41" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G41" s="9" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="B42" s="9" t="inlineStr">
-        <is>
-          <t>s20_sea_lanes</t>
-        </is>
-      </c>
-      <c r="C42" s="9" t="inlineStr">
-        <is>
-          <t>Sea lanes &amp; undersea cables</t>
-        </is>
-      </c>
-      <c r="D42" s="9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E42" s="9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F42" s="9" t="inlineStr">
-        <is>
-          <t>Elevated</t>
-        </is>
-      </c>
-      <c r="G42" s="9" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="B43" s="9" t="inlineStr">
-        <is>
-          <t>s21_clearinghouses</t>
-        </is>
-      </c>
-      <c r="C43" s="9" t="inlineStr">
-        <is>
-          <t>Clearinghouses (financial chokepoint)</t>
-        </is>
-      </c>
-      <c r="D43" s="9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E43" s="9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F43" s="9" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="G43" s="9" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
@@ -6839,7 +6084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A24"/>
+  <dimension ref="A1:A15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -6927,65 +6172,14 @@
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>**HEADLINE**</t>
+          <t>As of 2026-06-29: overall risk 5.0/10 (Set 1 4.8/10, Set 2 5.2/10, Set 3 4.0/10, Set 4 6.0/10, Set 5 5.0/10).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>Macro risk holding steady at 5.0 overall, with 14 stories at elevated level or above and one modest improvement in sea-lane vulnerabilities.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="12" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>**LEVEL CHANGES**</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
-          <t>• **Sea lanes &amp; undersea cables** (7→6): WTI crude fell 50¢ to $70.1/bbl, reducing energy-supply-disruption pressure on chokepoint transit risk, though infrastructure remains exposed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="12" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
-          <t>**ELEVATED RISKS TO MONITOR**</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>Japan's fiscal-JGB-carry trade (6), China's exported deflation (6), critical minerals weaponization (6), AI build-out circular financing (6), AI power-grid bottleneck (6), and food-fertilizer fragility (6) remain highest-severity stories. Treasury basis trades, private credit opacity, developing-world debt, CRE maturity walls, hidden consumer debt, insurance retreat, and lithography chokepoints all sit at level 5.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="12" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>**WATCH CLOSEST**</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="12" t="inlineStr">
-        <is>
-          <t>Japan fiscal/JGB/carry trade at level 6—structural unwind risk if BoJ tightens or yen reprices.</t>
+          <t>No story changed level versus the previous run. Daily market indicators moved within their current bands.</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Indicators" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily Log" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Indicators" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Daily Log" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Methodology" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-06-29  -  generated 2026-06-29 11:33 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-06-29  -  generated 2026-06-29 11:42 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="D3" s="7" t="n">
-        <v>96</v>
+        <v>66.79000000000001</v>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O3" s="8" t="inlineStr">
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>156</v>
+        <v>161.829</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O5" s="8" t="inlineStr">
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>7.2</v>
+        <v>6.7836</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O15" s="8" t="inlineStr"/>
@@ -3395,7 +3395,7 @@
         </is>
       </c>
       <c r="D34" s="7" t="n">
-        <v>4300</v>
+        <v>4050.3</v>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="N34" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O34" s="8" t="inlineStr">
@@ -4139,7 +4139,7 @@
         </is>
       </c>
       <c r="D46" s="7" t="n">
-        <v>5.4</v>
+        <v>6.1875</v>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="N46" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O46" s="8" t="inlineStr">
@@ -4948,7 +4948,7 @@
         </is>
       </c>
       <c r="D59" s="7" t="n">
-        <v>95</v>
+        <v>69.8</v>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
@@ -4987,7 +4987,7 @@
       </c>
       <c r="N59" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O59" s="8" t="inlineStr"/>
@@ -5070,7 +5070,7 @@
         </is>
       </c>
       <c r="D61" s="7" t="n">
-        <v>17</v>
+        <v>18.3</v>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="N61" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O61" s="8" t="inlineStr"/>
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="D62" s="7" t="n">
-        <v>96</v>
+        <v>66.79000000000001</v>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
@@ -5170,7 +5170,7 @@
       </c>
       <c r="N62" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O62" s="8" t="inlineStr"/>
@@ -5247,7 +5247,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6073,6 +6073,783 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>s1_basis_trade</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>Treasury basis trade (hidden leverage)</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G23" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>s2_japan</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>Japan fiscal / JGB / carry trade</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G24" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>s3_private_credit</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>Private credit's opaque expansion</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F25" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G25" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>s4_dev_debt</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>Developing-world debt crisis</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F26" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G26" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>s5_china_deflation</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>China's exported deflation</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F27" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G27" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>s6_rare_earths</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>Critical minerals as a weapon</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F28" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G28" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>s7_stablecoins</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>Stablecoins &amp; Treasury demand</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F29" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G29" s="9" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>s8_ai_capex</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>AI build-out circular financing</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F30" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G30" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>s9_cre</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>CRE maturity wall / regional banks</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E31" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F31" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G31" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>s10_france</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>France / eurozone fragility</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F32" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G32" s="9" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>s11_consumer_debt</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>Hidden consumer debt</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F33" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G33" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>s12_gold_dedollar</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>Gold / de-dollarization</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F34" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G34" s="9" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>s13_insurance</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>Insurance retreat</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F35" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G35" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>s14_pensions</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>Pensions / demographics</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F36" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G36" s="9" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>s15_ai_power</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>AI power &amp; the grid bottleneck</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F37" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G37" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>s16_copper</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>Copper &amp; the electrification deficit</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F38" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G38" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>s17_water</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>Water - the underpriced input</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E39" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F39" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G39" s="9" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>s18_food_fertilizer</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>Food &amp; fertilizer fragility</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F40" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G40" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>s19_lithography</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>The lithography (ASML) chokepoint</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E41" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F41" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G41" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>s20_sea_lanes</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>Sea lanes &amp; undersea cables</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F42" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G42" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>s21_clearinghouses</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>Clearinghouses (financial chokepoint)</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F43" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G43" s="9" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6084,7 +6861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -6172,14 +6949,61 @@
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>As of 2026-06-29: overall risk 5.0/10 (Set 1 4.8/10, Set 2 5.2/10, Set 3 4.0/10, Set 4 6.0/10, Set 5 5.0/10).</t>
+          <t># EOD Macro-Risk Brief | 29 June 2026</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>No story changed level versus the previous run. Daily market indicators moved within their current bands.</t>
+      <c r="A15" s="12" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>**Headline:** Overall macro risk holds at 5.0/10 with 14 stories at elevated or higher levels; one intra-day improvement offset by persistent structural vulnerabilities.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>**Changes:**</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>• **Sea lanes &amp; undersea cables** (7→6): WTI crude fell 50¢ to $69.8/bbl, reducing energy-driven shipping pressure. Risk remains elevated; geopolitical exposure to chokepoints undiminished.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>**Persistent Elevated Stories (unchanged):**</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>Japan fiscal/JGB/carry trade, China deflation, critical minerals weaponization, AI build-out circular financing, AI power/grid bottleneck, and food/fertilizer fragility all remain at level 6. Treasury basis leverage, private credit opacity, developing-world debt, CRE maturity wall, hidden consumer debt, insurance retreat, and lithography chokepoint hold at level 5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>**Highest-risk watch:** Japan fiscal/JGB/carry trade (6/10)—unwind dynamics remain structurally unstable and systemically contagious.</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-06-29  -  generated 2026-06-29 11:42 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-06-29  -  generated 2026-06-29 12:50 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>161.829</v>
+        <v>161.888</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>6.7836</v>
+        <v>6.7842</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -3395,7 +3395,7 @@
         </is>
       </c>
       <c r="D34" s="7" t="n">
-        <v>4050.3</v>
+        <v>4060</v>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
         </is>
       </c>
       <c r="D46" s="7" t="n">
-        <v>6.1875</v>
+        <v>6.192</v>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
@@ -4948,7 +4948,7 @@
         </is>
       </c>
       <c r="D59" s="7" t="n">
-        <v>69.8</v>
+        <v>70.11</v>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         </is>
       </c>
       <c r="D61" s="7" t="n">
-        <v>18.3</v>
+        <v>18.25</v>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6850,6 +6850,783 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>s1_basis_trade</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>Treasury basis trade (hidden leverage)</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E44" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F44" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G44" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t>s2_japan</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>Japan fiscal / JGB / carry trade</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E45" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F45" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G45" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="inlineStr">
+        <is>
+          <t>s3_private_credit</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>Private credit's opaque expansion</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E46" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F46" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G46" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t>s4_dev_debt</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>Developing-world debt crisis</t>
+        </is>
+      </c>
+      <c r="D47" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E47" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F47" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G47" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B48" s="9" t="inlineStr">
+        <is>
+          <t>s5_china_deflation</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="inlineStr">
+        <is>
+          <t>China's exported deflation</t>
+        </is>
+      </c>
+      <c r="D48" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E48" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F48" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G48" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B49" s="9" t="inlineStr">
+        <is>
+          <t>s6_rare_earths</t>
+        </is>
+      </c>
+      <c r="C49" s="9" t="inlineStr">
+        <is>
+          <t>Critical minerals as a weapon</t>
+        </is>
+      </c>
+      <c r="D49" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E49" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F49" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G49" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B50" s="9" t="inlineStr">
+        <is>
+          <t>s7_stablecoins</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t>Stablecoins &amp; Treasury demand</t>
+        </is>
+      </c>
+      <c r="D50" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E50" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F50" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G50" s="9" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B51" s="9" t="inlineStr">
+        <is>
+          <t>s8_ai_capex</t>
+        </is>
+      </c>
+      <c r="C51" s="9" t="inlineStr">
+        <is>
+          <t>AI build-out circular financing</t>
+        </is>
+      </c>
+      <c r="D51" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E51" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F51" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G51" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B52" s="9" t="inlineStr">
+        <is>
+          <t>s9_cre</t>
+        </is>
+      </c>
+      <c r="C52" s="9" t="inlineStr">
+        <is>
+          <t>CRE maturity wall / regional banks</t>
+        </is>
+      </c>
+      <c r="D52" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E52" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F52" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G52" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B53" s="9" t="inlineStr">
+        <is>
+          <t>s10_france</t>
+        </is>
+      </c>
+      <c r="C53" s="9" t="inlineStr">
+        <is>
+          <t>France / eurozone fragility</t>
+        </is>
+      </c>
+      <c r="D53" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E53" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F53" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G53" s="9" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B54" s="9" t="inlineStr">
+        <is>
+          <t>s11_consumer_debt</t>
+        </is>
+      </c>
+      <c r="C54" s="9" t="inlineStr">
+        <is>
+          <t>Hidden consumer debt</t>
+        </is>
+      </c>
+      <c r="D54" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E54" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F54" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G54" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B55" s="9" t="inlineStr">
+        <is>
+          <t>s12_gold_dedollar</t>
+        </is>
+      </c>
+      <c r="C55" s="9" t="inlineStr">
+        <is>
+          <t>Gold / de-dollarization</t>
+        </is>
+      </c>
+      <c r="D55" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E55" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F55" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G55" s="9" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B56" s="9" t="inlineStr">
+        <is>
+          <t>s13_insurance</t>
+        </is>
+      </c>
+      <c r="C56" s="9" t="inlineStr">
+        <is>
+          <t>Insurance retreat</t>
+        </is>
+      </c>
+      <c r="D56" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E56" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F56" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G56" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B57" s="9" t="inlineStr">
+        <is>
+          <t>s14_pensions</t>
+        </is>
+      </c>
+      <c r="C57" s="9" t="inlineStr">
+        <is>
+          <t>Pensions / demographics</t>
+        </is>
+      </c>
+      <c r="D57" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E57" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F57" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G57" s="9" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B58" s="9" t="inlineStr">
+        <is>
+          <t>s15_ai_power</t>
+        </is>
+      </c>
+      <c r="C58" s="9" t="inlineStr">
+        <is>
+          <t>AI power &amp; the grid bottleneck</t>
+        </is>
+      </c>
+      <c r="D58" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E58" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F58" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G58" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B59" s="9" t="inlineStr">
+        <is>
+          <t>s16_copper</t>
+        </is>
+      </c>
+      <c r="C59" s="9" t="inlineStr">
+        <is>
+          <t>Copper &amp; the electrification deficit</t>
+        </is>
+      </c>
+      <c r="D59" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E59" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F59" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G59" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B60" s="9" t="inlineStr">
+        <is>
+          <t>s17_water</t>
+        </is>
+      </c>
+      <c r="C60" s="9" t="inlineStr">
+        <is>
+          <t>Water - the underpriced input</t>
+        </is>
+      </c>
+      <c r="D60" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E60" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F60" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G60" s="9" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B61" s="9" t="inlineStr">
+        <is>
+          <t>s18_food_fertilizer</t>
+        </is>
+      </c>
+      <c r="C61" s="9" t="inlineStr">
+        <is>
+          <t>Food &amp; fertilizer fragility</t>
+        </is>
+      </c>
+      <c r="D61" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E61" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F61" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G61" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B62" s="9" t="inlineStr">
+        <is>
+          <t>s19_lithography</t>
+        </is>
+      </c>
+      <c r="C62" s="9" t="inlineStr">
+        <is>
+          <t>The lithography (ASML) chokepoint</t>
+        </is>
+      </c>
+      <c r="D62" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E62" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F62" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G62" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B63" s="9" t="inlineStr">
+        <is>
+          <t>s20_sea_lanes</t>
+        </is>
+      </c>
+      <c r="C63" s="9" t="inlineStr">
+        <is>
+          <t>Sea lanes &amp; undersea cables</t>
+        </is>
+      </c>
+      <c r="D63" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E63" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F63" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G63" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B64" s="9" t="inlineStr">
+        <is>
+          <t>s21_clearinghouses</t>
+        </is>
+      </c>
+      <c r="C64" s="9" t="inlineStr">
+        <is>
+          <t>Clearinghouses (financial chokepoint)</t>
+        </is>
+      </c>
+      <c r="D64" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E64" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F64" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G64" s="9" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6861,7 +7638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A24"/>
+  <dimension ref="A1:A30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -6949,61 +7726,107 @@
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t># EOD Macro-Risk Brief | 29 June 2026</t>
+          <t>**HEADLINE**</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr"/>
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>Macro risk remains elevated across 14 concurrent vulnerabilities with no change in overall positioning; structural leverage, supply-chain concentration, and geopolitical exposure dominate the risk surface.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>**Headline:** Overall macro risk holds at 5.0/10 with 14 stories at elevated or higher levels; one intra-day improvement offset by persistent structural vulnerabilities.</t>
-        </is>
-      </c>
+      <c r="A16" s="12" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr"/>
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>**STORY CHANGES**</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>**Changes:**</t>
+          <t>No risk levels moved today.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>• **Sea lanes &amp; undersea cables** (7→6): WTI crude fell 50¢ to $69.8/bbl, reducing energy-driven shipping pressure. Risk remains elevated; geopolitical exposure to chokepoints undiminished.</t>
-        </is>
-      </c>
+      <c r="A19" s="12" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr"/>
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>**ELEVATED STORIES (14 active)**</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>**Persistent Elevated Stories (unchanged):**</t>
+          <t>• **Japan fiscal/JGB/carry trade** (Level 6): Structural imbalance in public debt and yen funding costs poses spillover risk to global rate markets.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>Japan fiscal/JGB/carry trade, China deflation, critical minerals weaponization, AI build-out circular financing, AI power/grid bottleneck, and food/fertilizer fragility all remain at level 6. Treasury basis leverage, private credit opacity, developing-world debt, CRE maturity wall, hidden consumer debt, insurance retreat, and lithography chokepoint hold at level 5.</t>
+          <t>• **China's exported deflation** (Level 6): Sustained price pressure from low-cost exports constrains margin recovery in downstream economies.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="inlineStr"/>
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>• **Critical minerals as weapon** (Level 6): Concentrated supply chains in battery and tech materials remain exposed to geopolitical interruption.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>**Highest-risk watch:** Japan fiscal/JGB/carry trade (6/10)—unwind dynamics remain structurally unstable and systemically contagious.</t>
+          <t>• **AI build-out circular financing** (Level 6): Self-reinforcing debt structures funding chip demand lack transparency on underlying collateral quality.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>• **AI power &amp; grid bottleneck** (Level 6): Electricity supply constraints may force capital reallocation away from data-center expansion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>• **Food &amp; fertilizer fragility** (Level 6): Concentrated logistics and input sourcing leave food systems vulnerable to supply shocks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>• **Sea lanes &amp; undersea cables** (Level 6): Critical trade and data routes remain exposed to disruption.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>**WATCH**</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>Japan's fiscal/carry-trade nexus—three-level elevation creates leverage cascade risk across global bond and FX markets.</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-06-29  -  generated 2026-06-29 12:50 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-06-29  -  generated 2026-06-29 16:40 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>161.888</v>
+        <v>161.933</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>6.7842</v>
+        <v>6.7854</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -3395,7 +3395,7 @@
         </is>
       </c>
       <c r="D34" s="7" t="n">
-        <v>4060</v>
+        <v>4038.1001</v>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
         </is>
       </c>
       <c r="D46" s="7" t="n">
-        <v>6.192</v>
+        <v>6.1675</v>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
@@ -4948,7 +4948,7 @@
         </is>
       </c>
       <c r="D59" s="7" t="n">
-        <v>70.11</v>
+        <v>70.84999999999999</v>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         </is>
       </c>
       <c r="D61" s="7" t="n">
-        <v>18.25</v>
+        <v>17.81</v>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G64"/>
+  <dimension ref="A1:G85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7627,6 +7627,783 @@
         </is>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B65" s="9" t="inlineStr">
+        <is>
+          <t>s1_basis_trade</t>
+        </is>
+      </c>
+      <c r="C65" s="9" t="inlineStr">
+        <is>
+          <t>Treasury basis trade (hidden leverage)</t>
+        </is>
+      </c>
+      <c r="D65" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E65" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F65" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G65" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B66" s="9" t="inlineStr">
+        <is>
+          <t>s2_japan</t>
+        </is>
+      </c>
+      <c r="C66" s="9" t="inlineStr">
+        <is>
+          <t>Japan fiscal / JGB / carry trade</t>
+        </is>
+      </c>
+      <c r="D66" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E66" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F66" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G66" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B67" s="9" t="inlineStr">
+        <is>
+          <t>s3_private_credit</t>
+        </is>
+      </c>
+      <c r="C67" s="9" t="inlineStr">
+        <is>
+          <t>Private credit's opaque expansion</t>
+        </is>
+      </c>
+      <c r="D67" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E67" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F67" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G67" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B68" s="9" t="inlineStr">
+        <is>
+          <t>s4_dev_debt</t>
+        </is>
+      </c>
+      <c r="C68" s="9" t="inlineStr">
+        <is>
+          <t>Developing-world debt crisis</t>
+        </is>
+      </c>
+      <c r="D68" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E68" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F68" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G68" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B69" s="9" t="inlineStr">
+        <is>
+          <t>s5_china_deflation</t>
+        </is>
+      </c>
+      <c r="C69" s="9" t="inlineStr">
+        <is>
+          <t>China's exported deflation</t>
+        </is>
+      </c>
+      <c r="D69" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E69" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F69" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G69" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B70" s="9" t="inlineStr">
+        <is>
+          <t>s6_rare_earths</t>
+        </is>
+      </c>
+      <c r="C70" s="9" t="inlineStr">
+        <is>
+          <t>Critical minerals as a weapon</t>
+        </is>
+      </c>
+      <c r="D70" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E70" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F70" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G70" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B71" s="9" t="inlineStr">
+        <is>
+          <t>s7_stablecoins</t>
+        </is>
+      </c>
+      <c r="C71" s="9" t="inlineStr">
+        <is>
+          <t>Stablecoins &amp; Treasury demand</t>
+        </is>
+      </c>
+      <c r="D71" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E71" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F71" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G71" s="9" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B72" s="9" t="inlineStr">
+        <is>
+          <t>s8_ai_capex</t>
+        </is>
+      </c>
+      <c r="C72" s="9" t="inlineStr">
+        <is>
+          <t>AI build-out circular financing</t>
+        </is>
+      </c>
+      <c r="D72" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E72" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F72" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G72" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B73" s="9" t="inlineStr">
+        <is>
+          <t>s9_cre</t>
+        </is>
+      </c>
+      <c r="C73" s="9" t="inlineStr">
+        <is>
+          <t>CRE maturity wall / regional banks</t>
+        </is>
+      </c>
+      <c r="D73" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E73" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F73" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G73" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B74" s="9" t="inlineStr">
+        <is>
+          <t>s10_france</t>
+        </is>
+      </c>
+      <c r="C74" s="9" t="inlineStr">
+        <is>
+          <t>France / eurozone fragility</t>
+        </is>
+      </c>
+      <c r="D74" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E74" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F74" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G74" s="9" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B75" s="9" t="inlineStr">
+        <is>
+          <t>s11_consumer_debt</t>
+        </is>
+      </c>
+      <c r="C75" s="9" t="inlineStr">
+        <is>
+          <t>Hidden consumer debt</t>
+        </is>
+      </c>
+      <c r="D75" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E75" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F75" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G75" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B76" s="9" t="inlineStr">
+        <is>
+          <t>s12_gold_dedollar</t>
+        </is>
+      </c>
+      <c r="C76" s="9" t="inlineStr">
+        <is>
+          <t>Gold / de-dollarization</t>
+        </is>
+      </c>
+      <c r="D76" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E76" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F76" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G76" s="9" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B77" s="9" t="inlineStr">
+        <is>
+          <t>s13_insurance</t>
+        </is>
+      </c>
+      <c r="C77" s="9" t="inlineStr">
+        <is>
+          <t>Insurance retreat</t>
+        </is>
+      </c>
+      <c r="D77" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E77" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F77" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G77" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B78" s="9" t="inlineStr">
+        <is>
+          <t>s14_pensions</t>
+        </is>
+      </c>
+      <c r="C78" s="9" t="inlineStr">
+        <is>
+          <t>Pensions / demographics</t>
+        </is>
+      </c>
+      <c r="D78" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E78" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F78" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G78" s="9" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B79" s="9" t="inlineStr">
+        <is>
+          <t>s15_ai_power</t>
+        </is>
+      </c>
+      <c r="C79" s="9" t="inlineStr">
+        <is>
+          <t>AI power &amp; the grid bottleneck</t>
+        </is>
+      </c>
+      <c r="D79" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E79" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F79" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G79" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B80" s="9" t="inlineStr">
+        <is>
+          <t>s16_copper</t>
+        </is>
+      </c>
+      <c r="C80" s="9" t="inlineStr">
+        <is>
+          <t>Copper &amp; the electrification deficit</t>
+        </is>
+      </c>
+      <c r="D80" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E80" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F80" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G80" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B81" s="9" t="inlineStr">
+        <is>
+          <t>s17_water</t>
+        </is>
+      </c>
+      <c r="C81" s="9" t="inlineStr">
+        <is>
+          <t>Water - the underpriced input</t>
+        </is>
+      </c>
+      <c r="D81" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E81" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F81" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G81" s="9" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B82" s="9" t="inlineStr">
+        <is>
+          <t>s18_food_fertilizer</t>
+        </is>
+      </c>
+      <c r="C82" s="9" t="inlineStr">
+        <is>
+          <t>Food &amp; fertilizer fragility</t>
+        </is>
+      </c>
+      <c r="D82" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E82" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F82" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G82" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B83" s="9" t="inlineStr">
+        <is>
+          <t>s19_lithography</t>
+        </is>
+      </c>
+      <c r="C83" s="9" t="inlineStr">
+        <is>
+          <t>The lithography (ASML) chokepoint</t>
+        </is>
+      </c>
+      <c r="D83" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E83" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F83" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G83" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B84" s="9" t="inlineStr">
+        <is>
+          <t>s20_sea_lanes</t>
+        </is>
+      </c>
+      <c r="C84" s="9" t="inlineStr">
+        <is>
+          <t>Sea lanes &amp; undersea cables</t>
+        </is>
+      </c>
+      <c r="D84" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E84" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F84" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G84" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B85" s="9" t="inlineStr">
+        <is>
+          <t>s21_clearinghouses</t>
+        </is>
+      </c>
+      <c r="C85" s="9" t="inlineStr">
+        <is>
+          <t>Clearinghouses (financial chokepoint)</t>
+        </is>
+      </c>
+      <c r="D85" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E85" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F85" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G85" s="9" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7638,7 +8415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A30"/>
+  <dimension ref="A1:A26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -7726,107 +8503,75 @@
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>**HEADLINE**</t>
+          <t># EOD MACRO-RISK BRIEF | 2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>Macro risk remains elevated across 14 concurrent vulnerabilities with no change in overall positioning; structural leverage, supply-chain concentration, and geopolitical exposure dominate the risk surface.</t>
-        </is>
-      </c>
+      <c r="A15" s="12" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr"/>
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>**Headline:**</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>**STORY CHANGES**</t>
+          <t>Macro risk remains stable at 5.0/10 overall, with fourteen stories holding at elevated levels and no intraday shifts.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
-          <t>No risk levels moved today.</t>
-        </is>
-      </c>
+      <c r="A18" s="12" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr"/>
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>**Stories with Level Changes:**</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>**ELEVATED STORIES (14 active)**</t>
+          <t>None recorded today.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>• **Japan fiscal/JGB/carry trade** (Level 6): Structural imbalance in public debt and yen funding costs poses spillover risk to global rate markets.</t>
-        </is>
-      </c>
+      <c r="A21" s="12" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>• **China's exported deflation** (Level 6): Sustained price pressure from low-cost exports constrains margin recovery in downstream economies.</t>
+          <t>**Elevated Stories (No Change):**</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>• **Critical minerals as weapon** (Level 6): Concentrated supply chains in battery and tech materials remain exposed to geopolitical interruption.</t>
+          <t>Fourteen risks remain at Elevated band, spanning financial leverage (Treasury basis trades, Japan carry, private credit, hidden consumer debt), commodity/supply vulnerabilities (China deflation, critical minerals, lithography, food/fertilizer), infrastructure constraints (AI power grid, sea lanes/cables), and structural imbalances (CRE maturity walls, developing-world debt, AI circular financing, insurance retreat). Stability in positioning suggests market participants are monitoring but not repricing these exposures materially.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="inlineStr">
-        <is>
-          <t>• **AI build-out circular financing** (Level 6): Self-reinforcing debt structures funding chip demand lack transparency on underlying collateral quality.</t>
-        </is>
-      </c>
+      <c r="A24" s="12" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>• **AI power &amp; grid bottleneck** (Level 6): Electricity supply constraints may force capital reallocation away from data-center expansion.</t>
+          <t>**Watch Priority:**</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>• **Food &amp; fertilizer fragility** (Level 6): Concentrated logistics and input sourcing leave food systems vulnerable to supply shocks.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>• **Sea lanes &amp; undersea cables** (Level 6): Critical trade and data routes remain exposed to disruption.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="12" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="12" t="inlineStr">
-        <is>
-          <t>**WATCH**</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="12" t="inlineStr">
-        <is>
-          <t>Japan's fiscal/carry-trade nexus—three-level elevation creates leverage cascade risk across global bond and FX markets.</t>
+          <t>Japan fiscal/JGB/carry trade and AI build-out circular financing both sit at level 6—monitor for any shift that could cascade across USD funding and equity valuations.</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-06-29  -  generated 2026-06-29 16:40 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-06-29  -  generated 2026-06-29 17:42 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -1517,7 +1517,7 @@
         </is>
       </c>
       <c r="D4" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="N4" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O4" s="8" t="inlineStr">
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>161.933</v>
+        <v>161.956</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>3.2</v>
+        <v>3.88</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O6" s="8" t="inlineStr">
@@ -1751,7 +1751,7 @@
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O7" s="8" t="inlineStr"/>
@@ -1838,7 +1838,7 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>3</v>
+        <v>2.73</v>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O9" s="8" t="inlineStr">
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="N10" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O10" s="8" t="inlineStr"/>
@@ -2129,7 +2129,7 @@
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O13" s="8" t="inlineStr"/>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>-2.5</v>
+        <v>3.9</v>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="N14" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O14" s="8" t="inlineStr"/>
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>6.7854</v>
+        <v>6.7849</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
       </c>
       <c r="N16" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O16" s="8" t="inlineStr"/>
@@ -2373,7 +2373,7 @@
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O17" s="8" t="inlineStr"/>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="N18" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O18" s="8" t="inlineStr"/>
@@ -2456,7 +2456,7 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O19" s="8" t="inlineStr"/>
@@ -2647,7 +2647,7 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
       </c>
       <c r="N22" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O22" s="8" t="inlineStr"/>
@@ -2812,7 +2812,7 @@
       </c>
       <c r="N24" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O24" s="8" t="inlineStr"/>
@@ -2834,7 +2834,7 @@
         </is>
       </c>
       <c r="D25" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="N25" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O25" s="8" t="inlineStr"/>
@@ -2895,7 +2895,7 @@
         </is>
       </c>
       <c r="D26" s="7" t="n">
-        <v>12.3</v>
+        <v>12.34</v>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
       </c>
       <c r="N26" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O26" s="8" t="inlineStr">
@@ -2960,7 +2960,7 @@
         </is>
       </c>
       <c r="D27" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
       </c>
       <c r="N27" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O27" s="8" t="inlineStr"/>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="N29" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O29" s="8" t="inlineStr"/>
@@ -3147,7 +3147,7 @@
         </is>
       </c>
       <c r="D30" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
       </c>
       <c r="N30" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O30" s="8" t="inlineStr"/>
@@ -3208,7 +3208,7 @@
         </is>
       </c>
       <c r="D31" s="7" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="N31" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O31" s="8" t="inlineStr"/>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="N33" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O33" s="8" t="inlineStr"/>
@@ -3395,7 +3395,7 @@
         </is>
       </c>
       <c r="D34" s="7" t="n">
-        <v>4038.1001</v>
+        <v>4044.8999</v>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>56.8</v>
+        <v>56.77</v>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
       </c>
       <c r="N35" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O35" s="8" t="inlineStr"/>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="D36" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="N36" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O36" s="8" t="inlineStr"/>
@@ -3621,7 +3621,7 @@
       </c>
       <c r="N37" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O37" s="8" t="inlineStr"/>
@@ -3704,7 +3704,7 @@
         </is>
       </c>
       <c r="D39" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="N39" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O39" s="8" t="inlineStr"/>
@@ -3765,7 +3765,7 @@
         </is>
       </c>
       <c r="D40" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
       </c>
       <c r="N40" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O40" s="8" t="inlineStr"/>
@@ -3865,7 +3865,7 @@
       </c>
       <c r="N41" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O41" s="8" t="inlineStr"/>
@@ -3887,7 +3887,7 @@
         </is>
       </c>
       <c r="D42" s="7" t="n">
-        <v>78</v>
+        <v>82.5</v>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
@@ -3926,7 +3926,7 @@
       </c>
       <c r="N42" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O42" s="8" t="inlineStr"/>
@@ -3948,7 +3948,7 @@
         </is>
       </c>
       <c r="D43" s="7" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="N43" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O43" s="8" t="inlineStr">
@@ -4013,7 +4013,7 @@
         </is>
       </c>
       <c r="D44" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
       </c>
       <c r="N44" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O44" s="8" t="inlineStr"/>
@@ -4113,7 +4113,7 @@
       </c>
       <c r="N45" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O45" s="8" t="inlineStr">
@@ -4139,7 +4139,7 @@
         </is>
       </c>
       <c r="D46" s="7" t="n">
-        <v>6.1675</v>
+        <v>6.1715</v>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
@@ -4243,7 +4243,7 @@
       </c>
       <c r="N47" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O47" s="8" t="inlineStr">
@@ -4269,7 +4269,7 @@
         </is>
       </c>
       <c r="D48" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
       </c>
       <c r="N48" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O48" s="8" t="inlineStr"/>
@@ -4330,7 +4330,7 @@
         </is>
       </c>
       <c r="D49" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
@@ -4369,7 +4369,7 @@
       </c>
       <c r="N49" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O49" s="8" t="inlineStr"/>
@@ -4391,7 +4391,7 @@
         </is>
       </c>
       <c r="D50" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
       </c>
       <c r="N50" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O50" s="8" t="inlineStr"/>
@@ -4452,7 +4452,7 @@
         </is>
       </c>
       <c r="D51" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
       </c>
       <c r="N51" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O51" s="8" t="inlineStr"/>
@@ -4552,7 +4552,7 @@
       </c>
       <c r="N52" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O52" s="8" t="inlineStr"/>
@@ -4613,7 +4613,7 @@
       </c>
       <c r="N53" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O53" s="8" t="inlineStr">
@@ -4678,7 +4678,7 @@
       </c>
       <c r="N54" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O54" s="8" t="inlineStr"/>
@@ -4739,7 +4739,7 @@
       </c>
       <c r="N55" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O55" s="8" t="inlineStr"/>
@@ -4761,7 +4761,7 @@
         </is>
       </c>
       <c r="D56" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="N56" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O56" s="8" t="inlineStr"/>
@@ -4861,7 +4861,7 @@
       </c>
       <c r="N57" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O57" s="8" t="inlineStr"/>
@@ -4883,7 +4883,7 @@
         </is>
       </c>
       <c r="D58" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
@@ -4922,7 +4922,7 @@
       </c>
       <c r="N58" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O58" s="8" t="inlineStr">
@@ -4948,7 +4948,7 @@
         </is>
       </c>
       <c r="D59" s="7" t="n">
-        <v>70.84999999999999</v>
+        <v>70.94</v>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
       </c>
       <c r="N60" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O60" s="8" t="inlineStr"/>
@@ -5070,7 +5070,7 @@
         </is>
       </c>
       <c r="D61" s="7" t="n">
-        <v>17.81</v>
+        <v>17.77</v>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
         </is>
       </c>
       <c r="D63" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
       </c>
       <c r="N63" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O63" s="8" t="inlineStr"/>
@@ -5247,7 +5247,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G85"/>
+  <dimension ref="A1:G106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8404,6 +8404,783 @@
         </is>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B86" s="9" t="inlineStr">
+        <is>
+          <t>s1_basis_trade</t>
+        </is>
+      </c>
+      <c r="C86" s="9" t="inlineStr">
+        <is>
+          <t>Treasury basis trade (hidden leverage)</t>
+        </is>
+      </c>
+      <c r="D86" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E86" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F86" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G86" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B87" s="9" t="inlineStr">
+        <is>
+          <t>s2_japan</t>
+        </is>
+      </c>
+      <c r="C87" s="9" t="inlineStr">
+        <is>
+          <t>Japan fiscal / JGB / carry trade</t>
+        </is>
+      </c>
+      <c r="D87" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E87" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F87" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G87" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B88" s="9" t="inlineStr">
+        <is>
+          <t>s3_private_credit</t>
+        </is>
+      </c>
+      <c r="C88" s="9" t="inlineStr">
+        <is>
+          <t>Private credit's opaque expansion</t>
+        </is>
+      </c>
+      <c r="D88" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E88" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F88" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G88" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B89" s="9" t="inlineStr">
+        <is>
+          <t>s4_dev_debt</t>
+        </is>
+      </c>
+      <c r="C89" s="9" t="inlineStr">
+        <is>
+          <t>Developing-world debt crisis</t>
+        </is>
+      </c>
+      <c r="D89" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E89" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F89" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G89" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B90" s="9" t="inlineStr">
+        <is>
+          <t>s5_china_deflation</t>
+        </is>
+      </c>
+      <c r="C90" s="9" t="inlineStr">
+        <is>
+          <t>China's exported deflation</t>
+        </is>
+      </c>
+      <c r="D90" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E90" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F90" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G90" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B91" s="9" t="inlineStr">
+        <is>
+          <t>s6_rare_earths</t>
+        </is>
+      </c>
+      <c r="C91" s="9" t="inlineStr">
+        <is>
+          <t>Critical minerals as a weapon</t>
+        </is>
+      </c>
+      <c r="D91" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E91" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F91" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G91" s="9" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B92" s="9" t="inlineStr">
+        <is>
+          <t>s7_stablecoins</t>
+        </is>
+      </c>
+      <c r="C92" s="9" t="inlineStr">
+        <is>
+          <t>Stablecoins &amp; Treasury demand</t>
+        </is>
+      </c>
+      <c r="D92" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E92" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F92" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G92" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B93" s="9" t="inlineStr">
+        <is>
+          <t>s8_ai_capex</t>
+        </is>
+      </c>
+      <c r="C93" s="9" t="inlineStr">
+        <is>
+          <t>AI build-out circular financing</t>
+        </is>
+      </c>
+      <c r="D93" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E93" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F93" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G93" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B94" s="9" t="inlineStr">
+        <is>
+          <t>s9_cre</t>
+        </is>
+      </c>
+      <c r="C94" s="9" t="inlineStr">
+        <is>
+          <t>CRE maturity wall / regional banks</t>
+        </is>
+      </c>
+      <c r="D94" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E94" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F94" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G94" s="9" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B95" s="9" t="inlineStr">
+        <is>
+          <t>s10_france</t>
+        </is>
+      </c>
+      <c r="C95" s="9" t="inlineStr">
+        <is>
+          <t>France / eurozone fragility</t>
+        </is>
+      </c>
+      <c r="D95" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E95" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F95" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G95" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B96" s="9" t="inlineStr">
+        <is>
+          <t>s11_consumer_debt</t>
+        </is>
+      </c>
+      <c r="C96" s="9" t="inlineStr">
+        <is>
+          <t>Hidden consumer debt</t>
+        </is>
+      </c>
+      <c r="D96" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E96" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F96" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G96" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B97" s="9" t="inlineStr">
+        <is>
+          <t>s12_gold_dedollar</t>
+        </is>
+      </c>
+      <c r="C97" s="9" t="inlineStr">
+        <is>
+          <t>Gold / de-dollarization</t>
+        </is>
+      </c>
+      <c r="D97" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E97" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F97" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G97" s="9" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B98" s="9" t="inlineStr">
+        <is>
+          <t>s13_insurance</t>
+        </is>
+      </c>
+      <c r="C98" s="9" t="inlineStr">
+        <is>
+          <t>Insurance retreat</t>
+        </is>
+      </c>
+      <c r="D98" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E98" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F98" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G98" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B99" s="9" t="inlineStr">
+        <is>
+          <t>s14_pensions</t>
+        </is>
+      </c>
+      <c r="C99" s="9" t="inlineStr">
+        <is>
+          <t>Pensions / demographics</t>
+        </is>
+      </c>
+      <c r="D99" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E99" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F99" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G99" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B100" s="9" t="inlineStr">
+        <is>
+          <t>s15_ai_power</t>
+        </is>
+      </c>
+      <c r="C100" s="9" t="inlineStr">
+        <is>
+          <t>AI power &amp; the grid bottleneck</t>
+        </is>
+      </c>
+      <c r="D100" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E100" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F100" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G100" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B101" s="9" t="inlineStr">
+        <is>
+          <t>s16_copper</t>
+        </is>
+      </c>
+      <c r="C101" s="9" t="inlineStr">
+        <is>
+          <t>Copper &amp; the electrification deficit</t>
+        </is>
+      </c>
+      <c r="D101" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E101" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F101" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G101" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B102" s="9" t="inlineStr">
+        <is>
+          <t>s17_water</t>
+        </is>
+      </c>
+      <c r="C102" s="9" t="inlineStr">
+        <is>
+          <t>Water - the underpriced input</t>
+        </is>
+      </c>
+      <c r="D102" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E102" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F102" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G102" s="9" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B103" s="9" t="inlineStr">
+        <is>
+          <t>s18_food_fertilizer</t>
+        </is>
+      </c>
+      <c r="C103" s="9" t="inlineStr">
+        <is>
+          <t>Food &amp; fertilizer fragility</t>
+        </is>
+      </c>
+      <c r="D103" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E103" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F103" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G103" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B104" s="9" t="inlineStr">
+        <is>
+          <t>s19_lithography</t>
+        </is>
+      </c>
+      <c r="C104" s="9" t="inlineStr">
+        <is>
+          <t>The lithography (ASML) chokepoint</t>
+        </is>
+      </c>
+      <c r="D104" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E104" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F104" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G104" s="9" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B105" s="9" t="inlineStr">
+        <is>
+          <t>s20_sea_lanes</t>
+        </is>
+      </c>
+      <c r="C105" s="9" t="inlineStr">
+        <is>
+          <t>Sea lanes &amp; undersea cables</t>
+        </is>
+      </c>
+      <c r="D105" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E105" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F105" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G105" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B106" s="9" t="inlineStr">
+        <is>
+          <t>s21_clearinghouses</t>
+        </is>
+      </c>
+      <c r="C106" s="9" t="inlineStr">
+        <is>
+          <t>Clearinghouses (financial chokepoint)</t>
+        </is>
+      </c>
+      <c r="D106" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E106" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F106" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G106" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8415,7 +9192,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A26"/>
+  <dimension ref="A1:A34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -8503,7 +9280,7 @@
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t># EOD MACRO-RISK BRIEF | 2026-06-29</t>
+          <t># EOD Macro Risk Brief – 29 June 2026</t>
         </is>
       </c>
     </row>
@@ -8513,31 +9290,27 @@
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>**Headline:**</t>
+          <t>**Headline:** Overall risk steady at 5.2, but four financial-stability stories escalated to Elevated while water stress intensified across supply chains.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>Macro risk remains stable at 5.0/10 overall, with fourteen stories holding at elevated levels and no intraday shifts.</t>
-        </is>
-      </c>
+      <c r="A17" s="12" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="inlineStr"/>
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>**Changes:**</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>**Stories with Level Changes:**</t>
-        </is>
-      </c>
+      <c r="A19" s="12" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>None recorded today.</t>
+          <t>• **Treasury basis trade** (5→6): SEC central-clearing timeline slipping; hidden leverage in cash-futures arbitrage now poses acute refinancing risk if rates spike.</t>
         </is>
       </c>
     </row>
@@ -8547,31 +9320,67 @@
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>**Elevated Stories (No Change):**</t>
+          <t>• **Private credit expansion** (5→6): Widespread redemption gates now active in large funds; liquidity mismatch could force fire sales if capital calls accelerate.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>Fourteen risks remain at Elevated band, spanning financial leverage (Treasury basis trades, Japan carry, private credit, hidden consumer debt), commodity/supply vulnerabilities (China deflation, critical minerals, lithography, food/fertilizer), infrastructure constraints (AI power grid, sea lanes/cables), and structural imbalances (CRE maturity walls, developing-world debt, AI circular financing, insurance retreat). Stability in positioning suggests market participants are monitoring but not repricing these exposures materially.</t>
-        </is>
-      </c>
+      <c r="A23" s="12" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="inlineStr"/>
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>• **CRE maturity wall** (5→6): Regional-bank stress clusters emerging; concentration risk to smaller lenders exposed to office/retail rollovers into higher-rate environment.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>**Watch Priority:**</t>
-        </is>
-      </c>
+      <c r="A25" s="12" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>Japan fiscal/JGB/carry trade and AI build-out circular financing both sit at level 6—monitor for any shift that could cascade across USD funding and equity valuations.</t>
+          <t>• **Hidden consumer debt** (5→6): Subprime auto 60+ delinquencies at 6.8%; downstream strain on auto-loan securitization and regional bank credit quality.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>• **Water – underpriced input** (4→5): Acute drought in chip/farm hubs; transboundary disputes (India-Pakistan Indus) and reservoir stress create tail risk to semiconductor and agricultural output.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>• **Gold/de-dollarization** (3→4): Reserve-weaponization rhetoric escalating; long-term confidence erosion in dollar settlement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="12" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>• **Insurance retreat** (5→4): Catastrophe losses below normal; risk pricing may soften prematurely.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="12" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>**Watch:** Private credit redemption gates—gateway to systemic liquidity stress.</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-06-29  -  generated 2026-06-29 17:42 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-06-29  -  generated 2026-06-29 18:28 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -1383,11 +1383,11 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>SOFR minus EFFR (bps)</t>
+          <t>SOFR minus EFFR (%)</t>
         </is>
       </c>
       <c r="D2" s="7" t="n">
-        <v>0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="N2" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O2" s="8" t="inlineStr">
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>161.956</v>
+        <v>161.933</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -1769,11 +1769,11 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>US high-yield OAS (bps)</t>
+          <t>US high-yield OAS (%, ≈310bps)</t>
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>3.1</v>
+        <v>2.83</v>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
       </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O8" s="8" t="inlineStr">
@@ -1964,7 +1964,7 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>121</v>
+        <v>120.3958</v>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O11" s="8" t="inlineStr">
@@ -2029,7 +2029,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>2</v>
+        <v>2.19</v>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O12" s="8" t="inlineStr"/>
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>6.7849</v>
+        <v>6.7839</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.1</v>
+        <v>0.17</v>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
       </c>
       <c r="N20" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O20" s="8" t="inlineStr">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>280</v>
+        <v>325</v>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O21" s="8" t="inlineStr">
@@ -2704,11 +2704,11 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>US investment-grade OAS (bps) - big-issuer proxy</t>
+          <t>US investment-grade OAS (%) - big-issuer proxy</t>
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>0.95</v>
+        <v>0.77</v>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
       </c>
       <c r="N23" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O23" s="8" t="inlineStr">
@@ -3017,11 +3017,11 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>OAT-Bund 10y spread (bps)</t>
+          <t>OAT-Bund 10y spread (%)</t>
         </is>
       </c>
       <c r="D28" s="7" t="n">
-        <v>0.72</v>
+        <v>0.6951000000000001</v>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
@@ -3060,12 +3060,12 @@
       </c>
       <c r="N28" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O28" s="8" t="inlineStr">
         <is>
-          <t>FRED rates in percent; spread shown in pp (0.72 = 72bps).</t>
+          <t>FRED rates in percent; spread shown in percentage points (0.72% = 72bps).</t>
         </is>
       </c>
     </row>
@@ -3269,7 +3269,7 @@
         </is>
       </c>
       <c r="D32" s="7" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
       </c>
       <c r="N32" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O32" s="8" t="inlineStr">
@@ -3395,7 +3395,7 @@
         </is>
       </c>
       <c r="D34" s="7" t="n">
-        <v>4044.8999</v>
+        <v>4038.3</v>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         </is>
       </c>
       <c r="D38" s="7" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
@@ -3682,7 +3682,7 @@
       </c>
       <c r="N38" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>live</t>
         </is>
       </c>
       <c r="O38" s="8" t="inlineStr"/>
@@ -3887,7 +3887,7 @@
         </is>
       </c>
       <c r="D42" s="7" t="n">
-        <v>82.5</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
         </is>
       </c>
       <c r="D46" s="7" t="n">
-        <v>6.1715</v>
+        <v>6.1765</v>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="D53" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         </is>
       </c>
       <c r="D54" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         </is>
       </c>
       <c r="D57" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         </is>
       </c>
       <c r="D58" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
@@ -4948,7 +4948,7 @@
         </is>
       </c>
       <c r="D59" s="7" t="n">
-        <v>70.94</v>
+        <v>70.88</v>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         </is>
       </c>
       <c r="D61" s="7" t="n">
-        <v>17.77</v>
+        <v>17.69</v>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G106"/>
+  <dimension ref="A1:G127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9181,6 +9181,783 @@
         </is>
       </c>
     </row>
+    <row r="107">
+      <c r="A107" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B107" s="9" t="inlineStr">
+        <is>
+          <t>s1_basis_trade</t>
+        </is>
+      </c>
+      <c r="C107" s="9" t="inlineStr">
+        <is>
+          <t>Treasury basis trade (hidden leverage)</t>
+        </is>
+      </c>
+      <c r="D107" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E107" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F107" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G107" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B108" s="9" t="inlineStr">
+        <is>
+          <t>s2_japan</t>
+        </is>
+      </c>
+      <c r="C108" s="9" t="inlineStr">
+        <is>
+          <t>Japan fiscal / JGB / carry trade</t>
+        </is>
+      </c>
+      <c r="D108" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E108" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F108" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G108" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B109" s="9" t="inlineStr">
+        <is>
+          <t>s3_private_credit</t>
+        </is>
+      </c>
+      <c r="C109" s="9" t="inlineStr">
+        <is>
+          <t>Private credit's opaque expansion</t>
+        </is>
+      </c>
+      <c r="D109" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E109" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F109" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G109" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B110" s="9" t="inlineStr">
+        <is>
+          <t>s4_dev_debt</t>
+        </is>
+      </c>
+      <c r="C110" s="9" t="inlineStr">
+        <is>
+          <t>Developing-world debt crisis</t>
+        </is>
+      </c>
+      <c r="D110" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E110" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F110" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G110" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B111" s="9" t="inlineStr">
+        <is>
+          <t>s5_china_deflation</t>
+        </is>
+      </c>
+      <c r="C111" s="9" t="inlineStr">
+        <is>
+          <t>China's exported deflation</t>
+        </is>
+      </c>
+      <c r="D111" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E111" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F111" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G111" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B112" s="9" t="inlineStr">
+        <is>
+          <t>s6_rare_earths</t>
+        </is>
+      </c>
+      <c r="C112" s="9" t="inlineStr">
+        <is>
+          <t>Critical minerals as a weapon</t>
+        </is>
+      </c>
+      <c r="D112" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E112" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F112" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G112" s="9" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B113" s="9" t="inlineStr">
+        <is>
+          <t>s7_stablecoins</t>
+        </is>
+      </c>
+      <c r="C113" s="9" t="inlineStr">
+        <is>
+          <t>Stablecoins &amp; Treasury demand</t>
+        </is>
+      </c>
+      <c r="D113" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E113" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F113" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G113" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B114" s="9" t="inlineStr">
+        <is>
+          <t>s8_ai_capex</t>
+        </is>
+      </c>
+      <c r="C114" s="9" t="inlineStr">
+        <is>
+          <t>AI build-out circular financing</t>
+        </is>
+      </c>
+      <c r="D114" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E114" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F114" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G114" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B115" s="9" t="inlineStr">
+        <is>
+          <t>s9_cre</t>
+        </is>
+      </c>
+      <c r="C115" s="9" t="inlineStr">
+        <is>
+          <t>CRE maturity wall / regional banks</t>
+        </is>
+      </c>
+      <c r="D115" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E115" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F115" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G115" s="9" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B116" s="9" t="inlineStr">
+        <is>
+          <t>s10_france</t>
+        </is>
+      </c>
+      <c r="C116" s="9" t="inlineStr">
+        <is>
+          <t>France / eurozone fragility</t>
+        </is>
+      </c>
+      <c r="D116" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E116" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F116" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G116" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B117" s="9" t="inlineStr">
+        <is>
+          <t>s11_consumer_debt</t>
+        </is>
+      </c>
+      <c r="C117" s="9" t="inlineStr">
+        <is>
+          <t>Hidden consumer debt</t>
+        </is>
+      </c>
+      <c r="D117" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E117" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F117" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G117" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B118" s="9" t="inlineStr">
+        <is>
+          <t>s12_gold_dedollar</t>
+        </is>
+      </c>
+      <c r="C118" s="9" t="inlineStr">
+        <is>
+          <t>Gold / de-dollarization</t>
+        </is>
+      </c>
+      <c r="D118" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E118" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F118" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G118" s="9" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B119" s="9" t="inlineStr">
+        <is>
+          <t>s13_insurance</t>
+        </is>
+      </c>
+      <c r="C119" s="9" t="inlineStr">
+        <is>
+          <t>Insurance retreat</t>
+        </is>
+      </c>
+      <c r="D119" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E119" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F119" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G119" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B120" s="9" t="inlineStr">
+        <is>
+          <t>s14_pensions</t>
+        </is>
+      </c>
+      <c r="C120" s="9" t="inlineStr">
+        <is>
+          <t>Pensions / demographics</t>
+        </is>
+      </c>
+      <c r="D120" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E120" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F120" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G120" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B121" s="9" t="inlineStr">
+        <is>
+          <t>s15_ai_power</t>
+        </is>
+      </c>
+      <c r="C121" s="9" t="inlineStr">
+        <is>
+          <t>AI power &amp; the grid bottleneck</t>
+        </is>
+      </c>
+      <c r="D121" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E121" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F121" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G121" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B122" s="9" t="inlineStr">
+        <is>
+          <t>s16_copper</t>
+        </is>
+      </c>
+      <c r="C122" s="9" t="inlineStr">
+        <is>
+          <t>Copper &amp; the electrification deficit</t>
+        </is>
+      </c>
+      <c r="D122" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E122" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F122" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G122" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B123" s="9" t="inlineStr">
+        <is>
+          <t>s17_water</t>
+        </is>
+      </c>
+      <c r="C123" s="9" t="inlineStr">
+        <is>
+          <t>Water - the underpriced input</t>
+        </is>
+      </c>
+      <c r="D123" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E123" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F123" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G123" s="9" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B124" s="9" t="inlineStr">
+        <is>
+          <t>s18_food_fertilizer</t>
+        </is>
+      </c>
+      <c r="C124" s="9" t="inlineStr">
+        <is>
+          <t>Food &amp; fertilizer fragility</t>
+        </is>
+      </c>
+      <c r="D124" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E124" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F124" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G124" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B125" s="9" t="inlineStr">
+        <is>
+          <t>s19_lithography</t>
+        </is>
+      </c>
+      <c r="C125" s="9" t="inlineStr">
+        <is>
+          <t>The lithography (ASML) chokepoint</t>
+        </is>
+      </c>
+      <c r="D125" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E125" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F125" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G125" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B126" s="9" t="inlineStr">
+        <is>
+          <t>s20_sea_lanes</t>
+        </is>
+      </c>
+      <c r="C126" s="9" t="inlineStr">
+        <is>
+          <t>Sea lanes &amp; undersea cables</t>
+        </is>
+      </c>
+      <c r="D126" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E126" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F126" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G126" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B127" s="9" t="inlineStr">
+        <is>
+          <t>s21_clearinghouses</t>
+        </is>
+      </c>
+      <c r="C127" s="9" t="inlineStr">
+        <is>
+          <t>Clearinghouses (financial chokepoint)</t>
+        </is>
+      </c>
+      <c r="D127" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E127" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F127" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G127" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9192,7 +9969,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A34"/>
+  <dimension ref="A1:A22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -9280,7 +10057,7 @@
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t># EOD Macro Risk Brief – 29 June 2026</t>
+          <t># EOD MACRO-RISK BRIEF | 2026-06-29</t>
         </is>
       </c>
     </row>
@@ -9290,7 +10067,7 @@
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>**Headline:** Overall risk steady at 5.2, but four financial-stability stories escalated to Elevated while water stress intensified across supply chains.</t>
+          <t>**Headline:** Overall risk stable at 5.2, but food-supply vulnerability escalated to High amid simultaneous China export controls and Gulf disruption.</t>
         </is>
       </c>
     </row>
@@ -9300,87 +10077,31 @@
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>**Changes:**</t>
+          <t>**Level Changes:**</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr"/>
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>• **Food &amp; fertilizer fragility** (6→7, now High): China tightened fertilizer export curbs (vs. baseline in-place status) and Hormuz/Gulf transit shifted from disrupted to cut, creating dual-source shock to global input availability.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
-          <t>• **Treasury basis trade** (5→6): SEC central-clearing timeline slipping; hidden leverage in cash-futures arbitrage now poses acute refinancing risk if rates spike.</t>
-        </is>
-      </c>
+      <c r="A20" s="12" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr"/>
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>**Watch Most Closely:**</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>• **Private credit expansion** (5→6): Widespread redemption gates now active in large funds; liquidity mismatch could force fire sales if capital calls accelerate.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="12" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="12" t="inlineStr">
-        <is>
-          <t>• **CRE maturity wall** (5→6): Regional-bank stress clusters emerging; concentration risk to smaller lenders exposed to office/retail rollovers into higher-rate environment.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="12" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="12" t="inlineStr">
-        <is>
-          <t>• **Hidden consumer debt** (5→6): Subprime auto 60+ delinquencies at 6.8%; downstream strain on auto-loan securitization and regional bank credit quality.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="12" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="12" t="inlineStr">
-        <is>
-          <t>• **Water – underpriced input** (4→5): Acute drought in chip/farm hubs; transboundary disputes (India-Pakistan Indus) and reservoir stress create tail risk to semiconductor and agricultural output.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="12" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="12" t="inlineStr">
-        <is>
-          <t>• **Gold/de-dollarization** (3→4): Reserve-weaponization rhetoric escalating; long-term confidence erosion in dollar settlement.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="12" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="12" t="inlineStr">
-        <is>
-          <t>• **Insurance retreat** (5→4): Catastrophe losses below normal; risk pricing may soften prematurely.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="12" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="12" t="inlineStr">
-        <is>
-          <t>**Watch:** Private credit redemption gates—gateway to systemic liquidity stress.</t>
+          <t>Food &amp; fertilizer fragility at Level 7—simultaneous export controls and chokepoint closure compress near-term planting and harvest cycles with limited substitution windows.</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-06-29  -  generated 2026-06-29 18:28 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-06-29  -  generated 2026-06-29 19:07 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>161.933</v>
+        <v>161.951</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>2.73</v>
+        <v>2</v>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>6.7839</v>
+        <v>6.7868</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>325</v>
+        <v>310</v>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
@@ -3395,7 +3395,7 @@
         </is>
       </c>
       <c r="D34" s="7" t="n">
-        <v>4038.3</v>
+        <v>4032.2</v>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
         </is>
       </c>
       <c r="D46" s="7" t="n">
-        <v>6.1765</v>
+        <v>6.178</v>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
         </is>
       </c>
       <c r="D49" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="D53" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         </is>
       </c>
       <c r="D57" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         </is>
       </c>
       <c r="D58" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
@@ -4948,7 +4948,7 @@
         </is>
       </c>
       <c r="D59" s="7" t="n">
-        <v>70.88</v>
+        <v>70.53</v>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="D60" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         </is>
       </c>
       <c r="D61" s="7" t="n">
-        <v>17.69</v>
+        <v>17.61</v>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G127"/>
+  <dimension ref="A1:G148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9958,6 +9958,783 @@
         </is>
       </c>
     </row>
+    <row r="128">
+      <c r="A128" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B128" s="9" t="inlineStr">
+        <is>
+          <t>s1_basis_trade</t>
+        </is>
+      </c>
+      <c r="C128" s="9" t="inlineStr">
+        <is>
+          <t>Treasury basis trade (hidden leverage)</t>
+        </is>
+      </c>
+      <c r="D128" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E128" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F128" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G128" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B129" s="9" t="inlineStr">
+        <is>
+          <t>s2_japan</t>
+        </is>
+      </c>
+      <c r="C129" s="9" t="inlineStr">
+        <is>
+          <t>Japan fiscal / JGB / carry trade</t>
+        </is>
+      </c>
+      <c r="D129" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E129" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F129" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G129" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B130" s="9" t="inlineStr">
+        <is>
+          <t>s3_private_credit</t>
+        </is>
+      </c>
+      <c r="C130" s="9" t="inlineStr">
+        <is>
+          <t>Private credit's opaque expansion</t>
+        </is>
+      </c>
+      <c r="D130" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E130" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F130" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G130" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B131" s="9" t="inlineStr">
+        <is>
+          <t>s4_dev_debt</t>
+        </is>
+      </c>
+      <c r="C131" s="9" t="inlineStr">
+        <is>
+          <t>Developing-world debt crisis</t>
+        </is>
+      </c>
+      <c r="D131" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E131" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F131" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G131" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B132" s="9" t="inlineStr">
+        <is>
+          <t>s5_china_deflation</t>
+        </is>
+      </c>
+      <c r="C132" s="9" t="inlineStr">
+        <is>
+          <t>China's exported deflation</t>
+        </is>
+      </c>
+      <c r="D132" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E132" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F132" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G132" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B133" s="9" t="inlineStr">
+        <is>
+          <t>s6_rare_earths</t>
+        </is>
+      </c>
+      <c r="C133" s="9" t="inlineStr">
+        <is>
+          <t>Critical minerals as a weapon</t>
+        </is>
+      </c>
+      <c r="D133" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E133" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F133" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G133" s="9" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B134" s="9" t="inlineStr">
+        <is>
+          <t>s7_stablecoins</t>
+        </is>
+      </c>
+      <c r="C134" s="9" t="inlineStr">
+        <is>
+          <t>Stablecoins &amp; Treasury demand</t>
+        </is>
+      </c>
+      <c r="D134" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E134" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F134" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G134" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B135" s="9" t="inlineStr">
+        <is>
+          <t>s8_ai_capex</t>
+        </is>
+      </c>
+      <c r="C135" s="9" t="inlineStr">
+        <is>
+          <t>AI build-out circular financing</t>
+        </is>
+      </c>
+      <c r="D135" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E135" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F135" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G135" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B136" s="9" t="inlineStr">
+        <is>
+          <t>s9_cre</t>
+        </is>
+      </c>
+      <c r="C136" s="9" t="inlineStr">
+        <is>
+          <t>CRE maturity wall / regional banks</t>
+        </is>
+      </c>
+      <c r="D136" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E136" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F136" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G136" s="9" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B137" s="9" t="inlineStr">
+        <is>
+          <t>s10_france</t>
+        </is>
+      </c>
+      <c r="C137" s="9" t="inlineStr">
+        <is>
+          <t>France / eurozone fragility</t>
+        </is>
+      </c>
+      <c r="D137" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E137" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F137" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G137" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B138" s="9" t="inlineStr">
+        <is>
+          <t>s11_consumer_debt</t>
+        </is>
+      </c>
+      <c r="C138" s="9" t="inlineStr">
+        <is>
+          <t>Hidden consumer debt</t>
+        </is>
+      </c>
+      <c r="D138" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E138" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F138" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G138" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B139" s="9" t="inlineStr">
+        <is>
+          <t>s12_gold_dedollar</t>
+        </is>
+      </c>
+      <c r="C139" s="9" t="inlineStr">
+        <is>
+          <t>Gold / de-dollarization</t>
+        </is>
+      </c>
+      <c r="D139" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E139" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F139" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G139" s="9" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B140" s="9" t="inlineStr">
+        <is>
+          <t>s13_insurance</t>
+        </is>
+      </c>
+      <c r="C140" s="9" t="inlineStr">
+        <is>
+          <t>Insurance retreat</t>
+        </is>
+      </c>
+      <c r="D140" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E140" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F140" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G140" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B141" s="9" t="inlineStr">
+        <is>
+          <t>s14_pensions</t>
+        </is>
+      </c>
+      <c r="C141" s="9" t="inlineStr">
+        <is>
+          <t>Pensions / demographics</t>
+        </is>
+      </c>
+      <c r="D141" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E141" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F141" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G141" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B142" s="9" t="inlineStr">
+        <is>
+          <t>s15_ai_power</t>
+        </is>
+      </c>
+      <c r="C142" s="9" t="inlineStr">
+        <is>
+          <t>AI power &amp; the grid bottleneck</t>
+        </is>
+      </c>
+      <c r="D142" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E142" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F142" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G142" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B143" s="9" t="inlineStr">
+        <is>
+          <t>s16_copper</t>
+        </is>
+      </c>
+      <c r="C143" s="9" t="inlineStr">
+        <is>
+          <t>Copper &amp; the electrification deficit</t>
+        </is>
+      </c>
+      <c r="D143" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E143" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F143" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G143" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B144" s="9" t="inlineStr">
+        <is>
+          <t>s17_water</t>
+        </is>
+      </c>
+      <c r="C144" s="9" t="inlineStr">
+        <is>
+          <t>Water - the underpriced input</t>
+        </is>
+      </c>
+      <c r="D144" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E144" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F144" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G144" s="9" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B145" s="9" t="inlineStr">
+        <is>
+          <t>s18_food_fertilizer</t>
+        </is>
+      </c>
+      <c r="C145" s="9" t="inlineStr">
+        <is>
+          <t>Food &amp; fertilizer fragility</t>
+        </is>
+      </c>
+      <c r="D145" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E145" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F145" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G145" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B146" s="9" t="inlineStr">
+        <is>
+          <t>s19_lithography</t>
+        </is>
+      </c>
+      <c r="C146" s="9" t="inlineStr">
+        <is>
+          <t>The lithography (ASML) chokepoint</t>
+        </is>
+      </c>
+      <c r="D146" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E146" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F146" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G146" s="9" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B147" s="9" t="inlineStr">
+        <is>
+          <t>s20_sea_lanes</t>
+        </is>
+      </c>
+      <c r="C147" s="9" t="inlineStr">
+        <is>
+          <t>Sea lanes &amp; undersea cables</t>
+        </is>
+      </c>
+      <c r="D147" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E147" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F147" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G147" s="9" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B148" s="9" t="inlineStr">
+        <is>
+          <t>s21_clearinghouses</t>
+        </is>
+      </c>
+      <c r="C148" s="9" t="inlineStr">
+        <is>
+          <t>Clearinghouses (financial chokepoint)</t>
+        </is>
+      </c>
+      <c r="D148" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E148" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F148" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G148" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9969,7 +10746,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A22"/>
+  <dimension ref="A1:A24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -10057,51 +10834,65 @@
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t># EOD MACRO-RISK BRIEF | 2026-06-29</t>
+          <t>**HEADLINE**</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr"/>
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>Macro risk remains steady at 5.2/10 with 14 stories in elevated band; one commodity pressure eased.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>**Headline:** Overall risk stable at 5.2, but food-supply vulnerability escalated to High amid simultaneous China export controls and Gulf disruption.</t>
-        </is>
-      </c>
+      <c r="A16" s="12" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr"/>
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>**LEVEL CHANGES**</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>**Level Changes:**</t>
+          <t>• **Food &amp; fertilizer fragility** (7→6): Hormuz/Gulf fertilizer disruption downgraded from "cut" to "disrupted" status, reducing acute supply-chain shock risk but leaving input chains strained.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>• **Food &amp; fertilizer fragility** (6→7, now High): China tightened fertilizer export curbs (vs. baseline in-place status) and Hormuz/Gulf transit shifted from disrupted to cut, creating dual-source shock to global input availability.</t>
-        </is>
-      </c>
+      <c r="A19" s="12" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr"/>
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>**ELEVATED-RISK WATCH LIST**</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>**Watch Most Closely:**</t>
+          <t>Fourteen stories remain at elevated (5–6/10): Treasury basis trades, Japan JGB/carry mechanics, private credit opacity, China deflation export, critical minerals weaponization, AI circular financing, CRE maturity walls, hidden consumer debt, AI power-grid bottlenecks, ASML lithography chokepoint, and sea-lane vulnerabilities all pose material contagion risk.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t>Food &amp; fertilizer fragility at Level 7—simultaneous export controls and chokepoint closure compress near-term planting and harvest cycles with limited substitution windows.</t>
+      <c r="A22" s="12" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>**TOP WATCH**</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>Treasury basis trade (6/10) and Japan fiscal/carry unwind (6/10) carry highest leverage and cross-market interconnection risk.</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-06-29  -  generated 2026-06-29 19:07 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-06-30  -  generated 2026-06-30 12:25 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -677,7 +677,7 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>China's exported deflation</t>
+          <t>China's price spillover (deflation or cost-push)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -1273,7 +1273,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O63"/>
+  <dimension ref="A1:O64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>161.951</v>
+        <v>162.424</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>2</v>
+        <v>2.73</v>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>120.3958</v>
+        <v>120.8866</v>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>China's exported deflation</t>
+          <t>China's price spillover (deflation or cost-push)</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>China PPI YoY (%) - more negative is worse</t>
+          <t>China PPI YoY (%) - large swing either way is worse</t>
         </is>
       </c>
       <c r="D14" s="7" t="n">
@@ -2155,14 +2155,14 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>lower_worse</t>
+          <t>two_sided</t>
         </is>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-3</v>
+        <v>4</v>
       </c>
       <c r="H14" s="4" t="n">
         <v>1</v>
@@ -2198,7 +2198,7 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>China's exported deflation</t>
+          <t>China's price spillover (deflation or cost-push)</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>6.7868</v>
+        <v>6.774</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>China's exported deflation</t>
+          <t>China's price spillover (deflation or cost-push)</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -2452,11 +2452,11 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Ex-China heavy rare-earth price premium (x China)</t>
+          <t>US domestic RE producer blacklist (0 none / 1 entity-specific ban / 2 sector-wide ban)</t>
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>4.5</v>
+        <v>1</v>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
@@ -2464,20 +2464,20 @@
         </is>
       </c>
       <c r="F19" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I19" s="4">
         <f>IF(D19&lt;=F19,0,IF(D19&lt;=G19,1,2))</f>
         <v/>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K19" s="4">
         <f>J19*(I19-H19)/2</f>
@@ -2490,7 +2490,7 @@
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>event</t>
         </is>
       </c>
       <c r="N19" s="4" t="inlineStr">
@@ -2503,21 +2503,21 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Stablecoins &amp; Treasury demand</t>
+          <t>Critical minerals as a weapon</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>s7_stablecoins</t>
+          <t>s6_rare_earths</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Largest stablecoin max peg deviation (%)</t>
+          <t>Ex-China heavy rare-earth price premium (x China)</t>
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.17</v>
+        <v>4.5</v>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
@@ -2525,20 +2525,20 @@
         </is>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" s="4">
         <f>IF(D20&lt;=F20,0,IF(D20&lt;=G20,1,2))</f>
         <v/>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="K20" s="4">
         <f>J20*(I20-H20)/2</f>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="N20" s="4" t="inlineStr">
@@ -2559,11 +2559,7 @@
           <t>live</t>
         </is>
       </c>
-      <c r="O20" s="8" t="inlineStr">
-        <is>
-          <t>USDC briefly hit ~$0.87 (13%) in Mar 2023.</t>
-        </is>
-      </c>
+      <c r="O20" s="8" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -2578,11 +2574,11 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Total USD stablecoin supply ($bn)</t>
+          <t>Largest stablecoin max peg deviation (%)</t>
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>310</v>
+        <v>0.167</v>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
@@ -2590,10 +2586,10 @@
         </is>
       </c>
       <c r="F21" s="4" t="n">
-        <v>350</v>
+        <v>0.5</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>600</v>
+        <v>2</v>
       </c>
       <c r="H21" s="4" t="n">
         <v>0</v>
@@ -2603,7 +2599,7 @@
         <v/>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="K21" s="4">
         <f>J21*(I21-H21)/2</f>
@@ -2616,7 +2612,7 @@
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="N21" s="4" t="inlineStr">
@@ -2626,7 +2622,7 @@
       </c>
       <c r="O21" s="8" t="inlineStr">
         <is>
-          <t>Bigger = more T-bill demand AND more run risk.</t>
+          <t>USDC briefly hit ~$0.87 (13%) in Mar 2023.</t>
         </is>
       </c>
     </row>
@@ -2643,11 +2639,11 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>GENIUS implementation friction (0 smooth / 1 gaps / 2 problems)</t>
+          <t>Total USD stablecoin supply ($bn)</t>
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>1</v>
+        <v>322</v>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
@@ -2655,10 +2651,10 @@
         </is>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1</v>
+        <v>600</v>
       </c>
       <c r="H22" s="4" t="n">
         <v>0</v>
@@ -2681,7 +2677,7 @@
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="N22" s="4" t="inlineStr">
@@ -2689,26 +2685,30 @@
           <t>live</t>
         </is>
       </c>
-      <c r="O22" s="8" t="inlineStr"/>
+      <c r="O22" s="8" t="inlineStr">
+        <is>
+          <t>Bigger = more T-bill demand AND more run risk.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>AI build-out circular financing</t>
+          <t>Stablecoins &amp; Treasury demand</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>s8_ai_capex</t>
+          <t>s7_stablecoins</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>US investment-grade OAS (%) - big-issuer proxy</t>
+          <t>GENIUS implementation friction (0 smooth / 1 gaps / 2 problems)</t>
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>0.77</v>
+        <v>1</v>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
@@ -2716,10 +2716,10 @@
         </is>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="H23" s="4" t="n">
         <v>0</v>
@@ -2729,7 +2729,7 @@
         <v/>
       </c>
       <c r="J23" s="4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K23" s="4">
         <f>J23*(I23-H23)/2</f>
@@ -2737,12 +2737,12 @@
       </c>
       <c r="L23" s="8" t="inlineStr">
         <is>
-          <t>fred:BAMLC0A0CM</t>
+          <t>manual</t>
         </is>
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>event</t>
         </is>
       </c>
       <c r="N23" s="4" t="inlineStr">
@@ -2750,11 +2750,7 @@
           <t>live</t>
         </is>
       </c>
-      <c r="O23" s="8" t="inlineStr">
-        <is>
-          <t>FRED in percent; 1.0 = 100bps.</t>
-        </is>
-      </c>
+      <c r="O23" s="8" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -2769,11 +2765,11 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>AI capex-vs-revenue gap concern (0 closing / 1 wide / 2 widening fast)</t>
+          <t>US investment-grade OAS (%) - big-issuer proxy</t>
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>1</v>
+        <v>0.77</v>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
@@ -2781,13 +2777,13 @@
         </is>
       </c>
       <c r="F24" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H24" s="4" t="n">
         <v>0</v>
-      </c>
-      <c r="G24" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H24" s="4" t="n">
-        <v>1</v>
       </c>
       <c r="I24" s="4">
         <f>IF(D24&lt;=F24,0,IF(D24&lt;=G24,1,2))</f>
@@ -2802,12 +2798,12 @@
       </c>
       <c r="L24" s="8" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>fred:BAMLC0A0CM</t>
         </is>
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="N24" s="4" t="inlineStr">
@@ -2815,7 +2811,11 @@
           <t>live</t>
         </is>
       </c>
-      <c r="O24" s="8" t="inlineStr"/>
+      <c r="O24" s="8" t="inlineStr">
+        <is>
+          <t>FRED in percent; 1.0 = 100bps.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>GPU-backed debt refinancing stress (0 none / 1 signs / 2 acute)</t>
+          <t>AI capex-vs-revenue gap concern (0 closing / 1 wide / 2 widening fast)</t>
         </is>
       </c>
       <c r="D25" s="7" t="n">
@@ -2848,7 +2848,7 @@
         <v>1</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" s="4">
         <f>IF(D25&lt;=F25,0,IF(D25&lt;=G25,1,2))</f>
@@ -2868,7 +2868,7 @@
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="N25" s="4" t="inlineStr">
@@ -2881,21 +2881,21 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>CRE maturity wall / regional banks</t>
+          <t>AI build-out circular financing</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>s9_cre</t>
+          <t>s8_ai_capex</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>CMBS office delinquency rate (%)</t>
+          <t>GPU-backed debt refinancing stress (0 none / 1 signs / 2 acute)</t>
         </is>
       </c>
       <c r="D26" s="7" t="n">
-        <v>12.34</v>
+        <v>1</v>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
@@ -2903,13 +2903,13 @@
         </is>
       </c>
       <c r="F26" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I26" s="4">
         <f>IF(D26&lt;=F26,0,IF(D26&lt;=G26,1,2))</f>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>event</t>
         </is>
       </c>
       <c r="N26" s="4" t="inlineStr">
@@ -2937,11 +2937,7 @@
           <t>live</t>
         </is>
       </c>
-      <c r="O26" s="8" t="inlineStr">
-        <is>
-          <t>Record 12.34% Jan 2026 (Trepp; paid feed).</t>
-        </is>
-      </c>
+      <c r="O26" s="8" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -2956,11 +2952,11 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Regional-bank CRE stress (0 calm / 1 isolated / 2 cluster)</t>
+          <t>CMBS office delinquency rate (%)</t>
         </is>
       </c>
       <c r="D27" s="7" t="n">
-        <v>1</v>
+        <v>11.2</v>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
@@ -2968,20 +2964,20 @@
         </is>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I27" s="4">
         <f>IF(D27&lt;=F27,0,IF(D27&lt;=G27,1,2))</f>
         <v/>
       </c>
       <c r="J27" s="4" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="K27" s="4">
         <f>J27*(I27-H27)/2</f>
@@ -2994,7 +2990,7 @@
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
@@ -3002,26 +2998,30 @@
           <t>live</t>
         </is>
       </c>
-      <c r="O27" s="8" t="inlineStr"/>
+      <c r="O27" s="8" t="inlineStr">
+        <is>
+          <t>Record 12.34% Jan 2026 (Trepp; paid feed).</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>France / eurozone fragility</t>
+          <t>CRE maturity wall / regional banks</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>s10_france</t>
+          <t>s9_cre</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>OAT-Bund 10y spread (%)</t>
+          <t>Regional-bank CRE stress (0 calm / 1 isolated / 2 cluster)</t>
         </is>
       </c>
       <c r="D28" s="7" t="n">
-        <v>0.6951000000000001</v>
+        <v>1</v>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
@@ -3029,20 +3029,20 @@
         </is>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I28" s="4">
         <f>IF(D28&lt;=F28,0,IF(D28&lt;=G28,1,2))</f>
         <v/>
       </c>
       <c r="J28" s="4" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="K28" s="4">
         <f>J28*(I28-H28)/2</f>
@@ -3050,12 +3050,12 @@
       </c>
       <c r="L28" s="8" t="inlineStr">
         <is>
-          <t>fred_spread:IRLTLT01FRM156N:IRLTLT01DEM156N</t>
+          <t>manual</t>
         </is>
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>event</t>
         </is>
       </c>
       <c r="N28" s="4" t="inlineStr">
@@ -3063,11 +3063,7 @@
           <t>live</t>
         </is>
       </c>
-      <c r="O28" s="8" t="inlineStr">
-        <is>
-          <t>FRED rates in percent; spread shown in percentage points (0.72% = 72bps).</t>
-        </is>
-      </c>
+      <c r="O28" s="8" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -3082,11 +3078,11 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Govt stability (0 stable / 1 fragile / 2 collapse-or-snap-election)</t>
+          <t>OAT-Bund 10y spread (%)</t>
         </is>
       </c>
       <c r="D29" s="7" t="n">
-        <v>1</v>
+        <v>0.6951000000000001</v>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
@@ -3094,10 +3090,10 @@
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="H29" s="4" t="n">
         <v>1</v>
@@ -3115,12 +3111,12 @@
       </c>
       <c r="L29" s="8" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>fred_spread:IRLTLT01FRM156N:IRLTLT01DEM156N</t>
         </is>
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="N29" s="4" t="inlineStr">
@@ -3128,7 +3124,11 @@
           <t>live</t>
         </is>
       </c>
-      <c r="O29" s="8" t="inlineStr"/>
+      <c r="O29" s="8" t="inlineStr">
+        <is>
+          <t>FRED rates in percent; spread shown in percentage points (0.72% = 72bps).</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Rating action (0 stable / 1 negative outlook / 2 downgrade)</t>
+          <t>Govt stability (0 stable / 1 fragile / 2 collapse-or-snap-election)</t>
         </is>
       </c>
       <c r="D30" s="7" t="n">
@@ -3161,7 +3161,7 @@
         <v>1</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30" s="4">
         <f>IF(D30&lt;=F30,0,IF(D30&lt;=G30,1,2))</f>
@@ -3194,21 +3194,21 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>Hidden consumer debt</t>
+          <t>France / eurozone fragility</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>s11_consumer_debt</t>
+          <t>s10_france</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Subprime auto 60+ day delinquency (%)</t>
+          <t>Rating action (0 stable / 1 negative outlook / 2 downgrade)</t>
         </is>
       </c>
       <c r="D31" s="7" t="n">
-        <v>6.8</v>
+        <v>2</v>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
@@ -3216,13 +3216,13 @@
         </is>
       </c>
       <c r="F31" s="4" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>6.5</v>
+        <v>1</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I31" s="4">
         <f>IF(D31&lt;=F31,0,IF(D31&lt;=G31,1,2))</f>
@@ -3242,7 +3242,7 @@
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>event</t>
         </is>
       </c>
       <c r="N31" s="4" t="inlineStr">
@@ -3265,11 +3265,11 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>US unemployment rate (%)</t>
+          <t>Subprime auto 60+ day delinquency (%)</t>
         </is>
       </c>
       <c r="D32" s="7" t="n">
-        <v>4.3</v>
+        <v>6.11</v>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="F32" s="4" t="n">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>4.8</v>
+        <v>6.5</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32" s="4">
         <f>IF(D32&lt;=F32,0,IF(D32&lt;=G32,1,2))</f>
@@ -3298,7 +3298,7 @@
       </c>
       <c r="L32" s="8" t="inlineStr">
         <is>
-          <t>fred:UNRATE</t>
+          <t>manual</t>
         </is>
       </c>
       <c r="M32" s="4" t="inlineStr">
@@ -3311,11 +3311,7 @@
           <t>live</t>
         </is>
       </c>
-      <c r="O32" s="8" t="inlineStr">
-        <is>
-          <t>The key accelerant for consumer stress.</t>
-        </is>
-      </c>
+      <c r="O32" s="8" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -3330,11 +3326,11 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>BNPL delinquency trend (0 stable / 1 rising / 2 spiking)</t>
+          <t>US unemployment rate (%)</t>
         </is>
       </c>
       <c r="D33" s="7" t="n">
-        <v>1</v>
+        <v>4.3</v>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
@@ -3342,20 +3338,20 @@
         </is>
       </c>
       <c r="F33" s="4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H33" s="4" t="n">
         <v>0</v>
-      </c>
-      <c r="G33" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H33" s="4" t="n">
-        <v>1</v>
       </c>
       <c r="I33" s="4">
         <f>IF(D33&lt;=F33,0,IF(D33&lt;=G33,1,2))</f>
         <v/>
       </c>
       <c r="J33" s="4" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K33" s="4">
         <f>J33*(I33-H33)/2</f>
@@ -3363,12 +3359,12 @@
       </c>
       <c r="L33" s="8" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>fred:UNRATE</t>
         </is>
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="N33" s="4" t="inlineStr">
@@ -3376,26 +3372,30 @@
           <t>live</t>
         </is>
       </c>
-      <c r="O33" s="8" t="inlineStr"/>
+      <c r="O33" s="8" t="inlineStr">
+        <is>
+          <t>The key accelerant for consumer stress.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>Gold / de-dollarization</t>
+          <t>Hidden consumer debt</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>s12_gold_dedollar</t>
+          <t>s11_consumer_debt</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Gold price (USD/oz)</t>
+          <t>BNPL delinquency trend (0 stable / 1 rising / 2 spiking)</t>
         </is>
       </c>
       <c r="D34" s="7" t="n">
-        <v>4032.2</v>
+        <v>1</v>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
@@ -3403,13 +3403,13 @@
         </is>
       </c>
       <c r="F34" s="4" t="n">
-        <v>4500</v>
+        <v>0</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>5500</v>
+        <v>1</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I34" s="4">
         <f>IF(D34&lt;=F34,0,IF(D34&lt;=G34,1,2))</f>
@@ -3424,12 +3424,12 @@
       </c>
       <c r="L34" s="8" t="inlineStr">
         <is>
-          <t>market:GC=F</t>
+          <t>manual</t>
         </is>
       </c>
       <c r="M34" s="4" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="N34" s="4" t="inlineStr">
@@ -3437,11 +3437,7 @@
           <t>live</t>
         </is>
       </c>
-      <c r="O34" s="8" t="inlineStr">
-        <is>
-          <t>Rising = stronger de-dollarization signal.</t>
-        </is>
-      </c>
+      <c r="O34" s="8" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
@@ -3456,32 +3452,32 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>USD share of FX reserves (%, IMF COFER)</t>
+          <t>Gold price (USD/oz)</t>
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>56.77</v>
+        <v>4043.8</v>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>lower_worse</t>
+          <t>higher_worse</t>
         </is>
       </c>
       <c r="F35" s="4" t="n">
-        <v>57</v>
+        <v>4500</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>54</v>
+        <v>5500</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I35" s="4">
-        <f>IF(D35&gt;=F35,0,IF(D35&gt;=G35,1,2))</f>
+        <f>IF(D35&lt;=F35,0,IF(D35&lt;=G35,1,2))</f>
         <v/>
       </c>
       <c r="J35" s="4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K35" s="4">
         <f>J35*(I35-H35)/2</f>
@@ -3489,12 +3485,12 @@
       </c>
       <c r="L35" s="8" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>market:GC=F</t>
         </is>
       </c>
       <c r="M35" s="4" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="N35" s="4" t="inlineStr">
@@ -3502,7 +3498,11 @@
           <t>live</t>
         </is>
       </c>
-      <c r="O35" s="8" t="inlineStr"/>
+      <c r="O35" s="8" t="inlineStr">
+        <is>
+          <t>Rising = stronger de-dollarization signal.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
@@ -3517,28 +3517,28 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Reserve-weaponization / settlement shift (0 none / 1 talk / 2 action)</t>
+          <t>USD share of FX reserves (%, IMF COFER)</t>
         </is>
       </c>
       <c r="D36" s="7" t="n">
-        <v>1</v>
+        <v>56.77</v>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>higher_worse</t>
+          <t>lower_worse</t>
         </is>
       </c>
       <c r="F36" s="4" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I36" s="4">
-        <f>IF(D36&lt;=F36,0,IF(D36&lt;=G36,1,2))</f>
+        <f>IF(D36&gt;=F36,0,IF(D36&gt;=G36,1,2))</f>
         <v/>
       </c>
       <c r="J36" s="4" t="n">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="M36" s="4" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="N36" s="4" t="inlineStr">
@@ -3568,17 +3568,17 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>Insurance retreat</t>
+          <t>Gold / de-dollarization</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>s13_insurance</t>
+          <t>s12_gold_dedollar</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Insurer non-renewals / exits (0 stable / 1 rising / 2 accelerating)</t>
+          <t>Reserve-weaponization / settlement shift (0 none / 1 talk / 2 action)</t>
         </is>
       </c>
       <c r="D37" s="7" t="n">
@@ -3596,7 +3596,7 @@
         <v>1</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I37" s="4">
         <f>IF(D37&lt;=F37,0,IF(D37&lt;=G37,1,2))</f>
@@ -3639,11 +3639,11 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>US single-family mortgage delinquency (%, FRED DRSFRMACBS)</t>
+          <t>Insurer non-renewals / exits (0 stable / 1 rising / 2 accelerating)</t>
         </is>
       </c>
       <c r="D38" s="7" t="n">
-        <v>1.89</v>
+        <v>1</v>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
@@ -3651,20 +3651,20 @@
         </is>
       </c>
       <c r="F38" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I38" s="4">
         <f>IF(D38&lt;=F38,0,IF(D38&lt;=G38,1,2))</f>
         <v/>
       </c>
       <c r="J38" s="4" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K38" s="4">
         <f>J38*(I38-H38)/2</f>
@@ -3672,12 +3672,12 @@
       </c>
       <c r="L38" s="8" t="inlineStr">
         <is>
-          <t>fred:DRSFRMACBS</t>
+          <t>manual</t>
         </is>
       </c>
       <c r="M38" s="4" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>event</t>
         </is>
       </c>
       <c r="N38" s="4" t="inlineStr">
@@ -3700,32 +3700,32 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Catastrophe-loss pressure (0 normal / 1 elevated / 2 severe season)</t>
+          <t>US single-family mortgage delinquency (%, FRED DRSFRMACBS)</t>
         </is>
       </c>
       <c r="D39" s="7" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>higher_worse</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G39" s="4" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H39" s="4" t="n">
         <v>0</v>
-      </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>higher_worse</t>
-        </is>
-      </c>
-      <c r="F39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H39" s="4" t="n">
-        <v>1</v>
       </c>
       <c r="I39" s="4">
         <f>IF(D39&lt;=F39,0,IF(D39&lt;=G39,1,2))</f>
         <v/>
       </c>
       <c r="J39" s="4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K39" s="4">
         <f>J39*(I39-H39)/2</f>
@@ -3733,12 +3733,12 @@
       </c>
       <c r="L39" s="8" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>fred:DRSFRMACBS</t>
         </is>
       </c>
       <c r="M39" s="4" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="N39" s="4" t="inlineStr">
@@ -3751,21 +3751,21 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>Pensions / demographics</t>
+          <t>Insurance retreat</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>s14_pensions</t>
+          <t>s13_insurance</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Social Security / pension reform shock (0 none / 1 debate / 2 cuts)</t>
+          <t>Catastrophe-loss pressure (0 normal / 1 elevated / 2 severe season)</t>
         </is>
       </c>
       <c r="D40" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>1</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I40" s="4">
         <f>IF(D40&lt;=F40,0,IF(D40&lt;=G40,1,2))</f>
@@ -3822,11 +3822,11 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Pension-fund leverage event, UK-2022 type (0 none / 1 stress / 2 blowup)</t>
+          <t>Social Security / pension reform shock (0 none / 1 debate / 2 cuts)</t>
         </is>
       </c>
       <c r="D41" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
@@ -3883,32 +3883,32 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Large public-pension funded ratio (%)</t>
+          <t>Pension-fund leverage event, UK-2022 type (0 none / 1 stress / 2 blowup)</t>
         </is>
       </c>
       <c r="D42" s="7" t="n">
-        <v>87.59999999999999</v>
+        <v>1</v>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>lower_worse</t>
+          <t>higher_worse</t>
         </is>
       </c>
       <c r="F42" s="4" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I42" s="4">
-        <f>IF(D42&gt;=F42,0,IF(D42&gt;=G42,1,2))</f>
+        <f>IF(D42&lt;=F42,0,IF(D42&lt;=G42,1,2))</f>
         <v/>
       </c>
       <c r="J42" s="4" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K42" s="4">
         <f>J42*(I42-H42)/2</f>
@@ -3921,7 +3921,7 @@
       </c>
       <c r="M42" s="4" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>event</t>
         </is>
       </c>
       <c r="N42" s="4" t="inlineStr">
@@ -3934,38 +3934,38 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>AI power &amp; the grid bottleneck</t>
+          <t>Pensions / demographics</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>s15_ai_power</t>
+          <t>s14_pensions</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Grid interconnection wait (months)</t>
+          <t>Large public-pension funded ratio (%)</t>
         </is>
       </c>
       <c r="D43" s="7" t="n">
-        <v>55</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>higher_worse</t>
+          <t>lower_worse</t>
         </is>
       </c>
       <c r="F43" s="4" t="n">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I43" s="4">
-        <f>IF(D43&lt;=F43,0,IF(D43&lt;=G43,1,2))</f>
+        <f>IF(D43&gt;=F43,0,IF(D43&gt;=G43,1,2))</f>
         <v/>
       </c>
       <c r="J43" s="4" t="n">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="M43" s="4" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="N43" s="4" t="inlineStr">
@@ -3990,11 +3990,7 @@
           <t>live</t>
         </is>
       </c>
-      <c r="O43" s="8" t="inlineStr">
-        <is>
-          <t>~22 months in 2000, ~54 in 2026.</t>
-        </is>
-      </c>
+      <c r="O43" s="8" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
@@ -4009,32 +4005,32 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Data-center moratoria / backlash (0 none / 1 spreading / 2 widespread)</t>
+          <t>Grid interconnection wait (months)</t>
         </is>
       </c>
       <c r="D44" s="7" t="n">
+        <v>55</v>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>higher_worse</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="G44" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="H44" s="4" t="n">
         <v>2</v>
-      </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>higher_worse</t>
-        </is>
-      </c>
-      <c r="F44" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H44" s="4" t="n">
-        <v>1</v>
       </c>
       <c r="I44" s="4">
         <f>IF(D44&lt;=F44,0,IF(D44&lt;=G44,1,2))</f>
         <v/>
       </c>
       <c r="J44" s="4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K44" s="4">
         <f>J44*(I44-H44)/2</f>
@@ -4047,7 +4043,7 @@
       </c>
       <c r="M44" s="4" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="N44" s="4" t="inlineStr">
@@ -4055,7 +4051,11 @@
           <t>live</t>
         </is>
       </c>
-      <c r="O44" s="8" t="inlineStr"/>
+      <c r="O44" s="8" t="inlineStr">
+        <is>
+          <t>~22 months in 2000, ~54 in 2026.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
@@ -4070,11 +4070,11 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>AI power-demand pressure (0 easing / 1 tight / 2 acute)</t>
+          <t>Data-center moratoria / backlash (0 none / 1 spreading / 2 widespread)</t>
         </is>
       </c>
       <c r="D45" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
       </c>
       <c r="M45" s="4" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>event</t>
         </is>
       </c>
       <c r="N45" s="4" t="inlineStr">
@@ -4116,30 +4116,26 @@
           <t>live</t>
         </is>
       </c>
-      <c r="O45" s="8" t="inlineStr">
-        <is>
-          <t>Wood Mac saw a late-2025 slowdown; watch capex guidance.</t>
-        </is>
-      </c>
+      <c r="O45" s="8" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>Copper &amp; the electrification deficit</t>
+          <t>AI power &amp; the grid bottleneck</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>s16_copper</t>
+          <t>s15_ai_power</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Copper price (USD/lb, COMEX HG=F)</t>
+          <t>AI power-demand pressure (0 easing / 1 tight / 2 acute)</t>
         </is>
       </c>
       <c r="D46" s="7" t="n">
-        <v>6.178</v>
+        <v>1</v>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
@@ -4147,10 +4143,10 @@
         </is>
       </c>
       <c r="F46" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H46" s="4" t="n">
         <v>1</v>
@@ -4160,7 +4156,7 @@
         <v/>
       </c>
       <c r="J46" s="4" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K46" s="4">
         <f>J46*(I46-H46)/2</f>
@@ -4168,12 +4164,12 @@
       </c>
       <c r="L46" s="8" t="inlineStr">
         <is>
-          <t>market:HG=F</t>
+          <t>manual</t>
         </is>
       </c>
       <c r="M46" s="4" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="N46" s="4" t="inlineStr">
@@ -4183,7 +4179,7 @@
       </c>
       <c r="O46" s="8" t="inlineStr">
         <is>
-          <t>~$12,000/ton = ~$5.44/lb.</t>
+          <t>Wood Mac saw a late-2025 slowdown; watch capex guidance.</t>
         </is>
       </c>
     </row>
@@ -4200,11 +4196,11 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Major mine disruptions (0 none / 1 some / 2 cluster)</t>
+          <t>Copper price (USD/lb, COMEX HG=F)</t>
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>2</v>
+        <v>6.2575</v>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
@@ -4212,10 +4208,10 @@
         </is>
       </c>
       <c r="F47" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H47" s="4" t="n">
         <v>1</v>
@@ -4225,7 +4221,7 @@
         <v/>
       </c>
       <c r="J47" s="4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K47" s="4">
         <f>J47*(I47-H47)/2</f>
@@ -4233,12 +4229,12 @@
       </c>
       <c r="L47" s="8" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>market:HG=F</t>
         </is>
       </c>
       <c r="M47" s="4" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="N47" s="4" t="inlineStr">
@@ -4248,7 +4244,7 @@
       </c>
       <c r="O47" s="8" t="inlineStr">
         <is>
-          <t>Grasberg mud intrusion, Kamoa-Kakula flooding.</t>
+          <t>~$12,000/ton = ~$5.44/lb.</t>
         </is>
       </c>
     </row>
@@ -4265,11 +4261,11 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Deficit timing (0 surplus / 1 balanced / 2 deficit)</t>
+          <t>Major mine disruptions (0 none / 1 some / 2 cluster)</t>
         </is>
       </c>
       <c r="D48" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
@@ -4290,7 +4286,7 @@
         <v/>
       </c>
       <c r="J48" s="4" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K48" s="4">
         <f>J48*(I48-H48)/2</f>
@@ -4303,7 +4299,7 @@
       </c>
       <c r="M48" s="4" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>event</t>
         </is>
       </c>
       <c r="N48" s="4" t="inlineStr">
@@ -4311,26 +4307,30 @@
           <t>live</t>
         </is>
       </c>
-      <c r="O48" s="8" t="inlineStr"/>
+      <c r="O48" s="8" t="inlineStr">
+        <is>
+          <t>Grasberg mud intrusion, Kamoa-Kakula flooding.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>Water - the underpriced input</t>
+          <t>Copper &amp; the electrification deficit</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>s17_water</t>
+          <t>s16_copper</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Drought in a chip/farm hub (0 none / 1 emerging / 2 acute)</t>
+          <t>Deficit timing (0 surplus / 1 balanced / 2 deficit)</t>
         </is>
       </c>
       <c r="D49" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
@@ -4351,7 +4351,7 @@
         <v/>
       </c>
       <c r="J49" s="4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K49" s="4">
         <f>J49*(I49-H49)/2</f>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="M49" s="4" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="N49" s="4" t="inlineStr">
@@ -4387,7 +4387,7 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>Key reservoir / basin stress (0 normal / 1 low / 2 critical)</t>
+          <t>Drought in a chip/farm hub (0 none / 1 emerging / 2 acute)</t>
         </is>
       </c>
       <c r="D50" s="7" t="n">
@@ -4412,7 +4412,7 @@
         <v/>
       </c>
       <c r="J50" s="4" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K50" s="4">
         <f>J50*(I50-H50)/2</f>
@@ -4425,7 +4425,7 @@
       </c>
       <c r="M50" s="4" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>event</t>
         </is>
       </c>
       <c r="N50" s="4" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Transboundary water dispute escalation (0 calm / 1 tense / 2 crisis)</t>
+          <t>Key reservoir / basin stress (0 normal / 1 low / 2 critical)</t>
         </is>
       </c>
       <c r="D51" s="7" t="n">
@@ -4466,7 +4466,7 @@
         <v>1</v>
       </c>
       <c r="H51" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I51" s="4">
         <f>IF(D51&lt;=F51,0,IF(D51&lt;=G51,1,2))</f>
@@ -4486,7 +4486,7 @@
       </c>
       <c r="M51" s="4" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="N51" s="4" t="inlineStr">
@@ -4499,21 +4499,21 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>Food &amp; fertilizer fragility</t>
+          <t>Water - the underpriced input</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>s18_food_fertilizer</t>
+          <t>s17_water</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>Food-price trend (0 falling / 1 elevated / 2 spiking)</t>
+          <t>Transboundary water dispute escalation (0 calm / 1 tense / 2 crisis)</t>
         </is>
       </c>
       <c r="D52" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
@@ -4527,7 +4527,7 @@
         <v>1</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I52" s="4">
         <f>IF(D52&lt;=F52,0,IF(D52&lt;=G52,1,2))</f>
@@ -4547,7 +4547,7 @@
       </c>
       <c r="M52" s="4" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>event</t>
         </is>
       </c>
       <c r="N52" s="4" t="inlineStr">
@@ -4570,7 +4570,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>China fertilizer export curbs (0 lifted / 1 in place / 2 tightened)</t>
+          <t>Food-price trend (0 falling / 1 elevated / 2 spiking)</t>
         </is>
       </c>
       <c r="D53" s="7" t="n">
@@ -4595,7 +4595,7 @@
         <v/>
       </c>
       <c r="J53" s="4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K53" s="4">
         <f>J53*(I53-H53)/2</f>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="M53" s="4" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="N53" s="4" t="inlineStr">
@@ -4616,11 +4616,7 @@
           <t>live</t>
         </is>
       </c>
-      <c r="O53" s="8" t="inlineStr">
-        <is>
-          <t>In place through late Aug 2026.</t>
-        </is>
-      </c>
+      <c r="O53" s="8" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
@@ -4635,7 +4631,7 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>Hormuz/Gulf disruption to fertilizer inputs (0 clear / 1 disrupted / 2 cut)</t>
+          <t>China fertilizer export curbs (0 lifted / 1 in place / 2 tightened)</t>
         </is>
       </c>
       <c r="D54" s="7" t="n">
@@ -4681,26 +4677,30 @@
           <t>live</t>
         </is>
       </c>
-      <c r="O54" s="8" t="inlineStr"/>
+      <c r="O54" s="8" t="inlineStr">
+        <is>
+          <t>In place through late Aug 2026.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>The lithography (ASML) chokepoint</t>
+          <t>Food &amp; fertilizer fragility</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>s19_lithography</t>
+          <t>s18_food_fertilizer</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>Taiwan / cross-strait tension (0 calm / 1 elevated / 2 crisis)</t>
+          <t>Hormuz/Gulf disruption to fertilizer inputs (0 clear / 1 disrupted / 2 cut)</t>
         </is>
       </c>
       <c r="D55" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
@@ -4721,7 +4721,7 @@
         <v/>
       </c>
       <c r="J55" s="4" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="K55" s="4">
         <f>J55*(I55-H55)/2</f>
@@ -4757,11 +4757,11 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>Export-control escalation (0 stable / 1 tightening / 2 retaliation)</t>
+          <t>Taiwan / cross-strait tension (0 calm / 1 elevated / 2 crisis)</t>
         </is>
       </c>
       <c r="D56" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         <v/>
       </c>
       <c r="J56" s="4" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="K56" s="4">
         <f>J56*(I56-H56)/2</f>
@@ -4818,11 +4818,11 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Single-point concentration (0 easing / 1 high / 2 extreme)</t>
+          <t>Export-control escalation (0 stable / 1 tightening / 2 retaliation)</t>
         </is>
       </c>
       <c r="D57" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
@@ -4856,7 +4856,7 @@
       </c>
       <c r="M57" s="4" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>event</t>
         </is>
       </c>
       <c r="N57" s="4" t="inlineStr">
@@ -4869,21 +4869,21 @@
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>Sea lanes &amp; undersea cables</t>
+          <t>The lithography (ASML) chokepoint</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>s20_sea_lanes</t>
+          <t>s19_lithography</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>Hormuz/Red Sea status (0 open / 1 contested / 2 closed)</t>
+          <t>Single-point concentration (0 easing / 1 high / 2 extreme)</t>
         </is>
       </c>
       <c r="D58" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
@@ -4897,14 +4897,14 @@
         <v>1</v>
       </c>
       <c r="H58" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I58" s="4">
         <f>IF(D58&lt;=F58,0,IF(D58&lt;=G58,1,2))</f>
         <v/>
       </c>
       <c r="J58" s="4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K58" s="4">
         <f>J58*(I58-H58)/2</f>
@@ -4917,7 +4917,7 @@
       </c>
       <c r="M58" s="4" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="N58" s="4" t="inlineStr">
@@ -4925,11 +4925,7 @@
           <t>live</t>
         </is>
       </c>
-      <c r="O58" s="8" t="inlineStr">
-        <is>
-          <t>Closed for months in 2026; ceasefire slowly reopening.</t>
-        </is>
-      </c>
+      <c r="O58" s="8" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
@@ -4944,11 +4940,11 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>WTI crude oil (USD/bbl, CL=F)</t>
+          <t>Hormuz/Red Sea status (0 open / 1 contested / 2 closed)</t>
         </is>
       </c>
       <c r="D59" s="7" t="n">
-        <v>70.53</v>
+        <v>1</v>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
@@ -4956,13 +4952,13 @@
         </is>
       </c>
       <c r="F59" s="4" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="G59" s="4" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="H59" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I59" s="4">
         <f>IF(D59&lt;=F59,0,IF(D59&lt;=G59,1,2))</f>
@@ -4977,12 +4973,12 @@
       </c>
       <c r="L59" s="8" t="inlineStr">
         <is>
-          <t>market:CL=F</t>
+          <t>manual</t>
         </is>
       </c>
       <c r="M59" s="4" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>event</t>
         </is>
       </c>
       <c r="N59" s="4" t="inlineStr">
@@ -4990,7 +4986,11 @@
           <t>live</t>
         </is>
       </c>
-      <c r="O59" s="8" t="inlineStr"/>
+      <c r="O59" s="8" t="inlineStr">
+        <is>
+          <t>Closed for months in 2026; ceasefire slowly reopening.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
@@ -5005,11 +5005,11 @@
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>Undersea cable incidents (0 none / 1 threatened / 2 cut)</t>
+          <t>WTI crude oil (USD/bbl, CL=F)</t>
         </is>
       </c>
       <c r="D60" s="7" t="n">
-        <v>2</v>
+        <v>71.16</v>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
@@ -5017,10 +5017,10 @@
         </is>
       </c>
       <c r="F60" s="4" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H60" s="4" t="n">
         <v>1</v>
@@ -5030,7 +5030,7 @@
         <v/>
       </c>
       <c r="J60" s="4" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K60" s="4">
         <f>J60*(I60-H60)/2</f>
@@ -5038,12 +5038,12 @@
       </c>
       <c r="L60" s="8" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>market:CL=F</t>
         </is>
       </c>
       <c r="M60" s="4" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="N60" s="4" t="inlineStr">
@@ -5056,21 +5056,21 @@
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>Clearinghouses (financial chokepoint)</t>
+          <t>Sea lanes &amp; undersea cables</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>s21_clearinghouses</t>
+          <t>s20_sea_lanes</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Equity volatility (VIX)</t>
+          <t>Undersea cable incidents (0 none / 1 threatened / 2 cut)</t>
         </is>
       </c>
       <c r="D61" s="7" t="n">
-        <v>17.61</v>
+        <v>2</v>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
@@ -5078,20 +5078,20 @@
         </is>
       </c>
       <c r="F61" s="4" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="H61" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I61" s="4">
         <f>IF(D61&lt;=F61,0,IF(D61&lt;=G61,1,2))</f>
         <v/>
       </c>
       <c r="J61" s="4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K61" s="4">
         <f>J61*(I61-H61)/2</f>
@@ -5099,12 +5099,12 @@
       </c>
       <c r="L61" s="8" t="inlineStr">
         <is>
-          <t>market:^VIX</t>
+          <t>manual</t>
         </is>
       </c>
       <c r="M61" s="4" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>event</t>
         </is>
       </c>
       <c r="N61" s="4" t="inlineStr">
@@ -5127,11 +5127,11 @@
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Treasury volatility (MOVE)</t>
+          <t>Equity volatility (VIX)</t>
         </is>
       </c>
       <c r="D62" s="7" t="n">
-        <v>66.79000000000001</v>
+        <v>17.54</v>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
@@ -5139,10 +5139,10 @@
         </is>
       </c>
       <c r="F62" s="4" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>130</v>
+        <v>30</v>
       </c>
       <c r="H62" s="4" t="n">
         <v>0</v>
@@ -5152,7 +5152,7 @@
         <v/>
       </c>
       <c r="J62" s="4" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K62" s="4">
         <f>J62*(I62-H62)/2</f>
@@ -5160,7 +5160,7 @@
       </c>
       <c r="L62" s="8" t="inlineStr">
         <is>
-          <t>market:^MOVE</t>
+          <t>market:^VIX</t>
         </is>
       </c>
       <c r="M62" s="4" t="inlineStr">
@@ -5188,11 +5188,11 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Treasury-clearing rollout stress (0 smooth / 1 friction / 2 problems)</t>
+          <t>Treasury volatility (MOVE)</t>
         </is>
       </c>
       <c r="D63" s="7" t="n">
-        <v>1</v>
+        <v>66.79000000000001</v>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
@@ -5200,10 +5200,10 @@
         </is>
       </c>
       <c r="F63" s="4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G63" s="4" t="n">
-        <v>1</v>
+        <v>130</v>
       </c>
       <c r="H63" s="4" t="n">
         <v>0</v>
@@ -5221,20 +5221,81 @@
       </c>
       <c r="L63" s="8" t="inlineStr">
         <is>
+          <t>market:^MOVE</t>
+        </is>
+      </c>
+      <c r="M63" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="N63" s="4" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="O63" s="8" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>Clearinghouses (financial chokepoint)</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>s21_clearinghouses</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>Treasury-clearing rollout stress (0 smooth / 1 friction / 2 problems)</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>higher_worse</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H64" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" s="4">
+        <f>IF(D64&lt;=F64,0,IF(D64&lt;=G64,1,2))</f>
+        <v/>
+      </c>
+      <c r="J64" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K64" s="4">
+        <f>J64*(I64-H64)/2</f>
+        <v/>
+      </c>
+      <c r="L64" s="8" t="inlineStr">
+        <is>
           <t>manual</t>
         </is>
       </c>
-      <c r="M63" s="4" t="inlineStr">
+      <c r="M64" s="4" t="inlineStr">
         <is>
           <t>event</t>
         </is>
       </c>
-      <c r="N63" s="4" t="inlineStr">
+      <c r="N64" s="4" t="inlineStr">
         <is>
           <t>live</t>
         </is>
       </c>
-      <c r="O63" s="8" t="inlineStr"/>
+      <c r="O64" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5247,7 +5308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G148"/>
+  <dimension ref="A1:H169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5257,6 +5318,7 @@
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5295,6 +5357,11 @@
           <t>Raw</t>
         </is>
       </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="inlineStr">
@@ -10732,6 +10799,888 @@
       <c r="G148" s="9" t="inlineStr">
         <is>
           <t>4.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B149" s="9" t="inlineStr">
+        <is>
+          <t>s1_basis_trade</t>
+        </is>
+      </c>
+      <c r="C149" s="9" t="inlineStr">
+        <is>
+          <t>Treasury basis trade (hidden leverage)</t>
+        </is>
+      </c>
+      <c r="D149" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E149" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F149" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G149" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H149" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B150" s="9" t="inlineStr">
+        <is>
+          <t>s2_japan</t>
+        </is>
+      </c>
+      <c r="C150" s="9" t="inlineStr">
+        <is>
+          <t>Japan fiscal / JGB / carry trade</t>
+        </is>
+      </c>
+      <c r="D150" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E150" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F150" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G150" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H150" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B151" s="9" t="inlineStr">
+        <is>
+          <t>s3_private_credit</t>
+        </is>
+      </c>
+      <c r="C151" s="9" t="inlineStr">
+        <is>
+          <t>Private credit's opaque expansion</t>
+        </is>
+      </c>
+      <c r="D151" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E151" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F151" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G151" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="H151" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B152" s="9" t="inlineStr">
+        <is>
+          <t>s4_dev_debt</t>
+        </is>
+      </c>
+      <c r="C152" s="9" t="inlineStr">
+        <is>
+          <t>Developing-world debt crisis</t>
+        </is>
+      </c>
+      <c r="D152" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E152" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F152" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G152" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H152" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B153" s="9" t="inlineStr">
+        <is>
+          <t>s5_china_deflation</t>
+        </is>
+      </c>
+      <c r="C153" s="9" t="inlineStr">
+        <is>
+          <t>China's price spillover (deflation or cost-push)</t>
+        </is>
+      </c>
+      <c r="D153" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E153" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F153" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G153" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="H153" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B154" s="9" t="inlineStr">
+        <is>
+          <t>s6_rare_earths</t>
+        </is>
+      </c>
+      <c r="C154" s="9" t="inlineStr">
+        <is>
+          <t>Critical minerals as a weapon</t>
+        </is>
+      </c>
+      <c r="D154" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E154" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F154" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G154" s="9" t="inlineStr">
+        <is>
+          <t>6.75</t>
+        </is>
+      </c>
+      <c r="H154" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B155" s="9" t="inlineStr">
+        <is>
+          <t>s7_stablecoins</t>
+        </is>
+      </c>
+      <c r="C155" s="9" t="inlineStr">
+        <is>
+          <t>Stablecoins &amp; Treasury demand</t>
+        </is>
+      </c>
+      <c r="D155" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E155" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F155" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G155" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H155" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B156" s="9" t="inlineStr">
+        <is>
+          <t>s8_ai_capex</t>
+        </is>
+      </c>
+      <c r="C156" s="9" t="inlineStr">
+        <is>
+          <t>AI build-out circular financing</t>
+        </is>
+      </c>
+      <c r="D156" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E156" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F156" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G156" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H156" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B157" s="9" t="inlineStr">
+        <is>
+          <t>s9_cre</t>
+        </is>
+      </c>
+      <c r="C157" s="9" t="inlineStr">
+        <is>
+          <t>CRE maturity wall / regional banks</t>
+        </is>
+      </c>
+      <c r="D157" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E157" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F157" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G157" s="9" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="H157" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B158" s="9" t="inlineStr">
+        <is>
+          <t>s10_france</t>
+        </is>
+      </c>
+      <c r="C158" s="9" t="inlineStr">
+        <is>
+          <t>France / eurozone fragility</t>
+        </is>
+      </c>
+      <c r="D158" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E158" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F158" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G158" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H158" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B159" s="9" t="inlineStr">
+        <is>
+          <t>s11_consumer_debt</t>
+        </is>
+      </c>
+      <c r="C159" s="9" t="inlineStr">
+        <is>
+          <t>Hidden consumer debt</t>
+        </is>
+      </c>
+      <c r="D159" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E159" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F159" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G159" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H159" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B160" s="9" t="inlineStr">
+        <is>
+          <t>s12_gold_dedollar</t>
+        </is>
+      </c>
+      <c r="C160" s="9" t="inlineStr">
+        <is>
+          <t>Gold / de-dollarization</t>
+        </is>
+      </c>
+      <c r="D160" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E160" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F160" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G160" s="9" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="H160" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B161" s="9" t="inlineStr">
+        <is>
+          <t>s13_insurance</t>
+        </is>
+      </c>
+      <c r="C161" s="9" t="inlineStr">
+        <is>
+          <t>Insurance retreat</t>
+        </is>
+      </c>
+      <c r="D161" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E161" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F161" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G161" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H161" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B162" s="9" t="inlineStr">
+        <is>
+          <t>s14_pensions</t>
+        </is>
+      </c>
+      <c r="C162" s="9" t="inlineStr">
+        <is>
+          <t>Pensions / demographics</t>
+        </is>
+      </c>
+      <c r="D162" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E162" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F162" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G162" s="9" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="H162" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B163" s="9" t="inlineStr">
+        <is>
+          <t>s15_ai_power</t>
+        </is>
+      </c>
+      <c r="C163" s="9" t="inlineStr">
+        <is>
+          <t>AI power &amp; the grid bottleneck</t>
+        </is>
+      </c>
+      <c r="D163" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E163" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F163" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G163" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H163" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B164" s="9" t="inlineStr">
+        <is>
+          <t>s16_copper</t>
+        </is>
+      </c>
+      <c r="C164" s="9" t="inlineStr">
+        <is>
+          <t>Copper &amp; the electrification deficit</t>
+        </is>
+      </c>
+      <c r="D164" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E164" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F164" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G164" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H164" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B165" s="9" t="inlineStr">
+        <is>
+          <t>s17_water</t>
+        </is>
+      </c>
+      <c r="C165" s="9" t="inlineStr">
+        <is>
+          <t>Water - the underpriced input</t>
+        </is>
+      </c>
+      <c r="D165" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E165" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F165" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G165" s="9" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="H165" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B166" s="9" t="inlineStr">
+        <is>
+          <t>s18_food_fertilizer</t>
+        </is>
+      </c>
+      <c r="C166" s="9" t="inlineStr">
+        <is>
+          <t>Food &amp; fertilizer fragility</t>
+        </is>
+      </c>
+      <c r="D166" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E166" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F166" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G166" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H166" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B167" s="9" t="inlineStr">
+        <is>
+          <t>s19_lithography</t>
+        </is>
+      </c>
+      <c r="C167" s="9" t="inlineStr">
+        <is>
+          <t>The lithography (ASML) chokepoint</t>
+        </is>
+      </c>
+      <c r="D167" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E167" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F167" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G167" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H167" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B168" s="9" t="inlineStr">
+        <is>
+          <t>s20_sea_lanes</t>
+        </is>
+      </c>
+      <c r="C168" s="9" t="inlineStr">
+        <is>
+          <t>Sea lanes &amp; undersea cables</t>
+        </is>
+      </c>
+      <c r="D168" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E168" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F168" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G168" s="9" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+      <c r="H168" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B169" s="9" t="inlineStr">
+        <is>
+          <t>s21_clearinghouses</t>
+        </is>
+      </c>
+      <c r="C169" s="9" t="inlineStr">
+        <is>
+          <t>Clearinghouses (financial chokepoint)</t>
+        </is>
+      </c>
+      <c r="D169" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E169" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F169" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G169" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H169" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
         </is>
       </c>
     </row>
@@ -10746,7 +11695,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A24"/>
+  <dimension ref="A1:A34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -10827,38 +11776,34 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>--- Daily narrative (2026-06-29) ---</t>
+          <t>--- Daily narrative (2026-06-30) ---</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>**HEADLINE**</t>
+          <t># EOD Macro-Risk Brief | 2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>Macro risk remains steady at 5.2/10 with 14 stories in elevated band; one commodity pressure eased.</t>
-        </is>
-      </c>
+      <c r="A15" s="12" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr"/>
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>**Overall risk elevated at 5.8; two critical stories escalated to High band on supply-chain weaponization.**</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>**LEVEL CHANGES**</t>
-        </is>
-      </c>
+      <c r="A17" s="12" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>• **Food &amp; fertilizer fragility** (7→6): Hormuz/Gulf fertilizer disruption downgraded from "cut" to "disrupted" status, reducing acute supply-chain shock risk but leaving input chains strained.</t>
+          <t>**Stories with level changes:**</t>
         </is>
       </c>
     </row>
@@ -10868,31 +11813,77 @@
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>**ELEVATED-RISK WATCH LIST**</t>
+          <t>- **Critical minerals as a weapon** (6→7, High): US rare-earth entity blacklist and 4.5x heavy rare-earth price premium vs. China signal active trade escalation; constrains US defense and advanced manufacturing supply chains.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>Fourteen stories remain at elevated (5–6/10): Treasury basis trades, Japan JGB/carry mechanics, private credit opacity, China deflation export, critical minerals weaponization, AI circular financing, CRE maturity walls, hidden consumer debt, AI power-grid bottlenecks, ASML lithography chokepoint, and sea-lane vulnerabilities all pose material contagion risk.</t>
-        </is>
-      </c>
+      <c r="A21" s="12" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="inlineStr"/>
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>- **Food &amp; fertilizer fragility** (6→7, High): China tightened fertilizer export curbs and Gulf disruption to inputs both intensified; threatens global crop input availability and food price stability.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>**TOP WATCH**</t>
-        </is>
-      </c>
+      <c r="A23" s="12" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>Treasury basis trade (6/10) and Japan fiscal/carry unwind (6/10) carry highest leverage and cross-market interconnection risk.</t>
+          <t>- **The lithography chokepoint** (5→6, Elevated): Export controls escalated to retaliation phase and fab concentration remains extreme; semiconductor supply concentration risk now acute.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>- **France / eurozone fragility** (4→5, Elevated): Moody's downgrade materialized; widens euro-area sovereign stress.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>- **Pensions / demographics** (4→5, Elevated): Social Security reform debate and UK-2022-type pension leverage stress both active; public-pension funded ratio at 87.6% shows margin erosion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>- **CRE maturity wall / regional banks** (6→5, Elevated): CMBS office delinquency improved but isolated regional bank CRE stress persists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="12" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>- **Hidden consumer debt** (6→5, Elevated): Improved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="12" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>**Highest priority:** Critical minerals weaponization now at High; near-term impact on defense procurement and allied supply chains.</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-06-30  -  generated 2026-06-30 12:25 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-06-30  -  generated 2026-06-30 13:55 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>162.424</v>
+        <v>162.445</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>6.774</v>
+        <v>6.775</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>4043.8</v>
+        <v>4038.1001</v>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>6.2575</v>
+        <v>6.2425</v>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="D60" s="7" t="n">
-        <v>71.16</v>
+        <v>70.79000000000001</v>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="D62" s="7" t="n">
-        <v>17.54</v>
+        <v>17.55</v>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H169"/>
+  <dimension ref="A1:H190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11684,6 +11684,888 @@
         </is>
       </c>
     </row>
+    <row r="170">
+      <c r="A170" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B170" s="9" t="inlineStr">
+        <is>
+          <t>s1_basis_trade</t>
+        </is>
+      </c>
+      <c r="C170" s="9" t="inlineStr">
+        <is>
+          <t>Treasury basis trade (hidden leverage)</t>
+        </is>
+      </c>
+      <c r="D170" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E170" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F170" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G170" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H170" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B171" s="9" t="inlineStr">
+        <is>
+          <t>s2_japan</t>
+        </is>
+      </c>
+      <c r="C171" s="9" t="inlineStr">
+        <is>
+          <t>Japan fiscal / JGB / carry trade</t>
+        </is>
+      </c>
+      <c r="D171" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E171" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F171" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G171" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H171" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B172" s="9" t="inlineStr">
+        <is>
+          <t>s3_private_credit</t>
+        </is>
+      </c>
+      <c r="C172" s="9" t="inlineStr">
+        <is>
+          <t>Private credit's opaque expansion</t>
+        </is>
+      </c>
+      <c r="D172" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E172" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F172" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G172" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="H172" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B173" s="9" t="inlineStr">
+        <is>
+          <t>s4_dev_debt</t>
+        </is>
+      </c>
+      <c r="C173" s="9" t="inlineStr">
+        <is>
+          <t>Developing-world debt crisis</t>
+        </is>
+      </c>
+      <c r="D173" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E173" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F173" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G173" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H173" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B174" s="9" t="inlineStr">
+        <is>
+          <t>s5_china_deflation</t>
+        </is>
+      </c>
+      <c r="C174" s="9" t="inlineStr">
+        <is>
+          <t>China's price spillover (deflation or cost-push)</t>
+        </is>
+      </c>
+      <c r="D174" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E174" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F174" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G174" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="H174" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B175" s="9" t="inlineStr">
+        <is>
+          <t>s6_rare_earths</t>
+        </is>
+      </c>
+      <c r="C175" s="9" t="inlineStr">
+        <is>
+          <t>Critical minerals as a weapon</t>
+        </is>
+      </c>
+      <c r="D175" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E175" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F175" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G175" s="9" t="inlineStr">
+        <is>
+          <t>6.75</t>
+        </is>
+      </c>
+      <c r="H175" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B176" s="9" t="inlineStr">
+        <is>
+          <t>s7_stablecoins</t>
+        </is>
+      </c>
+      <c r="C176" s="9" t="inlineStr">
+        <is>
+          <t>Stablecoins &amp; Treasury demand</t>
+        </is>
+      </c>
+      <c r="D176" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E176" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F176" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G176" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H176" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B177" s="9" t="inlineStr">
+        <is>
+          <t>s8_ai_capex</t>
+        </is>
+      </c>
+      <c r="C177" s="9" t="inlineStr">
+        <is>
+          <t>AI build-out circular financing</t>
+        </is>
+      </c>
+      <c r="D177" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E177" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F177" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G177" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H177" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B178" s="9" t="inlineStr">
+        <is>
+          <t>s9_cre</t>
+        </is>
+      </c>
+      <c r="C178" s="9" t="inlineStr">
+        <is>
+          <t>CRE maturity wall / regional banks</t>
+        </is>
+      </c>
+      <c r="D178" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E178" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F178" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G178" s="9" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="H178" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B179" s="9" t="inlineStr">
+        <is>
+          <t>s10_france</t>
+        </is>
+      </c>
+      <c r="C179" s="9" t="inlineStr">
+        <is>
+          <t>France / eurozone fragility</t>
+        </is>
+      </c>
+      <c r="D179" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E179" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F179" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G179" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H179" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B180" s="9" t="inlineStr">
+        <is>
+          <t>s11_consumer_debt</t>
+        </is>
+      </c>
+      <c r="C180" s="9" t="inlineStr">
+        <is>
+          <t>Hidden consumer debt</t>
+        </is>
+      </c>
+      <c r="D180" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E180" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F180" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G180" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H180" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B181" s="9" t="inlineStr">
+        <is>
+          <t>s12_gold_dedollar</t>
+        </is>
+      </c>
+      <c r="C181" s="9" t="inlineStr">
+        <is>
+          <t>Gold / de-dollarization</t>
+        </is>
+      </c>
+      <c r="D181" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E181" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F181" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G181" s="9" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="H181" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B182" s="9" t="inlineStr">
+        <is>
+          <t>s13_insurance</t>
+        </is>
+      </c>
+      <c r="C182" s="9" t="inlineStr">
+        <is>
+          <t>Insurance retreat</t>
+        </is>
+      </c>
+      <c r="D182" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E182" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F182" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G182" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H182" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B183" s="9" t="inlineStr">
+        <is>
+          <t>s14_pensions</t>
+        </is>
+      </c>
+      <c r="C183" s="9" t="inlineStr">
+        <is>
+          <t>Pensions / demographics</t>
+        </is>
+      </c>
+      <c r="D183" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E183" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F183" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G183" s="9" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="H183" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B184" s="9" t="inlineStr">
+        <is>
+          <t>s15_ai_power</t>
+        </is>
+      </c>
+      <c r="C184" s="9" t="inlineStr">
+        <is>
+          <t>AI power &amp; the grid bottleneck</t>
+        </is>
+      </c>
+      <c r="D184" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E184" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F184" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G184" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H184" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B185" s="9" t="inlineStr">
+        <is>
+          <t>s16_copper</t>
+        </is>
+      </c>
+      <c r="C185" s="9" t="inlineStr">
+        <is>
+          <t>Copper &amp; the electrification deficit</t>
+        </is>
+      </c>
+      <c r="D185" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E185" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F185" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G185" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H185" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B186" s="9" t="inlineStr">
+        <is>
+          <t>s17_water</t>
+        </is>
+      </c>
+      <c r="C186" s="9" t="inlineStr">
+        <is>
+          <t>Water - the underpriced input</t>
+        </is>
+      </c>
+      <c r="D186" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E186" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F186" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G186" s="9" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="H186" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B187" s="9" t="inlineStr">
+        <is>
+          <t>s18_food_fertilizer</t>
+        </is>
+      </c>
+      <c r="C187" s="9" t="inlineStr">
+        <is>
+          <t>Food &amp; fertilizer fragility</t>
+        </is>
+      </c>
+      <c r="D187" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E187" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F187" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G187" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H187" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B188" s="9" t="inlineStr">
+        <is>
+          <t>s19_lithography</t>
+        </is>
+      </c>
+      <c r="C188" s="9" t="inlineStr">
+        <is>
+          <t>The lithography (ASML) chokepoint</t>
+        </is>
+      </c>
+      <c r="D188" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E188" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F188" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G188" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H188" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B189" s="9" t="inlineStr">
+        <is>
+          <t>s20_sea_lanes</t>
+        </is>
+      </c>
+      <c r="C189" s="9" t="inlineStr">
+        <is>
+          <t>Sea lanes &amp; undersea cables</t>
+        </is>
+      </c>
+      <c r="D189" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E189" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F189" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G189" s="9" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+      <c r="H189" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B190" s="9" t="inlineStr">
+        <is>
+          <t>s21_clearinghouses</t>
+        </is>
+      </c>
+      <c r="C190" s="9" t="inlineStr">
+        <is>
+          <t>Clearinghouses (financial chokepoint)</t>
+        </is>
+      </c>
+      <c r="D190" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E190" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F190" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G190" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H190" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11695,7 +12577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A34"/>
+  <dimension ref="A1:A22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -11793,7 +12675,7 @@
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>**Overall risk elevated at 5.8; two critical stories escalated to High band on supply-chain weaponization.**</t>
+          <t>**Overall risk stable at 5.8 with sixteen stories at Elevated or High levels; no intraday changes but structural vulnerabilities persist across finance, supply chains, and geopolitics.**</t>
         </is>
       </c>
     </row>
@@ -11803,7 +12685,7 @@
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>**Stories with level changes:**</t>
+          <t>**No level changes recorded today.** The aggregate risk score remains anchored by persistent Elevated risks across Treasury basis trades, Japan's fiscal-carry nexus, opaque private credit expansion, and China's deflationary spillover—each at level 6—alongside five Elevated risks in real estate, sovereign debt, and demographics.</t>
         </is>
       </c>
     </row>
@@ -11813,7 +12695,7 @@
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>- **Critical minerals as a weapon** (6→7, High): US rare-earth entity blacklist and 4.5x heavy rare-earth price premium vs. China signal active trade escalation; constrains US defense and advanced manufacturing supply chains.</t>
+          <t>Two stories remain at High (level 7): **Critical minerals as a weapon** and **Food &amp; fertilizer fragility**, reflecting geopolitical fragmentation and agricultural dependency risks that could cascade into broader supply shocks.</t>
         </is>
       </c>
     </row>
@@ -11823,67 +12705,7 @@
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>- **Food &amp; fertilizer fragility** (6→7, High): China tightened fertilizer export curbs and Gulf disruption to inputs both intensified; threatens global crop input availability and food price stability.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="12" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="12" t="inlineStr">
-        <is>
-          <t>- **The lithography chokepoint** (5→6, Elevated): Export controls escalated to retaliation phase and fab concentration remains extreme; semiconductor supply concentration risk now acute.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="12" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="12" t="inlineStr">
-        <is>
-          <t>- **France / eurozone fragility** (4→5, Elevated): Moody's downgrade materialized; widens euro-area sovereign stress.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="12" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="12" t="inlineStr">
-        <is>
-          <t>- **Pensions / demographics** (4→5, Elevated): Social Security reform debate and UK-2022-type pension leverage stress both active; public-pension funded ratio at 87.6% shows margin erosion.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="12" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="12" t="inlineStr">
-        <is>
-          <t>- **CRE maturity wall / regional banks** (6→5, Elevated): CMBS office delinquency improved but isolated regional bank CRE stress persists.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="12" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="12" t="inlineStr">
-        <is>
-          <t>- **Hidden consumer debt** (6→5, Elevated): Improved.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="12" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="12" t="inlineStr">
-        <is>
-          <t>**Highest priority:** Critical minerals weaponization now at High; near-term impact on defense procurement and allied supply chains.</t>
+          <t>**Watch closest: Critical minerals weaponization (level 7)** — underpins both energy transition and defense supply chains with limited near-term substitutes or reserve buffers.</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-06-30  -  generated 2026-06-30 13:55 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-06-30  -  generated 2026-06-30 16:10 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>162.445</v>
+        <v>162.657</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>6.775</v>
+        <v>6.7751</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.167</v>
+        <v>0.15</v>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         </is>
       </c>
       <c r="D32" s="7" t="n">
-        <v>6.11</v>
+        <v>6.8</v>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>4038.1001</v>
+        <v>4048.3999</v>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
@@ -3887,7 +3887,7 @@
         </is>
       </c>
       <c r="D42" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
@@ -4135,7 +4135,7 @@
         </is>
       </c>
       <c r="D46" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>6.2425</v>
+        <v>6.2555</v>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="D52" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         </is>
       </c>
       <c r="D55" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="D60" s="7" t="n">
-        <v>70.79000000000001</v>
+        <v>69.83</v>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         </is>
       </c>
       <c r="D61" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="D62" s="7" t="n">
-        <v>17.55</v>
+        <v>16.86</v>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H190"/>
+  <dimension ref="A1:H211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12566,6 +12566,888 @@
         </is>
       </c>
     </row>
+    <row r="191">
+      <c r="A191" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B191" s="9" t="inlineStr">
+        <is>
+          <t>s1_basis_trade</t>
+        </is>
+      </c>
+      <c r="C191" s="9" t="inlineStr">
+        <is>
+          <t>Treasury basis trade (hidden leverage)</t>
+        </is>
+      </c>
+      <c r="D191" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E191" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F191" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G191" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H191" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B192" s="9" t="inlineStr">
+        <is>
+          <t>s2_japan</t>
+        </is>
+      </c>
+      <c r="C192" s="9" t="inlineStr">
+        <is>
+          <t>Japan fiscal / JGB / carry trade</t>
+        </is>
+      </c>
+      <c r="D192" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E192" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F192" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G192" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H192" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B193" s="9" t="inlineStr">
+        <is>
+          <t>s3_private_credit</t>
+        </is>
+      </c>
+      <c r="C193" s="9" t="inlineStr">
+        <is>
+          <t>Private credit's opaque expansion</t>
+        </is>
+      </c>
+      <c r="D193" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E193" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F193" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G193" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="H193" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B194" s="9" t="inlineStr">
+        <is>
+          <t>s4_dev_debt</t>
+        </is>
+      </c>
+      <c r="C194" s="9" t="inlineStr">
+        <is>
+          <t>Developing-world debt crisis</t>
+        </is>
+      </c>
+      <c r="D194" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E194" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F194" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G194" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H194" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B195" s="9" t="inlineStr">
+        <is>
+          <t>s5_china_deflation</t>
+        </is>
+      </c>
+      <c r="C195" s="9" t="inlineStr">
+        <is>
+          <t>China's price spillover (deflation or cost-push)</t>
+        </is>
+      </c>
+      <c r="D195" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E195" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F195" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G195" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H195" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B196" s="9" t="inlineStr">
+        <is>
+          <t>s6_rare_earths</t>
+        </is>
+      </c>
+      <c r="C196" s="9" t="inlineStr">
+        <is>
+          <t>Critical minerals as a weapon</t>
+        </is>
+      </c>
+      <c r="D196" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E196" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F196" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G196" s="9" t="inlineStr">
+        <is>
+          <t>6.75</t>
+        </is>
+      </c>
+      <c r="H196" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B197" s="9" t="inlineStr">
+        <is>
+          <t>s7_stablecoins</t>
+        </is>
+      </c>
+      <c r="C197" s="9" t="inlineStr">
+        <is>
+          <t>Stablecoins &amp; Treasury demand</t>
+        </is>
+      </c>
+      <c r="D197" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E197" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F197" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G197" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H197" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B198" s="9" t="inlineStr">
+        <is>
+          <t>s8_ai_capex</t>
+        </is>
+      </c>
+      <c r="C198" s="9" t="inlineStr">
+        <is>
+          <t>AI build-out circular financing</t>
+        </is>
+      </c>
+      <c r="D198" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E198" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F198" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G198" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H198" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B199" s="9" t="inlineStr">
+        <is>
+          <t>s9_cre</t>
+        </is>
+      </c>
+      <c r="C199" s="9" t="inlineStr">
+        <is>
+          <t>CRE maturity wall / regional banks</t>
+        </is>
+      </c>
+      <c r="D199" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E199" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F199" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G199" s="9" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="H199" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B200" s="9" t="inlineStr">
+        <is>
+          <t>s10_france</t>
+        </is>
+      </c>
+      <c r="C200" s="9" t="inlineStr">
+        <is>
+          <t>France / eurozone fragility</t>
+        </is>
+      </c>
+      <c r="D200" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E200" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F200" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G200" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H200" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B201" s="9" t="inlineStr">
+        <is>
+          <t>s11_consumer_debt</t>
+        </is>
+      </c>
+      <c r="C201" s="9" t="inlineStr">
+        <is>
+          <t>Hidden consumer debt</t>
+        </is>
+      </c>
+      <c r="D201" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E201" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F201" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G201" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H201" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B202" s="9" t="inlineStr">
+        <is>
+          <t>s12_gold_dedollar</t>
+        </is>
+      </c>
+      <c r="C202" s="9" t="inlineStr">
+        <is>
+          <t>Gold / de-dollarization</t>
+        </is>
+      </c>
+      <c r="D202" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E202" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F202" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G202" s="9" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="H202" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B203" s="9" t="inlineStr">
+        <is>
+          <t>s13_insurance</t>
+        </is>
+      </c>
+      <c r="C203" s="9" t="inlineStr">
+        <is>
+          <t>Insurance retreat</t>
+        </is>
+      </c>
+      <c r="D203" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E203" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F203" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G203" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H203" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B204" s="9" t="inlineStr">
+        <is>
+          <t>s14_pensions</t>
+        </is>
+      </c>
+      <c r="C204" s="9" t="inlineStr">
+        <is>
+          <t>Pensions / demographics</t>
+        </is>
+      </c>
+      <c r="D204" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E204" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F204" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G204" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H204" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B205" s="9" t="inlineStr">
+        <is>
+          <t>s15_ai_power</t>
+        </is>
+      </c>
+      <c r="C205" s="9" t="inlineStr">
+        <is>
+          <t>AI power &amp; the grid bottleneck</t>
+        </is>
+      </c>
+      <c r="D205" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E205" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F205" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G205" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H205" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B206" s="9" t="inlineStr">
+        <is>
+          <t>s16_copper</t>
+        </is>
+      </c>
+      <c r="C206" s="9" t="inlineStr">
+        <is>
+          <t>Copper &amp; the electrification deficit</t>
+        </is>
+      </c>
+      <c r="D206" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E206" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F206" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G206" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H206" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B207" s="9" t="inlineStr">
+        <is>
+          <t>s17_water</t>
+        </is>
+      </c>
+      <c r="C207" s="9" t="inlineStr">
+        <is>
+          <t>Water - the underpriced input</t>
+        </is>
+      </c>
+      <c r="D207" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E207" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F207" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G207" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H207" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B208" s="9" t="inlineStr">
+        <is>
+          <t>s18_food_fertilizer</t>
+        </is>
+      </c>
+      <c r="C208" s="9" t="inlineStr">
+        <is>
+          <t>Food &amp; fertilizer fragility</t>
+        </is>
+      </c>
+      <c r="D208" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E208" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F208" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G208" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H208" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B209" s="9" t="inlineStr">
+        <is>
+          <t>s19_lithography</t>
+        </is>
+      </c>
+      <c r="C209" s="9" t="inlineStr">
+        <is>
+          <t>The lithography (ASML) chokepoint</t>
+        </is>
+      </c>
+      <c r="D209" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E209" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F209" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G209" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H209" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B210" s="9" t="inlineStr">
+        <is>
+          <t>s20_sea_lanes</t>
+        </is>
+      </c>
+      <c r="C210" s="9" t="inlineStr">
+        <is>
+          <t>Sea lanes &amp; undersea cables</t>
+        </is>
+      </c>
+      <c r="D210" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E210" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F210" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G210" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="H210" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B211" s="9" t="inlineStr">
+        <is>
+          <t>s21_clearinghouses</t>
+        </is>
+      </c>
+      <c r="C211" s="9" t="inlineStr">
+        <is>
+          <t>Clearinghouses (financial chokepoint)</t>
+        </is>
+      </c>
+      <c r="D211" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E211" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F211" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G211" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H211" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12577,7 +13459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A22"/>
+  <dimension ref="A1:A28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -12665,47 +13547,81 @@
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t># EOD Macro-Risk Brief | 2026-06-30</t>
+          <t>**HEADLINE**</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr"/>
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>Overall macro risk ticked up to 5.8, driven by escalating AI infrastructure strain and consumer debt stress offsetting modest pension relief.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>**Overall risk stable at 5.8 with sixteen stories at Elevated or High levels; no intraday changes but structural vulnerabilities persist across finance, supply chains, and geopolitics.**</t>
-        </is>
-      </c>
+      <c r="A16" s="12" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr"/>
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>**STORIES WITH LEVEL CHANGES**</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
-          <t>**No level changes recorded today.** The aggregate risk score remains anchored by persistent Elevated risks across Treasury basis trades, Japan's fiscal-carry nexus, opaque private credit expansion, and China's deflationary spillover—each at level 6—alongside five Elevated risks in real estate, sovereign debt, and demographics.</t>
-        </is>
-      </c>
+      <c r="A18" s="12" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr"/>
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>• **Hidden consumer debt: 5 → 6 (Elevated).** Subprime auto 60+ day delinquencies rose 0.5 percentage points to 6.8%; signals weakening household payment capacity and potential downstream credit losses.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
-          <t>Two stories remain at High (level 7): **Critical minerals as a weapon** and **Food &amp; fertilizer fragility**, reflecting geopolitical fragmentation and agricultural dependency risks that could cascade into broader supply shocks.</t>
-        </is>
-      </c>
+      <c r="A20" s="12" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr"/>
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>• **AI power &amp; the grid bottleneck: 6 → 7 (High).** Data-center moratoria have spread to widespread status and acute power-demand pressure persists; constrains AI capex rollout and risks brownouts in grid-stressed regions.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t>**Watch closest: Critical minerals weaponization (level 7)** — underpins both energy transition and defense supply chains with limited near-term substitutes or reserve buffers.</t>
+      <c r="A22" s="12" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>• **Food &amp; fertilizer fragility: 7 → 6 (Elevated).** China's tightened fertilizer export curbs remain in place but broader supply conditions have stabilized; reduces near-term crop-cost volatility risk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>• **Pensions / demographics: 5 → 4 (Moderate).** Public-pension funded ratios improved to 87.6% and Social Security debate remains at discussion stage; reduces acute fiscal cliff risk in near term.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>**HIGHEST RISK TO WATCH**</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>AI power &amp; the grid bottleneck at level 7—widespread moratoria combined with acute demand pressure risks sustained infrastructure investment delays and regional supply disruptions.</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-06-30  -  generated 2026-06-30 16:10 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-07-01  -  generated 2026-07-01 14:07 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
         </is>
       </c>
       <c r="D2" s="7" t="n">
-        <v>-0.01</v>
+        <v>0.05</v>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>162.657</v>
+        <v>162.384</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>6.7751</v>
+        <v>6.7788</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>4048.3999</v>
+        <v>4105.8999</v>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>6.2555</v>
+        <v>6.209</v>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="D60" s="7" t="n">
-        <v>69.83</v>
+        <v>69.08</v>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="D62" s="7" t="n">
-        <v>16.86</v>
+        <v>16.71</v>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H211"/>
+  <dimension ref="A1:H232"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -13443,6 +13443,888 @@
         </is>
       </c>
       <c r="H211" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B212" s="9" t="inlineStr">
+        <is>
+          <t>s1_basis_trade</t>
+        </is>
+      </c>
+      <c r="C212" s="9" t="inlineStr">
+        <is>
+          <t>Treasury basis trade (hidden leverage)</t>
+        </is>
+      </c>
+      <c r="D212" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E212" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F212" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G212" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H212" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B213" s="9" t="inlineStr">
+        <is>
+          <t>s2_japan</t>
+        </is>
+      </c>
+      <c r="C213" s="9" t="inlineStr">
+        <is>
+          <t>Japan fiscal / JGB / carry trade</t>
+        </is>
+      </c>
+      <c r="D213" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E213" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F213" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G213" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H213" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B214" s="9" t="inlineStr">
+        <is>
+          <t>s3_private_credit</t>
+        </is>
+      </c>
+      <c r="C214" s="9" t="inlineStr">
+        <is>
+          <t>Private credit's opaque expansion</t>
+        </is>
+      </c>
+      <c r="D214" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E214" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F214" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G214" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="H214" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B215" s="9" t="inlineStr">
+        <is>
+          <t>s4_dev_debt</t>
+        </is>
+      </c>
+      <c r="C215" s="9" t="inlineStr">
+        <is>
+          <t>Developing-world debt crisis</t>
+        </is>
+      </c>
+      <c r="D215" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E215" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F215" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G215" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H215" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B216" s="9" t="inlineStr">
+        <is>
+          <t>s5_china_deflation</t>
+        </is>
+      </c>
+      <c r="C216" s="9" t="inlineStr">
+        <is>
+          <t>China's price spillover (deflation or cost-push)</t>
+        </is>
+      </c>
+      <c r="D216" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E216" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F216" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G216" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H216" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B217" s="9" t="inlineStr">
+        <is>
+          <t>s6_rare_earths</t>
+        </is>
+      </c>
+      <c r="C217" s="9" t="inlineStr">
+        <is>
+          <t>Critical minerals as a weapon</t>
+        </is>
+      </c>
+      <c r="D217" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E217" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F217" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G217" s="9" t="inlineStr">
+        <is>
+          <t>6.75</t>
+        </is>
+      </c>
+      <c r="H217" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B218" s="9" t="inlineStr">
+        <is>
+          <t>s7_stablecoins</t>
+        </is>
+      </c>
+      <c r="C218" s="9" t="inlineStr">
+        <is>
+          <t>Stablecoins &amp; Treasury demand</t>
+        </is>
+      </c>
+      <c r="D218" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E218" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F218" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G218" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H218" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B219" s="9" t="inlineStr">
+        <is>
+          <t>s8_ai_capex</t>
+        </is>
+      </c>
+      <c r="C219" s="9" t="inlineStr">
+        <is>
+          <t>AI build-out circular financing</t>
+        </is>
+      </c>
+      <c r="D219" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E219" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F219" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G219" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H219" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B220" s="9" t="inlineStr">
+        <is>
+          <t>s9_cre</t>
+        </is>
+      </c>
+      <c r="C220" s="9" t="inlineStr">
+        <is>
+          <t>CRE maturity wall / regional banks</t>
+        </is>
+      </c>
+      <c r="D220" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E220" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F220" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G220" s="9" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="H220" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B221" s="9" t="inlineStr">
+        <is>
+          <t>s10_france</t>
+        </is>
+      </c>
+      <c r="C221" s="9" t="inlineStr">
+        <is>
+          <t>France / eurozone fragility</t>
+        </is>
+      </c>
+      <c r="D221" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E221" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F221" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G221" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H221" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B222" s="9" t="inlineStr">
+        <is>
+          <t>s11_consumer_debt</t>
+        </is>
+      </c>
+      <c r="C222" s="9" t="inlineStr">
+        <is>
+          <t>Hidden consumer debt</t>
+        </is>
+      </c>
+      <c r="D222" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E222" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F222" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G222" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H222" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B223" s="9" t="inlineStr">
+        <is>
+          <t>s12_gold_dedollar</t>
+        </is>
+      </c>
+      <c r="C223" s="9" t="inlineStr">
+        <is>
+          <t>Gold / de-dollarization</t>
+        </is>
+      </c>
+      <c r="D223" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E223" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F223" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G223" s="9" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="H223" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B224" s="9" t="inlineStr">
+        <is>
+          <t>s13_insurance</t>
+        </is>
+      </c>
+      <c r="C224" s="9" t="inlineStr">
+        <is>
+          <t>Insurance retreat</t>
+        </is>
+      </c>
+      <c r="D224" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E224" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F224" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G224" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H224" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B225" s="9" t="inlineStr">
+        <is>
+          <t>s14_pensions</t>
+        </is>
+      </c>
+      <c r="C225" s="9" t="inlineStr">
+        <is>
+          <t>Pensions / demographics</t>
+        </is>
+      </c>
+      <c r="D225" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E225" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F225" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G225" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H225" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B226" s="9" t="inlineStr">
+        <is>
+          <t>s15_ai_power</t>
+        </is>
+      </c>
+      <c r="C226" s="9" t="inlineStr">
+        <is>
+          <t>AI power &amp; the grid bottleneck</t>
+        </is>
+      </c>
+      <c r="D226" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E226" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F226" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G226" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H226" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B227" s="9" t="inlineStr">
+        <is>
+          <t>s16_copper</t>
+        </is>
+      </c>
+      <c r="C227" s="9" t="inlineStr">
+        <is>
+          <t>Copper &amp; the electrification deficit</t>
+        </is>
+      </c>
+      <c r="D227" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E227" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F227" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G227" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H227" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B228" s="9" t="inlineStr">
+        <is>
+          <t>s17_water</t>
+        </is>
+      </c>
+      <c r="C228" s="9" t="inlineStr">
+        <is>
+          <t>Water - the underpriced input</t>
+        </is>
+      </c>
+      <c r="D228" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E228" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F228" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G228" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H228" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B229" s="9" t="inlineStr">
+        <is>
+          <t>s18_food_fertilizer</t>
+        </is>
+      </c>
+      <c r="C229" s="9" t="inlineStr">
+        <is>
+          <t>Food &amp; fertilizer fragility</t>
+        </is>
+      </c>
+      <c r="D229" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E229" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F229" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G229" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H229" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B230" s="9" t="inlineStr">
+        <is>
+          <t>s19_lithography</t>
+        </is>
+      </c>
+      <c r="C230" s="9" t="inlineStr">
+        <is>
+          <t>The lithography (ASML) chokepoint</t>
+        </is>
+      </c>
+      <c r="D230" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E230" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F230" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G230" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H230" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B231" s="9" t="inlineStr">
+        <is>
+          <t>s20_sea_lanes</t>
+        </is>
+      </c>
+      <c r="C231" s="9" t="inlineStr">
+        <is>
+          <t>Sea lanes &amp; undersea cables</t>
+        </is>
+      </c>
+      <c r="D231" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E231" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F231" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G231" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="H231" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B232" s="9" t="inlineStr">
+        <is>
+          <t>s21_clearinghouses</t>
+        </is>
+      </c>
+      <c r="C232" s="9" t="inlineStr">
+        <is>
+          <t>Clearinghouses (financial chokepoint)</t>
+        </is>
+      </c>
+      <c r="D232" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E232" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F232" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G232" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H232" s="9" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
@@ -13540,7 +14422,7 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>--- Daily narrative (2026-06-30) ---</t>
+          <t>--- Daily narrative (2026-07-01) ---</t>
         </is>
       </c>
     </row>
@@ -13554,7 +14436,7 @@
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>Overall macro risk ticked up to 5.8, driven by escalating AI infrastructure strain and consumer debt stress offsetting modest pension relief.</t>
+          <t>Macro risk remains elevated at 5.8 overall, with critical minerals and AI infrastructure constraints at High level driving structural vulnerabilities across finance, supply chains, and geopolitics.</t>
         </is>
       </c>
     </row>
@@ -13564,47 +14446,59 @@
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>**STORIES WITH LEVEL CHANGES**</t>
+          <t>**NO LEVEL CHANGES RECORDED TODAY**</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="inlineStr"/>
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>The dataset shows no intraday shifts; all risks remain at their standing levels.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>• **Hidden consumer debt: 5 → 6 (Elevated).** Subprime auto 60+ day delinquencies rose 0.5 percentage points to 6.8%; signals weakening household payment capacity and potential downstream credit losses.</t>
-        </is>
-      </c>
+      <c r="A19" s="12" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr"/>
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>**ELEVATED RISKS PERSISTING (15 stories)**</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>• **AI power &amp; the grid bottleneck: 6 → 7 (High).** Data-center moratoria have spread to widespread status and acute power-demand pressure persists; constrains AI capex rollout and risks brownouts in grid-stressed regions.</t>
+          <t>Key structural pressures holding steady:</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="inlineStr"/>
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>- **Critical minerals weaponization** (Level 7) and **AI power/grid bottleneck** (Level 7) remain the two highest-risk domains, creating cascading exposure across tech and industrial sectors.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>• **Food &amp; fertilizer fragility: 7 → 6 (Elevated).** China's tightened fertilizer export curbs remain in place but broader supply conditions have stabilized; reduces near-term crop-cost volatility risk.</t>
+          <t>- **Hidden leverage** via Treasury basis trades, Japanese carry positioning, and private credit opacity (all Level 6) sustain systemic fragility in shadow finance.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="inlineStr"/>
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>- **China's price spillover, hidden consumer debt, and food/fertilizer fragility** (Level 6) compound real-economy stress.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>• **Pensions / demographics: 5 → 4 (Moderate).** Public-pension funded ratios improved to 87.6% and Social Security debate remains at discussion stage; reduces acute fiscal cliff risk in near term.</t>
+          <t>- **CRE maturity walls and eurozone fragility** (Level 5) pose regional banking and sovereign risks.</t>
         </is>
       </c>
     </row>
@@ -13614,14 +14508,14 @@
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>**HIGHEST RISK TO WATCH**</t>
+          <t>**WATCH PRIORITY**</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>AI power &amp; the grid bottleneck at level 7—widespread moratoria combined with acute demand pressure risks sustained infrastructure investment delays and regional supply disruptions.</t>
+          <t>Critical minerals supply concentration remains the highest-risk chokepoint with no off-ramps visible.</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-07-01  -  generated 2026-07-01 14:07 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-07-02  -  generated 2026-07-02 13:30 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
         </is>
       </c>
       <c r="D2" s="7" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>162.384</v>
+        <v>161.122</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>6.7788</v>
+        <v>6.7742</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>4105.8999</v>
+        <v>4131</v>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>6.209</v>
+        <v>6.1905</v>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="D60" s="7" t="n">
-        <v>69.08</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="D62" s="7" t="n">
-        <v>16.71</v>
+        <v>16.23</v>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H232"/>
+  <dimension ref="A1:H253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -14330,6 +14330,888 @@
         </is>
       </c>
     </row>
+    <row r="233">
+      <c r="A233" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B233" s="9" t="inlineStr">
+        <is>
+          <t>s1_basis_trade</t>
+        </is>
+      </c>
+      <c r="C233" s="9" t="inlineStr">
+        <is>
+          <t>Treasury basis trade (hidden leverage)</t>
+        </is>
+      </c>
+      <c r="D233" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E233" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F233" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G233" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H233" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B234" s="9" t="inlineStr">
+        <is>
+          <t>s2_japan</t>
+        </is>
+      </c>
+      <c r="C234" s="9" t="inlineStr">
+        <is>
+          <t>Japan fiscal / JGB / carry trade</t>
+        </is>
+      </c>
+      <c r="D234" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E234" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F234" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G234" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H234" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B235" s="9" t="inlineStr">
+        <is>
+          <t>s3_private_credit</t>
+        </is>
+      </c>
+      <c r="C235" s="9" t="inlineStr">
+        <is>
+          <t>Private credit's opaque expansion</t>
+        </is>
+      </c>
+      <c r="D235" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E235" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F235" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G235" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="H235" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B236" s="9" t="inlineStr">
+        <is>
+          <t>s4_dev_debt</t>
+        </is>
+      </c>
+      <c r="C236" s="9" t="inlineStr">
+        <is>
+          <t>Developing-world debt crisis</t>
+        </is>
+      </c>
+      <c r="D236" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E236" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F236" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G236" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H236" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B237" s="9" t="inlineStr">
+        <is>
+          <t>s5_china_deflation</t>
+        </is>
+      </c>
+      <c r="C237" s="9" t="inlineStr">
+        <is>
+          <t>China's price spillover (deflation or cost-push)</t>
+        </is>
+      </c>
+      <c r="D237" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E237" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F237" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G237" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H237" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B238" s="9" t="inlineStr">
+        <is>
+          <t>s6_rare_earths</t>
+        </is>
+      </c>
+      <c r="C238" s="9" t="inlineStr">
+        <is>
+          <t>Critical minerals as a weapon</t>
+        </is>
+      </c>
+      <c r="D238" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E238" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F238" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G238" s="9" t="inlineStr">
+        <is>
+          <t>6.75</t>
+        </is>
+      </c>
+      <c r="H238" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B239" s="9" t="inlineStr">
+        <is>
+          <t>s7_stablecoins</t>
+        </is>
+      </c>
+      <c r="C239" s="9" t="inlineStr">
+        <is>
+          <t>Stablecoins &amp; Treasury demand</t>
+        </is>
+      </c>
+      <c r="D239" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E239" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F239" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G239" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H239" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B240" s="9" t="inlineStr">
+        <is>
+          <t>s8_ai_capex</t>
+        </is>
+      </c>
+      <c r="C240" s="9" t="inlineStr">
+        <is>
+          <t>AI build-out circular financing</t>
+        </is>
+      </c>
+      <c r="D240" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E240" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F240" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G240" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H240" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B241" s="9" t="inlineStr">
+        <is>
+          <t>s9_cre</t>
+        </is>
+      </c>
+      <c r="C241" s="9" t="inlineStr">
+        <is>
+          <t>CRE maturity wall / regional banks</t>
+        </is>
+      </c>
+      <c r="D241" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E241" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F241" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G241" s="9" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="H241" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B242" s="9" t="inlineStr">
+        <is>
+          <t>s10_france</t>
+        </is>
+      </c>
+      <c r="C242" s="9" t="inlineStr">
+        <is>
+          <t>France / eurozone fragility</t>
+        </is>
+      </c>
+      <c r="D242" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E242" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F242" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G242" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H242" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B243" s="9" t="inlineStr">
+        <is>
+          <t>s11_consumer_debt</t>
+        </is>
+      </c>
+      <c r="C243" s="9" t="inlineStr">
+        <is>
+          <t>Hidden consumer debt</t>
+        </is>
+      </c>
+      <c r="D243" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E243" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F243" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G243" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H243" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B244" s="9" t="inlineStr">
+        <is>
+          <t>s12_gold_dedollar</t>
+        </is>
+      </c>
+      <c r="C244" s="9" t="inlineStr">
+        <is>
+          <t>Gold / de-dollarization</t>
+        </is>
+      </c>
+      <c r="D244" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E244" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F244" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G244" s="9" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="H244" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B245" s="9" t="inlineStr">
+        <is>
+          <t>s13_insurance</t>
+        </is>
+      </c>
+      <c r="C245" s="9" t="inlineStr">
+        <is>
+          <t>Insurance retreat</t>
+        </is>
+      </c>
+      <c r="D245" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E245" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F245" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G245" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H245" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B246" s="9" t="inlineStr">
+        <is>
+          <t>s14_pensions</t>
+        </is>
+      </c>
+      <c r="C246" s="9" t="inlineStr">
+        <is>
+          <t>Pensions / demographics</t>
+        </is>
+      </c>
+      <c r="D246" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E246" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F246" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G246" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H246" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B247" s="9" t="inlineStr">
+        <is>
+          <t>s15_ai_power</t>
+        </is>
+      </c>
+      <c r="C247" s="9" t="inlineStr">
+        <is>
+          <t>AI power &amp; the grid bottleneck</t>
+        </is>
+      </c>
+      <c r="D247" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E247" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F247" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G247" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H247" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B248" s="9" t="inlineStr">
+        <is>
+          <t>s16_copper</t>
+        </is>
+      </c>
+      <c r="C248" s="9" t="inlineStr">
+        <is>
+          <t>Copper &amp; the electrification deficit</t>
+        </is>
+      </c>
+      <c r="D248" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E248" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F248" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G248" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H248" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B249" s="9" t="inlineStr">
+        <is>
+          <t>s17_water</t>
+        </is>
+      </c>
+      <c r="C249" s="9" t="inlineStr">
+        <is>
+          <t>Water - the underpriced input</t>
+        </is>
+      </c>
+      <c r="D249" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E249" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F249" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G249" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H249" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B250" s="9" t="inlineStr">
+        <is>
+          <t>s18_food_fertilizer</t>
+        </is>
+      </c>
+      <c r="C250" s="9" t="inlineStr">
+        <is>
+          <t>Food &amp; fertilizer fragility</t>
+        </is>
+      </c>
+      <c r="D250" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E250" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F250" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G250" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H250" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B251" s="9" t="inlineStr">
+        <is>
+          <t>s19_lithography</t>
+        </is>
+      </c>
+      <c r="C251" s="9" t="inlineStr">
+        <is>
+          <t>The lithography (ASML) chokepoint</t>
+        </is>
+      </c>
+      <c r="D251" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E251" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F251" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G251" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H251" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B252" s="9" t="inlineStr">
+        <is>
+          <t>s20_sea_lanes</t>
+        </is>
+      </c>
+      <c r="C252" s="9" t="inlineStr">
+        <is>
+          <t>Sea lanes &amp; undersea cables</t>
+        </is>
+      </c>
+      <c r="D252" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E252" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F252" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G252" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="H252" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B253" s="9" t="inlineStr">
+        <is>
+          <t>s21_clearinghouses</t>
+        </is>
+      </c>
+      <c r="C253" s="9" t="inlineStr">
+        <is>
+          <t>Clearinghouses (financial chokepoint)</t>
+        </is>
+      </c>
+      <c r="D253" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E253" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F253" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G253" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H253" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14341,7 +15223,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A28"/>
+  <dimension ref="A1:A24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -14422,100 +15304,68 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>--- Daily narrative (2026-07-01) ---</t>
+          <t>--- Daily narrative (2026-07-02) ---</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>**HEADLINE**</t>
+          <t># EOD MACRO-RISK BRIEF | 2 July 2026</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>Macro risk remains elevated at 5.8 overall, with critical minerals and AI infrastructure constraints at High level driving structural vulnerabilities across finance, supply chains, and geopolitics.</t>
-        </is>
-      </c>
+      <c r="A15" s="12" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr"/>
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>**Overall risk stands at 5.8/10—Elevated—with no intraday moves but two High-level structural vulnerabilities persistent.**</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>**NO LEVEL CHANGES RECORDED TODAY**</t>
-        </is>
-      </c>
+      <c r="A17" s="12" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>The dataset shows no intraday shifts; all risks remain at their standing levels.</t>
+          <t>No risk levels changed today. However, two stories remain at High (7/10):</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr"/>
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>- **AI power &amp; the grid bottleneck**: Electricity capacity constraints threaten AI infrastructure scaling; grid investment lag creates supply-demand mismatch.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>**ELEVATED RISKS PERSISTING (15 stories)**</t>
+          <t>- **Critical minerals as a weapon**: Concentrated supply chains in strategic commodities expose economies to supply disruption or coercion.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>Key structural pressures holding steady:</t>
-        </is>
-      </c>
+      <c r="A21" s="12" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>- **Critical minerals weaponization** (Level 7) and **AI power/grid bottleneck** (Level 7) remain the two highest-risk domains, creating cascading exposure across tech and industrial sectors.</t>
+          <t>Nine additional risks sit at Elevated (6/10), spanning financial leverage (Treasury basis trades, private credit opacity), geopolitical spillovers (China deflation, sea lanes), and structural imbalances (CRE maturity wall, hidden consumer debt, lithography chokepoint).</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>- **Hidden leverage** via Treasury basis trades, Japanese carry positioning, and private credit opacity (all Level 6) sustain systemic fragility in shadow finance.</t>
-        </is>
-      </c>
+      <c r="A23" s="12" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>- **China's price spillover, hidden consumer debt, and food/fertilizer fragility** (Level 6) compound real-economy stress.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>- **CRE maturity walls and eurozone fragility** (Level 5) pose regional banking and sovereign risks.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="12" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>**WATCH PRIORITY**</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="12" t="inlineStr">
-        <is>
-          <t>Critical minerals supply concentration remains the highest-risk chokepoint with no off-ramps visible.</t>
+          <t>**Watch**: AI power &amp; grid bottleneck—energy constraints may become the binding constraint on AI capex assumptions embedded across equity and credit valuations.</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-07-02  -  generated 2026-07-02 13:30 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-07-03  -  generated 2026-07-03 13:42 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>161.122</v>
+        <v>161.242</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>6.7742</v>
+        <v>6.7694</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -3330,7 +3330,7 @@
         </is>
       </c>
       <c r="D33" s="7" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>4131</v>
+        <v>4178.8999</v>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>6.1905</v>
+        <v>6.213</v>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="D60" s="7" t="n">
-        <v>67.56999999999999</v>
+        <v>68.66</v>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="D62" s="7" t="n">
-        <v>16.23</v>
+        <v>15.93</v>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H253"/>
+  <dimension ref="A1:H274"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -15212,6 +15212,888 @@
         </is>
       </c>
     </row>
+    <row r="254">
+      <c r="A254" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B254" s="9" t="inlineStr">
+        <is>
+          <t>s1_basis_trade</t>
+        </is>
+      </c>
+      <c r="C254" s="9" t="inlineStr">
+        <is>
+          <t>Treasury basis trade (hidden leverage)</t>
+        </is>
+      </c>
+      <c r="D254" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E254" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F254" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G254" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H254" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B255" s="9" t="inlineStr">
+        <is>
+          <t>s2_japan</t>
+        </is>
+      </c>
+      <c r="C255" s="9" t="inlineStr">
+        <is>
+          <t>Japan fiscal / JGB / carry trade</t>
+        </is>
+      </c>
+      <c r="D255" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E255" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F255" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G255" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H255" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B256" s="9" t="inlineStr">
+        <is>
+          <t>s3_private_credit</t>
+        </is>
+      </c>
+      <c r="C256" s="9" t="inlineStr">
+        <is>
+          <t>Private credit's opaque expansion</t>
+        </is>
+      </c>
+      <c r="D256" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E256" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F256" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G256" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="H256" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B257" s="9" t="inlineStr">
+        <is>
+          <t>s4_dev_debt</t>
+        </is>
+      </c>
+      <c r="C257" s="9" t="inlineStr">
+        <is>
+          <t>Developing-world debt crisis</t>
+        </is>
+      </c>
+      <c r="D257" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E257" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F257" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G257" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H257" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B258" s="9" t="inlineStr">
+        <is>
+          <t>s5_china_deflation</t>
+        </is>
+      </c>
+      <c r="C258" s="9" t="inlineStr">
+        <is>
+          <t>China's price spillover (deflation or cost-push)</t>
+        </is>
+      </c>
+      <c r="D258" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E258" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F258" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G258" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H258" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B259" s="9" t="inlineStr">
+        <is>
+          <t>s6_rare_earths</t>
+        </is>
+      </c>
+      <c r="C259" s="9" t="inlineStr">
+        <is>
+          <t>Critical minerals as a weapon</t>
+        </is>
+      </c>
+      <c r="D259" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E259" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F259" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G259" s="9" t="inlineStr">
+        <is>
+          <t>6.75</t>
+        </is>
+      </c>
+      <c r="H259" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B260" s="9" t="inlineStr">
+        <is>
+          <t>s7_stablecoins</t>
+        </is>
+      </c>
+      <c r="C260" s="9" t="inlineStr">
+        <is>
+          <t>Stablecoins &amp; Treasury demand</t>
+        </is>
+      </c>
+      <c r="D260" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E260" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F260" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G260" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H260" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B261" s="9" t="inlineStr">
+        <is>
+          <t>s8_ai_capex</t>
+        </is>
+      </c>
+      <c r="C261" s="9" t="inlineStr">
+        <is>
+          <t>AI build-out circular financing</t>
+        </is>
+      </c>
+      <c r="D261" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E261" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F261" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G261" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H261" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B262" s="9" t="inlineStr">
+        <is>
+          <t>s9_cre</t>
+        </is>
+      </c>
+      <c r="C262" s="9" t="inlineStr">
+        <is>
+          <t>CRE maturity wall / regional banks</t>
+        </is>
+      </c>
+      <c r="D262" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E262" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F262" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G262" s="9" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="H262" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B263" s="9" t="inlineStr">
+        <is>
+          <t>s10_france</t>
+        </is>
+      </c>
+      <c r="C263" s="9" t="inlineStr">
+        <is>
+          <t>France / eurozone fragility</t>
+        </is>
+      </c>
+      <c r="D263" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E263" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F263" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G263" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H263" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B264" s="9" t="inlineStr">
+        <is>
+          <t>s11_consumer_debt</t>
+        </is>
+      </c>
+      <c r="C264" s="9" t="inlineStr">
+        <is>
+          <t>Hidden consumer debt</t>
+        </is>
+      </c>
+      <c r="D264" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E264" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F264" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G264" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H264" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B265" s="9" t="inlineStr">
+        <is>
+          <t>s12_gold_dedollar</t>
+        </is>
+      </c>
+      <c r="C265" s="9" t="inlineStr">
+        <is>
+          <t>Gold / de-dollarization</t>
+        </is>
+      </c>
+      <c r="D265" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E265" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F265" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G265" s="9" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="H265" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B266" s="9" t="inlineStr">
+        <is>
+          <t>s13_insurance</t>
+        </is>
+      </c>
+      <c r="C266" s="9" t="inlineStr">
+        <is>
+          <t>Insurance retreat</t>
+        </is>
+      </c>
+      <c r="D266" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E266" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F266" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G266" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H266" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B267" s="9" t="inlineStr">
+        <is>
+          <t>s14_pensions</t>
+        </is>
+      </c>
+      <c r="C267" s="9" t="inlineStr">
+        <is>
+          <t>Pensions / demographics</t>
+        </is>
+      </c>
+      <c r="D267" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E267" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F267" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G267" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H267" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B268" s="9" t="inlineStr">
+        <is>
+          <t>s15_ai_power</t>
+        </is>
+      </c>
+      <c r="C268" s="9" t="inlineStr">
+        <is>
+          <t>AI power &amp; the grid bottleneck</t>
+        </is>
+      </c>
+      <c r="D268" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E268" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F268" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G268" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H268" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B269" s="9" t="inlineStr">
+        <is>
+          <t>s16_copper</t>
+        </is>
+      </c>
+      <c r="C269" s="9" t="inlineStr">
+        <is>
+          <t>Copper &amp; the electrification deficit</t>
+        </is>
+      </c>
+      <c r="D269" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E269" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F269" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G269" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H269" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B270" s="9" t="inlineStr">
+        <is>
+          <t>s17_water</t>
+        </is>
+      </c>
+      <c r="C270" s="9" t="inlineStr">
+        <is>
+          <t>Water - the underpriced input</t>
+        </is>
+      </c>
+      <c r="D270" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E270" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F270" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G270" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H270" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B271" s="9" t="inlineStr">
+        <is>
+          <t>s18_food_fertilizer</t>
+        </is>
+      </c>
+      <c r="C271" s="9" t="inlineStr">
+        <is>
+          <t>Food &amp; fertilizer fragility</t>
+        </is>
+      </c>
+      <c r="D271" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E271" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F271" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G271" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H271" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B272" s="9" t="inlineStr">
+        <is>
+          <t>s19_lithography</t>
+        </is>
+      </c>
+      <c r="C272" s="9" t="inlineStr">
+        <is>
+          <t>The lithography (ASML) chokepoint</t>
+        </is>
+      </c>
+      <c r="D272" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E272" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F272" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G272" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H272" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B273" s="9" t="inlineStr">
+        <is>
+          <t>s20_sea_lanes</t>
+        </is>
+      </c>
+      <c r="C273" s="9" t="inlineStr">
+        <is>
+          <t>Sea lanes &amp; undersea cables</t>
+        </is>
+      </c>
+      <c r="D273" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E273" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F273" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G273" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="H273" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B274" s="9" t="inlineStr">
+        <is>
+          <t>s21_clearinghouses</t>
+        </is>
+      </c>
+      <c r="C274" s="9" t="inlineStr">
+        <is>
+          <t>Clearinghouses (financial chokepoint)</t>
+        </is>
+      </c>
+      <c r="D274" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E274" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F274" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G274" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H274" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15223,7 +16105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A24"/>
+  <dimension ref="A1:A21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -15304,14 +16186,14 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>--- Daily narrative (2026-07-02) ---</t>
+          <t>--- Daily narrative (2026-07-03) ---</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t># EOD MACRO-RISK BRIEF | 2 July 2026</t>
+          <t># EOD Macro-Risk Brief | 2026-07-03</t>
         </is>
       </c>
     </row>
@@ -15321,7 +16203,7 @@
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>**Overall risk stands at 5.8/10—Elevated—with no intraday moves but two High-level structural vulnerabilities persistent.**</t>
+          <t>**Headline:** Overall risk stable at 5.8, but developing-world debt crisis escalated to Elevated on higher US real yields.</t>
         </is>
       </c>
     </row>
@@ -15331,41 +16213,24 @@
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>No risk levels changed today. However, two stories remain at High (7/10):</t>
+          <t>**Stories with level changes:**</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>- **AI power &amp; the grid bottleneck**: Electricity capacity constraints threaten AI infrastructure scaling; grid investment lag creates supply-demand mismatch.</t>
+          <t>• **Developing-world debt crisis** (5→6, now Elevated): US 10y real yield rose 50bps to 2.25%, widening debt service costs for emerging markets and increasing refinancing pressure.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
-          <t>- **Critical minerals as a weapon**: Concentrated supply chains in strategic commodities expose economies to supply disruption or coercion.</t>
-        </is>
-      </c>
+      <c r="A20" s="12" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t>Nine additional risks sit at Elevated (6/10), spanning financial leverage (Treasury basis trades, private credit opacity), geopolitical spillovers (China deflation, sea lanes), and structural imbalances (CRE maturity wall, hidden consumer debt, lithography chokepoint).</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="12" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="12" t="inlineStr">
-        <is>
-          <t>**Watch**: AI power &amp; grid bottleneck—energy constraints may become the binding constraint on AI capex assumptions embedded across equity and credit valuations.</t>
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>**Highest-risk watch:** Critical minerals as a weapon and AI power &amp; grid bottleneck both remain at level 7 (High); the latter poses acute infrastructure constraints as build-out accelerates.</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-07-03  -  generated 2026-07-03 13:42 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-07-03  -  generated 2026-07-03 20:58 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>161.242</v>
+        <v>161.357</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>3.88</v>
+        <v>3.937</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
       </c>
       <c r="L6" s="8" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>mof_jgb:30</t>
         </is>
       </c>
       <c r="M6" s="4" t="inlineStr">
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>6.7694</v>
+        <v>6.7702</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.15</v>
+        <v>0.09</v>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
       </c>
       <c r="L21" s="8" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>llama:largest_peg_dev</t>
         </is>
       </c>
       <c r="M21" s="4" t="inlineStr">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>325</v>
+        <v>310.4</v>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
@@ -2672,12 +2672,12 @@
       </c>
       <c r="L22" s="8" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>llama:stablecoin_total_bn</t>
         </is>
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="N22" s="4" t="inlineStr">
@@ -2769,7 +2769,7 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.76</v>
+        <v>0.75</v>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>4178.8999</v>
+        <v>4187.2998</v>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
@@ -4009,7 +4009,7 @@
         </is>
       </c>
       <c r="D44" s="7" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>6.213</v>
+        <v>6.224</v>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="D60" s="7" t="n">
-        <v>68.66</v>
+        <v>68.78</v>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="D62" s="7" t="n">
-        <v>15.93</v>
+        <v>15.81</v>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H274"/>
+  <dimension ref="A1:H295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -16089,6 +16089,888 @@
         </is>
       </c>
       <c r="H274" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B275" s="9" t="inlineStr">
+        <is>
+          <t>s1_basis_trade</t>
+        </is>
+      </c>
+      <c r="C275" s="9" t="inlineStr">
+        <is>
+          <t>Treasury basis trade (hidden leverage)</t>
+        </is>
+      </c>
+      <c r="D275" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E275" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F275" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G275" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H275" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B276" s="9" t="inlineStr">
+        <is>
+          <t>s2_japan</t>
+        </is>
+      </c>
+      <c r="C276" s="9" t="inlineStr">
+        <is>
+          <t>Japan fiscal / JGB / carry trade</t>
+        </is>
+      </c>
+      <c r="D276" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E276" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F276" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G276" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H276" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B277" s="9" t="inlineStr">
+        <is>
+          <t>s3_private_credit</t>
+        </is>
+      </c>
+      <c r="C277" s="9" t="inlineStr">
+        <is>
+          <t>Private credit's opaque expansion</t>
+        </is>
+      </c>
+      <c r="D277" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E277" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F277" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G277" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="H277" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B278" s="9" t="inlineStr">
+        <is>
+          <t>s4_dev_debt</t>
+        </is>
+      </c>
+      <c r="C278" s="9" t="inlineStr">
+        <is>
+          <t>Developing-world debt crisis</t>
+        </is>
+      </c>
+      <c r="D278" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E278" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F278" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G278" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H278" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B279" s="9" t="inlineStr">
+        <is>
+          <t>s5_china_deflation</t>
+        </is>
+      </c>
+      <c r="C279" s="9" t="inlineStr">
+        <is>
+          <t>China's price spillover (deflation or cost-push)</t>
+        </is>
+      </c>
+      <c r="D279" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E279" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F279" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G279" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H279" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B280" s="9" t="inlineStr">
+        <is>
+          <t>s6_rare_earths</t>
+        </is>
+      </c>
+      <c r="C280" s="9" t="inlineStr">
+        <is>
+          <t>Critical minerals as a weapon</t>
+        </is>
+      </c>
+      <c r="D280" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E280" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F280" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G280" s="9" t="inlineStr">
+        <is>
+          <t>6.75</t>
+        </is>
+      </c>
+      <c r="H280" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B281" s="9" t="inlineStr">
+        <is>
+          <t>s7_stablecoins</t>
+        </is>
+      </c>
+      <c r="C281" s="9" t="inlineStr">
+        <is>
+          <t>Stablecoins &amp; Treasury demand</t>
+        </is>
+      </c>
+      <c r="D281" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E281" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F281" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G281" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H281" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B282" s="9" t="inlineStr">
+        <is>
+          <t>s8_ai_capex</t>
+        </is>
+      </c>
+      <c r="C282" s="9" t="inlineStr">
+        <is>
+          <t>AI build-out circular financing</t>
+        </is>
+      </c>
+      <c r="D282" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E282" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F282" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G282" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H282" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B283" s="9" t="inlineStr">
+        <is>
+          <t>s9_cre</t>
+        </is>
+      </c>
+      <c r="C283" s="9" t="inlineStr">
+        <is>
+          <t>CRE maturity wall / regional banks</t>
+        </is>
+      </c>
+      <c r="D283" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E283" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F283" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G283" s="9" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="H283" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B284" s="9" t="inlineStr">
+        <is>
+          <t>s10_france</t>
+        </is>
+      </c>
+      <c r="C284" s="9" t="inlineStr">
+        <is>
+          <t>France / eurozone fragility</t>
+        </is>
+      </c>
+      <c r="D284" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E284" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F284" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G284" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H284" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B285" s="9" t="inlineStr">
+        <is>
+          <t>s11_consumer_debt</t>
+        </is>
+      </c>
+      <c r="C285" s="9" t="inlineStr">
+        <is>
+          <t>Hidden consumer debt</t>
+        </is>
+      </c>
+      <c r="D285" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E285" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F285" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G285" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H285" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B286" s="9" t="inlineStr">
+        <is>
+          <t>s12_gold_dedollar</t>
+        </is>
+      </c>
+      <c r="C286" s="9" t="inlineStr">
+        <is>
+          <t>Gold / de-dollarization</t>
+        </is>
+      </c>
+      <c r="D286" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E286" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F286" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G286" s="9" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="H286" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B287" s="9" t="inlineStr">
+        <is>
+          <t>s13_insurance</t>
+        </is>
+      </c>
+      <c r="C287" s="9" t="inlineStr">
+        <is>
+          <t>Insurance retreat</t>
+        </is>
+      </c>
+      <c r="D287" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E287" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F287" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G287" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H287" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B288" s="9" t="inlineStr">
+        <is>
+          <t>s14_pensions</t>
+        </is>
+      </c>
+      <c r="C288" s="9" t="inlineStr">
+        <is>
+          <t>Pensions / demographics</t>
+        </is>
+      </c>
+      <c r="D288" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E288" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F288" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G288" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H288" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B289" s="9" t="inlineStr">
+        <is>
+          <t>s15_ai_power</t>
+        </is>
+      </c>
+      <c r="C289" s="9" t="inlineStr">
+        <is>
+          <t>AI power &amp; the grid bottleneck</t>
+        </is>
+      </c>
+      <c r="D289" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E289" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F289" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G289" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H289" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B290" s="9" t="inlineStr">
+        <is>
+          <t>s16_copper</t>
+        </is>
+      </c>
+      <c r="C290" s="9" t="inlineStr">
+        <is>
+          <t>Copper &amp; the electrification deficit</t>
+        </is>
+      </c>
+      <c r="D290" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E290" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F290" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G290" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H290" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B291" s="9" t="inlineStr">
+        <is>
+          <t>s17_water</t>
+        </is>
+      </c>
+      <c r="C291" s="9" t="inlineStr">
+        <is>
+          <t>Water - the underpriced input</t>
+        </is>
+      </c>
+      <c r="D291" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E291" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F291" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G291" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H291" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B292" s="9" t="inlineStr">
+        <is>
+          <t>s18_food_fertilizer</t>
+        </is>
+      </c>
+      <c r="C292" s="9" t="inlineStr">
+        <is>
+          <t>Food &amp; fertilizer fragility</t>
+        </is>
+      </c>
+      <c r="D292" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E292" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F292" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G292" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H292" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B293" s="9" t="inlineStr">
+        <is>
+          <t>s19_lithography</t>
+        </is>
+      </c>
+      <c r="C293" s="9" t="inlineStr">
+        <is>
+          <t>The lithography (ASML) chokepoint</t>
+        </is>
+      </c>
+      <c r="D293" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E293" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F293" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G293" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H293" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B294" s="9" t="inlineStr">
+        <is>
+          <t>s20_sea_lanes</t>
+        </is>
+      </c>
+      <c r="C294" s="9" t="inlineStr">
+        <is>
+          <t>Sea lanes &amp; undersea cables</t>
+        </is>
+      </c>
+      <c r="D294" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E294" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F294" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G294" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="H294" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B295" s="9" t="inlineStr">
+        <is>
+          <t>s21_clearinghouses</t>
+        </is>
+      </c>
+      <c r="C295" s="9" t="inlineStr">
+        <is>
+          <t>Clearinghouses (financial chokepoint)</t>
+        </is>
+      </c>
+      <c r="D295" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E295" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F295" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G295" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H295" s="9" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
@@ -16193,44 +17075,48 @@
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t># EOD Macro-Risk Brief | 2026-07-03</t>
+          <t>**HEADLINE**</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr"/>
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>Macro risk remains elevated at 6.2 overall; Japan carry-trade vulnerability intensified as 30-year JGB yields spike.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>**Headline:** Overall risk stable at 5.8, but developing-world debt crisis escalated to Elevated on higher US real yields.</t>
-        </is>
-      </c>
+      <c r="A16" s="12" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr"/>
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>**CHANGES**</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>**Stories with level changes:**</t>
+          <t>• **Japan fiscal / JGB / carry trade** (6→7, now High): 30-year JGB yield jumped to 3.937% (band shift +1.0), lifting risk from Elevated to High; tighter funding costs and unwind risk in yen-funded positions globally.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>• **Developing-world debt crisis** (5→6, now Elevated): US 10y real yield rose 50bps to 2.25%, widening debt service costs for emerging markets and increasing refinancing pressure.</t>
-        </is>
-      </c>
+      <c r="A19" s="12" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr"/>
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>**KEY WATCH**</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>**Highest-risk watch:** Critical minerals as a weapon and AI power &amp; grid bottleneck both remain at level 7 (High); the latter poses acute infrastructure constraints as build-out accelerates.</t>
+          <t>Three stories now sit at Level 7 (High): Japan carry trade, Critical minerals weaponization, and AI power/grid bottleneck—Japan's move most acute for near-term leverage unwind.</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-07-03  -  generated 2026-07-03 20:58 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-07-03  -  generated 2026-07-03 21:41 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>161.357</v>
+        <v>161.337</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>310.4</v>
+        <v>310.5</v>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H295"/>
+  <dimension ref="A1:H316"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -16976,6 +16976,888 @@
         </is>
       </c>
     </row>
+    <row r="296">
+      <c r="A296" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B296" s="9" t="inlineStr">
+        <is>
+          <t>s1_basis_trade</t>
+        </is>
+      </c>
+      <c r="C296" s="9" t="inlineStr">
+        <is>
+          <t>Treasury basis trade (hidden leverage)</t>
+        </is>
+      </c>
+      <c r="D296" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E296" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F296" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G296" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H296" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B297" s="9" t="inlineStr">
+        <is>
+          <t>s2_japan</t>
+        </is>
+      </c>
+      <c r="C297" s="9" t="inlineStr">
+        <is>
+          <t>Japan fiscal / JGB / carry trade</t>
+        </is>
+      </c>
+      <c r="D297" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E297" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F297" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G297" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H297" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B298" s="9" t="inlineStr">
+        <is>
+          <t>s3_private_credit</t>
+        </is>
+      </c>
+      <c r="C298" s="9" t="inlineStr">
+        <is>
+          <t>Private credit's opaque expansion</t>
+        </is>
+      </c>
+      <c r="D298" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E298" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F298" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G298" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="H298" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B299" s="9" t="inlineStr">
+        <is>
+          <t>s4_dev_debt</t>
+        </is>
+      </c>
+      <c r="C299" s="9" t="inlineStr">
+        <is>
+          <t>Developing-world debt crisis</t>
+        </is>
+      </c>
+      <c r="D299" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E299" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F299" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G299" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H299" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B300" s="9" t="inlineStr">
+        <is>
+          <t>s5_china_deflation</t>
+        </is>
+      </c>
+      <c r="C300" s="9" t="inlineStr">
+        <is>
+          <t>China's price spillover (deflation or cost-push)</t>
+        </is>
+      </c>
+      <c r="D300" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E300" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F300" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G300" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H300" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B301" s="9" t="inlineStr">
+        <is>
+          <t>s6_rare_earths</t>
+        </is>
+      </c>
+      <c r="C301" s="9" t="inlineStr">
+        <is>
+          <t>Critical minerals as a weapon</t>
+        </is>
+      </c>
+      <c r="D301" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E301" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F301" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G301" s="9" t="inlineStr">
+        <is>
+          <t>6.75</t>
+        </is>
+      </c>
+      <c r="H301" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B302" s="9" t="inlineStr">
+        <is>
+          <t>s7_stablecoins</t>
+        </is>
+      </c>
+      <c r="C302" s="9" t="inlineStr">
+        <is>
+          <t>Stablecoins &amp; Treasury demand</t>
+        </is>
+      </c>
+      <c r="D302" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E302" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F302" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G302" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H302" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B303" s="9" t="inlineStr">
+        <is>
+          <t>s8_ai_capex</t>
+        </is>
+      </c>
+      <c r="C303" s="9" t="inlineStr">
+        <is>
+          <t>AI build-out circular financing</t>
+        </is>
+      </c>
+      <c r="D303" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E303" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F303" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G303" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H303" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B304" s="9" t="inlineStr">
+        <is>
+          <t>s9_cre</t>
+        </is>
+      </c>
+      <c r="C304" s="9" t="inlineStr">
+        <is>
+          <t>CRE maturity wall / regional banks</t>
+        </is>
+      </c>
+      <c r="D304" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E304" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F304" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G304" s="9" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="H304" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B305" s="9" t="inlineStr">
+        <is>
+          <t>s10_france</t>
+        </is>
+      </c>
+      <c r="C305" s="9" t="inlineStr">
+        <is>
+          <t>France / eurozone fragility</t>
+        </is>
+      </c>
+      <c r="D305" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E305" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F305" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G305" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H305" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B306" s="9" t="inlineStr">
+        <is>
+          <t>s11_consumer_debt</t>
+        </is>
+      </c>
+      <c r="C306" s="9" t="inlineStr">
+        <is>
+          <t>Hidden consumer debt</t>
+        </is>
+      </c>
+      <c r="D306" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E306" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F306" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G306" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H306" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B307" s="9" t="inlineStr">
+        <is>
+          <t>s12_gold_dedollar</t>
+        </is>
+      </c>
+      <c r="C307" s="9" t="inlineStr">
+        <is>
+          <t>Gold / de-dollarization</t>
+        </is>
+      </c>
+      <c r="D307" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E307" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F307" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G307" s="9" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="H307" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B308" s="9" t="inlineStr">
+        <is>
+          <t>s13_insurance</t>
+        </is>
+      </c>
+      <c r="C308" s="9" t="inlineStr">
+        <is>
+          <t>Insurance retreat</t>
+        </is>
+      </c>
+      <c r="D308" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E308" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F308" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G308" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H308" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B309" s="9" t="inlineStr">
+        <is>
+          <t>s14_pensions</t>
+        </is>
+      </c>
+      <c r="C309" s="9" t="inlineStr">
+        <is>
+          <t>Pensions / demographics</t>
+        </is>
+      </c>
+      <c r="D309" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E309" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F309" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G309" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H309" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B310" s="9" t="inlineStr">
+        <is>
+          <t>s15_ai_power</t>
+        </is>
+      </c>
+      <c r="C310" s="9" t="inlineStr">
+        <is>
+          <t>AI power &amp; the grid bottleneck</t>
+        </is>
+      </c>
+      <c r="D310" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E310" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F310" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G310" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H310" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B311" s="9" t="inlineStr">
+        <is>
+          <t>s16_copper</t>
+        </is>
+      </c>
+      <c r="C311" s="9" t="inlineStr">
+        <is>
+          <t>Copper &amp; the electrification deficit</t>
+        </is>
+      </c>
+      <c r="D311" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E311" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F311" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G311" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H311" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B312" s="9" t="inlineStr">
+        <is>
+          <t>s17_water</t>
+        </is>
+      </c>
+      <c r="C312" s="9" t="inlineStr">
+        <is>
+          <t>Water - the underpriced input</t>
+        </is>
+      </c>
+      <c r="D312" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E312" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F312" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G312" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H312" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B313" s="9" t="inlineStr">
+        <is>
+          <t>s18_food_fertilizer</t>
+        </is>
+      </c>
+      <c r="C313" s="9" t="inlineStr">
+        <is>
+          <t>Food &amp; fertilizer fragility</t>
+        </is>
+      </c>
+      <c r="D313" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E313" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F313" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G313" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H313" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B314" s="9" t="inlineStr">
+        <is>
+          <t>s19_lithography</t>
+        </is>
+      </c>
+      <c r="C314" s="9" t="inlineStr">
+        <is>
+          <t>The lithography (ASML) chokepoint</t>
+        </is>
+      </c>
+      <c r="D314" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E314" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F314" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G314" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H314" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B315" s="9" t="inlineStr">
+        <is>
+          <t>s20_sea_lanes</t>
+        </is>
+      </c>
+      <c r="C315" s="9" t="inlineStr">
+        <is>
+          <t>Sea lanes &amp; undersea cables</t>
+        </is>
+      </c>
+      <c r="D315" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E315" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F315" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G315" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="H315" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B316" s="9" t="inlineStr">
+        <is>
+          <t>s21_clearinghouses</t>
+        </is>
+      </c>
+      <c r="C316" s="9" t="inlineStr">
+        <is>
+          <t>Clearinghouses (financial chokepoint)</t>
+        </is>
+      </c>
+      <c r="D316" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E316" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F316" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G316" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H316" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16987,7 +17869,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A21"/>
+  <dimension ref="A1:A27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -17082,7 +17964,7 @@
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>Macro risk remains elevated at 6.2 overall; Japan carry-trade vulnerability intensified as 30-year JGB yields spike.</t>
+          <t>Macro risk remains elevated at 6.2, with three High-rated threats—Japan carry-trade unwinding, critical minerals weaponization, and AI power constraints—posing systemic spillover potential.</t>
         </is>
       </c>
     </row>
@@ -17092,14 +17974,14 @@
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>**CHANGES**</t>
+          <t>**STORIES WITH LEVEL CHANGES**</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>• **Japan fiscal / JGB / carry trade** (6→7, now High): 30-year JGB yield jumped to 3.937% (band shift +1.0), lifting risk from Elevated to High; tighter funding costs and unwind risk in yen-funded positions globally.</t>
+          <t>No stories changed risk level today.</t>
         </is>
       </c>
     </row>
@@ -17109,14 +17991,52 @@
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>**KEY WATCH**</t>
+          <t>**ELEVATED OR HIGHER RISKS (15 active)**</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>Three stories now sit at Level 7 (High): Japan carry trade, Critical minerals weaponization, and AI power/grid bottleneck—Japan's move most acute for near-term leverage unwind.</t>
+          <t>- **Japan fiscal/JGB/carry trade (Level 7, High):** Structural imbalance in JGB yields and yen carry positioning creates acute unwinding risk; could trigger forced deleveraging across global markets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>- **Critical minerals as weapon (Level 7, High):** Geopolitical control of rare earths and battery metals threatens supply chains; direct exposure to industrial and energy transition timelines.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>- **AI power &amp; grid bottleneck (Level 7, High):** Data center demand outpacing grid capacity; infrastructure lag risks compute-driven financing models and stranded capex.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>- **Treasury basis / Private credit / Hidden consumer debt / Food fragility / Lithography chokepoint / Sea lanes (Levels 5–6, Elevated):** Secondary leverage, opacity, and supply concentration amplify contagion vectors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>**WATCH**</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>Japan fiscal/carry unwind—most proximate trigger for cross-asset volatility given leverage embedded in global portfolios.</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-07-03  -  generated 2026-07-03 21:41 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-07-03  -  generated 2026-07-03 22:14 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H316"/>
+  <dimension ref="A1:H337"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -17858,6 +17858,888 @@
         </is>
       </c>
     </row>
+    <row r="317">
+      <c r="A317" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B317" s="9" t="inlineStr">
+        <is>
+          <t>s1_basis_trade</t>
+        </is>
+      </c>
+      <c r="C317" s="9" t="inlineStr">
+        <is>
+          <t>Treasury basis trade (hidden leverage)</t>
+        </is>
+      </c>
+      <c r="D317" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E317" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F317" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G317" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H317" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B318" s="9" t="inlineStr">
+        <is>
+          <t>s2_japan</t>
+        </is>
+      </c>
+      <c r="C318" s="9" t="inlineStr">
+        <is>
+          <t>Japan fiscal / JGB / carry trade</t>
+        </is>
+      </c>
+      <c r="D318" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E318" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F318" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G318" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H318" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B319" s="9" t="inlineStr">
+        <is>
+          <t>s3_private_credit</t>
+        </is>
+      </c>
+      <c r="C319" s="9" t="inlineStr">
+        <is>
+          <t>Private credit's opaque expansion</t>
+        </is>
+      </c>
+      <c r="D319" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E319" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F319" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G319" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="H319" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B320" s="9" t="inlineStr">
+        <is>
+          <t>s4_dev_debt</t>
+        </is>
+      </c>
+      <c r="C320" s="9" t="inlineStr">
+        <is>
+          <t>Developing-world debt crisis</t>
+        </is>
+      </c>
+      <c r="D320" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E320" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F320" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G320" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H320" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B321" s="9" t="inlineStr">
+        <is>
+          <t>s5_china_deflation</t>
+        </is>
+      </c>
+      <c r="C321" s="9" t="inlineStr">
+        <is>
+          <t>China's price spillover (deflation or cost-push)</t>
+        </is>
+      </c>
+      <c r="D321" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E321" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F321" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G321" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H321" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B322" s="9" t="inlineStr">
+        <is>
+          <t>s6_rare_earths</t>
+        </is>
+      </c>
+      <c r="C322" s="9" t="inlineStr">
+        <is>
+          <t>Critical minerals as a weapon</t>
+        </is>
+      </c>
+      <c r="D322" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E322" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F322" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G322" s="9" t="inlineStr">
+        <is>
+          <t>6.75</t>
+        </is>
+      </c>
+      <c r="H322" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B323" s="9" t="inlineStr">
+        <is>
+          <t>s7_stablecoins</t>
+        </is>
+      </c>
+      <c r="C323" s="9" t="inlineStr">
+        <is>
+          <t>Stablecoins &amp; Treasury demand</t>
+        </is>
+      </c>
+      <c r="D323" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E323" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F323" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G323" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H323" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B324" s="9" t="inlineStr">
+        <is>
+          <t>s8_ai_capex</t>
+        </is>
+      </c>
+      <c r="C324" s="9" t="inlineStr">
+        <is>
+          <t>AI build-out circular financing</t>
+        </is>
+      </c>
+      <c r="D324" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E324" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F324" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G324" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H324" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B325" s="9" t="inlineStr">
+        <is>
+          <t>s9_cre</t>
+        </is>
+      </c>
+      <c r="C325" s="9" t="inlineStr">
+        <is>
+          <t>CRE maturity wall / regional banks</t>
+        </is>
+      </c>
+      <c r="D325" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E325" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F325" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G325" s="9" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="H325" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B326" s="9" t="inlineStr">
+        <is>
+          <t>s10_france</t>
+        </is>
+      </c>
+      <c r="C326" s="9" t="inlineStr">
+        <is>
+          <t>France / eurozone fragility</t>
+        </is>
+      </c>
+      <c r="D326" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E326" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F326" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G326" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H326" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B327" s="9" t="inlineStr">
+        <is>
+          <t>s11_consumer_debt</t>
+        </is>
+      </c>
+      <c r="C327" s="9" t="inlineStr">
+        <is>
+          <t>Hidden consumer debt</t>
+        </is>
+      </c>
+      <c r="D327" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E327" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F327" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G327" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H327" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B328" s="9" t="inlineStr">
+        <is>
+          <t>s12_gold_dedollar</t>
+        </is>
+      </c>
+      <c r="C328" s="9" t="inlineStr">
+        <is>
+          <t>Gold / de-dollarization</t>
+        </is>
+      </c>
+      <c r="D328" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E328" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F328" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G328" s="9" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="H328" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B329" s="9" t="inlineStr">
+        <is>
+          <t>s13_insurance</t>
+        </is>
+      </c>
+      <c r="C329" s="9" t="inlineStr">
+        <is>
+          <t>Insurance retreat</t>
+        </is>
+      </c>
+      <c r="D329" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E329" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F329" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G329" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H329" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B330" s="9" t="inlineStr">
+        <is>
+          <t>s14_pensions</t>
+        </is>
+      </c>
+      <c r="C330" s="9" t="inlineStr">
+        <is>
+          <t>Pensions / demographics</t>
+        </is>
+      </c>
+      <c r="D330" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E330" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F330" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G330" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H330" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B331" s="9" t="inlineStr">
+        <is>
+          <t>s15_ai_power</t>
+        </is>
+      </c>
+      <c r="C331" s="9" t="inlineStr">
+        <is>
+          <t>AI power &amp; the grid bottleneck</t>
+        </is>
+      </c>
+      <c r="D331" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E331" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F331" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G331" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H331" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B332" s="9" t="inlineStr">
+        <is>
+          <t>s16_copper</t>
+        </is>
+      </c>
+      <c r="C332" s="9" t="inlineStr">
+        <is>
+          <t>Copper &amp; the electrification deficit</t>
+        </is>
+      </c>
+      <c r="D332" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E332" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F332" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G332" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H332" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B333" s="9" t="inlineStr">
+        <is>
+          <t>s17_water</t>
+        </is>
+      </c>
+      <c r="C333" s="9" t="inlineStr">
+        <is>
+          <t>Water - the underpriced input</t>
+        </is>
+      </c>
+      <c r="D333" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E333" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F333" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G333" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H333" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B334" s="9" t="inlineStr">
+        <is>
+          <t>s18_food_fertilizer</t>
+        </is>
+      </c>
+      <c r="C334" s="9" t="inlineStr">
+        <is>
+          <t>Food &amp; fertilizer fragility</t>
+        </is>
+      </c>
+      <c r="D334" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E334" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F334" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G334" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H334" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B335" s="9" t="inlineStr">
+        <is>
+          <t>s19_lithography</t>
+        </is>
+      </c>
+      <c r="C335" s="9" t="inlineStr">
+        <is>
+          <t>The lithography (ASML) chokepoint</t>
+        </is>
+      </c>
+      <c r="D335" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E335" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F335" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G335" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H335" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B336" s="9" t="inlineStr">
+        <is>
+          <t>s20_sea_lanes</t>
+        </is>
+      </c>
+      <c r="C336" s="9" t="inlineStr">
+        <is>
+          <t>Sea lanes &amp; undersea cables</t>
+        </is>
+      </c>
+      <c r="D336" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E336" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F336" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G336" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="H336" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B337" s="9" t="inlineStr">
+        <is>
+          <t>s21_clearinghouses</t>
+        </is>
+      </c>
+      <c r="C337" s="9" t="inlineStr">
+        <is>
+          <t>Clearinghouses (financial chokepoint)</t>
+        </is>
+      </c>
+      <c r="D337" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E337" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F337" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G337" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H337" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -17869,7 +18751,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A27"/>
+  <dimension ref="A1:A24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -17957,31 +18839,27 @@
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>**HEADLINE**</t>
+          <t># EOD Macro-Risk Brief | 2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>Macro risk remains elevated at 6.2, with three High-rated threats—Japan carry-trade unwinding, critical minerals weaponization, and AI power constraints—posing systemic spillover potential.</t>
-        </is>
-      </c>
+      <c r="A15" s="12" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr"/>
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>**Overall macro risk stands at 6.2 (High), with no intraday level changes but persistent elevation across structural vulnerabilities.**</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>**STORIES WITH LEVEL CHANGES**</t>
-        </is>
-      </c>
+      <c r="A17" s="12" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>No stories changed risk level today.</t>
+          <t>No stories moved today. Fifteen risks remain at Elevated or High bands:</t>
         </is>
       </c>
     </row>
@@ -17991,52 +18869,27 @@
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>**ELEVATED OR HIGHER RISKS (15 active)**</t>
+          <t>• **High-band risks** (3 stories): Japan fiscal/JGB/carry trade (7), Critical minerals weaponization (7), and AI power grid bottleneck (7) anchor the top tier.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>- **Japan fiscal/JGB/carry trade (Level 7, High):** Structural imbalance in JGB yields and yen carry positioning creates acute unwinding risk; could trigger forced deleveraging across global markets.</t>
-        </is>
-      </c>
+      <c r="A21" s="12" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>- **Critical minerals as weapon (Level 7, High):** Geopolitical control of rare earths and battery metals threatens supply chains; direct exposure to industrial and energy transition timelines.</t>
+          <t>• **Elevated-band risks** (12 stories) span financial leverage (Treasury basis trades, private credit opacity, hidden consumer debt), macro imbalances (China deflation/cost-push spillover, developing-world debt, eurozone fragility), and supply-chain chokepoints (ASML lithography, sea lanes/undersea cables, food/fertilizer, water constraints, AI financing circularity).</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>- **AI power &amp; grid bottleneck (Level 7, High):** Data center demand outpacing grid capacity; infrastructure lag risks compute-driven financing models and stranded capex.</t>
-        </is>
-      </c>
+      <c r="A23" s="12" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>- **Treasury basis / Private credit / Hidden consumer debt / Food fragility / Lithography chokepoint / Sea lanes (Levels 5–6, Elevated):** Secondary leverage, opacity, and supply concentration amplify contagion vectors.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="12" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="12" t="inlineStr">
-        <is>
-          <t>**WATCH**</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>Japan fiscal/carry unwind—most proximate trigger for cross-asset volatility given leverage embedded in global portfolios.</t>
+          <t>**Watch closest:** Japan's carry-trade unwind and structural fiscal stress (level 7)—reversal dynamics could trigger rapid deleveraging across correlated markets.</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-07-03  -  generated 2026-07-03 22:14 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-07-04  -  generated 2026-07-04 10:52 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>310.5</v>
+        <v>310.6</v>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="D62" s="7" t="n">
-        <v>15.81</v>
+        <v>16.15</v>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H337"/>
+  <dimension ref="A1:H358"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -18735,6 +18735,888 @@
         </is>
       </c>
       <c r="H337" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B338" s="9" t="inlineStr">
+        <is>
+          <t>s1_basis_trade</t>
+        </is>
+      </c>
+      <c r="C338" s="9" t="inlineStr">
+        <is>
+          <t>Treasury basis trade (hidden leverage)</t>
+        </is>
+      </c>
+      <c r="D338" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E338" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F338" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G338" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H338" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B339" s="9" t="inlineStr">
+        <is>
+          <t>s2_japan</t>
+        </is>
+      </c>
+      <c r="C339" s="9" t="inlineStr">
+        <is>
+          <t>Japan fiscal / JGB / carry trade</t>
+        </is>
+      </c>
+      <c r="D339" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E339" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F339" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G339" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H339" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B340" s="9" t="inlineStr">
+        <is>
+          <t>s3_private_credit</t>
+        </is>
+      </c>
+      <c r="C340" s="9" t="inlineStr">
+        <is>
+          <t>Private credit's opaque expansion</t>
+        </is>
+      </c>
+      <c r="D340" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E340" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F340" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G340" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="H340" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B341" s="9" t="inlineStr">
+        <is>
+          <t>s4_dev_debt</t>
+        </is>
+      </c>
+      <c r="C341" s="9" t="inlineStr">
+        <is>
+          <t>Developing-world debt crisis</t>
+        </is>
+      </c>
+      <c r="D341" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E341" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F341" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G341" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H341" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B342" s="9" t="inlineStr">
+        <is>
+          <t>s5_china_deflation</t>
+        </is>
+      </c>
+      <c r="C342" s="9" t="inlineStr">
+        <is>
+          <t>China's price spillover (deflation or cost-push)</t>
+        </is>
+      </c>
+      <c r="D342" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E342" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F342" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G342" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H342" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B343" s="9" t="inlineStr">
+        <is>
+          <t>s6_rare_earths</t>
+        </is>
+      </c>
+      <c r="C343" s="9" t="inlineStr">
+        <is>
+          <t>Critical minerals as a weapon</t>
+        </is>
+      </c>
+      <c r="D343" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E343" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F343" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G343" s="9" t="inlineStr">
+        <is>
+          <t>6.75</t>
+        </is>
+      </c>
+      <c r="H343" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B344" s="9" t="inlineStr">
+        <is>
+          <t>s7_stablecoins</t>
+        </is>
+      </c>
+      <c r="C344" s="9" t="inlineStr">
+        <is>
+          <t>Stablecoins &amp; Treasury demand</t>
+        </is>
+      </c>
+      <c r="D344" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E344" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F344" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G344" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H344" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B345" s="9" t="inlineStr">
+        <is>
+          <t>s8_ai_capex</t>
+        </is>
+      </c>
+      <c r="C345" s="9" t="inlineStr">
+        <is>
+          <t>AI build-out circular financing</t>
+        </is>
+      </c>
+      <c r="D345" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E345" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F345" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G345" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H345" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B346" s="9" t="inlineStr">
+        <is>
+          <t>s9_cre</t>
+        </is>
+      </c>
+      <c r="C346" s="9" t="inlineStr">
+        <is>
+          <t>CRE maturity wall / regional banks</t>
+        </is>
+      </c>
+      <c r="D346" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E346" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F346" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G346" s="9" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="H346" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B347" s="9" t="inlineStr">
+        <is>
+          <t>s10_france</t>
+        </is>
+      </c>
+      <c r="C347" s="9" t="inlineStr">
+        <is>
+          <t>France / eurozone fragility</t>
+        </is>
+      </c>
+      <c r="D347" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E347" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F347" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G347" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H347" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B348" s="9" t="inlineStr">
+        <is>
+          <t>s11_consumer_debt</t>
+        </is>
+      </c>
+      <c r="C348" s="9" t="inlineStr">
+        <is>
+          <t>Hidden consumer debt</t>
+        </is>
+      </c>
+      <c r="D348" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E348" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F348" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G348" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H348" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B349" s="9" t="inlineStr">
+        <is>
+          <t>s12_gold_dedollar</t>
+        </is>
+      </c>
+      <c r="C349" s="9" t="inlineStr">
+        <is>
+          <t>Gold / de-dollarization</t>
+        </is>
+      </c>
+      <c r="D349" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E349" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F349" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G349" s="9" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="H349" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B350" s="9" t="inlineStr">
+        <is>
+          <t>s13_insurance</t>
+        </is>
+      </c>
+      <c r="C350" s="9" t="inlineStr">
+        <is>
+          <t>Insurance retreat</t>
+        </is>
+      </c>
+      <c r="D350" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E350" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F350" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G350" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H350" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B351" s="9" t="inlineStr">
+        <is>
+          <t>s14_pensions</t>
+        </is>
+      </c>
+      <c r="C351" s="9" t="inlineStr">
+        <is>
+          <t>Pensions / demographics</t>
+        </is>
+      </c>
+      <c r="D351" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E351" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F351" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G351" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H351" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B352" s="9" t="inlineStr">
+        <is>
+          <t>s15_ai_power</t>
+        </is>
+      </c>
+      <c r="C352" s="9" t="inlineStr">
+        <is>
+          <t>AI power &amp; the grid bottleneck</t>
+        </is>
+      </c>
+      <c r="D352" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E352" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F352" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G352" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H352" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B353" s="9" t="inlineStr">
+        <is>
+          <t>s16_copper</t>
+        </is>
+      </c>
+      <c r="C353" s="9" t="inlineStr">
+        <is>
+          <t>Copper &amp; the electrification deficit</t>
+        </is>
+      </c>
+      <c r="D353" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E353" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F353" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G353" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H353" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B354" s="9" t="inlineStr">
+        <is>
+          <t>s17_water</t>
+        </is>
+      </c>
+      <c r="C354" s="9" t="inlineStr">
+        <is>
+          <t>Water - the underpriced input</t>
+        </is>
+      </c>
+      <c r="D354" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E354" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F354" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G354" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H354" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B355" s="9" t="inlineStr">
+        <is>
+          <t>s18_food_fertilizer</t>
+        </is>
+      </c>
+      <c r="C355" s="9" t="inlineStr">
+        <is>
+          <t>Food &amp; fertilizer fragility</t>
+        </is>
+      </c>
+      <c r="D355" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E355" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F355" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G355" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H355" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B356" s="9" t="inlineStr">
+        <is>
+          <t>s19_lithography</t>
+        </is>
+      </c>
+      <c r="C356" s="9" t="inlineStr">
+        <is>
+          <t>The lithography (ASML) chokepoint</t>
+        </is>
+      </c>
+      <c r="D356" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E356" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F356" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G356" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H356" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B357" s="9" t="inlineStr">
+        <is>
+          <t>s20_sea_lanes</t>
+        </is>
+      </c>
+      <c r="C357" s="9" t="inlineStr">
+        <is>
+          <t>Sea lanes &amp; undersea cables</t>
+        </is>
+      </c>
+      <c r="D357" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E357" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F357" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G357" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="H357" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B358" s="9" t="inlineStr">
+        <is>
+          <t>s21_clearinghouses</t>
+        </is>
+      </c>
+      <c r="C358" s="9" t="inlineStr">
+        <is>
+          <t>Clearinghouses (financial chokepoint)</t>
+        </is>
+      </c>
+      <c r="D358" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E358" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F358" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G358" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H358" s="9" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
@@ -18832,34 +19714,38 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>--- Daily narrative (2026-07-03) ---</t>
+          <t>--- Daily narrative (2026-07-04) ---</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t># EOD Macro-Risk Brief | 2026-07-03</t>
+          <t>**HEADLINE**</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr"/>
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>Macro risk holds at elevated 6.2 with no intraday moves, but three structural vulnerabilities—Japan's carry trade, AI infrastructure bottlenecks, and critical minerals weaponization—remain at High (level 7).</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>**Overall macro risk stands at 6.2 (High), with no intraday level changes but persistent elevation across structural vulnerabilities.**</t>
-        </is>
-      </c>
+      <c r="A16" s="12" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr"/>
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>**STORIES WITH LEVEL CHANGES**</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>No stories moved today. Fifteen risks remain at Elevated or High bands:</t>
+          <t>No changes recorded today.</t>
         </is>
       </c>
     </row>
@@ -18869,27 +19755,31 @@
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>• **High-band risks** (3 stories): Japan fiscal/JGB/carry trade (7), Critical minerals weaponization (7), and AI power grid bottleneck (7) anchor the top tier.</t>
+          <t>**ELEVATED RISKS TO NOTE**</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr"/>
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>Fifteen risks remain in Elevated or High bands, spanning financial leverage (Treasury basis trades, private credit opacity), geopolitical supply chains (ASML lithography, critical minerals), and structural imbalances (Japan fiscal/JGB carry, China deflation spillover, developing-world debt, hidden consumer leverage, CRE maturity walls, and food/fertilizer fragility).</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t>• **Elevated-band risks** (12 stories) span financial leverage (Treasury basis trades, private credit opacity, hidden consumer debt), macro imbalances (China deflation/cost-push spillover, developing-world debt, eurozone fragility), and supply-chain chokepoints (ASML lithography, sea lanes/undersea cables, food/fertilizer, water constraints, AI financing circularity).</t>
-        </is>
-      </c>
+      <c r="A22" s="12" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="inlineStr"/>
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>**HIGHEST-RISK WATCH**</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>**Watch closest:** Japan's carry-trade unwind and structural fiscal stress (level 7)—reversal dynamics could trigger rapid deleveraging across correlated markets.</t>
+          <t>Japan fiscal/JGB/carry trade (level 7): unwind dynamics could trigger cross-asset volatility across currencies and equities given embedded leverage in yen positions.</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-07-04  -  generated 2026-07-04 10:52 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-07-04  -  generated 2026-07-04 10:58 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -19633,7 +19633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A24"/>
+  <dimension ref="A1:A29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -19728,7 +19728,7 @@
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>Macro risk holds at elevated 6.2 with no intraday moves, but three structural vulnerabilities—Japan's carry trade, AI infrastructure bottlenecks, and critical minerals weaponization—remain at High (level 7).</t>
+          <t>Macro risk holds at elevated 6.2, with three High-band threats anchoring systemic vulnerabilities in finance, supply chains, and infrastructure.</t>
         </is>
       </c>
     </row>
@@ -19745,7 +19745,7 @@
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>No changes recorded today.</t>
+          <t>No risk levels changed today; all positions held steady.</t>
         </is>
       </c>
     </row>
@@ -19755,31 +19755,66 @@
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>**ELEVATED RISKS TO NOTE**</t>
+          <t>**ELEVATED OR HIGHER RISKS (Static Portfolio)**</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>Fifteen risks remain in Elevated or High bands, spanning financial leverage (Treasury basis trades, private credit opacity), geopolitical supply chains (ASML lithography, critical minerals), and structural imbalances (Japan fiscal/JGB carry, China deflation spillover, developing-world debt, hidden consumer leverage, CRE maturity walls, and food/fertilizer fragility).</t>
+          <t>- **Japan fiscal/JGB/carry trade (7, High):** Persistent BoJ policy uncertainty and carry-unwind exposure threaten cross-border funding chains.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="inlineStr"/>
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>- **Critical minerals as a weapon (7, High):** Geopolitical weaponization of rare-earth supply continues to fragment industrial inputs.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>**HIGHEST-RISK WATCH**</t>
+          <t>- **AI power &amp; grid bottleneck (7, High):** Accelerating compute demand strains electricity infrastructure without corresponding grid investment.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>Japan fiscal/JGB/carry trade (level 7): unwind dynamics could trigger cross-asset volatility across currencies and equities given embedded leverage in yen positions.</t>
+          <t>- **Treasury basis trade (6, Elevated):** Hidden leverage in repo markets remains opaque; basis blowouts could trigger forced liquidations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>- **Private credit's opaque expansion (6, Elevated):** Rapid growth in unregulated credit channels limits risk visibility and fire-sale exposure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>- **Developing-world debt crisis (6, Elevated):** Refinancing pressures persist amid higher rates and tightening external conditions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>**WATCH CLOSEST**</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>Japan fiscal/JGB/carry trade: BoJ divergence from global rates remains the most acute tail-risk trigger for immediate cross-asset volatility.</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-07-04  -  generated 2026-07-04 10:58 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-07-04  -  generated 2026-07-04 11:37 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>310.6</v>
+        <v>309.9</v>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
@@ -19633,7 +19633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A29"/>
+  <dimension ref="A1:A27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -19728,7 +19728,7 @@
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>Macro risk holds at elevated 6.2, with three High-band threats anchoring systemic vulnerabilities in finance, supply chains, and infrastructure.</t>
+          <t>Macro risk holds steady at 6.2 overall with three High-level risks dominating: Japan's carry-trade vulnerability, critical minerals weaponization, and AI power-grid constraints.</t>
         </is>
       </c>
     </row>
@@ -19738,14 +19738,14 @@
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>**STORIES WITH LEVEL CHANGES**</t>
+          <t>**NO LEVEL CHANGES TODAY**</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>No risk levels changed today; all positions held steady.</t>
+          <t>The changes array is empty; all elevated and high risks remain at their current levels.</t>
         </is>
       </c>
     </row>
@@ -19755,66 +19755,52 @@
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>**ELEVATED OR HIGHER RISKS (Static Portfolio)**</t>
+          <t>**KEY STORIES AT ELEVATED+ RISK**</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>- **Japan fiscal/JGB/carry trade (7, High):** Persistent BoJ policy uncertainty and carry-unwind exposure threaten cross-border funding chains.</t>
+          <t>- **Japan fiscal/JGB/carry trade (Level 7, High)**: Persistent BoJ policy uncertainty and funding cost pressures sustain vulnerability to rapid deleveraging.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>- **Critical minerals as a weapon (7, High):** Geopolitical weaponization of rare-earth supply continues to fragment industrial inputs.</t>
+          <t>- **Critical minerals as weapon (Level 7, High)**: Ongoing supply-chain concentration risk; geopolitical control of rare earths and battery materials remains a structural pressure point.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>- **AI power &amp; grid bottleneck (7, High):** Accelerating compute demand strains electricity infrastructure without corresponding grid investment.</t>
+          <t>- **AI power &amp; grid bottleneck (Level 7, High)**: Semiconductor facility and data-center demand for electricity continues to outpace grid modernization timelines.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>- **Treasury basis trade (6, Elevated):** Hidden leverage in repo markets remains opaque; basis blowouts could trigger forced liquidations.</t>
+          <t>- **Treasury basis trade hidden leverage (Level 6, Elevated)**: Structural leverage in repo-based arbitrage trades remains opaque to regulators.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>- **Private credit's opaque expansion (6, Elevated):** Rapid growth in unregulated credit channels limits risk visibility and fire-sale exposure.</t>
+          <t>- **Private credit's opaque expansion (Level 6, Elevated)**: Unregulated lending growth sustains procyclical risk in downturns.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="12" t="inlineStr">
-        <is>
-          <t>- **Developing-world debt crisis (6, Elevated):** Refinancing pressures persist amid higher rates and tightening external conditions.</t>
-        </is>
-      </c>
+      <c r="A26" s="12" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="12" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="12" t="inlineStr">
-        <is>
-          <t>**WATCH CLOSEST**</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="12" t="inlineStr">
-        <is>
-          <t>Japan fiscal/JGB/carry trade: BoJ divergence from global rates remains the most acute tail-risk trigger for immediate cross-asset volatility.</t>
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>**WATCH CLOSEST**: Japan fiscal/JGB/carry trade—reversal could trigger cascade across global fixed income and FX markets.</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-07-04  -  generated 2026-07-04 11:37 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-07-04  -  generated 2026-07-04 14:03 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -19728,7 +19728,7 @@
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>Macro risk holds steady at 6.2 overall with three High-level risks dominating: Japan's carry-trade vulnerability, critical minerals weaponization, and AI power-grid constraints.</t>
+          <t>Macro risk remains elevated at 6.2 overall, with no intraday level changes but persistent concentration in leverage, supply-chain chokepoints, and geopolitical weaponization.</t>
         </is>
       </c>
     </row>
@@ -19738,14 +19738,14 @@
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>**NO LEVEL CHANGES TODAY**</t>
+          <t>**STORIES WITH LEVEL CHANGES**</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>The changes array is empty; all elevated and high risks remain at their current levels.</t>
+          <t>None recorded today.</t>
         </is>
       </c>
     </row>
@@ -19755,52 +19755,52 @@
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>**KEY STORIES AT ELEVATED+ RISK**</t>
+          <t>**ELEVATED &amp; HIGH-RISK STORIES OUTSTANDING**</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>- **Japan fiscal/JGB/carry trade (Level 7, High)**: Persistent BoJ policy uncertainty and funding cost pressures sustain vulnerability to rapid deleveraging.</t>
+          <t>• **Japan fiscal/JGB/carry trade** (Level 7, High): Structural imbalance in Japanese debt and yen funding remain acute; unwind risk in leveraged positions.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>- **Critical minerals as weapon (Level 7, High)**: Ongoing supply-chain concentration risk; geopolitical control of rare earths and battery materials remains a structural pressure point.</t>
+          <t>• **Critical minerals as a weapon** (Level 7, High): Supply concentration continues to pose asymmetric vulnerability across energy and defense sectors.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>- **AI power &amp; grid bottleneck (Level 7, High)**: Semiconductor facility and data-center demand for electricity continues to outpace grid modernization timelines.</t>
+          <t>• **AI power &amp; grid bottleneck** (Level 7, High): Data-center demand outpacing infrastructure; cascading brownout or capex disappointment risk.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>- **Treasury basis trade hidden leverage (Level 6, Elevated)**: Structural leverage in repo-based arbitrage trades remains opaque to regulators.</t>
+          <t>• Six stories at Level 6 (Elevated): Treasury basis, private credit opacity, developing-world debt, China deflation spillover, AI circular financing, and lithography chokepoints all sustain material tail risks.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>- **Private credit's opaque expansion (Level 6, Elevated)**: Unregulated lending growth sustains procyclical risk in downturns.</t>
-        </is>
-      </c>
+      <c r="A25" s="12" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="12" t="inlineStr"/>
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>**WATCH CLOSEST**</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>**WATCH CLOSEST**: Japan fiscal/JGB/carry trade—reversal could trigger cascade across global fixed income and FX markets.</t>
+          <t>Japan fiscal/JGB/carry trade unwinding—widest spillover surface into equities and FX.</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-07-04  -  generated 2026-07-04 14:03 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-07-04  -  generated 2026-07-04 14:25 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -19633,7 +19633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A27"/>
+  <dimension ref="A1:A24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -19728,7 +19728,7 @@
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>Macro risk remains elevated at 6.2 overall, with no intraday level changes but persistent concentration in leverage, supply-chain chokepoints, and geopolitical weaponization.</t>
+          <t>Macro risk holds at elevated overall level (6.2) with three High-band stressors—Japan carry trade, critical minerals weaponization, and AI power infrastructure—posing systemic contagion risks.</t>
         </is>
       </c>
     </row>
@@ -19738,14 +19738,14 @@
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>**STORIES WITH LEVEL CHANGES**</t>
+          <t>**NO LEVEL CHANGES TODAY**</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>None recorded today.</t>
+          <t>The changes array is empty; no stories shifted risk bands on 4 July 2026.</t>
         </is>
       </c>
     </row>
@@ -19755,52 +19755,31 @@
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>**ELEVATED &amp; HIGH-RISK STORIES OUTSTANDING**</t>
+          <t>**ELEVATED-OR-HIGHER SUMMARY**</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>• **Japan fiscal/JGB/carry trade** (Level 7, High): Structural imbalance in Japanese debt and yen funding remain acute; unwind risk in leveraged positions.</t>
+          <t>Fifteen risks remain at Elevated (6) or High (7) levels. Three stand at High: Japan's fiscal/JGB/carry-trade nexus (7) threatens cross-border deleveraging; critical minerals leverage as geopolitical tool (7) risks supply shocks; AI power-grid bottleneck (7) could constrain infrastructure investment. Eight sit at Elevated (6)—including Treasury basis trades, private credit opacity, developing-world debt, China deflation spillover, AI circular financing, hidden consumer debt, food fragility, and lithography chokepoints—each creating secondary spillover risk. Five remain Elevated (5): CRE maturity wall, eurozone fragility, and water underpricing.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t>• **Critical minerals as a weapon** (Level 7, High): Supply concentration continues to pose asymmetric vulnerability across energy and defense sectors.</t>
-        </is>
-      </c>
+      <c r="A22" s="12" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>• **AI power &amp; grid bottleneck** (Level 7, High): Data-center demand outpacing infrastructure; cascading brownout or capex disappointment risk.</t>
+          <t>**WATCH**</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>• Six stories at Level 6 (Elevated): Treasury basis, private credit opacity, developing-world debt, China deflation spillover, AI circular financing, and lithography chokepoints all sustain material tail risks.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="12" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="12" t="inlineStr">
-        <is>
-          <t>**WATCH CLOSEST**</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>Japan fiscal/JGB/carry trade unwinding—widest spillover surface into equities and FX.</t>
+          <t>Japan's carry-trade unwind remains the highest-risk story given its potential to trigger rapid capital flows and margin calls across global markets.</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-07-04  -  generated 2026-07-04 14:25 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-07-05  -  generated 2026-07-05 10:17 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="D3" s="7" t="n">
-        <v>66.79000000000001</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
         </is>
       </c>
       <c r="D63" s="7" t="n">
-        <v>66.79000000000001</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H358"/>
+  <dimension ref="A1:H379"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -19622,6 +19622,888 @@
         </is>
       </c>
     </row>
+    <row r="359">
+      <c r="A359" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B359" s="9" t="inlineStr">
+        <is>
+          <t>s1_basis_trade</t>
+        </is>
+      </c>
+      <c r="C359" s="9" t="inlineStr">
+        <is>
+          <t>Treasury basis trade (hidden leverage)</t>
+        </is>
+      </c>
+      <c r="D359" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E359" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F359" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G359" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H359" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B360" s="9" t="inlineStr">
+        <is>
+          <t>s2_japan</t>
+        </is>
+      </c>
+      <c r="C360" s="9" t="inlineStr">
+        <is>
+          <t>Japan fiscal / JGB / carry trade</t>
+        </is>
+      </c>
+      <c r="D360" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E360" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F360" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G360" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H360" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B361" s="9" t="inlineStr">
+        <is>
+          <t>s3_private_credit</t>
+        </is>
+      </c>
+      <c r="C361" s="9" t="inlineStr">
+        <is>
+          <t>Private credit's opaque expansion</t>
+        </is>
+      </c>
+      <c r="D361" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E361" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F361" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G361" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="H361" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B362" s="9" t="inlineStr">
+        <is>
+          <t>s4_dev_debt</t>
+        </is>
+      </c>
+      <c r="C362" s="9" t="inlineStr">
+        <is>
+          <t>Developing-world debt crisis</t>
+        </is>
+      </c>
+      <c r="D362" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E362" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F362" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G362" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H362" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B363" s="9" t="inlineStr">
+        <is>
+          <t>s5_china_deflation</t>
+        </is>
+      </c>
+      <c r="C363" s="9" t="inlineStr">
+        <is>
+          <t>China's price spillover (deflation or cost-push)</t>
+        </is>
+      </c>
+      <c r="D363" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E363" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F363" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G363" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H363" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B364" s="9" t="inlineStr">
+        <is>
+          <t>s6_rare_earths</t>
+        </is>
+      </c>
+      <c r="C364" s="9" t="inlineStr">
+        <is>
+          <t>Critical minerals as a weapon</t>
+        </is>
+      </c>
+      <c r="D364" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E364" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F364" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G364" s="9" t="inlineStr">
+        <is>
+          <t>6.75</t>
+        </is>
+      </c>
+      <c r="H364" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B365" s="9" t="inlineStr">
+        <is>
+          <t>s7_stablecoins</t>
+        </is>
+      </c>
+      <c r="C365" s="9" t="inlineStr">
+        <is>
+          <t>Stablecoins &amp; Treasury demand</t>
+        </is>
+      </c>
+      <c r="D365" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E365" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F365" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G365" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H365" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B366" s="9" t="inlineStr">
+        <is>
+          <t>s8_ai_capex</t>
+        </is>
+      </c>
+      <c r="C366" s="9" t="inlineStr">
+        <is>
+          <t>AI build-out circular financing</t>
+        </is>
+      </c>
+      <c r="D366" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E366" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F366" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G366" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H366" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B367" s="9" t="inlineStr">
+        <is>
+          <t>s9_cre</t>
+        </is>
+      </c>
+      <c r="C367" s="9" t="inlineStr">
+        <is>
+          <t>CRE maturity wall / regional banks</t>
+        </is>
+      </c>
+      <c r="D367" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E367" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F367" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G367" s="9" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="H367" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B368" s="9" t="inlineStr">
+        <is>
+          <t>s10_france</t>
+        </is>
+      </c>
+      <c r="C368" s="9" t="inlineStr">
+        <is>
+          <t>France / eurozone fragility</t>
+        </is>
+      </c>
+      <c r="D368" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E368" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F368" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G368" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H368" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B369" s="9" t="inlineStr">
+        <is>
+          <t>s11_consumer_debt</t>
+        </is>
+      </c>
+      <c r="C369" s="9" t="inlineStr">
+        <is>
+          <t>Hidden consumer debt</t>
+        </is>
+      </c>
+      <c r="D369" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E369" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F369" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G369" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H369" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B370" s="9" t="inlineStr">
+        <is>
+          <t>s12_gold_dedollar</t>
+        </is>
+      </c>
+      <c r="C370" s="9" t="inlineStr">
+        <is>
+          <t>Gold / de-dollarization</t>
+        </is>
+      </c>
+      <c r="D370" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E370" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F370" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G370" s="9" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="H370" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B371" s="9" t="inlineStr">
+        <is>
+          <t>s13_insurance</t>
+        </is>
+      </c>
+      <c r="C371" s="9" t="inlineStr">
+        <is>
+          <t>Insurance retreat</t>
+        </is>
+      </c>
+      <c r="D371" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E371" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F371" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G371" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H371" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B372" s="9" t="inlineStr">
+        <is>
+          <t>s14_pensions</t>
+        </is>
+      </c>
+      <c r="C372" s="9" t="inlineStr">
+        <is>
+          <t>Pensions / demographics</t>
+        </is>
+      </c>
+      <c r="D372" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E372" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F372" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G372" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H372" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B373" s="9" t="inlineStr">
+        <is>
+          <t>s15_ai_power</t>
+        </is>
+      </c>
+      <c r="C373" s="9" t="inlineStr">
+        <is>
+          <t>AI power &amp; the grid bottleneck</t>
+        </is>
+      </c>
+      <c r="D373" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E373" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F373" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G373" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H373" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B374" s="9" t="inlineStr">
+        <is>
+          <t>s16_copper</t>
+        </is>
+      </c>
+      <c r="C374" s="9" t="inlineStr">
+        <is>
+          <t>Copper &amp; the electrification deficit</t>
+        </is>
+      </c>
+      <c r="D374" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E374" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F374" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G374" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H374" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B375" s="9" t="inlineStr">
+        <is>
+          <t>s17_water</t>
+        </is>
+      </c>
+      <c r="C375" s="9" t="inlineStr">
+        <is>
+          <t>Water - the underpriced input</t>
+        </is>
+      </c>
+      <c r="D375" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E375" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F375" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G375" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H375" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B376" s="9" t="inlineStr">
+        <is>
+          <t>s18_food_fertilizer</t>
+        </is>
+      </c>
+      <c r="C376" s="9" t="inlineStr">
+        <is>
+          <t>Food &amp; fertilizer fragility</t>
+        </is>
+      </c>
+      <c r="D376" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E376" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F376" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G376" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H376" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B377" s="9" t="inlineStr">
+        <is>
+          <t>s19_lithography</t>
+        </is>
+      </c>
+      <c r="C377" s="9" t="inlineStr">
+        <is>
+          <t>The lithography (ASML) chokepoint</t>
+        </is>
+      </c>
+      <c r="D377" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E377" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F377" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G377" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H377" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B378" s="9" t="inlineStr">
+        <is>
+          <t>s20_sea_lanes</t>
+        </is>
+      </c>
+      <c r="C378" s="9" t="inlineStr">
+        <is>
+          <t>Sea lanes &amp; undersea cables</t>
+        </is>
+      </c>
+      <c r="D378" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E378" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F378" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G378" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="H378" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B379" s="9" t="inlineStr">
+        <is>
+          <t>s21_clearinghouses</t>
+        </is>
+      </c>
+      <c r="C379" s="9" t="inlineStr">
+        <is>
+          <t>Clearinghouses (financial chokepoint)</t>
+        </is>
+      </c>
+      <c r="D379" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E379" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F379" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G379" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H379" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -19633,7 +20515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A24"/>
+  <dimension ref="A1:A27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -19714,7 +20596,7 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>--- Daily narrative (2026-07-04) ---</t>
+          <t>--- Daily narrative (2026-07-05) ---</t>
         </is>
       </c>
     </row>
@@ -19728,7 +20610,7 @@
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>Macro risk holds at elevated overall level (6.2) with three High-band stressors—Japan carry trade, critical minerals weaponization, and AI power infrastructure—posing systemic contagion risks.</t>
+          <t>Overall macro risk stands at 6.2/10 with no intraday changes; three High-level risks (Japan carry trade, critical minerals weaponization, AI power grid bottleneck) remain the primary pressure points.</t>
         </is>
       </c>
     </row>
@@ -19738,14 +20620,14 @@
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>**NO LEVEL CHANGES TODAY**</t>
+          <t>**NO CHANGES REPORTED**</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>The changes array is empty; no stories shifted risk bands on 4 July 2026.</t>
+          <t>The changes array is empty; no risk levels shifted during the session.</t>
         </is>
       </c>
     </row>
@@ -19755,31 +20637,52 @@
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>**ELEVATED-OR-HIGHER SUMMARY**</t>
+          <t>**ELEVATED OR HIGHER RISKS**</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>Fifteen risks remain at Elevated (6) or High (7) levels. Three stand at High: Japan's fiscal/JGB/carry-trade nexus (7) threatens cross-border deleveraging; critical minerals leverage as geopolitical tool (7) risks supply shocks; AI power-grid bottleneck (7) could constrain infrastructure investment. Eight sit at Elevated (6)—including Treasury basis trades, private credit opacity, developing-world debt, China deflation spillover, AI circular financing, hidden consumer debt, food fragility, and lithography chokepoints—each creating secondary spillover risk. Five remain Elevated (5): CRE maturity wall, eurozone fragility, and water underpricing.</t>
+          <t>Fifteen risks remain at Elevated (5–6) or High (7) bands:</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="inlineStr"/>
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>- **High band (7):** Japan fiscal/JGB/carry trade; critical minerals as weapon; AI power &amp; grid bottleneck</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>**WATCH**</t>
+          <t>- **Elevated band (6):** Treasury basis trades, private credit opacity, developing-world debt, China deflation/cost-push spillover, AI circular financing, hidden consumer debt, food/fertilizer fragility, lithography chokepoint, sea lanes/undersea cables</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>Japan's carry-trade unwind remains the highest-risk story given its potential to trigger rapid capital flows and margin calls across global markets.</t>
+          <t>- **Elevated band (5):** CRE maturity wall, France/eurozone fragility, water underpricing</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>**WATCH**</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>Japan fiscal/JGB/carry trade (7/10, High) carries the sharpest tail risk to cross-border capital flows and FX volatility.</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-07-05  -  generated 2026-07-05 10:17 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-07-05  -  generated 2026-07-05 10:21 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>309.9</v>
+        <v>309.8</v>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
@@ -20515,7 +20515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A27"/>
+  <dimension ref="A1:A20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -20603,31 +20603,27 @@
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>**HEADLINE**</t>
+          <t># EOD Macro-Risk Brief | 2026-07-05</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>Overall macro risk stands at 6.2/10 with no intraday changes; three High-level risks (Japan carry trade, critical minerals weaponization, AI power grid bottleneck) remain the primary pressure points.</t>
-        </is>
-      </c>
+      <c r="A15" s="12" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr"/>
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>**Overall risk stable at 6.2; no intraday level changes, but three High-band risks remain acute.**</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>**NO CHANGES REPORTED**</t>
-        </is>
-      </c>
+      <c r="A17" s="12" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>The changes array is empty; no risk levels shifted during the session.</t>
+          <t>No stories moved today. Persistent elevated risks span financial leverage (Treasury basis trades, private credit opacity), geopolitical supply chains (critical minerals weaponization, ASML lithography chokepoint), and structural imbalances (Japan's fiscal-carry nexus, China deflation spillover, developing-world debt servicing, AI power demand vs. grid constraints).</t>
         </is>
       </c>
     </row>
@@ -20637,52 +20633,7 @@
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>**ELEVATED OR HIGHER RISKS**</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>Fifteen risks remain at Elevated (5–6) or High (7) bands:</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t>- **High band (7):** Japan fiscal/JGB/carry trade; critical minerals as weapon; AI power &amp; grid bottleneck</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>- **Elevated band (6):** Treasury basis trades, private credit opacity, developing-world debt, China deflation/cost-push spillover, AI circular financing, hidden consumer debt, food/fertilizer fragility, lithography chokepoint, sea lanes/undersea cables</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="12" t="inlineStr">
-        <is>
-          <t>- **Elevated band (5):** CRE maturity wall, France/eurozone fragility, water underpricing</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="12" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="12" t="inlineStr">
-        <is>
-          <t>**WATCH**</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>Japan fiscal/JGB/carry trade (7/10, High) carries the sharpest tail risk to cross-border capital flows and FX volatility.</t>
+          <t>**Watch closest:** Japan fiscal / JGB / carry trade (Level 7, High)—unwind tail risk remains the highest-consequence trigger for cross-asset volatility and margin calls across global leveraged positions.</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-07-05  -  generated 2026-07-05 10:21 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-07-05  -  generated 2026-07-05 16:42 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>309.8</v>
+        <v>309.9</v>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
@@ -20515,7 +20515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A20"/>
+  <dimension ref="A1:A27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -20603,27 +20603,31 @@
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t># EOD Macro-Risk Brief | 2026-07-05</t>
+          <t>**HEADLINE**</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr"/>
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>Macro risk holds at 6.2 overall, with three High-level stresses in Japan carry trades, critical minerals weaponization, and AI power demands creating overlapping tail-risk channels.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>**Overall risk stable at 6.2; no intraday level changes, but three High-band risks remain acute.**</t>
-        </is>
-      </c>
+      <c r="A16" s="12" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr"/>
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>**NO LEVEL CHANGES RECORDED**</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>No stories moved today. Persistent elevated risks span financial leverage (Treasury basis trades, private credit opacity), geopolitical supply chains (critical minerals weaponization, ASML lithography chokepoint), and structural imbalances (Japan's fiscal-carry nexus, China deflation spillover, developing-world debt servicing, AI power demand vs. grid constraints).</t>
+          <t>The changes array is empty; no stories moved between risk bands today.</t>
         </is>
       </c>
     </row>
@@ -20633,7 +20637,52 @@
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>**Watch closest:** Japan fiscal / JGB / carry trade (Level 7, High)—unwind tail risk remains the highest-consequence trigger for cross-asset volatility and margin calls across global leveraged positions.</t>
+          <t>**ELEVATED OR HIGHER RISKS (STANDING POSITIONS)**</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>• **Japan fiscal/JGB/carry trade (High, 7):** Persistent yen-carry unwind risk; potential for rapid deleveraging across global equities and credit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>• **Critical minerals as weapon (High, 7):** Supply concentration remains weaponizable; disruption would cascade through EV and defense supply chains.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>• **AI power &amp; grid bottleneck (High, 7):** Structural electricity shortage for AI compute expansion; capex constraints and grid stress widening.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>• Eight Elevated (6) risks span Treasury basis leverage, private credit opacity, EM debt, China deflation, AI financing circularity, consumer debt, and supply chokepoints (lithography, food, sea lanes).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>**WATCH PRIORITY**</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>Japan carry-trade unwind remains the highest-risk trigger for rapid cross-asset repricing given leverage embedded across global equities and credit markets.</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-07-05  -  generated 2026-07-05 16:42 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-07-05  -  generated 2026-07-05 19:03 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>6.7702</v>
+        <v>6.7792</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>309.9</v>
+        <v>310</v>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
@@ -20515,7 +20515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A27"/>
+  <dimension ref="A1:A26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -20603,31 +20603,27 @@
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>**HEADLINE**</t>
+          <t># EOD Macro-Risk Brief | 2026-07-05</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>Macro risk holds at 6.2 overall, with three High-level stresses in Japan carry trades, critical minerals weaponization, and AI power demands creating overlapping tail-risk channels.</t>
-        </is>
-      </c>
+      <c r="A15" s="12" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr"/>
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>**Overall system risk at 6.2 (High): structural vulnerabilities span finance, supply chains, and geopolitics with no material changes today.**</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>**NO LEVEL CHANGES RECORDED**</t>
-        </is>
-      </c>
+      <c r="A17" s="12" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>The changes array is empty; no stories moved between risk bands today.</t>
+          <t>No risk levels shifted today. Fifteen risks remain elevated or higher across three zones:</t>
         </is>
       </c>
     </row>
@@ -20637,35 +20633,27 @@
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>**ELEVATED OR HIGHER RISKS (STANDING POSITIONS)**</t>
+          <t>• **Financial leverage**: Treasury basis trades, private credit opacity, and hidden consumer debt create counterparty and valuation exposure.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>• **Japan fiscal/JGB/carry trade (High, 7):** Persistent yen-carry unwind risk; potential for rapid deleveraging across global equities and credit.</t>
-        </is>
-      </c>
+      <c r="A21" s="12" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>• **Critical minerals as weapon (High, 7):** Supply concentration remains weaponizable; disruption would cascade through EV and defense supply chains.</t>
+          <t>• **Geopolitical/supply**: Critical minerals weaponization, ASML lithography concentration, and sea-lane/undersea-cable vulnerability threaten tech and energy security.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>• **AI power &amp; grid bottleneck (High, 7):** Structural electricity shortage for AI compute expansion; capex constraints and grid stress widening.</t>
-        </is>
-      </c>
+      <c r="A23" s="12" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>• Eight Elevated (6) risks span Treasury basis leverage, private credit opacity, EM debt, China deflation, AI financing circularity, consumer debt, and supply chokepoints (lithography, food, sea lanes).</t>
+          <t>• **Macro imbalances**: Japan's carry-trade and fiscal stress (Level 7), China's deflationary spillover, developing-world debt servicing, CRE maturity walls, and eurozone fragility amplify recession risk.</t>
         </is>
       </c>
     </row>
@@ -20675,14 +20663,7 @@
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>**WATCH PRIORITY**</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>Japan carry-trade unwind remains the highest-risk trigger for rapid cross-asset repricing given leverage embedded across global equities and credit markets.</t>
+          <t>**Watch: Japan fiscal/JGB/carry trade (Level 7)—unwind dynamics could cascade across FX and credit markets.**</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-07-05  -  generated 2026-07-05 19:03 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-07-05  -  generated 2026-07-05 20:12 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>161.337</v>
+        <v>161.329</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
@@ -20515,7 +20515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A26"/>
+  <dimension ref="A1:A31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -20603,27 +20603,31 @@
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t># EOD Macro-Risk Brief | 2026-07-05</t>
+          <t>**HEADLINE**</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr"/>
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>Overall macro risk stands at 6.2 (High), with no intraday changes but three stories at elevated 7-level intensity.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>**Overall system risk at 6.2 (High): structural vulnerabilities span finance, supply chains, and geopolitics with no material changes today.**</t>
-        </is>
-      </c>
+      <c r="A16" s="12" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr"/>
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>**KEY STORIES AT ELEVATED OR HIGHER**</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>No risk levels shifted today. Fifteen risks remain elevated or higher across three zones:</t>
+          <t>No level changes recorded today. Persistent elevated risks include:</t>
         </is>
       </c>
     </row>
@@ -20633,7 +20637,7 @@
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>• **Financial leverage**: Treasury basis trades, private credit opacity, and hidden consumer debt create counterparty and valuation exposure.</t>
+          <t>• **Japan fiscal/JGB/carry trade (Level 7)** – Structural imbalance in JGB yields and yen carry positioning creates tail risk for rapid deleveraging.</t>
         </is>
       </c>
     </row>
@@ -20643,7 +20647,7 @@
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>• **Geopolitical/supply**: Critical minerals weaponization, ASML lithography concentration, and sea-lane/undersea-cable vulnerability threaten tech and energy security.</t>
+          <t>• **Critical minerals as a weapon (Level 7)** – Geopolitical control of supply chains remains a structural fault line affecting industrial production.</t>
         </is>
       </c>
     </row>
@@ -20653,7 +20657,7 @@
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>• **Macro imbalances**: Japan's carry-trade and fiscal stress (Level 7), China's deflationary spillover, developing-world debt servicing, CRE maturity walls, and eurozone fragility amplify recession risk.</t>
+          <t>• **AI power &amp; grid bottleneck (Level 7)** – Demand-supply mismatch in electricity infrastructure poses capex and reliability constraints.</t>
         </is>
       </c>
     </row>
@@ -20663,7 +20667,34 @@
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>**Watch: Japan fiscal/JGB/carry trade (Level 7)—unwind dynamics could cascade across FX and credit markets.**</t>
+          <t>• **Treasury basis trade (Level 6)** – Hidden leverage in repo-like structures creates opacity in financial plumbing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>• **Private credit expansion (Level 6)** – Continued opacity in valuation and liquidity terms elevates cliff risk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>**TO WATCH**</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>Japan's carry trade and fiscal deterioration (Level 7) presents the highest contagion risk given global positioning.</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-07-05  -  generated 2026-07-05 20:12 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-07-05  -  generated 2026-07-05 20:15 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -20515,7 +20515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A31"/>
+  <dimension ref="A1:A25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -20603,14 +20603,14 @@
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>**HEADLINE**</t>
+          <t>**HEADLINE:**</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>Overall macro risk stands at 6.2 (High), with no intraday changes but three stories at elevated 7-level intensity.</t>
+          <t>Macro risk closed at 6.2/10 with no intraday moves; structural vulnerabilities in Japan carry trades, AI infrastructure, and critical minerals remain the dominant concerns.</t>
         </is>
       </c>
     </row>
@@ -20620,34 +20620,38 @@
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>**KEY STORIES AT ELEVATED OR HIGHER**</t>
+          <t>**NO LEVEL CHANGES RECORDED TODAY** — the changes array is empty; all elevated or high-risk stories held steady.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
-          <t>No level changes recorded today. Persistent elevated risks include:</t>
-        </is>
-      </c>
+      <c r="A18" s="12" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr"/>
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>**HIGHEST-RISK STORIES (Level 7):**</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>• **Japan fiscal/JGB/carry trade (Level 7)** – Structural imbalance in JGB yields and yen carry positioning creates tail risk for rapid deleveraging.</t>
+          <t>- Japan fiscal/JGB/carry trade unwind remains the single largest tail risk for cross-asset volatility.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr"/>
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>- AI power demand and grid capacity constraints pose near-term infrastructure stress.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>• **Critical minerals as a weapon (Level 7)** – Geopolitical control of supply chains remains a structural fault line affecting industrial production.</t>
+          <t>- Critical minerals weaponization creates geopolitical leverage points for supply disruption.</t>
         </is>
       </c>
     </row>
@@ -20657,44 +20661,14 @@
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>• **AI power &amp; grid bottleneck (Level 7)** – Demand-supply mismatch in electricity infrastructure poses capex and reliability constraints.</t>
+          <t>**WATCH LINE:**</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="12" t="inlineStr">
-        <is>
-          <t>• **Treasury basis trade (Level 6)** – Hidden leverage in repo-like structures creates opacity in financial plumbing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="12" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="12" t="inlineStr">
-        <is>
-          <t>• **Private credit expansion (Level 6)** – Continued opacity in valuation and liquidity terms elevates cliff risk.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="12" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="12" t="inlineStr">
-        <is>
-          <t>**TO WATCH**</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="12" t="inlineStr">
-        <is>
-          <t>Japan's carry trade and fiscal deterioration (Level 7) presents the highest contagion risk given global positioning.</t>
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>Japan's carry-trade structure is the critical pressure point; any BoJ policy signal or yen move could trigger rapid deleveraging across correlated markets.</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-07-05  -  generated 2026-07-05 20:15 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-07-05  -  generated 2026-07-05 20:17 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -20515,7 +20515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A25"/>
+  <dimension ref="A1:A27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -20603,14 +20603,14 @@
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>**HEADLINE:**</t>
+          <t>**HEADLINE**</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>Macro risk closed at 6.2/10 with no intraday moves; structural vulnerabilities in Japan carry trades, AI infrastructure, and critical minerals remain the dominant concerns.</t>
+          <t>Macro risk holds at elevated levels (6.2) with no intraday moves; Japan carry trade and AI infrastructure constraints remain highest-severity exposures.</t>
         </is>
       </c>
     </row>
@@ -20620,55 +20620,69 @@
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>**NO LEVEL CHANGES RECORDED TODAY** — the changes array is empty; all elevated or high-risk stories held steady.</t>
+          <t>**STORIES WITH LEVEL CHANGES**</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="inlineStr"/>
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>No risk levels changed today; the tracker reflects stable positioning across 15 elevated or higher risks.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>**HIGHEST-RISK STORIES (Level 7):**</t>
-        </is>
-      </c>
+      <c r="A19" s="12" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>- Japan fiscal/JGB/carry trade unwind remains the single largest tail risk for cross-asset volatility.</t>
+          <t>**KEY ELEVATED RISKS (unchanged)**</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>- AI power demand and grid capacity constraints pose near-term infrastructure stress.</t>
+          <t>• **Japan fiscal/JGB/carry trade** (Level 7, High): Persistent yen volatility and unwind risk in leveraged positions; potential for sharp cross-asset liquidations.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>- Critical minerals weaponization creates geopolitical leverage points for supply disruption.</t>
+          <t>• **AI power &amp; grid bottleneck** (Level 7, High): Data-center demand outpacing power infrastructure; capex delays or blackout risk in constrained regions.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="inlineStr"/>
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>• **Critical minerals as weapon** (Level 7, High): Supply concentration in geopolitically sensitive regions; exposure to tech and energy transition.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>**WATCH LINE:**</t>
+          <t>• Treasury basis trades (Level 6), private credit opacity (Level 6), and developing-world debt (Level 6) remain material secondary risks.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>Japan's carry-trade structure is the critical pressure point; any BoJ policy signal or yen move could trigger rapid deleveraging across correlated markets.</t>
+      <c r="A25" s="12" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>**TO WATCH**</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>Japan fiscal/JGB/carry trade (Level 7)—any BoJ policy signal or volatility spike could trigger rapid deleveraging across global markets.</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-07-05  -  generated 2026-07-05 20:17 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-07-05  -  generated 2026-07-05 20:21 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -20515,7 +20515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A27"/>
+  <dimension ref="A1:A22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -20603,86 +20603,51 @@
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>**HEADLINE**</t>
+          <t># EOD MACRO-RISK BRIEF | 2026-07-05</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>Macro risk holds at elevated levels (6.2) with no intraday moves; Japan carry trade and AI infrastructure constraints remain highest-severity exposures.</t>
-        </is>
-      </c>
+      <c r="A15" s="12" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr"/>
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>**Overall risk stable at 6.2; no level changes today but 15 stories remain elevated or higher.**</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>**STORIES WITH LEVEL CHANGES**</t>
-        </is>
-      </c>
+      <c r="A17" s="12" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>No risk levels changed today; the tracker reflects stable positioning across 15 elevated or higher risks.</t>
+          <t>No stories moved today. Risk landscape unchanged across all tracked domains:</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr"/>
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>- **Three High-level risks** persist: Japan fiscal/JGB/carry trade (7), Critical minerals weaponization (7), AI power grid bottleneck (7).</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>**KEY ELEVATED RISKS (unchanged)**</t>
+          <t>- **12 Elevated risks** span financial leverage (Treasury basis, private credit), emerging-market stress (developing-world debt, China deflation), supply chain concentration (ASML lithography, sea lanes), and structural imbalances (CRE, hidden consumer debt, food fragility).</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>• **Japan fiscal/JGB/carry trade** (Level 7, High): Persistent yen volatility and unwind risk in leveraged positions; potential for sharp cross-asset liquidations.</t>
-        </is>
-      </c>
+      <c r="A21" s="12" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>• **AI power &amp; grid bottleneck** (Level 7, High): Data-center demand outpacing power infrastructure; capex delays or blackout risk in constrained regions.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>• **Critical minerals as weapon** (Level 7, High): Supply concentration in geopolitically sensitive regions; exposure to tech and energy transition.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="12" t="inlineStr">
-        <is>
-          <t>• Treasury basis trades (Level 6), private credit opacity (Level 6), and developing-world debt (Level 6) remain material secondary risks.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="12" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="12" t="inlineStr">
-        <is>
-          <t>**TO WATCH**</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>Japan fiscal/JGB/carry trade (Level 7)—any BoJ policy signal or volatility spike could trigger rapid deleveraging across global markets.</t>
+          <t>**Watch closest:** Japan fiscal/JGB/carry trade (level 7)—largest unwind tail risk in leveraged FX markets given persistent policy divergence.</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-07-05  -  generated 2026-07-05 20:21 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-07-05  -  generated 2026-07-05 21:37 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>161.329</v>
+        <v>161.275</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>6.7792</v>
+        <v>6.7702</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -20515,7 +20515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A22"/>
+  <dimension ref="A1:A24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -20603,51 +20603,65 @@
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t># EOD MACRO-RISK BRIEF | 2026-07-05</t>
+          <t>**HEADLINE**</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr"/>
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>Overall macro risk remains elevated at 6.2, with three stories at High level—Japan carry trade, critical minerals weaponization, and AI power grid constraints—presenting the largest tail risks.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>**Overall risk stable at 6.2; no level changes today but 15 stories remain elevated or higher.**</t>
-        </is>
-      </c>
+      <c r="A16" s="12" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr"/>
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>**STORIES WITH LEVEL CHANGES**</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>No stories moved today. Risk landscape unchanged across all tracked domains:</t>
+          <t>No intraday level changes recorded.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>- **Three High-level risks** persist: Japan fiscal/JGB/carry trade (7), Critical minerals weaponization (7), AI power grid bottleneck (7).</t>
-        </is>
-      </c>
+      <c r="A19" s="12" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>- **12 Elevated risks** span financial leverage (Treasury basis, private credit), emerging-market stress (developing-world debt, China deflation), supply chain concentration (ASML lithography, sea lanes), and structural imbalances (CRE, hidden consumer debt, food fragility).</t>
+          <t>**ELEVATED OR HIGHER RISKS TO NOTE**</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr"/>
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>Treasury basis trades (hidden leverage), private credit opacity, developing-world debt stress, China's deflationary spillover, AI circular financing, hidden consumer debt, food/fertilizer fragility, ASML lithography concentration, and sea lane/subsea cable exposure all remain at Elevated (level 6). France/eurozone fragility and CRE maturity walls sit at level 5 (Elevated). Water as an underpriced input flagged at level 5.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t>**Watch closest:** Japan fiscal/JGB/carry trade (level 7)—largest unwind tail risk in leveraged FX markets given persistent policy divergence.</t>
+      <c r="A22" s="12" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>**TOP WATCH**</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>Japan fiscal/JGB/carry trade at level 7 (High) remains the most systemically consequential story given yen carry unwind potential and global funding shock risk.</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-07-05  -  generated 2026-07-05 21:37 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-07-06  -  generated 2026-07-06 15:04 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
         </is>
       </c>
       <c r="D2" s="7" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>161.275</v>
+        <v>162.371</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>3.937</v>
+        <v>3.94</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>2.73</v>
+        <v>6</v>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>6.7702</v>
+        <v>6.7842</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
         </is>
       </c>
       <c r="D27" s="7" t="n">
-        <v>11.2</v>
+        <v>11.57</v>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>4187.2998</v>
+        <v>4145.7002</v>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>6.224</v>
+        <v>6.1975</v>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="D52" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="D60" s="7" t="n">
-        <v>68.78</v>
+        <v>69.01000000000001</v>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="D62" s="7" t="n">
-        <v>16.15</v>
+        <v>16.08</v>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H379"/>
+  <dimension ref="A1:H400"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -20504,6 +20504,888 @@
         </is>
       </c>
     </row>
+    <row r="380">
+      <c r="A380" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B380" s="9" t="inlineStr">
+        <is>
+          <t>s1_basis_trade</t>
+        </is>
+      </c>
+      <c r="C380" s="9" t="inlineStr">
+        <is>
+          <t>Treasury basis trade (hidden leverage)</t>
+        </is>
+      </c>
+      <c r="D380" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E380" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F380" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G380" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H380" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B381" s="9" t="inlineStr">
+        <is>
+          <t>s2_japan</t>
+        </is>
+      </c>
+      <c r="C381" s="9" t="inlineStr">
+        <is>
+          <t>Japan fiscal / JGB / carry trade</t>
+        </is>
+      </c>
+      <c r="D381" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E381" s="9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F381" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G381" s="9" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="H381" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B382" s="9" t="inlineStr">
+        <is>
+          <t>s3_private_credit</t>
+        </is>
+      </c>
+      <c r="C382" s="9" t="inlineStr">
+        <is>
+          <t>Private credit's opaque expansion</t>
+        </is>
+      </c>
+      <c r="D382" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E382" s="9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F382" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G382" s="9" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="H382" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B383" s="9" t="inlineStr">
+        <is>
+          <t>s4_dev_debt</t>
+        </is>
+      </c>
+      <c r="C383" s="9" t="inlineStr">
+        <is>
+          <t>Developing-world debt crisis</t>
+        </is>
+      </c>
+      <c r="D383" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E383" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F383" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G383" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H383" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B384" s="9" t="inlineStr">
+        <is>
+          <t>s5_china_deflation</t>
+        </is>
+      </c>
+      <c r="C384" s="9" t="inlineStr">
+        <is>
+          <t>China's price spillover (deflation or cost-push)</t>
+        </is>
+      </c>
+      <c r="D384" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E384" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F384" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G384" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H384" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B385" s="9" t="inlineStr">
+        <is>
+          <t>s6_rare_earths</t>
+        </is>
+      </c>
+      <c r="C385" s="9" t="inlineStr">
+        <is>
+          <t>Critical minerals as a weapon</t>
+        </is>
+      </c>
+      <c r="D385" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E385" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F385" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G385" s="9" t="inlineStr">
+        <is>
+          <t>6.75</t>
+        </is>
+      </c>
+      <c r="H385" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B386" s="9" t="inlineStr">
+        <is>
+          <t>s7_stablecoins</t>
+        </is>
+      </c>
+      <c r="C386" s="9" t="inlineStr">
+        <is>
+          <t>Stablecoins &amp; Treasury demand</t>
+        </is>
+      </c>
+      <c r="D386" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E386" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F386" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G386" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H386" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B387" s="9" t="inlineStr">
+        <is>
+          <t>s8_ai_capex</t>
+        </is>
+      </c>
+      <c r="C387" s="9" t="inlineStr">
+        <is>
+          <t>AI build-out circular financing</t>
+        </is>
+      </c>
+      <c r="D387" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E387" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F387" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G387" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H387" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B388" s="9" t="inlineStr">
+        <is>
+          <t>s9_cre</t>
+        </is>
+      </c>
+      <c r="C388" s="9" t="inlineStr">
+        <is>
+          <t>CRE maturity wall / regional banks</t>
+        </is>
+      </c>
+      <c r="D388" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E388" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F388" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G388" s="9" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="H388" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B389" s="9" t="inlineStr">
+        <is>
+          <t>s10_france</t>
+        </is>
+      </c>
+      <c r="C389" s="9" t="inlineStr">
+        <is>
+          <t>France / eurozone fragility</t>
+        </is>
+      </c>
+      <c r="D389" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E389" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F389" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G389" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H389" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B390" s="9" t="inlineStr">
+        <is>
+          <t>s11_consumer_debt</t>
+        </is>
+      </c>
+      <c r="C390" s="9" t="inlineStr">
+        <is>
+          <t>Hidden consumer debt</t>
+        </is>
+      </c>
+      <c r="D390" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E390" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F390" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G390" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H390" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B391" s="9" t="inlineStr">
+        <is>
+          <t>s12_gold_dedollar</t>
+        </is>
+      </c>
+      <c r="C391" s="9" t="inlineStr">
+        <is>
+          <t>Gold / de-dollarization</t>
+        </is>
+      </c>
+      <c r="D391" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E391" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F391" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G391" s="9" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="H391" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B392" s="9" t="inlineStr">
+        <is>
+          <t>s13_insurance</t>
+        </is>
+      </c>
+      <c r="C392" s="9" t="inlineStr">
+        <is>
+          <t>Insurance retreat</t>
+        </is>
+      </c>
+      <c r="D392" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E392" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F392" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G392" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H392" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B393" s="9" t="inlineStr">
+        <is>
+          <t>s14_pensions</t>
+        </is>
+      </c>
+      <c r="C393" s="9" t="inlineStr">
+        <is>
+          <t>Pensions / demographics</t>
+        </is>
+      </c>
+      <c r="D393" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E393" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F393" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G393" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H393" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B394" s="9" t="inlineStr">
+        <is>
+          <t>s15_ai_power</t>
+        </is>
+      </c>
+      <c r="C394" s="9" t="inlineStr">
+        <is>
+          <t>AI power &amp; the grid bottleneck</t>
+        </is>
+      </c>
+      <c r="D394" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E394" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F394" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G394" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H394" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B395" s="9" t="inlineStr">
+        <is>
+          <t>s16_copper</t>
+        </is>
+      </c>
+      <c r="C395" s="9" t="inlineStr">
+        <is>
+          <t>Copper &amp; the electrification deficit</t>
+        </is>
+      </c>
+      <c r="D395" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E395" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F395" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G395" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H395" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B396" s="9" t="inlineStr">
+        <is>
+          <t>s17_water</t>
+        </is>
+      </c>
+      <c r="C396" s="9" t="inlineStr">
+        <is>
+          <t>Water - the underpriced input</t>
+        </is>
+      </c>
+      <c r="D396" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E396" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F396" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G396" s="9" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="H396" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B397" s="9" t="inlineStr">
+        <is>
+          <t>s18_food_fertilizer</t>
+        </is>
+      </c>
+      <c r="C397" s="9" t="inlineStr">
+        <is>
+          <t>Food &amp; fertilizer fragility</t>
+        </is>
+      </c>
+      <c r="D397" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E397" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F397" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G397" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H397" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B398" s="9" t="inlineStr">
+        <is>
+          <t>s19_lithography</t>
+        </is>
+      </c>
+      <c r="C398" s="9" t="inlineStr">
+        <is>
+          <t>The lithography (ASML) chokepoint</t>
+        </is>
+      </c>
+      <c r="D398" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E398" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F398" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G398" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H398" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B399" s="9" t="inlineStr">
+        <is>
+          <t>s20_sea_lanes</t>
+        </is>
+      </c>
+      <c r="C399" s="9" t="inlineStr">
+        <is>
+          <t>Sea lanes &amp; undersea cables</t>
+        </is>
+      </c>
+      <c r="D399" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E399" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F399" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G399" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="H399" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B400" s="9" t="inlineStr">
+        <is>
+          <t>s21_clearinghouses</t>
+        </is>
+      </c>
+      <c r="C400" s="9" t="inlineStr">
+        <is>
+          <t>Clearinghouses (financial chokepoint)</t>
+        </is>
+      </c>
+      <c r="D400" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E400" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F400" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G400" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H400" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -20515,7 +21397,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A24"/>
+  <dimension ref="A1:A22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -20596,38 +21478,34 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>--- Daily narrative (2026-07-05) ---</t>
+          <t>--- Daily narrative (2026-07-06) ---</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>**HEADLINE**</t>
+          <t># EOD Macro Risk Brief | 2026-07-06</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>Overall macro risk remains elevated at 6.2, with three stories at High level—Japan carry trade, critical minerals weaponization, and AI power grid constraints—presenting the largest tail risks.</t>
-        </is>
-      </c>
+      <c r="A15" s="12" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr"/>
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>**Overall risk elevated to 6.8; two high-risk stories shifted materially higher.**</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>**STORIES WITH LEVEL CHANGES**</t>
-        </is>
-      </c>
+      <c r="A17" s="12" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>No intraday level changes recorded.</t>
+          <t>• **Japan fiscal/JGB/carry trade** (7→8, High): 30-year JGB yield rose to 3.94% and Takaichi plan financing clarity deteriorated to "disorderly"—dual pressures threatening yen carry unwind and domestic debt sustainability.</t>
         </is>
       </c>
     </row>
@@ -20637,31 +21515,17 @@
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>**ELEVATED OR HIGHER RISKS TO NOTE**</t>
+          <t>• **Private credit's opaque expansion** (6→8, High): Direct-lending default rate hit 6.0% and large-fund redemption gates now widespread—signals stress in $2.5tr+ market with limited transparency and potential liquidity cascades.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>Treasury basis trades (hidden leverage), private credit opacity, developing-world debt stress, China's deflationary spillover, AI circular financing, hidden consumer debt, food/fertilizer fragility, ASML lithography concentration, and sea lane/subsea cable exposure all remain at Elevated (level 6). France/eurozone fragility and CRE maturity walls sit at level 5 (Elevated). Water as an underpriced input flagged at level 5.</t>
-        </is>
-      </c>
+      <c r="A21" s="12" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>**TOP WATCH**</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="12" t="inlineStr">
-        <is>
-          <t>Japan fiscal/JGB/carry trade at level 7 (High) remains the most systemically consequential story given yen carry unwind potential and global funding shock risk.</t>
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>**Highest priority watch:** Private credit redemption gates; widespread gating in a market lacking central clearing or real-time pricing creates tail-risk contagion to broader credit.</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-07-06  -  generated 2026-07-06 15:04 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-07-07  -  generated 2026-07-07 14:07 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
         </is>
       </c>
       <c r="D2" s="7" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>162.371</v>
+        <v>162.003</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>3.94</v>
+        <v>3.976</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>120.8866</v>
+        <v>120.6902</v>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>6.7842</v>
+        <v>6.7805</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>310</v>
+        <v>310.6</v>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>4145.7002</v>
+        <v>4173.2998</v>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>6.1975</v>
+        <v>6.2435</v>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="D60" s="7" t="n">
-        <v>69.01000000000001</v>
+        <v>69.94</v>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="D62" s="7" t="n">
-        <v>16.08</v>
+        <v>15.96</v>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H400"/>
+  <dimension ref="A1:H421"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -21386,6 +21386,888 @@
         </is>
       </c>
     </row>
+    <row r="401">
+      <c r="A401" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B401" s="9" t="inlineStr">
+        <is>
+          <t>s1_basis_trade</t>
+        </is>
+      </c>
+      <c r="C401" s="9" t="inlineStr">
+        <is>
+          <t>Treasury basis trade (hidden leverage)</t>
+        </is>
+      </c>
+      <c r="D401" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E401" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F401" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G401" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H401" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B402" s="9" t="inlineStr">
+        <is>
+          <t>s2_japan</t>
+        </is>
+      </c>
+      <c r="C402" s="9" t="inlineStr">
+        <is>
+          <t>Japan fiscal / JGB / carry trade</t>
+        </is>
+      </c>
+      <c r="D402" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E402" s="9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F402" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G402" s="9" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="H402" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B403" s="9" t="inlineStr">
+        <is>
+          <t>s3_private_credit</t>
+        </is>
+      </c>
+      <c r="C403" s="9" t="inlineStr">
+        <is>
+          <t>Private credit's opaque expansion</t>
+        </is>
+      </c>
+      <c r="D403" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E403" s="9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F403" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G403" s="9" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="H403" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B404" s="9" t="inlineStr">
+        <is>
+          <t>s4_dev_debt</t>
+        </is>
+      </c>
+      <c r="C404" s="9" t="inlineStr">
+        <is>
+          <t>Developing-world debt crisis</t>
+        </is>
+      </c>
+      <c r="D404" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E404" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F404" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G404" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H404" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B405" s="9" t="inlineStr">
+        <is>
+          <t>s5_china_deflation</t>
+        </is>
+      </c>
+      <c r="C405" s="9" t="inlineStr">
+        <is>
+          <t>China's price spillover (deflation or cost-push)</t>
+        </is>
+      </c>
+      <c r="D405" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E405" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F405" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G405" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H405" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B406" s="9" t="inlineStr">
+        <is>
+          <t>s6_rare_earths</t>
+        </is>
+      </c>
+      <c r="C406" s="9" t="inlineStr">
+        <is>
+          <t>Critical minerals as a weapon</t>
+        </is>
+      </c>
+      <c r="D406" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E406" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F406" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G406" s="9" t="inlineStr">
+        <is>
+          <t>6.75</t>
+        </is>
+      </c>
+      <c r="H406" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B407" s="9" t="inlineStr">
+        <is>
+          <t>s7_stablecoins</t>
+        </is>
+      </c>
+      <c r="C407" s="9" t="inlineStr">
+        <is>
+          <t>Stablecoins &amp; Treasury demand</t>
+        </is>
+      </c>
+      <c r="D407" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E407" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F407" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G407" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H407" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B408" s="9" t="inlineStr">
+        <is>
+          <t>s8_ai_capex</t>
+        </is>
+      </c>
+      <c r="C408" s="9" t="inlineStr">
+        <is>
+          <t>AI build-out circular financing</t>
+        </is>
+      </c>
+      <c r="D408" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E408" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F408" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G408" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H408" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B409" s="9" t="inlineStr">
+        <is>
+          <t>s9_cre</t>
+        </is>
+      </c>
+      <c r="C409" s="9" t="inlineStr">
+        <is>
+          <t>CRE maturity wall / regional banks</t>
+        </is>
+      </c>
+      <c r="D409" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E409" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F409" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G409" s="9" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="H409" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B410" s="9" t="inlineStr">
+        <is>
+          <t>s10_france</t>
+        </is>
+      </c>
+      <c r="C410" s="9" t="inlineStr">
+        <is>
+          <t>France / eurozone fragility</t>
+        </is>
+      </c>
+      <c r="D410" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E410" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F410" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G410" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H410" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B411" s="9" t="inlineStr">
+        <is>
+          <t>s11_consumer_debt</t>
+        </is>
+      </c>
+      <c r="C411" s="9" t="inlineStr">
+        <is>
+          <t>Hidden consumer debt</t>
+        </is>
+      </c>
+      <c r="D411" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E411" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F411" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G411" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H411" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B412" s="9" t="inlineStr">
+        <is>
+          <t>s12_gold_dedollar</t>
+        </is>
+      </c>
+      <c r="C412" s="9" t="inlineStr">
+        <is>
+          <t>Gold / de-dollarization</t>
+        </is>
+      </c>
+      <c r="D412" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E412" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F412" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G412" s="9" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="H412" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B413" s="9" t="inlineStr">
+        <is>
+          <t>s13_insurance</t>
+        </is>
+      </c>
+      <c r="C413" s="9" t="inlineStr">
+        <is>
+          <t>Insurance retreat</t>
+        </is>
+      </c>
+      <c r="D413" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E413" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F413" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G413" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H413" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B414" s="9" t="inlineStr">
+        <is>
+          <t>s14_pensions</t>
+        </is>
+      </c>
+      <c r="C414" s="9" t="inlineStr">
+        <is>
+          <t>Pensions / demographics</t>
+        </is>
+      </c>
+      <c r="D414" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E414" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F414" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G414" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H414" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B415" s="9" t="inlineStr">
+        <is>
+          <t>s15_ai_power</t>
+        </is>
+      </c>
+      <c r="C415" s="9" t="inlineStr">
+        <is>
+          <t>AI power &amp; the grid bottleneck</t>
+        </is>
+      </c>
+      <c r="D415" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E415" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F415" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G415" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H415" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B416" s="9" t="inlineStr">
+        <is>
+          <t>s16_copper</t>
+        </is>
+      </c>
+      <c r="C416" s="9" t="inlineStr">
+        <is>
+          <t>Copper &amp; the electrification deficit</t>
+        </is>
+      </c>
+      <c r="D416" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E416" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F416" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G416" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H416" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B417" s="9" t="inlineStr">
+        <is>
+          <t>s17_water</t>
+        </is>
+      </c>
+      <c r="C417" s="9" t="inlineStr">
+        <is>
+          <t>Water - the underpriced input</t>
+        </is>
+      </c>
+      <c r="D417" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E417" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F417" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G417" s="9" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="H417" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B418" s="9" t="inlineStr">
+        <is>
+          <t>s18_food_fertilizer</t>
+        </is>
+      </c>
+      <c r="C418" s="9" t="inlineStr">
+        <is>
+          <t>Food &amp; fertilizer fragility</t>
+        </is>
+      </c>
+      <c r="D418" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E418" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F418" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G418" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H418" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B419" s="9" t="inlineStr">
+        <is>
+          <t>s19_lithography</t>
+        </is>
+      </c>
+      <c r="C419" s="9" t="inlineStr">
+        <is>
+          <t>The lithography (ASML) chokepoint</t>
+        </is>
+      </c>
+      <c r="D419" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E419" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F419" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G419" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H419" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B420" s="9" t="inlineStr">
+        <is>
+          <t>s20_sea_lanes</t>
+        </is>
+      </c>
+      <c r="C420" s="9" t="inlineStr">
+        <is>
+          <t>Sea lanes &amp; undersea cables</t>
+        </is>
+      </c>
+      <c r="D420" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E420" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F420" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G420" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="H420" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B421" s="9" t="inlineStr">
+        <is>
+          <t>s21_clearinghouses</t>
+        </is>
+      </c>
+      <c r="C421" s="9" t="inlineStr">
+        <is>
+          <t>Clearinghouses (financial chokepoint)</t>
+        </is>
+      </c>
+      <c r="D421" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E421" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F421" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G421" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H421" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -21397,7 +22279,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A22"/>
+  <dimension ref="A1:A26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -21478,14 +22360,14 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>--- Daily narrative (2026-07-06) ---</t>
+          <t>--- Daily narrative (2026-07-07) ---</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t># EOD Macro Risk Brief | 2026-07-06</t>
+          <t># EOD Macro-Risk Brief | 7 July 2026</t>
         </is>
       </c>
     </row>
@@ -21495,7 +22377,7 @@
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>**Overall risk elevated to 6.8; two high-risk stories shifted materially higher.**</t>
+          <t>**Headline:** Overall macro risk elevated at 6.8 with no intraday level changes; structural vulnerabilities in Japan carry trade, private credit, and critical minerals remain the highest-risk vectors.</t>
         </is>
       </c>
     </row>
@@ -21505,27 +22387,55 @@
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>• **Japan fiscal/JGB/carry trade** (7→8, High): 30-year JGB yield rose to 3.94% and Takaichi plan financing clarity deteriorated to "disorderly"—dual pressures threatening yen carry unwind and domestic debt sustainability.</t>
+          <t>**Key Stories (No Changes Today):**</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr"/>
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>No risk levels shifted during the session.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
-          <t>• **Private credit's opaque expansion** (6→8, High): Direct-lending default rate hit 6.0% and large-fund redemption gates now widespread—signals stress in $2.5tr+ market with limited transparency and potential liquidity cascades.</t>
-        </is>
-      </c>
+      <c r="A20" s="12" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr"/>
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>**Elevated &amp; High-Risk Exposures Currently Active:**</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>**Highest priority watch:** Private credit redemption gates; widespread gating in a market lacking central clearing or real-time pricing creates tail-risk contagion to broader credit.</t>
+          <t>- **Japan fiscal/JGB/carry trade (Level 8, High)** and **Private credit expansion (Level 8, High)** represent the twin systemic peaks; both involve hidden leverage and opacity in asset pricing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>- **Critical minerals (Level 7, High)** and **AI power/grid bottleneck (Level 7, High)** pose structural supply constraints with geopolitical and infrastructure dimensions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>- Six stories at Level 6 (Treasury basis, developing-world debt, China deflation spillover, AI financing, hidden consumer debt, food fragility, lithography, sea lanes) reflect distributed tail risks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>**Watch Most Closely:** Japan fiscal/JGB/carry trade unwinding remains the single highest-risk trigger for rapid cross-asset repricing given leverage concentration and global carry exposure.</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-07-07  -  generated 2026-07-07 14:07 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-07-08  -  generated 2026-07-08 11:48 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>162.003</v>
+        <v>162.472</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>3.976</v>
+        <v>3.951</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Direct-lending default rate (%)</t>
+          <t>Direct-lending default rate (%, Fitch incl. distressed exchanges)</t>
         </is>
       </c>
       <c r="D9" s="7" t="n">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="O9" s="8" t="inlineStr">
         <is>
-          <t>Morgan Stanley flagged a possible move toward 8%.</t>
+          <t>Anchored to Fitch's inclusive measure (counts distressed exchanges; Apr-2026 record 6.0%). Proskauer's count-based index runs ~2-3pts lower - dissent context only. Morgan Stanley flagged a possible move toward 8%.</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>6.7805</v>
+        <v>6.799</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>310.6</v>
+        <v>310.4</v>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>4173.2998</v>
+        <v>4053.2</v>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>6.2435</v>
+        <v>6.0715</v>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="D60" s="7" t="n">
-        <v>69.94</v>
+        <v>74.52</v>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="D62" s="7" t="n">
-        <v>15.96</v>
+        <v>18.34</v>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H421"/>
+  <dimension ref="A1:H442"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -22263,6 +22263,888 @@
         </is>
       </c>
       <c r="H421" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B422" s="9" t="inlineStr">
+        <is>
+          <t>s1_basis_trade</t>
+        </is>
+      </c>
+      <c r="C422" s="9" t="inlineStr">
+        <is>
+          <t>Treasury basis trade (hidden leverage)</t>
+        </is>
+      </c>
+      <c r="D422" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E422" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F422" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G422" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H422" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B423" s="9" t="inlineStr">
+        <is>
+          <t>s2_japan</t>
+        </is>
+      </c>
+      <c r="C423" s="9" t="inlineStr">
+        <is>
+          <t>Japan fiscal / JGB / carry trade</t>
+        </is>
+      </c>
+      <c r="D423" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E423" s="9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F423" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G423" s="9" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="H423" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B424" s="9" t="inlineStr">
+        <is>
+          <t>s3_private_credit</t>
+        </is>
+      </c>
+      <c r="C424" s="9" t="inlineStr">
+        <is>
+          <t>Private credit's opaque expansion</t>
+        </is>
+      </c>
+      <c r="D424" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E424" s="9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F424" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G424" s="9" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="H424" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B425" s="9" t="inlineStr">
+        <is>
+          <t>s4_dev_debt</t>
+        </is>
+      </c>
+      <c r="C425" s="9" t="inlineStr">
+        <is>
+          <t>Developing-world debt crisis</t>
+        </is>
+      </c>
+      <c r="D425" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E425" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F425" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G425" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H425" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B426" s="9" t="inlineStr">
+        <is>
+          <t>s5_china_deflation</t>
+        </is>
+      </c>
+      <c r="C426" s="9" t="inlineStr">
+        <is>
+          <t>China's price spillover (deflation or cost-push)</t>
+        </is>
+      </c>
+      <c r="D426" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E426" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F426" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G426" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H426" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B427" s="9" t="inlineStr">
+        <is>
+          <t>s6_rare_earths</t>
+        </is>
+      </c>
+      <c r="C427" s="9" t="inlineStr">
+        <is>
+          <t>Critical minerals as a weapon</t>
+        </is>
+      </c>
+      <c r="D427" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E427" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F427" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G427" s="9" t="inlineStr">
+        <is>
+          <t>6.75</t>
+        </is>
+      </c>
+      <c r="H427" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B428" s="9" t="inlineStr">
+        <is>
+          <t>s7_stablecoins</t>
+        </is>
+      </c>
+      <c r="C428" s="9" t="inlineStr">
+        <is>
+          <t>Stablecoins &amp; Treasury demand</t>
+        </is>
+      </c>
+      <c r="D428" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E428" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F428" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G428" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H428" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B429" s="9" t="inlineStr">
+        <is>
+          <t>s8_ai_capex</t>
+        </is>
+      </c>
+      <c r="C429" s="9" t="inlineStr">
+        <is>
+          <t>AI build-out circular financing</t>
+        </is>
+      </c>
+      <c r="D429" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E429" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F429" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G429" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H429" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B430" s="9" t="inlineStr">
+        <is>
+          <t>s9_cre</t>
+        </is>
+      </c>
+      <c r="C430" s="9" t="inlineStr">
+        <is>
+          <t>CRE maturity wall / regional banks</t>
+        </is>
+      </c>
+      <c r="D430" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E430" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F430" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G430" s="9" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="H430" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B431" s="9" t="inlineStr">
+        <is>
+          <t>s10_france</t>
+        </is>
+      </c>
+      <c r="C431" s="9" t="inlineStr">
+        <is>
+          <t>France / eurozone fragility</t>
+        </is>
+      </c>
+      <c r="D431" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E431" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F431" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G431" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H431" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B432" s="9" t="inlineStr">
+        <is>
+          <t>s11_consumer_debt</t>
+        </is>
+      </c>
+      <c r="C432" s="9" t="inlineStr">
+        <is>
+          <t>Hidden consumer debt</t>
+        </is>
+      </c>
+      <c r="D432" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E432" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F432" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G432" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H432" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B433" s="9" t="inlineStr">
+        <is>
+          <t>s12_gold_dedollar</t>
+        </is>
+      </c>
+      <c r="C433" s="9" t="inlineStr">
+        <is>
+          <t>Gold / de-dollarization</t>
+        </is>
+      </c>
+      <c r="D433" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E433" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F433" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G433" s="9" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="H433" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B434" s="9" t="inlineStr">
+        <is>
+          <t>s13_insurance</t>
+        </is>
+      </c>
+      <c r="C434" s="9" t="inlineStr">
+        <is>
+          <t>Insurance retreat</t>
+        </is>
+      </c>
+      <c r="D434" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E434" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F434" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G434" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H434" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B435" s="9" t="inlineStr">
+        <is>
+          <t>s14_pensions</t>
+        </is>
+      </c>
+      <c r="C435" s="9" t="inlineStr">
+        <is>
+          <t>Pensions / demographics</t>
+        </is>
+      </c>
+      <c r="D435" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E435" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F435" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G435" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H435" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B436" s="9" t="inlineStr">
+        <is>
+          <t>s15_ai_power</t>
+        </is>
+      </c>
+      <c r="C436" s="9" t="inlineStr">
+        <is>
+          <t>AI power &amp; the grid bottleneck</t>
+        </is>
+      </c>
+      <c r="D436" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E436" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F436" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G436" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H436" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B437" s="9" t="inlineStr">
+        <is>
+          <t>s16_copper</t>
+        </is>
+      </c>
+      <c r="C437" s="9" t="inlineStr">
+        <is>
+          <t>Copper &amp; the electrification deficit</t>
+        </is>
+      </c>
+      <c r="D437" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E437" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F437" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G437" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H437" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B438" s="9" t="inlineStr">
+        <is>
+          <t>s17_water</t>
+        </is>
+      </c>
+      <c r="C438" s="9" t="inlineStr">
+        <is>
+          <t>Water - the underpriced input</t>
+        </is>
+      </c>
+      <c r="D438" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E438" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F438" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G438" s="9" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="H438" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B439" s="9" t="inlineStr">
+        <is>
+          <t>s18_food_fertilizer</t>
+        </is>
+      </c>
+      <c r="C439" s="9" t="inlineStr">
+        <is>
+          <t>Food &amp; fertilizer fragility</t>
+        </is>
+      </c>
+      <c r="D439" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E439" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F439" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G439" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H439" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B440" s="9" t="inlineStr">
+        <is>
+          <t>s19_lithography</t>
+        </is>
+      </c>
+      <c r="C440" s="9" t="inlineStr">
+        <is>
+          <t>The lithography (ASML) chokepoint</t>
+        </is>
+      </c>
+      <c r="D440" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E440" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F440" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G440" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H440" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B441" s="9" t="inlineStr">
+        <is>
+          <t>s20_sea_lanes</t>
+        </is>
+      </c>
+      <c r="C441" s="9" t="inlineStr">
+        <is>
+          <t>Sea lanes &amp; undersea cables</t>
+        </is>
+      </c>
+      <c r="D441" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E441" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F441" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G441" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="H441" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B442" s="9" t="inlineStr">
+        <is>
+          <t>s21_clearinghouses</t>
+        </is>
+      </c>
+      <c r="C442" s="9" t="inlineStr">
+        <is>
+          <t>Clearinghouses (financial chokepoint)</t>
+        </is>
+      </c>
+      <c r="D442" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E442" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F442" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G442" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H442" s="9" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
@@ -22360,14 +23242,14 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>--- Daily narrative (2026-07-07) ---</t>
+          <t>--- Daily narrative (2026-07-08) ---</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t># EOD Macro-Risk Brief | 7 July 2026</t>
+          <t>**EOD MACRO-RISK BRIEF | 2026-07-08**</t>
         </is>
       </c>
     </row>
@@ -22377,65 +23259,69 @@
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>**Headline:** Overall macro risk elevated at 6.8 with no intraday level changes; structural vulnerabilities in Japan carry trade, private credit, and critical minerals remain the highest-risk vectors.</t>
+          <t>**Headline:**</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr"/>
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>Macro risk stands elevated at 6.8 overall, with three High-band stories (Japan carry/fiscal, private credit opacity, critical minerals weaponization) anchoring systemic vulnerability.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
-          <t>**Key Stories (No Changes Today):**</t>
-        </is>
-      </c>
+      <c r="A18" s="12" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>No risk levels shifted during the session.</t>
+          <t>**Stories at High Risk (Level 7–8):**</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr"/>
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>- **Japan fiscal/JGB/carry trade (8):** Largest structural imbalance; unwinding could trigger yen spike and multi-asset contagion.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>**Elevated &amp; High-Risk Exposures Currently Active:**</t>
+          <t>- **Private credit's opaque expansion (8):** Hidden leverage outside regulated banking; forced selling risk in stress scenario.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>- **Japan fiscal/JGB/carry trade (Level 8, High)** and **Private credit expansion (Level 8, High)** represent the twin systemic peaks; both involve hidden leverage and opacity in asset pricing.</t>
+          <t>- **Critical minerals as a weapon (7):** Supply concentration risk; geopolitical disruption to manufacturing and energy transition.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>- **Critical minerals (Level 7, High)** and **AI power/grid bottleneck (Level 7, High)** pose structural supply constraints with geopolitical and infrastructure dimensions.</t>
+          <t>- **AI power &amp; grid bottleneck (7):** Infrastructure constraint limiting capex returns; strains utilities and electricity markets.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="inlineStr">
-        <is>
-          <t>- Six stories at Level 6 (Treasury basis, developing-world debt, China deflation spillover, AI financing, hidden consumer debt, food fragility, lithography, sea lanes) reflect distributed tail risks.</t>
-        </is>
-      </c>
+      <c r="A24" s="12" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="inlineStr"/>
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>**Key Watch:**</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>**Watch Most Closely:** Japan fiscal/JGB/carry trade unwinding remains the single highest-risk trigger for rapid cross-asset repricing given leverage concentration and global carry exposure.</t>
+          <t>Japan fiscal/carry trade remains the dominant tail risk—monitor BoJ policy signals and JGB yield moves for early stress signals.</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-07-08  -  generated 2026-07-08 11:48 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-07-09  -  generated 2026-07-09 14:12 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
         </is>
       </c>
       <c r="D2" s="7" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>162.472</v>
+        <v>162.365</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>3.951</v>
+        <v>3.998</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>2.72</v>
+        <v>2.67</v>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>6.799</v>
+        <v>6.7833</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>310.4</v>
+        <v>309.8</v>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>4053.2</v>
+        <v>4139.8999</v>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>6.0715</v>
+        <v>6.2725</v>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="D60" s="7" t="n">
-        <v>74.52</v>
+        <v>72.64</v>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="D62" s="7" t="n">
-        <v>18.34</v>
+        <v>16.44</v>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H442"/>
+  <dimension ref="A1:H463"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -23150,6 +23150,888 @@
         </is>
       </c>
     </row>
+    <row r="443">
+      <c r="A443" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B443" s="9" t="inlineStr">
+        <is>
+          <t>s1_basis_trade</t>
+        </is>
+      </c>
+      <c r="C443" s="9" t="inlineStr">
+        <is>
+          <t>Treasury basis trade (hidden leverage)</t>
+        </is>
+      </c>
+      <c r="D443" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E443" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F443" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G443" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H443" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B444" s="9" t="inlineStr">
+        <is>
+          <t>s2_japan</t>
+        </is>
+      </c>
+      <c r="C444" s="9" t="inlineStr">
+        <is>
+          <t>Japan fiscal / JGB / carry trade</t>
+        </is>
+      </c>
+      <c r="D444" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E444" s="9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F444" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G444" s="9" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="H444" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B445" s="9" t="inlineStr">
+        <is>
+          <t>s3_private_credit</t>
+        </is>
+      </c>
+      <c r="C445" s="9" t="inlineStr">
+        <is>
+          <t>Private credit's opaque expansion</t>
+        </is>
+      </c>
+      <c r="D445" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E445" s="9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F445" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G445" s="9" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="H445" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B446" s="9" t="inlineStr">
+        <is>
+          <t>s4_dev_debt</t>
+        </is>
+      </c>
+      <c r="C446" s="9" t="inlineStr">
+        <is>
+          <t>Developing-world debt crisis</t>
+        </is>
+      </c>
+      <c r="D446" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E446" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F446" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G446" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H446" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B447" s="9" t="inlineStr">
+        <is>
+          <t>s5_china_deflation</t>
+        </is>
+      </c>
+      <c r="C447" s="9" t="inlineStr">
+        <is>
+          <t>China's price spillover (deflation or cost-push)</t>
+        </is>
+      </c>
+      <c r="D447" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E447" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F447" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G447" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H447" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B448" s="9" t="inlineStr">
+        <is>
+          <t>s6_rare_earths</t>
+        </is>
+      </c>
+      <c r="C448" s="9" t="inlineStr">
+        <is>
+          <t>Critical minerals as a weapon</t>
+        </is>
+      </c>
+      <c r="D448" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E448" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F448" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G448" s="9" t="inlineStr">
+        <is>
+          <t>6.75</t>
+        </is>
+      </c>
+      <c r="H448" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B449" s="9" t="inlineStr">
+        <is>
+          <t>s7_stablecoins</t>
+        </is>
+      </c>
+      <c r="C449" s="9" t="inlineStr">
+        <is>
+          <t>Stablecoins &amp; Treasury demand</t>
+        </is>
+      </c>
+      <c r="D449" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E449" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F449" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G449" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H449" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B450" s="9" t="inlineStr">
+        <is>
+          <t>s8_ai_capex</t>
+        </is>
+      </c>
+      <c r="C450" s="9" t="inlineStr">
+        <is>
+          <t>AI build-out circular financing</t>
+        </is>
+      </c>
+      <c r="D450" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E450" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F450" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G450" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H450" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B451" s="9" t="inlineStr">
+        <is>
+          <t>s9_cre</t>
+        </is>
+      </c>
+      <c r="C451" s="9" t="inlineStr">
+        <is>
+          <t>CRE maturity wall / regional banks</t>
+        </is>
+      </c>
+      <c r="D451" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E451" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F451" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G451" s="9" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="H451" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B452" s="9" t="inlineStr">
+        <is>
+          <t>s10_france</t>
+        </is>
+      </c>
+      <c r="C452" s="9" t="inlineStr">
+        <is>
+          <t>France / eurozone fragility</t>
+        </is>
+      </c>
+      <c r="D452" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E452" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F452" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G452" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H452" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B453" s="9" t="inlineStr">
+        <is>
+          <t>s11_consumer_debt</t>
+        </is>
+      </c>
+      <c r="C453" s="9" t="inlineStr">
+        <is>
+          <t>Hidden consumer debt</t>
+        </is>
+      </c>
+      <c r="D453" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E453" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F453" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G453" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H453" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B454" s="9" t="inlineStr">
+        <is>
+          <t>s12_gold_dedollar</t>
+        </is>
+      </c>
+      <c r="C454" s="9" t="inlineStr">
+        <is>
+          <t>Gold / de-dollarization</t>
+        </is>
+      </c>
+      <c r="D454" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E454" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F454" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G454" s="9" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="H454" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B455" s="9" t="inlineStr">
+        <is>
+          <t>s13_insurance</t>
+        </is>
+      </c>
+      <c r="C455" s="9" t="inlineStr">
+        <is>
+          <t>Insurance retreat</t>
+        </is>
+      </c>
+      <c r="D455" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E455" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F455" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G455" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H455" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B456" s="9" t="inlineStr">
+        <is>
+          <t>s14_pensions</t>
+        </is>
+      </c>
+      <c r="C456" s="9" t="inlineStr">
+        <is>
+          <t>Pensions / demographics</t>
+        </is>
+      </c>
+      <c r="D456" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E456" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F456" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G456" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H456" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B457" s="9" t="inlineStr">
+        <is>
+          <t>s15_ai_power</t>
+        </is>
+      </c>
+      <c r="C457" s="9" t="inlineStr">
+        <is>
+          <t>AI power &amp; the grid bottleneck</t>
+        </is>
+      </c>
+      <c r="D457" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E457" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F457" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G457" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H457" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B458" s="9" t="inlineStr">
+        <is>
+          <t>s16_copper</t>
+        </is>
+      </c>
+      <c r="C458" s="9" t="inlineStr">
+        <is>
+          <t>Copper &amp; the electrification deficit</t>
+        </is>
+      </c>
+      <c r="D458" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E458" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F458" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G458" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H458" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B459" s="9" t="inlineStr">
+        <is>
+          <t>s17_water</t>
+        </is>
+      </c>
+      <c r="C459" s="9" t="inlineStr">
+        <is>
+          <t>Water - the underpriced input</t>
+        </is>
+      </c>
+      <c r="D459" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E459" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F459" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G459" s="9" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="H459" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B460" s="9" t="inlineStr">
+        <is>
+          <t>s18_food_fertilizer</t>
+        </is>
+      </c>
+      <c r="C460" s="9" t="inlineStr">
+        <is>
+          <t>Food &amp; fertilizer fragility</t>
+        </is>
+      </c>
+      <c r="D460" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E460" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F460" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G460" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H460" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B461" s="9" t="inlineStr">
+        <is>
+          <t>s19_lithography</t>
+        </is>
+      </c>
+      <c r="C461" s="9" t="inlineStr">
+        <is>
+          <t>The lithography (ASML) chokepoint</t>
+        </is>
+      </c>
+      <c r="D461" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E461" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F461" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G461" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H461" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B462" s="9" t="inlineStr">
+        <is>
+          <t>s20_sea_lanes</t>
+        </is>
+      </c>
+      <c r="C462" s="9" t="inlineStr">
+        <is>
+          <t>Sea lanes &amp; undersea cables</t>
+        </is>
+      </c>
+      <c r="D462" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E462" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F462" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G462" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="H462" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B463" s="9" t="inlineStr">
+        <is>
+          <t>s21_clearinghouses</t>
+        </is>
+      </c>
+      <c r="C463" s="9" t="inlineStr">
+        <is>
+          <t>Clearinghouses (financial chokepoint)</t>
+        </is>
+      </c>
+      <c r="D463" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E463" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F463" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G463" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H463" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -23161,7 +24043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A26"/>
+  <dimension ref="A1:A29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -23242,86 +24124,107 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>--- Daily narrative (2026-07-08) ---</t>
+          <t>--- Daily narrative (2026-07-09) ---</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>**EOD MACRO-RISK BRIEF | 2026-07-08**</t>
+          <t>**HEADLINE**</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr"/>
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>Macro risk elevated at 6.8 overall, with Japan carry trade and private credit opacity at High level and no material changes today.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>**Headline:**</t>
-        </is>
-      </c>
+      <c r="A16" s="12" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>Macro risk stands elevated at 6.8 overall, with three High-band stories (Japan carry/fiscal, private credit opacity, critical minerals weaponization) anchoring systemic vulnerability.</t>
+          <t>**STORY CHANGES**</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="inlineStr"/>
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>No risk levels shifted today.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>**Stories at High Risk (Level 7–8):**</t>
-        </is>
-      </c>
+      <c r="A19" s="12" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>- **Japan fiscal/JGB/carry trade (8):** Largest structural imbalance; unwinding could trigger yen spike and multi-asset contagion.</t>
+          <t>**ELEVATED &amp; HIGH RISKS (unchanged)**</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>- **Private credit's opaque expansion (8):** Hidden leverage outside regulated banking; forced selling risk in stress scenario.</t>
+          <t>• **Japan fiscal/JGB/carry trade (8/High)** – Structural imbalances in JGB yields and FX volatility could trigger rapid deleveraging across global markets.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>- **Critical minerals as a weapon (7):** Supply concentration risk; geopolitical disruption to manufacturing and energy transition.</t>
+          <t>• **Private credit's opaque expansion (8/High)** – Continued growth in unregulated lending with limited transparency poses systemic stress if liquidity seizes.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>- **AI power &amp; grid bottleneck (7):** Infrastructure constraint limiting capex returns; strains utilities and electricity markets.</t>
+          <t>• **Critical minerals as a weapon (7/High)** – Supply concentration remains weaponizable; disruption would cascade through EV and renewable supply chains.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="inlineStr"/>
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>• **AI power &amp; grid bottleneck (7/High)** – Data center demand outpacing infrastructure; regional blackouts or chronic undersupply risk.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>**Key Watch:**</t>
+          <t>• **Treasury basis trade (6/Elevated)** – Hidden leverage embedded in repo-adjacent structures could amplify volatility in a rate shock.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>Japan fiscal/carry trade remains the dominant tail risk—monitor BoJ policy signals and JGB yield moves for early stress signals.</t>
+          <t>• Developing-world debt, China deflation spillover, hidden consumer debt, CRE maturity wall, food fragility, lithography chokepoint, and undersea cable vulnerability all remain at Elevated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>**TOP WATCH**</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>Japan fiscal/JGB/carry trade unwind poses the highest near-term systemic contagion risk.</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-07-09  -  generated 2026-07-09 14:12 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-07-10  -  generated 2026-07-10 13:31 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
         </is>
       </c>
       <c r="D2" s="7" t="n">
-        <v>-0.04</v>
+        <v>-0.09</v>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="D3" s="7" t="n">
-        <v>65.40000000000001</v>
+        <v>68.8935</v>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>162.365</v>
+        <v>161.784</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>3.998</v>
+        <v>4.013</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>6.7833</v>
+        <v>6.7663</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>309.8</v>
+        <v>310.4</v>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>4139.8999</v>
+        <v>4110.8999</v>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>6.2725</v>
+        <v>6.273</v>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="D60" s="7" t="n">
-        <v>72.64</v>
+        <v>72.11</v>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="D62" s="7" t="n">
-        <v>16.44</v>
+        <v>15.73</v>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
         </is>
       </c>
       <c r="D63" s="7" t="n">
-        <v>65.40000000000001</v>
+        <v>68.8935</v>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H463"/>
+  <dimension ref="A1:H484"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -24032,6 +24032,888 @@
         </is>
       </c>
     </row>
+    <row r="464">
+      <c r="A464" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B464" s="9" t="inlineStr">
+        <is>
+          <t>s1_basis_trade</t>
+        </is>
+      </c>
+      <c r="C464" s="9" t="inlineStr">
+        <is>
+          <t>Treasury basis trade (hidden leverage)</t>
+        </is>
+      </c>
+      <c r="D464" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E464" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F464" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G464" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H464" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B465" s="9" t="inlineStr">
+        <is>
+          <t>s2_japan</t>
+        </is>
+      </c>
+      <c r="C465" s="9" t="inlineStr">
+        <is>
+          <t>Japan fiscal / JGB / carry trade</t>
+        </is>
+      </c>
+      <c r="D465" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E465" s="9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F465" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G465" s="9" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="H465" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B466" s="9" t="inlineStr">
+        <is>
+          <t>s3_private_credit</t>
+        </is>
+      </c>
+      <c r="C466" s="9" t="inlineStr">
+        <is>
+          <t>Private credit's opaque expansion</t>
+        </is>
+      </c>
+      <c r="D466" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E466" s="9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F466" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G466" s="9" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="H466" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B467" s="9" t="inlineStr">
+        <is>
+          <t>s4_dev_debt</t>
+        </is>
+      </c>
+      <c r="C467" s="9" t="inlineStr">
+        <is>
+          <t>Developing-world debt crisis</t>
+        </is>
+      </c>
+      <c r="D467" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E467" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F467" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G467" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H467" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B468" s="9" t="inlineStr">
+        <is>
+          <t>s5_china_deflation</t>
+        </is>
+      </c>
+      <c r="C468" s="9" t="inlineStr">
+        <is>
+          <t>China's price spillover (deflation or cost-push)</t>
+        </is>
+      </c>
+      <c r="D468" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E468" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F468" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G468" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H468" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B469" s="9" t="inlineStr">
+        <is>
+          <t>s6_rare_earths</t>
+        </is>
+      </c>
+      <c r="C469" s="9" t="inlineStr">
+        <is>
+          <t>Critical minerals as a weapon</t>
+        </is>
+      </c>
+      <c r="D469" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E469" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F469" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G469" s="9" t="inlineStr">
+        <is>
+          <t>6.75</t>
+        </is>
+      </c>
+      <c r="H469" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B470" s="9" t="inlineStr">
+        <is>
+          <t>s7_stablecoins</t>
+        </is>
+      </c>
+      <c r="C470" s="9" t="inlineStr">
+        <is>
+          <t>Stablecoins &amp; Treasury demand</t>
+        </is>
+      </c>
+      <c r="D470" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E470" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F470" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G470" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H470" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B471" s="9" t="inlineStr">
+        <is>
+          <t>s8_ai_capex</t>
+        </is>
+      </c>
+      <c r="C471" s="9" t="inlineStr">
+        <is>
+          <t>AI build-out circular financing</t>
+        </is>
+      </c>
+      <c r="D471" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E471" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F471" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G471" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H471" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B472" s="9" t="inlineStr">
+        <is>
+          <t>s9_cre</t>
+        </is>
+      </c>
+      <c r="C472" s="9" t="inlineStr">
+        <is>
+          <t>CRE maturity wall / regional banks</t>
+        </is>
+      </c>
+      <c r="D472" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E472" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F472" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G472" s="9" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="H472" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B473" s="9" t="inlineStr">
+        <is>
+          <t>s10_france</t>
+        </is>
+      </c>
+      <c r="C473" s="9" t="inlineStr">
+        <is>
+          <t>France / eurozone fragility</t>
+        </is>
+      </c>
+      <c r="D473" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E473" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F473" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G473" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H473" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B474" s="9" t="inlineStr">
+        <is>
+          <t>s11_consumer_debt</t>
+        </is>
+      </c>
+      <c r="C474" s="9" t="inlineStr">
+        <is>
+          <t>Hidden consumer debt</t>
+        </is>
+      </c>
+      <c r="D474" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E474" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F474" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G474" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H474" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B475" s="9" t="inlineStr">
+        <is>
+          <t>s12_gold_dedollar</t>
+        </is>
+      </c>
+      <c r="C475" s="9" t="inlineStr">
+        <is>
+          <t>Gold / de-dollarization</t>
+        </is>
+      </c>
+      <c r="D475" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E475" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F475" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G475" s="9" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="H475" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B476" s="9" t="inlineStr">
+        <is>
+          <t>s13_insurance</t>
+        </is>
+      </c>
+      <c r="C476" s="9" t="inlineStr">
+        <is>
+          <t>Insurance retreat</t>
+        </is>
+      </c>
+      <c r="D476" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E476" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F476" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G476" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H476" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B477" s="9" t="inlineStr">
+        <is>
+          <t>s14_pensions</t>
+        </is>
+      </c>
+      <c r="C477" s="9" t="inlineStr">
+        <is>
+          <t>Pensions / demographics</t>
+        </is>
+      </c>
+      <c r="D477" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E477" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F477" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G477" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H477" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B478" s="9" t="inlineStr">
+        <is>
+          <t>s15_ai_power</t>
+        </is>
+      </c>
+      <c r="C478" s="9" t="inlineStr">
+        <is>
+          <t>AI power &amp; the grid bottleneck</t>
+        </is>
+      </c>
+      <c r="D478" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E478" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F478" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G478" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H478" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B479" s="9" t="inlineStr">
+        <is>
+          <t>s16_copper</t>
+        </is>
+      </c>
+      <c r="C479" s="9" t="inlineStr">
+        <is>
+          <t>Copper &amp; the electrification deficit</t>
+        </is>
+      </c>
+      <c r="D479" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E479" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F479" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G479" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H479" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B480" s="9" t="inlineStr">
+        <is>
+          <t>s17_water</t>
+        </is>
+      </c>
+      <c r="C480" s="9" t="inlineStr">
+        <is>
+          <t>Water - the underpriced input</t>
+        </is>
+      </c>
+      <c r="D480" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E480" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F480" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G480" s="9" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="H480" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B481" s="9" t="inlineStr">
+        <is>
+          <t>s18_food_fertilizer</t>
+        </is>
+      </c>
+      <c r="C481" s="9" t="inlineStr">
+        <is>
+          <t>Food &amp; fertilizer fragility</t>
+        </is>
+      </c>
+      <c r="D481" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E481" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F481" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G481" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H481" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B482" s="9" t="inlineStr">
+        <is>
+          <t>s19_lithography</t>
+        </is>
+      </c>
+      <c r="C482" s="9" t="inlineStr">
+        <is>
+          <t>The lithography (ASML) chokepoint</t>
+        </is>
+      </c>
+      <c r="D482" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E482" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F482" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G482" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H482" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B483" s="9" t="inlineStr">
+        <is>
+          <t>s20_sea_lanes</t>
+        </is>
+      </c>
+      <c r="C483" s="9" t="inlineStr">
+        <is>
+          <t>Sea lanes &amp; undersea cables</t>
+        </is>
+      </c>
+      <c r="D483" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E483" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F483" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G483" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="H483" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B484" s="9" t="inlineStr">
+        <is>
+          <t>s21_clearinghouses</t>
+        </is>
+      </c>
+      <c r="C484" s="9" t="inlineStr">
+        <is>
+          <t>Clearinghouses (financial chokepoint)</t>
+        </is>
+      </c>
+      <c r="D484" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E484" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F484" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G484" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H484" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -24043,7 +24925,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A29"/>
+  <dimension ref="A1:A25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -24124,107 +25006,75 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>--- Daily narrative (2026-07-09) ---</t>
+          <t>--- Daily narrative (2026-07-10) ---</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>**HEADLINE**</t>
+          <t>**EOD MACRO-RISK BRIEF | 10 JUL 2026**</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>Macro risk elevated at 6.8 overall, with Japan carry trade and private credit opacity at High level and no material changes today.</t>
-        </is>
-      </c>
+      <c r="A15" s="12" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr"/>
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>**Headline:** Systemic risk elevated at 6.8 overall, with no intraday level changes but persistent concentration in Japan carry-trade unwind and opaque credit expansion.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>**STORY CHANGES**</t>
-        </is>
-      </c>
+      <c r="A17" s="12" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>No risk levels shifted today.</t>
+          <t>**Stories at Elevated or Higher:**</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr"/>
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>No level movements recorded today. The portfolio remains anchored by two High-band risks:</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>**ELEVATED &amp; HIGH RISKS (unchanged)**</t>
+          <t>- **Japan fiscal/JGB/carry trade (Level 8):** Sustained BoJ policy uncertainty continues to threaten cross-border funding withdrawals and cascade volatility into emerging FX.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>• **Japan fiscal/JGB/carry trade (8/High)** – Structural imbalances in JGB yields and FX volatility could trigger rapid deleveraging across global markets.</t>
+          <t>- **Private credit's opaque expansion (Level 8):** Lack of real-time transparency in non-bank lending creates tail-risk of forced liquidations if redemption pressure emerges.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t>• **Private credit's opaque expansion (8/High)** – Continued growth in unregulated lending with limited transparency poses systemic stress if liquidity seizes.</t>
-        </is>
-      </c>
+      <c r="A22" s="12" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>• **Critical minerals as a weapon (7/High)** – Supply concentration remains weaponizable; disruption would cascade through EV and renewable supply chains.</t>
+          <t>Supporting High-band risks include critical minerals weaponization (L7) and AI power-grid bottlenecks (L7), both structural supply-side constraints with limited near-term mitigation.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="inlineStr">
-        <is>
-          <t>• **AI power &amp; grid bottleneck (7/High)** – Data center demand outpacing infrastructure; regional blackouts or chronic undersupply risk.</t>
-        </is>
-      </c>
+      <c r="A24" s="12" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>• **Treasury basis trade (6/Elevated)** – Hidden leverage embedded in repo-adjacent structures could amplify volatility in a rate shock.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="12" t="inlineStr">
-        <is>
-          <t>• Developing-world debt, China deflation spillover, hidden consumer debt, CRE maturity wall, food fragility, lithography chokepoint, and undersea cable vulnerability all remain at Elevated.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="12" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="12" t="inlineStr">
-        <is>
-          <t>**TOP WATCH**</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="12" t="inlineStr">
-        <is>
-          <t>Japan fiscal/JGB/carry trade unwind poses the highest near-term systemic contagion risk.</t>
+          <t>**Watch:** Japan fiscal/JGB/carry trade remains the highest-risk story; any BoJ policy surprise or JGB yield spike could trigger immediate contagion across rates and currencies.</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-07-10  -  generated 2026-07-10 13:31 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-07-13  -  generated 2026-07-13 13:39 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
         </is>
       </c>
       <c r="D2" s="7" t="n">
-        <v>-0.09</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="D3" s="7" t="n">
-        <v>68.8935</v>
+        <v>69.55</v>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>161.784</v>
+        <v>162.158</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>4.013</v>
+        <v>3.938</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>6.7663</v>
+        <v>6.7651</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>310.4</v>
+        <v>310.8</v>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>4110.8999</v>
+        <v>4070.8</v>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>6.273</v>
+        <v>6.347</v>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="D60" s="7" t="n">
-        <v>72.11</v>
+        <v>73.67</v>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="D62" s="7" t="n">
-        <v>15.73</v>
+        <v>16.4</v>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
         </is>
       </c>
       <c r="D63" s="7" t="n">
-        <v>68.8935</v>
+        <v>69.55</v>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H484"/>
+  <dimension ref="A1:H505"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -24914,6 +24914,888 @@
         </is>
       </c>
     </row>
+    <row r="485">
+      <c r="A485" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B485" s="9" t="inlineStr">
+        <is>
+          <t>s1_basis_trade</t>
+        </is>
+      </c>
+      <c r="C485" s="9" t="inlineStr">
+        <is>
+          <t>Treasury basis trade (hidden leverage)</t>
+        </is>
+      </c>
+      <c r="D485" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E485" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F485" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G485" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H485" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B486" s="9" t="inlineStr">
+        <is>
+          <t>s2_japan</t>
+        </is>
+      </c>
+      <c r="C486" s="9" t="inlineStr">
+        <is>
+          <t>Japan fiscal / JGB / carry trade</t>
+        </is>
+      </c>
+      <c r="D486" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E486" s="9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F486" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G486" s="9" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="H486" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B487" s="9" t="inlineStr">
+        <is>
+          <t>s3_private_credit</t>
+        </is>
+      </c>
+      <c r="C487" s="9" t="inlineStr">
+        <is>
+          <t>Private credit's opaque expansion</t>
+        </is>
+      </c>
+      <c r="D487" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E487" s="9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F487" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G487" s="9" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="H487" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B488" s="9" t="inlineStr">
+        <is>
+          <t>s4_dev_debt</t>
+        </is>
+      </c>
+      <c r="C488" s="9" t="inlineStr">
+        <is>
+          <t>Developing-world debt crisis</t>
+        </is>
+      </c>
+      <c r="D488" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E488" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F488" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G488" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H488" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B489" s="9" t="inlineStr">
+        <is>
+          <t>s5_china_deflation</t>
+        </is>
+      </c>
+      <c r="C489" s="9" t="inlineStr">
+        <is>
+          <t>China's price spillover (deflation or cost-push)</t>
+        </is>
+      </c>
+      <c r="D489" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E489" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F489" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G489" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H489" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B490" s="9" t="inlineStr">
+        <is>
+          <t>s6_rare_earths</t>
+        </is>
+      </c>
+      <c r="C490" s="9" t="inlineStr">
+        <is>
+          <t>Critical minerals as a weapon</t>
+        </is>
+      </c>
+      <c r="D490" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E490" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F490" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G490" s="9" t="inlineStr">
+        <is>
+          <t>6.75</t>
+        </is>
+      </c>
+      <c r="H490" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B491" s="9" t="inlineStr">
+        <is>
+          <t>s7_stablecoins</t>
+        </is>
+      </c>
+      <c r="C491" s="9" t="inlineStr">
+        <is>
+          <t>Stablecoins &amp; Treasury demand</t>
+        </is>
+      </c>
+      <c r="D491" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E491" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F491" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G491" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H491" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B492" s="9" t="inlineStr">
+        <is>
+          <t>s8_ai_capex</t>
+        </is>
+      </c>
+      <c r="C492" s="9" t="inlineStr">
+        <is>
+          <t>AI build-out circular financing</t>
+        </is>
+      </c>
+      <c r="D492" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E492" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F492" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G492" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H492" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B493" s="9" t="inlineStr">
+        <is>
+          <t>s9_cre</t>
+        </is>
+      </c>
+      <c r="C493" s="9" t="inlineStr">
+        <is>
+          <t>CRE maturity wall / regional banks</t>
+        </is>
+      </c>
+      <c r="D493" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E493" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F493" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G493" s="9" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="H493" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B494" s="9" t="inlineStr">
+        <is>
+          <t>s10_france</t>
+        </is>
+      </c>
+      <c r="C494" s="9" t="inlineStr">
+        <is>
+          <t>France / eurozone fragility</t>
+        </is>
+      </c>
+      <c r="D494" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E494" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F494" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G494" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H494" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B495" s="9" t="inlineStr">
+        <is>
+          <t>s11_consumer_debt</t>
+        </is>
+      </c>
+      <c r="C495" s="9" t="inlineStr">
+        <is>
+          <t>Hidden consumer debt</t>
+        </is>
+      </c>
+      <c r="D495" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E495" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F495" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G495" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H495" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B496" s="9" t="inlineStr">
+        <is>
+          <t>s12_gold_dedollar</t>
+        </is>
+      </c>
+      <c r="C496" s="9" t="inlineStr">
+        <is>
+          <t>Gold / de-dollarization</t>
+        </is>
+      </c>
+      <c r="D496" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E496" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F496" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G496" s="9" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="H496" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B497" s="9" t="inlineStr">
+        <is>
+          <t>s13_insurance</t>
+        </is>
+      </c>
+      <c r="C497" s="9" t="inlineStr">
+        <is>
+          <t>Insurance retreat</t>
+        </is>
+      </c>
+      <c r="D497" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E497" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F497" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G497" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H497" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B498" s="9" t="inlineStr">
+        <is>
+          <t>s14_pensions</t>
+        </is>
+      </c>
+      <c r="C498" s="9" t="inlineStr">
+        <is>
+          <t>Pensions / demographics</t>
+        </is>
+      </c>
+      <c r="D498" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E498" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F498" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G498" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H498" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B499" s="9" t="inlineStr">
+        <is>
+          <t>s15_ai_power</t>
+        </is>
+      </c>
+      <c r="C499" s="9" t="inlineStr">
+        <is>
+          <t>AI power &amp; the grid bottleneck</t>
+        </is>
+      </c>
+      <c r="D499" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E499" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F499" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G499" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H499" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B500" s="9" t="inlineStr">
+        <is>
+          <t>s16_copper</t>
+        </is>
+      </c>
+      <c r="C500" s="9" t="inlineStr">
+        <is>
+          <t>Copper &amp; the electrification deficit</t>
+        </is>
+      </c>
+      <c r="D500" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E500" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F500" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G500" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H500" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B501" s="9" t="inlineStr">
+        <is>
+          <t>s17_water</t>
+        </is>
+      </c>
+      <c r="C501" s="9" t="inlineStr">
+        <is>
+          <t>Water - the underpriced input</t>
+        </is>
+      </c>
+      <c r="D501" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E501" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F501" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G501" s="9" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="H501" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B502" s="9" t="inlineStr">
+        <is>
+          <t>s18_food_fertilizer</t>
+        </is>
+      </c>
+      <c r="C502" s="9" t="inlineStr">
+        <is>
+          <t>Food &amp; fertilizer fragility</t>
+        </is>
+      </c>
+      <c r="D502" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E502" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F502" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G502" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H502" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B503" s="9" t="inlineStr">
+        <is>
+          <t>s19_lithography</t>
+        </is>
+      </c>
+      <c r="C503" s="9" t="inlineStr">
+        <is>
+          <t>The lithography (ASML) chokepoint</t>
+        </is>
+      </c>
+      <c r="D503" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E503" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F503" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G503" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H503" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B504" s="9" t="inlineStr">
+        <is>
+          <t>s20_sea_lanes</t>
+        </is>
+      </c>
+      <c r="C504" s="9" t="inlineStr">
+        <is>
+          <t>Sea lanes &amp; undersea cables</t>
+        </is>
+      </c>
+      <c r="D504" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E504" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F504" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G504" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="H504" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B505" s="9" t="inlineStr">
+        <is>
+          <t>s21_clearinghouses</t>
+        </is>
+      </c>
+      <c r="C505" s="9" t="inlineStr">
+        <is>
+          <t>Clearinghouses (financial chokepoint)</t>
+        </is>
+      </c>
+      <c r="D505" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E505" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F505" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G505" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H505" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -24925,7 +25807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A25"/>
+  <dimension ref="A1:A26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -25006,65 +25888,69 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>--- Daily narrative (2026-07-10) ---</t>
+          <t>--- Daily narrative (2026-07-13) ---</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>**EOD MACRO-RISK BRIEF | 10 JUL 2026**</t>
+          <t>**HEADLINE**</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr"/>
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>Macro risk remains elevated at 6.8 overall, with no intraday changes; structural vulnerabilities in Japan carry trades, opaque private credit, and AI infrastructure compete for immediate attention.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>**Headline:** Systemic risk elevated at 6.8 overall, with no intraday level changes but persistent concentration in Japan carry-trade unwind and opaque credit expansion.</t>
-        </is>
-      </c>
+      <c r="A16" s="12" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr"/>
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>**NO LEVEL CHANGES RECORDED TODAY**</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
-          <t>**Stories at Elevated or Higher:**</t>
-        </is>
-      </c>
+      <c r="A18" s="12" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>No level movements recorded today. The portfolio remains anchored by two High-band risks:</t>
+          <t>**TOP RISKS TO MONITOR**</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>- **Japan fiscal/JGB/carry trade (Level 8):** Sustained BoJ policy uncertainty continues to threaten cross-border funding withdrawals and cascade volatility into emerging FX.</t>
+          <t>• Japan fiscal/JGB/carry trade (Level 8, High): Yen volatility and funding stress could trigger rapid unwinding of leveraged positions across global equities and credit.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>- **Private credit's opaque expansion (Level 8):** Lack of real-time transparency in non-bank lending creates tail-risk of forced liquidations if redemption pressure emerges.</t>
+          <t>• Private credit's opaque expansion (Level 8, High): Valuation opacity and illiquidity in shadow finance create hidden tail risk if redemption pressures spike.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="inlineStr"/>
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>• Critical minerals as a weapon (Level 7, High): Supply concentration and geopolitical weaponization risk disrupting EV and renewable transitions.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>Supporting High-band risks include critical minerals weaponization (L7) and AI power-grid bottlenecks (L7), both structural supply-side constraints with limited near-term mitigation.</t>
+          <t>• AI power &amp; grid bottleneck (Level 7, High): Surging AI compute demand outpacing grid infrastructure; energy cost inflation and reliability constraints emerging.</t>
         </is>
       </c>
     </row>
@@ -25074,7 +25960,14 @@
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>**Watch:** Japan fiscal/JGB/carry trade remains the highest-risk story; any BoJ policy surprise or JGB yield spike could trigger immediate contagion across rates and currencies.</t>
+          <t>**WATCH CLOSEST**</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>Japan fiscal/JGB carry trade unwind remains the single highest-probability catalyst for cross-asset volatility.</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-07-13  -  generated 2026-07-13 13:39 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-07-13  -  generated 2026-07-13 20:13 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="D3" s="7" t="n">
-        <v>69.55</v>
+        <v>69.5493</v>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>162.158</v>
+        <v>162.436</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>6.7651</v>
+        <v>6.7709</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>310.8</v>
+        <v>310.6</v>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>4070.8</v>
+        <v>4009.2</v>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="D36" s="7" t="n">
-        <v>56.77</v>
+        <v>57.13</v>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>6.347</v>
+        <v>6.2785</v>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="D52" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         </is>
       </c>
       <c r="D55" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="D60" s="7" t="n">
-        <v>73.67</v>
+        <v>77.68000000000001</v>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="D62" s="7" t="n">
-        <v>16.4</v>
+        <v>17.12</v>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
         </is>
       </c>
       <c r="D63" s="7" t="n">
-        <v>69.55</v>
+        <v>69.5493</v>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
@@ -25105,17 +25105,17 @@
       </c>
       <c r="E489" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F489" s="9" t="inlineStr">
         <is>
-          <t>Elevated</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G489" s="9" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="H489" s="9" t="inlineStr">
@@ -25399,7 +25399,7 @@
       </c>
       <c r="E496" s="9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F496" s="9" t="inlineStr">
@@ -25409,7 +25409,7 @@
       </c>
       <c r="G496" s="9" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="H496" s="9" t="inlineStr">
@@ -25619,7 +25619,7 @@
       </c>
       <c r="G501" s="9" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="H501" s="9" t="inlineStr">
@@ -25651,17 +25651,17 @@
       </c>
       <c r="E502" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F502" s="9" t="inlineStr">
         <is>
-          <t>Elevated</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G502" s="9" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="H502" s="9" t="inlineStr">
@@ -25902,7 +25902,7 @@
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>Macro risk remains elevated at 6.8 overall, with no intraday changes; structural vulnerabilities in Japan carry trades, opaque private credit, and AI infrastructure compete for immediate attention.</t>
+          <t>Overall macro risk elevated at 7.6 with three stories shifting into or within High bands; China supply shocks and financial leverage remain dominant concerns.</t>
         </is>
       </c>
     </row>
@@ -25912,7 +25912,7 @@
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>**NO LEVEL CHANGES RECORDED TODAY**</t>
+          <t>**STORIES WITH LEVEL CHANGES**</t>
         </is>
       </c>
     </row>
@@ -25922,35 +25922,27 @@
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>**TOP RISKS TO MONITOR**</t>
+          <t>• **China's price spillover (6→7, High):** PPI swung to +4.1% YoY and anti-dumping actions escalated; risk is imported deflation or cost-push inflation spilling globally, constraining policy space.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
-          <t>• Japan fiscal/JGB/carry trade (Level 8, High): Yen volatility and funding stress could trigger rapid unwinding of leveraged positions across global equities and credit.</t>
-        </is>
-      </c>
+      <c r="A20" s="12" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>• Private credit's opaque expansion (Level 8, High): Valuation opacity and illiquidity in shadow finance create hidden tail risk if redemption pressures spike.</t>
+          <t>• **Food &amp; fertilizer fragility (6→7, High):** China tightened export curbs and Gulf/Hormuz disruption intensified; agricultural input scarcity threatens food price volatility and emerging-market vulnerability.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t>• Critical minerals as a weapon (Level 7, High): Supply concentration and geopolitical weaponization risk disrupting EV and renewable transitions.</t>
-        </is>
-      </c>
+      <c r="A22" s="12" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>• AI power &amp; grid bottleneck (Level 7, High): Surging AI compute demand outpacing grid infrastructure; energy cost inflation and reliability constraints emerging.</t>
+          <t>• **Gold / de-dollarization (4→3, Moderate):** USD reserve share stabilized at 57.1% and weaponization rhetoric remains at talk-stage only; risk ebbs slightly but structural shift remains monitored.</t>
         </is>
       </c>
     </row>
@@ -25960,14 +25952,14 @@
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>**WATCH CLOSEST**</t>
+          <t>**TOP WATCH**</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>Japan fiscal/JGB carry trade unwind remains the single highest-probability catalyst for cross-asset volatility.</t>
+          <t>Japan fiscal/JGB/carry trade at level 8 (High) poses the highest unwind risk if rates or volatility spike unexpectedly.</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-07-13  -  generated 2026-07-13 20:13 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-07-14  -  generated 2026-07-14 12:51 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="D3" s="7" t="n">
-        <v>69.5493</v>
+        <v>69.55</v>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>162.436</v>
+        <v>161.811</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>3.938</v>
+        <v>3.922</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>120.6902</v>
+        <v>120.5046</v>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>6.7709</v>
+        <v>6.7578</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>310.6</v>
+        <v>308.4</v>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>4009.2</v>
+        <v>4093.2</v>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>6.2785</v>
+        <v>6.397</v>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="D60" s="7" t="n">
-        <v>77.68000000000001</v>
+        <v>80.63</v>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="D62" s="7" t="n">
-        <v>17.12</v>
+        <v>16.6</v>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
         </is>
       </c>
       <c r="D63" s="7" t="n">
-        <v>69.5493</v>
+        <v>69.55</v>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H505"/>
+  <dimension ref="A1:H526"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -25796,6 +25796,888 @@
         </is>
       </c>
     </row>
+    <row r="506">
+      <c r="A506" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B506" s="9" t="inlineStr">
+        <is>
+          <t>s1_basis_trade</t>
+        </is>
+      </c>
+      <c r="C506" s="9" t="inlineStr">
+        <is>
+          <t>Treasury basis trade (hidden leverage)</t>
+        </is>
+      </c>
+      <c r="D506" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E506" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F506" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G506" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H506" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B507" s="9" t="inlineStr">
+        <is>
+          <t>s2_japan</t>
+        </is>
+      </c>
+      <c r="C507" s="9" t="inlineStr">
+        <is>
+          <t>Japan fiscal / JGB / carry trade</t>
+        </is>
+      </c>
+      <c r="D507" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E507" s="9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F507" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G507" s="9" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="H507" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B508" s="9" t="inlineStr">
+        <is>
+          <t>s3_private_credit</t>
+        </is>
+      </c>
+      <c r="C508" s="9" t="inlineStr">
+        <is>
+          <t>Private credit's opaque expansion</t>
+        </is>
+      </c>
+      <c r="D508" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E508" s="9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F508" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G508" s="9" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="H508" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B509" s="9" t="inlineStr">
+        <is>
+          <t>s4_dev_debt</t>
+        </is>
+      </c>
+      <c r="C509" s="9" t="inlineStr">
+        <is>
+          <t>Developing-world debt crisis</t>
+        </is>
+      </c>
+      <c r="D509" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E509" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F509" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G509" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H509" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B510" s="9" t="inlineStr">
+        <is>
+          <t>s5_china_deflation</t>
+        </is>
+      </c>
+      <c r="C510" s="9" t="inlineStr">
+        <is>
+          <t>China's price spillover (deflation or cost-push)</t>
+        </is>
+      </c>
+      <c r="D510" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E510" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F510" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G510" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H510" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B511" s="9" t="inlineStr">
+        <is>
+          <t>s6_rare_earths</t>
+        </is>
+      </c>
+      <c r="C511" s="9" t="inlineStr">
+        <is>
+          <t>Critical minerals as a weapon</t>
+        </is>
+      </c>
+      <c r="D511" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E511" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F511" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G511" s="9" t="inlineStr">
+        <is>
+          <t>6.75</t>
+        </is>
+      </c>
+      <c r="H511" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B512" s="9" t="inlineStr">
+        <is>
+          <t>s7_stablecoins</t>
+        </is>
+      </c>
+      <c r="C512" s="9" t="inlineStr">
+        <is>
+          <t>Stablecoins &amp; Treasury demand</t>
+        </is>
+      </c>
+      <c r="D512" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E512" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F512" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G512" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H512" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B513" s="9" t="inlineStr">
+        <is>
+          <t>s8_ai_capex</t>
+        </is>
+      </c>
+      <c r="C513" s="9" t="inlineStr">
+        <is>
+          <t>AI build-out circular financing</t>
+        </is>
+      </c>
+      <c r="D513" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E513" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F513" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G513" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H513" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B514" s="9" t="inlineStr">
+        <is>
+          <t>s9_cre</t>
+        </is>
+      </c>
+      <c r="C514" s="9" t="inlineStr">
+        <is>
+          <t>CRE maturity wall / regional banks</t>
+        </is>
+      </c>
+      <c r="D514" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E514" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F514" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G514" s="9" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="H514" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B515" s="9" t="inlineStr">
+        <is>
+          <t>s10_france</t>
+        </is>
+      </c>
+      <c r="C515" s="9" t="inlineStr">
+        <is>
+          <t>France / eurozone fragility</t>
+        </is>
+      </c>
+      <c r="D515" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E515" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F515" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G515" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H515" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B516" s="9" t="inlineStr">
+        <is>
+          <t>s11_consumer_debt</t>
+        </is>
+      </c>
+      <c r="C516" s="9" t="inlineStr">
+        <is>
+          <t>Hidden consumer debt</t>
+        </is>
+      </c>
+      <c r="D516" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E516" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F516" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G516" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H516" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B517" s="9" t="inlineStr">
+        <is>
+          <t>s12_gold_dedollar</t>
+        </is>
+      </c>
+      <c r="C517" s="9" t="inlineStr">
+        <is>
+          <t>Gold / de-dollarization</t>
+        </is>
+      </c>
+      <c r="D517" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E517" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F517" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G517" s="9" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="H517" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B518" s="9" t="inlineStr">
+        <is>
+          <t>s13_insurance</t>
+        </is>
+      </c>
+      <c r="C518" s="9" t="inlineStr">
+        <is>
+          <t>Insurance retreat</t>
+        </is>
+      </c>
+      <c r="D518" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E518" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F518" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G518" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H518" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B519" s="9" t="inlineStr">
+        <is>
+          <t>s14_pensions</t>
+        </is>
+      </c>
+      <c r="C519" s="9" t="inlineStr">
+        <is>
+          <t>Pensions / demographics</t>
+        </is>
+      </c>
+      <c r="D519" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E519" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F519" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G519" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H519" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B520" s="9" t="inlineStr">
+        <is>
+          <t>s15_ai_power</t>
+        </is>
+      </c>
+      <c r="C520" s="9" t="inlineStr">
+        <is>
+          <t>AI power &amp; the grid bottleneck</t>
+        </is>
+      </c>
+      <c r="D520" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E520" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F520" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G520" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H520" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B521" s="9" t="inlineStr">
+        <is>
+          <t>s16_copper</t>
+        </is>
+      </c>
+      <c r="C521" s="9" t="inlineStr">
+        <is>
+          <t>Copper &amp; the electrification deficit</t>
+        </is>
+      </c>
+      <c r="D521" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E521" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F521" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G521" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H521" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B522" s="9" t="inlineStr">
+        <is>
+          <t>s17_water</t>
+        </is>
+      </c>
+      <c r="C522" s="9" t="inlineStr">
+        <is>
+          <t>Water - the underpriced input</t>
+        </is>
+      </c>
+      <c r="D522" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E522" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F522" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G522" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H522" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B523" s="9" t="inlineStr">
+        <is>
+          <t>s18_food_fertilizer</t>
+        </is>
+      </c>
+      <c r="C523" s="9" t="inlineStr">
+        <is>
+          <t>Food &amp; fertilizer fragility</t>
+        </is>
+      </c>
+      <c r="D523" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E523" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F523" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G523" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H523" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B524" s="9" t="inlineStr">
+        <is>
+          <t>s19_lithography</t>
+        </is>
+      </c>
+      <c r="C524" s="9" t="inlineStr">
+        <is>
+          <t>The lithography (ASML) chokepoint</t>
+        </is>
+      </c>
+      <c r="D524" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E524" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F524" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G524" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H524" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B525" s="9" t="inlineStr">
+        <is>
+          <t>s20_sea_lanes</t>
+        </is>
+      </c>
+      <c r="C525" s="9" t="inlineStr">
+        <is>
+          <t>Sea lanes &amp; undersea cables</t>
+        </is>
+      </c>
+      <c r="D525" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E525" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F525" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G525" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H525" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B526" s="9" t="inlineStr">
+        <is>
+          <t>s21_clearinghouses</t>
+        </is>
+      </c>
+      <c r="C526" s="9" t="inlineStr">
+        <is>
+          <t>Clearinghouses (financial chokepoint)</t>
+        </is>
+      </c>
+      <c r="D526" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E526" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F526" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G526" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H526" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -25807,7 +26689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A26"/>
+  <dimension ref="A1:A28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -25888,7 +26770,7 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>--- Daily narrative (2026-07-13) ---</t>
+          <t>--- Daily narrative (2026-07-14) ---</t>
         </is>
       </c>
     </row>
@@ -25902,7 +26784,7 @@
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>Overall macro risk elevated at 7.6 with three stories shifting into or within High bands; China supply shocks and financial leverage remain dominant concerns.</t>
+          <t>Macro risk holds at elevated levels (7.6/10) with no intraday changes; structural leverage and supply-chain vulnerabilities remain the primary concern vectors.</t>
         </is>
       </c>
     </row>
@@ -25917,49 +26799,71 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="inlineStr"/>
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>No risk levels changed today.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>• **China's price spillover (6→7, High):** PPI swung to +4.1% YoY and anti-dumping actions escalated; risk is imported deflation or cost-push inflation spilling globally, constraining policy space.</t>
-        </is>
-      </c>
+      <c r="A19" s="12" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr"/>
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>**ELEVATED AND HIGH RISKS (Status quo)**</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>• **Food &amp; fertilizer fragility (6→7, High):** China tightened export curbs and Gulf/Hormuz disruption intensified; agricultural input scarcity threatens food price volatility and emerging-market vulnerability.</t>
+          <t>- Japan fiscal/JGB/carry trade (8/10, High): Persistent BoJ policy uncertainty and carry-trade unwind potential create sharp repricing risk for global equities and FX.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="inlineStr"/>
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>- Private credit's opaque expansion (8/10, High): Continued non-bank lending growth with limited transparency poses contagion risk to credit markets if liquidity dries.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>• **Gold / de-dollarization (4→3, Moderate):** USD reserve share stabilized at 57.1% and weaponization rhetoric remains at talk-stage only; risk ebbs slightly but structural shift remains monitored.</t>
+          <t>- Food &amp; fertilizer fragility (7/10, High): Supply concentration risk remains acute; geopolitical disruption could spike input costs globally.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="inlineStr"/>
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>- AI power &amp; the grid bottleneck (7/10, High): Demand surge outpaces infrastructure; brownouts or capex strain could constrain productivity gains.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
+          <t>- China's price spillover (7/10, High): Deflationary or cost-push transmission channels unresolved; policy miscalibration risk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
           <t>**TOP WATCH**</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="12" t="inlineStr">
-        <is>
-          <t>Japan fiscal/JGB/carry trade at level 8 (High) poses the highest unwind risk if rates or volatility spike unexpectedly.</t>
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>Japan fiscal/JGB/carry trade at 8/10—catalyst density highest for near-term volatility spillover into global markets.</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-07-14  -  generated 2026-07-14 12:51 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-07-15  -  generated 2026-07-15 12:56 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
         </is>
       </c>
       <c r="D2" s="7" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.02</v>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>161.811</v>
+        <v>162.221</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>3.922</v>
+        <v>3.787</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>6.7578</v>
+        <v>6.759</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>308.4</v>
+        <v>308.7</v>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>4093.2</v>
+        <v>4068.8999</v>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>6.397</v>
+        <v>6.3895</v>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="D60" s="7" t="n">
-        <v>80.63</v>
+        <v>79.64</v>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="D62" s="7" t="n">
-        <v>16.6</v>
+        <v>16.21</v>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H526"/>
+  <dimension ref="A1:H547"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -26678,6 +26678,888 @@
         </is>
       </c>
     </row>
+    <row r="527">
+      <c r="A527" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B527" s="9" t="inlineStr">
+        <is>
+          <t>s1_basis_trade</t>
+        </is>
+      </c>
+      <c r="C527" s="9" t="inlineStr">
+        <is>
+          <t>Treasury basis trade (hidden leverage)</t>
+        </is>
+      </c>
+      <c r="D527" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E527" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F527" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G527" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H527" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B528" s="9" t="inlineStr">
+        <is>
+          <t>s2_japan</t>
+        </is>
+      </c>
+      <c r="C528" s="9" t="inlineStr">
+        <is>
+          <t>Japan fiscal / JGB / carry trade</t>
+        </is>
+      </c>
+      <c r="D528" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E528" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F528" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G528" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H528" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B529" s="9" t="inlineStr">
+        <is>
+          <t>s3_private_credit</t>
+        </is>
+      </c>
+      <c r="C529" s="9" t="inlineStr">
+        <is>
+          <t>Private credit's opaque expansion</t>
+        </is>
+      </c>
+      <c r="D529" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E529" s="9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F529" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G529" s="9" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="H529" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B530" s="9" t="inlineStr">
+        <is>
+          <t>s4_dev_debt</t>
+        </is>
+      </c>
+      <c r="C530" s="9" t="inlineStr">
+        <is>
+          <t>Developing-world debt crisis</t>
+        </is>
+      </c>
+      <c r="D530" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E530" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F530" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G530" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H530" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B531" s="9" t="inlineStr">
+        <is>
+          <t>s5_china_deflation</t>
+        </is>
+      </c>
+      <c r="C531" s="9" t="inlineStr">
+        <is>
+          <t>China's price spillover (deflation or cost-push)</t>
+        </is>
+      </c>
+      <c r="D531" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E531" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F531" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G531" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H531" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B532" s="9" t="inlineStr">
+        <is>
+          <t>s6_rare_earths</t>
+        </is>
+      </c>
+      <c r="C532" s="9" t="inlineStr">
+        <is>
+          <t>Critical minerals as a weapon</t>
+        </is>
+      </c>
+      <c r="D532" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E532" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F532" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G532" s="9" t="inlineStr">
+        <is>
+          <t>6.75</t>
+        </is>
+      </c>
+      <c r="H532" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B533" s="9" t="inlineStr">
+        <is>
+          <t>s7_stablecoins</t>
+        </is>
+      </c>
+      <c r="C533" s="9" t="inlineStr">
+        <is>
+          <t>Stablecoins &amp; Treasury demand</t>
+        </is>
+      </c>
+      <c r="D533" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E533" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F533" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G533" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H533" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B534" s="9" t="inlineStr">
+        <is>
+          <t>s8_ai_capex</t>
+        </is>
+      </c>
+      <c r="C534" s="9" t="inlineStr">
+        <is>
+          <t>AI build-out circular financing</t>
+        </is>
+      </c>
+      <c r="D534" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E534" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F534" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G534" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H534" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B535" s="9" t="inlineStr">
+        <is>
+          <t>s9_cre</t>
+        </is>
+      </c>
+      <c r="C535" s="9" t="inlineStr">
+        <is>
+          <t>CRE maturity wall / regional banks</t>
+        </is>
+      </c>
+      <c r="D535" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E535" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F535" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G535" s="9" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="H535" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B536" s="9" t="inlineStr">
+        <is>
+          <t>s10_france</t>
+        </is>
+      </c>
+      <c r="C536" s="9" t="inlineStr">
+        <is>
+          <t>France / eurozone fragility</t>
+        </is>
+      </c>
+      <c r="D536" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E536" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F536" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G536" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H536" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B537" s="9" t="inlineStr">
+        <is>
+          <t>s11_consumer_debt</t>
+        </is>
+      </c>
+      <c r="C537" s="9" t="inlineStr">
+        <is>
+          <t>Hidden consumer debt</t>
+        </is>
+      </c>
+      <c r="D537" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E537" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F537" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G537" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H537" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B538" s="9" t="inlineStr">
+        <is>
+          <t>s12_gold_dedollar</t>
+        </is>
+      </c>
+      <c r="C538" s="9" t="inlineStr">
+        <is>
+          <t>Gold / de-dollarization</t>
+        </is>
+      </c>
+      <c r="D538" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E538" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F538" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G538" s="9" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="H538" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B539" s="9" t="inlineStr">
+        <is>
+          <t>s13_insurance</t>
+        </is>
+      </c>
+      <c r="C539" s="9" t="inlineStr">
+        <is>
+          <t>Insurance retreat</t>
+        </is>
+      </c>
+      <c r="D539" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E539" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F539" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G539" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H539" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B540" s="9" t="inlineStr">
+        <is>
+          <t>s14_pensions</t>
+        </is>
+      </c>
+      <c r="C540" s="9" t="inlineStr">
+        <is>
+          <t>Pensions / demographics</t>
+        </is>
+      </c>
+      <c r="D540" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E540" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F540" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G540" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H540" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B541" s="9" t="inlineStr">
+        <is>
+          <t>s15_ai_power</t>
+        </is>
+      </c>
+      <c r="C541" s="9" t="inlineStr">
+        <is>
+          <t>AI power &amp; the grid bottleneck</t>
+        </is>
+      </c>
+      <c r="D541" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E541" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F541" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G541" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H541" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B542" s="9" t="inlineStr">
+        <is>
+          <t>s16_copper</t>
+        </is>
+      </c>
+      <c r="C542" s="9" t="inlineStr">
+        <is>
+          <t>Copper &amp; the electrification deficit</t>
+        </is>
+      </c>
+      <c r="D542" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E542" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F542" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G542" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H542" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B543" s="9" t="inlineStr">
+        <is>
+          <t>s17_water</t>
+        </is>
+      </c>
+      <c r="C543" s="9" t="inlineStr">
+        <is>
+          <t>Water - the underpriced input</t>
+        </is>
+      </c>
+      <c r="D543" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E543" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F543" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G543" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H543" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B544" s="9" t="inlineStr">
+        <is>
+          <t>s18_food_fertilizer</t>
+        </is>
+      </c>
+      <c r="C544" s="9" t="inlineStr">
+        <is>
+          <t>Food &amp; fertilizer fragility</t>
+        </is>
+      </c>
+      <c r="D544" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E544" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F544" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G544" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H544" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B545" s="9" t="inlineStr">
+        <is>
+          <t>s19_lithography</t>
+        </is>
+      </c>
+      <c r="C545" s="9" t="inlineStr">
+        <is>
+          <t>The lithography (ASML) chokepoint</t>
+        </is>
+      </c>
+      <c r="D545" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E545" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F545" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G545" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H545" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B546" s="9" t="inlineStr">
+        <is>
+          <t>s20_sea_lanes</t>
+        </is>
+      </c>
+      <c r="C546" s="9" t="inlineStr">
+        <is>
+          <t>Sea lanes &amp; undersea cables</t>
+        </is>
+      </c>
+      <c r="D546" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E546" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F546" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G546" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="H546" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B547" s="9" t="inlineStr">
+        <is>
+          <t>s21_clearinghouses</t>
+        </is>
+      </c>
+      <c r="C547" s="9" t="inlineStr">
+        <is>
+          <t>Clearinghouses (financial chokepoint)</t>
+        </is>
+      </c>
+      <c r="D547" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E547" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F547" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G547" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H547" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -26689,7 +27571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A28"/>
+  <dimension ref="A1:A25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -26770,21 +27652,21 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>--- Daily narrative (2026-07-14) ---</t>
+          <t>--- Daily narrative (2026-07-15) ---</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>**HEADLINE**</t>
+          <t xml:space="preserve">**HEADLINE**  </t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>Macro risk holds at elevated levels (7.6/10) with no intraday changes; structural leverage and supply-chain vulnerabilities remain the primary concern vectors.</t>
+          <t>Macro risk rose to 7.5 overall, driven by Japan fiscal deterioration and persistent structural vulnerabilities across credit, supply chains, and geopolitics.</t>
         </is>
       </c>
     </row>
@@ -26799,71 +27681,46 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
-          <t>No risk levels changed today.</t>
-        </is>
-      </c>
+      <c r="A18" s="12" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr"/>
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>• **Japan fiscal / JGB / carry trade** (8→7, High): 30-year JGB yield jumped 50bp to 3.787% and Takaichi plan financing clarity deteriorated to "disorderly" status. Risk of forced deleveraging in yen carry positions and fiscal-monetary coordination failure remains elevated despite modest level decline.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
-          <t>**ELEVATED AND HIGH RISKS (Status quo)**</t>
-        </is>
-      </c>
+      <c r="A20" s="12" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>- Japan fiscal/JGB/carry trade (8/10, High): Persistent BoJ policy uncertainty and carry-trade unwind potential create sharp repricing risk for global equities and FX.</t>
+          <t xml:space="preserve">**ELEVATED &amp; HIGH-RISK STORIES** (no change today)  </t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>- Private credit's opaque expansion (8/10, High): Continued non-bank lending growth with limited transparency poses contagion risk to credit markets if liquidity dries.</t>
+          <t>Private credit opacity at 8 (High), China price spillover at 7 (High), AI power demand at 7 (High), Food/fertilizer fragility at 7 (High), Critical minerals weaponization at 7 (High), Treasury basis leverage at 6 (Elevated), Hidden consumer debt at 6 (Elevated).</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>- Food &amp; fertilizer fragility (7/10, High): Supply concentration risk remains acute; geopolitical disruption could spike input costs globally.</t>
-        </is>
-      </c>
+      <c r="A23" s="12" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>- AI power &amp; the grid bottleneck (7/10, High): Demand surge outpaces infrastructure; brownouts or capex strain could constrain productivity gains.</t>
+          <t xml:space="preserve">**TO WATCH**  </t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>- China's price spillover (7/10, High): Deflationary or cost-push transmission channels unresolved; policy miscalibration risk.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="12" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>**TOP WATCH**</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="12" t="inlineStr">
-        <is>
-          <t>Japan fiscal/JGB/carry trade at 8/10—catalyst density highest for near-term volatility spillover into global markets.</t>
+          <t>Private credit expansion (level 8) poses the highest tail risk given opacity and interconnection to traditional finance.</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-07-15  -  generated 2026-07-15 12:56 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-07-16  -  generated 2026-07-16 13:04 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
         </is>
       </c>
       <c r="D2" s="7" t="n">
-        <v>-0.02</v>
+        <v>0.01</v>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>162.221</v>
+        <v>162.291</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>3.787</v>
+        <v>3.802</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>2.69</v>
+        <v>2.72</v>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>6.759</v>
+        <v>6.7572</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>308.7</v>
+        <v>308.9</v>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>4068.8999</v>
+        <v>4000.8</v>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>6.3895</v>
+        <v>6.3585</v>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="D60" s="7" t="n">
-        <v>79.64</v>
+        <v>80.51000000000001</v>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="D62" s="7" t="n">
-        <v>16.21</v>
+        <v>16.34</v>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H547"/>
+  <dimension ref="A1:H568"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -27555,6 +27555,888 @@
         </is>
       </c>
       <c r="H547" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B548" s="9" t="inlineStr">
+        <is>
+          <t>s1_basis_trade</t>
+        </is>
+      </c>
+      <c r="C548" s="9" t="inlineStr">
+        <is>
+          <t>Treasury basis trade (hidden leverage)</t>
+        </is>
+      </c>
+      <c r="D548" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E548" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F548" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G548" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H548" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B549" s="9" t="inlineStr">
+        <is>
+          <t>s2_japan</t>
+        </is>
+      </c>
+      <c r="C549" s="9" t="inlineStr">
+        <is>
+          <t>Japan fiscal / JGB / carry trade</t>
+        </is>
+      </c>
+      <c r="D549" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E549" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F549" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G549" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H549" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B550" s="9" t="inlineStr">
+        <is>
+          <t>s3_private_credit</t>
+        </is>
+      </c>
+      <c r="C550" s="9" t="inlineStr">
+        <is>
+          <t>Private credit's opaque expansion</t>
+        </is>
+      </c>
+      <c r="D550" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E550" s="9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F550" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G550" s="9" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="H550" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B551" s="9" t="inlineStr">
+        <is>
+          <t>s4_dev_debt</t>
+        </is>
+      </c>
+      <c r="C551" s="9" t="inlineStr">
+        <is>
+          <t>Developing-world debt crisis</t>
+        </is>
+      </c>
+      <c r="D551" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E551" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F551" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G551" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H551" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B552" s="9" t="inlineStr">
+        <is>
+          <t>s5_china_deflation</t>
+        </is>
+      </c>
+      <c r="C552" s="9" t="inlineStr">
+        <is>
+          <t>China's price spillover (deflation or cost-push)</t>
+        </is>
+      </c>
+      <c r="D552" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E552" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F552" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G552" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H552" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B553" s="9" t="inlineStr">
+        <is>
+          <t>s6_rare_earths</t>
+        </is>
+      </c>
+      <c r="C553" s="9" t="inlineStr">
+        <is>
+          <t>Critical minerals as a weapon</t>
+        </is>
+      </c>
+      <c r="D553" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E553" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F553" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G553" s="9" t="inlineStr">
+        <is>
+          <t>6.75</t>
+        </is>
+      </c>
+      <c r="H553" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B554" s="9" t="inlineStr">
+        <is>
+          <t>s7_stablecoins</t>
+        </is>
+      </c>
+      <c r="C554" s="9" t="inlineStr">
+        <is>
+          <t>Stablecoins &amp; Treasury demand</t>
+        </is>
+      </c>
+      <c r="D554" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E554" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F554" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G554" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H554" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B555" s="9" t="inlineStr">
+        <is>
+          <t>s8_ai_capex</t>
+        </is>
+      </c>
+      <c r="C555" s="9" t="inlineStr">
+        <is>
+          <t>AI build-out circular financing</t>
+        </is>
+      </c>
+      <c r="D555" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E555" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F555" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G555" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H555" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B556" s="9" t="inlineStr">
+        <is>
+          <t>s9_cre</t>
+        </is>
+      </c>
+      <c r="C556" s="9" t="inlineStr">
+        <is>
+          <t>CRE maturity wall / regional banks</t>
+        </is>
+      </c>
+      <c r="D556" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E556" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F556" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G556" s="9" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="H556" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B557" s="9" t="inlineStr">
+        <is>
+          <t>s10_france</t>
+        </is>
+      </c>
+      <c r="C557" s="9" t="inlineStr">
+        <is>
+          <t>France / eurozone fragility</t>
+        </is>
+      </c>
+      <c r="D557" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E557" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F557" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G557" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H557" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B558" s="9" t="inlineStr">
+        <is>
+          <t>s11_consumer_debt</t>
+        </is>
+      </c>
+      <c r="C558" s="9" t="inlineStr">
+        <is>
+          <t>Hidden consumer debt</t>
+        </is>
+      </c>
+      <c r="D558" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E558" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F558" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G558" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H558" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B559" s="9" t="inlineStr">
+        <is>
+          <t>s12_gold_dedollar</t>
+        </is>
+      </c>
+      <c r="C559" s="9" t="inlineStr">
+        <is>
+          <t>Gold / de-dollarization</t>
+        </is>
+      </c>
+      <c r="D559" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E559" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F559" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G559" s="9" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="H559" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B560" s="9" t="inlineStr">
+        <is>
+          <t>s13_insurance</t>
+        </is>
+      </c>
+      <c r="C560" s="9" t="inlineStr">
+        <is>
+          <t>Insurance retreat</t>
+        </is>
+      </c>
+      <c r="D560" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E560" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F560" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G560" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H560" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B561" s="9" t="inlineStr">
+        <is>
+          <t>s14_pensions</t>
+        </is>
+      </c>
+      <c r="C561" s="9" t="inlineStr">
+        <is>
+          <t>Pensions / demographics</t>
+        </is>
+      </c>
+      <c r="D561" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E561" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F561" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G561" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H561" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B562" s="9" t="inlineStr">
+        <is>
+          <t>s15_ai_power</t>
+        </is>
+      </c>
+      <c r="C562" s="9" t="inlineStr">
+        <is>
+          <t>AI power &amp; the grid bottleneck</t>
+        </is>
+      </c>
+      <c r="D562" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E562" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F562" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G562" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H562" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B563" s="9" t="inlineStr">
+        <is>
+          <t>s16_copper</t>
+        </is>
+      </c>
+      <c r="C563" s="9" t="inlineStr">
+        <is>
+          <t>Copper &amp; the electrification deficit</t>
+        </is>
+      </c>
+      <c r="D563" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E563" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F563" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G563" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H563" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B564" s="9" t="inlineStr">
+        <is>
+          <t>s17_water</t>
+        </is>
+      </c>
+      <c r="C564" s="9" t="inlineStr">
+        <is>
+          <t>Water - the underpriced input</t>
+        </is>
+      </c>
+      <c r="D564" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E564" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F564" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G564" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H564" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B565" s="9" t="inlineStr">
+        <is>
+          <t>s18_food_fertilizer</t>
+        </is>
+      </c>
+      <c r="C565" s="9" t="inlineStr">
+        <is>
+          <t>Food &amp; fertilizer fragility</t>
+        </is>
+      </c>
+      <c r="D565" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E565" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F565" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G565" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H565" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B566" s="9" t="inlineStr">
+        <is>
+          <t>s19_lithography</t>
+        </is>
+      </c>
+      <c r="C566" s="9" t="inlineStr">
+        <is>
+          <t>The lithography (ASML) chokepoint</t>
+        </is>
+      </c>
+      <c r="D566" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E566" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F566" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G566" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H566" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B567" s="9" t="inlineStr">
+        <is>
+          <t>s20_sea_lanes</t>
+        </is>
+      </c>
+      <c r="C567" s="9" t="inlineStr">
+        <is>
+          <t>Sea lanes &amp; undersea cables</t>
+        </is>
+      </c>
+      <c r="D567" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E567" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F567" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G567" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H567" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B568" s="9" t="inlineStr">
+        <is>
+          <t>s21_clearinghouses</t>
+        </is>
+      </c>
+      <c r="C568" s="9" t="inlineStr">
+        <is>
+          <t>Clearinghouses (financial chokepoint)</t>
+        </is>
+      </c>
+      <c r="D568" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E568" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F568" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G568" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H568" s="9" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
@@ -27652,21 +28534,21 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>--- Daily narrative (2026-07-15) ---</t>
+          <t>--- Daily narrative (2026-07-16) ---</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">**HEADLINE**  </t>
+          <t>**HEADLINE:**</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>Macro risk rose to 7.5 overall, driven by Japan fiscal deterioration and persistent structural vulnerabilities across credit, supply chains, and geopolitics.</t>
+          <t>Macro risk remains elevated at 7.5 overall, driven by structural financial vulnerabilities and supply-chain weaponization with no intraday level changes.</t>
         </is>
       </c>
     </row>
@@ -27676,34 +28558,38 @@
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>**STORIES WITH LEVEL CHANGES**</t>
+          <t>**STORIES WITH LEVEL CHANGES:**</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="inlineStr"/>
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>None—all elevated and high-risk positions held steady.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>• **Japan fiscal / JGB / carry trade** (8→7, High): 30-year JGB yield jumped 50bp to 3.787% and Takaichi plan financing clarity deteriorated to "disorderly" status. Risk of forced deleveraging in yen carry positions and fiscal-monetary coordination failure remains elevated despite modest level decline.</t>
-        </is>
-      </c>
+      <c r="A19" s="12" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr"/>
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>**ELEVATED OR HIGHER STORIES (15 active):**</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">**ELEVATED &amp; HIGH-RISK STORIES** (no change today)  </t>
+          <t>- **High band (7–8):** Private credit opacity (8), Japan carry trade (7), China deflation spillover (7), critical minerals weaponization (7), AI power grid bottleneck (7), food &amp; fertilizer fragility (7)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>Private credit opacity at 8 (High), China price spillover at 7 (High), AI power demand at 7 (High), Food/fertilizer fragility at 7 (High), Critical minerals weaponization at 7 (High), Treasury basis leverage at 6 (Elevated), Hidden consumer debt at 6 (Elevated).</t>
+          <t>- **Elevated band (5–6):** Treasury basis leverage, developing-world debt, AI circular financing, CRE maturity wall, France/eurozone fragility, hidden consumer debt, ASML lithography chokepoint, sea lanes &amp; undersea cables, water underpricing</t>
         </is>
       </c>
     </row>
@@ -27713,14 +28599,14 @@
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">**TO WATCH**  </t>
+          <t>**TOP WATCH:**</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>Private credit expansion (level 8) poses the highest tail risk given opacity and interconnection to traditional finance.</t>
+          <t>Private credit's opaque expansion at level 8—least transparent segment of non-bank finance with highest flagged risk of systemic spillover.</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-07-16  -  generated 2026-07-16 13:04 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-07-17  -  generated 2026-07-17 12:45 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>162.291</v>
+        <v>162.396</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>3.802</v>
+        <v>3.862</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>6.7572</v>
+        <v>6.777</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>308.9</v>
+        <v>309.3</v>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
@@ -3082,7 +3082,7 @@
         </is>
       </c>
       <c r="D29" s="7" t="n">
-        <v>0.6951000000000001</v>
+        <v>0.71</v>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>4000.8</v>
+        <v>3984.8999</v>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>6.3585</v>
+        <v>6.2105</v>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="D60" s="7" t="n">
-        <v>80.51000000000001</v>
+        <v>80.36</v>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="D62" s="7" t="n">
-        <v>16.34</v>
+        <v>18.45</v>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H568"/>
+  <dimension ref="A1:H589"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -28442,6 +28442,888 @@
         </is>
       </c>
     </row>
+    <row r="569">
+      <c r="A569" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B569" s="9" t="inlineStr">
+        <is>
+          <t>s1_basis_trade</t>
+        </is>
+      </c>
+      <c r="C569" s="9" t="inlineStr">
+        <is>
+          <t>Treasury basis trade (hidden leverage)</t>
+        </is>
+      </c>
+      <c r="D569" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E569" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F569" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G569" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H569" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B570" s="9" t="inlineStr">
+        <is>
+          <t>s2_japan</t>
+        </is>
+      </c>
+      <c r="C570" s="9" t="inlineStr">
+        <is>
+          <t>Japan fiscal / JGB / carry trade</t>
+        </is>
+      </c>
+      <c r="D570" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E570" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F570" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G570" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H570" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B571" s="9" t="inlineStr">
+        <is>
+          <t>s3_private_credit</t>
+        </is>
+      </c>
+      <c r="C571" s="9" t="inlineStr">
+        <is>
+          <t>Private credit's opaque expansion</t>
+        </is>
+      </c>
+      <c r="D571" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E571" s="9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F571" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G571" s="9" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="H571" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B572" s="9" t="inlineStr">
+        <is>
+          <t>s4_dev_debt</t>
+        </is>
+      </c>
+      <c r="C572" s="9" t="inlineStr">
+        <is>
+          <t>Developing-world debt crisis</t>
+        </is>
+      </c>
+      <c r="D572" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E572" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F572" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G572" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H572" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B573" s="9" t="inlineStr">
+        <is>
+          <t>s5_china_deflation</t>
+        </is>
+      </c>
+      <c r="C573" s="9" t="inlineStr">
+        <is>
+          <t>China's price spillover (deflation or cost-push)</t>
+        </is>
+      </c>
+      <c r="D573" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E573" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F573" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G573" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H573" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B574" s="9" t="inlineStr">
+        <is>
+          <t>s6_rare_earths</t>
+        </is>
+      </c>
+      <c r="C574" s="9" t="inlineStr">
+        <is>
+          <t>Critical minerals as a weapon</t>
+        </is>
+      </c>
+      <c r="D574" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E574" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F574" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G574" s="9" t="inlineStr">
+        <is>
+          <t>6.75</t>
+        </is>
+      </c>
+      <c r="H574" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B575" s="9" t="inlineStr">
+        <is>
+          <t>s7_stablecoins</t>
+        </is>
+      </c>
+      <c r="C575" s="9" t="inlineStr">
+        <is>
+          <t>Stablecoins &amp; Treasury demand</t>
+        </is>
+      </c>
+      <c r="D575" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E575" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F575" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G575" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H575" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B576" s="9" t="inlineStr">
+        <is>
+          <t>s8_ai_capex</t>
+        </is>
+      </c>
+      <c r="C576" s="9" t="inlineStr">
+        <is>
+          <t>AI build-out circular financing</t>
+        </is>
+      </c>
+      <c r="D576" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E576" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F576" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G576" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H576" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B577" s="9" t="inlineStr">
+        <is>
+          <t>s9_cre</t>
+        </is>
+      </c>
+      <c r="C577" s="9" t="inlineStr">
+        <is>
+          <t>CRE maturity wall / regional banks</t>
+        </is>
+      </c>
+      <c r="D577" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E577" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F577" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G577" s="9" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="H577" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B578" s="9" t="inlineStr">
+        <is>
+          <t>s10_france</t>
+        </is>
+      </c>
+      <c r="C578" s="9" t="inlineStr">
+        <is>
+          <t>France / eurozone fragility</t>
+        </is>
+      </c>
+      <c r="D578" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E578" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F578" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G578" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H578" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B579" s="9" t="inlineStr">
+        <is>
+          <t>s11_consumer_debt</t>
+        </is>
+      </c>
+      <c r="C579" s="9" t="inlineStr">
+        <is>
+          <t>Hidden consumer debt</t>
+        </is>
+      </c>
+      <c r="D579" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E579" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F579" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G579" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H579" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B580" s="9" t="inlineStr">
+        <is>
+          <t>s12_gold_dedollar</t>
+        </is>
+      </c>
+      <c r="C580" s="9" t="inlineStr">
+        <is>
+          <t>Gold / de-dollarization</t>
+        </is>
+      </c>
+      <c r="D580" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E580" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F580" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G580" s="9" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="H580" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B581" s="9" t="inlineStr">
+        <is>
+          <t>s13_insurance</t>
+        </is>
+      </c>
+      <c r="C581" s="9" t="inlineStr">
+        <is>
+          <t>Insurance retreat</t>
+        </is>
+      </c>
+      <c r="D581" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E581" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F581" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G581" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H581" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B582" s="9" t="inlineStr">
+        <is>
+          <t>s14_pensions</t>
+        </is>
+      </c>
+      <c r="C582" s="9" t="inlineStr">
+        <is>
+          <t>Pensions / demographics</t>
+        </is>
+      </c>
+      <c r="D582" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E582" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F582" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G582" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H582" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B583" s="9" t="inlineStr">
+        <is>
+          <t>s15_ai_power</t>
+        </is>
+      </c>
+      <c r="C583" s="9" t="inlineStr">
+        <is>
+          <t>AI power &amp; the grid bottleneck</t>
+        </is>
+      </c>
+      <c r="D583" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E583" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F583" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G583" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H583" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B584" s="9" t="inlineStr">
+        <is>
+          <t>s16_copper</t>
+        </is>
+      </c>
+      <c r="C584" s="9" t="inlineStr">
+        <is>
+          <t>Copper &amp; the electrification deficit</t>
+        </is>
+      </c>
+      <c r="D584" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E584" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F584" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G584" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H584" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B585" s="9" t="inlineStr">
+        <is>
+          <t>s17_water</t>
+        </is>
+      </c>
+      <c r="C585" s="9" t="inlineStr">
+        <is>
+          <t>Water - the underpriced input</t>
+        </is>
+      </c>
+      <c r="D585" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E585" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F585" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G585" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H585" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B586" s="9" t="inlineStr">
+        <is>
+          <t>s18_food_fertilizer</t>
+        </is>
+      </c>
+      <c r="C586" s="9" t="inlineStr">
+        <is>
+          <t>Food &amp; fertilizer fragility</t>
+        </is>
+      </c>
+      <c r="D586" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E586" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F586" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G586" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H586" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B587" s="9" t="inlineStr">
+        <is>
+          <t>s19_lithography</t>
+        </is>
+      </c>
+      <c r="C587" s="9" t="inlineStr">
+        <is>
+          <t>The lithography (ASML) chokepoint</t>
+        </is>
+      </c>
+      <c r="D587" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E587" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F587" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G587" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H587" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B588" s="9" t="inlineStr">
+        <is>
+          <t>s20_sea_lanes</t>
+        </is>
+      </c>
+      <c r="C588" s="9" t="inlineStr">
+        <is>
+          <t>Sea lanes &amp; undersea cables</t>
+        </is>
+      </c>
+      <c r="D588" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E588" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F588" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G588" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H588" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B589" s="9" t="inlineStr">
+        <is>
+          <t>s21_clearinghouses</t>
+        </is>
+      </c>
+      <c r="C589" s="9" t="inlineStr">
+        <is>
+          <t>Clearinghouses (financial chokepoint)</t>
+        </is>
+      </c>
+      <c r="D589" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E589" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F589" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G589" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H589" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -28453,7 +29335,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A25"/>
+  <dimension ref="A1:A31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -28534,21 +29416,21 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>--- Daily narrative (2026-07-16) ---</t>
+          <t>--- Daily narrative (2026-07-17) ---</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>**HEADLINE:**</t>
+          <t>**HEADLINE**</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>Macro risk remains elevated at 7.5 overall, driven by structural financial vulnerabilities and supply-chain weaponization with no intraday level changes.</t>
+          <t>Overall macro risk at 7.5/10 with no intraday changes; four stories at High (8.0) or near it dominate tail risk.</t>
         </is>
       </c>
     </row>
@@ -28558,14 +29440,14 @@
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>**STORIES WITH LEVEL CHANGES:**</t>
+          <t>**KEY STORIES**</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>None—all elevated and high-risk positions held steady.</t>
+          <t>No risk-level changes recorded today. Current elevated and high-risk exposures include:</t>
         </is>
       </c>
     </row>
@@ -28575,21 +29457,17 @@
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>**ELEVATED OR HIGHER STORIES (15 active):**</t>
+          <t>• **Private credit's opaque expansion** (Level 8, High) – largest single risk; opacity in underwriting and leverage could trigger sudden repricing.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>- **High band (7–8):** Private credit opacity (8), Japan carry trade (7), China deflation spillover (7), critical minerals weaponization (7), AI power grid bottleneck (7), food &amp; fertilizer fragility (7)</t>
-        </is>
-      </c>
+      <c r="A21" s="12" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>- **Elevated band (5–6):** Treasury basis leverage, developing-world debt, AI circular financing, CRE maturity wall, France/eurozone fragility, hidden consumer debt, ASML lithography chokepoint, sea lanes &amp; undersea cables, water underpricing</t>
+          <t>• **Japan fiscal/JGB/carry trade** (Level 7, High) – sustained funding stress and yen volatility create cross-border liquidity contagion risk.</t>
         </is>
       </c>
     </row>
@@ -28599,14 +29477,44 @@
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>**TOP WATCH:**</t>
+          <t>• **China's price spillover** (Level 7, High) – deflationary exports or cost-push inflation pressure global monetary policy transmission.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>Private credit's opaque expansion at level 8—least transparent segment of non-bank finance with highest flagged risk of systemic spillover.</t>
+      <c r="A25" s="12" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>• **Food &amp; fertilizer fragility** (Level 7, High) – supply shocks remain vulnerable to geopolitical disruption.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>• **AI power &amp; grid bottleneck** (Level 7, High) – infrastructure capacity lag threatens acceleration timeline and sector valuations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>**WATCH CLOSEST**</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>Private credit opacity (8.0) poses the highest unquantified leverage risk to financial stability if redemption pressure emerges.</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-07-17  -  generated 2026-07-17 12:45 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-07-20  -  generated 2026-07-20 13:34 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
         </is>
       </c>
       <c r="D2" s="7" t="n">
-        <v>0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="D3" s="7" t="n">
-        <v>69.55</v>
+        <v>70.88</v>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>162.396</v>
+        <v>162.412</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>6.777</v>
+        <v>6.756</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>309.3</v>
+        <v>309.4</v>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.79</v>
+        <v>0.78</v>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>3984.8999</v>
+        <v>4011.8999</v>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>6.2105</v>
+        <v>6.3275</v>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         </is>
       </c>
       <c r="D55" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         </is>
       </c>
       <c r="D59" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="D60" s="7" t="n">
-        <v>80.36</v>
+        <v>81.67</v>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="D62" s="7" t="n">
-        <v>18.45</v>
+        <v>18.11</v>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
         </is>
       </c>
       <c r="D63" s="7" t="n">
-        <v>69.55</v>
+        <v>70.88</v>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H589"/>
+  <dimension ref="A1:H610"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -29324,6 +29324,888 @@
         </is>
       </c>
     </row>
+    <row r="590">
+      <c r="A590" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B590" s="9" t="inlineStr">
+        <is>
+          <t>s1_basis_trade</t>
+        </is>
+      </c>
+      <c r="C590" s="9" t="inlineStr">
+        <is>
+          <t>Treasury basis trade (hidden leverage)</t>
+        </is>
+      </c>
+      <c r="D590" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E590" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F590" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G590" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H590" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B591" s="9" t="inlineStr">
+        <is>
+          <t>s2_japan</t>
+        </is>
+      </c>
+      <c r="C591" s="9" t="inlineStr">
+        <is>
+          <t>Japan fiscal / JGB / carry trade</t>
+        </is>
+      </c>
+      <c r="D591" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E591" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F591" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G591" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H591" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B592" s="9" t="inlineStr">
+        <is>
+          <t>s3_private_credit</t>
+        </is>
+      </c>
+      <c r="C592" s="9" t="inlineStr">
+        <is>
+          <t>Private credit's opaque expansion</t>
+        </is>
+      </c>
+      <c r="D592" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E592" s="9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F592" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G592" s="9" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="H592" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B593" s="9" t="inlineStr">
+        <is>
+          <t>s4_dev_debt</t>
+        </is>
+      </c>
+      <c r="C593" s="9" t="inlineStr">
+        <is>
+          <t>Developing-world debt crisis</t>
+        </is>
+      </c>
+      <c r="D593" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E593" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F593" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G593" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H593" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B594" s="9" t="inlineStr">
+        <is>
+          <t>s5_china_deflation</t>
+        </is>
+      </c>
+      <c r="C594" s="9" t="inlineStr">
+        <is>
+          <t>China's price spillover (deflation or cost-push)</t>
+        </is>
+      </c>
+      <c r="D594" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E594" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F594" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G594" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H594" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B595" s="9" t="inlineStr">
+        <is>
+          <t>s6_rare_earths</t>
+        </is>
+      </c>
+      <c r="C595" s="9" t="inlineStr">
+        <is>
+          <t>Critical minerals as a weapon</t>
+        </is>
+      </c>
+      <c r="D595" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E595" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F595" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G595" s="9" t="inlineStr">
+        <is>
+          <t>6.75</t>
+        </is>
+      </c>
+      <c r="H595" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B596" s="9" t="inlineStr">
+        <is>
+          <t>s7_stablecoins</t>
+        </is>
+      </c>
+      <c r="C596" s="9" t="inlineStr">
+        <is>
+          <t>Stablecoins &amp; Treasury demand</t>
+        </is>
+      </c>
+      <c r="D596" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E596" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F596" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G596" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H596" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B597" s="9" t="inlineStr">
+        <is>
+          <t>s8_ai_capex</t>
+        </is>
+      </c>
+      <c r="C597" s="9" t="inlineStr">
+        <is>
+          <t>AI build-out circular financing</t>
+        </is>
+      </c>
+      <c r="D597" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E597" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F597" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G597" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H597" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B598" s="9" t="inlineStr">
+        <is>
+          <t>s9_cre</t>
+        </is>
+      </c>
+      <c r="C598" s="9" t="inlineStr">
+        <is>
+          <t>CRE maturity wall / regional banks</t>
+        </is>
+      </c>
+      <c r="D598" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E598" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F598" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G598" s="9" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="H598" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B599" s="9" t="inlineStr">
+        <is>
+          <t>s10_france</t>
+        </is>
+      </c>
+      <c r="C599" s="9" t="inlineStr">
+        <is>
+          <t>France / eurozone fragility</t>
+        </is>
+      </c>
+      <c r="D599" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E599" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F599" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G599" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H599" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B600" s="9" t="inlineStr">
+        <is>
+          <t>s11_consumer_debt</t>
+        </is>
+      </c>
+      <c r="C600" s="9" t="inlineStr">
+        <is>
+          <t>Hidden consumer debt</t>
+        </is>
+      </c>
+      <c r="D600" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E600" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F600" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G600" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H600" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B601" s="9" t="inlineStr">
+        <is>
+          <t>s12_gold_dedollar</t>
+        </is>
+      </c>
+      <c r="C601" s="9" t="inlineStr">
+        <is>
+          <t>Gold / de-dollarization</t>
+        </is>
+      </c>
+      <c r="D601" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E601" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F601" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G601" s="9" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="H601" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B602" s="9" t="inlineStr">
+        <is>
+          <t>s13_insurance</t>
+        </is>
+      </c>
+      <c r="C602" s="9" t="inlineStr">
+        <is>
+          <t>Insurance retreat</t>
+        </is>
+      </c>
+      <c r="D602" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E602" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F602" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G602" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H602" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B603" s="9" t="inlineStr">
+        <is>
+          <t>s14_pensions</t>
+        </is>
+      </c>
+      <c r="C603" s="9" t="inlineStr">
+        <is>
+          <t>Pensions / demographics</t>
+        </is>
+      </c>
+      <c r="D603" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E603" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F603" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G603" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H603" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B604" s="9" t="inlineStr">
+        <is>
+          <t>s15_ai_power</t>
+        </is>
+      </c>
+      <c r="C604" s="9" t="inlineStr">
+        <is>
+          <t>AI power &amp; the grid bottleneck</t>
+        </is>
+      </c>
+      <c r="D604" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E604" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F604" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G604" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H604" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B605" s="9" t="inlineStr">
+        <is>
+          <t>s16_copper</t>
+        </is>
+      </c>
+      <c r="C605" s="9" t="inlineStr">
+        <is>
+          <t>Copper &amp; the electrification deficit</t>
+        </is>
+      </c>
+      <c r="D605" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E605" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F605" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G605" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H605" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B606" s="9" t="inlineStr">
+        <is>
+          <t>s17_water</t>
+        </is>
+      </c>
+      <c r="C606" s="9" t="inlineStr">
+        <is>
+          <t>Water - the underpriced input</t>
+        </is>
+      </c>
+      <c r="D606" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E606" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F606" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G606" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H606" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B607" s="9" t="inlineStr">
+        <is>
+          <t>s18_food_fertilizer</t>
+        </is>
+      </c>
+      <c r="C607" s="9" t="inlineStr">
+        <is>
+          <t>Food &amp; fertilizer fragility</t>
+        </is>
+      </c>
+      <c r="D607" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E607" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F607" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G607" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H607" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B608" s="9" t="inlineStr">
+        <is>
+          <t>s19_lithography</t>
+        </is>
+      </c>
+      <c r="C608" s="9" t="inlineStr">
+        <is>
+          <t>The lithography (ASML) chokepoint</t>
+        </is>
+      </c>
+      <c r="D608" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E608" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F608" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G608" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H608" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B609" s="9" t="inlineStr">
+        <is>
+          <t>s20_sea_lanes</t>
+        </is>
+      </c>
+      <c r="C609" s="9" t="inlineStr">
+        <is>
+          <t>Sea lanes &amp; undersea cables</t>
+        </is>
+      </c>
+      <c r="D609" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E609" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F609" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G609" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H609" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B610" s="9" t="inlineStr">
+        <is>
+          <t>s21_clearinghouses</t>
+        </is>
+      </c>
+      <c r="C610" s="9" t="inlineStr">
+        <is>
+          <t>Clearinghouses (financial chokepoint)</t>
+        </is>
+      </c>
+      <c r="D610" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E610" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F610" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G610" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H610" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -29335,7 +30217,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A31"/>
+  <dimension ref="A1:A28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -29416,7 +30298,7 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>--- Daily narrative (2026-07-17) ---</t>
+          <t>--- Daily narrative (2026-07-20) ---</t>
         </is>
       </c>
     </row>
@@ -29430,7 +30312,7 @@
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>Overall macro risk at 7.5/10 with no intraday changes; four stories at High (8.0) or near it dominate tail risk.</t>
+          <t>Overall macro risk rose to 7.1 as sea-lane vulnerabilities escalated, offsetting declines in Japan carry-trade and emerging-market debt pressures.</t>
         </is>
       </c>
     </row>
@@ -29440,81 +30322,64 @@
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>**KEY STORIES**</t>
+          <t>**CHANGED STORIES**</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
-          <t>No risk-level changes recorded today. Current elevated and high-risk exposures include:</t>
-        </is>
-      </c>
+      <c r="A18" s="12" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr"/>
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>• **Sea lanes &amp; undersea cables** (6→7, High): Escalated on unspecified geopolitical or infrastructure trigger; elevates supply-chain disruption risk for critical trade and digital connectivity.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
-          <t>• **Private credit's opaque expansion** (Level 8, High) – largest single risk; opacity in underwriting and leverage could trigger sudden repricing.</t>
-        </is>
-      </c>
+      <c r="A20" s="12" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr"/>
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>• **Japan fiscal/JGB/carry trade** (7→6, Elevated): 30-year JGB yield rose 50bp to 3.86%, reducing yen funding cost advantage and easing near-term unwind pressure on leveraged positions.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t>• **Japan fiscal/JGB/carry trade** (Level 7, High) – sustained funding stress and yen volatility create cross-border liquidity contagion risk.</t>
-        </is>
-      </c>
+      <c r="A22" s="12" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="inlineStr"/>
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>• **Developing-world debt crisis** (6→5, Elevated): US real 10y yield at 2.35% and zero new IMF programs/missed coupons signal reduced refinancing stress, though backdrop remains fragile.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="inlineStr">
-        <is>
-          <t>• **China's price spillover** (Level 7, High) – deflationary exports or cost-push inflation pressure global monetary policy transmission.</t>
-        </is>
-      </c>
+      <c r="A24" s="12" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="inlineStr"/>
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>• **Food &amp; fertilizer fragility** (7→6, Elevated): China's tightened fertilizer export curbs persist; risk downgrade reflects data lag rather than policy reversal.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="12" t="inlineStr">
-        <is>
-          <t>• **Food &amp; fertilizer fragility** (Level 7, High) – supply shocks remain vulnerable to geopolitical disruption.</t>
-        </is>
-      </c>
+      <c r="A26" s="12" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="12" t="inlineStr"/>
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>**TOP WATCH**</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>• **AI power &amp; grid bottleneck** (Level 7, High) – infrastructure capacity lag threatens acceleration timeline and sector valuations.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="12" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="12" t="inlineStr">
-        <is>
-          <t>**WATCH CLOSEST**</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="12" t="inlineStr">
-        <is>
-          <t>Private credit opacity (8.0) poses the highest unquantified leverage risk to financial stability if redemption pressure emerges.</t>
+          <t>Private credit's opaque expansion (8, High) remains the highest-risk outlier; no driver data suggests structural opacity in leverage is unmonitored.</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-07-20  -  generated 2026-07-20 13:34 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-07-21  -  generated 2026-07-21 13:02 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
         </is>
       </c>
       <c r="D2" s="7" t="n">
-        <v>-0.04</v>
+        <v>-0.06</v>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>162.412</v>
+        <v>162.74</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>3.862</v>
+        <v>3.894</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>120.5046</v>
+        <v>120.5315</v>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>2.35</v>
+        <v>2.31</v>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>6.756</v>
+        <v>6.754</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>309.4</v>
+        <v>308.3</v>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>4011.8999</v>
+        <v>4060.6001</v>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>6.3275</v>
+        <v>6.5265</v>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="D60" s="7" t="n">
-        <v>81.67</v>
+        <v>84.16</v>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="D62" s="7" t="n">
-        <v>18.11</v>
+        <v>17.89</v>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H610"/>
+  <dimension ref="A1:H631"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -30201,6 +30201,888 @@
         </is>
       </c>
       <c r="H610" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B611" s="9" t="inlineStr">
+        <is>
+          <t>s1_basis_trade</t>
+        </is>
+      </c>
+      <c r="C611" s="9" t="inlineStr">
+        <is>
+          <t>Treasury basis trade (hidden leverage)</t>
+        </is>
+      </c>
+      <c r="D611" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E611" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F611" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G611" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H611" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B612" s="9" t="inlineStr">
+        <is>
+          <t>s2_japan</t>
+        </is>
+      </c>
+      <c r="C612" s="9" t="inlineStr">
+        <is>
+          <t>Japan fiscal / JGB / carry trade</t>
+        </is>
+      </c>
+      <c r="D612" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E612" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F612" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G612" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H612" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B613" s="9" t="inlineStr">
+        <is>
+          <t>s3_private_credit</t>
+        </is>
+      </c>
+      <c r="C613" s="9" t="inlineStr">
+        <is>
+          <t>Private credit's opaque expansion</t>
+        </is>
+      </c>
+      <c r="D613" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E613" s="9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F613" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G613" s="9" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="H613" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B614" s="9" t="inlineStr">
+        <is>
+          <t>s4_dev_debt</t>
+        </is>
+      </c>
+      <c r="C614" s="9" t="inlineStr">
+        <is>
+          <t>Developing-world debt crisis</t>
+        </is>
+      </c>
+      <c r="D614" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E614" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F614" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G614" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H614" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B615" s="9" t="inlineStr">
+        <is>
+          <t>s5_china_deflation</t>
+        </is>
+      </c>
+      <c r="C615" s="9" t="inlineStr">
+        <is>
+          <t>China's price spillover (deflation or cost-push)</t>
+        </is>
+      </c>
+      <c r="D615" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E615" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F615" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G615" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H615" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B616" s="9" t="inlineStr">
+        <is>
+          <t>s6_rare_earths</t>
+        </is>
+      </c>
+      <c r="C616" s="9" t="inlineStr">
+        <is>
+          <t>Critical minerals as a weapon</t>
+        </is>
+      </c>
+      <c r="D616" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E616" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F616" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G616" s="9" t="inlineStr">
+        <is>
+          <t>6.75</t>
+        </is>
+      </c>
+      <c r="H616" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B617" s="9" t="inlineStr">
+        <is>
+          <t>s7_stablecoins</t>
+        </is>
+      </c>
+      <c r="C617" s="9" t="inlineStr">
+        <is>
+          <t>Stablecoins &amp; Treasury demand</t>
+        </is>
+      </c>
+      <c r="D617" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E617" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F617" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G617" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H617" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B618" s="9" t="inlineStr">
+        <is>
+          <t>s8_ai_capex</t>
+        </is>
+      </c>
+      <c r="C618" s="9" t="inlineStr">
+        <is>
+          <t>AI build-out circular financing</t>
+        </is>
+      </c>
+      <c r="D618" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E618" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F618" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G618" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H618" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B619" s="9" t="inlineStr">
+        <is>
+          <t>s9_cre</t>
+        </is>
+      </c>
+      <c r="C619" s="9" t="inlineStr">
+        <is>
+          <t>CRE maturity wall / regional banks</t>
+        </is>
+      </c>
+      <c r="D619" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E619" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F619" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G619" s="9" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="H619" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B620" s="9" t="inlineStr">
+        <is>
+          <t>s10_france</t>
+        </is>
+      </c>
+      <c r="C620" s="9" t="inlineStr">
+        <is>
+          <t>France / eurozone fragility</t>
+        </is>
+      </c>
+      <c r="D620" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E620" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F620" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G620" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H620" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B621" s="9" t="inlineStr">
+        <is>
+          <t>s11_consumer_debt</t>
+        </is>
+      </c>
+      <c r="C621" s="9" t="inlineStr">
+        <is>
+          <t>Hidden consumer debt</t>
+        </is>
+      </c>
+      <c r="D621" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E621" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F621" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G621" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H621" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B622" s="9" t="inlineStr">
+        <is>
+          <t>s12_gold_dedollar</t>
+        </is>
+      </c>
+      <c r="C622" s="9" t="inlineStr">
+        <is>
+          <t>Gold / de-dollarization</t>
+        </is>
+      </c>
+      <c r="D622" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E622" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F622" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G622" s="9" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="H622" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B623" s="9" t="inlineStr">
+        <is>
+          <t>s13_insurance</t>
+        </is>
+      </c>
+      <c r="C623" s="9" t="inlineStr">
+        <is>
+          <t>Insurance retreat</t>
+        </is>
+      </c>
+      <c r="D623" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E623" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F623" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G623" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H623" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B624" s="9" t="inlineStr">
+        <is>
+          <t>s14_pensions</t>
+        </is>
+      </c>
+      <c r="C624" s="9" t="inlineStr">
+        <is>
+          <t>Pensions / demographics</t>
+        </is>
+      </c>
+      <c r="D624" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E624" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F624" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G624" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H624" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B625" s="9" t="inlineStr">
+        <is>
+          <t>s15_ai_power</t>
+        </is>
+      </c>
+      <c r="C625" s="9" t="inlineStr">
+        <is>
+          <t>AI power &amp; the grid bottleneck</t>
+        </is>
+      </c>
+      <c r="D625" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E625" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F625" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G625" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H625" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B626" s="9" t="inlineStr">
+        <is>
+          <t>s16_copper</t>
+        </is>
+      </c>
+      <c r="C626" s="9" t="inlineStr">
+        <is>
+          <t>Copper &amp; the electrification deficit</t>
+        </is>
+      </c>
+      <c r="D626" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E626" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F626" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G626" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H626" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B627" s="9" t="inlineStr">
+        <is>
+          <t>s17_water</t>
+        </is>
+      </c>
+      <c r="C627" s="9" t="inlineStr">
+        <is>
+          <t>Water - the underpriced input</t>
+        </is>
+      </c>
+      <c r="D627" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E627" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F627" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G627" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H627" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B628" s="9" t="inlineStr">
+        <is>
+          <t>s18_food_fertilizer</t>
+        </is>
+      </c>
+      <c r="C628" s="9" t="inlineStr">
+        <is>
+          <t>Food &amp; fertilizer fragility</t>
+        </is>
+      </c>
+      <c r="D628" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E628" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F628" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G628" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H628" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B629" s="9" t="inlineStr">
+        <is>
+          <t>s19_lithography</t>
+        </is>
+      </c>
+      <c r="C629" s="9" t="inlineStr">
+        <is>
+          <t>The lithography (ASML) chokepoint</t>
+        </is>
+      </c>
+      <c r="D629" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E629" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F629" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G629" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H629" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B630" s="9" t="inlineStr">
+        <is>
+          <t>s20_sea_lanes</t>
+        </is>
+      </c>
+      <c r="C630" s="9" t="inlineStr">
+        <is>
+          <t>Sea lanes &amp; undersea cables</t>
+        </is>
+      </c>
+      <c r="D630" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E630" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F630" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G630" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H630" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B631" s="9" t="inlineStr">
+        <is>
+          <t>s21_clearinghouses</t>
+        </is>
+      </c>
+      <c r="C631" s="9" t="inlineStr">
+        <is>
+          <t>Clearinghouses (financial chokepoint)</t>
+        </is>
+      </c>
+      <c r="D631" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E631" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F631" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G631" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H631" s="9" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
@@ -30298,7 +31180,7 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>--- Daily narrative (2026-07-20) ---</t>
+          <t>--- Daily narrative (2026-07-21) ---</t>
         </is>
       </c>
     </row>
@@ -30312,7 +31194,7 @@
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>Overall macro risk rose to 7.1 as sea-lane vulnerabilities escalated, offsetting declines in Japan carry-trade and emerging-market debt pressures.</t>
+          <t>Macro risk remains elevated at 7.1 overall, with structural vulnerabilities concentrated in financial leverage, commodity spillovers, and critical infrastructure chokepoints.</t>
         </is>
       </c>
     </row>
@@ -30322,47 +31204,59 @@
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>**CHANGED STORIES**</t>
+          <t>**STORIES WITH LEVEL CHANGES**</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="inlineStr"/>
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>No changes recorded since yesterday.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>• **Sea lanes &amp; undersea cables** (6→7, High): Escalated on unspecified geopolitical or infrastructure trigger; elevates supply-chain disruption risk for critical trade and digital connectivity.</t>
-        </is>
-      </c>
+      <c r="A19" s="12" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr"/>
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>**ELEVATED OR HIGHER RISKS**</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>• **Japan fiscal/JGB/carry trade** (7→6, Elevated): 30-year JGB yield rose 50bp to 3.86%, reducing yen funding cost advantage and easing near-term unwind pressure on leveraged positions.</t>
+          <t>• **Private credit's opaque expansion** (8/High): Unregulated growth in illiquid assets creates hidden counterparty and liquidity risk across institutional portfolios.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="inlineStr"/>
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>• **China's price spillover** (7/High): Deflationary or cost-push dynamics from China could destabilize global monetary conditions and emerging-market debt servicing.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>• **Developing-world debt crisis** (6→5, Elevated): US real 10y yield at 2.35% and zero new IMF programs/missed coupons signal reduced refinancing stress, though backdrop remains fragile.</t>
+          <t>• **Critical minerals as a weapon** (7/High): Geopolitical weaponization of rare-earth and battery supply chains threatens technology and energy transitions.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="inlineStr"/>
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>• **AI power &amp; grid bottleneck** (7/High): Explosive compute demand outpacing grid infrastructure creates energy-cost and systemic reliability risks.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>• **Food &amp; fertilizer fragility** (7→6, Elevated): China's tightened fertilizer export curbs persist; risk downgrade reflects data lag rather than policy reversal.</t>
+          <t>• **Sea lanes &amp; undersea cables** (7/High): Corridor fragmentation and cable vulnerability expose digital and trade infrastructure to disruption.</t>
         </is>
       </c>
     </row>
@@ -30372,14 +31266,14 @@
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>**TOP WATCH**</t>
+          <t>**WATCH**</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>Private credit's opaque expansion (8, High) remains the highest-risk outlier; no driver data suggests structural opacity in leverage is unmonitored.</t>
+          <t>Private credit opacity (level 8) remains the highest single-point-of-failure risk; shadow banking scale now rivals regulated finance with minimal disclosure.</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-07-21  -  generated 2026-07-21 13:02 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-07-22  -  generated 2026-07-22 13:07 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
         </is>
       </c>
       <c r="D2" s="7" t="n">
-        <v>-0.06</v>
+        <v>-0.02</v>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>162.74</v>
+        <v>163.085</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>3.894</v>
+        <v>3.905</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>6.754</v>
+        <v>6.7612</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>308.3</v>
+        <v>309.2</v>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.79</v>
+        <v>0.78</v>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>4060.6001</v>
+        <v>4117.2002</v>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>6.5265</v>
+        <v>6.4985</v>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="D60" s="7" t="n">
-        <v>84.16</v>
+        <v>87.5</v>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="D62" s="7" t="n">
-        <v>17.89</v>
+        <v>17.44</v>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H631"/>
+  <dimension ref="A1:H652"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -31088,6 +31088,888 @@
         </is>
       </c>
     </row>
+    <row r="632">
+      <c r="A632" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B632" s="9" t="inlineStr">
+        <is>
+          <t>s1_basis_trade</t>
+        </is>
+      </c>
+      <c r="C632" s="9" t="inlineStr">
+        <is>
+          <t>Treasury basis trade (hidden leverage)</t>
+        </is>
+      </c>
+      <c r="D632" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E632" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F632" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G632" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H632" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B633" s="9" t="inlineStr">
+        <is>
+          <t>s2_japan</t>
+        </is>
+      </c>
+      <c r="C633" s="9" t="inlineStr">
+        <is>
+          <t>Japan fiscal / JGB / carry trade</t>
+        </is>
+      </c>
+      <c r="D633" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E633" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F633" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G633" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H633" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B634" s="9" t="inlineStr">
+        <is>
+          <t>s3_private_credit</t>
+        </is>
+      </c>
+      <c r="C634" s="9" t="inlineStr">
+        <is>
+          <t>Private credit's opaque expansion</t>
+        </is>
+      </c>
+      <c r="D634" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E634" s="9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F634" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G634" s="9" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="H634" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B635" s="9" t="inlineStr">
+        <is>
+          <t>s4_dev_debt</t>
+        </is>
+      </c>
+      <c r="C635" s="9" t="inlineStr">
+        <is>
+          <t>Developing-world debt crisis</t>
+        </is>
+      </c>
+      <c r="D635" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E635" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F635" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G635" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H635" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B636" s="9" t="inlineStr">
+        <is>
+          <t>s5_china_deflation</t>
+        </is>
+      </c>
+      <c r="C636" s="9" t="inlineStr">
+        <is>
+          <t>China's price spillover (deflation or cost-push)</t>
+        </is>
+      </c>
+      <c r="D636" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E636" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F636" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G636" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H636" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B637" s="9" t="inlineStr">
+        <is>
+          <t>s6_rare_earths</t>
+        </is>
+      </c>
+      <c r="C637" s="9" t="inlineStr">
+        <is>
+          <t>Critical minerals as a weapon</t>
+        </is>
+      </c>
+      <c r="D637" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E637" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F637" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G637" s="9" t="inlineStr">
+        <is>
+          <t>6.75</t>
+        </is>
+      </c>
+      <c r="H637" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B638" s="9" t="inlineStr">
+        <is>
+          <t>s7_stablecoins</t>
+        </is>
+      </c>
+      <c r="C638" s="9" t="inlineStr">
+        <is>
+          <t>Stablecoins &amp; Treasury demand</t>
+        </is>
+      </c>
+      <c r="D638" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E638" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F638" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G638" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H638" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B639" s="9" t="inlineStr">
+        <is>
+          <t>s8_ai_capex</t>
+        </is>
+      </c>
+      <c r="C639" s="9" t="inlineStr">
+        <is>
+          <t>AI build-out circular financing</t>
+        </is>
+      </c>
+      <c r="D639" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E639" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F639" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G639" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H639" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B640" s="9" t="inlineStr">
+        <is>
+          <t>s9_cre</t>
+        </is>
+      </c>
+      <c r="C640" s="9" t="inlineStr">
+        <is>
+          <t>CRE maturity wall / regional banks</t>
+        </is>
+      </c>
+      <c r="D640" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E640" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F640" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G640" s="9" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="H640" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B641" s="9" t="inlineStr">
+        <is>
+          <t>s10_france</t>
+        </is>
+      </c>
+      <c r="C641" s="9" t="inlineStr">
+        <is>
+          <t>France / eurozone fragility</t>
+        </is>
+      </c>
+      <c r="D641" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E641" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F641" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G641" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H641" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B642" s="9" t="inlineStr">
+        <is>
+          <t>s11_consumer_debt</t>
+        </is>
+      </c>
+      <c r="C642" s="9" t="inlineStr">
+        <is>
+          <t>Hidden consumer debt</t>
+        </is>
+      </c>
+      <c r="D642" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E642" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F642" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G642" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H642" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B643" s="9" t="inlineStr">
+        <is>
+          <t>s12_gold_dedollar</t>
+        </is>
+      </c>
+      <c r="C643" s="9" t="inlineStr">
+        <is>
+          <t>Gold / de-dollarization</t>
+        </is>
+      </c>
+      <c r="D643" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E643" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F643" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G643" s="9" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="H643" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B644" s="9" t="inlineStr">
+        <is>
+          <t>s13_insurance</t>
+        </is>
+      </c>
+      <c r="C644" s="9" t="inlineStr">
+        <is>
+          <t>Insurance retreat</t>
+        </is>
+      </c>
+      <c r="D644" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E644" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F644" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G644" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H644" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B645" s="9" t="inlineStr">
+        <is>
+          <t>s14_pensions</t>
+        </is>
+      </c>
+      <c r="C645" s="9" t="inlineStr">
+        <is>
+          <t>Pensions / demographics</t>
+        </is>
+      </c>
+      <c r="D645" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E645" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F645" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G645" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H645" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B646" s="9" t="inlineStr">
+        <is>
+          <t>s15_ai_power</t>
+        </is>
+      </c>
+      <c r="C646" s="9" t="inlineStr">
+        <is>
+          <t>AI power &amp; the grid bottleneck</t>
+        </is>
+      </c>
+      <c r="D646" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E646" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F646" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G646" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H646" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B647" s="9" t="inlineStr">
+        <is>
+          <t>s16_copper</t>
+        </is>
+      </c>
+      <c r="C647" s="9" t="inlineStr">
+        <is>
+          <t>Copper &amp; the electrification deficit</t>
+        </is>
+      </c>
+      <c r="D647" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E647" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F647" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G647" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H647" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B648" s="9" t="inlineStr">
+        <is>
+          <t>s17_water</t>
+        </is>
+      </c>
+      <c r="C648" s="9" t="inlineStr">
+        <is>
+          <t>Water - the underpriced input</t>
+        </is>
+      </c>
+      <c r="D648" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E648" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F648" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G648" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H648" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B649" s="9" t="inlineStr">
+        <is>
+          <t>s18_food_fertilizer</t>
+        </is>
+      </c>
+      <c r="C649" s="9" t="inlineStr">
+        <is>
+          <t>Food &amp; fertilizer fragility</t>
+        </is>
+      </c>
+      <c r="D649" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E649" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F649" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G649" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H649" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B650" s="9" t="inlineStr">
+        <is>
+          <t>s19_lithography</t>
+        </is>
+      </c>
+      <c r="C650" s="9" t="inlineStr">
+        <is>
+          <t>The lithography (ASML) chokepoint</t>
+        </is>
+      </c>
+      <c r="D650" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E650" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F650" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G650" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H650" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B651" s="9" t="inlineStr">
+        <is>
+          <t>s20_sea_lanes</t>
+        </is>
+      </c>
+      <c r="C651" s="9" t="inlineStr">
+        <is>
+          <t>Sea lanes &amp; undersea cables</t>
+        </is>
+      </c>
+      <c r="D651" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E651" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F651" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G651" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H651" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B652" s="9" t="inlineStr">
+        <is>
+          <t>s21_clearinghouses</t>
+        </is>
+      </c>
+      <c r="C652" s="9" t="inlineStr">
+        <is>
+          <t>Clearinghouses (financial chokepoint)</t>
+        </is>
+      </c>
+      <c r="D652" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E652" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F652" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G652" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H652" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -31099,7 +31981,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A28"/>
+  <dimension ref="A1:A25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -31180,7 +32062,7 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>--- Daily narrative (2026-07-21) ---</t>
+          <t>--- Daily narrative (2026-07-22) ---</t>
         </is>
       </c>
     </row>
@@ -31194,7 +32076,7 @@
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>Macro risk remains elevated at 7.1 overall, with structural vulnerabilities concentrated in financial leverage, commodity spillovers, and critical infrastructure chokepoints.</t>
+          <t>Overall macro risk stands at 7.5/10, driven by structural leverage, supply-chain concentration, and geopolitical fragmentation.</t>
         </is>
       </c>
     </row>
@@ -31204,14 +32086,14 @@
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>**STORIES WITH LEVEL CHANGES**</t>
+          <t>**LEVEL CHANGES**</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>No changes recorded since yesterday.</t>
+          <t>• **Japan fiscal / JGB / carry trade** (6→7, now High): 30-year JGB yield rose to 3.905%, breaking into band 2 stress territory. Unwinding risk in yen carry trades and fiscal sustainability concerns now acute.</t>
         </is>
       </c>
     </row>
@@ -31221,59 +32103,38 @@
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>**ELEVATED OR HIGHER RISKS**</t>
+          <t>**SUSTAINED HIGH-RISK STORIES**</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>• **Private credit's opaque expansion** (8/High): Unregulated growth in illiquid assets creates hidden counterparty and liquidity risk across institutional portfolios.</t>
+          <t>• Private credit opaque expansion (8/10) remains most severe; Treasury basis trades and AI circular financing pose hidden leverage risks (both 6/10).</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>• **China's price spillover** (7/High): Deflationary or cost-push dynamics from China could destabilize global monetary conditions and emerging-market debt servicing.</t>
+          <t>• China price spillover, critical minerals weaponization, and sea-lane disruption each at 7/10—structural and geopolitical.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>• **Critical minerals as a weapon** (7/High): Geopolitical weaponization of rare-earth and battery supply chains threatens technology and energy transitions.</t>
-        </is>
-      </c>
+      <c r="A23" s="12" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>• **AI power &amp; grid bottleneck** (7/High): Explosive compute demand outpacing grid infrastructure creates energy-cost and systemic reliability risks.</t>
+          <t>**TO WATCH**</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>• **Sea lanes &amp; undersea cables** (7/High): Corridor fragmentation and cable vulnerability expose digital and trade infrastructure to disruption.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="12" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>**WATCH**</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="12" t="inlineStr">
-        <is>
-          <t>Private credit opacity (level 8) remains the highest single-point-of-failure risk; shadow banking scale now rivals regulated finance with minimal disclosure.</t>
+          <t>Private credit's opaque expansion at 8/10 represents the system's highest concentration risk.</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-07-22  -  generated 2026-07-22 13:07 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-07-23  -  generated 2026-07-23 13:09 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
         </is>
       </c>
       <c r="D2" s="7" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>163.085</v>
+        <v>163.79</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>3.905</v>
+        <v>3.901</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>6.7612</v>
+        <v>6.7628</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>309.2</v>
+        <v>310.1</v>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>4117.2002</v>
+        <v>4063.8999</v>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>6.4985</v>
+        <v>6.4225</v>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="D60" s="7" t="n">
-        <v>87.5</v>
+        <v>90.88</v>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="D62" s="7" t="n">
-        <v>17.44</v>
+        <v>18.94</v>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H652"/>
+  <dimension ref="A1:H673"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -31970,6 +31970,888 @@
         </is>
       </c>
     </row>
+    <row r="653">
+      <c r="A653" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B653" s="9" t="inlineStr">
+        <is>
+          <t>s1_basis_trade</t>
+        </is>
+      </c>
+      <c r="C653" s="9" t="inlineStr">
+        <is>
+          <t>Treasury basis trade (hidden leverage)</t>
+        </is>
+      </c>
+      <c r="D653" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E653" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F653" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G653" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H653" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B654" s="9" t="inlineStr">
+        <is>
+          <t>s2_japan</t>
+        </is>
+      </c>
+      <c r="C654" s="9" t="inlineStr">
+        <is>
+          <t>Japan fiscal / JGB / carry trade</t>
+        </is>
+      </c>
+      <c r="D654" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E654" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F654" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G654" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H654" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B655" s="9" t="inlineStr">
+        <is>
+          <t>s3_private_credit</t>
+        </is>
+      </c>
+      <c r="C655" s="9" t="inlineStr">
+        <is>
+          <t>Private credit's opaque expansion</t>
+        </is>
+      </c>
+      <c r="D655" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E655" s="9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F655" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G655" s="9" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="H655" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B656" s="9" t="inlineStr">
+        <is>
+          <t>s4_dev_debt</t>
+        </is>
+      </c>
+      <c r="C656" s="9" t="inlineStr">
+        <is>
+          <t>Developing-world debt crisis</t>
+        </is>
+      </c>
+      <c r="D656" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E656" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F656" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G656" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H656" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B657" s="9" t="inlineStr">
+        <is>
+          <t>s5_china_deflation</t>
+        </is>
+      </c>
+      <c r="C657" s="9" t="inlineStr">
+        <is>
+          <t>China's price spillover (deflation or cost-push)</t>
+        </is>
+      </c>
+      <c r="D657" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E657" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F657" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G657" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H657" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B658" s="9" t="inlineStr">
+        <is>
+          <t>s6_rare_earths</t>
+        </is>
+      </c>
+      <c r="C658" s="9" t="inlineStr">
+        <is>
+          <t>Critical minerals as a weapon</t>
+        </is>
+      </c>
+      <c r="D658" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E658" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F658" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G658" s="9" t="inlineStr">
+        <is>
+          <t>6.75</t>
+        </is>
+      </c>
+      <c r="H658" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B659" s="9" t="inlineStr">
+        <is>
+          <t>s7_stablecoins</t>
+        </is>
+      </c>
+      <c r="C659" s="9" t="inlineStr">
+        <is>
+          <t>Stablecoins &amp; Treasury demand</t>
+        </is>
+      </c>
+      <c r="D659" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E659" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F659" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G659" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H659" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B660" s="9" t="inlineStr">
+        <is>
+          <t>s8_ai_capex</t>
+        </is>
+      </c>
+      <c r="C660" s="9" t="inlineStr">
+        <is>
+          <t>AI build-out circular financing</t>
+        </is>
+      </c>
+      <c r="D660" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E660" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F660" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G660" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H660" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B661" s="9" t="inlineStr">
+        <is>
+          <t>s9_cre</t>
+        </is>
+      </c>
+      <c r="C661" s="9" t="inlineStr">
+        <is>
+          <t>CRE maturity wall / regional banks</t>
+        </is>
+      </c>
+      <c r="D661" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E661" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F661" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G661" s="9" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="H661" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B662" s="9" t="inlineStr">
+        <is>
+          <t>s10_france</t>
+        </is>
+      </c>
+      <c r="C662" s="9" t="inlineStr">
+        <is>
+          <t>France / eurozone fragility</t>
+        </is>
+      </c>
+      <c r="D662" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E662" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F662" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G662" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H662" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B663" s="9" t="inlineStr">
+        <is>
+          <t>s11_consumer_debt</t>
+        </is>
+      </c>
+      <c r="C663" s="9" t="inlineStr">
+        <is>
+          <t>Hidden consumer debt</t>
+        </is>
+      </c>
+      <c r="D663" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E663" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F663" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G663" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H663" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B664" s="9" t="inlineStr">
+        <is>
+          <t>s12_gold_dedollar</t>
+        </is>
+      </c>
+      <c r="C664" s="9" t="inlineStr">
+        <is>
+          <t>Gold / de-dollarization</t>
+        </is>
+      </c>
+      <c r="D664" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E664" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F664" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G664" s="9" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="H664" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B665" s="9" t="inlineStr">
+        <is>
+          <t>s13_insurance</t>
+        </is>
+      </c>
+      <c r="C665" s="9" t="inlineStr">
+        <is>
+          <t>Insurance retreat</t>
+        </is>
+      </c>
+      <c r="D665" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E665" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F665" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G665" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H665" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B666" s="9" t="inlineStr">
+        <is>
+          <t>s14_pensions</t>
+        </is>
+      </c>
+      <c r="C666" s="9" t="inlineStr">
+        <is>
+          <t>Pensions / demographics</t>
+        </is>
+      </c>
+      <c r="D666" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E666" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F666" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G666" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H666" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B667" s="9" t="inlineStr">
+        <is>
+          <t>s15_ai_power</t>
+        </is>
+      </c>
+      <c r="C667" s="9" t="inlineStr">
+        <is>
+          <t>AI power &amp; the grid bottleneck</t>
+        </is>
+      </c>
+      <c r="D667" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E667" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F667" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G667" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H667" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B668" s="9" t="inlineStr">
+        <is>
+          <t>s16_copper</t>
+        </is>
+      </c>
+      <c r="C668" s="9" t="inlineStr">
+        <is>
+          <t>Copper &amp; the electrification deficit</t>
+        </is>
+      </c>
+      <c r="D668" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E668" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F668" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G668" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H668" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B669" s="9" t="inlineStr">
+        <is>
+          <t>s17_water</t>
+        </is>
+      </c>
+      <c r="C669" s="9" t="inlineStr">
+        <is>
+          <t>Water - the underpriced input</t>
+        </is>
+      </c>
+      <c r="D669" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E669" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F669" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G669" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H669" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B670" s="9" t="inlineStr">
+        <is>
+          <t>s18_food_fertilizer</t>
+        </is>
+      </c>
+      <c r="C670" s="9" t="inlineStr">
+        <is>
+          <t>Food &amp; fertilizer fragility</t>
+        </is>
+      </c>
+      <c r="D670" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E670" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F670" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G670" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H670" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B671" s="9" t="inlineStr">
+        <is>
+          <t>s19_lithography</t>
+        </is>
+      </c>
+      <c r="C671" s="9" t="inlineStr">
+        <is>
+          <t>The lithography (ASML) chokepoint</t>
+        </is>
+      </c>
+      <c r="D671" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E671" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F671" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G671" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H671" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B672" s="9" t="inlineStr">
+        <is>
+          <t>s20_sea_lanes</t>
+        </is>
+      </c>
+      <c r="C672" s="9" t="inlineStr">
+        <is>
+          <t>Sea lanes &amp; undersea cables</t>
+        </is>
+      </c>
+      <c r="D672" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E672" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F672" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G672" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H672" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B673" s="9" t="inlineStr">
+        <is>
+          <t>s21_clearinghouses</t>
+        </is>
+      </c>
+      <c r="C673" s="9" t="inlineStr">
+        <is>
+          <t>Clearinghouses (financial chokepoint)</t>
+        </is>
+      </c>
+      <c r="D673" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E673" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F673" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G673" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H673" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -31981,7 +32863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A25"/>
+  <dimension ref="A1:A30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -32062,7 +32944,7 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>--- Daily narrative (2026-07-22) ---</t>
+          <t>--- Daily narrative (2026-07-23) ---</t>
         </is>
       </c>
     </row>
@@ -32076,7 +32958,7 @@
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>Overall macro risk stands at 7.5/10, driven by structural leverage, supply-chain concentration, and geopolitical fragmentation.</t>
+          <t>Overall macro risk remains elevated at 7.5 with no intraday changes, driven by concentrated stress in financial leverage, geopolitical commodity control, and infrastructure bottlenecks.</t>
         </is>
       </c>
     </row>
@@ -32086,14 +32968,14 @@
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>**LEVEL CHANGES**</t>
+          <t>**KEY STORIES**</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>• **Japan fiscal / JGB / carry trade** (6→7, now High): 30-year JGB yield rose to 3.905%, breaking into band 2 stress territory. Unwinding risk in yen carry trades and fiscal sustainability concerns now acute.</t>
+          <t>No risk-level changes were recorded today.</t>
         </is>
       </c>
     </row>
@@ -32103,38 +32985,73 @@
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>**SUSTAINED HIGH-RISK STORIES**</t>
+          <t>**ELEVATED OR HIGHER (15 active risks)**</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>• Private credit opaque expansion (8/10) remains most severe; Treasury basis trades and AI circular financing pose hidden leverage risks (both 6/10).</t>
+          <t>- **Private credit's opaque expansion** (Level 8, High): Largest single risk; minimal transparency on leverage and collateral quality creates systemic stability exposure.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>• China price spillover, critical minerals weaponization, and sea-lane disruption each at 7/10—structural and geopolitical.</t>
+          <t>- **Japan fiscal / JGB / carry trade** (Level 7): Unwind risk persists amid rate volatility; foreign deleveraging could cascade.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="inlineStr"/>
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>- **China's price spillover** (Level 7): Deflation/cost-push dynamics threaten regional demand and margin compression.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>**TO WATCH**</t>
+          <t>- **Critical minerals as a weapon** (Level 7): Supply weaponization limits industrial decarbonization and tech supply chains.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>Private credit's opaque expansion at 8/10 represents the system's highest concentration risk.</t>
+          <t>- **AI power &amp; the grid bottleneck** (Level 7): Infrastructure capacity constraints threaten AI capex viability and grid stability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>- **Sea lanes &amp; undersea cables** (Level 7): Geopolitical chokepoints on critical connectivity routes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>- Six stories at Level 6 (Elevated): Treasury basis trades, AI financing circularity, hidden consumer debt, food fragility, lithography concentration, and food-fertilizer links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>**TO WATCH**</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>Private credit expansion (Level 8) remains the highest-risk story given opacity and systemic contagion vectors.</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-07-23  -  generated 2026-07-23 13:09 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-07-24  -  generated 2026-07-24 13:04 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
         </is>
       </c>
       <c r="D2" s="7" t="n">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>163.79</v>
+        <v>163.86</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>3.901</v>
+        <v>3.929</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>2.37</v>
+        <v>2.39</v>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>6.7628</v>
+        <v>6.7611</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>4063.8999</v>
+        <v>4057.6001</v>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>6.4225</v>
+        <v>6.3415</v>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="D60" s="7" t="n">
-        <v>90.88</v>
+        <v>89.44</v>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="D62" s="7" t="n">
-        <v>18.94</v>
+        <v>18.79</v>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H673"/>
+  <dimension ref="A1:H694"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -32852,6 +32852,888 @@
         </is>
       </c>
     </row>
+    <row r="674">
+      <c r="A674" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B674" s="9" t="inlineStr">
+        <is>
+          <t>s1_basis_trade</t>
+        </is>
+      </c>
+      <c r="C674" s="9" t="inlineStr">
+        <is>
+          <t>Treasury basis trade (hidden leverage)</t>
+        </is>
+      </c>
+      <c r="D674" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E674" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F674" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G674" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H674" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B675" s="9" t="inlineStr">
+        <is>
+          <t>s2_japan</t>
+        </is>
+      </c>
+      <c r="C675" s="9" t="inlineStr">
+        <is>
+          <t>Japan fiscal / JGB / carry trade</t>
+        </is>
+      </c>
+      <c r="D675" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E675" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F675" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G675" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H675" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B676" s="9" t="inlineStr">
+        <is>
+          <t>s3_private_credit</t>
+        </is>
+      </c>
+      <c r="C676" s="9" t="inlineStr">
+        <is>
+          <t>Private credit's opaque expansion</t>
+        </is>
+      </c>
+      <c r="D676" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E676" s="9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F676" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G676" s="9" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="H676" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B677" s="9" t="inlineStr">
+        <is>
+          <t>s4_dev_debt</t>
+        </is>
+      </c>
+      <c r="C677" s="9" t="inlineStr">
+        <is>
+          <t>Developing-world debt crisis</t>
+        </is>
+      </c>
+      <c r="D677" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E677" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F677" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G677" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H677" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B678" s="9" t="inlineStr">
+        <is>
+          <t>s5_china_deflation</t>
+        </is>
+      </c>
+      <c r="C678" s="9" t="inlineStr">
+        <is>
+          <t>China's price spillover (deflation or cost-push)</t>
+        </is>
+      </c>
+      <c r="D678" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E678" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F678" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G678" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H678" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B679" s="9" t="inlineStr">
+        <is>
+          <t>s6_rare_earths</t>
+        </is>
+      </c>
+      <c r="C679" s="9" t="inlineStr">
+        <is>
+          <t>Critical minerals as a weapon</t>
+        </is>
+      </c>
+      <c r="D679" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E679" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F679" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G679" s="9" t="inlineStr">
+        <is>
+          <t>6.75</t>
+        </is>
+      </c>
+      <c r="H679" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B680" s="9" t="inlineStr">
+        <is>
+          <t>s7_stablecoins</t>
+        </is>
+      </c>
+      <c r="C680" s="9" t="inlineStr">
+        <is>
+          <t>Stablecoins &amp; Treasury demand</t>
+        </is>
+      </c>
+      <c r="D680" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E680" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F680" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G680" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H680" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B681" s="9" t="inlineStr">
+        <is>
+          <t>s8_ai_capex</t>
+        </is>
+      </c>
+      <c r="C681" s="9" t="inlineStr">
+        <is>
+          <t>AI build-out circular financing</t>
+        </is>
+      </c>
+      <c r="D681" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E681" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F681" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G681" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H681" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B682" s="9" t="inlineStr">
+        <is>
+          <t>s9_cre</t>
+        </is>
+      </c>
+      <c r="C682" s="9" t="inlineStr">
+        <is>
+          <t>CRE maturity wall / regional banks</t>
+        </is>
+      </c>
+      <c r="D682" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E682" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F682" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G682" s="9" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="H682" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B683" s="9" t="inlineStr">
+        <is>
+          <t>s10_france</t>
+        </is>
+      </c>
+      <c r="C683" s="9" t="inlineStr">
+        <is>
+          <t>France / eurozone fragility</t>
+        </is>
+      </c>
+      <c r="D683" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E683" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F683" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G683" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H683" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B684" s="9" t="inlineStr">
+        <is>
+          <t>s11_consumer_debt</t>
+        </is>
+      </c>
+      <c r="C684" s="9" t="inlineStr">
+        <is>
+          <t>Hidden consumer debt</t>
+        </is>
+      </c>
+      <c r="D684" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E684" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F684" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G684" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H684" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B685" s="9" t="inlineStr">
+        <is>
+          <t>s12_gold_dedollar</t>
+        </is>
+      </c>
+      <c r="C685" s="9" t="inlineStr">
+        <is>
+          <t>Gold / de-dollarization</t>
+        </is>
+      </c>
+      <c r="D685" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E685" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F685" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G685" s="9" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="H685" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B686" s="9" t="inlineStr">
+        <is>
+          <t>s13_insurance</t>
+        </is>
+      </c>
+      <c r="C686" s="9" t="inlineStr">
+        <is>
+          <t>Insurance retreat</t>
+        </is>
+      </c>
+      <c r="D686" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E686" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F686" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G686" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H686" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B687" s="9" t="inlineStr">
+        <is>
+          <t>s14_pensions</t>
+        </is>
+      </c>
+      <c r="C687" s="9" t="inlineStr">
+        <is>
+          <t>Pensions / demographics</t>
+        </is>
+      </c>
+      <c r="D687" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E687" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F687" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G687" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H687" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B688" s="9" t="inlineStr">
+        <is>
+          <t>s15_ai_power</t>
+        </is>
+      </c>
+      <c r="C688" s="9" t="inlineStr">
+        <is>
+          <t>AI power &amp; the grid bottleneck</t>
+        </is>
+      </c>
+      <c r="D688" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E688" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F688" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G688" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H688" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B689" s="9" t="inlineStr">
+        <is>
+          <t>s16_copper</t>
+        </is>
+      </c>
+      <c r="C689" s="9" t="inlineStr">
+        <is>
+          <t>Copper &amp; the electrification deficit</t>
+        </is>
+      </c>
+      <c r="D689" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E689" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F689" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G689" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H689" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B690" s="9" t="inlineStr">
+        <is>
+          <t>s17_water</t>
+        </is>
+      </c>
+      <c r="C690" s="9" t="inlineStr">
+        <is>
+          <t>Water - the underpriced input</t>
+        </is>
+      </c>
+      <c r="D690" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E690" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F690" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G690" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H690" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B691" s="9" t="inlineStr">
+        <is>
+          <t>s18_food_fertilizer</t>
+        </is>
+      </c>
+      <c r="C691" s="9" t="inlineStr">
+        <is>
+          <t>Food &amp; fertilizer fragility</t>
+        </is>
+      </c>
+      <c r="D691" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E691" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F691" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G691" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H691" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B692" s="9" t="inlineStr">
+        <is>
+          <t>s19_lithography</t>
+        </is>
+      </c>
+      <c r="C692" s="9" t="inlineStr">
+        <is>
+          <t>The lithography (ASML) chokepoint</t>
+        </is>
+      </c>
+      <c r="D692" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E692" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F692" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G692" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H692" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B693" s="9" t="inlineStr">
+        <is>
+          <t>s20_sea_lanes</t>
+        </is>
+      </c>
+      <c r="C693" s="9" t="inlineStr">
+        <is>
+          <t>Sea lanes &amp; undersea cables</t>
+        </is>
+      </c>
+      <c r="D693" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E693" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F693" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G693" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H693" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B694" s="9" t="inlineStr">
+        <is>
+          <t>s21_clearinghouses</t>
+        </is>
+      </c>
+      <c r="C694" s="9" t="inlineStr">
+        <is>
+          <t>Clearinghouses (financial chokepoint)</t>
+        </is>
+      </c>
+      <c r="D694" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E694" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F694" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G694" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H694" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -32863,7 +33745,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A30"/>
+  <dimension ref="A1:A28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -32944,7 +33826,7 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>--- Daily narrative (2026-07-23) ---</t>
+          <t>--- Daily narrative (2026-07-24) ---</t>
         </is>
       </c>
     </row>
@@ -32958,7 +33840,7 @@
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>Overall macro risk remains elevated at 7.5 with no intraday changes, driven by concentrated stress in financial leverage, geopolitical commodity control, and infrastructure bottlenecks.</t>
+          <t>Macro risk holds at elevated 7.5 overall, with structural vulnerabilities concentrated in credit opacity, geopolitical supply leverage, and AI infrastructure dependencies.</t>
         </is>
       </c>
     </row>
@@ -32968,14 +33850,14 @@
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>**KEY STORIES**</t>
+          <t>**STORIES WITH LEVEL CHANGES**</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>No risk-level changes were recorded today.</t>
+          <t>No intraday level changes recorded.</t>
         </is>
       </c>
     </row>
@@ -32985,73 +33867,59 @@
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>**ELEVATED OR HIGHER (15 active risks)**</t>
+          <t>**ELEVATED OR HIGHER RISKS (SNAPSHOT)**</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>- **Private credit's opaque expansion** (Level 8, High): Largest single risk; minimal transparency on leverage and collateral quality creates systemic stability exposure.</t>
+          <t>- **Private credit's opaque expansion** (8, High): Least-regulated shadow lending now represents material systemic exposure with limited transparency on counterparty risk and drawdown timing.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>- **Japan fiscal / JGB / carry trade** (Level 7): Unwind risk persists amid rate volatility; foreign deleveraging could cascade.</t>
+          <t>- **Japan fiscal/JGB/carry trade** (7, High): Persistent structural imbalance creates unwind risk if BoJ policy shifts; triggering margin calls across leveraged FX positions.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>- **China's price spillover** (Level 7): Deflation/cost-push dynamics threaten regional demand and margin compression.</t>
+          <t>- **China's price spillover** (7, High): Deflationary exports and/or input cost spikes propagate unevenly across trading partners, complicating monetary policy coordination.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>- **Critical minerals as a weapon** (Level 7): Supply weaponization limits industrial decarbonization and tech supply chains.</t>
+          <t>- **Critical minerals as a weapon** (7, High): Supply concentration enables coercive leverage; disruption cascades through EV and defense supply chains.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>- **AI power &amp; the grid bottleneck** (Level 7): Infrastructure capacity constraints threaten AI capex viability and grid stability.</t>
+          <t>- **AI power &amp; the grid bottleneck** (7, High): Data center demand outpacing grid buildout; capex mismatches invite brownout and stranded asset risk.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>- **Sea lanes &amp; undersea cables** (Level 7): Geopolitical chokepoints on critical connectivity routes.</t>
+          <t>- **Sea lanes &amp; undersea cables** (7, High): Chokepoint vulnerability to disruption; single-point failures threaten digital and physical trade flows.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>- Six stories at Level 6 (Elevated): Treasury basis trades, AI financing circularity, hidden consumer debt, food fragility, lithography concentration, and food-fertilizer links.</t>
-        </is>
-      </c>
+      <c r="A27" s="12" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="12" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="12" t="inlineStr">
-        <is>
-          <t>**TO WATCH**</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="12" t="inlineStr">
-        <is>
-          <t>Private credit expansion (Level 8) remains the highest-risk story given opacity and systemic contagion vectors.</t>
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>**WATCH:** Private credit opacity paired with AI circular financing (both 6–8 band) creates correlated leverage risk if rates spike or growth disappoints.</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-07-24  -  generated 2026-07-24 13:04 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-07-27  -  generated 2026-07-27 14:02 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="D3" s="7" t="n">
-        <v>70.88</v>
+        <v>76.8175</v>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>163.86</v>
+        <v>163.718</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>3.929</v>
+        <v>3.98</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>2.68</v>
+        <v>2.77</v>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>2.39</v>
+        <v>2.43</v>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>6.7611</v>
+        <v>6.7541</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>310.1</v>
+        <v>309.1</v>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
         </is>
       </c>
       <c r="D27" s="7" t="n">
-        <v>11.57</v>
+        <v>11.7</v>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         </is>
       </c>
       <c r="D32" s="7" t="n">
-        <v>6.8</v>
+        <v>6.11</v>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>4057.6001</v>
+        <v>4088.6001</v>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         </is>
       </c>
       <c r="D43" s="7" t="n">
-        <v>87.59999999999999</v>
+        <v>85</v>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>6.3415</v>
+        <v>6.4015</v>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         </is>
       </c>
       <c r="D55" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="D60" s="7" t="n">
-        <v>89.44</v>
+        <v>83.83</v>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="D62" s="7" t="n">
-        <v>18.79</v>
+        <v>17.88</v>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
         </is>
       </c>
       <c r="D63" s="7" t="n">
-        <v>70.88</v>
+        <v>76.8175</v>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H694"/>
+  <dimension ref="A1:H715"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -33729,6 +33729,888 @@
         </is>
       </c>
       <c r="H694" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B695" s="9" t="inlineStr">
+        <is>
+          <t>s1_basis_trade</t>
+        </is>
+      </c>
+      <c r="C695" s="9" t="inlineStr">
+        <is>
+          <t>Treasury basis trade (hidden leverage)</t>
+        </is>
+      </c>
+      <c r="D695" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E695" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F695" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G695" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H695" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B696" s="9" t="inlineStr">
+        <is>
+          <t>s2_japan</t>
+        </is>
+      </c>
+      <c r="C696" s="9" t="inlineStr">
+        <is>
+          <t>Japan fiscal / JGB / carry trade</t>
+        </is>
+      </c>
+      <c r="D696" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E696" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F696" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G696" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H696" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B697" s="9" t="inlineStr">
+        <is>
+          <t>s3_private_credit</t>
+        </is>
+      </c>
+      <c r="C697" s="9" t="inlineStr">
+        <is>
+          <t>Private credit's opaque expansion</t>
+        </is>
+      </c>
+      <c r="D697" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E697" s="9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F697" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G697" s="9" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="H697" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B698" s="9" t="inlineStr">
+        <is>
+          <t>s4_dev_debt</t>
+        </is>
+      </c>
+      <c r="C698" s="9" t="inlineStr">
+        <is>
+          <t>Developing-world debt crisis</t>
+        </is>
+      </c>
+      <c r="D698" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E698" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F698" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G698" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H698" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B699" s="9" t="inlineStr">
+        <is>
+          <t>s5_china_deflation</t>
+        </is>
+      </c>
+      <c r="C699" s="9" t="inlineStr">
+        <is>
+          <t>China's price spillover (deflation or cost-push)</t>
+        </is>
+      </c>
+      <c r="D699" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E699" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F699" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G699" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H699" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B700" s="9" t="inlineStr">
+        <is>
+          <t>s6_rare_earths</t>
+        </is>
+      </c>
+      <c r="C700" s="9" t="inlineStr">
+        <is>
+          <t>Critical minerals as a weapon</t>
+        </is>
+      </c>
+      <c r="D700" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E700" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F700" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G700" s="9" t="inlineStr">
+        <is>
+          <t>6.75</t>
+        </is>
+      </c>
+      <c r="H700" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B701" s="9" t="inlineStr">
+        <is>
+          <t>s7_stablecoins</t>
+        </is>
+      </c>
+      <c r="C701" s="9" t="inlineStr">
+        <is>
+          <t>Stablecoins &amp; Treasury demand</t>
+        </is>
+      </c>
+      <c r="D701" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E701" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F701" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G701" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H701" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B702" s="9" t="inlineStr">
+        <is>
+          <t>s8_ai_capex</t>
+        </is>
+      </c>
+      <c r="C702" s="9" t="inlineStr">
+        <is>
+          <t>AI build-out circular financing</t>
+        </is>
+      </c>
+      <c r="D702" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E702" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F702" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G702" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H702" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B703" s="9" t="inlineStr">
+        <is>
+          <t>s9_cre</t>
+        </is>
+      </c>
+      <c r="C703" s="9" t="inlineStr">
+        <is>
+          <t>CRE maturity wall / regional banks</t>
+        </is>
+      </c>
+      <c r="D703" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E703" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F703" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G703" s="9" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="H703" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B704" s="9" t="inlineStr">
+        <is>
+          <t>s10_france</t>
+        </is>
+      </c>
+      <c r="C704" s="9" t="inlineStr">
+        <is>
+          <t>France / eurozone fragility</t>
+        </is>
+      </c>
+      <c r="D704" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E704" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F704" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G704" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H704" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B705" s="9" t="inlineStr">
+        <is>
+          <t>s11_consumer_debt</t>
+        </is>
+      </c>
+      <c r="C705" s="9" t="inlineStr">
+        <is>
+          <t>Hidden consumer debt</t>
+        </is>
+      </c>
+      <c r="D705" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E705" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F705" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G705" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H705" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B706" s="9" t="inlineStr">
+        <is>
+          <t>s12_gold_dedollar</t>
+        </is>
+      </c>
+      <c r="C706" s="9" t="inlineStr">
+        <is>
+          <t>Gold / de-dollarization</t>
+        </is>
+      </c>
+      <c r="D706" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E706" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F706" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G706" s="9" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="H706" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B707" s="9" t="inlineStr">
+        <is>
+          <t>s13_insurance</t>
+        </is>
+      </c>
+      <c r="C707" s="9" t="inlineStr">
+        <is>
+          <t>Insurance retreat</t>
+        </is>
+      </c>
+      <c r="D707" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E707" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F707" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G707" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H707" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B708" s="9" t="inlineStr">
+        <is>
+          <t>s14_pensions</t>
+        </is>
+      </c>
+      <c r="C708" s="9" t="inlineStr">
+        <is>
+          <t>Pensions / demographics</t>
+        </is>
+      </c>
+      <c r="D708" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E708" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F708" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G708" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H708" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B709" s="9" t="inlineStr">
+        <is>
+          <t>s15_ai_power</t>
+        </is>
+      </c>
+      <c r="C709" s="9" t="inlineStr">
+        <is>
+          <t>AI power &amp; the grid bottleneck</t>
+        </is>
+      </c>
+      <c r="D709" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E709" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F709" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G709" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H709" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B710" s="9" t="inlineStr">
+        <is>
+          <t>s16_copper</t>
+        </is>
+      </c>
+      <c r="C710" s="9" t="inlineStr">
+        <is>
+          <t>Copper &amp; the electrification deficit</t>
+        </is>
+      </c>
+      <c r="D710" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E710" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F710" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G710" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H710" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B711" s="9" t="inlineStr">
+        <is>
+          <t>s17_water</t>
+        </is>
+      </c>
+      <c r="C711" s="9" t="inlineStr">
+        <is>
+          <t>Water - the underpriced input</t>
+        </is>
+      </c>
+      <c r="D711" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E711" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F711" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G711" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H711" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B712" s="9" t="inlineStr">
+        <is>
+          <t>s18_food_fertilizer</t>
+        </is>
+      </c>
+      <c r="C712" s="9" t="inlineStr">
+        <is>
+          <t>Food &amp; fertilizer fragility</t>
+        </is>
+      </c>
+      <c r="D712" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E712" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F712" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G712" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H712" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B713" s="9" t="inlineStr">
+        <is>
+          <t>s19_lithography</t>
+        </is>
+      </c>
+      <c r="C713" s="9" t="inlineStr">
+        <is>
+          <t>The lithography (ASML) chokepoint</t>
+        </is>
+      </c>
+      <c r="D713" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E713" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F713" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G713" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H713" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B714" s="9" t="inlineStr">
+        <is>
+          <t>s20_sea_lanes</t>
+        </is>
+      </c>
+      <c r="C714" s="9" t="inlineStr">
+        <is>
+          <t>Sea lanes &amp; undersea cables</t>
+        </is>
+      </c>
+      <c r="D714" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E714" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F714" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G714" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H714" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B715" s="9" t="inlineStr">
+        <is>
+          <t>s21_clearinghouses</t>
+        </is>
+      </c>
+      <c r="C715" s="9" t="inlineStr">
+        <is>
+          <t>Clearinghouses (financial chokepoint)</t>
+        </is>
+      </c>
+      <c r="D715" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E715" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F715" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G715" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H715" s="9" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
@@ -33826,100 +34708,88 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>--- Daily narrative (2026-07-24) ---</t>
+          <t>--- Daily narrative (2026-07-27) ---</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>**HEADLINE**</t>
+          <t>**EOD BRIEF | 2026-07-27**</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>Macro risk holds at elevated 7.5 overall, with structural vulnerabilities concentrated in credit opacity, geopolitical supply leverage, and AI infrastructure dependencies.</t>
-        </is>
-      </c>
+      <c r="A15" s="12" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr"/>
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>**Headline:**</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>**STORIES WITH LEVEL CHANGES**</t>
+          <t>Overall macro risk elevated to 7.9 as supply-chain fragility and emerging-market debt pressures intensify.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
-          <t>No intraday level changes recorded.</t>
-        </is>
-      </c>
+      <c r="A18" s="12" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr"/>
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>**Changes:**</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
-          <t>**ELEVATED OR HIGHER RISKS (SNAPSHOT)**</t>
-        </is>
-      </c>
+      <c r="A20" s="12" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>- **Private credit's opaque expansion** (8, High): Least-regulated shadow lending now represents material systemic exposure with limited transparency on counterparty risk and drawdown timing.</t>
+          <t>• **Developing-world debt crisis** (5→6, Elevated): US 10-year real yields rose 50bp to 2.43%, raising refinancing costs for vulnerable sovereigns and increasing default risk.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t>- **Japan fiscal/JGB/carry trade** (7, High): Persistent structural imbalance creates unwind risk if BoJ policy shifts; triggering margin calls across leveraged FX positions.</t>
-        </is>
-      </c>
+      <c r="A22" s="12" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>- **China's price spillover** (7, High): Deflationary exports and/or input cost spikes propagate unevenly across trading partners, complicating monetary policy coordination.</t>
+          <t>• **Food &amp; fertilizer fragility** (6→7, High): China tightened fertilizer export curbs and Gulf/Hormuz fertilizer inputs remain cut, compressing global agricultural supply ahead of harvest season.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="inlineStr">
-        <is>
-          <t>- **Critical minerals as a weapon** (7, High): Supply concentration enables coercive leverage; disruption cascades through EV and defense supply chains.</t>
-        </is>
-      </c>
+      <c r="A24" s="12" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>- **AI power &amp; the grid bottleneck** (7, High): Data center demand outpacing grid buildout; capex mismatches invite brownout and stranded asset risk.</t>
+          <t>• **Hidden consumer debt** (6→5, Elevated): Risk moderated with no new drivers reported; however, debt servicing remains structurally vulnerable.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="12" t="inlineStr">
-        <is>
-          <t>- **Sea lanes &amp; undersea cables** (7, High): Chokepoint vulnerability to disruption; single-point failures threaten digital and physical trade flows.</t>
-        </is>
-      </c>
+      <c r="A26" s="12" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="12" t="inlineStr"/>
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>**Watch:**</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>**WATCH:** Private credit opacity paired with AI circular financing (both 6–8 band) creates correlated leverage risk if rates spike or growth disappoints.</t>
+          <t>Private credit's opaque expansion (level 8, High) remains the highest systemic risk, with no visibility into counterparty leverage or mark-to-market stress in downturn scenarios.</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-07-27  -  generated 2026-07-27 14:02 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-07-28  -  generated 2026-07-28 13:16 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="D3" s="7" t="n">
-        <v>76.8175</v>
+        <v>77.2128</v>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>163.718</v>
+        <v>163.873</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>3.98</v>
+        <v>3.969</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>120.5315</v>
+        <v>120.7105</v>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>6.7541</v>
+        <v>6.7595</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>309.1</v>
+        <v>307.9</v>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>4088.6001</v>
+        <v>4033.3999</v>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>6.4015</v>
+        <v>6.313</v>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="D60" s="7" t="n">
-        <v>83.83</v>
+        <v>81.19</v>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="D62" s="7" t="n">
-        <v>17.88</v>
+        <v>18.71</v>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
         </is>
       </c>
       <c r="D63" s="7" t="n">
-        <v>76.8175</v>
+        <v>77.2128</v>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H715"/>
+  <dimension ref="A1:H736"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -34616,6 +34616,888 @@
         </is>
       </c>
     </row>
+    <row r="716">
+      <c r="A716" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B716" s="9" t="inlineStr">
+        <is>
+          <t>s1_basis_trade</t>
+        </is>
+      </c>
+      <c r="C716" s="9" t="inlineStr">
+        <is>
+          <t>Treasury basis trade (hidden leverage)</t>
+        </is>
+      </c>
+      <c r="D716" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E716" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F716" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G716" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H716" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B717" s="9" t="inlineStr">
+        <is>
+          <t>s2_japan</t>
+        </is>
+      </c>
+      <c r="C717" s="9" t="inlineStr">
+        <is>
+          <t>Japan fiscal / JGB / carry trade</t>
+        </is>
+      </c>
+      <c r="D717" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E717" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F717" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G717" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H717" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B718" s="9" t="inlineStr">
+        <is>
+          <t>s3_private_credit</t>
+        </is>
+      </c>
+      <c r="C718" s="9" t="inlineStr">
+        <is>
+          <t>Private credit's opaque expansion</t>
+        </is>
+      </c>
+      <c r="D718" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E718" s="9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F718" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G718" s="9" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="H718" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B719" s="9" t="inlineStr">
+        <is>
+          <t>s4_dev_debt</t>
+        </is>
+      </c>
+      <c r="C719" s="9" t="inlineStr">
+        <is>
+          <t>Developing-world debt crisis</t>
+        </is>
+      </c>
+      <c r="D719" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E719" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F719" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G719" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H719" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B720" s="9" t="inlineStr">
+        <is>
+          <t>s5_china_deflation</t>
+        </is>
+      </c>
+      <c r="C720" s="9" t="inlineStr">
+        <is>
+          <t>China's price spillover (deflation or cost-push)</t>
+        </is>
+      </c>
+      <c r="D720" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E720" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F720" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G720" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H720" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B721" s="9" t="inlineStr">
+        <is>
+          <t>s6_rare_earths</t>
+        </is>
+      </c>
+      <c r="C721" s="9" t="inlineStr">
+        <is>
+          <t>Critical minerals as a weapon</t>
+        </is>
+      </c>
+      <c r="D721" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E721" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F721" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G721" s="9" t="inlineStr">
+        <is>
+          <t>6.75</t>
+        </is>
+      </c>
+      <c r="H721" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B722" s="9" t="inlineStr">
+        <is>
+          <t>s7_stablecoins</t>
+        </is>
+      </c>
+      <c r="C722" s="9" t="inlineStr">
+        <is>
+          <t>Stablecoins &amp; Treasury demand</t>
+        </is>
+      </c>
+      <c r="D722" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E722" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F722" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G722" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H722" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B723" s="9" t="inlineStr">
+        <is>
+          <t>s8_ai_capex</t>
+        </is>
+      </c>
+      <c r="C723" s="9" t="inlineStr">
+        <is>
+          <t>AI build-out circular financing</t>
+        </is>
+      </c>
+      <c r="D723" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E723" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F723" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G723" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H723" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B724" s="9" t="inlineStr">
+        <is>
+          <t>s9_cre</t>
+        </is>
+      </c>
+      <c r="C724" s="9" t="inlineStr">
+        <is>
+          <t>CRE maturity wall / regional banks</t>
+        </is>
+      </c>
+      <c r="D724" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E724" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F724" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G724" s="9" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="H724" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B725" s="9" t="inlineStr">
+        <is>
+          <t>s10_france</t>
+        </is>
+      </c>
+      <c r="C725" s="9" t="inlineStr">
+        <is>
+          <t>France / eurozone fragility</t>
+        </is>
+      </c>
+      <c r="D725" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E725" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F725" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G725" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H725" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B726" s="9" t="inlineStr">
+        <is>
+          <t>s11_consumer_debt</t>
+        </is>
+      </c>
+      <c r="C726" s="9" t="inlineStr">
+        <is>
+          <t>Hidden consumer debt</t>
+        </is>
+      </c>
+      <c r="D726" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E726" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F726" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G726" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H726" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B727" s="9" t="inlineStr">
+        <is>
+          <t>s12_gold_dedollar</t>
+        </is>
+      </c>
+      <c r="C727" s="9" t="inlineStr">
+        <is>
+          <t>Gold / de-dollarization</t>
+        </is>
+      </c>
+      <c r="D727" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E727" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F727" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G727" s="9" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="H727" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B728" s="9" t="inlineStr">
+        <is>
+          <t>s13_insurance</t>
+        </is>
+      </c>
+      <c r="C728" s="9" t="inlineStr">
+        <is>
+          <t>Insurance retreat</t>
+        </is>
+      </c>
+      <c r="D728" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E728" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F728" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G728" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H728" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B729" s="9" t="inlineStr">
+        <is>
+          <t>s14_pensions</t>
+        </is>
+      </c>
+      <c r="C729" s="9" t="inlineStr">
+        <is>
+          <t>Pensions / demographics</t>
+        </is>
+      </c>
+      <c r="D729" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E729" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F729" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G729" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H729" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B730" s="9" t="inlineStr">
+        <is>
+          <t>s15_ai_power</t>
+        </is>
+      </c>
+      <c r="C730" s="9" t="inlineStr">
+        <is>
+          <t>AI power &amp; the grid bottleneck</t>
+        </is>
+      </c>
+      <c r="D730" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E730" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F730" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G730" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H730" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B731" s="9" t="inlineStr">
+        <is>
+          <t>s16_copper</t>
+        </is>
+      </c>
+      <c r="C731" s="9" t="inlineStr">
+        <is>
+          <t>Copper &amp; the electrification deficit</t>
+        </is>
+      </c>
+      <c r="D731" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E731" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F731" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G731" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H731" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B732" s="9" t="inlineStr">
+        <is>
+          <t>s17_water</t>
+        </is>
+      </c>
+      <c r="C732" s="9" t="inlineStr">
+        <is>
+          <t>Water - the underpriced input</t>
+        </is>
+      </c>
+      <c r="D732" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E732" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F732" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G732" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H732" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B733" s="9" t="inlineStr">
+        <is>
+          <t>s18_food_fertilizer</t>
+        </is>
+      </c>
+      <c r="C733" s="9" t="inlineStr">
+        <is>
+          <t>Food &amp; fertilizer fragility</t>
+        </is>
+      </c>
+      <c r="D733" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E733" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F733" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G733" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H733" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B734" s="9" t="inlineStr">
+        <is>
+          <t>s19_lithography</t>
+        </is>
+      </c>
+      <c r="C734" s="9" t="inlineStr">
+        <is>
+          <t>The lithography (ASML) chokepoint</t>
+        </is>
+      </c>
+      <c r="D734" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E734" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F734" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G734" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H734" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B735" s="9" t="inlineStr">
+        <is>
+          <t>s20_sea_lanes</t>
+        </is>
+      </c>
+      <c r="C735" s="9" t="inlineStr">
+        <is>
+          <t>Sea lanes &amp; undersea cables</t>
+        </is>
+      </c>
+      <c r="D735" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E735" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F735" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G735" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H735" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B736" s="9" t="inlineStr">
+        <is>
+          <t>s21_clearinghouses</t>
+        </is>
+      </c>
+      <c r="C736" s="9" t="inlineStr">
+        <is>
+          <t>Clearinghouses (financial chokepoint)</t>
+        </is>
+      </c>
+      <c r="D736" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E736" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F736" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G736" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H736" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -34627,7 +35509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A28"/>
+  <dimension ref="A1:A25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -34708,14 +35590,14 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>--- Daily narrative (2026-07-27) ---</t>
+          <t>--- Daily narrative (2026-07-28) ---</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>**EOD BRIEF | 2026-07-27**</t>
+          <t>**EOD MACRO-RISK BRIEF | 28 July 2026**</t>
         </is>
       </c>
     </row>
@@ -34732,7 +35614,7 @@
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>Overall macro risk elevated to 7.9 as supply-chain fragility and emerging-market debt pressures intensify.</t>
+          <t>Systemic risk remains High, driven by opaque leverage in credit markets, geopolitical weaponization of critical inputs, and structural vulnerabilities spanning finance, energy, and supply chains.</t>
         </is>
       </c>
     </row>
@@ -34742,7 +35624,7 @@
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>**Changes:**</t>
+          <t>**Key Stories (No intraday changes reported):**</t>
         </is>
       </c>
     </row>
@@ -34752,7 +35634,7 @@
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>• **Developing-world debt crisis** (5→6, Elevated): US 10-year real yields rose 50bp to 2.43%, raising refinancing costs for vulnerable sovereigns and increasing default risk.</t>
+          <t xml:space="preserve">**High-band risks:** Private credit's opaque expansion (level 8) poses the greatest shock potential via hidden counterparty exposure. Japan's fiscal-JGB-carry nexus, China's deflationary spillover, critical minerals weaponization, AI power-grid bottlenecks, food-fertilizer fragility, and sea lanes/undersea cable disruption each remain systemic touch-points. </t>
         </is>
       </c>
     </row>
@@ -34762,7 +35644,7 @@
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>• **Food &amp; fertilizer fragility** (6→7, High): China tightened fertilizer export curbs and Gulf/Hormuz fertilizer inputs remain cut, compressing global agricultural supply ahead of harvest season.</t>
+          <t>**Elevated-band risks:** Treasury basis trades, developing-world debt, AI circular financing, CRE maturity walls, eurozone fragility, hidden consumer debt, ASML lithography chokepoint, and water underpricing all warrant continued monitoring.</t>
         </is>
       </c>
     </row>
@@ -34772,24 +35654,7 @@
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>• **Hidden consumer debt** (6→5, Elevated): Risk moderated with no new drivers reported; however, debt servicing remains structurally vulnerable.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="12" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>**Watch:**</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="12" t="inlineStr">
-        <is>
-          <t>Private credit's opaque expansion (level 8, High) remains the highest systemic risk, with no visibility into counterparty leverage or mark-to-market stress in downturn scenarios.</t>
+          <t>**Watch closest:** Private credit's opaque expansion—level 8—remains the highest-intensity risk; opacity prevents real-time contagion assessment and magnifies tail-event probability.</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-07-28  -  generated 2026-07-28 13:16 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-07-29  -  generated 2026-07-29 13:20 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
         </is>
       </c>
       <c r="D2" s="7" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="D3" s="7" t="n">
-        <v>77.2128</v>
+        <v>76.0938</v>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>163.873</v>
+        <v>163.764</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>3.969</v>
+        <v>3.98</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>2.79</v>
+        <v>2.81</v>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>6.7595</v>
+        <v>6.7559</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>307.9</v>
+        <v>307.7</v>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>4033.3999</v>
+        <v>4074.7</v>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>6.313</v>
+        <v>6.304</v>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="D60" s="7" t="n">
-        <v>81.19</v>
+        <v>84.51000000000001</v>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="D62" s="7" t="n">
-        <v>18.71</v>
+        <v>18.86</v>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
         </is>
       </c>
       <c r="D63" s="7" t="n">
-        <v>77.2128</v>
+        <v>76.0938</v>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H736"/>
+  <dimension ref="A1:H757"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -35498,6 +35498,888 @@
         </is>
       </c>
     </row>
+    <row r="737">
+      <c r="A737" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B737" s="9" t="inlineStr">
+        <is>
+          <t>s1_basis_trade</t>
+        </is>
+      </c>
+      <c r="C737" s="9" t="inlineStr">
+        <is>
+          <t>Treasury basis trade (hidden leverage)</t>
+        </is>
+      </c>
+      <c r="D737" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E737" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F737" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G737" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H737" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B738" s="9" t="inlineStr">
+        <is>
+          <t>s2_japan</t>
+        </is>
+      </c>
+      <c r="C738" s="9" t="inlineStr">
+        <is>
+          <t>Japan fiscal / JGB / carry trade</t>
+        </is>
+      </c>
+      <c r="D738" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E738" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F738" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G738" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H738" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B739" s="9" t="inlineStr">
+        <is>
+          <t>s3_private_credit</t>
+        </is>
+      </c>
+      <c r="C739" s="9" t="inlineStr">
+        <is>
+          <t>Private credit's opaque expansion</t>
+        </is>
+      </c>
+      <c r="D739" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E739" s="9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F739" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G739" s="9" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="H739" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B740" s="9" t="inlineStr">
+        <is>
+          <t>s4_dev_debt</t>
+        </is>
+      </c>
+      <c r="C740" s="9" t="inlineStr">
+        <is>
+          <t>Developing-world debt crisis</t>
+        </is>
+      </c>
+      <c r="D740" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E740" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F740" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G740" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H740" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B741" s="9" t="inlineStr">
+        <is>
+          <t>s5_china_deflation</t>
+        </is>
+      </c>
+      <c r="C741" s="9" t="inlineStr">
+        <is>
+          <t>China's price spillover (deflation or cost-push)</t>
+        </is>
+      </c>
+      <c r="D741" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E741" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F741" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G741" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H741" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B742" s="9" t="inlineStr">
+        <is>
+          <t>s6_rare_earths</t>
+        </is>
+      </c>
+      <c r="C742" s="9" t="inlineStr">
+        <is>
+          <t>Critical minerals as a weapon</t>
+        </is>
+      </c>
+      <c r="D742" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E742" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F742" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G742" s="9" t="inlineStr">
+        <is>
+          <t>6.75</t>
+        </is>
+      </c>
+      <c r="H742" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B743" s="9" t="inlineStr">
+        <is>
+          <t>s7_stablecoins</t>
+        </is>
+      </c>
+      <c r="C743" s="9" t="inlineStr">
+        <is>
+          <t>Stablecoins &amp; Treasury demand</t>
+        </is>
+      </c>
+      <c r="D743" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E743" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F743" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G743" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H743" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B744" s="9" t="inlineStr">
+        <is>
+          <t>s8_ai_capex</t>
+        </is>
+      </c>
+      <c r="C744" s="9" t="inlineStr">
+        <is>
+          <t>AI build-out circular financing</t>
+        </is>
+      </c>
+      <c r="D744" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E744" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F744" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G744" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H744" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B745" s="9" t="inlineStr">
+        <is>
+          <t>s9_cre</t>
+        </is>
+      </c>
+      <c r="C745" s="9" t="inlineStr">
+        <is>
+          <t>CRE maturity wall / regional banks</t>
+        </is>
+      </c>
+      <c r="D745" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E745" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F745" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G745" s="9" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="H745" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B746" s="9" t="inlineStr">
+        <is>
+          <t>s10_france</t>
+        </is>
+      </c>
+      <c r="C746" s="9" t="inlineStr">
+        <is>
+          <t>France / eurozone fragility</t>
+        </is>
+      </c>
+      <c r="D746" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E746" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F746" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G746" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H746" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B747" s="9" t="inlineStr">
+        <is>
+          <t>s11_consumer_debt</t>
+        </is>
+      </c>
+      <c r="C747" s="9" t="inlineStr">
+        <is>
+          <t>Hidden consumer debt</t>
+        </is>
+      </c>
+      <c r="D747" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E747" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F747" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G747" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H747" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B748" s="9" t="inlineStr">
+        <is>
+          <t>s12_gold_dedollar</t>
+        </is>
+      </c>
+      <c r="C748" s="9" t="inlineStr">
+        <is>
+          <t>Gold / de-dollarization</t>
+        </is>
+      </c>
+      <c r="D748" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E748" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F748" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G748" s="9" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="H748" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B749" s="9" t="inlineStr">
+        <is>
+          <t>s13_insurance</t>
+        </is>
+      </c>
+      <c r="C749" s="9" t="inlineStr">
+        <is>
+          <t>Insurance retreat</t>
+        </is>
+      </c>
+      <c r="D749" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E749" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F749" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G749" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H749" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B750" s="9" t="inlineStr">
+        <is>
+          <t>s14_pensions</t>
+        </is>
+      </c>
+      <c r="C750" s="9" t="inlineStr">
+        <is>
+          <t>Pensions / demographics</t>
+        </is>
+      </c>
+      <c r="D750" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E750" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F750" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G750" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H750" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B751" s="9" t="inlineStr">
+        <is>
+          <t>s15_ai_power</t>
+        </is>
+      </c>
+      <c r="C751" s="9" t="inlineStr">
+        <is>
+          <t>AI power &amp; the grid bottleneck</t>
+        </is>
+      </c>
+      <c r="D751" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E751" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F751" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G751" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H751" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B752" s="9" t="inlineStr">
+        <is>
+          <t>s16_copper</t>
+        </is>
+      </c>
+      <c r="C752" s="9" t="inlineStr">
+        <is>
+          <t>Copper &amp; the electrification deficit</t>
+        </is>
+      </c>
+      <c r="D752" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E752" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F752" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G752" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H752" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B753" s="9" t="inlineStr">
+        <is>
+          <t>s17_water</t>
+        </is>
+      </c>
+      <c r="C753" s="9" t="inlineStr">
+        <is>
+          <t>Water - the underpriced input</t>
+        </is>
+      </c>
+      <c r="D753" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E753" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F753" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G753" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H753" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B754" s="9" t="inlineStr">
+        <is>
+          <t>s18_food_fertilizer</t>
+        </is>
+      </c>
+      <c r="C754" s="9" t="inlineStr">
+        <is>
+          <t>Food &amp; fertilizer fragility</t>
+        </is>
+      </c>
+      <c r="D754" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E754" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F754" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G754" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H754" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B755" s="9" t="inlineStr">
+        <is>
+          <t>s19_lithography</t>
+        </is>
+      </c>
+      <c r="C755" s="9" t="inlineStr">
+        <is>
+          <t>The lithography (ASML) chokepoint</t>
+        </is>
+      </c>
+      <c r="D755" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E755" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F755" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G755" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H755" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B756" s="9" t="inlineStr">
+        <is>
+          <t>s20_sea_lanes</t>
+        </is>
+      </c>
+      <c r="C756" s="9" t="inlineStr">
+        <is>
+          <t>Sea lanes &amp; undersea cables</t>
+        </is>
+      </c>
+      <c r="D756" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E756" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F756" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G756" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H756" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B757" s="9" t="inlineStr">
+        <is>
+          <t>s21_clearinghouses</t>
+        </is>
+      </c>
+      <c r="C757" s="9" t="inlineStr">
+        <is>
+          <t>Clearinghouses (financial chokepoint)</t>
+        </is>
+      </c>
+      <c r="D757" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E757" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F757" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G757" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H757" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -35509,7 +36391,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A25"/>
+  <dimension ref="A1:A23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -35590,71 +36472,65 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>--- Daily narrative (2026-07-28) ---</t>
+          <t>--- Daily narrative (2026-07-29) ---</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>**EOD MACRO-RISK BRIEF | 28 July 2026**</t>
+          <t xml:space="preserve">**HEADLINE**  </t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr"/>
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>Macro risk stands at High, driven by structural leverage in credit markets, geopolitical supply-chain weaponization, and systemic interconnections across AI, energy, and semiconductors.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>**Headline:**</t>
-        </is>
-      </c>
+      <c r="A16" s="12" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>Systemic risk remains High, driven by opaque leverage in credit markets, geopolitical weaponization of critical inputs, and structural vulnerabilities spanning finance, energy, and supply chains.</t>
+          <t xml:space="preserve">**KEY STORIES (No changes today)**  </t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="inlineStr"/>
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Four stories remain at High band: Japan's fiscal/JGB/carry trade complex; private credit's opaque $2T+ expansion; China's deflationary spillover; critical minerals as geopolitical tools; AI power demand straining grid capacity; food/fertilizer fragility; and sea lanes/undersea cable vulnerability.  </t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>**Key Stories (No intraday changes reported):**</t>
-        </is>
-      </c>
+      <c r="A19" s="12" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr"/>
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>Six Elevated-band stories persist: Treasury basis trades embedding hidden leverage; developing-world debt stress; AI build-out circular financing; CRE maturity wall pressure; eurozone fragility; hidden consumer debt; ASML lithography chokepoint; and water input underpricing.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">**High-band risks:** Private credit's opaque expansion (level 8) poses the greatest shock potential via hidden counterparty exposure. Japan's fiscal-JGB-carry nexus, China's deflationary spillover, critical minerals weaponization, AI power-grid bottlenecks, food-fertilizer fragility, and sea lanes/undersea cable disruption each remain systemic touch-points. </t>
-        </is>
-      </c>
+      <c r="A21" s="12" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="inlineStr"/>
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">**WATCH**  </t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>**Elevated-band risks:** Treasury basis trades, developing-world debt, AI circular financing, CRE maturity walls, eurozone fragility, hidden consumer debt, ASML lithography chokepoint, and water underpricing all warrant continued monitoring.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="12" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>**Watch closest:** Private credit's opaque expansion—level 8—remains the highest-intensity risk; opacity prevents real-time contagion assessment and magnifies tail-event probability.</t>
+          <t>Private credit (level 8) remains highest risk—opacity, maturity mismatch, and pro-cyclical forced selling in a shock create systemic contagion vectors.</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-07-29  -  generated 2026-07-29 13:20 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-07-30  -  generated 2026-07-30 13:11 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="D3" s="7" t="n">
-        <v>76.0938</v>
+        <v>74.181</v>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>163.764</v>
+        <v>162.874</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>3.98</v>
+        <v>3.941</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>2.81</v>
+        <v>2.84</v>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>6.7559</v>
+        <v>6.7441</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>307.7</v>
+        <v>307.2</v>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>4074.7</v>
+        <v>4129</v>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>6.304</v>
+        <v>6.4405</v>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="D60" s="7" t="n">
-        <v>84.51000000000001</v>
+        <v>84.05</v>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="D62" s="7" t="n">
-        <v>18.86</v>
+        <v>19.05</v>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
         </is>
       </c>
       <c r="D63" s="7" t="n">
-        <v>76.0938</v>
+        <v>74.181</v>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H757"/>
+  <dimension ref="A1:H778"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -36380,6 +36380,888 @@
         </is>
       </c>
     </row>
+    <row r="758">
+      <c r="A758" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B758" s="9" t="inlineStr">
+        <is>
+          <t>s1_basis_trade</t>
+        </is>
+      </c>
+      <c r="C758" s="9" t="inlineStr">
+        <is>
+          <t>Treasury basis trade (hidden leverage)</t>
+        </is>
+      </c>
+      <c r="D758" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E758" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F758" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G758" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H758" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B759" s="9" t="inlineStr">
+        <is>
+          <t>s2_japan</t>
+        </is>
+      </c>
+      <c r="C759" s="9" t="inlineStr">
+        <is>
+          <t>Japan fiscal / JGB / carry trade</t>
+        </is>
+      </c>
+      <c r="D759" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E759" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F759" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G759" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H759" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B760" s="9" t="inlineStr">
+        <is>
+          <t>s3_private_credit</t>
+        </is>
+      </c>
+      <c r="C760" s="9" t="inlineStr">
+        <is>
+          <t>Private credit's opaque expansion</t>
+        </is>
+      </c>
+      <c r="D760" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E760" s="9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F760" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G760" s="9" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="H760" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B761" s="9" t="inlineStr">
+        <is>
+          <t>s4_dev_debt</t>
+        </is>
+      </c>
+      <c r="C761" s="9" t="inlineStr">
+        <is>
+          <t>Developing-world debt crisis</t>
+        </is>
+      </c>
+      <c r="D761" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E761" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F761" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G761" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H761" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B762" s="9" t="inlineStr">
+        <is>
+          <t>s5_china_deflation</t>
+        </is>
+      </c>
+      <c r="C762" s="9" t="inlineStr">
+        <is>
+          <t>China's price spillover (deflation or cost-push)</t>
+        </is>
+      </c>
+      <c r="D762" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E762" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F762" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G762" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H762" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B763" s="9" t="inlineStr">
+        <is>
+          <t>s6_rare_earths</t>
+        </is>
+      </c>
+      <c r="C763" s="9" t="inlineStr">
+        <is>
+          <t>Critical minerals as a weapon</t>
+        </is>
+      </c>
+      <c r="D763" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E763" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F763" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G763" s="9" t="inlineStr">
+        <is>
+          <t>6.75</t>
+        </is>
+      </c>
+      <c r="H763" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B764" s="9" t="inlineStr">
+        <is>
+          <t>s7_stablecoins</t>
+        </is>
+      </c>
+      <c r="C764" s="9" t="inlineStr">
+        <is>
+          <t>Stablecoins &amp; Treasury demand</t>
+        </is>
+      </c>
+      <c r="D764" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E764" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F764" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G764" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H764" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B765" s="9" t="inlineStr">
+        <is>
+          <t>s8_ai_capex</t>
+        </is>
+      </c>
+      <c r="C765" s="9" t="inlineStr">
+        <is>
+          <t>AI build-out circular financing</t>
+        </is>
+      </c>
+      <c r="D765" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E765" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F765" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G765" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H765" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B766" s="9" t="inlineStr">
+        <is>
+          <t>s9_cre</t>
+        </is>
+      </c>
+      <c r="C766" s="9" t="inlineStr">
+        <is>
+          <t>CRE maturity wall / regional banks</t>
+        </is>
+      </c>
+      <c r="D766" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E766" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F766" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G766" s="9" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="H766" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B767" s="9" t="inlineStr">
+        <is>
+          <t>s10_france</t>
+        </is>
+      </c>
+      <c r="C767" s="9" t="inlineStr">
+        <is>
+          <t>France / eurozone fragility</t>
+        </is>
+      </c>
+      <c r="D767" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E767" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F767" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G767" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H767" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B768" s="9" t="inlineStr">
+        <is>
+          <t>s11_consumer_debt</t>
+        </is>
+      </c>
+      <c r="C768" s="9" t="inlineStr">
+        <is>
+          <t>Hidden consumer debt</t>
+        </is>
+      </c>
+      <c r="D768" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E768" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F768" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G768" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H768" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B769" s="9" t="inlineStr">
+        <is>
+          <t>s12_gold_dedollar</t>
+        </is>
+      </c>
+      <c r="C769" s="9" t="inlineStr">
+        <is>
+          <t>Gold / de-dollarization</t>
+        </is>
+      </c>
+      <c r="D769" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E769" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F769" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G769" s="9" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="H769" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B770" s="9" t="inlineStr">
+        <is>
+          <t>s13_insurance</t>
+        </is>
+      </c>
+      <c r="C770" s="9" t="inlineStr">
+        <is>
+          <t>Insurance retreat</t>
+        </is>
+      </c>
+      <c r="D770" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E770" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F770" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G770" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H770" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B771" s="9" t="inlineStr">
+        <is>
+          <t>s14_pensions</t>
+        </is>
+      </c>
+      <c r="C771" s="9" t="inlineStr">
+        <is>
+          <t>Pensions / demographics</t>
+        </is>
+      </c>
+      <c r="D771" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E771" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F771" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G771" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H771" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B772" s="9" t="inlineStr">
+        <is>
+          <t>s15_ai_power</t>
+        </is>
+      </c>
+      <c r="C772" s="9" t="inlineStr">
+        <is>
+          <t>AI power &amp; the grid bottleneck</t>
+        </is>
+      </c>
+      <c r="D772" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E772" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F772" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G772" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H772" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B773" s="9" t="inlineStr">
+        <is>
+          <t>s16_copper</t>
+        </is>
+      </c>
+      <c r="C773" s="9" t="inlineStr">
+        <is>
+          <t>Copper &amp; the electrification deficit</t>
+        </is>
+      </c>
+      <c r="D773" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E773" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F773" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G773" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H773" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B774" s="9" t="inlineStr">
+        <is>
+          <t>s17_water</t>
+        </is>
+      </c>
+      <c r="C774" s="9" t="inlineStr">
+        <is>
+          <t>Water - the underpriced input</t>
+        </is>
+      </c>
+      <c r="D774" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E774" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F774" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G774" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H774" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B775" s="9" t="inlineStr">
+        <is>
+          <t>s18_food_fertilizer</t>
+        </is>
+      </c>
+      <c r="C775" s="9" t="inlineStr">
+        <is>
+          <t>Food &amp; fertilizer fragility</t>
+        </is>
+      </c>
+      <c r="D775" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E775" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F775" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G775" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H775" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B776" s="9" t="inlineStr">
+        <is>
+          <t>s19_lithography</t>
+        </is>
+      </c>
+      <c r="C776" s="9" t="inlineStr">
+        <is>
+          <t>The lithography (ASML) chokepoint</t>
+        </is>
+      </c>
+      <c r="D776" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E776" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F776" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G776" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H776" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B777" s="9" t="inlineStr">
+        <is>
+          <t>s20_sea_lanes</t>
+        </is>
+      </c>
+      <c r="C777" s="9" t="inlineStr">
+        <is>
+          <t>Sea lanes &amp; undersea cables</t>
+        </is>
+      </c>
+      <c r="D777" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E777" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F777" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G777" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H777" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B778" s="9" t="inlineStr">
+        <is>
+          <t>s21_clearinghouses</t>
+        </is>
+      </c>
+      <c r="C778" s="9" t="inlineStr">
+        <is>
+          <t>Clearinghouses (financial chokepoint)</t>
+        </is>
+      </c>
+      <c r="D778" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E778" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F778" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G778" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H778" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -36391,7 +37273,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A23"/>
+  <dimension ref="A1:A29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -36472,21 +37354,21 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>--- Daily narrative (2026-07-29) ---</t>
+          <t>--- Daily narrative (2026-07-30) ---</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">**HEADLINE**  </t>
+          <t>**HEADLINE**</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>Macro risk stands at High, driven by structural leverage in credit markets, geopolitical supply-chain weaponization, and systemic interconnections across AI, energy, and semiconductors.</t>
+          <t>Macro risk stands at High, with financial leverage, supply-chain weaponization, and commodity fragility dominating the risk surface.</t>
         </is>
       </c>
     </row>
@@ -36496,14 +37378,14 @@
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">**KEY STORIES (No changes today)**  </t>
+          <t>**STORIES WITH NO CHANGES TODAY**</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Four stories remain at High band: Japan's fiscal/JGB/carry trade complex; private credit's opaque $2T+ expansion; China's deflationary spillover; critical minerals as geopolitical tools; AI power demand straining grid capacity; food/fertilizer fragility; and sea lanes/undersea cable vulnerability.  </t>
+          <t>No risk-level movements recorded.</t>
         </is>
       </c>
     </row>
@@ -36513,24 +37395,66 @@
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>Six Elevated-band stories persist: Treasury basis trades embedding hidden leverage; developing-world debt stress; AI build-out circular financing; CRE maturity wall pressure; eurozone fragility; hidden consumer debt; ASML lithography chokepoint; and water input underpricing.</t>
+          <t>**ACTIVE RISKS TO MONITOR**</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr"/>
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>• **Private credit's opaque expansion** (High): Unregulated shadow lending now at systemic scale; opacity prevents early loss detection.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">**WATCH**  </t>
+          <t>• **Japan fiscal / JGB / carry trade** (High): BOJ policy divergence and yen carry unwind remain acute tail risks.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>Private credit (level 8) remains highest risk—opacity, maturity mismatch, and pro-cyclical forced selling in a shock create systemic contagion vectors.</t>
+          <t>• **China's price spillover** (High): Deflationary or stagflationary exports threaten global policy space and EM currency stability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>• **Food &amp; fertilizer fragility** (High): Supply concentration and geopolitical stress sustain input-cost volatility.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>• **Sea lanes &amp; undersea cables** (High): Chokepoint vulnerabilities persist in critical trade and telecom infrastructure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>• **AI power &amp; the grid bottleneck** (High): Compute demand outpacing power supply; investment cycle risk acute.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>**WATCH PRIORITY**</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>Private credit's opaque expansion (level 8) poses the highest-risk scenario: rapid loss recognition could trigger uncontrolled deleveraging across counterparties with no transparency cushion.</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-07-30  -  generated 2026-07-30 13:11 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-07-31  -  generated 2026-07-31 13:16 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="D3" s="7" t="n">
-        <v>74.181</v>
+        <v>77.0933</v>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>162.874</v>
+        <v>160.49</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>3.941</v>
+        <v>3.971</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>2.84</v>
+        <v>2.87</v>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>6.7441</v>
+        <v>6.7424</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.14</v>
+        <v>0.11</v>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>307.2</v>
+        <v>306.8</v>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>4129</v>
+        <v>4093.5</v>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>6.4405</v>
+        <v>6.494</v>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="D60" s="7" t="n">
-        <v>84.05</v>
+        <v>85.55</v>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="D62" s="7" t="n">
-        <v>19.05</v>
+        <v>17.26</v>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
         </is>
       </c>
       <c r="D63" s="7" t="n">
-        <v>74.181</v>
+        <v>77.0933</v>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H778"/>
+  <dimension ref="A1:H799"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -37262,6 +37262,888 @@
         </is>
       </c>
     </row>
+    <row r="779">
+      <c r="A779" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B779" s="9" t="inlineStr">
+        <is>
+          <t>s1_basis_trade</t>
+        </is>
+      </c>
+      <c r="C779" s="9" t="inlineStr">
+        <is>
+          <t>Treasury basis trade (hidden leverage)</t>
+        </is>
+      </c>
+      <c r="D779" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E779" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F779" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G779" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H779" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B780" s="9" t="inlineStr">
+        <is>
+          <t>s2_japan</t>
+        </is>
+      </c>
+      <c r="C780" s="9" t="inlineStr">
+        <is>
+          <t>Japan fiscal / JGB / carry trade</t>
+        </is>
+      </c>
+      <c r="D780" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E780" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F780" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G780" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H780" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B781" s="9" t="inlineStr">
+        <is>
+          <t>s3_private_credit</t>
+        </is>
+      </c>
+      <c r="C781" s="9" t="inlineStr">
+        <is>
+          <t>Private credit's opaque expansion</t>
+        </is>
+      </c>
+      <c r="D781" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E781" s="9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F781" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G781" s="9" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="H781" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B782" s="9" t="inlineStr">
+        <is>
+          <t>s4_dev_debt</t>
+        </is>
+      </c>
+      <c r="C782" s="9" t="inlineStr">
+        <is>
+          <t>Developing-world debt crisis</t>
+        </is>
+      </c>
+      <c r="D782" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E782" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F782" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G782" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H782" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B783" s="9" t="inlineStr">
+        <is>
+          <t>s5_china_deflation</t>
+        </is>
+      </c>
+      <c r="C783" s="9" t="inlineStr">
+        <is>
+          <t>China's price spillover (deflation or cost-push)</t>
+        </is>
+      </c>
+      <c r="D783" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E783" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F783" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G783" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H783" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B784" s="9" t="inlineStr">
+        <is>
+          <t>s6_rare_earths</t>
+        </is>
+      </c>
+      <c r="C784" s="9" t="inlineStr">
+        <is>
+          <t>Critical minerals as a weapon</t>
+        </is>
+      </c>
+      <c r="D784" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E784" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F784" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G784" s="9" t="inlineStr">
+        <is>
+          <t>6.75</t>
+        </is>
+      </c>
+      <c r="H784" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B785" s="9" t="inlineStr">
+        <is>
+          <t>s7_stablecoins</t>
+        </is>
+      </c>
+      <c r="C785" s="9" t="inlineStr">
+        <is>
+          <t>Stablecoins &amp; Treasury demand</t>
+        </is>
+      </c>
+      <c r="D785" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E785" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F785" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G785" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H785" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B786" s="9" t="inlineStr">
+        <is>
+          <t>s8_ai_capex</t>
+        </is>
+      </c>
+      <c r="C786" s="9" t="inlineStr">
+        <is>
+          <t>AI build-out circular financing</t>
+        </is>
+      </c>
+      <c r="D786" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E786" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F786" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G786" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H786" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B787" s="9" t="inlineStr">
+        <is>
+          <t>s9_cre</t>
+        </is>
+      </c>
+      <c r="C787" s="9" t="inlineStr">
+        <is>
+          <t>CRE maturity wall / regional banks</t>
+        </is>
+      </c>
+      <c r="D787" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E787" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F787" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G787" s="9" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="H787" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B788" s="9" t="inlineStr">
+        <is>
+          <t>s10_france</t>
+        </is>
+      </c>
+      <c r="C788" s="9" t="inlineStr">
+        <is>
+          <t>France / eurozone fragility</t>
+        </is>
+      </c>
+      <c r="D788" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E788" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F788" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G788" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H788" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B789" s="9" t="inlineStr">
+        <is>
+          <t>s11_consumer_debt</t>
+        </is>
+      </c>
+      <c r="C789" s="9" t="inlineStr">
+        <is>
+          <t>Hidden consumer debt</t>
+        </is>
+      </c>
+      <c r="D789" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E789" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F789" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G789" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H789" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B790" s="9" t="inlineStr">
+        <is>
+          <t>s12_gold_dedollar</t>
+        </is>
+      </c>
+      <c r="C790" s="9" t="inlineStr">
+        <is>
+          <t>Gold / de-dollarization</t>
+        </is>
+      </c>
+      <c r="D790" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E790" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F790" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G790" s="9" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="H790" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B791" s="9" t="inlineStr">
+        <is>
+          <t>s13_insurance</t>
+        </is>
+      </c>
+      <c r="C791" s="9" t="inlineStr">
+        <is>
+          <t>Insurance retreat</t>
+        </is>
+      </c>
+      <c r="D791" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E791" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F791" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G791" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H791" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B792" s="9" t="inlineStr">
+        <is>
+          <t>s14_pensions</t>
+        </is>
+      </c>
+      <c r="C792" s="9" t="inlineStr">
+        <is>
+          <t>Pensions / demographics</t>
+        </is>
+      </c>
+      <c r="D792" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E792" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F792" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G792" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H792" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B793" s="9" t="inlineStr">
+        <is>
+          <t>s15_ai_power</t>
+        </is>
+      </c>
+      <c r="C793" s="9" t="inlineStr">
+        <is>
+          <t>AI power &amp; the grid bottleneck</t>
+        </is>
+      </c>
+      <c r="D793" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E793" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F793" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G793" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H793" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B794" s="9" t="inlineStr">
+        <is>
+          <t>s16_copper</t>
+        </is>
+      </c>
+      <c r="C794" s="9" t="inlineStr">
+        <is>
+          <t>Copper &amp; the electrification deficit</t>
+        </is>
+      </c>
+      <c r="D794" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E794" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F794" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G794" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H794" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B795" s="9" t="inlineStr">
+        <is>
+          <t>s17_water</t>
+        </is>
+      </c>
+      <c r="C795" s="9" t="inlineStr">
+        <is>
+          <t>Water - the underpriced input</t>
+        </is>
+      </c>
+      <c r="D795" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E795" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F795" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G795" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H795" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B796" s="9" t="inlineStr">
+        <is>
+          <t>s18_food_fertilizer</t>
+        </is>
+      </c>
+      <c r="C796" s="9" t="inlineStr">
+        <is>
+          <t>Food &amp; fertilizer fragility</t>
+        </is>
+      </c>
+      <c r="D796" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E796" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F796" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G796" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H796" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B797" s="9" t="inlineStr">
+        <is>
+          <t>s19_lithography</t>
+        </is>
+      </c>
+      <c r="C797" s="9" t="inlineStr">
+        <is>
+          <t>The lithography (ASML) chokepoint</t>
+        </is>
+      </c>
+      <c r="D797" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E797" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F797" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G797" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H797" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B798" s="9" t="inlineStr">
+        <is>
+          <t>s20_sea_lanes</t>
+        </is>
+      </c>
+      <c r="C798" s="9" t="inlineStr">
+        <is>
+          <t>Sea lanes &amp; undersea cables</t>
+        </is>
+      </c>
+      <c r="D798" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E798" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F798" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G798" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H798" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B799" s="9" t="inlineStr">
+        <is>
+          <t>s21_clearinghouses</t>
+        </is>
+      </c>
+      <c r="C799" s="9" t="inlineStr">
+        <is>
+          <t>Clearinghouses (financial chokepoint)</t>
+        </is>
+      </c>
+      <c r="D799" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E799" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F799" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G799" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H799" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -37273,7 +38155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A29"/>
+  <dimension ref="A1:A30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -37354,7 +38236,7 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>--- Daily narrative (2026-07-30) ---</t>
+          <t>--- Daily narrative (2026-07-31) ---</t>
         </is>
       </c>
     </row>
@@ -37368,7 +38250,7 @@
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>Macro risk stands at High, with financial leverage, supply-chain weaponization, and commodity fragility dominating the risk surface.</t>
+          <t>Macro risk stands at High, driven by structural leverage in credit markets, geopolitical supply-chain weaponisation, and energy constraints tied to AI expansion.</t>
         </is>
       </c>
     </row>
@@ -37378,14 +38260,14 @@
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>**STORIES WITH NO CHANGES TODAY**</t>
+          <t>**STORY UPDATES**</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>No risk-level movements recorded.</t>
+          <t>No intraday level changes recorded.</t>
         </is>
       </c>
     </row>
@@ -37395,66 +38277,73 @@
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>**ACTIVE RISKS TO MONITOR**</t>
+          <t>**PERSISTENT ELEVATED OR HIGHER RISKS**</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>• **Private credit's opaque expansion** (High): Unregulated shadow lending now at systemic scale; opacity prevents early loss detection.</t>
+          <t>• **Private credit's opaque expansion** (High) — Rapid off-balance-sheet lending growth with limited regulatory visibility; default contagion risk if rates remain elevated.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>• **Japan fiscal / JGB / carry trade** (High): BOJ policy divergence and yen carry unwind remain acute tail risks.</t>
+          <t>• **Japan fiscal / JGB / carry trade** (High) — BOJ normalisation alongside unwind potential; systemic spillover to leveraged positions globally.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>• **China's price spillover** (High): Deflationary or stagflationary exports threaten global policy space and EM currency stability.</t>
+          <t>• **China's price spillover** (High) — Deflationary or input-cost shocks propagate through supply chains and emerging-market margins.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>• **Food &amp; fertilizer fragility** (High): Supply concentration and geopolitical stress sustain input-cost volatility.</t>
+          <t>• **Food &amp; fertilizer fragility** (High) — Supply concentration and geopolitical friction; inflation or shortage risk to commodity-dependent economies.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>• **Sea lanes &amp; undersea cables** (High): Chokepoint vulnerabilities persist in critical trade and telecom infrastructure.</t>
+          <t>• **Sea lanes &amp; undersea cables** (High) — Chokepoint exposure; trade disruption or comms failure in contested waters.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>• **AI power &amp; the grid bottleneck** (High): Compute demand outpacing power supply; investment cycle risk acute.</t>
+          <t>• **AI power &amp; the grid bottleneck** (High) — Electricity demand outpacing capacity; brownouts or cost pass-through.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="12" t="inlineStr"/>
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>• **Critical minerals as a weapon** (High) — Cartel or export control risk on rare earths and battery metals.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="12" t="inlineStr">
-        <is>
-          <t>**WATCH PRIORITY**</t>
-        </is>
-      </c>
+      <c r="A28" s="12" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>Private credit's opaque expansion (level 8) poses the highest-risk scenario: rapid loss recognition could trigger uncontrolled deleveraging across counterparties with no transparency cushion.</t>
+          <t>**WATCH CLOSEST**</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>Private credit opacity at High — largest tail risk if rates compress or defaults spike suddenly.</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-07-31  -  generated 2026-07-31 13:16 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-08-03  -  generated 2026-08-03 14:05 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
         </is>
       </c>
       <c r="D2" s="7" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="D3" s="7" t="n">
-        <v>77.0933</v>
+        <v>83.0244</v>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>160.49</v>
+        <v>156.505</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>3.971</v>
+        <v>3.982</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>2.87</v>
+        <v>2.84</v>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>6.7424</v>
+        <v>6.7422</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>306.8</v>
+        <v>306.6</v>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>4093.5</v>
+        <v>4084.8999</v>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
@@ -4009,7 +4009,7 @@
         </is>
       </c>
       <c r="D44" s="7" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>6.494</v>
+        <v>6.4635</v>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         </is>
       </c>
       <c r="D55" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         </is>
       </c>
       <c r="D59" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="D60" s="7" t="n">
-        <v>85.55</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         </is>
       </c>
       <c r="D61" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="D62" s="7" t="n">
-        <v>17.26</v>
+        <v>16.25</v>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
         </is>
       </c>
       <c r="D63" s="7" t="n">
-        <v>77.0933</v>
+        <v>83.0244</v>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
         </is>
       </c>
       <c r="D64" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H799"/>
+  <dimension ref="A1:H820"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -38144,6 +38144,888 @@
         </is>
       </c>
     </row>
+    <row r="800">
+      <c r="A800" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B800" s="9" t="inlineStr">
+        <is>
+          <t>s1_basis_trade</t>
+        </is>
+      </c>
+      <c r="C800" s="9" t="inlineStr">
+        <is>
+          <t>Treasury basis trade (hidden leverage)</t>
+        </is>
+      </c>
+      <c r="D800" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E800" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F800" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G800" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H800" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B801" s="9" t="inlineStr">
+        <is>
+          <t>s2_japan</t>
+        </is>
+      </c>
+      <c r="C801" s="9" t="inlineStr">
+        <is>
+          <t>Japan fiscal / JGB / carry trade</t>
+        </is>
+      </c>
+      <c r="D801" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E801" s="9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F801" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G801" s="9" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="H801" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B802" s="9" t="inlineStr">
+        <is>
+          <t>s3_private_credit</t>
+        </is>
+      </c>
+      <c r="C802" s="9" t="inlineStr">
+        <is>
+          <t>Private credit's opaque expansion</t>
+        </is>
+      </c>
+      <c r="D802" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E802" s="9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F802" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G802" s="9" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="H802" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B803" s="9" t="inlineStr">
+        <is>
+          <t>s4_dev_debt</t>
+        </is>
+      </c>
+      <c r="C803" s="9" t="inlineStr">
+        <is>
+          <t>Developing-world debt crisis</t>
+        </is>
+      </c>
+      <c r="D803" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E803" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F803" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G803" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="H803" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B804" s="9" t="inlineStr">
+        <is>
+          <t>s5_china_deflation</t>
+        </is>
+      </c>
+      <c r="C804" s="9" t="inlineStr">
+        <is>
+          <t>China's price spillover (deflation or cost-push)</t>
+        </is>
+      </c>
+      <c r="D804" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E804" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F804" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G804" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H804" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B805" s="9" t="inlineStr">
+        <is>
+          <t>s6_rare_earths</t>
+        </is>
+      </c>
+      <c r="C805" s="9" t="inlineStr">
+        <is>
+          <t>Critical minerals as a weapon</t>
+        </is>
+      </c>
+      <c r="D805" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E805" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F805" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G805" s="9" t="inlineStr">
+        <is>
+          <t>6.75</t>
+        </is>
+      </c>
+      <c r="H805" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B806" s="9" t="inlineStr">
+        <is>
+          <t>s7_stablecoins</t>
+        </is>
+      </c>
+      <c r="C806" s="9" t="inlineStr">
+        <is>
+          <t>Stablecoins &amp; Treasury demand</t>
+        </is>
+      </c>
+      <c r="D806" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E806" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F806" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G806" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H806" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B807" s="9" t="inlineStr">
+        <is>
+          <t>s8_ai_capex</t>
+        </is>
+      </c>
+      <c r="C807" s="9" t="inlineStr">
+        <is>
+          <t>AI build-out circular financing</t>
+        </is>
+      </c>
+      <c r="D807" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E807" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F807" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G807" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H807" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B808" s="9" t="inlineStr">
+        <is>
+          <t>s9_cre</t>
+        </is>
+      </c>
+      <c r="C808" s="9" t="inlineStr">
+        <is>
+          <t>CRE maturity wall / regional banks</t>
+        </is>
+      </c>
+      <c r="D808" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E808" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F808" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G808" s="9" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="H808" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B809" s="9" t="inlineStr">
+        <is>
+          <t>s10_france</t>
+        </is>
+      </c>
+      <c r="C809" s="9" t="inlineStr">
+        <is>
+          <t>France / eurozone fragility</t>
+        </is>
+      </c>
+      <c r="D809" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E809" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F809" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G809" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H809" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B810" s="9" t="inlineStr">
+        <is>
+          <t>s11_consumer_debt</t>
+        </is>
+      </c>
+      <c r="C810" s="9" t="inlineStr">
+        <is>
+          <t>Hidden consumer debt</t>
+        </is>
+      </c>
+      <c r="D810" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E810" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F810" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G810" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H810" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B811" s="9" t="inlineStr">
+        <is>
+          <t>s12_gold_dedollar</t>
+        </is>
+      </c>
+      <c r="C811" s="9" t="inlineStr">
+        <is>
+          <t>Gold / de-dollarization</t>
+        </is>
+      </c>
+      <c r="D811" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E811" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F811" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G811" s="9" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="H811" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B812" s="9" t="inlineStr">
+        <is>
+          <t>s13_insurance</t>
+        </is>
+      </c>
+      <c r="C812" s="9" t="inlineStr">
+        <is>
+          <t>Insurance retreat</t>
+        </is>
+      </c>
+      <c r="D812" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E812" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F812" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G812" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H812" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B813" s="9" t="inlineStr">
+        <is>
+          <t>s14_pensions</t>
+        </is>
+      </c>
+      <c r="C813" s="9" t="inlineStr">
+        <is>
+          <t>Pensions / demographics</t>
+        </is>
+      </c>
+      <c r="D813" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E813" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F813" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G813" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H813" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B814" s="9" t="inlineStr">
+        <is>
+          <t>s15_ai_power</t>
+        </is>
+      </c>
+      <c r="C814" s="9" t="inlineStr">
+        <is>
+          <t>AI power &amp; the grid bottleneck</t>
+        </is>
+      </c>
+      <c r="D814" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E814" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F814" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G814" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H814" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B815" s="9" t="inlineStr">
+        <is>
+          <t>s16_copper</t>
+        </is>
+      </c>
+      <c r="C815" s="9" t="inlineStr">
+        <is>
+          <t>Copper &amp; the electrification deficit</t>
+        </is>
+      </c>
+      <c r="D815" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E815" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F815" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G815" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H815" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B816" s="9" t="inlineStr">
+        <is>
+          <t>s17_water</t>
+        </is>
+      </c>
+      <c r="C816" s="9" t="inlineStr">
+        <is>
+          <t>Water - the underpriced input</t>
+        </is>
+      </c>
+      <c r="D816" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E816" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F816" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G816" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H816" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B817" s="9" t="inlineStr">
+        <is>
+          <t>s18_food_fertilizer</t>
+        </is>
+      </c>
+      <c r="C817" s="9" t="inlineStr">
+        <is>
+          <t>Food &amp; fertilizer fragility</t>
+        </is>
+      </c>
+      <c r="D817" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E817" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F817" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G817" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H817" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B818" s="9" t="inlineStr">
+        <is>
+          <t>s19_lithography</t>
+        </is>
+      </c>
+      <c r="C818" s="9" t="inlineStr">
+        <is>
+          <t>The lithography (ASML) chokepoint</t>
+        </is>
+      </c>
+      <c r="D818" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E818" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F818" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G818" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H818" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B819" s="9" t="inlineStr">
+        <is>
+          <t>s20_sea_lanes</t>
+        </is>
+      </c>
+      <c r="C819" s="9" t="inlineStr">
+        <is>
+          <t>Sea lanes &amp; undersea cables</t>
+        </is>
+      </c>
+      <c r="D819" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E819" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F819" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G819" s="9" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+      <c r="H819" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B820" s="9" t="inlineStr">
+        <is>
+          <t>s21_clearinghouses</t>
+        </is>
+      </c>
+      <c r="C820" s="9" t="inlineStr">
+        <is>
+          <t>Clearinghouses (financial chokepoint)</t>
+        </is>
+      </c>
+      <c r="D820" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E820" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F820" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G820" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H820" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -38155,7 +39037,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A30"/>
+  <dimension ref="A1:A26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -38236,7 +39118,7 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>--- Daily narrative (2026-07-31) ---</t>
+          <t>--- Daily narrative (2026-08-03) ---</t>
         </is>
       </c>
     </row>
@@ -38250,7 +39132,7 @@
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>Macro risk stands at High, driven by structural leverage in credit markets, geopolitical supply-chain weaponisation, and energy constraints tied to AI expansion.</t>
+          <t>Macro risk remains High, with Japan's carry-trade vulnerability sharpening while maritime and food-supply pressures ease moderately.</t>
         </is>
       </c>
     </row>
@@ -38260,90 +39142,54 @@
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>**STORY UPDATES**</t>
+          <t>**STORIES WITH LEVEL CHANGES**</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
-          <t>No intraday level changes recorded.</t>
-        </is>
-      </c>
+      <c r="A18" s="12" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr"/>
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>• **Japan fiscal / JGB / carry trade** (7→8, High): 30-year JGB yield jumped to 3.98% and Takaichi plan financing clarity deteriorated to "disorderly." Unwinding risk in yen carry trades and domestic debt-servicing pressures intensify.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
-          <t>**PERSISTENT ELEVATED OR HIGHER RISKS**</t>
-        </is>
-      </c>
+      <c r="A20" s="12" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>• **Private credit's opaque expansion** (High) — Rapid off-balance-sheet lending growth with limited regulatory visibility; default contagion risk if rates remain elevated.</t>
+          <t>• **Food &amp; fertilizer fragility** (7→6, Elevated): China's fertilizer export curbs remain tightened but no further escalation; global supply vulnerability persists despite score decline.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t>• **Japan fiscal / JGB / carry trade** (High) — BOJ normalisation alongside unwind potential; systemic spillover to leveraged positions globally.</t>
-        </is>
-      </c>
+      <c r="A22" s="12" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>• **China's price spillover** (High) — Deflationary or input-cost shocks propagate through supply chains and emerging-market margins.</t>
+          <t>• **Sea lanes &amp; undersea cables** (7→6, Elevated): Red Sea status improved from "closed" to "contested," WTI fell to $78.6/bbl, and cable-cut risk remains. Shipping cost relief offsets persistent infrastructure vulnerability.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="inlineStr">
-        <is>
-          <t>• **Food &amp; fertilizer fragility** (High) — Supply concentration and geopolitical friction; inflation or shortage risk to commodity-dependent economies.</t>
-        </is>
-      </c>
+      <c r="A24" s="12" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>• **Sea lanes &amp; undersea cables** (High) — Chokepoint exposure; trade disruption or comms failure in contested waters.</t>
+          <t>**WATCH**</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>• **AI power &amp; the grid bottleneck** (High) — Electricity demand outpacing capacity; brownouts or cost pass-through.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>• **Critical minerals as a weapon** (High) — Cartel or export control risk on rare earths and battery metals.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="12" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="12" t="inlineStr">
-        <is>
-          <t>**WATCH CLOSEST**</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="12" t="inlineStr">
-        <is>
-          <t>Private credit opacity at High — largest tail risk if rates compress or defaults spike suddenly.</t>
+          <t>Japan's carry trade—now High risk—poses tail-event contagion if BoJ guidance shifts further or global rate differentials compress.</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-08-03  -  generated 2026-08-03 14:05 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-08-04  -  generated 2026-08-04 13:20 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
         </is>
       </c>
       <c r="D2" s="7" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="D3" s="7" t="n">
-        <v>83.0244</v>
+        <v>80.48390000000001</v>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>156.505</v>
+        <v>157.5</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>120.7105</v>
+        <v>119.7034</v>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>2.41</v>
+        <v>2.47</v>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>6.7422</v>
+        <v>6.7392</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>306.6</v>
+        <v>306.8</v>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>4084.8999</v>
+        <v>4120.6001</v>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>6.4635</v>
+        <v>6.6325</v>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="D60" s="7" t="n">
-        <v>78.59999999999999</v>
+        <v>77.58</v>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="D62" s="7" t="n">
-        <v>16.25</v>
+        <v>15.58</v>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
         </is>
       </c>
       <c r="D63" s="7" t="n">
-        <v>83.0244</v>
+        <v>80.48390000000001</v>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H820"/>
+  <dimension ref="A1:H841"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -39026,6 +39026,888 @@
         </is>
       </c>
     </row>
+    <row r="821">
+      <c r="A821" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B821" s="9" t="inlineStr">
+        <is>
+          <t>s1_basis_trade</t>
+        </is>
+      </c>
+      <c r="C821" s="9" t="inlineStr">
+        <is>
+          <t>Treasury basis trade (hidden leverage)</t>
+        </is>
+      </c>
+      <c r="D821" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E821" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F821" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G821" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H821" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B822" s="9" t="inlineStr">
+        <is>
+          <t>s2_japan</t>
+        </is>
+      </c>
+      <c r="C822" s="9" t="inlineStr">
+        <is>
+          <t>Japan fiscal / JGB / carry trade</t>
+        </is>
+      </c>
+      <c r="D822" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E822" s="9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F822" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G822" s="9" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="H822" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B823" s="9" t="inlineStr">
+        <is>
+          <t>s3_private_credit</t>
+        </is>
+      </c>
+      <c r="C823" s="9" t="inlineStr">
+        <is>
+          <t>Private credit's opaque expansion</t>
+        </is>
+      </c>
+      <c r="D823" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E823" s="9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F823" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G823" s="9" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="H823" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B824" s="9" t="inlineStr">
+        <is>
+          <t>s4_dev_debt</t>
+        </is>
+      </c>
+      <c r="C824" s="9" t="inlineStr">
+        <is>
+          <t>Developing-world debt crisis</t>
+        </is>
+      </c>
+      <c r="D824" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E824" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F824" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G824" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="H824" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B825" s="9" t="inlineStr">
+        <is>
+          <t>s5_china_deflation</t>
+        </is>
+      </c>
+      <c r="C825" s="9" t="inlineStr">
+        <is>
+          <t>China's price spillover (deflation or cost-push)</t>
+        </is>
+      </c>
+      <c r="D825" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E825" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F825" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G825" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H825" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B826" s="9" t="inlineStr">
+        <is>
+          <t>s6_rare_earths</t>
+        </is>
+      </c>
+      <c r="C826" s="9" t="inlineStr">
+        <is>
+          <t>Critical minerals as a weapon</t>
+        </is>
+      </c>
+      <c r="D826" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E826" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F826" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G826" s="9" t="inlineStr">
+        <is>
+          <t>6.75</t>
+        </is>
+      </c>
+      <c r="H826" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B827" s="9" t="inlineStr">
+        <is>
+          <t>s7_stablecoins</t>
+        </is>
+      </c>
+      <c r="C827" s="9" t="inlineStr">
+        <is>
+          <t>Stablecoins &amp; Treasury demand</t>
+        </is>
+      </c>
+      <c r="D827" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E827" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F827" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G827" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H827" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B828" s="9" t="inlineStr">
+        <is>
+          <t>s8_ai_capex</t>
+        </is>
+      </c>
+      <c r="C828" s="9" t="inlineStr">
+        <is>
+          <t>AI build-out circular financing</t>
+        </is>
+      </c>
+      <c r="D828" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E828" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F828" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G828" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H828" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B829" s="9" t="inlineStr">
+        <is>
+          <t>s9_cre</t>
+        </is>
+      </c>
+      <c r="C829" s="9" t="inlineStr">
+        <is>
+          <t>CRE maturity wall / regional banks</t>
+        </is>
+      </c>
+      <c r="D829" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E829" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F829" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G829" s="9" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="H829" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B830" s="9" t="inlineStr">
+        <is>
+          <t>s10_france</t>
+        </is>
+      </c>
+      <c r="C830" s="9" t="inlineStr">
+        <is>
+          <t>France / eurozone fragility</t>
+        </is>
+      </c>
+      <c r="D830" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E830" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F830" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G830" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H830" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B831" s="9" t="inlineStr">
+        <is>
+          <t>s11_consumer_debt</t>
+        </is>
+      </c>
+      <c r="C831" s="9" t="inlineStr">
+        <is>
+          <t>Hidden consumer debt</t>
+        </is>
+      </c>
+      <c r="D831" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E831" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F831" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G831" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H831" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B832" s="9" t="inlineStr">
+        <is>
+          <t>s12_gold_dedollar</t>
+        </is>
+      </c>
+      <c r="C832" s="9" t="inlineStr">
+        <is>
+          <t>Gold / de-dollarization</t>
+        </is>
+      </c>
+      <c r="D832" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E832" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F832" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G832" s="9" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="H832" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B833" s="9" t="inlineStr">
+        <is>
+          <t>s13_insurance</t>
+        </is>
+      </c>
+      <c r="C833" s="9" t="inlineStr">
+        <is>
+          <t>Insurance retreat</t>
+        </is>
+      </c>
+      <c r="D833" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E833" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F833" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G833" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H833" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B834" s="9" t="inlineStr">
+        <is>
+          <t>s14_pensions</t>
+        </is>
+      </c>
+      <c r="C834" s="9" t="inlineStr">
+        <is>
+          <t>Pensions / demographics</t>
+        </is>
+      </c>
+      <c r="D834" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E834" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F834" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G834" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H834" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B835" s="9" t="inlineStr">
+        <is>
+          <t>s15_ai_power</t>
+        </is>
+      </c>
+      <c r="C835" s="9" t="inlineStr">
+        <is>
+          <t>AI power &amp; the grid bottleneck</t>
+        </is>
+      </c>
+      <c r="D835" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E835" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F835" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G835" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H835" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B836" s="9" t="inlineStr">
+        <is>
+          <t>s16_copper</t>
+        </is>
+      </c>
+      <c r="C836" s="9" t="inlineStr">
+        <is>
+          <t>Copper &amp; the electrification deficit</t>
+        </is>
+      </c>
+      <c r="D836" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E836" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F836" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G836" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H836" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B837" s="9" t="inlineStr">
+        <is>
+          <t>s17_water</t>
+        </is>
+      </c>
+      <c r="C837" s="9" t="inlineStr">
+        <is>
+          <t>Water - the underpriced input</t>
+        </is>
+      </c>
+      <c r="D837" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E837" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F837" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G837" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H837" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B838" s="9" t="inlineStr">
+        <is>
+          <t>s18_food_fertilizer</t>
+        </is>
+      </c>
+      <c r="C838" s="9" t="inlineStr">
+        <is>
+          <t>Food &amp; fertilizer fragility</t>
+        </is>
+      </c>
+      <c r="D838" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E838" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F838" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G838" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H838" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B839" s="9" t="inlineStr">
+        <is>
+          <t>s19_lithography</t>
+        </is>
+      </c>
+      <c r="C839" s="9" t="inlineStr">
+        <is>
+          <t>The lithography (ASML) chokepoint</t>
+        </is>
+      </c>
+      <c r="D839" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E839" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F839" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G839" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H839" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B840" s="9" t="inlineStr">
+        <is>
+          <t>s20_sea_lanes</t>
+        </is>
+      </c>
+      <c r="C840" s="9" t="inlineStr">
+        <is>
+          <t>Sea lanes &amp; undersea cables</t>
+        </is>
+      </c>
+      <c r="D840" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E840" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F840" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G840" s="9" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+      <c r="H840" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B841" s="9" t="inlineStr">
+        <is>
+          <t>s21_clearinghouses</t>
+        </is>
+      </c>
+      <c r="C841" s="9" t="inlineStr">
+        <is>
+          <t>Clearinghouses (financial chokepoint)</t>
+        </is>
+      </c>
+      <c r="D841" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E841" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F841" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G841" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H841" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -39037,7 +39919,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A26"/>
+  <dimension ref="A1:A20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -39118,78 +40000,44 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>--- Daily narrative (2026-08-03) ---</t>
+          <t>--- Daily narrative (2026-08-04) ---</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>**HEADLINE**</t>
+          <t># EOD Macro Risk Brief | 2026-08-04</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>Macro risk remains High, with Japan's carry-trade vulnerability sharpening while maritime and food-supply pressures ease moderately.</t>
-        </is>
-      </c>
+      <c r="A15" s="12" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr"/>
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>**Overall macro risk stands at High, driven by structural leverage and supply-chain concentration across finance and critical infrastructure.**</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>**STORIES WITH LEVEL CHANGES**</t>
-        </is>
-      </c>
+      <c r="A17" s="12" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="inlineStr"/>
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>**No intraday level changes recorded.** Risk composition remains stable with four High-band stories anchoring the aggregate: Japan's fiscal-JGB-carry nexus, private credit opacity, China's deflationary spillover, and AI power-grid bottlenecks. Six Elevated-band stories—including Treasury basis leverage, developing-world debt, and critical minerals weaponization—sustain pressure on secondary markets and emerging sovereigns.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>• **Japan fiscal / JGB / carry trade** (7→8, High): 30-year JGB yield jumped to 3.98% and Takaichi plan financing clarity deteriorated to "disorderly." Unwinding risk in yen carry trades and domestic debt-servicing pressures intensify.</t>
-        </is>
-      </c>
+      <c r="A19" s="12" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>• **Food &amp; fertilizer fragility** (7→6, Elevated): China's fertilizer export curbs remain tightened but no further escalation; global supply vulnerability persists despite score decline.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="12" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>• **Sea lanes &amp; undersea cables** (7→6, Elevated): Red Sea status improved from "closed" to "contested," WTI fell to $78.6/bbl, and cable-cut risk remains. Shipping cost relief offsets persistent infrastructure vulnerability.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="12" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>**WATCH**</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="12" t="inlineStr">
-        <is>
-          <t>Japan's carry trade—now High risk—poses tail-event contagion if BoJ guidance shifts further or global rate differentials compress.</t>
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>**Watch closest:** Japan fiscal / JGB / carry trade (High) — unwind dynamics in yen-funded positions remain the single highest-probability trigger for cross-asset volatility given leverage concentration and geopolitical JGB rollover risks.</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-08-04  -  generated 2026-08-04 13:20 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-08-05  -  generated 2026-08-05 13:18 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
         </is>
       </c>
       <c r="D2" s="7" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="D3" s="7" t="n">
-        <v>80.48390000000001</v>
+        <v>77.5565</v>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>157.5</v>
+        <v>157.572</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>3.982</v>
+        <v>3.99</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>2.47</v>
+        <v>2.43</v>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>6.7392</v>
+        <v>6.7371</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.11</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>306.8</v>
+        <v>306.9</v>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.8</v>
+        <v>0.78</v>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>4120.6001</v>
+        <v>4255.1001</v>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>6.6325</v>
+        <v>6.6985</v>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="D60" s="7" t="n">
-        <v>77.58</v>
+        <v>75.73</v>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="D62" s="7" t="n">
-        <v>15.58</v>
+        <v>16.86</v>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
         </is>
       </c>
       <c r="D63" s="7" t="n">
-        <v>80.48390000000001</v>
+        <v>77.5565</v>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H841"/>
+  <dimension ref="A1:H862"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -39908,6 +39908,888 @@
         </is>
       </c>
     </row>
+    <row r="842">
+      <c r="A842" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B842" s="9" t="inlineStr">
+        <is>
+          <t>s1_basis_trade</t>
+        </is>
+      </c>
+      <c r="C842" s="9" t="inlineStr">
+        <is>
+          <t>Treasury basis trade (hidden leverage)</t>
+        </is>
+      </c>
+      <c r="D842" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E842" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F842" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G842" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H842" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B843" s="9" t="inlineStr">
+        <is>
+          <t>s2_japan</t>
+        </is>
+      </c>
+      <c r="C843" s="9" t="inlineStr">
+        <is>
+          <t>Japan fiscal / JGB / carry trade</t>
+        </is>
+      </c>
+      <c r="D843" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E843" s="9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F843" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G843" s="9" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="H843" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B844" s="9" t="inlineStr">
+        <is>
+          <t>s3_private_credit</t>
+        </is>
+      </c>
+      <c r="C844" s="9" t="inlineStr">
+        <is>
+          <t>Private credit's opaque expansion</t>
+        </is>
+      </c>
+      <c r="D844" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E844" s="9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F844" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G844" s="9" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="H844" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B845" s="9" t="inlineStr">
+        <is>
+          <t>s4_dev_debt</t>
+        </is>
+      </c>
+      <c r="C845" s="9" t="inlineStr">
+        <is>
+          <t>Developing-world debt crisis</t>
+        </is>
+      </c>
+      <c r="D845" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E845" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F845" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G845" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="H845" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B846" s="9" t="inlineStr">
+        <is>
+          <t>s5_china_deflation</t>
+        </is>
+      </c>
+      <c r="C846" s="9" t="inlineStr">
+        <is>
+          <t>China's price spillover (deflation or cost-push)</t>
+        </is>
+      </c>
+      <c r="D846" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E846" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F846" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G846" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H846" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B847" s="9" t="inlineStr">
+        <is>
+          <t>s6_rare_earths</t>
+        </is>
+      </c>
+      <c r="C847" s="9" t="inlineStr">
+        <is>
+          <t>Critical minerals as a weapon</t>
+        </is>
+      </c>
+      <c r="D847" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E847" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F847" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G847" s="9" t="inlineStr">
+        <is>
+          <t>6.75</t>
+        </is>
+      </c>
+      <c r="H847" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B848" s="9" t="inlineStr">
+        <is>
+          <t>s7_stablecoins</t>
+        </is>
+      </c>
+      <c r="C848" s="9" t="inlineStr">
+        <is>
+          <t>Stablecoins &amp; Treasury demand</t>
+        </is>
+      </c>
+      <c r="D848" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E848" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F848" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G848" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H848" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B849" s="9" t="inlineStr">
+        <is>
+          <t>s8_ai_capex</t>
+        </is>
+      </c>
+      <c r="C849" s="9" t="inlineStr">
+        <is>
+          <t>AI build-out circular financing</t>
+        </is>
+      </c>
+      <c r="D849" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E849" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F849" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G849" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H849" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B850" s="9" t="inlineStr">
+        <is>
+          <t>s9_cre</t>
+        </is>
+      </c>
+      <c r="C850" s="9" t="inlineStr">
+        <is>
+          <t>CRE maturity wall / regional banks</t>
+        </is>
+      </c>
+      <c r="D850" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E850" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F850" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G850" s="9" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="H850" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B851" s="9" t="inlineStr">
+        <is>
+          <t>s10_france</t>
+        </is>
+      </c>
+      <c r="C851" s="9" t="inlineStr">
+        <is>
+          <t>France / eurozone fragility</t>
+        </is>
+      </c>
+      <c r="D851" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E851" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F851" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G851" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H851" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B852" s="9" t="inlineStr">
+        <is>
+          <t>s11_consumer_debt</t>
+        </is>
+      </c>
+      <c r="C852" s="9" t="inlineStr">
+        <is>
+          <t>Hidden consumer debt</t>
+        </is>
+      </c>
+      <c r="D852" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E852" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F852" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G852" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H852" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B853" s="9" t="inlineStr">
+        <is>
+          <t>s12_gold_dedollar</t>
+        </is>
+      </c>
+      <c r="C853" s="9" t="inlineStr">
+        <is>
+          <t>Gold / de-dollarization</t>
+        </is>
+      </c>
+      <c r="D853" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E853" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F853" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G853" s="9" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="H853" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B854" s="9" t="inlineStr">
+        <is>
+          <t>s13_insurance</t>
+        </is>
+      </c>
+      <c r="C854" s="9" t="inlineStr">
+        <is>
+          <t>Insurance retreat</t>
+        </is>
+      </c>
+      <c r="D854" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E854" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F854" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G854" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H854" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B855" s="9" t="inlineStr">
+        <is>
+          <t>s14_pensions</t>
+        </is>
+      </c>
+      <c r="C855" s="9" t="inlineStr">
+        <is>
+          <t>Pensions / demographics</t>
+        </is>
+      </c>
+      <c r="D855" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E855" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F855" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G855" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H855" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B856" s="9" t="inlineStr">
+        <is>
+          <t>s15_ai_power</t>
+        </is>
+      </c>
+      <c r="C856" s="9" t="inlineStr">
+        <is>
+          <t>AI power &amp; the grid bottleneck</t>
+        </is>
+      </c>
+      <c r="D856" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E856" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F856" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G856" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H856" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B857" s="9" t="inlineStr">
+        <is>
+          <t>s16_copper</t>
+        </is>
+      </c>
+      <c r="C857" s="9" t="inlineStr">
+        <is>
+          <t>Copper &amp; the electrification deficit</t>
+        </is>
+      </c>
+      <c r="D857" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E857" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F857" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G857" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H857" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B858" s="9" t="inlineStr">
+        <is>
+          <t>s17_water</t>
+        </is>
+      </c>
+      <c r="C858" s="9" t="inlineStr">
+        <is>
+          <t>Water - the underpriced input</t>
+        </is>
+      </c>
+      <c r="D858" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E858" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F858" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G858" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H858" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B859" s="9" t="inlineStr">
+        <is>
+          <t>s18_food_fertilizer</t>
+        </is>
+      </c>
+      <c r="C859" s="9" t="inlineStr">
+        <is>
+          <t>Food &amp; fertilizer fragility</t>
+        </is>
+      </c>
+      <c r="D859" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E859" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F859" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G859" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H859" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B860" s="9" t="inlineStr">
+        <is>
+          <t>s19_lithography</t>
+        </is>
+      </c>
+      <c r="C860" s="9" t="inlineStr">
+        <is>
+          <t>The lithography (ASML) chokepoint</t>
+        </is>
+      </c>
+      <c r="D860" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E860" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F860" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G860" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H860" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B861" s="9" t="inlineStr">
+        <is>
+          <t>s20_sea_lanes</t>
+        </is>
+      </c>
+      <c r="C861" s="9" t="inlineStr">
+        <is>
+          <t>Sea lanes &amp; undersea cables</t>
+        </is>
+      </c>
+      <c r="D861" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E861" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F861" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G861" s="9" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+      <c r="H861" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B862" s="9" t="inlineStr">
+        <is>
+          <t>s21_clearinghouses</t>
+        </is>
+      </c>
+      <c r="C862" s="9" t="inlineStr">
+        <is>
+          <t>Clearinghouses (financial chokepoint)</t>
+        </is>
+      </c>
+      <c r="D862" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E862" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F862" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G862" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H862" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -39919,7 +40801,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A20"/>
+  <dimension ref="A1:A26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -40000,34 +40882,38 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>--- Daily narrative (2026-08-04) ---</t>
+          <t>--- Daily narrative (2026-08-05) ---</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t># EOD Macro Risk Brief | 2026-08-04</t>
+          <t>**HEADLINE**</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr"/>
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>Macro risk stands at High, with four structural vulnerabilities—Japan's carry-trade exposure, opaque private credit, China's deflationary spillover, and critical minerals weaponization—posing concurrent systemic threats.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>**Overall macro risk stands at High, driven by structural leverage and supply-chain concentration across finance and critical infrastructure.**</t>
-        </is>
-      </c>
+      <c r="A16" s="12" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr"/>
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>**NO LEVEL CHANGES TODAY**</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>**No intraday level changes recorded.** Risk composition remains stable with four High-band stories anchoring the aggregate: Japan's fiscal-JGB-carry nexus, private credit opacity, China's deflationary spillover, and AI power-grid bottlenecks. Six Elevated-band stories—including Treasury basis leverage, developing-world debt, and critical minerals weaponization—sustain pressure on secondary markets and emerging sovereigns.</t>
+          <t>No stories moved between risk bands on 5 August.</t>
         </is>
       </c>
     </row>
@@ -40037,7 +40923,41 @@
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>**Watch closest:** Japan fiscal / JGB / carry trade (High) — unwind dynamics in yen-funded positions remain the single highest-probability trigger for cross-asset volatility given leverage concentration and geopolitical JGB rollover risks.</t>
+          <t>**PERSISTENT ELEVATED &amp; HIGH RISKS**</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>Four stories remain High: Japan fiscal/JGB/carry trade (BoJ normalization vulnerability); private credit's opaque expansion (leverage and opacity in shadow finance); China's price spillover (global disinflationary/stagflationary risk); AI power &amp; grid bottleneck (infrastructure constraint on tech capex cycle).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>Nine stories remain Elevated, including treasury basis hidden leverage, developing-world debt, AI circular financing, CRE maturity wall, eurozone fragility, hidden consumer debt, food/fertilizer fragility, ASML chokepoint, and sea lanes/undersea cables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>**TOP WATCH**</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>Japan fiscal/JGB/carry trade remains the highest-risk story; unwinding could trigger swift yen appreciation and forced deleveraging across global markets.</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-08-05  -  generated 2026-08-05 13:18 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-08-06  -  generated 2026-08-06 13:13 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
         </is>
       </c>
       <c r="D2" s="7" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="D3" s="7" t="n">
-        <v>77.5565</v>
+        <v>73.5809</v>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>157.572</v>
+        <v>157.912</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>3.99</v>
+        <v>3.966</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>2.78</v>
+        <v>2.73</v>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>6.7371</v>
+        <v>6.7376</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>306.9</v>
+        <v>307.8</v>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>4255.1001</v>
+        <v>4309.2998</v>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>6.6985</v>
+        <v>6.7555</v>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="D60" s="7" t="n">
-        <v>75.73</v>
+        <v>76.41</v>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="D62" s="7" t="n">
-        <v>16.86</v>
+        <v>15.97</v>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
         </is>
       </c>
       <c r="D63" s="7" t="n">
-        <v>77.5565</v>
+        <v>73.5809</v>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H862"/>
+  <dimension ref="A1:H883"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -40790,6 +40790,888 @@
         </is>
       </c>
     </row>
+    <row r="863">
+      <c r="A863" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B863" s="9" t="inlineStr">
+        <is>
+          <t>s1_basis_trade</t>
+        </is>
+      </c>
+      <c r="C863" s="9" t="inlineStr">
+        <is>
+          <t>Treasury basis trade (hidden leverage)</t>
+        </is>
+      </c>
+      <c r="D863" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E863" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F863" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G863" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H863" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B864" s="9" t="inlineStr">
+        <is>
+          <t>s2_japan</t>
+        </is>
+      </c>
+      <c r="C864" s="9" t="inlineStr">
+        <is>
+          <t>Japan fiscal / JGB / carry trade</t>
+        </is>
+      </c>
+      <c r="D864" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E864" s="9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F864" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G864" s="9" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="H864" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B865" s="9" t="inlineStr">
+        <is>
+          <t>s3_private_credit</t>
+        </is>
+      </c>
+      <c r="C865" s="9" t="inlineStr">
+        <is>
+          <t>Private credit's opaque expansion</t>
+        </is>
+      </c>
+      <c r="D865" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E865" s="9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F865" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G865" s="9" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="H865" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B866" s="9" t="inlineStr">
+        <is>
+          <t>s4_dev_debt</t>
+        </is>
+      </c>
+      <c r="C866" s="9" t="inlineStr">
+        <is>
+          <t>Developing-world debt crisis</t>
+        </is>
+      </c>
+      <c r="D866" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E866" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F866" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G866" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="H866" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B867" s="9" t="inlineStr">
+        <is>
+          <t>s5_china_deflation</t>
+        </is>
+      </c>
+      <c r="C867" s="9" t="inlineStr">
+        <is>
+          <t>China's price spillover (deflation or cost-push)</t>
+        </is>
+      </c>
+      <c r="D867" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E867" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F867" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G867" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H867" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B868" s="9" t="inlineStr">
+        <is>
+          <t>s6_rare_earths</t>
+        </is>
+      </c>
+      <c r="C868" s="9" t="inlineStr">
+        <is>
+          <t>Critical minerals as a weapon</t>
+        </is>
+      </c>
+      <c r="D868" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E868" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F868" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G868" s="9" t="inlineStr">
+        <is>
+          <t>6.75</t>
+        </is>
+      </c>
+      <c r="H868" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B869" s="9" t="inlineStr">
+        <is>
+          <t>s7_stablecoins</t>
+        </is>
+      </c>
+      <c r="C869" s="9" t="inlineStr">
+        <is>
+          <t>Stablecoins &amp; Treasury demand</t>
+        </is>
+      </c>
+      <c r="D869" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E869" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F869" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G869" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H869" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B870" s="9" t="inlineStr">
+        <is>
+          <t>s8_ai_capex</t>
+        </is>
+      </c>
+      <c r="C870" s="9" t="inlineStr">
+        <is>
+          <t>AI build-out circular financing</t>
+        </is>
+      </c>
+      <c r="D870" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E870" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F870" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G870" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H870" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B871" s="9" t="inlineStr">
+        <is>
+          <t>s9_cre</t>
+        </is>
+      </c>
+      <c r="C871" s="9" t="inlineStr">
+        <is>
+          <t>CRE maturity wall / regional banks</t>
+        </is>
+      </c>
+      <c r="D871" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E871" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F871" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G871" s="9" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="H871" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B872" s="9" t="inlineStr">
+        <is>
+          <t>s10_france</t>
+        </is>
+      </c>
+      <c r="C872" s="9" t="inlineStr">
+        <is>
+          <t>France / eurozone fragility</t>
+        </is>
+      </c>
+      <c r="D872" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E872" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F872" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G872" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H872" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B873" s="9" t="inlineStr">
+        <is>
+          <t>s11_consumer_debt</t>
+        </is>
+      </c>
+      <c r="C873" s="9" t="inlineStr">
+        <is>
+          <t>Hidden consumer debt</t>
+        </is>
+      </c>
+      <c r="D873" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E873" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F873" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G873" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H873" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B874" s="9" t="inlineStr">
+        <is>
+          <t>s12_gold_dedollar</t>
+        </is>
+      </c>
+      <c r="C874" s="9" t="inlineStr">
+        <is>
+          <t>Gold / de-dollarization</t>
+        </is>
+      </c>
+      <c r="D874" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E874" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F874" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G874" s="9" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="H874" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B875" s="9" t="inlineStr">
+        <is>
+          <t>s13_insurance</t>
+        </is>
+      </c>
+      <c r="C875" s="9" t="inlineStr">
+        <is>
+          <t>Insurance retreat</t>
+        </is>
+      </c>
+      <c r="D875" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E875" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F875" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G875" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H875" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B876" s="9" t="inlineStr">
+        <is>
+          <t>s14_pensions</t>
+        </is>
+      </c>
+      <c r="C876" s="9" t="inlineStr">
+        <is>
+          <t>Pensions / demographics</t>
+        </is>
+      </c>
+      <c r="D876" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E876" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F876" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G876" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H876" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B877" s="9" t="inlineStr">
+        <is>
+          <t>s15_ai_power</t>
+        </is>
+      </c>
+      <c r="C877" s="9" t="inlineStr">
+        <is>
+          <t>AI power &amp; the grid bottleneck</t>
+        </is>
+      </c>
+      <c r="D877" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E877" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F877" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G877" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H877" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B878" s="9" t="inlineStr">
+        <is>
+          <t>s16_copper</t>
+        </is>
+      </c>
+      <c r="C878" s="9" t="inlineStr">
+        <is>
+          <t>Copper &amp; the electrification deficit</t>
+        </is>
+      </c>
+      <c r="D878" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E878" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F878" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G878" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H878" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B879" s="9" t="inlineStr">
+        <is>
+          <t>s17_water</t>
+        </is>
+      </c>
+      <c r="C879" s="9" t="inlineStr">
+        <is>
+          <t>Water - the underpriced input</t>
+        </is>
+      </c>
+      <c r="D879" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E879" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F879" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G879" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H879" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B880" s="9" t="inlineStr">
+        <is>
+          <t>s18_food_fertilizer</t>
+        </is>
+      </c>
+      <c r="C880" s="9" t="inlineStr">
+        <is>
+          <t>Food &amp; fertilizer fragility</t>
+        </is>
+      </c>
+      <c r="D880" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E880" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F880" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G880" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H880" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B881" s="9" t="inlineStr">
+        <is>
+          <t>s19_lithography</t>
+        </is>
+      </c>
+      <c r="C881" s="9" t="inlineStr">
+        <is>
+          <t>The lithography (ASML) chokepoint</t>
+        </is>
+      </c>
+      <c r="D881" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E881" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F881" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G881" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H881" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B882" s="9" t="inlineStr">
+        <is>
+          <t>s20_sea_lanes</t>
+        </is>
+      </c>
+      <c r="C882" s="9" t="inlineStr">
+        <is>
+          <t>Sea lanes &amp; undersea cables</t>
+        </is>
+      </c>
+      <c r="D882" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E882" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F882" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G882" s="9" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+      <c r="H882" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B883" s="9" t="inlineStr">
+        <is>
+          <t>s21_clearinghouses</t>
+        </is>
+      </c>
+      <c r="C883" s="9" t="inlineStr">
+        <is>
+          <t>Clearinghouses (financial chokepoint)</t>
+        </is>
+      </c>
+      <c r="D883" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E883" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F883" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G883" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H883" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -40801,7 +41683,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A26"/>
+  <dimension ref="A1:A31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -40882,7 +41764,7 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>--- Daily narrative (2026-08-05) ---</t>
+          <t>--- Daily narrative (2026-08-06) ---</t>
         </is>
       </c>
     </row>
@@ -40896,7 +41778,7 @@
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>Macro risk stands at High, with four structural vulnerabilities—Japan's carry-trade exposure, opaque private credit, China's deflationary spillover, and critical minerals weaponization—posing concurrent systemic threats.</t>
+          <t>Macro risk stands at High, anchored by four critical structural vulnerabilities across finance, commodities, and geopolitics with no intraday changes.</t>
         </is>
       </c>
     </row>
@@ -40906,14 +41788,14 @@
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>**NO LEVEL CHANGES TODAY**</t>
+          <t>**KEY STORIES**</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>No stories moved between risk bands on 5 August.</t>
+          <t>No positions moved today. Persistent High-band risks include:</t>
         </is>
       </c>
     </row>
@@ -40923,41 +41805,64 @@
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>**PERSISTENT ELEVATED &amp; HIGH RISKS**</t>
+          <t>• **Japan fiscal/JGB/carry trade** – Structural imbalance in JGB yields and carry funding remains systemically exposed to rapid rate repricing.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>Four stories remain High: Japan fiscal/JGB/carry trade (BoJ normalization vulnerability); private credit's opaque expansion (leverage and opacity in shadow finance); China's price spillover (global disinflationary/stagflationary risk); AI power &amp; grid bottleneck (infrastructure constraint on tech capex cycle).</t>
-        </is>
-      </c>
+      <c r="A21" s="12" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="inlineStr"/>
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>• **Private credit's opaque expansion** – Unregulated growth and opacity in credit intermediation create contagion risk across institutional portfolios.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>Nine stories remain Elevated, including treasury basis hidden leverage, developing-world debt, AI circular financing, CRE maturity wall, eurozone fragility, hidden consumer debt, food/fertilizer fragility, ASML chokepoint, and sea lanes/undersea cables.</t>
-        </is>
-      </c>
+      <c r="A23" s="12" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="inlineStr"/>
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>• **China's price spillover** – Deflationary or cost-push transmission to global supply chains threatens margin compression across sectors.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>**TOP WATCH**</t>
-        </is>
-      </c>
+      <c r="A25" s="12" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>Japan fiscal/JGB/carry trade remains the highest-risk story; unwinding could trigger swift yen appreciation and forced deleveraging across global markets.</t>
+          <t>• **AI power &amp; grid bottleneck** – Accelerating compute demand outpacing grid capacity expansion creates infrastructure constraint.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>• **Critical minerals as a weapon** – Supply concentration and geopolitical leverage over energy transition inputs remain unresolved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>**WATCH CLOSEST**</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>Private credit opacity and Japan carry-trade stability—both offer limited visibility into stress propagation paths.</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-08-06  -  generated 2026-08-06 13:13 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-08-07  -  generated 2026-08-07 12:25 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="D3" s="7" t="n">
-        <v>73.5809</v>
+        <v>76.1169</v>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>157.912</v>
+        <v>158.335</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>3.966</v>
+        <v>3.919</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>6.7376</v>
+        <v>6.7372</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>307.8</v>
+        <v>307.7</v>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>4309.2998</v>
+        <v>4371.8999</v>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>6.7555</v>
+        <v>6.645</v>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="D60" s="7" t="n">
-        <v>76.41</v>
+        <v>77.09</v>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="D62" s="7" t="n">
-        <v>15.97</v>
+        <v>15.22</v>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
         </is>
       </c>
       <c r="D63" s="7" t="n">
-        <v>73.5809</v>
+        <v>76.1169</v>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H883"/>
+  <dimension ref="A1:H904"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -41672,6 +41672,888 @@
         </is>
       </c>
     </row>
+    <row r="884">
+      <c r="A884" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B884" s="9" t="inlineStr">
+        <is>
+          <t>s1_basis_trade</t>
+        </is>
+      </c>
+      <c r="C884" s="9" t="inlineStr">
+        <is>
+          <t>Treasury basis trade (hidden leverage)</t>
+        </is>
+      </c>
+      <c r="D884" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E884" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F884" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G884" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H884" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B885" s="9" t="inlineStr">
+        <is>
+          <t>s2_japan</t>
+        </is>
+      </c>
+      <c r="C885" s="9" t="inlineStr">
+        <is>
+          <t>Japan fiscal / JGB / carry trade</t>
+        </is>
+      </c>
+      <c r="D885" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E885" s="9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F885" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G885" s="9" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="H885" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B886" s="9" t="inlineStr">
+        <is>
+          <t>s3_private_credit</t>
+        </is>
+      </c>
+      <c r="C886" s="9" t="inlineStr">
+        <is>
+          <t>Private credit's opaque expansion</t>
+        </is>
+      </c>
+      <c r="D886" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E886" s="9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F886" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G886" s="9" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="H886" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B887" s="9" t="inlineStr">
+        <is>
+          <t>s4_dev_debt</t>
+        </is>
+      </c>
+      <c r="C887" s="9" t="inlineStr">
+        <is>
+          <t>Developing-world debt crisis</t>
+        </is>
+      </c>
+      <c r="D887" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E887" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F887" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G887" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="H887" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B888" s="9" t="inlineStr">
+        <is>
+          <t>s5_china_deflation</t>
+        </is>
+      </c>
+      <c r="C888" s="9" t="inlineStr">
+        <is>
+          <t>China's price spillover (deflation or cost-push)</t>
+        </is>
+      </c>
+      <c r="D888" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E888" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F888" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G888" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H888" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B889" s="9" t="inlineStr">
+        <is>
+          <t>s6_rare_earths</t>
+        </is>
+      </c>
+      <c r="C889" s="9" t="inlineStr">
+        <is>
+          <t>Critical minerals as a weapon</t>
+        </is>
+      </c>
+      <c r="D889" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E889" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F889" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G889" s="9" t="inlineStr">
+        <is>
+          <t>6.75</t>
+        </is>
+      </c>
+      <c r="H889" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B890" s="9" t="inlineStr">
+        <is>
+          <t>s7_stablecoins</t>
+        </is>
+      </c>
+      <c r="C890" s="9" t="inlineStr">
+        <is>
+          <t>Stablecoins &amp; Treasury demand</t>
+        </is>
+      </c>
+      <c r="D890" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E890" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F890" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G890" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H890" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B891" s="9" t="inlineStr">
+        <is>
+          <t>s8_ai_capex</t>
+        </is>
+      </c>
+      <c r="C891" s="9" t="inlineStr">
+        <is>
+          <t>AI build-out circular financing</t>
+        </is>
+      </c>
+      <c r="D891" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E891" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F891" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G891" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H891" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B892" s="9" t="inlineStr">
+        <is>
+          <t>s9_cre</t>
+        </is>
+      </c>
+      <c r="C892" s="9" t="inlineStr">
+        <is>
+          <t>CRE maturity wall / regional banks</t>
+        </is>
+      </c>
+      <c r="D892" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E892" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F892" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G892" s="9" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="H892" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B893" s="9" t="inlineStr">
+        <is>
+          <t>s10_france</t>
+        </is>
+      </c>
+      <c r="C893" s="9" t="inlineStr">
+        <is>
+          <t>France / eurozone fragility</t>
+        </is>
+      </c>
+      <c r="D893" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E893" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F893" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G893" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H893" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B894" s="9" t="inlineStr">
+        <is>
+          <t>s11_consumer_debt</t>
+        </is>
+      </c>
+      <c r="C894" s="9" t="inlineStr">
+        <is>
+          <t>Hidden consumer debt</t>
+        </is>
+      </c>
+      <c r="D894" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E894" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F894" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G894" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H894" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B895" s="9" t="inlineStr">
+        <is>
+          <t>s12_gold_dedollar</t>
+        </is>
+      </c>
+      <c r="C895" s="9" t="inlineStr">
+        <is>
+          <t>Gold / de-dollarization</t>
+        </is>
+      </c>
+      <c r="D895" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E895" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F895" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G895" s="9" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="H895" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B896" s="9" t="inlineStr">
+        <is>
+          <t>s13_insurance</t>
+        </is>
+      </c>
+      <c r="C896" s="9" t="inlineStr">
+        <is>
+          <t>Insurance retreat</t>
+        </is>
+      </c>
+      <c r="D896" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E896" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F896" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G896" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H896" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B897" s="9" t="inlineStr">
+        <is>
+          <t>s14_pensions</t>
+        </is>
+      </c>
+      <c r="C897" s="9" t="inlineStr">
+        <is>
+          <t>Pensions / demographics</t>
+        </is>
+      </c>
+      <c r="D897" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E897" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F897" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G897" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H897" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B898" s="9" t="inlineStr">
+        <is>
+          <t>s15_ai_power</t>
+        </is>
+      </c>
+      <c r="C898" s="9" t="inlineStr">
+        <is>
+          <t>AI power &amp; the grid bottleneck</t>
+        </is>
+      </c>
+      <c r="D898" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E898" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F898" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G898" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H898" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B899" s="9" t="inlineStr">
+        <is>
+          <t>s16_copper</t>
+        </is>
+      </c>
+      <c r="C899" s="9" t="inlineStr">
+        <is>
+          <t>Copper &amp; the electrification deficit</t>
+        </is>
+      </c>
+      <c r="D899" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E899" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F899" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G899" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H899" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B900" s="9" t="inlineStr">
+        <is>
+          <t>s17_water</t>
+        </is>
+      </c>
+      <c r="C900" s="9" t="inlineStr">
+        <is>
+          <t>Water - the underpriced input</t>
+        </is>
+      </c>
+      <c r="D900" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E900" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F900" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G900" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H900" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B901" s="9" t="inlineStr">
+        <is>
+          <t>s18_food_fertilizer</t>
+        </is>
+      </c>
+      <c r="C901" s="9" t="inlineStr">
+        <is>
+          <t>Food &amp; fertilizer fragility</t>
+        </is>
+      </c>
+      <c r="D901" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E901" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F901" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G901" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H901" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B902" s="9" t="inlineStr">
+        <is>
+          <t>s19_lithography</t>
+        </is>
+      </c>
+      <c r="C902" s="9" t="inlineStr">
+        <is>
+          <t>The lithography (ASML) chokepoint</t>
+        </is>
+      </c>
+      <c r="D902" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E902" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F902" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G902" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H902" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B903" s="9" t="inlineStr">
+        <is>
+          <t>s20_sea_lanes</t>
+        </is>
+      </c>
+      <c r="C903" s="9" t="inlineStr">
+        <is>
+          <t>Sea lanes &amp; undersea cables</t>
+        </is>
+      </c>
+      <c r="D903" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E903" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F903" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G903" s="9" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+      <c r="H903" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B904" s="9" t="inlineStr">
+        <is>
+          <t>s21_clearinghouses</t>
+        </is>
+      </c>
+      <c r="C904" s="9" t="inlineStr">
+        <is>
+          <t>Clearinghouses (financial chokepoint)</t>
+        </is>
+      </c>
+      <c r="D904" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E904" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F904" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G904" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H904" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -41683,7 +42565,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A31"/>
+  <dimension ref="A1:A28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -41764,7 +42646,7 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>--- Daily narrative (2026-08-06) ---</t>
+          <t>--- Daily narrative (2026-08-07) ---</t>
         </is>
       </c>
     </row>
@@ -41778,7 +42660,7 @@
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>Macro risk stands at High, anchored by four critical structural vulnerabilities across finance, commodities, and geopolitics with no intraday changes.</t>
+          <t>Macro risk stands at High, driven by four critical structural vulnerabilities: Japan's carry-trade and fiscal instability, opaque private credit expansion, China's deflationary spillover, and AI infrastructure financing circularity.</t>
         </is>
       </c>
     </row>
@@ -41788,81 +42670,64 @@
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>**KEY STORIES**</t>
+          <t>**STORIES (no intraday changes)**</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
-          <t>No positions moved today. Persistent High-band risks include:</t>
-        </is>
-      </c>
+      <c r="A18" s="12" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr"/>
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>• **Japan fiscal / JGB / carry trade** (High): Persistent yen weakness and fiscal stress sustain carry-trade unwind risk; sudden reversal could trigger forced deleveraging across global equities and credit.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
-          <t>• **Japan fiscal/JGB/carry trade** – Structural imbalance in JGB yields and carry funding remains systemically exposed to rapid rate repricing.</t>
-        </is>
-      </c>
+      <c r="A20" s="12" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr"/>
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>• **Private credit's opaque expansion** (High): Continued rapid growth in unregulated lending pools with poor transparency increases systemic contagion risk if rates or defaults accelerate.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t>• **Private credit's opaque expansion** – Unregulated growth and opacity in credit intermediation create contagion risk across institutional portfolios.</t>
-        </is>
-      </c>
+      <c r="A22" s="12" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="inlineStr"/>
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>• **China's price spillover** (High): Deflationary pressures exportable to developed economies risk margin compression and central bank policy divergence.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="inlineStr">
-        <is>
-          <t>• **China's price spillover** – Deflationary or cost-push transmission to global supply chains threatens margin compression across sectors.</t>
-        </is>
-      </c>
+      <c r="A24" s="12" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="inlineStr"/>
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>• **AI power &amp; the grid bottleneck** (High): Sustained demand surge outpacing grid capacity creates supply constraints and energy-cost volatility for capex-dependent sectors.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="12" t="inlineStr">
-        <is>
-          <t>• **AI power &amp; grid bottleneck** – Accelerating compute demand outpacing grid capacity expansion creates infrastructure constraint.</t>
-        </is>
-      </c>
+      <c r="A26" s="12" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="12" t="inlineStr"/>
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>**WATCH**</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>• **Critical minerals as a weapon** – Supply concentration and geopolitical leverage over energy transition inputs remain unresolved.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="12" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="12" t="inlineStr">
-        <is>
-          <t>**WATCH CLOSEST**</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="12" t="inlineStr">
-        <is>
-          <t>Private credit opacity and Japan carry-trade stability—both offer limited visibility into stress propagation paths.</t>
+          <t>Japan fiscal / JGB / carry trade remains the highest-risk trigger for sudden cross-asset volatility.</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-08-07  -  generated 2026-08-07 12:25 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-08-10  -  generated 2026-08-10 12:33 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
         </is>
       </c>
       <c r="D2" s="7" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="D3" s="7" t="n">
-        <v>76.1169</v>
+        <v>72.03019999999999</v>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>158.335</v>
+        <v>158.74</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>3.919</v>
+        <v>3.925</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>6.7372</v>
+        <v>6.7324</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>307.7</v>
+        <v>306.7</v>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
         </is>
       </c>
       <c r="D27" s="7" t="n">
-        <v>11.7</v>
+        <v>12.34</v>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
@@ -3330,7 +3330,7 @@
         </is>
       </c>
       <c r="D33" s="7" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>4371.8999</v>
+        <v>4389</v>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
@@ -4009,7 +4009,7 @@
         </is>
       </c>
       <c r="D44" s="7" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>6.645</v>
+        <v>6.6235</v>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="D52" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="D60" s="7" t="n">
-        <v>77.09</v>
+        <v>79.47</v>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         </is>
       </c>
       <c r="D61" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="D62" s="7" t="n">
-        <v>15.22</v>
+        <v>15.45</v>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
         </is>
       </c>
       <c r="D63" s="7" t="n">
-        <v>76.1169</v>
+        <v>72.03019999999999</v>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H904"/>
+  <dimension ref="A1:H925"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -42554,6 +42554,888 @@
         </is>
       </c>
     </row>
+    <row r="905">
+      <c r="A905" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B905" s="9" t="inlineStr">
+        <is>
+          <t>s1_basis_trade</t>
+        </is>
+      </c>
+      <c r="C905" s="9" t="inlineStr">
+        <is>
+          <t>Treasury basis trade (hidden leverage)</t>
+        </is>
+      </c>
+      <c r="D905" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E905" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F905" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G905" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H905" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B906" s="9" t="inlineStr">
+        <is>
+          <t>s2_japan</t>
+        </is>
+      </c>
+      <c r="C906" s="9" t="inlineStr">
+        <is>
+          <t>Japan fiscal / JGB / carry trade</t>
+        </is>
+      </c>
+      <c r="D906" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E906" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F906" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G906" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H906" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B907" s="9" t="inlineStr">
+        <is>
+          <t>s3_private_credit</t>
+        </is>
+      </c>
+      <c r="C907" s="9" t="inlineStr">
+        <is>
+          <t>Private credit's opaque expansion</t>
+        </is>
+      </c>
+      <c r="D907" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E907" s="9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F907" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G907" s="9" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="H907" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B908" s="9" t="inlineStr">
+        <is>
+          <t>s4_dev_debt</t>
+        </is>
+      </c>
+      <c r="C908" s="9" t="inlineStr">
+        <is>
+          <t>Developing-world debt crisis</t>
+        </is>
+      </c>
+      <c r="D908" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E908" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F908" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G908" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H908" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B909" s="9" t="inlineStr">
+        <is>
+          <t>s5_china_deflation</t>
+        </is>
+      </c>
+      <c r="C909" s="9" t="inlineStr">
+        <is>
+          <t>China's price spillover (deflation or cost-push)</t>
+        </is>
+      </c>
+      <c r="D909" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E909" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F909" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G909" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H909" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B910" s="9" t="inlineStr">
+        <is>
+          <t>s6_rare_earths</t>
+        </is>
+      </c>
+      <c r="C910" s="9" t="inlineStr">
+        <is>
+          <t>Critical minerals as a weapon</t>
+        </is>
+      </c>
+      <c r="D910" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E910" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F910" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G910" s="9" t="inlineStr">
+        <is>
+          <t>6.75</t>
+        </is>
+      </c>
+      <c r="H910" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B911" s="9" t="inlineStr">
+        <is>
+          <t>s7_stablecoins</t>
+        </is>
+      </c>
+      <c r="C911" s="9" t="inlineStr">
+        <is>
+          <t>Stablecoins &amp; Treasury demand</t>
+        </is>
+      </c>
+      <c r="D911" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E911" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F911" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G911" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H911" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B912" s="9" t="inlineStr">
+        <is>
+          <t>s8_ai_capex</t>
+        </is>
+      </c>
+      <c r="C912" s="9" t="inlineStr">
+        <is>
+          <t>AI build-out circular financing</t>
+        </is>
+      </c>
+      <c r="D912" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E912" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F912" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G912" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H912" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B913" s="9" t="inlineStr">
+        <is>
+          <t>s9_cre</t>
+        </is>
+      </c>
+      <c r="C913" s="9" t="inlineStr">
+        <is>
+          <t>CRE maturity wall / regional banks</t>
+        </is>
+      </c>
+      <c r="D913" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E913" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F913" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G913" s="9" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+      <c r="H913" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B914" s="9" t="inlineStr">
+        <is>
+          <t>s10_france</t>
+        </is>
+      </c>
+      <c r="C914" s="9" t="inlineStr">
+        <is>
+          <t>France / eurozone fragility</t>
+        </is>
+      </c>
+      <c r="D914" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E914" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F914" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G914" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H914" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B915" s="9" t="inlineStr">
+        <is>
+          <t>s11_consumer_debt</t>
+        </is>
+      </c>
+      <c r="C915" s="9" t="inlineStr">
+        <is>
+          <t>Hidden consumer debt</t>
+        </is>
+      </c>
+      <c r="D915" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E915" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F915" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G915" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H915" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B916" s="9" t="inlineStr">
+        <is>
+          <t>s12_gold_dedollar</t>
+        </is>
+      </c>
+      <c r="C916" s="9" t="inlineStr">
+        <is>
+          <t>Gold / de-dollarization</t>
+        </is>
+      </c>
+      <c r="D916" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E916" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F916" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G916" s="9" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="H916" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B917" s="9" t="inlineStr">
+        <is>
+          <t>s13_insurance</t>
+        </is>
+      </c>
+      <c r="C917" s="9" t="inlineStr">
+        <is>
+          <t>Insurance retreat</t>
+        </is>
+      </c>
+      <c r="D917" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E917" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F917" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G917" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H917" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B918" s="9" t="inlineStr">
+        <is>
+          <t>s14_pensions</t>
+        </is>
+      </c>
+      <c r="C918" s="9" t="inlineStr">
+        <is>
+          <t>Pensions / demographics</t>
+        </is>
+      </c>
+      <c r="D918" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E918" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F918" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G918" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H918" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B919" s="9" t="inlineStr">
+        <is>
+          <t>s15_ai_power</t>
+        </is>
+      </c>
+      <c r="C919" s="9" t="inlineStr">
+        <is>
+          <t>AI power &amp; the grid bottleneck</t>
+        </is>
+      </c>
+      <c r="D919" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E919" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F919" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G919" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H919" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B920" s="9" t="inlineStr">
+        <is>
+          <t>s16_copper</t>
+        </is>
+      </c>
+      <c r="C920" s="9" t="inlineStr">
+        <is>
+          <t>Copper &amp; the electrification deficit</t>
+        </is>
+      </c>
+      <c r="D920" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E920" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F920" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G920" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H920" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B921" s="9" t="inlineStr">
+        <is>
+          <t>s17_water</t>
+        </is>
+      </c>
+      <c r="C921" s="9" t="inlineStr">
+        <is>
+          <t>Water - the underpriced input</t>
+        </is>
+      </c>
+      <c r="D921" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E921" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F921" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G921" s="9" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="H921" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B922" s="9" t="inlineStr">
+        <is>
+          <t>s18_food_fertilizer</t>
+        </is>
+      </c>
+      <c r="C922" s="9" t="inlineStr">
+        <is>
+          <t>Food &amp; fertilizer fragility</t>
+        </is>
+      </c>
+      <c r="D922" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E922" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F922" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G922" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H922" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B923" s="9" t="inlineStr">
+        <is>
+          <t>s19_lithography</t>
+        </is>
+      </c>
+      <c r="C923" s="9" t="inlineStr">
+        <is>
+          <t>The lithography (ASML) chokepoint</t>
+        </is>
+      </c>
+      <c r="D923" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E923" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F923" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G923" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H923" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B924" s="9" t="inlineStr">
+        <is>
+          <t>s20_sea_lanes</t>
+        </is>
+      </c>
+      <c r="C924" s="9" t="inlineStr">
+        <is>
+          <t>Sea lanes &amp; undersea cables</t>
+        </is>
+      </c>
+      <c r="D924" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E924" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F924" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G924" s="9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="H924" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B925" s="9" t="inlineStr">
+        <is>
+          <t>s21_clearinghouses</t>
+        </is>
+      </c>
+      <c r="C925" s="9" t="inlineStr">
+        <is>
+          <t>Clearinghouses (financial chokepoint)</t>
+        </is>
+      </c>
+      <c r="D925" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E925" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F925" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G925" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H925" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -42565,7 +43447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A28"/>
+  <dimension ref="A1:A24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -42646,88 +43528,64 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>--- Daily narrative (2026-08-07) ---</t>
+          <t>--- Daily narrative (2026-08-10) ---</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>**HEADLINE**</t>
+          <t># EOD Macro Risk Brief | 2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>Macro risk stands at High, driven by four critical structural vulnerabilities: Japan's carry-trade and fiscal instability, opaque private credit expansion, China's deflationary spillover, and AI infrastructure financing circularity.</t>
-        </is>
-      </c>
+      <c r="A15" s="12" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr"/>
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>**Overall risk stands at High, with three stories shifting today.**</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>**STORIES (no intraday changes)**</t>
-        </is>
-      </c>
+      <c r="A17" s="12" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="inlineStr"/>
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>• **Japan fiscal / JGB / carry trade** fell from 8 to High: 30-year JGB yield rose to 3.925%, easing near-term unwind pressure but leaving structural carry-trade fragility intact.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>• **Japan fiscal / JGB / carry trade** (High): Persistent yen weakness and fiscal stress sustain carry-trade unwind risk; sudden reversal could trigger forced deleveraging across global equities and credit.</t>
-        </is>
-      </c>
+      <c r="A19" s="12" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr"/>
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>• **China's price spillover** declined from 7 to Elevated: tariff/anti-dumping actions remain escalating (level 2), but the score moderated by 1 point, reducing immediate deflationary or cost-push contagion risk to trading partners.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>• **Private credit's opaque expansion** (High): Continued rapid growth in unregulated lending pools with poor transparency increases systemic contagion risk if rates or defaults accelerate.</t>
-        </is>
-      </c>
+      <c r="A21" s="12" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="inlineStr"/>
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>• **CRE maturity wall / regional banks** rose from 5 to Elevated: regional-bank CRE stress moved to isolated status (level 1), signaling early cluster formation risk among smaller lenders facing refinancing pressure.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>• **China's price spillover** (High): Deflationary pressures exportable to developed economies risk margin compression and central bank policy divergence.</t>
-        </is>
-      </c>
+      <c r="A23" s="12" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>• **AI power &amp; the grid bottleneck** (High): Sustained demand surge outpacing grid capacity creates supply constraints and energy-cost volatility for capex-dependent sectors.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="12" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>**WATCH**</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="12" t="inlineStr">
-        <is>
-          <t>Japan fiscal / JGB / carry trade remains the highest-risk trigger for sudden cross-asset volatility.</t>
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>**Top watch:** Private credit's opaque expansion remains at High (8)—largest unmonitored leverage pool in the system.</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-08-10  -  generated 2026-08-10 12:33 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-08-11  -  generated 2026-08-11 12:27 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
         </is>
       </c>
       <c r="D2" s="7" t="n">
-        <v>0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="D3" s="7" t="n">
-        <v>72.03019999999999</v>
+        <v>75.4556</v>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>158.74</v>
+        <v>159.33</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>119.7034</v>
+        <v>119.0649</v>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>6.7324</v>
+        <v>6.7332</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>306.7</v>
+        <v>306.4</v>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>4389</v>
+        <v>4453.3999</v>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>6.6235</v>
+        <v>6.6635</v>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="D60" s="7" t="n">
-        <v>79.47</v>
+        <v>82.31</v>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="D62" s="7" t="n">
-        <v>15.45</v>
+        <v>15.46</v>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
         </is>
       </c>
       <c r="D63" s="7" t="n">
-        <v>72.03019999999999</v>
+        <v>75.4556</v>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H925"/>
+  <dimension ref="A1:H946"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -43436,6 +43436,888 @@
         </is>
       </c>
     </row>
+    <row r="926">
+      <c r="A926" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B926" s="9" t="inlineStr">
+        <is>
+          <t>s1_basis_trade</t>
+        </is>
+      </c>
+      <c r="C926" s="9" t="inlineStr">
+        <is>
+          <t>Treasury basis trade (hidden leverage)</t>
+        </is>
+      </c>
+      <c r="D926" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E926" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F926" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G926" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H926" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B927" s="9" t="inlineStr">
+        <is>
+          <t>s2_japan</t>
+        </is>
+      </c>
+      <c r="C927" s="9" t="inlineStr">
+        <is>
+          <t>Japan fiscal / JGB / carry trade</t>
+        </is>
+      </c>
+      <c r="D927" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E927" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F927" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G927" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H927" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B928" s="9" t="inlineStr">
+        <is>
+          <t>s3_private_credit</t>
+        </is>
+      </c>
+      <c r="C928" s="9" t="inlineStr">
+        <is>
+          <t>Private credit's opaque expansion</t>
+        </is>
+      </c>
+      <c r="D928" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E928" s="9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F928" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G928" s="9" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="H928" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B929" s="9" t="inlineStr">
+        <is>
+          <t>s4_dev_debt</t>
+        </is>
+      </c>
+      <c r="C929" s="9" t="inlineStr">
+        <is>
+          <t>Developing-world debt crisis</t>
+        </is>
+      </c>
+      <c r="D929" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E929" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F929" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G929" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H929" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B930" s="9" t="inlineStr">
+        <is>
+          <t>s5_china_deflation</t>
+        </is>
+      </c>
+      <c r="C930" s="9" t="inlineStr">
+        <is>
+          <t>China's price spillover (deflation or cost-push)</t>
+        </is>
+      </c>
+      <c r="D930" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E930" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F930" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G930" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H930" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B931" s="9" t="inlineStr">
+        <is>
+          <t>s6_rare_earths</t>
+        </is>
+      </c>
+      <c r="C931" s="9" t="inlineStr">
+        <is>
+          <t>Critical minerals as a weapon</t>
+        </is>
+      </c>
+      <c r="D931" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E931" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F931" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G931" s="9" t="inlineStr">
+        <is>
+          <t>6.75</t>
+        </is>
+      </c>
+      <c r="H931" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B932" s="9" t="inlineStr">
+        <is>
+          <t>s7_stablecoins</t>
+        </is>
+      </c>
+      <c r="C932" s="9" t="inlineStr">
+        <is>
+          <t>Stablecoins &amp; Treasury demand</t>
+        </is>
+      </c>
+      <c r="D932" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E932" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F932" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G932" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H932" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B933" s="9" t="inlineStr">
+        <is>
+          <t>s8_ai_capex</t>
+        </is>
+      </c>
+      <c r="C933" s="9" t="inlineStr">
+        <is>
+          <t>AI build-out circular financing</t>
+        </is>
+      </c>
+      <c r="D933" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E933" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F933" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G933" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H933" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B934" s="9" t="inlineStr">
+        <is>
+          <t>s9_cre</t>
+        </is>
+      </c>
+      <c r="C934" s="9" t="inlineStr">
+        <is>
+          <t>CRE maturity wall / regional banks</t>
+        </is>
+      </c>
+      <c r="D934" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E934" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F934" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G934" s="9" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+      <c r="H934" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B935" s="9" t="inlineStr">
+        <is>
+          <t>s10_france</t>
+        </is>
+      </c>
+      <c r="C935" s="9" t="inlineStr">
+        <is>
+          <t>France / eurozone fragility</t>
+        </is>
+      </c>
+      <c r="D935" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E935" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F935" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G935" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H935" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B936" s="9" t="inlineStr">
+        <is>
+          <t>s11_consumer_debt</t>
+        </is>
+      </c>
+      <c r="C936" s="9" t="inlineStr">
+        <is>
+          <t>Hidden consumer debt</t>
+        </is>
+      </c>
+      <c r="D936" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E936" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F936" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G936" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H936" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B937" s="9" t="inlineStr">
+        <is>
+          <t>s12_gold_dedollar</t>
+        </is>
+      </c>
+      <c r="C937" s="9" t="inlineStr">
+        <is>
+          <t>Gold / de-dollarization</t>
+        </is>
+      </c>
+      <c r="D937" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E937" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F937" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G937" s="9" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="H937" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B938" s="9" t="inlineStr">
+        <is>
+          <t>s13_insurance</t>
+        </is>
+      </c>
+      <c r="C938" s="9" t="inlineStr">
+        <is>
+          <t>Insurance retreat</t>
+        </is>
+      </c>
+      <c r="D938" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E938" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F938" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G938" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H938" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B939" s="9" t="inlineStr">
+        <is>
+          <t>s14_pensions</t>
+        </is>
+      </c>
+      <c r="C939" s="9" t="inlineStr">
+        <is>
+          <t>Pensions / demographics</t>
+        </is>
+      </c>
+      <c r="D939" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E939" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F939" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G939" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H939" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B940" s="9" t="inlineStr">
+        <is>
+          <t>s15_ai_power</t>
+        </is>
+      </c>
+      <c r="C940" s="9" t="inlineStr">
+        <is>
+          <t>AI power &amp; the grid bottleneck</t>
+        </is>
+      </c>
+      <c r="D940" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E940" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F940" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G940" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H940" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B941" s="9" t="inlineStr">
+        <is>
+          <t>s16_copper</t>
+        </is>
+      </c>
+      <c r="C941" s="9" t="inlineStr">
+        <is>
+          <t>Copper &amp; the electrification deficit</t>
+        </is>
+      </c>
+      <c r="D941" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E941" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F941" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G941" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H941" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B942" s="9" t="inlineStr">
+        <is>
+          <t>s17_water</t>
+        </is>
+      </c>
+      <c r="C942" s="9" t="inlineStr">
+        <is>
+          <t>Water - the underpriced input</t>
+        </is>
+      </c>
+      <c r="D942" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E942" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F942" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G942" s="9" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="H942" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B943" s="9" t="inlineStr">
+        <is>
+          <t>s18_food_fertilizer</t>
+        </is>
+      </c>
+      <c r="C943" s="9" t="inlineStr">
+        <is>
+          <t>Food &amp; fertilizer fragility</t>
+        </is>
+      </c>
+      <c r="D943" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E943" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F943" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G943" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H943" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B944" s="9" t="inlineStr">
+        <is>
+          <t>s19_lithography</t>
+        </is>
+      </c>
+      <c r="C944" s="9" t="inlineStr">
+        <is>
+          <t>The lithography (ASML) chokepoint</t>
+        </is>
+      </c>
+      <c r="D944" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E944" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F944" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G944" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H944" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B945" s="9" t="inlineStr">
+        <is>
+          <t>s20_sea_lanes</t>
+        </is>
+      </c>
+      <c r="C945" s="9" t="inlineStr">
+        <is>
+          <t>Sea lanes &amp; undersea cables</t>
+        </is>
+      </c>
+      <c r="D945" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E945" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F945" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G945" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H945" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B946" s="9" t="inlineStr">
+        <is>
+          <t>s21_clearinghouses</t>
+        </is>
+      </c>
+      <c r="C946" s="9" t="inlineStr">
+        <is>
+          <t>Clearinghouses (financial chokepoint)</t>
+        </is>
+      </c>
+      <c r="D946" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E946" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F946" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G946" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H946" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -43447,7 +44329,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A24"/>
+  <dimension ref="A1:A23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -43528,14 +44410,14 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>--- Daily narrative (2026-08-10) ---</t>
+          <t>--- Daily narrative (2026-08-11) ---</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t># EOD Macro Risk Brief | 2026-08-10</t>
+          <t>**EOD MACRO-RISK BRIEF | 11 August 2026**</t>
         </is>
       </c>
     </row>
@@ -43545,27 +44427,31 @@
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>**Overall risk stands at High, with three stories shifting today.**</t>
+          <t>**Headline:**</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr"/>
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>Macro risk stands at High, driven by structural leverage, opaque credit expansion, and geopolitical supply-chain concentration.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
-          <t>• **Japan fiscal / JGB / carry trade** fell from 8 to High: 30-year JGB yield rose to 3.925%, easing near-term unwind pressure but leaving structural carry-trade fragility intact.</t>
-        </is>
-      </c>
+      <c r="A18" s="12" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr"/>
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>**Key Stories (No Changes):**</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>• **China's price spillover** declined from 7 to Elevated: tariff/anti-dumping actions remain escalating (level 2), but the score moderated by 1 point, reducing immediate deflationary or cost-push contagion risk to trading partners.</t>
+          <t>No risk-level movements recorded today. Persistent High-band risks include private credit's opaque expansion (level 8), Japan's fiscal and carry-trade vulnerability (level 7), and AI power-grid bottlenecks (level 7). Critical minerals weaponization also remains High. Elevated risks span Treasury basis trades, developing-world debt, China's deflationary spillover, CRE maturity pressures, and semiconductor chokepoints.</t>
         </is>
       </c>
     </row>
@@ -43575,17 +44461,14 @@
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>• **CRE maturity wall / regional banks** rose from 5 to Elevated: regional-bank CRE stress moved to isolated status (level 1), signaling early cluster formation risk among smaller lenders facing refinancing pressure.</t>
+          <t>**Watch:**</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="12" t="inlineStr">
-        <is>
-          <t>**Top watch:** Private credit's opaque expansion remains at High (8)—largest unmonitored leverage pool in the system.</t>
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>Private credit's opaque expansion (level 8, High) remains the single highest-risk vector, given its scale, opacity, and interconnection to financial stability.</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-08-11  -  generated 2026-08-11 12:27 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-08-12  -  generated 2026-08-12 12:28 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
         </is>
       </c>
       <c r="D2" s="7" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="D3" s="7" t="n">
-        <v>75.4556</v>
+        <v>77.9153</v>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>159.33</v>
+        <v>159.034</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>3.925</v>
+        <v>3.957</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>6.7332</v>
+        <v>6.7318</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>306.4</v>
+        <v>307.4</v>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>4453.3999</v>
+        <v>4467.2002</v>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>6.6635</v>
+        <v>6.6745</v>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="D60" s="7" t="n">
-        <v>82.31</v>
+        <v>83.7</v>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="D62" s="7" t="n">
-        <v>15.46</v>
+        <v>15.37</v>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
         </is>
       </c>
       <c r="D63" s="7" t="n">
-        <v>75.4556</v>
+        <v>77.9153</v>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H946"/>
+  <dimension ref="A1:H967"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -44318,6 +44318,888 @@
         </is>
       </c>
     </row>
+    <row r="947">
+      <c r="A947" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B947" s="9" t="inlineStr">
+        <is>
+          <t>s1_basis_trade</t>
+        </is>
+      </c>
+      <c r="C947" s="9" t="inlineStr">
+        <is>
+          <t>Treasury basis trade (hidden leverage)</t>
+        </is>
+      </c>
+      <c r="D947" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E947" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F947" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G947" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H947" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B948" s="9" t="inlineStr">
+        <is>
+          <t>s2_japan</t>
+        </is>
+      </c>
+      <c r="C948" s="9" t="inlineStr">
+        <is>
+          <t>Japan fiscal / JGB / carry trade</t>
+        </is>
+      </c>
+      <c r="D948" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E948" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F948" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G948" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H948" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B949" s="9" t="inlineStr">
+        <is>
+          <t>s3_private_credit</t>
+        </is>
+      </c>
+      <c r="C949" s="9" t="inlineStr">
+        <is>
+          <t>Private credit's opaque expansion</t>
+        </is>
+      </c>
+      <c r="D949" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E949" s="9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F949" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G949" s="9" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="H949" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B950" s="9" t="inlineStr">
+        <is>
+          <t>s4_dev_debt</t>
+        </is>
+      </c>
+      <c r="C950" s="9" t="inlineStr">
+        <is>
+          <t>Developing-world debt crisis</t>
+        </is>
+      </c>
+      <c r="D950" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E950" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F950" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G950" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H950" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B951" s="9" t="inlineStr">
+        <is>
+          <t>s5_china_deflation</t>
+        </is>
+      </c>
+      <c r="C951" s="9" t="inlineStr">
+        <is>
+          <t>China's price spillover (deflation or cost-push)</t>
+        </is>
+      </c>
+      <c r="D951" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E951" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F951" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G951" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H951" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B952" s="9" t="inlineStr">
+        <is>
+          <t>s6_rare_earths</t>
+        </is>
+      </c>
+      <c r="C952" s="9" t="inlineStr">
+        <is>
+          <t>Critical minerals as a weapon</t>
+        </is>
+      </c>
+      <c r="D952" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E952" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F952" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G952" s="9" t="inlineStr">
+        <is>
+          <t>6.75</t>
+        </is>
+      </c>
+      <c r="H952" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B953" s="9" t="inlineStr">
+        <is>
+          <t>s7_stablecoins</t>
+        </is>
+      </c>
+      <c r="C953" s="9" t="inlineStr">
+        <is>
+          <t>Stablecoins &amp; Treasury demand</t>
+        </is>
+      </c>
+      <c r="D953" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E953" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F953" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G953" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H953" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B954" s="9" t="inlineStr">
+        <is>
+          <t>s8_ai_capex</t>
+        </is>
+      </c>
+      <c r="C954" s="9" t="inlineStr">
+        <is>
+          <t>AI build-out circular financing</t>
+        </is>
+      </c>
+      <c r="D954" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E954" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F954" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G954" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H954" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B955" s="9" t="inlineStr">
+        <is>
+          <t>s9_cre</t>
+        </is>
+      </c>
+      <c r="C955" s="9" t="inlineStr">
+        <is>
+          <t>CRE maturity wall / regional banks</t>
+        </is>
+      </c>
+      <c r="D955" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E955" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F955" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G955" s="9" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+      <c r="H955" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B956" s="9" t="inlineStr">
+        <is>
+          <t>s10_france</t>
+        </is>
+      </c>
+      <c r="C956" s="9" t="inlineStr">
+        <is>
+          <t>France / eurozone fragility</t>
+        </is>
+      </c>
+      <c r="D956" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E956" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F956" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G956" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H956" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B957" s="9" t="inlineStr">
+        <is>
+          <t>s11_consumer_debt</t>
+        </is>
+      </c>
+      <c r="C957" s="9" t="inlineStr">
+        <is>
+          <t>Hidden consumer debt</t>
+        </is>
+      </c>
+      <c r="D957" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E957" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F957" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G957" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H957" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B958" s="9" t="inlineStr">
+        <is>
+          <t>s12_gold_dedollar</t>
+        </is>
+      </c>
+      <c r="C958" s="9" t="inlineStr">
+        <is>
+          <t>Gold / de-dollarization</t>
+        </is>
+      </c>
+      <c r="D958" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E958" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F958" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G958" s="9" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="H958" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B959" s="9" t="inlineStr">
+        <is>
+          <t>s13_insurance</t>
+        </is>
+      </c>
+      <c r="C959" s="9" t="inlineStr">
+        <is>
+          <t>Insurance retreat</t>
+        </is>
+      </c>
+      <c r="D959" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E959" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F959" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G959" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H959" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B960" s="9" t="inlineStr">
+        <is>
+          <t>s14_pensions</t>
+        </is>
+      </c>
+      <c r="C960" s="9" t="inlineStr">
+        <is>
+          <t>Pensions / demographics</t>
+        </is>
+      </c>
+      <c r="D960" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E960" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F960" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G960" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H960" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B961" s="9" t="inlineStr">
+        <is>
+          <t>s15_ai_power</t>
+        </is>
+      </c>
+      <c r="C961" s="9" t="inlineStr">
+        <is>
+          <t>AI power &amp; the grid bottleneck</t>
+        </is>
+      </c>
+      <c r="D961" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E961" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F961" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G961" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H961" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B962" s="9" t="inlineStr">
+        <is>
+          <t>s16_copper</t>
+        </is>
+      </c>
+      <c r="C962" s="9" t="inlineStr">
+        <is>
+          <t>Copper &amp; the electrification deficit</t>
+        </is>
+      </c>
+      <c r="D962" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E962" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F962" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G962" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H962" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B963" s="9" t="inlineStr">
+        <is>
+          <t>s17_water</t>
+        </is>
+      </c>
+      <c r="C963" s="9" t="inlineStr">
+        <is>
+          <t>Water - the underpriced input</t>
+        </is>
+      </c>
+      <c r="D963" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E963" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F963" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G963" s="9" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="H963" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B964" s="9" t="inlineStr">
+        <is>
+          <t>s18_food_fertilizer</t>
+        </is>
+      </c>
+      <c r="C964" s="9" t="inlineStr">
+        <is>
+          <t>Food &amp; fertilizer fragility</t>
+        </is>
+      </c>
+      <c r="D964" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E964" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F964" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G964" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H964" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B965" s="9" t="inlineStr">
+        <is>
+          <t>s19_lithography</t>
+        </is>
+      </c>
+      <c r="C965" s="9" t="inlineStr">
+        <is>
+          <t>The lithography (ASML) chokepoint</t>
+        </is>
+      </c>
+      <c r="D965" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E965" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F965" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G965" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H965" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B966" s="9" t="inlineStr">
+        <is>
+          <t>s20_sea_lanes</t>
+        </is>
+      </c>
+      <c r="C966" s="9" t="inlineStr">
+        <is>
+          <t>Sea lanes &amp; undersea cables</t>
+        </is>
+      </c>
+      <c r="D966" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E966" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F966" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G966" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H966" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B967" s="9" t="inlineStr">
+        <is>
+          <t>s21_clearinghouses</t>
+        </is>
+      </c>
+      <c r="C967" s="9" t="inlineStr">
+        <is>
+          <t>Clearinghouses (financial chokepoint)</t>
+        </is>
+      </c>
+      <c r="D967" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E967" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F967" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G967" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H967" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -44329,7 +45211,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A23"/>
+  <dimension ref="A1:A32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -44410,31 +45292,31 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>--- Daily narrative (2026-08-11) ---</t>
+          <t>--- Daily narrative (2026-08-12) ---</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>**EOD MACRO-RISK BRIEF | 11 August 2026**</t>
+          <t>**HEADLINE**</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr"/>
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>Macro risk stands at High, anchored by three acute vulnerabilities: opaque private credit expansion, Japan's carry-trade unwind risk, and AI infrastructure financing loops.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>**Headline:**</t>
-        </is>
-      </c>
+      <c r="A16" s="12" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>Macro risk stands at High, driven by structural leverage, opaque credit expansion, and geopolitical supply-chain concentration.</t>
+          <t>**STORIES AT ELEVATED OR HIGHER (no intraday changes)**</t>
         </is>
       </c>
     </row>
@@ -44444,31 +45326,74 @@
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>**Key Stories (No Changes):**</t>
+          <t>• **Private credit's opaque expansion** (High): Systemic leverage concentrated in unregulated channels poses contagion risk if redemptions spike or asset quality deteriorates.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
-          <t>No risk-level movements recorded today. Persistent High-band risks include private credit's opaque expansion (level 8), Japan's fiscal and carry-trade vulnerability (level 7), and AI power-grid bottlenecks (level 7). Critical minerals weaponization also remains High. Elevated risks span Treasury basis trades, developing-world debt, China's deflationary spillover, CRE maturity pressures, and semiconductor chokepoints.</t>
-        </is>
-      </c>
+      <c r="A20" s="12" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr"/>
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>• **Japan fiscal / JGB / carry trade** (High): Persistent BoJ policy uncertainty and rising rates threaten unwinding of dollar-yen carry positions, risking sudden deleveraging across correlated markets.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t>**Watch:**</t>
-        </is>
-      </c>
+      <c r="A22" s="12" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>Private credit's opaque expansion (level 8, High) remains the single highest-risk vector, given its scale, opacity, and interconnection to financial stability.</t>
+          <t>• **AI power &amp; the grid bottleneck** (High): Datacenter demand outpacing grid capacity creates stranded capex and brownout risk, pressuring energy costs and project viability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>• **Critical minerals as a weapon** (High): Supply concentration and geopolitical fragility expose manufacturing and energy transition to disruption and price volatility.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>• **Treasury basis trade (hidden leverage)** (Elevated): Embedded leverage in cash-futures arbitrage poses flash-crash risk if funding conditions tighten unexpectedly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>• **Developing-world debt crisis** (Elevated): External refinancing pressure and FX stress amid higher rates increase sovereign default risk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="12" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>**WATCH MOST CLOSELY**</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>Private credit opacity and redemption stress—smallest friction point for system-wide contagion.</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-08-12  -  generated 2026-08-12 12:28 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-08-13  -  generated 2026-08-13 12:29 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
         </is>
       </c>
       <c r="D2" s="7" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="D3" s="7" t="n">
-        <v>77.9153</v>
+        <v>72.0887</v>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>159.034</v>
+        <v>159.355</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>3.957</v>
+        <v>3.989</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>6.7318</v>
+        <v>6.7319</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>307.4</v>
+        <v>307.5</v>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>4467.2002</v>
+        <v>4442</v>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>6.6745</v>
+        <v>6.5925</v>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="D60" s="7" t="n">
-        <v>83.7</v>
+        <v>81.59</v>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="D62" s="7" t="n">
-        <v>15.37</v>
+        <v>14.58</v>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
         </is>
       </c>
       <c r="D63" s="7" t="n">
-        <v>77.9153</v>
+        <v>72.0887</v>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H967"/>
+  <dimension ref="A1:H988"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -45200,6 +45200,888 @@
         </is>
       </c>
     </row>
+    <row r="968">
+      <c r="A968" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B968" s="9" t="inlineStr">
+        <is>
+          <t>s1_basis_trade</t>
+        </is>
+      </c>
+      <c r="C968" s="9" t="inlineStr">
+        <is>
+          <t>Treasury basis trade (hidden leverage)</t>
+        </is>
+      </c>
+      <c r="D968" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E968" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F968" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G968" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H968" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B969" s="9" t="inlineStr">
+        <is>
+          <t>s2_japan</t>
+        </is>
+      </c>
+      <c r="C969" s="9" t="inlineStr">
+        <is>
+          <t>Japan fiscal / JGB / carry trade</t>
+        </is>
+      </c>
+      <c r="D969" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E969" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F969" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G969" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H969" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B970" s="9" t="inlineStr">
+        <is>
+          <t>s3_private_credit</t>
+        </is>
+      </c>
+      <c r="C970" s="9" t="inlineStr">
+        <is>
+          <t>Private credit's opaque expansion</t>
+        </is>
+      </c>
+      <c r="D970" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E970" s="9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F970" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G970" s="9" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="H970" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B971" s="9" t="inlineStr">
+        <is>
+          <t>s4_dev_debt</t>
+        </is>
+      </c>
+      <c r="C971" s="9" t="inlineStr">
+        <is>
+          <t>Developing-world debt crisis</t>
+        </is>
+      </c>
+      <c r="D971" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E971" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F971" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G971" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H971" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B972" s="9" t="inlineStr">
+        <is>
+          <t>s5_china_deflation</t>
+        </is>
+      </c>
+      <c r="C972" s="9" t="inlineStr">
+        <is>
+          <t>China's price spillover (deflation or cost-push)</t>
+        </is>
+      </c>
+      <c r="D972" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E972" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F972" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G972" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H972" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B973" s="9" t="inlineStr">
+        <is>
+          <t>s6_rare_earths</t>
+        </is>
+      </c>
+      <c r="C973" s="9" t="inlineStr">
+        <is>
+          <t>Critical minerals as a weapon</t>
+        </is>
+      </c>
+      <c r="D973" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E973" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F973" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G973" s="9" t="inlineStr">
+        <is>
+          <t>6.75</t>
+        </is>
+      </c>
+      <c r="H973" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B974" s="9" t="inlineStr">
+        <is>
+          <t>s7_stablecoins</t>
+        </is>
+      </c>
+      <c r="C974" s="9" t="inlineStr">
+        <is>
+          <t>Stablecoins &amp; Treasury demand</t>
+        </is>
+      </c>
+      <c r="D974" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E974" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F974" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G974" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H974" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B975" s="9" t="inlineStr">
+        <is>
+          <t>s8_ai_capex</t>
+        </is>
+      </c>
+      <c r="C975" s="9" t="inlineStr">
+        <is>
+          <t>AI build-out circular financing</t>
+        </is>
+      </c>
+      <c r="D975" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E975" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F975" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G975" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H975" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B976" s="9" t="inlineStr">
+        <is>
+          <t>s9_cre</t>
+        </is>
+      </c>
+      <c r="C976" s="9" t="inlineStr">
+        <is>
+          <t>CRE maturity wall / regional banks</t>
+        </is>
+      </c>
+      <c r="D976" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E976" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F976" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G976" s="9" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+      <c r="H976" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B977" s="9" t="inlineStr">
+        <is>
+          <t>s10_france</t>
+        </is>
+      </c>
+      <c r="C977" s="9" t="inlineStr">
+        <is>
+          <t>France / eurozone fragility</t>
+        </is>
+      </c>
+      <c r="D977" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E977" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F977" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G977" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H977" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B978" s="9" t="inlineStr">
+        <is>
+          <t>s11_consumer_debt</t>
+        </is>
+      </c>
+      <c r="C978" s="9" t="inlineStr">
+        <is>
+          <t>Hidden consumer debt</t>
+        </is>
+      </c>
+      <c r="D978" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E978" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F978" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G978" s="9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H978" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B979" s="9" t="inlineStr">
+        <is>
+          <t>s12_gold_dedollar</t>
+        </is>
+      </c>
+      <c r="C979" s="9" t="inlineStr">
+        <is>
+          <t>Gold / de-dollarization</t>
+        </is>
+      </c>
+      <c r="D979" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E979" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F979" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G979" s="9" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="H979" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B980" s="9" t="inlineStr">
+        <is>
+          <t>s13_insurance</t>
+        </is>
+      </c>
+      <c r="C980" s="9" t="inlineStr">
+        <is>
+          <t>Insurance retreat</t>
+        </is>
+      </c>
+      <c r="D980" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E980" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F980" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G980" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H980" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B981" s="9" t="inlineStr">
+        <is>
+          <t>s14_pensions</t>
+        </is>
+      </c>
+      <c r="C981" s="9" t="inlineStr">
+        <is>
+          <t>Pensions / demographics</t>
+        </is>
+      </c>
+      <c r="D981" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E981" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F981" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G981" s="9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="H981" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B982" s="9" t="inlineStr">
+        <is>
+          <t>s15_ai_power</t>
+        </is>
+      </c>
+      <c r="C982" s="9" t="inlineStr">
+        <is>
+          <t>AI power &amp; the grid bottleneck</t>
+        </is>
+      </c>
+      <c r="D982" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E982" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F982" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G982" s="9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H982" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B983" s="9" t="inlineStr">
+        <is>
+          <t>s16_copper</t>
+        </is>
+      </c>
+      <c r="C983" s="9" t="inlineStr">
+        <is>
+          <t>Copper &amp; the electrification deficit</t>
+        </is>
+      </c>
+      <c r="D983" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E983" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F983" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G983" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H983" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B984" s="9" t="inlineStr">
+        <is>
+          <t>s17_water</t>
+        </is>
+      </c>
+      <c r="C984" s="9" t="inlineStr">
+        <is>
+          <t>Water - the underpriced input</t>
+        </is>
+      </c>
+      <c r="D984" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E984" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F984" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G984" s="9" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="H984" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B985" s="9" t="inlineStr">
+        <is>
+          <t>s18_food_fertilizer</t>
+        </is>
+      </c>
+      <c r="C985" s="9" t="inlineStr">
+        <is>
+          <t>Food &amp; fertilizer fragility</t>
+        </is>
+      </c>
+      <c r="D985" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E985" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F985" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G985" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H985" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B986" s="9" t="inlineStr">
+        <is>
+          <t>s19_lithography</t>
+        </is>
+      </c>
+      <c r="C986" s="9" t="inlineStr">
+        <is>
+          <t>The lithography (ASML) chokepoint</t>
+        </is>
+      </c>
+      <c r="D986" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E986" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F986" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G986" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H986" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B987" s="9" t="inlineStr">
+        <is>
+          <t>s20_sea_lanes</t>
+        </is>
+      </c>
+      <c r="C987" s="9" t="inlineStr">
+        <is>
+          <t>Sea lanes &amp; undersea cables</t>
+        </is>
+      </c>
+      <c r="D987" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E987" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F987" s="9" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="G987" s="9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H987" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B988" s="9" t="inlineStr">
+        <is>
+          <t>s21_clearinghouses</t>
+        </is>
+      </c>
+      <c r="C988" s="9" t="inlineStr">
+        <is>
+          <t>Clearinghouses (financial chokepoint)</t>
+        </is>
+      </c>
+      <c r="D988" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E988" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F988" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G988" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H988" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -45211,7 +46093,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A32"/>
+  <dimension ref="A1:A28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -45292,31 +46174,31 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>--- Daily narrative (2026-08-12) ---</t>
+          <t>--- Daily narrative (2026-08-13) ---</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
+          <t>**EOD MACRO-RISK BRIEF | 2026-08-13**</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
           <t>**HEADLINE**</t>
         </is>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>Macro risk stands at High, anchored by three acute vulnerabilities: opaque private credit expansion, Japan's carry-trade unwind risk, and AI infrastructure financing loops.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="12" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>**STORIES AT ELEVATED OR HIGHER (no intraday changes)**</t>
+          <t>Overall macro risk remains High, with no intraday level changes but persistent exposure across financial leverage, geopolitical supply chains, and structural imbalances.</t>
         </is>
       </c>
     </row>
@@ -45326,7 +46208,7 @@
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>• **Private credit's opaque expansion** (High): Systemic leverage concentrated in unregulated channels poses contagion risk if redemptions spike or asset quality deteriorates.</t>
+          <t>**NO STORIES WITH LEVEL CHANGES TODAY**</t>
         </is>
       </c>
     </row>
@@ -45336,27 +46218,35 @@
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>• **Japan fiscal / JGB / carry trade** (High): Persistent BoJ policy uncertainty and rising rates threaten unwinding of dollar-yen carry positions, risking sudden deleveraging across correlated markets.</t>
+          <t>**Key Stories at Elevated or Higher Risk:**</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="inlineStr"/>
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>- **Private credit's opaque expansion** (High): Continued rapid growth in unregulated credit channels without transparent pricing or stress-test data; amplifies systemic contagion risk if rates spike or demand falters.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>• **AI power &amp; the grid bottleneck** (High): Datacenter demand outpacing grid capacity creates stranded capex and brownout risk, pressuring energy costs and project viability.</t>
+          <t>- **Japan fiscal / JGB / carry trade** (High): Structural yen weakness and high public debt create unwind risk; unwinding leveraged carry positions could trigger sharp currency and rate moves.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="inlineStr"/>
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>- **AI power &amp; the grid bottleneck** (High): Surging datacenter demand outpacing grid capacity; physical infrastructure lag creates brownout and cost-inflation risk.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>• **Critical minerals as a weapon** (High): Supply concentration and geopolitical fragility expose manufacturing and energy transition to disruption and price volatility.</t>
+          <t>- **Critical minerals as a weapon** (High): Geopolitical concentration of rare earths and battery materials; supply weaponisation constrains energy transition and manufacturing resilience.</t>
         </is>
       </c>
     </row>
@@ -45366,34 +46256,14 @@
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>• **Treasury basis trade (hidden leverage)** (Elevated): Embedded leverage in cash-futures arbitrage poses flash-crash risk if funding conditions tighten unexpectedly.</t>
+          <t>**WATCH CLOSEST:**</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="12" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="12" t="inlineStr">
-        <is>
-          <t>• **Developing-world debt crisis** (Elevated): External refinancing pressure and FX stress amid higher rates increase sovereign default risk.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="12" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="12" t="inlineStr">
-        <is>
-          <t>**WATCH MOST CLOSELY**</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="12" t="inlineStr">
-        <is>
-          <t>Private credit opacity and redemption stress—smallest friction point for system-wide contagion.</t>
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>Private credit's opaque expansion at level 8 — largest single risk score — with no regulatory transparency into leverage or valuation.</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-08-14  -  generated 2026-08-14 12:26 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-08-17  -  generated 2026-08-17 12:02 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="D3" s="7" t="n">
-        <v>69.2283</v>
+        <v>69.5796</v>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>158.817</v>
+        <v>159.24</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>2.42</v>
+        <v>2.39</v>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>6.7407</v>
+        <v>6.7386</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>307.5</v>
+        <v>307.2</v>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
         </is>
       </c>
       <c r="D27" s="7" t="n">
-        <v>12.34</v>
+        <v>11.71</v>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         </is>
       </c>
       <c r="D32" s="7" t="n">
-        <v>6.11</v>
+        <v>5.67</v>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>4426.1001</v>
+        <v>4456.3999</v>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
@@ -4009,7 +4009,7 @@
         </is>
       </c>
       <c r="D44" s="7" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>6.589</v>
+        <v>6.6895</v>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
         </is>
       </c>
       <c r="D49" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         </is>
       </c>
       <c r="D50" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         </is>
       </c>
       <c r="D54" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         </is>
       </c>
       <c r="D55" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         </is>
       </c>
       <c r="D59" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="D60" s="7" t="n">
-        <v>81.98</v>
+        <v>82.48999999999999</v>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="D62" s="7" t="n">
-        <v>14.53</v>
+        <v>14.91</v>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
         </is>
       </c>
       <c r="D63" s="7" t="n">
-        <v>69.2283</v>
+        <v>69.5796</v>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="G9" s="9" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4.25</t>
         </is>
       </c>
     </row>
@@ -5793,17 +5793,17 @@
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Elevated</t>
         </is>
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.5</t>
         </is>
       </c>
     </row>
@@ -7421,7 +7421,7 @@
       </c>
       <c r="E57" s="9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F57" s="9" t="inlineStr">
@@ -7431,7 +7431,7 @@
       </c>
       <c r="G57" s="9" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5.5</t>
         </is>
       </c>
     </row>
@@ -7468,7 +7468,7 @@
       </c>
       <c r="G58" s="9" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>6.5</t>
         </is>
       </c>
     </row>
@@ -7495,7 +7495,7 @@
       </c>
       <c r="E59" s="9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F59" s="9" t="inlineStr">
@@ -7505,7 +7505,7 @@
       </c>
       <c r="G59" s="9" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>6.0</t>
         </is>
       </c>
     </row>
@@ -7579,7 +7579,7 @@
       </c>
       <c r="G61" s="9" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>5.5</t>
         </is>
       </c>
     </row>
@@ -7616,7 +7616,7 @@
       </c>
       <c r="G62" s="9" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>6.25</t>
         </is>
       </c>
     </row>
@@ -7653,7 +7653,7 @@
       </c>
       <c r="G63" s="9" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4.25</t>
         </is>
       </c>
     </row>
@@ -7690,7 +7690,7 @@
       </c>
       <c r="G64" s="9" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>6.5</t>
         </is>
       </c>
     </row>
@@ -7717,7 +7717,7 @@
       </c>
       <c r="E65" s="9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F65" s="9" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="G65" s="9" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5.75</t>
         </is>
       </c>
     </row>
@@ -7764,7 +7764,7 @@
       </c>
       <c r="G66" s="9" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4.5</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="E67" s="9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F67" s="9" t="inlineStr">
@@ -7801,7 +7801,7 @@
       </c>
       <c r="G67" s="9" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5.5</t>
         </is>
       </c>
     </row>
@@ -7828,7 +7828,7 @@
       </c>
       <c r="E68" s="9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F68" s="9" t="inlineStr">
@@ -7838,7 +7838,7 @@
       </c>
       <c r="G68" s="9" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>3.5</t>
         </is>
       </c>
     </row>
@@ -7865,17 +7865,17 @@
       </c>
       <c r="E69" s="9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F69" s="9" t="inlineStr">
         <is>
-          <t>Elevated</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="G69" s="9" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.5</t>
         </is>
       </c>
     </row>
@@ -7912,7 +7912,7 @@
       </c>
       <c r="G70" s="9" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4.25</t>
         </is>
       </c>
     </row>
@@ -7949,7 +7949,7 @@
       </c>
       <c r="G71" s="9" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>6.5</t>
         </is>
       </c>
     </row>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="G72" s="9" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.5</t>
         </is>
       </c>
     </row>
@@ -8013,17 +8013,17 @@
       </c>
       <c r="E73" s="9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F73" s="9" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Elevated</t>
         </is>
       </c>
       <c r="G73" s="9" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>5.25</t>
         </is>
       </c>
     </row>
@@ -8097,7 +8097,7 @@
       </c>
       <c r="G75" s="9" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5.25</t>
         </is>
       </c>
     </row>
@@ -8134,7 +8134,7 @@
       </c>
       <c r="G76" s="9" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6.0</t>
         </is>
       </c>
     </row>
@@ -8171,7 +8171,7 @@
       </c>
       <c r="G77" s="9" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4.25</t>
         </is>
       </c>
     </row>
@@ -8827,17 +8827,17 @@
       </c>
       <c r="E95" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F95" s="9" t="inlineStr">
         <is>
-          <t>Elevated</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G95" s="9" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>7.0</t>
         </is>
       </c>
     </row>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="G96" s="9" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -8911,7 +8911,7 @@
       </c>
       <c r="G97" s="9" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>6.5</t>
         </is>
       </c>
     </row>
@@ -9577,7 +9577,7 @@
       </c>
       <c r="G115" s="9" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>4.75</t>
         </is>
       </c>
     </row>
@@ -9604,17 +9604,17 @@
       </c>
       <c r="E116" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F116" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Elevated</t>
         </is>
       </c>
       <c r="G116" s="9" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.5</t>
         </is>
       </c>
     </row>
@@ -9651,7 +9651,7 @@
       </c>
       <c r="G117" s="9" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5.25</t>
         </is>
       </c>
     </row>
@@ -9688,7 +9688,7 @@
       </c>
       <c r="G118" s="9" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6.25</t>
         </is>
       </c>
     </row>
@@ -9732,7 +9732,7 @@
     <row r="120">
       <c r="A120" s="9" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B120" s="9" t="inlineStr">
@@ -9763,13 +9763,18 @@
       <c r="G120" s="9" t="inlineStr">
         <is>
           <t>5.5</t>
+        </is>
+      </c>
+      <c r="H120" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="9" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B121" s="9" t="inlineStr">
@@ -9800,13 +9805,18 @@
       <c r="G121" s="9" t="inlineStr">
         <is>
           <t>6.5</t>
+        </is>
+      </c>
+      <c r="H121" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="9" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B122" s="9" t="inlineStr">
@@ -9837,13 +9847,18 @@
       <c r="G122" s="9" t="inlineStr">
         <is>
           <t>6.0</t>
+        </is>
+      </c>
+      <c r="H122" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="9" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B123" s="9" t="inlineStr">
@@ -9874,13 +9889,18 @@
       <c r="G123" s="9" t="inlineStr">
         <is>
           <t>5.0</t>
+        </is>
+      </c>
+      <c r="H123" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="9" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B124" s="9" t="inlineStr">
@@ -9890,7 +9910,7 @@
       </c>
       <c r="C124" s="9" t="inlineStr">
         <is>
-          <t>China's exported deflation</t>
+          <t>China's price spillover (deflation or cost-push)</t>
         </is>
       </c>
       <c r="D124" s="9" t="inlineStr">
@@ -9910,14 +9930,19 @@
       </c>
       <c r="G124" s="9" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="H124" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="9" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B125" s="9" t="inlineStr">
@@ -9937,24 +9962,29 @@
       </c>
       <c r="E125" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F125" s="9" t="inlineStr">
         <is>
-          <t>Elevated</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G125" s="9" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>6.75</t>
+        </is>
+      </c>
+      <c r="H125" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="9" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B126" s="9" t="inlineStr">
@@ -9985,13 +10015,18 @@
       <c r="G126" s="9" t="inlineStr">
         <is>
           <t>4.25</t>
+        </is>
+      </c>
+      <c r="H126" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="9" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B127" s="9" t="inlineStr">
@@ -10022,13 +10057,18 @@
       <c r="G127" s="9" t="inlineStr">
         <is>
           <t>6.5</t>
+        </is>
+      </c>
+      <c r="H127" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="9" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B128" s="9" t="inlineStr">
@@ -10048,7 +10088,7 @@
       </c>
       <c r="E128" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F128" s="9" t="inlineStr">
@@ -10058,14 +10098,19 @@
       </c>
       <c r="G128" s="9" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="H128" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="9" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B129" s="9" t="inlineStr">
@@ -10085,24 +10130,29 @@
       </c>
       <c r="E129" s="9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F129" s="9" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Elevated</t>
         </is>
       </c>
       <c r="G129" s="9" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H129" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="9" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B130" s="9" t="inlineStr">
@@ -10122,7 +10172,7 @@
       </c>
       <c r="E130" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F130" s="9" t="inlineStr">
@@ -10132,14 +10182,19 @@
       </c>
       <c r="G130" s="9" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H130" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="9" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B131" s="9" t="inlineStr">
@@ -10170,13 +10225,18 @@
       <c r="G131" s="9" t="inlineStr">
         <is>
           <t>3.5</t>
+        </is>
+      </c>
+      <c r="H131" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="9" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B132" s="9" t="inlineStr">
@@ -10207,13 +10267,18 @@
       <c r="G132" s="9" t="inlineStr">
         <is>
           <t>4.5</t>
+        </is>
+      </c>
+      <c r="H132" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="9" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B133" s="9" t="inlineStr">
@@ -10233,24 +10298,29 @@
       </c>
       <c r="E133" s="9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F133" s="9" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Elevated</t>
         </is>
       </c>
       <c r="G133" s="9" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="H133" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="9" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B134" s="9" t="inlineStr">
@@ -10281,13 +10351,18 @@
       <c r="G134" s="9" t="inlineStr">
         <is>
           <t>6.5</t>
+        </is>
+      </c>
+      <c r="H134" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="9" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B135" s="9" t="inlineStr">
@@ -10318,13 +10393,18 @@
       <c r="G135" s="9" t="inlineStr">
         <is>
           <t>4.5</t>
+        </is>
+      </c>
+      <c r="H135" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="9" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B136" s="9" t="inlineStr">
@@ -10354,14 +10434,19 @@
       </c>
       <c r="G136" s="9" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="H136" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="9" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B137" s="9" t="inlineStr">
@@ -10381,24 +10466,29 @@
       </c>
       <c r="E137" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F137" s="9" t="inlineStr">
         <is>
-          <t>Elevated</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G137" s="9" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H137" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="9" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B138" s="9" t="inlineStr">
@@ -10418,7 +10508,7 @@
       </c>
       <c r="E138" s="9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F138" s="9" t="inlineStr">
@@ -10428,14 +10518,19 @@
       </c>
       <c r="G138" s="9" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H138" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="9" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B139" s="9" t="inlineStr">
@@ -10466,13 +10561,18 @@
       <c r="G139" s="9" t="inlineStr">
         <is>
           <t>6.25</t>
+        </is>
+      </c>
+      <c r="H139" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="9" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B140" s="9" t="inlineStr">
@@ -10503,6 +10603,11 @@
       <c r="G140" s="9" t="inlineStr">
         <is>
           <t>4.25</t>
+        </is>
+      </c>
+      <c r="H140" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
         </is>
       </c>
     </row>
@@ -11589,7 +11694,7 @@
       </c>
       <c r="G166" s="9" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="H166" s="9" t="inlineStr">
@@ -11831,7 +11936,7 @@
       </c>
       <c r="E172" s="9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F172" s="9" t="inlineStr">
@@ -11841,7 +11946,7 @@
       </c>
       <c r="G172" s="9" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="H172" s="9" t="inlineStr">
@@ -11957,17 +12062,17 @@
       </c>
       <c r="E175" s="9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F175" s="9" t="inlineStr">
         <is>
-          <t>Elevated</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="G175" s="9" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="H175" s="9" t="inlineStr">
@@ -11999,17 +12104,17 @@
       </c>
       <c r="E176" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F176" s="9" t="inlineStr">
         <is>
-          <t>Elevated</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G176" s="9" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="H176" s="9" t="inlineStr">
@@ -12093,7 +12198,7 @@
       </c>
       <c r="G178" s="9" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="H178" s="9" t="inlineStr">
@@ -12125,17 +12230,17 @@
       </c>
       <c r="E179" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F179" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Elevated</t>
         </is>
       </c>
       <c r="G179" s="9" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="H179" s="9" t="inlineStr">
@@ -12219,7 +12324,7 @@
       </c>
       <c r="G181" s="9" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="H181" s="9" t="inlineStr">
@@ -12273,7 +12378,7 @@
     <row r="183">
       <c r="A183" s="9" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B183" s="9" t="inlineStr">
@@ -12315,7 +12420,7 @@
     <row r="184">
       <c r="A184" s="9" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B184" s="9" t="inlineStr">
@@ -12357,7 +12462,7 @@
     <row r="185">
       <c r="A185" s="9" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B185" s="9" t="inlineStr">
@@ -12399,7 +12504,7 @@
     <row r="186">
       <c r="A186" s="9" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B186" s="9" t="inlineStr">
@@ -12441,7 +12546,7 @@
     <row r="187">
       <c r="A187" s="9" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B187" s="9" t="inlineStr">
@@ -12483,7 +12588,7 @@
     <row r="188">
       <c r="A188" s="9" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B188" s="9" t="inlineStr">
@@ -12525,7 +12630,7 @@
     <row r="189">
       <c r="A189" s="9" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B189" s="9" t="inlineStr">
@@ -12567,7 +12672,7 @@
     <row r="190">
       <c r="A190" s="9" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B190" s="9" t="inlineStr">
@@ -12609,7 +12714,7 @@
     <row r="191">
       <c r="A191" s="9" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B191" s="9" t="inlineStr">
@@ -12651,7 +12756,7 @@
     <row r="192">
       <c r="A192" s="9" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B192" s="9" t="inlineStr">
@@ -12693,7 +12798,7 @@
     <row r="193">
       <c r="A193" s="9" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B193" s="9" t="inlineStr">
@@ -12735,7 +12840,7 @@
     <row r="194">
       <c r="A194" s="9" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B194" s="9" t="inlineStr">
@@ -12777,7 +12882,7 @@
     <row r="195">
       <c r="A195" s="9" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B195" s="9" t="inlineStr">
@@ -12819,7 +12924,7 @@
     <row r="196">
       <c r="A196" s="9" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B196" s="9" t="inlineStr">
@@ -12861,7 +12966,7 @@
     <row r="197">
       <c r="A197" s="9" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B197" s="9" t="inlineStr">
@@ -12903,7 +13008,7 @@
     <row r="198">
       <c r="A198" s="9" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B198" s="9" t="inlineStr">
@@ -12945,7 +13050,7 @@
     <row r="199">
       <c r="A199" s="9" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B199" s="9" t="inlineStr">
@@ -12987,7 +13092,7 @@
     <row r="200">
       <c r="A200" s="9" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B200" s="9" t="inlineStr">
@@ -13029,7 +13134,7 @@
     <row r="201">
       <c r="A201" s="9" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B201" s="9" t="inlineStr">
@@ -13071,7 +13176,7 @@
     <row r="202">
       <c r="A202" s="9" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B202" s="9" t="inlineStr">
@@ -13113,7 +13218,7 @@
     <row r="203">
       <c r="A203" s="9" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B203" s="9" t="inlineStr">
@@ -13155,7 +13260,7 @@
     <row r="204">
       <c r="A204" s="9" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B204" s="9" t="inlineStr">
@@ -13197,7 +13302,7 @@
     <row r="205">
       <c r="A205" s="9" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B205" s="9" t="inlineStr">
@@ -13239,7 +13344,7 @@
     <row r="206">
       <c r="A206" s="9" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B206" s="9" t="inlineStr">
@@ -13281,7 +13386,7 @@
     <row r="207">
       <c r="A207" s="9" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B207" s="9" t="inlineStr">
@@ -13323,7 +13428,7 @@
     <row r="208">
       <c r="A208" s="9" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B208" s="9" t="inlineStr">
@@ -13365,7 +13470,7 @@
     <row r="209">
       <c r="A209" s="9" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B209" s="9" t="inlineStr">
@@ -13407,7 +13512,7 @@
     <row r="210">
       <c r="A210" s="9" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B210" s="9" t="inlineStr">
@@ -13449,7 +13554,7 @@
     <row r="211">
       <c r="A211" s="9" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B211" s="9" t="inlineStr">
@@ -13491,7 +13596,7 @@
     <row r="212">
       <c r="A212" s="9" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B212" s="9" t="inlineStr">
@@ -13533,7 +13638,7 @@
     <row r="213">
       <c r="A213" s="9" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B213" s="9" t="inlineStr">
@@ -13575,7 +13680,7 @@
     <row r="214">
       <c r="A214" s="9" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B214" s="9" t="inlineStr">
@@ -13617,7 +13722,7 @@
     <row r="215">
       <c r="A215" s="9" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B215" s="9" t="inlineStr">
@@ -13659,7 +13764,7 @@
     <row r="216">
       <c r="A216" s="9" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B216" s="9" t="inlineStr">
@@ -13701,7 +13806,7 @@
     <row r="217">
       <c r="A217" s="9" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B217" s="9" t="inlineStr">
@@ -13743,7 +13848,7 @@
     <row r="218">
       <c r="A218" s="9" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B218" s="9" t="inlineStr">
@@ -13785,7 +13890,7 @@
     <row r="219">
       <c r="A219" s="9" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B219" s="9" t="inlineStr">
@@ -13827,7 +13932,7 @@
     <row r="220">
       <c r="A220" s="9" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B220" s="9" t="inlineStr">
@@ -13869,7 +13974,7 @@
     <row r="221">
       <c r="A221" s="9" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B221" s="9" t="inlineStr">
@@ -13911,7 +14016,7 @@
     <row r="222">
       <c r="A222" s="9" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B222" s="9" t="inlineStr">
@@ -13953,7 +14058,7 @@
     <row r="223">
       <c r="A223" s="9" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B223" s="9" t="inlineStr">
@@ -13995,7 +14100,7 @@
     <row r="224">
       <c r="A224" s="9" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B224" s="9" t="inlineStr">
@@ -14037,7 +14142,7 @@
     <row r="225">
       <c r="A225" s="9" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B225" s="9" t="inlineStr">
@@ -14079,7 +14184,7 @@
     <row r="226">
       <c r="A226" s="9" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B226" s="9" t="inlineStr">
@@ -14121,7 +14226,7 @@
     <row r="227">
       <c r="A227" s="9" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B227" s="9" t="inlineStr">
@@ -14163,7 +14268,7 @@
     <row r="228">
       <c r="A228" s="9" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B228" s="9" t="inlineStr">
@@ -14183,7 +14288,7 @@
       </c>
       <c r="E228" s="9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F228" s="9" t="inlineStr">
@@ -14193,7 +14298,7 @@
       </c>
       <c r="G228" s="9" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="H228" s="9" t="inlineStr">
@@ -14205,7 +14310,7 @@
     <row r="229">
       <c r="A229" s="9" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B229" s="9" t="inlineStr">
@@ -14247,7 +14352,7 @@
     <row r="230">
       <c r="A230" s="9" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B230" s="9" t="inlineStr">
@@ -14289,7 +14394,7 @@
     <row r="231">
       <c r="A231" s="9" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B231" s="9" t="inlineStr">
@@ -14331,7 +14436,7 @@
     <row r="232">
       <c r="A232" s="9" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B232" s="9" t="inlineStr">
@@ -14373,7 +14478,7 @@
     <row r="233">
       <c r="A233" s="9" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B233" s="9" t="inlineStr">
@@ -14415,7 +14520,7 @@
     <row r="234">
       <c r="A234" s="9" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B234" s="9" t="inlineStr">
@@ -14457,7 +14562,7 @@
     <row r="235">
       <c r="A235" s="9" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B235" s="9" t="inlineStr">
@@ -14499,7 +14604,7 @@
     <row r="236">
       <c r="A236" s="9" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B236" s="9" t="inlineStr">
@@ -14541,7 +14646,7 @@
     <row r="237">
       <c r="A237" s="9" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B237" s="9" t="inlineStr">
@@ -14583,7 +14688,7 @@
     <row r="238">
       <c r="A238" s="9" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B238" s="9" t="inlineStr">
@@ -14625,7 +14730,7 @@
     <row r="239">
       <c r="A239" s="9" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B239" s="9" t="inlineStr">
@@ -14667,7 +14772,7 @@
     <row r="240">
       <c r="A240" s="9" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B240" s="9" t="inlineStr">
@@ -14709,7 +14814,7 @@
     <row r="241">
       <c r="A241" s="9" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B241" s="9" t="inlineStr">
@@ -14751,7 +14856,7 @@
     <row r="242">
       <c r="A242" s="9" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B242" s="9" t="inlineStr">
@@ -14793,7 +14898,7 @@
     <row r="243">
       <c r="A243" s="9" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B243" s="9" t="inlineStr">
@@ -14835,7 +14940,7 @@
     <row r="244">
       <c r="A244" s="9" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B244" s="9" t="inlineStr">
@@ -14877,7 +14982,7 @@
     <row r="245">
       <c r="A245" s="9" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B245" s="9" t="inlineStr">
@@ -14981,17 +15086,17 @@
       </c>
       <c r="E247" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F247" s="9" t="inlineStr">
         <is>
-          <t>Elevated</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G247" s="9" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="H247" s="9" t="inlineStr">
@@ -17565,7 +17670,7 @@
     <row r="309">
       <c r="A309" s="9" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B309" s="9" t="inlineStr">
@@ -17607,7 +17712,7 @@
     <row r="310">
       <c r="A310" s="9" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B310" s="9" t="inlineStr">
@@ -17649,7 +17754,7 @@
     <row r="311">
       <c r="A311" s="9" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B311" s="9" t="inlineStr">
@@ -17691,7 +17796,7 @@
     <row r="312">
       <c r="A312" s="9" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B312" s="9" t="inlineStr">
@@ -17733,7 +17838,7 @@
     <row r="313">
       <c r="A313" s="9" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B313" s="9" t="inlineStr">
@@ -17775,7 +17880,7 @@
     <row r="314">
       <c r="A314" s="9" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B314" s="9" t="inlineStr">
@@ -17817,7 +17922,7 @@
     <row r="315">
       <c r="A315" s="9" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B315" s="9" t="inlineStr">
@@ -17859,7 +17964,7 @@
     <row r="316">
       <c r="A316" s="9" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B316" s="9" t="inlineStr">
@@ -17901,7 +18006,7 @@
     <row r="317">
       <c r="A317" s="9" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B317" s="9" t="inlineStr">
@@ -17943,7 +18048,7 @@
     <row r="318">
       <c r="A318" s="9" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B318" s="9" t="inlineStr">
@@ -17985,7 +18090,7 @@
     <row r="319">
       <c r="A319" s="9" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B319" s="9" t="inlineStr">
@@ -18027,7 +18132,7 @@
     <row r="320">
       <c r="A320" s="9" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B320" s="9" t="inlineStr">
@@ -18069,7 +18174,7 @@
     <row r="321">
       <c r="A321" s="9" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B321" s="9" t="inlineStr">
@@ -18111,7 +18216,7 @@
     <row r="322">
       <c r="A322" s="9" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B322" s="9" t="inlineStr">
@@ -18153,7 +18258,7 @@
     <row r="323">
       <c r="A323" s="9" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B323" s="9" t="inlineStr">
@@ -18195,7 +18300,7 @@
     <row r="324">
       <c r="A324" s="9" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B324" s="9" t="inlineStr">
@@ -18237,7 +18342,7 @@
     <row r="325">
       <c r="A325" s="9" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B325" s="9" t="inlineStr">
@@ -18279,7 +18384,7 @@
     <row r="326">
       <c r="A326" s="9" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B326" s="9" t="inlineStr">
@@ -18321,7 +18426,7 @@
     <row r="327">
       <c r="A327" s="9" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B327" s="9" t="inlineStr">
@@ -18363,7 +18468,7 @@
     <row r="328">
       <c r="A328" s="9" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B328" s="9" t="inlineStr">
@@ -18405,7 +18510,7 @@
     <row r="329">
       <c r="A329" s="9" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B329" s="9" t="inlineStr">
@@ -18447,7 +18552,7 @@
     <row r="330">
       <c r="A330" s="9" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B330" s="9" t="inlineStr">
@@ -18489,7 +18594,7 @@
     <row r="331">
       <c r="A331" s="9" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B331" s="9" t="inlineStr">
@@ -18531,7 +18636,7 @@
     <row r="332">
       <c r="A332" s="9" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B332" s="9" t="inlineStr">
@@ -18573,7 +18678,7 @@
     <row r="333">
       <c r="A333" s="9" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B333" s="9" t="inlineStr">
@@ -18615,7 +18720,7 @@
     <row r="334">
       <c r="A334" s="9" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B334" s="9" t="inlineStr">
@@ -18657,7 +18762,7 @@
     <row r="335">
       <c r="A335" s="9" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B335" s="9" t="inlineStr">
@@ -18699,7 +18804,7 @@
     <row r="336">
       <c r="A336" s="9" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B336" s="9" t="inlineStr">
@@ -18741,7 +18846,7 @@
     <row r="337">
       <c r="A337" s="9" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B337" s="9" t="inlineStr">
@@ -18783,7 +18888,7 @@
     <row r="338">
       <c r="A338" s="9" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B338" s="9" t="inlineStr">
@@ -18825,7 +18930,7 @@
     <row r="339">
       <c r="A339" s="9" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B339" s="9" t="inlineStr">
@@ -18867,7 +18972,7 @@
     <row r="340">
       <c r="A340" s="9" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B340" s="9" t="inlineStr">
@@ -18909,7 +19014,7 @@
     <row r="341">
       <c r="A341" s="9" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B341" s="9" t="inlineStr">
@@ -18951,7 +19056,7 @@
     <row r="342">
       <c r="A342" s="9" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B342" s="9" t="inlineStr">
@@ -18993,7 +19098,7 @@
     <row r="343">
       <c r="A343" s="9" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B343" s="9" t="inlineStr">
@@ -19035,7 +19140,7 @@
     <row r="344">
       <c r="A344" s="9" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B344" s="9" t="inlineStr">
@@ -19077,7 +19182,7 @@
     <row r="345">
       <c r="A345" s="9" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B345" s="9" t="inlineStr">
@@ -19119,7 +19224,7 @@
     <row r="346">
       <c r="A346" s="9" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B346" s="9" t="inlineStr">
@@ -19161,7 +19266,7 @@
     <row r="347">
       <c r="A347" s="9" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B347" s="9" t="inlineStr">
@@ -19203,7 +19308,7 @@
     <row r="348">
       <c r="A348" s="9" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B348" s="9" t="inlineStr">
@@ -19245,7 +19350,7 @@
     <row r="349">
       <c r="A349" s="9" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B349" s="9" t="inlineStr">
@@ -19287,7 +19392,7 @@
     <row r="350">
       <c r="A350" s="9" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B350" s="9" t="inlineStr">
@@ -19329,7 +19434,7 @@
     <row r="351">
       <c r="A351" s="9" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B351" s="9" t="inlineStr">
@@ -19371,7 +19476,7 @@
     <row r="352">
       <c r="A352" s="9" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B352" s="9" t="inlineStr">
@@ -19391,7 +19496,7 @@
       </c>
       <c r="E352" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F352" s="9" t="inlineStr">
@@ -19401,7 +19506,7 @@
       </c>
       <c r="G352" s="9" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="H352" s="9" t="inlineStr">
@@ -19413,7 +19518,7 @@
     <row r="353">
       <c r="A353" s="9" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B353" s="9" t="inlineStr">
@@ -19433,17 +19538,17 @@
       </c>
       <c r="E353" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F353" s="9" t="inlineStr">
         <is>
-          <t>Elevated</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G353" s="9" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="H353" s="9" t="inlineStr">
@@ -19455,7 +19560,7 @@
     <row r="354">
       <c r="A354" s="9" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B354" s="9" t="inlineStr">
@@ -19497,7 +19602,7 @@
     <row r="355">
       <c r="A355" s="9" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B355" s="9" t="inlineStr">
@@ -19539,7 +19644,7 @@
     <row r="356">
       <c r="A356" s="9" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B356" s="9" t="inlineStr">
@@ -19581,7 +19686,7 @@
     <row r="357">
       <c r="A357" s="9" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B357" s="9" t="inlineStr">
@@ -19623,7 +19728,7 @@
     <row r="358">
       <c r="A358" s="9" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B358" s="9" t="inlineStr">
@@ -19665,7 +19770,7 @@
     <row r="359">
       <c r="A359" s="9" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B359" s="9" t="inlineStr">
@@ -19707,7 +19812,7 @@
     <row r="360">
       <c r="A360" s="9" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B360" s="9" t="inlineStr">
@@ -19749,7 +19854,7 @@
     <row r="361">
       <c r="A361" s="9" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B361" s="9" t="inlineStr">
@@ -19791,7 +19896,7 @@
     <row r="362">
       <c r="A362" s="9" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B362" s="9" t="inlineStr">
@@ -19833,7 +19938,7 @@
     <row r="363">
       <c r="A363" s="9" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B363" s="9" t="inlineStr">
@@ -19875,7 +19980,7 @@
     <row r="364">
       <c r="A364" s="9" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B364" s="9" t="inlineStr">
@@ -19917,7 +20022,7 @@
     <row r="365">
       <c r="A365" s="9" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B365" s="9" t="inlineStr">
@@ -19959,7 +20064,7 @@
     <row r="366">
       <c r="A366" s="9" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B366" s="9" t="inlineStr">
@@ -20001,7 +20106,7 @@
     <row r="367">
       <c r="A367" s="9" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B367" s="9" t="inlineStr">
@@ -20031,7 +20136,7 @@
       </c>
       <c r="G367" s="9" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="H367" s="9" t="inlineStr">
@@ -20043,7 +20148,7 @@
     <row r="368">
       <c r="A368" s="9" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B368" s="9" t="inlineStr">
@@ -20085,7 +20190,7 @@
     <row r="369">
       <c r="A369" s="9" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B369" s="9" t="inlineStr">
@@ -20127,7 +20232,7 @@
     <row r="370">
       <c r="A370" s="9" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B370" s="9" t="inlineStr">
@@ -20169,7 +20274,7 @@
     <row r="371">
       <c r="A371" s="9" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B371" s="9" t="inlineStr">
@@ -20211,7 +20316,7 @@
     <row r="372">
       <c r="A372" s="9" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B372" s="9" t="inlineStr">
@@ -20253,7 +20358,7 @@
     <row r="373">
       <c r="A373" s="9" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B373" s="9" t="inlineStr">
@@ -20295,7 +20400,7 @@
     <row r="374">
       <c r="A374" s="9" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B374" s="9" t="inlineStr">
@@ -20337,7 +20442,7 @@
     <row r="375">
       <c r="A375" s="9" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B375" s="9" t="inlineStr">
@@ -20379,7 +20484,7 @@
     <row r="376">
       <c r="A376" s="9" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B376" s="9" t="inlineStr">
@@ -20421,7 +20526,7 @@
     <row r="377">
       <c r="A377" s="9" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B377" s="9" t="inlineStr">
@@ -20463,7 +20568,7 @@
     <row r="378">
       <c r="A378" s="9" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B378" s="9" t="inlineStr">
@@ -20505,7 +20610,7 @@
     <row r="379">
       <c r="A379" s="9" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B379" s="9" t="inlineStr">
@@ -20547,7 +20652,7 @@
     <row r="380">
       <c r="A380" s="9" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B380" s="9" t="inlineStr">
@@ -20589,7 +20694,7 @@
     <row r="381">
       <c r="A381" s="9" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B381" s="9" t="inlineStr">
@@ -20631,7 +20736,7 @@
     <row r="382">
       <c r="A382" s="9" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B382" s="9" t="inlineStr">
@@ -20673,7 +20778,7 @@
     <row r="383">
       <c r="A383" s="9" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B383" s="9" t="inlineStr">
@@ -20715,7 +20820,7 @@
     <row r="384">
       <c r="A384" s="9" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B384" s="9" t="inlineStr">
@@ -20757,7 +20862,7 @@
     <row r="385">
       <c r="A385" s="9" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B385" s="9" t="inlineStr">
@@ -20799,7 +20904,7 @@
     <row r="386">
       <c r="A386" s="9" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B386" s="9" t="inlineStr">
@@ -20841,7 +20946,7 @@
     <row r="387">
       <c r="A387" s="9" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B387" s="9" t="inlineStr">
@@ -20883,7 +20988,7 @@
     <row r="388">
       <c r="A388" s="9" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B388" s="9" t="inlineStr">
@@ -20925,7 +21030,7 @@
     <row r="389">
       <c r="A389" s="9" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B389" s="9" t="inlineStr">
@@ -20967,7 +21072,7 @@
     <row r="390">
       <c r="A390" s="9" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B390" s="9" t="inlineStr">
@@ -21009,7 +21114,7 @@
     <row r="391">
       <c r="A391" s="9" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B391" s="9" t="inlineStr">
@@ -21051,7 +21156,7 @@
     <row r="392">
       <c r="A392" s="9" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B392" s="9" t="inlineStr">
@@ -21093,7 +21198,7 @@
     <row r="393">
       <c r="A393" s="9" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B393" s="9" t="inlineStr">
@@ -21135,7 +21240,7 @@
     <row r="394">
       <c r="A394" s="9" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B394" s="9" t="inlineStr">
@@ -21177,7 +21282,7 @@
     <row r="395">
       <c r="A395" s="9" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B395" s="9" t="inlineStr">
@@ -21219,7 +21324,7 @@
     <row r="396">
       <c r="A396" s="9" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B396" s="9" t="inlineStr">
@@ -21261,7 +21366,7 @@
     <row r="397">
       <c r="A397" s="9" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B397" s="9" t="inlineStr">
@@ -21303,7 +21408,7 @@
     <row r="398">
       <c r="A398" s="9" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B398" s="9" t="inlineStr">
@@ -21345,7 +21450,7 @@
     <row r="399">
       <c r="A399" s="9" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B399" s="9" t="inlineStr">
@@ -21387,7 +21492,7 @@
     <row r="400">
       <c r="A400" s="9" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B400" s="9" t="inlineStr">
@@ -21429,7 +21534,7 @@
     <row r="401">
       <c r="A401" s="9" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B401" s="9" t="inlineStr">
@@ -21471,7 +21576,7 @@
     <row r="402">
       <c r="A402" s="9" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B402" s="9" t="inlineStr">
@@ -21513,7 +21618,7 @@
     <row r="403">
       <c r="A403" s="9" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B403" s="9" t="inlineStr">
@@ -21555,7 +21660,7 @@
     <row r="404">
       <c r="A404" s="9" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B404" s="9" t="inlineStr">
@@ -21597,7 +21702,7 @@
     <row r="405">
       <c r="A405" s="9" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B405" s="9" t="inlineStr">
@@ -21639,7 +21744,7 @@
     <row r="406">
       <c r="A406" s="9" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B406" s="9" t="inlineStr">
@@ -21681,7 +21786,7 @@
     <row r="407">
       <c r="A407" s="9" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B407" s="9" t="inlineStr">
@@ -21723,7 +21828,7 @@
     <row r="408">
       <c r="A408" s="9" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B408" s="9" t="inlineStr">
@@ -21765,7 +21870,7 @@
     <row r="409">
       <c r="A409" s="9" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B409" s="9" t="inlineStr">
@@ -21807,7 +21912,7 @@
     <row r="410">
       <c r="A410" s="9" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B410" s="9" t="inlineStr">
@@ -21849,7 +21954,7 @@
     <row r="411">
       <c r="A411" s="9" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B411" s="9" t="inlineStr">
@@ -21891,7 +21996,7 @@
     <row r="412">
       <c r="A412" s="9" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B412" s="9" t="inlineStr">
@@ -21933,7 +22038,7 @@
     <row r="413">
       <c r="A413" s="9" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B413" s="9" t="inlineStr">
@@ -21975,7 +22080,7 @@
     <row r="414">
       <c r="A414" s="9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B414" s="9" t="inlineStr">
@@ -22017,7 +22122,7 @@
     <row r="415">
       <c r="A415" s="9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B415" s="9" t="inlineStr">
@@ -22059,7 +22164,7 @@
     <row r="416">
       <c r="A416" s="9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B416" s="9" t="inlineStr">
@@ -22101,7 +22206,7 @@
     <row r="417">
       <c r="A417" s="9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B417" s="9" t="inlineStr">
@@ -22143,7 +22248,7 @@
     <row r="418">
       <c r="A418" s="9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B418" s="9" t="inlineStr">
@@ -22185,7 +22290,7 @@
     <row r="419">
       <c r="A419" s="9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B419" s="9" t="inlineStr">
@@ -22227,7 +22332,7 @@
     <row r="420">
       <c r="A420" s="9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B420" s="9" t="inlineStr">
@@ -22269,7 +22374,7 @@
     <row r="421">
       <c r="A421" s="9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B421" s="9" t="inlineStr">
@@ -22311,7 +22416,7 @@
     <row r="422">
       <c r="A422" s="9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B422" s="9" t="inlineStr">
@@ -22353,7 +22458,7 @@
     <row r="423">
       <c r="A423" s="9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B423" s="9" t="inlineStr">
@@ -22395,7 +22500,7 @@
     <row r="424">
       <c r="A424" s="9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B424" s="9" t="inlineStr">
@@ -22437,7 +22542,7 @@
     <row r="425">
       <c r="A425" s="9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B425" s="9" t="inlineStr">
@@ -22479,7 +22584,7 @@
     <row r="426">
       <c r="A426" s="9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B426" s="9" t="inlineStr">
@@ -22521,7 +22626,7 @@
     <row r="427">
       <c r="A427" s="9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B427" s="9" t="inlineStr">
@@ -22563,7 +22668,7 @@
     <row r="428">
       <c r="A428" s="9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B428" s="9" t="inlineStr">
@@ -22605,7 +22710,7 @@
     <row r="429">
       <c r="A429" s="9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B429" s="9" t="inlineStr">
@@ -22647,7 +22752,7 @@
     <row r="430">
       <c r="A430" s="9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B430" s="9" t="inlineStr">
@@ -22689,7 +22794,7 @@
     <row r="431">
       <c r="A431" s="9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B431" s="9" t="inlineStr">
@@ -22731,7 +22836,7 @@
     <row r="432">
       <c r="A432" s="9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B432" s="9" t="inlineStr">
@@ -22773,7 +22878,7 @@
     <row r="433">
       <c r="A433" s="9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B433" s="9" t="inlineStr">
@@ -22815,7 +22920,7 @@
     <row r="434">
       <c r="A434" s="9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B434" s="9" t="inlineStr">
@@ -22857,7 +22962,7 @@
     <row r="435">
       <c r="A435" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B435" s="9" t="inlineStr">
@@ -22899,7 +23004,7 @@
     <row r="436">
       <c r="A436" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B436" s="9" t="inlineStr">
@@ -22941,7 +23046,7 @@
     <row r="437">
       <c r="A437" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B437" s="9" t="inlineStr">
@@ -22983,7 +23088,7 @@
     <row r="438">
       <c r="A438" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B438" s="9" t="inlineStr">
@@ -23025,7 +23130,7 @@
     <row r="439">
       <c r="A439" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B439" s="9" t="inlineStr">
@@ -23067,7 +23172,7 @@
     <row r="440">
       <c r="A440" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B440" s="9" t="inlineStr">
@@ -23109,7 +23214,7 @@
     <row r="441">
       <c r="A441" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B441" s="9" t="inlineStr">
@@ -23151,7 +23256,7 @@
     <row r="442">
       <c r="A442" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B442" s="9" t="inlineStr">
@@ -23193,7 +23298,7 @@
     <row r="443">
       <c r="A443" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B443" s="9" t="inlineStr">
@@ -23235,7 +23340,7 @@
     <row r="444">
       <c r="A444" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B444" s="9" t="inlineStr">
@@ -23277,7 +23382,7 @@
     <row r="445">
       <c r="A445" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B445" s="9" t="inlineStr">
@@ -23319,7 +23424,7 @@
     <row r="446">
       <c r="A446" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B446" s="9" t="inlineStr">
@@ -23361,7 +23466,7 @@
     <row r="447">
       <c r="A447" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B447" s="9" t="inlineStr">
@@ -23403,7 +23508,7 @@
     <row r="448">
       <c r="A448" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B448" s="9" t="inlineStr">
@@ -23445,7 +23550,7 @@
     <row r="449">
       <c r="A449" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B449" s="9" t="inlineStr">
@@ -23487,7 +23592,7 @@
     <row r="450">
       <c r="A450" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B450" s="9" t="inlineStr">
@@ -23529,7 +23634,7 @@
     <row r="451">
       <c r="A451" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B451" s="9" t="inlineStr">
@@ -23571,7 +23676,7 @@
     <row r="452">
       <c r="A452" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B452" s="9" t="inlineStr">
@@ -23613,7 +23718,7 @@
     <row r="453">
       <c r="A453" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B453" s="9" t="inlineStr">
@@ -23655,7 +23760,7 @@
     <row r="454">
       <c r="A454" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B454" s="9" t="inlineStr">
@@ -23697,7 +23802,7 @@
     <row r="455">
       <c r="A455" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B455" s="9" t="inlineStr">
@@ -23739,7 +23844,7 @@
     <row r="456">
       <c r="A456" s="9" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B456" s="9" t="inlineStr">
@@ -23781,7 +23886,7 @@
     <row r="457">
       <c r="A457" s="9" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B457" s="9" t="inlineStr">
@@ -23823,7 +23928,7 @@
     <row r="458">
       <c r="A458" s="9" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B458" s="9" t="inlineStr">
@@ -23865,7 +23970,7 @@
     <row r="459">
       <c r="A459" s="9" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B459" s="9" t="inlineStr">
@@ -23907,7 +24012,7 @@
     <row r="460">
       <c r="A460" s="9" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B460" s="9" t="inlineStr">
@@ -23927,17 +24032,17 @@
       </c>
       <c r="E460" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F460" s="9" t="inlineStr">
         <is>
-          <t>Elevated</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G460" s="9" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="H460" s="9" t="inlineStr">
@@ -23949,7 +24054,7 @@
     <row r="461">
       <c r="A461" s="9" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B461" s="9" t="inlineStr">
@@ -23991,7 +24096,7 @@
     <row r="462">
       <c r="A462" s="9" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B462" s="9" t="inlineStr">
@@ -24033,7 +24138,7 @@
     <row r="463">
       <c r="A463" s="9" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B463" s="9" t="inlineStr">
@@ -24075,7 +24180,7 @@
     <row r="464">
       <c r="A464" s="9" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B464" s="9" t="inlineStr">
@@ -24117,7 +24222,7 @@
     <row r="465">
       <c r="A465" s="9" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B465" s="9" t="inlineStr">
@@ -24159,7 +24264,7 @@
     <row r="466">
       <c r="A466" s="9" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B466" s="9" t="inlineStr">
@@ -24201,7 +24306,7 @@
     <row r="467">
       <c r="A467" s="9" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B467" s="9" t="inlineStr">
@@ -24221,7 +24326,7 @@
       </c>
       <c r="E467" s="9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F467" s="9" t="inlineStr">
@@ -24231,7 +24336,7 @@
       </c>
       <c r="G467" s="9" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="H467" s="9" t="inlineStr">
@@ -24243,7 +24348,7 @@
     <row r="468">
       <c r="A468" s="9" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B468" s="9" t="inlineStr">
@@ -24285,7 +24390,7 @@
     <row r="469">
       <c r="A469" s="9" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B469" s="9" t="inlineStr">
@@ -24327,7 +24432,7 @@
     <row r="470">
       <c r="A470" s="9" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B470" s="9" t="inlineStr">
@@ -24369,7 +24474,7 @@
     <row r="471">
       <c r="A471" s="9" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B471" s="9" t="inlineStr">
@@ -24411,7 +24516,7 @@
     <row r="472">
       <c r="A472" s="9" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B472" s="9" t="inlineStr">
@@ -24441,7 +24546,7 @@
       </c>
       <c r="G472" s="9" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="H472" s="9" t="inlineStr">
@@ -24453,7 +24558,7 @@
     <row r="473">
       <c r="A473" s="9" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B473" s="9" t="inlineStr">
@@ -24473,17 +24578,17 @@
       </c>
       <c r="E473" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F473" s="9" t="inlineStr">
         <is>
-          <t>Elevated</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G473" s="9" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="H473" s="9" t="inlineStr">
@@ -24495,7 +24600,7 @@
     <row r="474">
       <c r="A474" s="9" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B474" s="9" t="inlineStr">
@@ -24537,7 +24642,7 @@
     <row r="475">
       <c r="A475" s="9" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B475" s="9" t="inlineStr">
@@ -24579,7 +24684,7 @@
     <row r="476">
       <c r="A476" s="9" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B476" s="9" t="inlineStr">
@@ -24621,7 +24726,7 @@
     <row r="477">
       <c r="A477" s="9" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B477" s="9" t="inlineStr">
@@ -24663,7 +24768,7 @@
     <row r="478">
       <c r="A478" s="9" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B478" s="9" t="inlineStr">
@@ -24705,7 +24810,7 @@
     <row r="479">
       <c r="A479" s="9" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B479" s="9" t="inlineStr">
@@ -24747,7 +24852,7 @@
     <row r="480">
       <c r="A480" s="9" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B480" s="9" t="inlineStr">
@@ -24789,7 +24894,7 @@
     <row r="481">
       <c r="A481" s="9" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B481" s="9" t="inlineStr">
@@ -24831,7 +24936,7 @@
     <row r="482">
       <c r="A482" s="9" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B482" s="9" t="inlineStr">
@@ -24873,7 +24978,7 @@
     <row r="483">
       <c r="A483" s="9" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B483" s="9" t="inlineStr">
@@ -24915,7 +25020,7 @@
     <row r="484">
       <c r="A484" s="9" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B484" s="9" t="inlineStr">
@@ -24957,7 +25062,7 @@
     <row r="485">
       <c r="A485" s="9" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B485" s="9" t="inlineStr">
@@ -24999,7 +25104,7 @@
     <row r="486">
       <c r="A486" s="9" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B486" s="9" t="inlineStr">
@@ -25041,7 +25146,7 @@
     <row r="487">
       <c r="A487" s="9" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B487" s="9" t="inlineStr">
@@ -25083,7 +25188,7 @@
     <row r="488">
       <c r="A488" s="9" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B488" s="9" t="inlineStr">
@@ -25125,7 +25230,7 @@
     <row r="489">
       <c r="A489" s="9" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B489" s="9" t="inlineStr">
@@ -25167,7 +25272,7 @@
     <row r="490">
       <c r="A490" s="9" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B490" s="9" t="inlineStr">
@@ -25209,7 +25314,7 @@
     <row r="491">
       <c r="A491" s="9" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B491" s="9" t="inlineStr">
@@ -25251,7 +25356,7 @@
     <row r="492">
       <c r="A492" s="9" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B492" s="9" t="inlineStr">
@@ -25293,7 +25398,7 @@
     <row r="493">
       <c r="A493" s="9" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B493" s="9" t="inlineStr">
@@ -25335,7 +25440,7 @@
     <row r="494">
       <c r="A494" s="9" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B494" s="9" t="inlineStr">
@@ -25377,7 +25482,7 @@
     <row r="495">
       <c r="A495" s="9" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B495" s="9" t="inlineStr">
@@ -25419,7 +25524,7 @@
     <row r="496">
       <c r="A496" s="9" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B496" s="9" t="inlineStr">
@@ -25449,7 +25554,7 @@
       </c>
       <c r="G496" s="9" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="H496" s="9" t="inlineStr">
@@ -25461,7 +25566,7 @@
     <row r="497">
       <c r="A497" s="9" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B497" s="9" t="inlineStr">
@@ -25503,7 +25608,7 @@
     <row r="498">
       <c r="A498" s="9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B498" s="9" t="inlineStr">
@@ -25545,7 +25650,7 @@
     <row r="499">
       <c r="A499" s="9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B499" s="9" t="inlineStr">
@@ -25565,7 +25670,7 @@
       </c>
       <c r="E499" s="9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F499" s="9" t="inlineStr">
@@ -25575,7 +25680,7 @@
       </c>
       <c r="G499" s="9" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="H499" s="9" t="inlineStr">
@@ -25587,7 +25692,7 @@
     <row r="500">
       <c r="A500" s="9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B500" s="9" t="inlineStr">
@@ -25629,7 +25734,7 @@
     <row r="501">
       <c r="A501" s="9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B501" s="9" t="inlineStr">
@@ -25671,7 +25776,7 @@
     <row r="502">
       <c r="A502" s="9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B502" s="9" t="inlineStr">
@@ -25713,7 +25818,7 @@
     <row r="503">
       <c r="A503" s="9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B503" s="9" t="inlineStr">
@@ -25755,7 +25860,7 @@
     <row r="504">
       <c r="A504" s="9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B504" s="9" t="inlineStr">
@@ -25797,7 +25902,7 @@
     <row r="505">
       <c r="A505" s="9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B505" s="9" t="inlineStr">
@@ -25839,7 +25944,7 @@
     <row r="506">
       <c r="A506" s="9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B506" s="9" t="inlineStr">
@@ -25881,7 +25986,7 @@
     <row r="507">
       <c r="A507" s="9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B507" s="9" t="inlineStr">
@@ -25923,7 +26028,7 @@
     <row r="508">
       <c r="A508" s="9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B508" s="9" t="inlineStr">
@@ -25965,7 +26070,7 @@
     <row r="509">
       <c r="A509" s="9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B509" s="9" t="inlineStr">
@@ -26007,7 +26112,7 @@
     <row r="510">
       <c r="A510" s="9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B510" s="9" t="inlineStr">
@@ -26049,7 +26154,7 @@
     <row r="511">
       <c r="A511" s="9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B511" s="9" t="inlineStr">
@@ -26091,7 +26196,7 @@
     <row r="512">
       <c r="A512" s="9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B512" s="9" t="inlineStr">
@@ -26133,7 +26238,7 @@
     <row r="513">
       <c r="A513" s="9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B513" s="9" t="inlineStr">
@@ -26175,7 +26280,7 @@
     <row r="514">
       <c r="A514" s="9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B514" s="9" t="inlineStr">
@@ -26217,7 +26322,7 @@
     <row r="515">
       <c r="A515" s="9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B515" s="9" t="inlineStr">
@@ -26259,7 +26364,7 @@
     <row r="516">
       <c r="A516" s="9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B516" s="9" t="inlineStr">
@@ -26301,7 +26406,7 @@
     <row r="517">
       <c r="A517" s="9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B517" s="9" t="inlineStr">
@@ -26331,7 +26436,7 @@
       </c>
       <c r="G517" s="9" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="H517" s="9" t="inlineStr">
@@ -26343,7 +26448,7 @@
     <row r="518">
       <c r="A518" s="9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B518" s="9" t="inlineStr">
@@ -26385,7 +26490,7 @@
     <row r="519">
       <c r="A519" s="9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B519" s="9" t="inlineStr">
@@ -26427,7 +26532,7 @@
     <row r="520">
       <c r="A520" s="9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B520" s="9" t="inlineStr">
@@ -26469,7 +26574,7 @@
     <row r="521">
       <c r="A521" s="9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B521" s="9" t="inlineStr">
@@ -26511,7 +26616,7 @@
     <row r="522">
       <c r="A522" s="9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B522" s="9" t="inlineStr">
@@ -26553,7 +26658,7 @@
     <row r="523">
       <c r="A523" s="9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B523" s="9" t="inlineStr">
@@ -26595,7 +26700,7 @@
     <row r="524">
       <c r="A524" s="9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B524" s="9" t="inlineStr">
@@ -26637,7 +26742,7 @@
     <row r="525">
       <c r="A525" s="9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B525" s="9" t="inlineStr">
@@ -26679,7 +26784,7 @@
     <row r="526">
       <c r="A526" s="9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B526" s="9" t="inlineStr">
@@ -26721,7 +26826,7 @@
     <row r="527">
       <c r="A527" s="9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B527" s="9" t="inlineStr">
@@ -26763,7 +26868,7 @@
     <row r="528">
       <c r="A528" s="9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B528" s="9" t="inlineStr">
@@ -26805,7 +26910,7 @@
     <row r="529">
       <c r="A529" s="9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B529" s="9" t="inlineStr">
@@ -26847,7 +26952,7 @@
     <row r="530">
       <c r="A530" s="9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B530" s="9" t="inlineStr">
@@ -26889,7 +26994,7 @@
     <row r="531">
       <c r="A531" s="9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B531" s="9" t="inlineStr">
@@ -26931,7 +27036,7 @@
     <row r="532">
       <c r="A532" s="9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B532" s="9" t="inlineStr">
@@ -26973,7 +27078,7 @@
     <row r="533">
       <c r="A533" s="9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B533" s="9" t="inlineStr">
@@ -27015,7 +27120,7 @@
     <row r="534">
       <c r="A534" s="9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B534" s="9" t="inlineStr">
@@ -27057,7 +27162,7 @@
     <row r="535">
       <c r="A535" s="9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B535" s="9" t="inlineStr">
@@ -27099,7 +27204,7 @@
     <row r="536">
       <c r="A536" s="9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B536" s="9" t="inlineStr">
@@ -27141,7 +27246,7 @@
     <row r="537">
       <c r="A537" s="9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B537" s="9" t="inlineStr">
@@ -27183,7 +27288,7 @@
     <row r="538">
       <c r="A538" s="9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B538" s="9" t="inlineStr">
@@ -27213,7 +27318,7 @@
       </c>
       <c r="G538" s="9" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="H538" s="9" t="inlineStr">
@@ -27225,7 +27330,7 @@
     <row r="539">
       <c r="A539" s="9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B539" s="9" t="inlineStr">
@@ -27267,7 +27372,7 @@
     <row r="540">
       <c r="A540" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B540" s="9" t="inlineStr">
@@ -27309,7 +27414,7 @@
     <row r="541">
       <c r="A541" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B541" s="9" t="inlineStr">
@@ -27351,7 +27456,7 @@
     <row r="542">
       <c r="A542" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B542" s="9" t="inlineStr">
@@ -27393,7 +27498,7 @@
     <row r="543">
       <c r="A543" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B543" s="9" t="inlineStr">
@@ -27435,7 +27540,7 @@
     <row r="544">
       <c r="A544" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B544" s="9" t="inlineStr">
@@ -27477,7 +27582,7 @@
     <row r="545">
       <c r="A545" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B545" s="9" t="inlineStr">
@@ -27519,7 +27624,7 @@
     <row r="546">
       <c r="A546" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B546" s="9" t="inlineStr">
@@ -27561,7 +27666,7 @@
     <row r="547">
       <c r="A547" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B547" s="9" t="inlineStr">
@@ -27603,7 +27708,7 @@
     <row r="548">
       <c r="A548" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B548" s="9" t="inlineStr">
@@ -27645,7 +27750,7 @@
     <row r="549">
       <c r="A549" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B549" s="9" t="inlineStr">
@@ -27687,7 +27792,7 @@
     <row r="550">
       <c r="A550" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B550" s="9" t="inlineStr">
@@ -27729,7 +27834,7 @@
     <row r="551">
       <c r="A551" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B551" s="9" t="inlineStr">
@@ -27771,7 +27876,7 @@
     <row r="552">
       <c r="A552" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B552" s="9" t="inlineStr">
@@ -27813,7 +27918,7 @@
     <row r="553">
       <c r="A553" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B553" s="9" t="inlineStr">
@@ -27855,7 +27960,7 @@
     <row r="554">
       <c r="A554" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B554" s="9" t="inlineStr">
@@ -27897,7 +28002,7 @@
     <row r="555">
       <c r="A555" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B555" s="9" t="inlineStr">
@@ -27939,7 +28044,7 @@
     <row r="556">
       <c r="A556" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B556" s="9" t="inlineStr">
@@ -27981,7 +28086,7 @@
     <row r="557">
       <c r="A557" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B557" s="9" t="inlineStr">
@@ -28023,7 +28128,7 @@
     <row r="558">
       <c r="A558" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B558" s="9" t="inlineStr">
@@ -28065,7 +28170,7 @@
     <row r="559">
       <c r="A559" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B559" s="9" t="inlineStr">
@@ -28107,7 +28212,7 @@
     <row r="560">
       <c r="A560" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B560" s="9" t="inlineStr">
@@ -28149,7 +28254,7 @@
     <row r="561">
       <c r="A561" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B561" s="9" t="inlineStr">
@@ -28191,7 +28296,7 @@
     <row r="562">
       <c r="A562" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B562" s="9" t="inlineStr">
@@ -28211,17 +28316,17 @@
       </c>
       <c r="E562" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F562" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Elevated</t>
         </is>
       </c>
       <c r="G562" s="9" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="H562" s="9" t="inlineStr">
@@ -28233,7 +28338,7 @@
     <row r="563">
       <c r="A563" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B563" s="9" t="inlineStr">
@@ -28275,7 +28380,7 @@
     <row r="564">
       <c r="A564" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B564" s="9" t="inlineStr">
@@ -28295,7 +28400,7 @@
       </c>
       <c r="E564" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F564" s="9" t="inlineStr">
@@ -28305,7 +28410,7 @@
       </c>
       <c r="G564" s="9" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="H564" s="9" t="inlineStr">
@@ -28317,7 +28422,7 @@
     <row r="565">
       <c r="A565" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B565" s="9" t="inlineStr">
@@ -28359,7 +28464,7 @@
     <row r="566">
       <c r="A566" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B566" s="9" t="inlineStr">
@@ -28401,7 +28506,7 @@
     <row r="567">
       <c r="A567" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B567" s="9" t="inlineStr">
@@ -28431,7 +28536,7 @@
       </c>
       <c r="G567" s="9" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="H567" s="9" t="inlineStr">
@@ -28443,7 +28548,7 @@
     <row r="568">
       <c r="A568" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B568" s="9" t="inlineStr">
@@ -28485,7 +28590,7 @@
     <row r="569">
       <c r="A569" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B569" s="9" t="inlineStr">
@@ -28527,7 +28632,7 @@
     <row r="570">
       <c r="A570" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B570" s="9" t="inlineStr">
@@ -28569,7 +28674,7 @@
     <row r="571">
       <c r="A571" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B571" s="9" t="inlineStr">
@@ -28611,7 +28716,7 @@
     <row r="572">
       <c r="A572" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B572" s="9" t="inlineStr">
@@ -28653,7 +28758,7 @@
     <row r="573">
       <c r="A573" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B573" s="9" t="inlineStr">
@@ -28695,7 +28800,7 @@
     <row r="574">
       <c r="A574" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B574" s="9" t="inlineStr">
@@ -28737,7 +28842,7 @@
     <row r="575">
       <c r="A575" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B575" s="9" t="inlineStr">
@@ -28779,7 +28884,7 @@
     <row r="576">
       <c r="A576" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B576" s="9" t="inlineStr">
@@ -28821,7 +28926,7 @@
     <row r="577">
       <c r="A577" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B577" s="9" t="inlineStr">
@@ -28863,7 +28968,7 @@
     <row r="578">
       <c r="A578" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B578" s="9" t="inlineStr">
@@ -28883,17 +28988,17 @@
       </c>
       <c r="E578" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F578" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Elevated</t>
         </is>
       </c>
       <c r="G578" s="9" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="H578" s="9" t="inlineStr">
@@ -28905,7 +29010,7 @@
     <row r="579">
       <c r="A579" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B579" s="9" t="inlineStr">
@@ -28947,7 +29052,7 @@
     <row r="580">
       <c r="A580" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B580" s="9" t="inlineStr">
@@ -28967,17 +29072,17 @@
       </c>
       <c r="E580" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F580" s="9" t="inlineStr">
         <is>
-          <t>Elevated</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G580" s="9" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="H580" s="9" t="inlineStr">
@@ -28989,7 +29094,7 @@
     <row r="581">
       <c r="A581" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B581" s="9" t="inlineStr">
@@ -29031,7 +29136,7 @@
     <row r="582">
       <c r="A582" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B582" s="9" t="inlineStr">
@@ -29073,7 +29178,7 @@
     <row r="583">
       <c r="A583" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B583" s="9" t="inlineStr">
@@ -29115,7 +29220,7 @@
     <row r="584">
       <c r="A584" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B584" s="9" t="inlineStr">
@@ -29157,7 +29262,7 @@
     <row r="585">
       <c r="A585" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B585" s="9" t="inlineStr">
@@ -29199,7 +29304,7 @@
     <row r="586">
       <c r="A586" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B586" s="9" t="inlineStr">
@@ -29241,7 +29346,7 @@
     <row r="587">
       <c r="A587" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B587" s="9" t="inlineStr">
@@ -29283,7 +29388,7 @@
     <row r="588">
       <c r="A588" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B588" s="9" t="inlineStr">
@@ -29325,7 +29430,7 @@
     <row r="589">
       <c r="A589" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B589" s="9" t="inlineStr">
@@ -29367,7 +29472,7 @@
     <row r="590">
       <c r="A590" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B590" s="9" t="inlineStr">
@@ -29409,7 +29514,7 @@
     <row r="591">
       <c r="A591" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B591" s="9" t="inlineStr">
@@ -29451,7 +29556,7 @@
     <row r="592">
       <c r="A592" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B592" s="9" t="inlineStr">
@@ -29493,7 +29598,7 @@
     <row r="593">
       <c r="A593" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B593" s="9" t="inlineStr">
@@ -29535,7 +29640,7 @@
     <row r="594">
       <c r="A594" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B594" s="9" t="inlineStr">
@@ -29577,7 +29682,7 @@
     <row r="595">
       <c r="A595" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B595" s="9" t="inlineStr">
@@ -29619,7 +29724,7 @@
     <row r="596">
       <c r="A596" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B596" s="9" t="inlineStr">
@@ -29661,7 +29766,7 @@
     <row r="597">
       <c r="A597" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B597" s="9" t="inlineStr">
@@ -29703,7 +29808,7 @@
     <row r="598">
       <c r="A598" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B598" s="9" t="inlineStr">
@@ -29745,7 +29850,7 @@
     <row r="599">
       <c r="A599" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B599" s="9" t="inlineStr">
@@ -29787,7 +29892,7 @@
     <row r="600">
       <c r="A600" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B600" s="9" t="inlineStr">
@@ -29829,7 +29934,7 @@
     <row r="601">
       <c r="A601" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B601" s="9" t="inlineStr">
@@ -29871,7 +29976,7 @@
     <row r="602">
       <c r="A602" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B602" s="9" t="inlineStr">
@@ -29913,7 +30018,7 @@
     <row r="603">
       <c r="A603" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B603" s="9" t="inlineStr">
@@ -29955,7 +30060,7 @@
     <row r="604">
       <c r="A604" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B604" s="9" t="inlineStr">
@@ -29975,17 +30080,17 @@
       </c>
       <c r="E604" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F604" s="9" t="inlineStr">
         <is>
-          <t>Elevated</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G604" s="9" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="H604" s="9" t="inlineStr">
@@ -29997,7 +30102,7 @@
     <row r="605">
       <c r="A605" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B605" s="9" t="inlineStr">
@@ -30039,7 +30144,7 @@
     <row r="606">
       <c r="A606" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B606" s="9" t="inlineStr">
@@ -30081,7 +30186,7 @@
     <row r="607">
       <c r="A607" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B607" s="9" t="inlineStr">
@@ -30123,7 +30228,7 @@
     <row r="608">
       <c r="A608" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B608" s="9" t="inlineStr">
@@ -30165,7 +30270,7 @@
     <row r="609">
       <c r="A609" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B609" s="9" t="inlineStr">
@@ -30207,7 +30312,7 @@
     <row r="610">
       <c r="A610" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B610" s="9" t="inlineStr">
@@ -30249,7 +30354,7 @@
     <row r="611">
       <c r="A611" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B611" s="9" t="inlineStr">
@@ -30291,7 +30396,7 @@
     <row r="612">
       <c r="A612" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B612" s="9" t="inlineStr">
@@ -30333,7 +30438,7 @@
     <row r="613">
       <c r="A613" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B613" s="9" t="inlineStr">
@@ -30375,7 +30480,7 @@
     <row r="614">
       <c r="A614" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B614" s="9" t="inlineStr">
@@ -30417,7 +30522,7 @@
     <row r="615">
       <c r="A615" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B615" s="9" t="inlineStr">
@@ -30459,7 +30564,7 @@
     <row r="616">
       <c r="A616" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B616" s="9" t="inlineStr">
@@ -30501,7 +30606,7 @@
     <row r="617">
       <c r="A617" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B617" s="9" t="inlineStr">
@@ -30543,7 +30648,7 @@
     <row r="618">
       <c r="A618" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B618" s="9" t="inlineStr">
@@ -30585,7 +30690,7 @@
     <row r="619">
       <c r="A619" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B619" s="9" t="inlineStr">
@@ -30627,7 +30732,7 @@
     <row r="620">
       <c r="A620" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B620" s="9" t="inlineStr">
@@ -30669,7 +30774,7 @@
     <row r="621">
       <c r="A621" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B621" s="9" t="inlineStr">
@@ -30711,7 +30816,7 @@
     <row r="622">
       <c r="A622" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B622" s="9" t="inlineStr">
@@ -30753,7 +30858,7 @@
     <row r="623">
       <c r="A623" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B623" s="9" t="inlineStr">
@@ -30795,7 +30900,7 @@
     <row r="624">
       <c r="A624" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B624" s="9" t="inlineStr">
@@ -30837,7 +30942,7 @@
     <row r="625">
       <c r="A625" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B625" s="9" t="inlineStr">
@@ -30879,7 +30984,7 @@
     <row r="626">
       <c r="A626" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B626" s="9" t="inlineStr">
@@ -30921,7 +31026,7 @@
     <row r="627">
       <c r="A627" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B627" s="9" t="inlineStr">
@@ -30963,7 +31068,7 @@
     <row r="628">
       <c r="A628" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B628" s="9" t="inlineStr">
@@ -31005,7 +31110,7 @@
     <row r="629">
       <c r="A629" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B629" s="9" t="inlineStr">
@@ -31047,7 +31152,7 @@
     <row r="630">
       <c r="A630" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B630" s="9" t="inlineStr">
@@ -31089,7 +31194,7 @@
     <row r="631">
       <c r="A631" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B631" s="9" t="inlineStr">
@@ -31131,7 +31236,7 @@
     <row r="632">
       <c r="A632" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B632" s="9" t="inlineStr">
@@ -31173,7 +31278,7 @@
     <row r="633">
       <c r="A633" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B633" s="9" t="inlineStr">
@@ -31215,7 +31320,7 @@
     <row r="634">
       <c r="A634" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B634" s="9" t="inlineStr">
@@ -31257,7 +31362,7 @@
     <row r="635">
       <c r="A635" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B635" s="9" t="inlineStr">
@@ -31299,7 +31404,7 @@
     <row r="636">
       <c r="A636" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B636" s="9" t="inlineStr">
@@ -31341,7 +31446,7 @@
     <row r="637">
       <c r="A637" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B637" s="9" t="inlineStr">
@@ -31383,7 +31488,7 @@
     <row r="638">
       <c r="A638" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B638" s="9" t="inlineStr">
@@ -31425,7 +31530,7 @@
     <row r="639">
       <c r="A639" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B639" s="9" t="inlineStr">
@@ -31467,7 +31572,7 @@
     <row r="640">
       <c r="A640" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B640" s="9" t="inlineStr">
@@ -31509,7 +31614,7 @@
     <row r="641">
       <c r="A641" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B641" s="9" t="inlineStr">
@@ -31551,7 +31656,7 @@
     <row r="642">
       <c r="A642" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B642" s="9" t="inlineStr">
@@ -31593,7 +31698,7 @@
     <row r="643">
       <c r="A643" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B643" s="9" t="inlineStr">
@@ -31635,7 +31740,7 @@
     <row r="644">
       <c r="A644" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B644" s="9" t="inlineStr">
@@ -31677,7 +31782,7 @@
     <row r="645">
       <c r="A645" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B645" s="9" t="inlineStr">
@@ -31719,7 +31824,7 @@
     <row r="646">
       <c r="A646" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B646" s="9" t="inlineStr">
@@ -31761,7 +31866,7 @@
     <row r="647">
       <c r="A647" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B647" s="9" t="inlineStr">
@@ -31803,7 +31908,7 @@
     <row r="648">
       <c r="A648" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B648" s="9" t="inlineStr">
@@ -31845,7 +31950,7 @@
     <row r="649">
       <c r="A649" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B649" s="9" t="inlineStr">
@@ -31887,7 +31992,7 @@
     <row r="650">
       <c r="A650" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B650" s="9" t="inlineStr">
@@ -31929,7 +32034,7 @@
     <row r="651">
       <c r="A651" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B651" s="9" t="inlineStr">
@@ -31971,7 +32076,7 @@
     <row r="652">
       <c r="A652" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B652" s="9" t="inlineStr">
@@ -32013,7 +32118,7 @@
     <row r="653">
       <c r="A653" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B653" s="9" t="inlineStr">
@@ -32055,7 +32160,7 @@
     <row r="654">
       <c r="A654" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B654" s="9" t="inlineStr">
@@ -32097,7 +32202,7 @@
     <row r="655">
       <c r="A655" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B655" s="9" t="inlineStr">
@@ -32139,7 +32244,7 @@
     <row r="656">
       <c r="A656" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B656" s="9" t="inlineStr">
@@ -32181,7 +32286,7 @@
     <row r="657">
       <c r="A657" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B657" s="9" t="inlineStr">
@@ -32223,7 +32328,7 @@
     <row r="658">
       <c r="A658" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B658" s="9" t="inlineStr">
@@ -32265,7 +32370,7 @@
     <row r="659">
       <c r="A659" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B659" s="9" t="inlineStr">
@@ -32307,7 +32412,7 @@
     <row r="660">
       <c r="A660" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B660" s="9" t="inlineStr">
@@ -32349,7 +32454,7 @@
     <row r="661">
       <c r="A661" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B661" s="9" t="inlineStr">
@@ -32391,7 +32496,7 @@
     <row r="662">
       <c r="A662" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B662" s="9" t="inlineStr">
@@ -32433,7 +32538,7 @@
     <row r="663">
       <c r="A663" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B663" s="9" t="inlineStr">
@@ -32475,7 +32580,7 @@
     <row r="664">
       <c r="A664" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B664" s="9" t="inlineStr">
@@ -32517,7 +32622,7 @@
     <row r="665">
       <c r="A665" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B665" s="9" t="inlineStr">
@@ -32559,7 +32664,7 @@
     <row r="666">
       <c r="A666" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B666" s="9" t="inlineStr">
@@ -32601,7 +32706,7 @@
     <row r="667">
       <c r="A667" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B667" s="9" t="inlineStr">
@@ -32643,7 +32748,7 @@
     <row r="668">
       <c r="A668" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B668" s="9" t="inlineStr">
@@ -32685,7 +32790,7 @@
     <row r="669">
       <c r="A669" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B669" s="9" t="inlineStr">
@@ -32705,7 +32810,7 @@
       </c>
       <c r="E669" s="9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F669" s="9" t="inlineStr">
@@ -32715,7 +32820,7 @@
       </c>
       <c r="G669" s="9" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="H669" s="9" t="inlineStr">
@@ -32727,7 +32832,7 @@
     <row r="670">
       <c r="A670" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B670" s="9" t="inlineStr">
@@ -32769,7 +32874,7 @@
     <row r="671">
       <c r="A671" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B671" s="9" t="inlineStr">
@@ -32811,7 +32916,7 @@
     <row r="672">
       <c r="A672" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B672" s="9" t="inlineStr">
@@ -32853,7 +32958,7 @@
     <row r="673">
       <c r="A673" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B673" s="9" t="inlineStr">
@@ -32895,7 +33000,7 @@
     <row r="674">
       <c r="A674" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B674" s="9" t="inlineStr">
@@ -32937,7 +33042,7 @@
     <row r="675">
       <c r="A675" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B675" s="9" t="inlineStr">
@@ -32979,7 +33084,7 @@
     <row r="676">
       <c r="A676" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B676" s="9" t="inlineStr">
@@ -32999,7 +33104,7 @@
       </c>
       <c r="E676" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F676" s="9" t="inlineStr">
@@ -33009,7 +33114,7 @@
       </c>
       <c r="G676" s="9" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="H676" s="9" t="inlineStr">
@@ -33021,7 +33126,7 @@
     <row r="677">
       <c r="A677" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B677" s="9" t="inlineStr">
@@ -33063,7 +33168,7 @@
     <row r="678">
       <c r="A678" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B678" s="9" t="inlineStr">
@@ -33105,7 +33210,7 @@
     <row r="679">
       <c r="A679" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B679" s="9" t="inlineStr">
@@ -33147,7 +33252,7 @@
     <row r="680">
       <c r="A680" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B680" s="9" t="inlineStr">
@@ -33189,7 +33294,7 @@
     <row r="681">
       <c r="A681" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B681" s="9" t="inlineStr">
@@ -33231,7 +33336,7 @@
     <row r="682">
       <c r="A682" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B682" s="9" t="inlineStr">
@@ -33273,7 +33378,7 @@
     <row r="683">
       <c r="A683" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B683" s="9" t="inlineStr">
@@ -33293,17 +33398,17 @@
       </c>
       <c r="E683" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F683" s="9" t="inlineStr">
         <is>
-          <t>Elevated</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G683" s="9" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="H683" s="9" t="inlineStr">
@@ -33315,7 +33420,7 @@
     <row r="684">
       <c r="A684" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B684" s="9" t="inlineStr">
@@ -33357,7 +33462,7 @@
     <row r="685">
       <c r="A685" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B685" s="9" t="inlineStr">
@@ -33399,7 +33504,7 @@
     <row r="686">
       <c r="A686" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B686" s="9" t="inlineStr">
@@ -33441,7 +33546,7 @@
     <row r="687">
       <c r="A687" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B687" s="9" t="inlineStr">
@@ -33483,7 +33588,7 @@
     <row r="688">
       <c r="A688" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B688" s="9" t="inlineStr">
@@ -33525,7 +33630,7 @@
     <row r="689">
       <c r="A689" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B689" s="9" t="inlineStr">
@@ -33567,7 +33672,7 @@
     <row r="690">
       <c r="A690" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B690" s="9" t="inlineStr">
@@ -33609,7 +33714,7 @@
     <row r="691">
       <c r="A691" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B691" s="9" t="inlineStr">
@@ -33651,7 +33756,7 @@
     <row r="692">
       <c r="A692" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B692" s="9" t="inlineStr">
@@ -33693,7 +33798,7 @@
     <row r="693">
       <c r="A693" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B693" s="9" t="inlineStr">
@@ -33735,7 +33840,7 @@
     <row r="694">
       <c r="A694" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B694" s="9" t="inlineStr">
@@ -33777,7 +33882,7 @@
     <row r="695">
       <c r="A695" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B695" s="9" t="inlineStr">
@@ -33819,7 +33924,7 @@
     <row r="696">
       <c r="A696" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B696" s="9" t="inlineStr">
@@ -33861,7 +33966,7 @@
     <row r="697">
       <c r="A697" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B697" s="9" t="inlineStr">
@@ -33903,7 +34008,7 @@
     <row r="698">
       <c r="A698" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B698" s="9" t="inlineStr">
@@ -33945,7 +34050,7 @@
     <row r="699">
       <c r="A699" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B699" s="9" t="inlineStr">
@@ -33987,7 +34092,7 @@
     <row r="700">
       <c r="A700" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B700" s="9" t="inlineStr">
@@ -34029,7 +34134,7 @@
     <row r="701">
       <c r="A701" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B701" s="9" t="inlineStr">
@@ -34071,7 +34176,7 @@
     <row r="702">
       <c r="A702" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B702" s="9" t="inlineStr">
@@ -34113,7 +34218,7 @@
     <row r="703">
       <c r="A703" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B703" s="9" t="inlineStr">
@@ -34155,7 +34260,7 @@
     <row r="704">
       <c r="A704" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B704" s="9" t="inlineStr">
@@ -34197,7 +34302,7 @@
     <row r="705">
       <c r="A705" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B705" s="9" t="inlineStr">
@@ -34239,7 +34344,7 @@
     <row r="706">
       <c r="A706" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B706" s="9" t="inlineStr">
@@ -34281,7 +34386,7 @@
     <row r="707">
       <c r="A707" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B707" s="9" t="inlineStr">
@@ -34323,7 +34428,7 @@
     <row r="708">
       <c r="A708" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B708" s="9" t="inlineStr">
@@ -34365,7 +34470,7 @@
     <row r="709">
       <c r="A709" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B709" s="9" t="inlineStr">
@@ -34407,7 +34512,7 @@
     <row r="710">
       <c r="A710" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B710" s="9" t="inlineStr">
@@ -34449,7 +34554,7 @@
     <row r="711">
       <c r="A711" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B711" s="9" t="inlineStr">
@@ -34491,7 +34596,7 @@
     <row r="712">
       <c r="A712" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B712" s="9" t="inlineStr">
@@ -34533,7 +34638,7 @@
     <row r="713">
       <c r="A713" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B713" s="9" t="inlineStr">
@@ -34575,7 +34680,7 @@
     <row r="714">
       <c r="A714" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B714" s="9" t="inlineStr">
@@ -34617,7 +34722,7 @@
     <row r="715">
       <c r="A715" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B715" s="9" t="inlineStr">
@@ -34659,7 +34764,7 @@
     <row r="716">
       <c r="A716" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B716" s="9" t="inlineStr">
@@ -34701,7 +34806,7 @@
     <row r="717">
       <c r="A717" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B717" s="9" t="inlineStr">
@@ -34743,7 +34848,7 @@
     <row r="718">
       <c r="A718" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B718" s="9" t="inlineStr">
@@ -34785,7 +34890,7 @@
     <row r="719">
       <c r="A719" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B719" s="9" t="inlineStr">
@@ -34827,7 +34932,7 @@
     <row r="720">
       <c r="A720" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B720" s="9" t="inlineStr">
@@ -34869,7 +34974,7 @@
     <row r="721">
       <c r="A721" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B721" s="9" t="inlineStr">
@@ -34911,7 +35016,7 @@
     <row r="722">
       <c r="A722" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B722" s="9" t="inlineStr">
@@ -34953,7 +35058,7 @@
     <row r="723">
       <c r="A723" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B723" s="9" t="inlineStr">
@@ -34995,7 +35100,7 @@
     <row r="724">
       <c r="A724" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B724" s="9" t="inlineStr">
@@ -35037,7 +35142,7 @@
     <row r="725">
       <c r="A725" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B725" s="9" t="inlineStr">
@@ -35079,7 +35184,7 @@
     <row r="726">
       <c r="A726" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B726" s="9" t="inlineStr">
@@ -35121,7 +35226,7 @@
     <row r="727">
       <c r="A727" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B727" s="9" t="inlineStr">
@@ -35163,7 +35268,7 @@
     <row r="728">
       <c r="A728" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B728" s="9" t="inlineStr">
@@ -35205,7 +35310,7 @@
     <row r="729">
       <c r="A729" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B729" s="9" t="inlineStr">
@@ -35247,7 +35352,7 @@
     <row r="730">
       <c r="A730" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B730" s="9" t="inlineStr">
@@ -35289,7 +35394,7 @@
     <row r="731">
       <c r="A731" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B731" s="9" t="inlineStr">
@@ -35331,7 +35436,7 @@
     <row r="732">
       <c r="A732" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B732" s="9" t="inlineStr">
@@ -35373,7 +35478,7 @@
     <row r="733">
       <c r="A733" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B733" s="9" t="inlineStr">
@@ -35415,7 +35520,7 @@
     <row r="734">
       <c r="A734" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B734" s="9" t="inlineStr">
@@ -35457,7 +35562,7 @@
     <row r="735">
       <c r="A735" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B735" s="9" t="inlineStr">
@@ -35499,7 +35604,7 @@
     <row r="736">
       <c r="A736" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B736" s="9" t="inlineStr">
@@ -35541,7 +35646,7 @@
     <row r="737">
       <c r="A737" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B737" s="9" t="inlineStr">
@@ -35583,7 +35688,7 @@
     <row r="738">
       <c r="A738" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B738" s="9" t="inlineStr">
@@ -35625,7 +35730,7 @@
     <row r="739">
       <c r="A739" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B739" s="9" t="inlineStr">
@@ -35667,7 +35772,7 @@
     <row r="740">
       <c r="A740" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B740" s="9" t="inlineStr">
@@ -35709,7 +35814,7 @@
     <row r="741">
       <c r="A741" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B741" s="9" t="inlineStr">
@@ -35751,7 +35856,7 @@
     <row r="742">
       <c r="A742" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B742" s="9" t="inlineStr">
@@ -35793,7 +35898,7 @@
     <row r="743">
       <c r="A743" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B743" s="9" t="inlineStr">
@@ -35835,7 +35940,7 @@
     <row r="744">
       <c r="A744" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B744" s="9" t="inlineStr">
@@ -35877,7 +35982,7 @@
     <row r="745">
       <c r="A745" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B745" s="9" t="inlineStr">
@@ -35919,7 +36024,7 @@
     <row r="746">
       <c r="A746" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B746" s="9" t="inlineStr">
@@ -35961,7 +36066,7 @@
     <row r="747">
       <c r="A747" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B747" s="9" t="inlineStr">
@@ -36003,7 +36108,7 @@
     <row r="748">
       <c r="A748" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B748" s="9" t="inlineStr">
@@ -36045,7 +36150,7 @@
     <row r="749">
       <c r="A749" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B749" s="9" t="inlineStr">
@@ -36087,7 +36192,7 @@
     <row r="750">
       <c r="A750" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B750" s="9" t="inlineStr">
@@ -36129,7 +36234,7 @@
     <row r="751">
       <c r="A751" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B751" s="9" t="inlineStr">
@@ -36171,7 +36276,7 @@
     <row r="752">
       <c r="A752" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B752" s="9" t="inlineStr">
@@ -36213,7 +36318,7 @@
     <row r="753">
       <c r="A753" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B753" s="9" t="inlineStr">
@@ -36255,7 +36360,7 @@
     <row r="754">
       <c r="A754" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B754" s="9" t="inlineStr">
@@ -36297,7 +36402,7 @@
     <row r="755">
       <c r="A755" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B755" s="9" t="inlineStr">
@@ -36339,7 +36444,7 @@
     <row r="756">
       <c r="A756" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B756" s="9" t="inlineStr">
@@ -36381,7 +36486,7 @@
     <row r="757">
       <c r="A757" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B757" s="9" t="inlineStr">
@@ -36423,7 +36528,7 @@
     <row r="758">
       <c r="A758" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B758" s="9" t="inlineStr">
@@ -36465,7 +36570,7 @@
     <row r="759">
       <c r="A759" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B759" s="9" t="inlineStr">
@@ -36507,7 +36612,7 @@
     <row r="760">
       <c r="A760" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B760" s="9" t="inlineStr">
@@ -36549,7 +36654,7 @@
     <row r="761">
       <c r="A761" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B761" s="9" t="inlineStr">
@@ -36591,7 +36696,7 @@
     <row r="762">
       <c r="A762" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B762" s="9" t="inlineStr">
@@ -36633,7 +36738,7 @@
     <row r="763">
       <c r="A763" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B763" s="9" t="inlineStr">
@@ -36675,7 +36780,7 @@
     <row r="764">
       <c r="A764" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B764" s="9" t="inlineStr">
@@ -36717,7 +36822,7 @@
     <row r="765">
       <c r="A765" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B765" s="9" t="inlineStr">
@@ -36759,7 +36864,7 @@
     <row r="766">
       <c r="A766" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B766" s="9" t="inlineStr">
@@ -36801,7 +36906,7 @@
     <row r="767">
       <c r="A767" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B767" s="9" t="inlineStr">
@@ -36843,7 +36948,7 @@
     <row r="768">
       <c r="A768" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B768" s="9" t="inlineStr">
@@ -36885,7 +36990,7 @@
     <row r="769">
       <c r="A769" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B769" s="9" t="inlineStr">
@@ -36927,7 +37032,7 @@
     <row r="770">
       <c r="A770" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B770" s="9" t="inlineStr">
@@ -36969,7 +37074,7 @@
     <row r="771">
       <c r="A771" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B771" s="9" t="inlineStr">
@@ -37011,7 +37116,7 @@
     <row r="772">
       <c r="A772" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B772" s="9" t="inlineStr">
@@ -37031,7 +37136,7 @@
       </c>
       <c r="E772" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F772" s="9" t="inlineStr">
@@ -37041,7 +37146,7 @@
       </c>
       <c r="G772" s="9" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="H772" s="9" t="inlineStr">
@@ -37053,7 +37158,7 @@
     <row r="773">
       <c r="A773" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B773" s="9" t="inlineStr">
@@ -37095,7 +37200,7 @@
     <row r="774">
       <c r="A774" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B774" s="9" t="inlineStr">
@@ -37125,7 +37230,7 @@
       </c>
       <c r="G774" s="9" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="H774" s="9" t="inlineStr">
@@ -37137,7 +37242,7 @@
     <row r="775">
       <c r="A775" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B775" s="9" t="inlineStr">
@@ -37179,7 +37284,7 @@
     <row r="776">
       <c r="A776" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B776" s="9" t="inlineStr">
@@ -37221,7 +37326,7 @@
     <row r="777">
       <c r="A777" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B777" s="9" t="inlineStr">
@@ -37263,7 +37368,7 @@
     <row r="778">
       <c r="A778" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B778" s="9" t="inlineStr">
@@ -37305,7 +37410,7 @@
     <row r="779">
       <c r="A779" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B779" s="9" t="inlineStr">
@@ -37347,7 +37452,7 @@
     <row r="780">
       <c r="A780" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B780" s="9" t="inlineStr">
@@ -37389,7 +37494,7 @@
     <row r="781">
       <c r="A781" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B781" s="9" t="inlineStr">
@@ -37431,7 +37536,7 @@
     <row r="782">
       <c r="A782" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B782" s="9" t="inlineStr">
@@ -37473,7 +37578,7 @@
     <row r="783">
       <c r="A783" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B783" s="9" t="inlineStr">
@@ -37515,7 +37620,7 @@
     <row r="784">
       <c r="A784" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B784" s="9" t="inlineStr">
@@ -37557,7 +37662,7 @@
     <row r="785">
       <c r="A785" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B785" s="9" t="inlineStr">
@@ -37599,7 +37704,7 @@
     <row r="786">
       <c r="A786" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B786" s="9" t="inlineStr">
@@ -37641,7 +37746,7 @@
     <row r="787">
       <c r="A787" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B787" s="9" t="inlineStr">
@@ -37683,7 +37788,7 @@
     <row r="788">
       <c r="A788" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B788" s="9" t="inlineStr">
@@ -37703,17 +37808,17 @@
       </c>
       <c r="E788" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F788" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Elevated</t>
         </is>
       </c>
       <c r="G788" s="9" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="H788" s="9" t="inlineStr">
@@ -37725,7 +37830,7 @@
     <row r="789">
       <c r="A789" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B789" s="9" t="inlineStr">
@@ -37767,7 +37872,7 @@
     <row r="790">
       <c r="A790" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B790" s="9" t="inlineStr">
@@ -37787,17 +37892,17 @@
       </c>
       <c r="E790" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F790" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Elevated</t>
         </is>
       </c>
       <c r="G790" s="9" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="H790" s="9" t="inlineStr">
@@ -37809,7 +37914,7 @@
     <row r="791">
       <c r="A791" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B791" s="9" t="inlineStr">
@@ -37839,7 +37944,7 @@
       </c>
       <c r="G791" s="9" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="H791" s="9" t="inlineStr">
@@ -37851,7 +37956,7 @@
     <row r="792">
       <c r="A792" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B792" s="9" t="inlineStr">
@@ -37893,7 +37998,7 @@
     <row r="793">
       <c r="A793" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B793" s="9" t="inlineStr">
@@ -37935,7 +38040,7 @@
     <row r="794">
       <c r="A794" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B794" s="9" t="inlineStr">
@@ -37977,7 +38082,7 @@
     <row r="795">
       <c r="A795" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B795" s="9" t="inlineStr">
@@ -38019,7 +38124,7 @@
     <row r="796">
       <c r="A796" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B796" s="9" t="inlineStr">
@@ -38061,7 +38166,7 @@
     <row r="797">
       <c r="A797" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B797" s="9" t="inlineStr">
@@ -38103,7 +38208,7 @@
     <row r="798">
       <c r="A798" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B798" s="9" t="inlineStr">
@@ -38145,7 +38250,7 @@
     <row r="799">
       <c r="A799" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B799" s="9" t="inlineStr">
@@ -38187,7 +38292,7 @@
     <row r="800">
       <c r="A800" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B800" s="9" t="inlineStr">
@@ -38229,7 +38334,7 @@
     <row r="801">
       <c r="A801" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B801" s="9" t="inlineStr">
@@ -38271,7 +38376,7 @@
     <row r="802">
       <c r="A802" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B802" s="9" t="inlineStr">
@@ -38313,7 +38418,7 @@
     <row r="803">
       <c r="A803" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B803" s="9" t="inlineStr">
@@ -38355,7 +38460,7 @@
     <row r="804">
       <c r="A804" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B804" s="9" t="inlineStr">
@@ -38397,7 +38502,7 @@
     <row r="805">
       <c r="A805" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B805" s="9" t="inlineStr">
@@ -38439,7 +38544,7 @@
     <row r="806">
       <c r="A806" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B806" s="9" t="inlineStr">
@@ -38481,7 +38586,7 @@
     <row r="807">
       <c r="A807" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B807" s="9" t="inlineStr">
@@ -38523,7 +38628,7 @@
     <row r="808">
       <c r="A808" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B808" s="9" t="inlineStr">
@@ -38565,7 +38670,7 @@
     <row r="809">
       <c r="A809" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B809" s="9" t="inlineStr">
@@ -38607,7 +38712,7 @@
     <row r="810">
       <c r="A810" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B810" s="9" t="inlineStr">
@@ -38649,7 +38754,7 @@
     <row r="811">
       <c r="A811" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B811" s="9" t="inlineStr">
@@ -38691,7 +38796,7 @@
     <row r="812">
       <c r="A812" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B812" s="9" t="inlineStr">
@@ -38733,7 +38838,7 @@
     <row r="813">
       <c r="A813" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B813" s="9" t="inlineStr">
@@ -38775,7 +38880,7 @@
     <row r="814">
       <c r="A814" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B814" s="9" t="inlineStr">
@@ -38817,7 +38922,7 @@
     <row r="815">
       <c r="A815" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B815" s="9" t="inlineStr">
@@ -38859,7 +38964,7 @@
     <row r="816">
       <c r="A816" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B816" s="9" t="inlineStr">
@@ -38901,7 +39006,7 @@
     <row r="817">
       <c r="A817" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B817" s="9" t="inlineStr">
@@ -38943,7 +39048,7 @@
     <row r="818">
       <c r="A818" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B818" s="9" t="inlineStr">
@@ -38985,7 +39090,7 @@
     <row r="819">
       <c r="A819" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B819" s="9" t="inlineStr">
@@ -39027,7 +39132,7 @@
     <row r="820">
       <c r="A820" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B820" s="9" t="inlineStr">
@@ -39069,7 +39174,7 @@
     <row r="821">
       <c r="A821" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B821" s="9" t="inlineStr">
@@ -39111,7 +39216,7 @@
     <row r="822">
       <c r="A822" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B822" s="9" t="inlineStr">
@@ -39153,7 +39258,7 @@
     <row r="823">
       <c r="A823" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B823" s="9" t="inlineStr">
@@ -39195,7 +39300,7 @@
     <row r="824">
       <c r="A824" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B824" s="9" t="inlineStr">
@@ -39237,7 +39342,7 @@
     <row r="825">
       <c r="A825" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B825" s="9" t="inlineStr">
@@ -39279,7 +39384,7 @@
     <row r="826">
       <c r="A826" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B826" s="9" t="inlineStr">
@@ -39321,7 +39426,7 @@
     <row r="827">
       <c r="A827" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B827" s="9" t="inlineStr">
@@ -39363,7 +39468,7 @@
     <row r="828">
       <c r="A828" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B828" s="9" t="inlineStr">
@@ -39405,7 +39510,7 @@
     <row r="829">
       <c r="A829" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B829" s="9" t="inlineStr">
@@ -39447,7 +39552,7 @@
     <row r="830">
       <c r="A830" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B830" s="9" t="inlineStr">
@@ -39489,7 +39594,7 @@
     <row r="831">
       <c r="A831" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B831" s="9" t="inlineStr">
@@ -39531,7 +39636,7 @@
     <row r="832">
       <c r="A832" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B832" s="9" t="inlineStr">
@@ -39573,7 +39678,7 @@
     <row r="833">
       <c r="A833" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B833" s="9" t="inlineStr">
@@ -39615,7 +39720,7 @@
     <row r="834">
       <c r="A834" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B834" s="9" t="inlineStr">
@@ -39657,7 +39762,7 @@
     <row r="835">
       <c r="A835" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B835" s="9" t="inlineStr">
@@ -39699,7 +39804,7 @@
     <row r="836">
       <c r="A836" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B836" s="9" t="inlineStr">
@@ -39741,7 +39846,7 @@
     <row r="837">
       <c r="A837" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B837" s="9" t="inlineStr">
@@ -39783,7 +39888,7 @@
     <row r="838">
       <c r="A838" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B838" s="9" t="inlineStr">
@@ -39825,7 +39930,7 @@
     <row r="839">
       <c r="A839" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B839" s="9" t="inlineStr">
@@ -39867,7 +39972,7 @@
     <row r="840">
       <c r="A840" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B840" s="9" t="inlineStr">
@@ -39909,7 +40014,7 @@
     <row r="841">
       <c r="A841" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B841" s="9" t="inlineStr">
@@ -39951,7 +40056,7 @@
     <row r="842">
       <c r="A842" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B842" s="9" t="inlineStr">
@@ -39993,7 +40098,7 @@
     <row r="843">
       <c r="A843" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B843" s="9" t="inlineStr">
@@ -40035,7 +40140,7 @@
     <row r="844">
       <c r="A844" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B844" s="9" t="inlineStr">
@@ -40077,7 +40182,7 @@
     <row r="845">
       <c r="A845" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B845" s="9" t="inlineStr">
@@ -40119,7 +40224,7 @@
     <row r="846">
       <c r="A846" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B846" s="9" t="inlineStr">
@@ -40161,7 +40266,7 @@
     <row r="847">
       <c r="A847" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B847" s="9" t="inlineStr">
@@ -40203,7 +40308,7 @@
     <row r="848">
       <c r="A848" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B848" s="9" t="inlineStr">
@@ -40245,7 +40350,7 @@
     <row r="849">
       <c r="A849" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B849" s="9" t="inlineStr">
@@ -40287,7 +40392,7 @@
     <row r="850">
       <c r="A850" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B850" s="9" t="inlineStr">
@@ -40329,7 +40434,7 @@
     <row r="851">
       <c r="A851" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B851" s="9" t="inlineStr">
@@ -40371,7 +40476,7 @@
     <row r="852">
       <c r="A852" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B852" s="9" t="inlineStr">
@@ -40413,7 +40518,7 @@
     <row r="853">
       <c r="A853" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B853" s="9" t="inlineStr">
@@ -40455,7 +40560,7 @@
     <row r="854">
       <c r="A854" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B854" s="9" t="inlineStr">
@@ -40497,7 +40602,7 @@
     <row r="855">
       <c r="A855" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B855" s="9" t="inlineStr">
@@ -40539,7 +40644,7 @@
     <row r="856">
       <c r="A856" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B856" s="9" t="inlineStr">
@@ -40581,7 +40686,7 @@
     <row r="857">
       <c r="A857" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B857" s="9" t="inlineStr">
@@ -40623,7 +40728,7 @@
     <row r="858">
       <c r="A858" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B858" s="9" t="inlineStr">
@@ -40665,7 +40770,7 @@
     <row r="859">
       <c r="A859" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B859" s="9" t="inlineStr">
@@ -40707,7 +40812,7 @@
     <row r="860">
       <c r="A860" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B860" s="9" t="inlineStr">
@@ -40749,7 +40854,7 @@
     <row r="861">
       <c r="A861" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B861" s="9" t="inlineStr">
@@ -40791,7 +40896,7 @@
     <row r="862">
       <c r="A862" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B862" s="9" t="inlineStr">
@@ -40833,7 +40938,7 @@
     <row r="863">
       <c r="A863" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B863" s="9" t="inlineStr">
@@ -40875,7 +40980,7 @@
     <row r="864">
       <c r="A864" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B864" s="9" t="inlineStr">
@@ -40917,7 +41022,7 @@
     <row r="865">
       <c r="A865" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B865" s="9" t="inlineStr">
@@ -40959,7 +41064,7 @@
     <row r="866">
       <c r="A866" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B866" s="9" t="inlineStr">
@@ -41001,7 +41106,7 @@
     <row r="867">
       <c r="A867" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B867" s="9" t="inlineStr">
@@ -41043,7 +41148,7 @@
     <row r="868">
       <c r="A868" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B868" s="9" t="inlineStr">
@@ -41085,7 +41190,7 @@
     <row r="869">
       <c r="A869" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B869" s="9" t="inlineStr">
@@ -41127,7 +41232,7 @@
     <row r="870">
       <c r="A870" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B870" s="9" t="inlineStr">
@@ -41169,7 +41274,7 @@
     <row r="871">
       <c r="A871" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B871" s="9" t="inlineStr">
@@ -41211,7 +41316,7 @@
     <row r="872">
       <c r="A872" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B872" s="9" t="inlineStr">
@@ -41253,7 +41358,7 @@
     <row r="873">
       <c r="A873" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B873" s="9" t="inlineStr">
@@ -41295,7 +41400,7 @@
     <row r="874">
       <c r="A874" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B874" s="9" t="inlineStr">
@@ -41337,7 +41442,7 @@
     <row r="875">
       <c r="A875" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B875" s="9" t="inlineStr">
@@ -41379,7 +41484,7 @@
     <row r="876">
       <c r="A876" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B876" s="9" t="inlineStr">
@@ -41421,7 +41526,7 @@
     <row r="877">
       <c r="A877" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B877" s="9" t="inlineStr">
@@ -41441,7 +41546,7 @@
       </c>
       <c r="E877" s="9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F877" s="9" t="inlineStr">
@@ -41451,7 +41556,7 @@
       </c>
       <c r="G877" s="9" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="H877" s="9" t="inlineStr">
@@ -41463,7 +41568,7 @@
     <row r="878">
       <c r="A878" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B878" s="9" t="inlineStr">
@@ -41505,7 +41610,7 @@
     <row r="879">
       <c r="A879" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B879" s="9" t="inlineStr">
@@ -41535,7 +41640,7 @@
       </c>
       <c r="G879" s="9" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="H879" s="9" t="inlineStr">
@@ -41547,7 +41652,7 @@
     <row r="880">
       <c r="A880" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B880" s="9" t="inlineStr">
@@ -41567,17 +41672,17 @@
       </c>
       <c r="E880" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F880" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Elevated</t>
         </is>
       </c>
       <c r="G880" s="9" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="H880" s="9" t="inlineStr">
@@ -41589,7 +41694,7 @@
     <row r="881">
       <c r="A881" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B881" s="9" t="inlineStr">
@@ -41631,7 +41736,7 @@
     <row r="882">
       <c r="A882" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B882" s="9" t="inlineStr">
@@ -41673,7 +41778,7 @@
     <row r="883">
       <c r="A883" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B883" s="9" t="inlineStr">
@@ -41715,7 +41820,7 @@
     <row r="884">
       <c r="A884" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B884" s="9" t="inlineStr">
@@ -41735,7 +41840,7 @@
       </c>
       <c r="E884" s="9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F884" s="9" t="inlineStr">
@@ -41745,7 +41850,7 @@
       </c>
       <c r="G884" s="9" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="H884" s="9" t="inlineStr">
@@ -41757,7 +41862,7 @@
     <row r="885">
       <c r="A885" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B885" s="9" t="inlineStr">
@@ -41799,7 +41904,7 @@
     <row r="886">
       <c r="A886" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B886" s="9" t="inlineStr">
@@ -41841,7 +41946,7 @@
     <row r="887">
       <c r="A887" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B887" s="9" t="inlineStr">
@@ -41883,7 +41988,7 @@
     <row r="888">
       <c r="A888" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B888" s="9" t="inlineStr">
@@ -41925,7 +42030,7 @@
     <row r="889">
       <c r="A889" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B889" s="9" t="inlineStr">
@@ -41967,7 +42072,7 @@
     <row r="890">
       <c r="A890" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B890" s="9" t="inlineStr">
@@ -42009,7 +42114,7 @@
     <row r="891">
       <c r="A891" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B891" s="9" t="inlineStr">
@@ -42051,7 +42156,7 @@
     <row r="892">
       <c r="A892" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B892" s="9" t="inlineStr">
@@ -42081,7 +42186,7 @@
       </c>
       <c r="G892" s="9" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="H892" s="9" t="inlineStr">
@@ -42093,7 +42198,7 @@
     <row r="893">
       <c r="A893" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B893" s="9" t="inlineStr">
@@ -42135,7 +42240,7 @@
     <row r="894">
       <c r="A894" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B894" s="9" t="inlineStr">
@@ -42177,7 +42282,7 @@
     <row r="895">
       <c r="A895" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B895" s="9" t="inlineStr">
@@ -42207,7 +42312,7 @@
       </c>
       <c r="G895" s="9" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="H895" s="9" t="inlineStr">
@@ -42219,7 +42324,7 @@
     <row r="896">
       <c r="A896" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B896" s="9" t="inlineStr">
@@ -42261,7 +42366,7 @@
     <row r="897">
       <c r="A897" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B897" s="9" t="inlineStr">
@@ -42303,7 +42408,7 @@
     <row r="898">
       <c r="A898" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B898" s="9" t="inlineStr">
@@ -42345,7 +42450,7 @@
     <row r="899">
       <c r="A899" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B899" s="9" t="inlineStr">
@@ -42387,7 +42492,7 @@
     <row r="900">
       <c r="A900" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B900" s="9" t="inlineStr">
@@ -42429,7 +42534,7 @@
     <row r="901">
       <c r="A901" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B901" s="9" t="inlineStr">
@@ -42471,7 +42576,7 @@
     <row r="902">
       <c r="A902" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B902" s="9" t="inlineStr">
@@ -42513,7 +42618,7 @@
     <row r="903">
       <c r="A903" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B903" s="9" t="inlineStr">
@@ -42555,7 +42660,7 @@
     <row r="904">
       <c r="A904" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B904" s="9" t="inlineStr">
@@ -42597,7 +42702,7 @@
     <row r="905">
       <c r="A905" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B905" s="9" t="inlineStr">
@@ -42639,7 +42744,7 @@
     <row r="906">
       <c r="A906" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B906" s="9" t="inlineStr">
@@ -42681,7 +42786,7 @@
     <row r="907">
       <c r="A907" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B907" s="9" t="inlineStr">
@@ -42723,7 +42828,7 @@
     <row r="908">
       <c r="A908" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B908" s="9" t="inlineStr">
@@ -42765,7 +42870,7 @@
     <row r="909">
       <c r="A909" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B909" s="9" t="inlineStr">
@@ -42807,7 +42912,7 @@
     <row r="910">
       <c r="A910" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B910" s="9" t="inlineStr">
@@ -42849,7 +42954,7 @@
     <row r="911">
       <c r="A911" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B911" s="9" t="inlineStr">
@@ -42891,7 +42996,7 @@
     <row r="912">
       <c r="A912" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B912" s="9" t="inlineStr">
@@ -42933,7 +43038,7 @@
     <row r="913">
       <c r="A913" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B913" s="9" t="inlineStr">
@@ -42975,7 +43080,7 @@
     <row r="914">
       <c r="A914" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B914" s="9" t="inlineStr">
@@ -43017,7 +43122,7 @@
     <row r="915">
       <c r="A915" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B915" s="9" t="inlineStr">
@@ -43059,7 +43164,7 @@
     <row r="916">
       <c r="A916" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B916" s="9" t="inlineStr">
@@ -43089,7 +43194,7 @@
       </c>
       <c r="G916" s="9" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="H916" s="9" t="inlineStr">
@@ -43101,7 +43206,7 @@
     <row r="917">
       <c r="A917" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B917" s="9" t="inlineStr">
@@ -43143,7 +43248,7 @@
     <row r="918">
       <c r="A918" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B918" s="9" t="inlineStr">
@@ -43185,7 +43290,7 @@
     <row r="919">
       <c r="A919" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B919" s="9" t="inlineStr">
@@ -43227,7 +43332,7 @@
     <row r="920">
       <c r="A920" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B920" s="9" t="inlineStr">
@@ -43269,7 +43374,7 @@
     <row r="921">
       <c r="A921" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B921" s="9" t="inlineStr">
@@ -43311,7 +43416,7 @@
     <row r="922">
       <c r="A922" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B922" s="9" t="inlineStr">
@@ -43353,7 +43458,7 @@
     <row r="923">
       <c r="A923" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B923" s="9" t="inlineStr">
@@ -43395,7 +43500,7 @@
     <row r="924">
       <c r="A924" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B924" s="9" t="inlineStr">
@@ -43437,7 +43542,7 @@
     <row r="925">
       <c r="A925" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B925" s="9" t="inlineStr">
@@ -43479,7 +43584,7 @@
     <row r="926">
       <c r="A926" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B926" s="9" t="inlineStr">
@@ -43521,7 +43626,7 @@
     <row r="927">
       <c r="A927" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B927" s="9" t="inlineStr">
@@ -43563,7 +43668,7 @@
     <row r="928">
       <c r="A928" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B928" s="9" t="inlineStr">
@@ -43605,7 +43710,7 @@
     <row r="929">
       <c r="A929" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B929" s="9" t="inlineStr">
@@ -43647,7 +43752,7 @@
     <row r="930">
       <c r="A930" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B930" s="9" t="inlineStr">
@@ -43689,7 +43794,7 @@
     <row r="931">
       <c r="A931" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B931" s="9" t="inlineStr">
@@ -43731,7 +43836,7 @@
     <row r="932">
       <c r="A932" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B932" s="9" t="inlineStr">
@@ -43773,7 +43878,7 @@
     <row r="933">
       <c r="A933" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B933" s="9" t="inlineStr">
@@ -43815,7 +43920,7 @@
     <row r="934">
       <c r="A934" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B934" s="9" t="inlineStr">
@@ -43857,7 +43962,7 @@
     <row r="935">
       <c r="A935" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B935" s="9" t="inlineStr">
@@ -43899,7 +44004,7 @@
     <row r="936">
       <c r="A936" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B936" s="9" t="inlineStr">
@@ -43941,7 +44046,7 @@
     <row r="937">
       <c r="A937" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B937" s="9" t="inlineStr">
@@ -43983,7 +44088,7 @@
     <row r="938">
       <c r="A938" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B938" s="9" t="inlineStr">
@@ -44025,7 +44130,7 @@
     <row r="939">
       <c r="A939" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B939" s="9" t="inlineStr">
@@ -44067,7 +44172,7 @@
     <row r="940">
       <c r="A940" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B940" s="9" t="inlineStr">
@@ -44109,7 +44214,7 @@
     <row r="941">
       <c r="A941" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B941" s="9" t="inlineStr">
@@ -44151,7 +44256,7 @@
     <row r="942">
       <c r="A942" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B942" s="9" t="inlineStr">
@@ -44193,7 +44298,7 @@
     <row r="943">
       <c r="A943" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B943" s="9" t="inlineStr">
@@ -44235,7 +44340,7 @@
     <row r="944">
       <c r="A944" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B944" s="9" t="inlineStr">
@@ -44277,7 +44382,7 @@
     <row r="945">
       <c r="A945" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B945" s="9" t="inlineStr">
@@ -44319,7 +44424,7 @@
     <row r="946">
       <c r="A946" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B946" s="9" t="inlineStr">
@@ -44361,7 +44466,7 @@
     <row r="947">
       <c r="A947" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B947" s="9" t="inlineStr">
@@ -44403,7 +44508,7 @@
     <row r="948">
       <c r="A948" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B948" s="9" t="inlineStr">
@@ -44445,7 +44550,7 @@
     <row r="949">
       <c r="A949" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B949" s="9" t="inlineStr">
@@ -44487,7 +44592,7 @@
     <row r="950">
       <c r="A950" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B950" s="9" t="inlineStr">
@@ -44529,7 +44634,7 @@
     <row r="951">
       <c r="A951" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B951" s="9" t="inlineStr">
@@ -44571,7 +44676,7 @@
     <row r="952">
       <c r="A952" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B952" s="9" t="inlineStr">
@@ -44613,7 +44718,7 @@
     <row r="953">
       <c r="A953" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B953" s="9" t="inlineStr">
@@ -44655,7 +44760,7 @@
     <row r="954">
       <c r="A954" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B954" s="9" t="inlineStr">
@@ -44697,7 +44802,7 @@
     <row r="955">
       <c r="A955" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B955" s="9" t="inlineStr">
@@ -44739,7 +44844,7 @@
     <row r="956">
       <c r="A956" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B956" s="9" t="inlineStr">
@@ -44781,7 +44886,7 @@
     <row r="957">
       <c r="A957" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B957" s="9" t="inlineStr">
@@ -44823,7 +44928,7 @@
     <row r="958">
       <c r="A958" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B958" s="9" t="inlineStr">
@@ -44865,7 +44970,7 @@
     <row r="959">
       <c r="A959" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B959" s="9" t="inlineStr">
@@ -44907,7 +45012,7 @@
     <row r="960">
       <c r="A960" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B960" s="9" t="inlineStr">
@@ -44949,7 +45054,7 @@
     <row r="961">
       <c r="A961" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B961" s="9" t="inlineStr">
@@ -44991,7 +45096,7 @@
     <row r="962">
       <c r="A962" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B962" s="9" t="inlineStr">
@@ -45033,7 +45138,7 @@
     <row r="963">
       <c r="A963" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B963" s="9" t="inlineStr">
@@ -45075,7 +45180,7 @@
     <row r="964">
       <c r="A964" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B964" s="9" t="inlineStr">
@@ -45117,7 +45222,7 @@
     <row r="965">
       <c r="A965" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B965" s="9" t="inlineStr">
@@ -45159,7 +45264,7 @@
     <row r="966">
       <c r="A966" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B966" s="9" t="inlineStr">
@@ -45201,7 +45306,7 @@
     <row r="967">
       <c r="A967" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B967" s="9" t="inlineStr">
@@ -45243,7 +45348,7 @@
     <row r="968">
       <c r="A968" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B968" s="9" t="inlineStr">
@@ -45285,7 +45390,7 @@
     <row r="969">
       <c r="A969" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B969" s="9" t="inlineStr">
@@ -45327,7 +45432,7 @@
     <row r="970">
       <c r="A970" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B970" s="9" t="inlineStr">
@@ -45369,7 +45474,7 @@
     <row r="971">
       <c r="A971" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B971" s="9" t="inlineStr">
@@ -45411,7 +45516,7 @@
     <row r="972">
       <c r="A972" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B972" s="9" t="inlineStr">
@@ -45453,7 +45558,7 @@
     <row r="973">
       <c r="A973" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B973" s="9" t="inlineStr">
@@ -45495,7 +45600,7 @@
     <row r="974">
       <c r="A974" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B974" s="9" t="inlineStr">
@@ -45537,7 +45642,7 @@
     <row r="975">
       <c r="A975" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B975" s="9" t="inlineStr">
@@ -45579,7 +45684,7 @@
     <row r="976">
       <c r="A976" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B976" s="9" t="inlineStr">
@@ -45621,7 +45726,7 @@
     <row r="977">
       <c r="A977" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B977" s="9" t="inlineStr">
@@ -45663,7 +45768,7 @@
     <row r="978">
       <c r="A978" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B978" s="9" t="inlineStr">
@@ -45705,7 +45810,7 @@
     <row r="979">
       <c r="A979" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B979" s="9" t="inlineStr">
@@ -45747,7 +45852,7 @@
     <row r="980">
       <c r="A980" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B980" s="9" t="inlineStr">
@@ -45789,7 +45894,7 @@
     <row r="981">
       <c r="A981" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B981" s="9" t="inlineStr">
@@ -45831,7 +45936,7 @@
     <row r="982">
       <c r="A982" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B982" s="9" t="inlineStr">
@@ -45873,7 +45978,7 @@
     <row r="983">
       <c r="A983" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B983" s="9" t="inlineStr">
@@ -45915,7 +46020,7 @@
     <row r="984">
       <c r="A984" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B984" s="9" t="inlineStr">
@@ -45957,7 +46062,7 @@
     <row r="985">
       <c r="A985" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B985" s="9" t="inlineStr">
@@ -45999,7 +46104,7 @@
     <row r="986">
       <c r="A986" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B986" s="9" t="inlineStr">
@@ -46019,17 +46124,17 @@
       </c>
       <c r="E986" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F986" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Elevated</t>
         </is>
       </c>
       <c r="G986" s="9" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="H986" s="9" t="inlineStr">
@@ -46041,7 +46146,7 @@
     <row r="987">
       <c r="A987" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B987" s="9" t="inlineStr">
@@ -46083,7 +46188,7 @@
     <row r="988">
       <c r="A988" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B988" s="9" t="inlineStr">
@@ -46125,7 +46230,7 @@
     <row r="989">
       <c r="A989" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B989" s="9" t="inlineStr">
@@ -46145,7 +46250,7 @@
       </c>
       <c r="E989" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F989" s="9" t="inlineStr">
@@ -46155,7 +46260,7 @@
       </c>
       <c r="G989" s="9" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="H989" s="9" t="inlineStr">
@@ -46167,7 +46272,7 @@
     <row r="990">
       <c r="A990" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B990" s="9" t="inlineStr">
@@ -46209,7 +46314,7 @@
     <row r="991">
       <c r="A991" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B991" s="9" t="inlineStr">
@@ -46251,7 +46356,7 @@
     <row r="992">
       <c r="A992" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B992" s="9" t="inlineStr">
@@ -46293,7 +46398,7 @@
     <row r="993">
       <c r="A993" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B993" s="9" t="inlineStr">
@@ -46335,7 +46440,7 @@
     <row r="994">
       <c r="A994" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B994" s="9" t="inlineStr">
@@ -46377,7 +46482,7 @@
     <row r="995">
       <c r="A995" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B995" s="9" t="inlineStr">
@@ -46419,7 +46524,7 @@
     <row r="996">
       <c r="A996" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B996" s="9" t="inlineStr">
@@ -46439,17 +46544,17 @@
       </c>
       <c r="E996" s="9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F996" s="9" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Elevated</t>
         </is>
       </c>
       <c r="G996" s="9" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="H996" s="9" t="inlineStr">
@@ -46461,7 +46566,7 @@
     <row r="997">
       <c r="A997" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B997" s="9" t="inlineStr">
@@ -46491,7 +46596,7 @@
       </c>
       <c r="G997" s="9" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="H997" s="9" t="inlineStr">
@@ -46503,7 +46608,7 @@
     <row r="998">
       <c r="A998" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B998" s="9" t="inlineStr">
@@ -46545,7 +46650,7 @@
     <row r="999">
       <c r="A999" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B999" s="9" t="inlineStr">
@@ -46587,7 +46692,7 @@
     <row r="1000">
       <c r="A1000" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B1000" s="9" t="inlineStr">
@@ -46607,17 +46712,17 @@
       </c>
       <c r="E1000" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F1000" s="9" t="inlineStr">
         <is>
-          <t>Elevated</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G1000" s="9" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="H1000" s="9" t="inlineStr">
@@ -46629,7 +46734,7 @@
     <row r="1001">
       <c r="A1001" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B1001" s="9" t="inlineStr">
@@ -46679,7 +46784,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A30"/>
+  <dimension ref="A1:A24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -46760,7 +46865,7 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>--- Daily narrative (2026-08-14) ---</t>
+          <t>--- Daily narrative (2026-08-17) ---</t>
         </is>
       </c>
     </row>
@@ -46774,7 +46879,7 @@
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>Macro risk stands at High, driven by concentrated exposure to private credit opacity, Japan carry-trade mechanics, and critical minerals weaponization.</t>
+          <t>Macro risk stands at High, with geopolitical supply-chain pressure and financial leverage offsetting modest relief in commodity and real-estate stress.</t>
         </is>
       </c>
     </row>
@@ -46784,90 +46889,52 @@
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>**NO CHANGES TODAY**</t>
+          <t>**CHANGES**</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>No stories shifted risk bands.</t>
+          <t>• **Critical minerals as a weapon** (7→6, Elevated): US entity-specific rare-earth producer ban reduced acute escalation risk; supply-chain weaponization remains a structural threat.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr"/>
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>• **CRE maturity wall / regional banks** (6→5, Elevated): CMBS office delinquencies stabilizing and isolated regional stress (not clustered) eased pressure; refinancing maturity remains live.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>**PERSISTENT ELEVATED/HIGH RISKS**</t>
+          <t>• **Copper &amp; the electrification deficit** (4→5, Elevated): Copper price spike ($6.69/lb) and cluster-level mine disruptions signal supply tightness; critical for grid and EV transition infrastructure.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>• **Private credit's opaque expansion** (High): Unregulated leverage and opacity in $2T+ market create hidden default contagion vectors into regulated finance.</t>
+          <t>• **Sea lanes &amp; undersea cables** (6→7, High): Escalated to High; geopolitical friction over maritime chokepoints and cable vulnerabilities now acute.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t>• **Japan fiscal / JGB / carry trade** (High): Yen instability and BOJ divergence threaten funding chains for leveraged trades globally.</t>
-        </is>
-      </c>
+      <c r="A22" s="12" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>• **Critical minerals as a weapon** (High): Supply concentration and geopolitical control over rare earths and battery metals underpin industrial/defense vulnerability.</t>
+          <t>**TOP WATCH**</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>• **AI power &amp; the grid bottleneck** (High): Demand surge outpacing infrastructure; localized strains could cascade into brownouts affecting data centers.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>• **Treasury basis trade (hidden leverage)** (Elevated): Off-balance-sheet leverage in repo/derivatives spreads amplifies shock transmission.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="12" t="inlineStr">
-        <is>
-          <t>• **Developing-world debt crisis** (Elevated): Currency pressure and refinancing cliff for emerging sovereigns.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>• **CRE maturity wall / regional banks** (Elevated): Refinancing stress and mark-to-market losses concentrate in smaller lenders.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="12" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="12" t="inlineStr">
-        <is>
-          <t>**WATCH MOST CLOSELY**</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="12" t="inlineStr">
-        <is>
-          <t>Private credit's opaque expansion carries the highest absolute level (8) and widest contagion surface into regulated banking.</t>
+          <t>Private credit's opaque expansion at High (level 8) remains the most systemically fragile story given interconnection risk and valuation opacity.</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-08-17  -  generated 2026-08-17 12:02 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-08-18  -  generated 2026-08-18 11:56 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="D3" s="7" t="n">
-        <v>69.5796</v>
+        <v>75.6302</v>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>159.24</v>
+        <v>159.698</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>4.002</v>
+        <v>4.05</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>2.71</v>
+        <v>2.67</v>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>119.0649</v>
+        <v>118.9028</v>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>6.7386</v>
+        <v>6.7305</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>307.2</v>
+        <v>307</v>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>4456.3999</v>
+        <v>4449.3999</v>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>6.6895</v>
+        <v>6.559</v>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="D60" s="7" t="n">
-        <v>82.48999999999999</v>
+        <v>84.03</v>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="D62" s="7" t="n">
-        <v>14.91</v>
+        <v>15.74</v>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
         </is>
       </c>
       <c r="D63" s="7" t="n">
-        <v>69.5796</v>
+        <v>75.6302</v>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
@@ -6644,7 +6644,7 @@
       </c>
       <c r="E36" s="9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F36" s="9" t="inlineStr">
@@ -6654,7 +6654,7 @@
       </c>
       <c r="G36" s="9" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5.5</t>
         </is>
       </c>
     </row>
@@ -6691,7 +6691,7 @@
       </c>
       <c r="G37" s="9" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>6.5</t>
         </is>
       </c>
     </row>
@@ -6718,7 +6718,7 @@
       </c>
       <c r="E38" s="9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F38" s="9" t="inlineStr">
@@ -6728,7 +6728,7 @@
       </c>
       <c r="G38" s="9" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>6.0</t>
         </is>
       </c>
     </row>
@@ -6802,7 +6802,7 @@
       </c>
       <c r="G40" s="9" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>5.5</t>
         </is>
       </c>
     </row>
@@ -6839,7 +6839,7 @@
       </c>
       <c r="G41" s="9" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>6.25</t>
         </is>
       </c>
     </row>
@@ -6876,7 +6876,7 @@
       </c>
       <c r="G42" s="9" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4.25</t>
         </is>
       </c>
     </row>
@@ -6913,7 +6913,7 @@
       </c>
       <c r="G43" s="9" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>6.5</t>
         </is>
       </c>
     </row>
@@ -6940,7 +6940,7 @@
       </c>
       <c r="E44" s="9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F44" s="9" t="inlineStr">
@@ -6950,7 +6950,7 @@
       </c>
       <c r="G44" s="9" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5.75</t>
         </is>
       </c>
     </row>
@@ -6987,7 +6987,7 @@
       </c>
       <c r="G45" s="9" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4.5</t>
         </is>
       </c>
     </row>
@@ -7014,7 +7014,7 @@
       </c>
       <c r="E46" s="9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F46" s="9" t="inlineStr">
@@ -7024,7 +7024,7 @@
       </c>
       <c r="G46" s="9" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5.5</t>
         </is>
       </c>
     </row>
@@ -7051,7 +7051,7 @@
       </c>
       <c r="E47" s="9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F47" s="9" t="inlineStr">
@@ -7061,7 +7061,7 @@
       </c>
       <c r="G47" s="9" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>3.5</t>
         </is>
       </c>
     </row>
@@ -7088,17 +7088,17 @@
       </c>
       <c r="E48" s="9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F48" s="9" t="inlineStr">
         <is>
-          <t>Elevated</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="G48" s="9" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.5</t>
         </is>
       </c>
     </row>
@@ -7135,7 +7135,7 @@
       </c>
       <c r="G49" s="9" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4.25</t>
         </is>
       </c>
     </row>
@@ -7172,7 +7172,7 @@
       </c>
       <c r="G50" s="9" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>6.5</t>
         </is>
       </c>
     </row>
@@ -7209,7 +7209,7 @@
       </c>
       <c r="G51" s="9" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.5</t>
         </is>
       </c>
     </row>
@@ -7236,17 +7236,17 @@
       </c>
       <c r="E52" s="9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F52" s="9" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Elevated</t>
         </is>
       </c>
       <c r="G52" s="9" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>5.25</t>
         </is>
       </c>
     </row>
@@ -7320,7 +7320,7 @@
       </c>
       <c r="G54" s="9" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5.25</t>
         </is>
       </c>
     </row>
@@ -7357,7 +7357,7 @@
       </c>
       <c r="G55" s="9" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6.0</t>
         </is>
       </c>
     </row>
@@ -7394,7 +7394,7 @@
       </c>
       <c r="G56" s="9" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4.25</t>
         </is>
       </c>
     </row>
@@ -8050,17 +8050,17 @@
       </c>
       <c r="E74" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F74" s="9" t="inlineStr">
         <is>
-          <t>Elevated</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G74" s="9" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>7.0</t>
         </is>
       </c>
     </row>
@@ -8097,7 +8097,7 @@
       </c>
       <c r="G75" s="9" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -8134,7 +8134,7 @@
       </c>
       <c r="G76" s="9" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>6.5</t>
         </is>
       </c>
     </row>
@@ -8800,7 +8800,7 @@
       </c>
       <c r="G94" s="9" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>4.75</t>
         </is>
       </c>
     </row>
@@ -8827,17 +8827,17 @@
       </c>
       <c r="E95" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F95" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Elevated</t>
         </is>
       </c>
       <c r="G95" s="9" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.5</t>
         </is>
       </c>
     </row>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="G96" s="9" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5.25</t>
         </is>
       </c>
     </row>
@@ -8911,7 +8911,7 @@
       </c>
       <c r="G97" s="9" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6.25</t>
         </is>
       </c>
     </row>
@@ -8955,7 +8955,7 @@
     <row r="99">
       <c r="A99" s="9" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B99" s="9" t="inlineStr">
@@ -8986,13 +8986,18 @@
       <c r="G99" s="9" t="inlineStr">
         <is>
           <t>5.5</t>
+        </is>
+      </c>
+      <c r="H99" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="9" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B100" s="9" t="inlineStr">
@@ -9023,13 +9028,18 @@
       <c r="G100" s="9" t="inlineStr">
         <is>
           <t>6.5</t>
+        </is>
+      </c>
+      <c r="H100" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="9" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B101" s="9" t="inlineStr">
@@ -9060,13 +9070,18 @@
       <c r="G101" s="9" t="inlineStr">
         <is>
           <t>6.0</t>
+        </is>
+      </c>
+      <c r="H101" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="9" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B102" s="9" t="inlineStr">
@@ -9097,13 +9112,18 @@
       <c r="G102" s="9" t="inlineStr">
         <is>
           <t>5.0</t>
+        </is>
+      </c>
+      <c r="H102" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="9" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B103" s="9" t="inlineStr">
@@ -9113,7 +9133,7 @@
       </c>
       <c r="C103" s="9" t="inlineStr">
         <is>
-          <t>China's exported deflation</t>
+          <t>China's price spillover (deflation or cost-push)</t>
         </is>
       </c>
       <c r="D103" s="9" t="inlineStr">
@@ -9133,14 +9153,19 @@
       </c>
       <c r="G103" s="9" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="H103" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="9" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B104" s="9" t="inlineStr">
@@ -9160,24 +9185,29 @@
       </c>
       <c r="E104" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F104" s="9" t="inlineStr">
         <is>
-          <t>Elevated</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G104" s="9" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>6.75</t>
+        </is>
+      </c>
+      <c r="H104" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="9" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B105" s="9" t="inlineStr">
@@ -9208,13 +9238,18 @@
       <c r="G105" s="9" t="inlineStr">
         <is>
           <t>4.25</t>
+        </is>
+      </c>
+      <c r="H105" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="9" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B106" s="9" t="inlineStr">
@@ -9245,13 +9280,18 @@
       <c r="G106" s="9" t="inlineStr">
         <is>
           <t>6.5</t>
+        </is>
+      </c>
+      <c r="H106" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="9" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B107" s="9" t="inlineStr">
@@ -9271,7 +9311,7 @@
       </c>
       <c r="E107" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F107" s="9" t="inlineStr">
@@ -9281,14 +9321,19 @@
       </c>
       <c r="G107" s="9" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="H107" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="9" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B108" s="9" t="inlineStr">
@@ -9308,24 +9353,29 @@
       </c>
       <c r="E108" s="9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F108" s="9" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Elevated</t>
         </is>
       </c>
       <c r="G108" s="9" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H108" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="9" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B109" s="9" t="inlineStr">
@@ -9345,7 +9395,7 @@
       </c>
       <c r="E109" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F109" s="9" t="inlineStr">
@@ -9355,14 +9405,19 @@
       </c>
       <c r="G109" s="9" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H109" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="9" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B110" s="9" t="inlineStr">
@@ -9393,13 +9448,18 @@
       <c r="G110" s="9" t="inlineStr">
         <is>
           <t>3.5</t>
+        </is>
+      </c>
+      <c r="H110" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="9" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B111" s="9" t="inlineStr">
@@ -9430,13 +9490,18 @@
       <c r="G111" s="9" t="inlineStr">
         <is>
           <t>4.5</t>
+        </is>
+      </c>
+      <c r="H111" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="9" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B112" s="9" t="inlineStr">
@@ -9456,24 +9521,29 @@
       </c>
       <c r="E112" s="9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F112" s="9" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Elevated</t>
         </is>
       </c>
       <c r="G112" s="9" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="H112" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="9" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B113" s="9" t="inlineStr">
@@ -9504,13 +9574,18 @@
       <c r="G113" s="9" t="inlineStr">
         <is>
           <t>6.5</t>
+        </is>
+      </c>
+      <c r="H113" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="9" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B114" s="9" t="inlineStr">
@@ -9541,13 +9616,18 @@
       <c r="G114" s="9" t="inlineStr">
         <is>
           <t>4.5</t>
+        </is>
+      </c>
+      <c r="H114" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="9" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B115" s="9" t="inlineStr">
@@ -9577,14 +9657,19 @@
       </c>
       <c r="G115" s="9" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="H115" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="9" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B116" s="9" t="inlineStr">
@@ -9604,24 +9689,29 @@
       </c>
       <c r="E116" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F116" s="9" t="inlineStr">
         <is>
-          <t>Elevated</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G116" s="9" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H116" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="9" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B117" s="9" t="inlineStr">
@@ -9641,7 +9731,7 @@
       </c>
       <c r="E117" s="9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F117" s="9" t="inlineStr">
@@ -9651,14 +9741,19 @@
       </c>
       <c r="G117" s="9" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H117" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="9" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B118" s="9" t="inlineStr">
@@ -9689,13 +9784,18 @@
       <c r="G118" s="9" t="inlineStr">
         <is>
           <t>6.25</t>
+        </is>
+      </c>
+      <c r="H118" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="9" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B119" s="9" t="inlineStr">
@@ -9726,6 +9826,11 @@
       <c r="G119" s="9" t="inlineStr">
         <is>
           <t>4.25</t>
+        </is>
+      </c>
+      <c r="H119" s="9" t="inlineStr">
+        <is>
+          <t>2.0</t>
         </is>
       </c>
     </row>
@@ -10812,7 +10917,7 @@
       </c>
       <c r="G145" s="9" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="H145" s="9" t="inlineStr">
@@ -11054,7 +11159,7 @@
       </c>
       <c r="E151" s="9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F151" s="9" t="inlineStr">
@@ -11064,7 +11169,7 @@
       </c>
       <c r="G151" s="9" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="H151" s="9" t="inlineStr">
@@ -11180,17 +11285,17 @@
       </c>
       <c r="E154" s="9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F154" s="9" t="inlineStr">
         <is>
-          <t>Elevated</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="G154" s="9" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="H154" s="9" t="inlineStr">
@@ -11222,17 +11327,17 @@
       </c>
       <c r="E155" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F155" s="9" t="inlineStr">
         <is>
-          <t>Elevated</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G155" s="9" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="H155" s="9" t="inlineStr">
@@ -11316,7 +11421,7 @@
       </c>
       <c r="G157" s="9" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="H157" s="9" t="inlineStr">
@@ -11348,17 +11453,17 @@
       </c>
       <c r="E158" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F158" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Elevated</t>
         </is>
       </c>
       <c r="G158" s="9" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="H158" s="9" t="inlineStr">
@@ -11442,7 +11547,7 @@
       </c>
       <c r="G160" s="9" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="H160" s="9" t="inlineStr">
@@ -11496,7 +11601,7 @@
     <row r="162">
       <c r="A162" s="9" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B162" s="9" t="inlineStr">
@@ -11538,7 +11643,7 @@
     <row r="163">
       <c r="A163" s="9" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B163" s="9" t="inlineStr">
@@ -11580,7 +11685,7 @@
     <row r="164">
       <c r="A164" s="9" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B164" s="9" t="inlineStr">
@@ -11622,7 +11727,7 @@
     <row r="165">
       <c r="A165" s="9" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B165" s="9" t="inlineStr">
@@ -11664,7 +11769,7 @@
     <row r="166">
       <c r="A166" s="9" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B166" s="9" t="inlineStr">
@@ -11706,7 +11811,7 @@
     <row r="167">
       <c r="A167" s="9" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B167" s="9" t="inlineStr">
@@ -11748,7 +11853,7 @@
     <row r="168">
       <c r="A168" s="9" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B168" s="9" t="inlineStr">
@@ -11790,7 +11895,7 @@
     <row r="169">
       <c r="A169" s="9" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B169" s="9" t="inlineStr">
@@ -11832,7 +11937,7 @@
     <row r="170">
       <c r="A170" s="9" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B170" s="9" t="inlineStr">
@@ -11874,7 +11979,7 @@
     <row r="171">
       <c r="A171" s="9" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B171" s="9" t="inlineStr">
@@ -11916,7 +12021,7 @@
     <row r="172">
       <c r="A172" s="9" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B172" s="9" t="inlineStr">
@@ -11958,7 +12063,7 @@
     <row r="173">
       <c r="A173" s="9" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B173" s="9" t="inlineStr">
@@ -12000,7 +12105,7 @@
     <row r="174">
       <c r="A174" s="9" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B174" s="9" t="inlineStr">
@@ -12042,7 +12147,7 @@
     <row r="175">
       <c r="A175" s="9" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B175" s="9" t="inlineStr">
@@ -12084,7 +12189,7 @@
     <row r="176">
       <c r="A176" s="9" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B176" s="9" t="inlineStr">
@@ -12126,7 +12231,7 @@
     <row r="177">
       <c r="A177" s="9" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B177" s="9" t="inlineStr">
@@ -12168,7 +12273,7 @@
     <row r="178">
       <c r="A178" s="9" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B178" s="9" t="inlineStr">
@@ -12210,7 +12315,7 @@
     <row r="179">
       <c r="A179" s="9" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B179" s="9" t="inlineStr">
@@ -12252,7 +12357,7 @@
     <row r="180">
       <c r="A180" s="9" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B180" s="9" t="inlineStr">
@@ -12294,7 +12399,7 @@
     <row r="181">
       <c r="A181" s="9" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B181" s="9" t="inlineStr">
@@ -12336,7 +12441,7 @@
     <row r="182">
       <c r="A182" s="9" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B182" s="9" t="inlineStr">
@@ -12378,7 +12483,7 @@
     <row r="183">
       <c r="A183" s="9" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B183" s="9" t="inlineStr">
@@ -12420,7 +12525,7 @@
     <row r="184">
       <c r="A184" s="9" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B184" s="9" t="inlineStr">
@@ -12462,7 +12567,7 @@
     <row r="185">
       <c r="A185" s="9" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B185" s="9" t="inlineStr">
@@ -12504,7 +12609,7 @@
     <row r="186">
       <c r="A186" s="9" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B186" s="9" t="inlineStr">
@@ -12546,7 +12651,7 @@
     <row r="187">
       <c r="A187" s="9" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B187" s="9" t="inlineStr">
@@ -12588,7 +12693,7 @@
     <row r="188">
       <c r="A188" s="9" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B188" s="9" t="inlineStr">
@@ -12630,7 +12735,7 @@
     <row r="189">
       <c r="A189" s="9" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B189" s="9" t="inlineStr">
@@ -12672,7 +12777,7 @@
     <row r="190">
       <c r="A190" s="9" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B190" s="9" t="inlineStr">
@@ -12714,7 +12819,7 @@
     <row r="191">
       <c r="A191" s="9" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B191" s="9" t="inlineStr">
@@ -12756,7 +12861,7 @@
     <row r="192">
       <c r="A192" s="9" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B192" s="9" t="inlineStr">
@@ -12798,7 +12903,7 @@
     <row r="193">
       <c r="A193" s="9" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B193" s="9" t="inlineStr">
@@ -12840,7 +12945,7 @@
     <row r="194">
       <c r="A194" s="9" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B194" s="9" t="inlineStr">
@@ -12882,7 +12987,7 @@
     <row r="195">
       <c r="A195" s="9" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B195" s="9" t="inlineStr">
@@ -12924,7 +13029,7 @@
     <row r="196">
       <c r="A196" s="9" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B196" s="9" t="inlineStr">
@@ -12966,7 +13071,7 @@
     <row r="197">
       <c r="A197" s="9" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B197" s="9" t="inlineStr">
@@ -13008,7 +13113,7 @@
     <row r="198">
       <c r="A198" s="9" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B198" s="9" t="inlineStr">
@@ -13050,7 +13155,7 @@
     <row r="199">
       <c r="A199" s="9" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B199" s="9" t="inlineStr">
@@ -13092,7 +13197,7 @@
     <row r="200">
       <c r="A200" s="9" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B200" s="9" t="inlineStr">
@@ -13134,7 +13239,7 @@
     <row r="201">
       <c r="A201" s="9" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B201" s="9" t="inlineStr">
@@ -13176,7 +13281,7 @@
     <row r="202">
       <c r="A202" s="9" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B202" s="9" t="inlineStr">
@@ -13218,7 +13323,7 @@
     <row r="203">
       <c r="A203" s="9" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B203" s="9" t="inlineStr">
@@ -13260,7 +13365,7 @@
     <row r="204">
       <c r="A204" s="9" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B204" s="9" t="inlineStr">
@@ -13302,7 +13407,7 @@
     <row r="205">
       <c r="A205" s="9" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B205" s="9" t="inlineStr">
@@ -13344,7 +13449,7 @@
     <row r="206">
       <c r="A206" s="9" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B206" s="9" t="inlineStr">
@@ -13386,7 +13491,7 @@
     <row r="207">
       <c r="A207" s="9" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B207" s="9" t="inlineStr">
@@ -13406,7 +13511,7 @@
       </c>
       <c r="E207" s="9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F207" s="9" t="inlineStr">
@@ -13416,7 +13521,7 @@
       </c>
       <c r="G207" s="9" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="H207" s="9" t="inlineStr">
@@ -13428,7 +13533,7 @@
     <row r="208">
       <c r="A208" s="9" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B208" s="9" t="inlineStr">
@@ -13470,7 +13575,7 @@
     <row r="209">
       <c r="A209" s="9" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B209" s="9" t="inlineStr">
@@ -13512,7 +13617,7 @@
     <row r="210">
       <c r="A210" s="9" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B210" s="9" t="inlineStr">
@@ -13554,7 +13659,7 @@
     <row r="211">
       <c r="A211" s="9" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B211" s="9" t="inlineStr">
@@ -13596,7 +13701,7 @@
     <row r="212">
       <c r="A212" s="9" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B212" s="9" t="inlineStr">
@@ -13638,7 +13743,7 @@
     <row r="213">
       <c r="A213" s="9" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B213" s="9" t="inlineStr">
@@ -13680,7 +13785,7 @@
     <row r="214">
       <c r="A214" s="9" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B214" s="9" t="inlineStr">
@@ -13722,7 +13827,7 @@
     <row r="215">
       <c r="A215" s="9" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B215" s="9" t="inlineStr">
@@ -13764,7 +13869,7 @@
     <row r="216">
       <c r="A216" s="9" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B216" s="9" t="inlineStr">
@@ -13806,7 +13911,7 @@
     <row r="217">
       <c r="A217" s="9" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B217" s="9" t="inlineStr">
@@ -13848,7 +13953,7 @@
     <row r="218">
       <c r="A218" s="9" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B218" s="9" t="inlineStr">
@@ -13890,7 +13995,7 @@
     <row r="219">
       <c r="A219" s="9" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B219" s="9" t="inlineStr">
@@ -13932,7 +14037,7 @@
     <row r="220">
       <c r="A220" s="9" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B220" s="9" t="inlineStr">
@@ -13974,7 +14079,7 @@
     <row r="221">
       <c r="A221" s="9" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B221" s="9" t="inlineStr">
@@ -14016,7 +14121,7 @@
     <row r="222">
       <c r="A222" s="9" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B222" s="9" t="inlineStr">
@@ -14058,7 +14163,7 @@
     <row r="223">
       <c r="A223" s="9" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B223" s="9" t="inlineStr">
@@ -14100,7 +14205,7 @@
     <row r="224">
       <c r="A224" s="9" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B224" s="9" t="inlineStr">
@@ -14204,17 +14309,17 @@
       </c>
       <c r="E226" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F226" s="9" t="inlineStr">
         <is>
-          <t>Elevated</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G226" s="9" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="H226" s="9" t="inlineStr">
@@ -16788,7 +16893,7 @@
     <row r="288">
       <c r="A288" s="9" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B288" s="9" t="inlineStr">
@@ -16830,7 +16935,7 @@
     <row r="289">
       <c r="A289" s="9" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B289" s="9" t="inlineStr">
@@ -16872,7 +16977,7 @@
     <row r="290">
       <c r="A290" s="9" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B290" s="9" t="inlineStr">
@@ -16914,7 +17019,7 @@
     <row r="291">
       <c r="A291" s="9" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B291" s="9" t="inlineStr">
@@ -16956,7 +17061,7 @@
     <row r="292">
       <c r="A292" s="9" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B292" s="9" t="inlineStr">
@@ -16998,7 +17103,7 @@
     <row r="293">
       <c r="A293" s="9" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B293" s="9" t="inlineStr">
@@ -17040,7 +17145,7 @@
     <row r="294">
       <c r="A294" s="9" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B294" s="9" t="inlineStr">
@@ -17082,7 +17187,7 @@
     <row r="295">
       <c r="A295" s="9" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B295" s="9" t="inlineStr">
@@ -17124,7 +17229,7 @@
     <row r="296">
       <c r="A296" s="9" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B296" s="9" t="inlineStr">
@@ -17166,7 +17271,7 @@
     <row r="297">
       <c r="A297" s="9" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B297" s="9" t="inlineStr">
@@ -17208,7 +17313,7 @@
     <row r="298">
       <c r="A298" s="9" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B298" s="9" t="inlineStr">
@@ -17250,7 +17355,7 @@
     <row r="299">
       <c r="A299" s="9" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B299" s="9" t="inlineStr">
@@ -17292,7 +17397,7 @@
     <row r="300">
       <c r="A300" s="9" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B300" s="9" t="inlineStr">
@@ -17334,7 +17439,7 @@
     <row r="301">
       <c r="A301" s="9" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B301" s="9" t="inlineStr">
@@ -17376,7 +17481,7 @@
     <row r="302">
       <c r="A302" s="9" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B302" s="9" t="inlineStr">
@@ -17418,7 +17523,7 @@
     <row r="303">
       <c r="A303" s="9" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B303" s="9" t="inlineStr">
@@ -17460,7 +17565,7 @@
     <row r="304">
       <c r="A304" s="9" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B304" s="9" t="inlineStr">
@@ -17502,7 +17607,7 @@
     <row r="305">
       <c r="A305" s="9" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B305" s="9" t="inlineStr">
@@ -17544,7 +17649,7 @@
     <row r="306">
       <c r="A306" s="9" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B306" s="9" t="inlineStr">
@@ -17586,7 +17691,7 @@
     <row r="307">
       <c r="A307" s="9" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B307" s="9" t="inlineStr">
@@ -17628,7 +17733,7 @@
     <row r="308">
       <c r="A308" s="9" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B308" s="9" t="inlineStr">
@@ -17670,7 +17775,7 @@
     <row r="309">
       <c r="A309" s="9" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B309" s="9" t="inlineStr">
@@ -17712,7 +17817,7 @@
     <row r="310">
       <c r="A310" s="9" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B310" s="9" t="inlineStr">
@@ -17754,7 +17859,7 @@
     <row r="311">
       <c r="A311" s="9" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B311" s="9" t="inlineStr">
@@ -17796,7 +17901,7 @@
     <row r="312">
       <c r="A312" s="9" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B312" s="9" t="inlineStr">
@@ -17838,7 +17943,7 @@
     <row r="313">
       <c r="A313" s="9" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B313" s="9" t="inlineStr">
@@ -17880,7 +17985,7 @@
     <row r="314">
       <c r="A314" s="9" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B314" s="9" t="inlineStr">
@@ -17922,7 +18027,7 @@
     <row r="315">
       <c r="A315" s="9" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B315" s="9" t="inlineStr">
@@ -17964,7 +18069,7 @@
     <row r="316">
       <c r="A316" s="9" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B316" s="9" t="inlineStr">
@@ -18006,7 +18111,7 @@
     <row r="317">
       <c r="A317" s="9" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B317" s="9" t="inlineStr">
@@ -18048,7 +18153,7 @@
     <row r="318">
       <c r="A318" s="9" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B318" s="9" t="inlineStr">
@@ -18090,7 +18195,7 @@
     <row r="319">
       <c r="A319" s="9" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B319" s="9" t="inlineStr">
@@ -18132,7 +18237,7 @@
     <row r="320">
       <c r="A320" s="9" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B320" s="9" t="inlineStr">
@@ -18174,7 +18279,7 @@
     <row r="321">
       <c r="A321" s="9" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B321" s="9" t="inlineStr">
@@ -18216,7 +18321,7 @@
     <row r="322">
       <c r="A322" s="9" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B322" s="9" t="inlineStr">
@@ -18258,7 +18363,7 @@
     <row r="323">
       <c r="A323" s="9" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B323" s="9" t="inlineStr">
@@ -18300,7 +18405,7 @@
     <row r="324">
       <c r="A324" s="9" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B324" s="9" t="inlineStr">
@@ -18342,7 +18447,7 @@
     <row r="325">
       <c r="A325" s="9" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B325" s="9" t="inlineStr">
@@ -18384,7 +18489,7 @@
     <row r="326">
       <c r="A326" s="9" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B326" s="9" t="inlineStr">
@@ -18426,7 +18531,7 @@
     <row r="327">
       <c r="A327" s="9" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B327" s="9" t="inlineStr">
@@ -18468,7 +18573,7 @@
     <row r="328">
       <c r="A328" s="9" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B328" s="9" t="inlineStr">
@@ -18510,7 +18615,7 @@
     <row r="329">
       <c r="A329" s="9" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B329" s="9" t="inlineStr">
@@ -18552,7 +18657,7 @@
     <row r="330">
       <c r="A330" s="9" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B330" s="9" t="inlineStr">
@@ -18594,7 +18699,7 @@
     <row r="331">
       <c r="A331" s="9" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B331" s="9" t="inlineStr">
@@ -18614,7 +18719,7 @@
       </c>
       <c r="E331" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F331" s="9" t="inlineStr">
@@ -18624,7 +18729,7 @@
       </c>
       <c r="G331" s="9" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="H331" s="9" t="inlineStr">
@@ -18636,7 +18741,7 @@
     <row r="332">
       <c r="A332" s="9" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B332" s="9" t="inlineStr">
@@ -18656,17 +18761,17 @@
       </c>
       <c r="E332" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F332" s="9" t="inlineStr">
         <is>
-          <t>Elevated</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G332" s="9" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="H332" s="9" t="inlineStr">
@@ -18678,7 +18783,7 @@
     <row r="333">
       <c r="A333" s="9" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B333" s="9" t="inlineStr">
@@ -18720,7 +18825,7 @@
     <row r="334">
       <c r="A334" s="9" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B334" s="9" t="inlineStr">
@@ -18762,7 +18867,7 @@
     <row r="335">
       <c r="A335" s="9" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B335" s="9" t="inlineStr">
@@ -18804,7 +18909,7 @@
     <row r="336">
       <c r="A336" s="9" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B336" s="9" t="inlineStr">
@@ -18846,7 +18951,7 @@
     <row r="337">
       <c r="A337" s="9" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B337" s="9" t="inlineStr">
@@ -18888,7 +18993,7 @@
     <row r="338">
       <c r="A338" s="9" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B338" s="9" t="inlineStr">
@@ -18930,7 +19035,7 @@
     <row r="339">
       <c r="A339" s="9" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B339" s="9" t="inlineStr">
@@ -18972,7 +19077,7 @@
     <row r="340">
       <c r="A340" s="9" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B340" s="9" t="inlineStr">
@@ -19014,7 +19119,7 @@
     <row r="341">
       <c r="A341" s="9" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B341" s="9" t="inlineStr">
@@ -19056,7 +19161,7 @@
     <row r="342">
       <c r="A342" s="9" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B342" s="9" t="inlineStr">
@@ -19098,7 +19203,7 @@
     <row r="343">
       <c r="A343" s="9" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B343" s="9" t="inlineStr">
@@ -19140,7 +19245,7 @@
     <row r="344">
       <c r="A344" s="9" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B344" s="9" t="inlineStr">
@@ -19182,7 +19287,7 @@
     <row r="345">
       <c r="A345" s="9" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B345" s="9" t="inlineStr">
@@ -19224,7 +19329,7 @@
     <row r="346">
       <c r="A346" s="9" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B346" s="9" t="inlineStr">
@@ -19254,7 +19359,7 @@
       </c>
       <c r="G346" s="9" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="H346" s="9" t="inlineStr">
@@ -19266,7 +19371,7 @@
     <row r="347">
       <c r="A347" s="9" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B347" s="9" t="inlineStr">
@@ -19308,7 +19413,7 @@
     <row r="348">
       <c r="A348" s="9" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B348" s="9" t="inlineStr">
@@ -19350,7 +19455,7 @@
     <row r="349">
       <c r="A349" s="9" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B349" s="9" t="inlineStr">
@@ -19392,7 +19497,7 @@
     <row r="350">
       <c r="A350" s="9" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B350" s="9" t="inlineStr">
@@ -19434,7 +19539,7 @@
     <row r="351">
       <c r="A351" s="9" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B351" s="9" t="inlineStr">
@@ -19476,7 +19581,7 @@
     <row r="352">
       <c r="A352" s="9" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B352" s="9" t="inlineStr">
@@ -19518,7 +19623,7 @@
     <row r="353">
       <c r="A353" s="9" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B353" s="9" t="inlineStr">
@@ -19560,7 +19665,7 @@
     <row r="354">
       <c r="A354" s="9" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B354" s="9" t="inlineStr">
@@ -19602,7 +19707,7 @@
     <row r="355">
       <c r="A355" s="9" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B355" s="9" t="inlineStr">
@@ -19644,7 +19749,7 @@
     <row r="356">
       <c r="A356" s="9" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B356" s="9" t="inlineStr">
@@ -19686,7 +19791,7 @@
     <row r="357">
       <c r="A357" s="9" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B357" s="9" t="inlineStr">
@@ -19728,7 +19833,7 @@
     <row r="358">
       <c r="A358" s="9" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B358" s="9" t="inlineStr">
@@ -19770,7 +19875,7 @@
     <row r="359">
       <c r="A359" s="9" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B359" s="9" t="inlineStr">
@@ -19812,7 +19917,7 @@
     <row r="360">
       <c r="A360" s="9" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B360" s="9" t="inlineStr">
@@ -19854,7 +19959,7 @@
     <row r="361">
       <c r="A361" s="9" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B361" s="9" t="inlineStr">
@@ -19896,7 +20001,7 @@
     <row r="362">
       <c r="A362" s="9" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B362" s="9" t="inlineStr">
@@ -19938,7 +20043,7 @@
     <row r="363">
       <c r="A363" s="9" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B363" s="9" t="inlineStr">
@@ -19980,7 +20085,7 @@
     <row r="364">
       <c r="A364" s="9" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B364" s="9" t="inlineStr">
@@ -20022,7 +20127,7 @@
     <row r="365">
       <c r="A365" s="9" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B365" s="9" t="inlineStr">
@@ -20064,7 +20169,7 @@
     <row r="366">
       <c r="A366" s="9" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B366" s="9" t="inlineStr">
@@ -20106,7 +20211,7 @@
     <row r="367">
       <c r="A367" s="9" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B367" s="9" t="inlineStr">
@@ -20148,7 +20253,7 @@
     <row r="368">
       <c r="A368" s="9" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B368" s="9" t="inlineStr">
@@ -20190,7 +20295,7 @@
     <row r="369">
       <c r="A369" s="9" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B369" s="9" t="inlineStr">
@@ -20232,7 +20337,7 @@
     <row r="370">
       <c r="A370" s="9" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B370" s="9" t="inlineStr">
@@ -20274,7 +20379,7 @@
     <row r="371">
       <c r="A371" s="9" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B371" s="9" t="inlineStr">
@@ -20316,7 +20421,7 @@
     <row r="372">
       <c r="A372" s="9" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B372" s="9" t="inlineStr">
@@ -20358,7 +20463,7 @@
     <row r="373">
       <c r="A373" s="9" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B373" s="9" t="inlineStr">
@@ -20400,7 +20505,7 @@
     <row r="374">
       <c r="A374" s="9" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B374" s="9" t="inlineStr">
@@ -20442,7 +20547,7 @@
     <row r="375">
       <c r="A375" s="9" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B375" s="9" t="inlineStr">
@@ -20484,7 +20589,7 @@
     <row r="376">
       <c r="A376" s="9" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B376" s="9" t="inlineStr">
@@ -20526,7 +20631,7 @@
     <row r="377">
       <c r="A377" s="9" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B377" s="9" t="inlineStr">
@@ -20568,7 +20673,7 @@
     <row r="378">
       <c r="A378" s="9" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B378" s="9" t="inlineStr">
@@ -20610,7 +20715,7 @@
     <row r="379">
       <c r="A379" s="9" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B379" s="9" t="inlineStr">
@@ -20652,7 +20757,7 @@
     <row r="380">
       <c r="A380" s="9" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B380" s="9" t="inlineStr">
@@ -20694,7 +20799,7 @@
     <row r="381">
       <c r="A381" s="9" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B381" s="9" t="inlineStr">
@@ -20736,7 +20841,7 @@
     <row r="382">
       <c r="A382" s="9" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B382" s="9" t="inlineStr">
@@ -20778,7 +20883,7 @@
     <row r="383">
       <c r="A383" s="9" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B383" s="9" t="inlineStr">
@@ -20820,7 +20925,7 @@
     <row r="384">
       <c r="A384" s="9" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B384" s="9" t="inlineStr">
@@ -20862,7 +20967,7 @@
     <row r="385">
       <c r="A385" s="9" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B385" s="9" t="inlineStr">
@@ -20904,7 +21009,7 @@
     <row r="386">
       <c r="A386" s="9" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B386" s="9" t="inlineStr">
@@ -20946,7 +21051,7 @@
     <row r="387">
       <c r="A387" s="9" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B387" s="9" t="inlineStr">
@@ -20988,7 +21093,7 @@
     <row r="388">
       <c r="A388" s="9" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B388" s="9" t="inlineStr">
@@ -21030,7 +21135,7 @@
     <row r="389">
       <c r="A389" s="9" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B389" s="9" t="inlineStr">
@@ -21072,7 +21177,7 @@
     <row r="390">
       <c r="A390" s="9" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B390" s="9" t="inlineStr">
@@ -21114,7 +21219,7 @@
     <row r="391">
       <c r="A391" s="9" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B391" s="9" t="inlineStr">
@@ -21156,7 +21261,7 @@
     <row r="392">
       <c r="A392" s="9" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B392" s="9" t="inlineStr">
@@ -21198,7 +21303,7 @@
     <row r="393">
       <c r="A393" s="9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B393" s="9" t="inlineStr">
@@ -21240,7 +21345,7 @@
     <row r="394">
       <c r="A394" s="9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B394" s="9" t="inlineStr">
@@ -21282,7 +21387,7 @@
     <row r="395">
       <c r="A395" s="9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B395" s="9" t="inlineStr">
@@ -21324,7 +21429,7 @@
     <row r="396">
       <c r="A396" s="9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B396" s="9" t="inlineStr">
@@ -21366,7 +21471,7 @@
     <row r="397">
       <c r="A397" s="9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B397" s="9" t="inlineStr">
@@ -21408,7 +21513,7 @@
     <row r="398">
       <c r="A398" s="9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B398" s="9" t="inlineStr">
@@ -21450,7 +21555,7 @@
     <row r="399">
       <c r="A399" s="9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B399" s="9" t="inlineStr">
@@ -21492,7 +21597,7 @@
     <row r="400">
       <c r="A400" s="9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B400" s="9" t="inlineStr">
@@ -21534,7 +21639,7 @@
     <row r="401">
       <c r="A401" s="9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B401" s="9" t="inlineStr">
@@ -21576,7 +21681,7 @@
     <row r="402">
       <c r="A402" s="9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B402" s="9" t="inlineStr">
@@ -21618,7 +21723,7 @@
     <row r="403">
       <c r="A403" s="9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B403" s="9" t="inlineStr">
@@ -21660,7 +21765,7 @@
     <row r="404">
       <c r="A404" s="9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B404" s="9" t="inlineStr">
@@ -21702,7 +21807,7 @@
     <row r="405">
       <c r="A405" s="9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B405" s="9" t="inlineStr">
@@ -21744,7 +21849,7 @@
     <row r="406">
       <c r="A406" s="9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B406" s="9" t="inlineStr">
@@ -21786,7 +21891,7 @@
     <row r="407">
       <c r="A407" s="9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B407" s="9" t="inlineStr">
@@ -21828,7 +21933,7 @@
     <row r="408">
       <c r="A408" s="9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B408" s="9" t="inlineStr">
@@ -21870,7 +21975,7 @@
     <row r="409">
       <c r="A409" s="9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B409" s="9" t="inlineStr">
@@ -21912,7 +22017,7 @@
     <row r="410">
       <c r="A410" s="9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B410" s="9" t="inlineStr">
@@ -21954,7 +22059,7 @@
     <row r="411">
       <c r="A411" s="9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B411" s="9" t="inlineStr">
@@ -21996,7 +22101,7 @@
     <row r="412">
       <c r="A412" s="9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B412" s="9" t="inlineStr">
@@ -22038,7 +22143,7 @@
     <row r="413">
       <c r="A413" s="9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B413" s="9" t="inlineStr">
@@ -22080,7 +22185,7 @@
     <row r="414">
       <c r="A414" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B414" s="9" t="inlineStr">
@@ -22122,7 +22227,7 @@
     <row r="415">
       <c r="A415" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B415" s="9" t="inlineStr">
@@ -22164,7 +22269,7 @@
     <row r="416">
       <c r="A416" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B416" s="9" t="inlineStr">
@@ -22206,7 +22311,7 @@
     <row r="417">
       <c r="A417" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B417" s="9" t="inlineStr">
@@ -22248,7 +22353,7 @@
     <row r="418">
       <c r="A418" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B418" s="9" t="inlineStr">
@@ -22290,7 +22395,7 @@
     <row r="419">
       <c r="A419" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B419" s="9" t="inlineStr">
@@ -22332,7 +22437,7 @@
     <row r="420">
       <c r="A420" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B420" s="9" t="inlineStr">
@@ -22374,7 +22479,7 @@
     <row r="421">
       <c r="A421" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B421" s="9" t="inlineStr">
@@ -22416,7 +22521,7 @@
     <row r="422">
       <c r="A422" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B422" s="9" t="inlineStr">
@@ -22458,7 +22563,7 @@
     <row r="423">
       <c r="A423" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B423" s="9" t="inlineStr">
@@ -22500,7 +22605,7 @@
     <row r="424">
       <c r="A424" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B424" s="9" t="inlineStr">
@@ -22542,7 +22647,7 @@
     <row r="425">
       <c r="A425" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B425" s="9" t="inlineStr">
@@ -22584,7 +22689,7 @@
     <row r="426">
       <c r="A426" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B426" s="9" t="inlineStr">
@@ -22626,7 +22731,7 @@
     <row r="427">
       <c r="A427" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B427" s="9" t="inlineStr">
@@ -22668,7 +22773,7 @@
     <row r="428">
       <c r="A428" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B428" s="9" t="inlineStr">
@@ -22710,7 +22815,7 @@
     <row r="429">
       <c r="A429" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B429" s="9" t="inlineStr">
@@ -22752,7 +22857,7 @@
     <row r="430">
       <c r="A430" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B430" s="9" t="inlineStr">
@@ -22794,7 +22899,7 @@
     <row r="431">
       <c r="A431" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B431" s="9" t="inlineStr">
@@ -22836,7 +22941,7 @@
     <row r="432">
       <c r="A432" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B432" s="9" t="inlineStr">
@@ -22878,7 +22983,7 @@
     <row r="433">
       <c r="A433" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B433" s="9" t="inlineStr">
@@ -22920,7 +23025,7 @@
     <row r="434">
       <c r="A434" s="9" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B434" s="9" t="inlineStr">
@@ -22962,7 +23067,7 @@
     <row r="435">
       <c r="A435" s="9" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B435" s="9" t="inlineStr">
@@ -23004,7 +23109,7 @@
     <row r="436">
       <c r="A436" s="9" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B436" s="9" t="inlineStr">
@@ -23046,7 +23151,7 @@
     <row r="437">
       <c r="A437" s="9" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B437" s="9" t="inlineStr">
@@ -23088,7 +23193,7 @@
     <row r="438">
       <c r="A438" s="9" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B438" s="9" t="inlineStr">
@@ -23130,7 +23235,7 @@
     <row r="439">
       <c r="A439" s="9" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B439" s="9" t="inlineStr">
@@ -23150,17 +23255,17 @@
       </c>
       <c r="E439" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F439" s="9" t="inlineStr">
         <is>
-          <t>Elevated</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G439" s="9" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="H439" s="9" t="inlineStr">
@@ -23172,7 +23277,7 @@
     <row r="440">
       <c r="A440" s="9" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B440" s="9" t="inlineStr">
@@ -23214,7 +23319,7 @@
     <row r="441">
       <c r="A441" s="9" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B441" s="9" t="inlineStr">
@@ -23256,7 +23361,7 @@
     <row r="442">
       <c r="A442" s="9" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B442" s="9" t="inlineStr">
@@ -23298,7 +23403,7 @@
     <row r="443">
       <c r="A443" s="9" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B443" s="9" t="inlineStr">
@@ -23340,7 +23445,7 @@
     <row r="444">
       <c r="A444" s="9" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B444" s="9" t="inlineStr">
@@ -23382,7 +23487,7 @@
     <row r="445">
       <c r="A445" s="9" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B445" s="9" t="inlineStr">
@@ -23424,7 +23529,7 @@
     <row r="446">
       <c r="A446" s="9" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B446" s="9" t="inlineStr">
@@ -23444,7 +23549,7 @@
       </c>
       <c r="E446" s="9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F446" s="9" t="inlineStr">
@@ -23454,7 +23559,7 @@
       </c>
       <c r="G446" s="9" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="H446" s="9" t="inlineStr">
@@ -23466,7 +23571,7 @@
     <row r="447">
       <c r="A447" s="9" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B447" s="9" t="inlineStr">
@@ -23508,7 +23613,7 @@
     <row r="448">
       <c r="A448" s="9" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B448" s="9" t="inlineStr">
@@ -23550,7 +23655,7 @@
     <row r="449">
       <c r="A449" s="9" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B449" s="9" t="inlineStr">
@@ -23592,7 +23697,7 @@
     <row r="450">
       <c r="A450" s="9" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B450" s="9" t="inlineStr">
@@ -23634,7 +23739,7 @@
     <row r="451">
       <c r="A451" s="9" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B451" s="9" t="inlineStr">
@@ -23664,7 +23769,7 @@
       </c>
       <c r="G451" s="9" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="H451" s="9" t="inlineStr">
@@ -23676,7 +23781,7 @@
     <row r="452">
       <c r="A452" s="9" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B452" s="9" t="inlineStr">
@@ -23696,17 +23801,17 @@
       </c>
       <c r="E452" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F452" s="9" t="inlineStr">
         <is>
-          <t>Elevated</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G452" s="9" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="H452" s="9" t="inlineStr">
@@ -23718,7 +23823,7 @@
     <row r="453">
       <c r="A453" s="9" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B453" s="9" t="inlineStr">
@@ -23760,7 +23865,7 @@
     <row r="454">
       <c r="A454" s="9" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B454" s="9" t="inlineStr">
@@ -23802,7 +23907,7 @@
     <row r="455">
       <c r="A455" s="9" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B455" s="9" t="inlineStr">
@@ -23844,7 +23949,7 @@
     <row r="456">
       <c r="A456" s="9" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B456" s="9" t="inlineStr">
@@ -23886,7 +23991,7 @@
     <row r="457">
       <c r="A457" s="9" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B457" s="9" t="inlineStr">
@@ -23928,7 +24033,7 @@
     <row r="458">
       <c r="A458" s="9" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B458" s="9" t="inlineStr">
@@ -23970,7 +24075,7 @@
     <row r="459">
       <c r="A459" s="9" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B459" s="9" t="inlineStr">
@@ -24012,7 +24117,7 @@
     <row r="460">
       <c r="A460" s="9" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B460" s="9" t="inlineStr">
@@ -24054,7 +24159,7 @@
     <row r="461">
       <c r="A461" s="9" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B461" s="9" t="inlineStr">
@@ -24096,7 +24201,7 @@
     <row r="462">
       <c r="A462" s="9" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B462" s="9" t="inlineStr">
@@ -24138,7 +24243,7 @@
     <row r="463">
       <c r="A463" s="9" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B463" s="9" t="inlineStr">
@@ -24180,7 +24285,7 @@
     <row r="464">
       <c r="A464" s="9" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B464" s="9" t="inlineStr">
@@ -24222,7 +24327,7 @@
     <row r="465">
       <c r="A465" s="9" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B465" s="9" t="inlineStr">
@@ -24264,7 +24369,7 @@
     <row r="466">
       <c r="A466" s="9" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B466" s="9" t="inlineStr">
@@ -24306,7 +24411,7 @@
     <row r="467">
       <c r="A467" s="9" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B467" s="9" t="inlineStr">
@@ -24348,7 +24453,7 @@
     <row r="468">
       <c r="A468" s="9" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B468" s="9" t="inlineStr">
@@ -24390,7 +24495,7 @@
     <row r="469">
       <c r="A469" s="9" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B469" s="9" t="inlineStr">
@@ -24432,7 +24537,7 @@
     <row r="470">
       <c r="A470" s="9" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B470" s="9" t="inlineStr">
@@ -24474,7 +24579,7 @@
     <row r="471">
       <c r="A471" s="9" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B471" s="9" t="inlineStr">
@@ -24516,7 +24621,7 @@
     <row r="472">
       <c r="A472" s="9" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B472" s="9" t="inlineStr">
@@ -24558,7 +24663,7 @@
     <row r="473">
       <c r="A473" s="9" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B473" s="9" t="inlineStr">
@@ -24600,7 +24705,7 @@
     <row r="474">
       <c r="A474" s="9" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B474" s="9" t="inlineStr">
@@ -24642,7 +24747,7 @@
     <row r="475">
       <c r="A475" s="9" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B475" s="9" t="inlineStr">
@@ -24672,7 +24777,7 @@
       </c>
       <c r="G475" s="9" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="H475" s="9" t="inlineStr">
@@ -24684,7 +24789,7 @@
     <row r="476">
       <c r="A476" s="9" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B476" s="9" t="inlineStr">
@@ -24726,7 +24831,7 @@
     <row r="477">
       <c r="A477" s="9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B477" s="9" t="inlineStr">
@@ -24768,7 +24873,7 @@
     <row r="478">
       <c r="A478" s="9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B478" s="9" t="inlineStr">
@@ -24788,7 +24893,7 @@
       </c>
       <c r="E478" s="9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F478" s="9" t="inlineStr">
@@ -24798,7 +24903,7 @@
       </c>
       <c r="G478" s="9" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="H478" s="9" t="inlineStr">
@@ -24810,7 +24915,7 @@
     <row r="479">
       <c r="A479" s="9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B479" s="9" t="inlineStr">
@@ -24852,7 +24957,7 @@
     <row r="480">
       <c r="A480" s="9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B480" s="9" t="inlineStr">
@@ -24894,7 +24999,7 @@
     <row r="481">
       <c r="A481" s="9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B481" s="9" t="inlineStr">
@@ -24936,7 +25041,7 @@
     <row r="482">
       <c r="A482" s="9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B482" s="9" t="inlineStr">
@@ -24978,7 +25083,7 @@
     <row r="483">
       <c r="A483" s="9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B483" s="9" t="inlineStr">
@@ -25020,7 +25125,7 @@
     <row r="484">
       <c r="A484" s="9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B484" s="9" t="inlineStr">
@@ -25062,7 +25167,7 @@
     <row r="485">
       <c r="A485" s="9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B485" s="9" t="inlineStr">
@@ -25104,7 +25209,7 @@
     <row r="486">
       <c r="A486" s="9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B486" s="9" t="inlineStr">
@@ -25146,7 +25251,7 @@
     <row r="487">
       <c r="A487" s="9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B487" s="9" t="inlineStr">
@@ -25188,7 +25293,7 @@
     <row r="488">
       <c r="A488" s="9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B488" s="9" t="inlineStr">
@@ -25230,7 +25335,7 @@
     <row r="489">
       <c r="A489" s="9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B489" s="9" t="inlineStr">
@@ -25272,7 +25377,7 @@
     <row r="490">
       <c r="A490" s="9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B490" s="9" t="inlineStr">
@@ -25314,7 +25419,7 @@
     <row r="491">
       <c r="A491" s="9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B491" s="9" t="inlineStr">
@@ -25356,7 +25461,7 @@
     <row r="492">
       <c r="A492" s="9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B492" s="9" t="inlineStr">
@@ -25398,7 +25503,7 @@
     <row r="493">
       <c r="A493" s="9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B493" s="9" t="inlineStr">
@@ -25440,7 +25545,7 @@
     <row r="494">
       <c r="A494" s="9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B494" s="9" t="inlineStr">
@@ -25482,7 +25587,7 @@
     <row r="495">
       <c r="A495" s="9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B495" s="9" t="inlineStr">
@@ -25524,7 +25629,7 @@
     <row r="496">
       <c r="A496" s="9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B496" s="9" t="inlineStr">
@@ -25554,7 +25659,7 @@
       </c>
       <c r="G496" s="9" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="H496" s="9" t="inlineStr">
@@ -25566,7 +25671,7 @@
     <row r="497">
       <c r="A497" s="9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B497" s="9" t="inlineStr">
@@ -25608,7 +25713,7 @@
     <row r="498">
       <c r="A498" s="9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B498" s="9" t="inlineStr">
@@ -25650,7 +25755,7 @@
     <row r="499">
       <c r="A499" s="9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B499" s="9" t="inlineStr">
@@ -25692,7 +25797,7 @@
     <row r="500">
       <c r="A500" s="9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B500" s="9" t="inlineStr">
@@ -25734,7 +25839,7 @@
     <row r="501">
       <c r="A501" s="9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B501" s="9" t="inlineStr">
@@ -25776,7 +25881,7 @@
     <row r="502">
       <c r="A502" s="9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B502" s="9" t="inlineStr">
@@ -25818,7 +25923,7 @@
     <row r="503">
       <c r="A503" s="9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B503" s="9" t="inlineStr">
@@ -25860,7 +25965,7 @@
     <row r="504">
       <c r="A504" s="9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B504" s="9" t="inlineStr">
@@ -25902,7 +26007,7 @@
     <row r="505">
       <c r="A505" s="9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B505" s="9" t="inlineStr">
@@ -25944,7 +26049,7 @@
     <row r="506">
       <c r="A506" s="9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B506" s="9" t="inlineStr">
@@ -25986,7 +26091,7 @@
     <row r="507">
       <c r="A507" s="9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B507" s="9" t="inlineStr">
@@ -26028,7 +26133,7 @@
     <row r="508">
       <c r="A508" s="9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B508" s="9" t="inlineStr">
@@ -26070,7 +26175,7 @@
     <row r="509">
       <c r="A509" s="9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B509" s="9" t="inlineStr">
@@ -26112,7 +26217,7 @@
     <row r="510">
       <c r="A510" s="9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B510" s="9" t="inlineStr">
@@ -26154,7 +26259,7 @@
     <row r="511">
       <c r="A511" s="9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B511" s="9" t="inlineStr">
@@ -26196,7 +26301,7 @@
     <row r="512">
       <c r="A512" s="9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B512" s="9" t="inlineStr">
@@ -26238,7 +26343,7 @@
     <row r="513">
       <c r="A513" s="9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B513" s="9" t="inlineStr">
@@ -26280,7 +26385,7 @@
     <row r="514">
       <c r="A514" s="9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B514" s="9" t="inlineStr">
@@ -26322,7 +26427,7 @@
     <row r="515">
       <c r="A515" s="9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B515" s="9" t="inlineStr">
@@ -26364,7 +26469,7 @@
     <row r="516">
       <c r="A516" s="9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B516" s="9" t="inlineStr">
@@ -26406,7 +26511,7 @@
     <row r="517">
       <c r="A517" s="9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B517" s="9" t="inlineStr">
@@ -26436,7 +26541,7 @@
       </c>
       <c r="G517" s="9" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="H517" s="9" t="inlineStr">
@@ -26448,7 +26553,7 @@
     <row r="518">
       <c r="A518" s="9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B518" s="9" t="inlineStr">
@@ -26490,7 +26595,7 @@
     <row r="519">
       <c r="A519" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B519" s="9" t="inlineStr">
@@ -26532,7 +26637,7 @@
     <row r="520">
       <c r="A520" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B520" s="9" t="inlineStr">
@@ -26574,7 +26679,7 @@
     <row r="521">
       <c r="A521" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B521" s="9" t="inlineStr">
@@ -26616,7 +26721,7 @@
     <row r="522">
       <c r="A522" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B522" s="9" t="inlineStr">
@@ -26658,7 +26763,7 @@
     <row r="523">
       <c r="A523" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B523" s="9" t="inlineStr">
@@ -26700,7 +26805,7 @@
     <row r="524">
       <c r="A524" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B524" s="9" t="inlineStr">
@@ -26742,7 +26847,7 @@
     <row r="525">
       <c r="A525" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B525" s="9" t="inlineStr">
@@ -26784,7 +26889,7 @@
     <row r="526">
       <c r="A526" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B526" s="9" t="inlineStr">
@@ -26826,7 +26931,7 @@
     <row r="527">
       <c r="A527" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B527" s="9" t="inlineStr">
@@ -26868,7 +26973,7 @@
     <row r="528">
       <c r="A528" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B528" s="9" t="inlineStr">
@@ -26910,7 +27015,7 @@
     <row r="529">
       <c r="A529" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B529" s="9" t="inlineStr">
@@ -26952,7 +27057,7 @@
     <row r="530">
       <c r="A530" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B530" s="9" t="inlineStr">
@@ -26994,7 +27099,7 @@
     <row r="531">
       <c r="A531" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B531" s="9" t="inlineStr">
@@ -27036,7 +27141,7 @@
     <row r="532">
       <c r="A532" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B532" s="9" t="inlineStr">
@@ -27078,7 +27183,7 @@
     <row r="533">
       <c r="A533" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B533" s="9" t="inlineStr">
@@ -27120,7 +27225,7 @@
     <row r="534">
       <c r="A534" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B534" s="9" t="inlineStr">
@@ -27162,7 +27267,7 @@
     <row r="535">
       <c r="A535" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B535" s="9" t="inlineStr">
@@ -27204,7 +27309,7 @@
     <row r="536">
       <c r="A536" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B536" s="9" t="inlineStr">
@@ -27246,7 +27351,7 @@
     <row r="537">
       <c r="A537" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B537" s="9" t="inlineStr">
@@ -27288,7 +27393,7 @@
     <row r="538">
       <c r="A538" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B538" s="9" t="inlineStr">
@@ -27330,7 +27435,7 @@
     <row r="539">
       <c r="A539" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B539" s="9" t="inlineStr">
@@ -27372,7 +27477,7 @@
     <row r="540">
       <c r="A540" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B540" s="9" t="inlineStr">
@@ -27414,7 +27519,7 @@
     <row r="541">
       <c r="A541" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B541" s="9" t="inlineStr">
@@ -27434,17 +27539,17 @@
       </c>
       <c r="E541" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F541" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Elevated</t>
         </is>
       </c>
       <c r="G541" s="9" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="H541" s="9" t="inlineStr">
@@ -27456,7 +27561,7 @@
     <row r="542">
       <c r="A542" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B542" s="9" t="inlineStr">
@@ -27498,7 +27603,7 @@
     <row r="543">
       <c r="A543" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B543" s="9" t="inlineStr">
@@ -27518,7 +27623,7 @@
       </c>
       <c r="E543" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F543" s="9" t="inlineStr">
@@ -27528,7 +27633,7 @@
       </c>
       <c r="G543" s="9" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="H543" s="9" t="inlineStr">
@@ -27540,7 +27645,7 @@
     <row r="544">
       <c r="A544" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B544" s="9" t="inlineStr">
@@ -27582,7 +27687,7 @@
     <row r="545">
       <c r="A545" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B545" s="9" t="inlineStr">
@@ -27624,7 +27729,7 @@
     <row r="546">
       <c r="A546" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B546" s="9" t="inlineStr">
@@ -27654,7 +27759,7 @@
       </c>
       <c r="G546" s="9" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="H546" s="9" t="inlineStr">
@@ -27666,7 +27771,7 @@
     <row r="547">
       <c r="A547" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B547" s="9" t="inlineStr">
@@ -27708,7 +27813,7 @@
     <row r="548">
       <c r="A548" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B548" s="9" t="inlineStr">
@@ -27750,7 +27855,7 @@
     <row r="549">
       <c r="A549" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B549" s="9" t="inlineStr">
@@ -27792,7 +27897,7 @@
     <row r="550">
       <c r="A550" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B550" s="9" t="inlineStr">
@@ -27834,7 +27939,7 @@
     <row r="551">
       <c r="A551" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B551" s="9" t="inlineStr">
@@ -27876,7 +27981,7 @@
     <row r="552">
       <c r="A552" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B552" s="9" t="inlineStr">
@@ -27918,7 +28023,7 @@
     <row r="553">
       <c r="A553" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B553" s="9" t="inlineStr">
@@ -27960,7 +28065,7 @@
     <row r="554">
       <c r="A554" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B554" s="9" t="inlineStr">
@@ -28002,7 +28107,7 @@
     <row r="555">
       <c r="A555" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B555" s="9" t="inlineStr">
@@ -28044,7 +28149,7 @@
     <row r="556">
       <c r="A556" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B556" s="9" t="inlineStr">
@@ -28086,7 +28191,7 @@
     <row r="557">
       <c r="A557" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B557" s="9" t="inlineStr">
@@ -28106,17 +28211,17 @@
       </c>
       <c r="E557" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F557" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Elevated</t>
         </is>
       </c>
       <c r="G557" s="9" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="H557" s="9" t="inlineStr">
@@ -28128,7 +28233,7 @@
     <row r="558">
       <c r="A558" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B558" s="9" t="inlineStr">
@@ -28170,7 +28275,7 @@
     <row r="559">
       <c r="A559" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B559" s="9" t="inlineStr">
@@ -28190,17 +28295,17 @@
       </c>
       <c r="E559" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F559" s="9" t="inlineStr">
         <is>
-          <t>Elevated</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G559" s="9" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="H559" s="9" t="inlineStr">
@@ -28212,7 +28317,7 @@
     <row r="560">
       <c r="A560" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B560" s="9" t="inlineStr">
@@ -28254,7 +28359,7 @@
     <row r="561">
       <c r="A561" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B561" s="9" t="inlineStr">
@@ -28296,7 +28401,7 @@
     <row r="562">
       <c r="A562" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B562" s="9" t="inlineStr">
@@ -28338,7 +28443,7 @@
     <row r="563">
       <c r="A563" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B563" s="9" t="inlineStr">
@@ -28380,7 +28485,7 @@
     <row r="564">
       <c r="A564" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B564" s="9" t="inlineStr">
@@ -28422,7 +28527,7 @@
     <row r="565">
       <c r="A565" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B565" s="9" t="inlineStr">
@@ -28464,7 +28569,7 @@
     <row r="566">
       <c r="A566" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B566" s="9" t="inlineStr">
@@ -28506,7 +28611,7 @@
     <row r="567">
       <c r="A567" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B567" s="9" t="inlineStr">
@@ -28548,7 +28653,7 @@
     <row r="568">
       <c r="A568" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B568" s="9" t="inlineStr">
@@ -28590,7 +28695,7 @@
     <row r="569">
       <c r="A569" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B569" s="9" t="inlineStr">
@@ -28632,7 +28737,7 @@
     <row r="570">
       <c r="A570" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B570" s="9" t="inlineStr">
@@ -28674,7 +28779,7 @@
     <row r="571">
       <c r="A571" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B571" s="9" t="inlineStr">
@@ -28716,7 +28821,7 @@
     <row r="572">
       <c r="A572" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B572" s="9" t="inlineStr">
@@ -28758,7 +28863,7 @@
     <row r="573">
       <c r="A573" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B573" s="9" t="inlineStr">
@@ -28800,7 +28905,7 @@
     <row r="574">
       <c r="A574" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B574" s="9" t="inlineStr">
@@ -28842,7 +28947,7 @@
     <row r="575">
       <c r="A575" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B575" s="9" t="inlineStr">
@@ -28884,7 +28989,7 @@
     <row r="576">
       <c r="A576" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B576" s="9" t="inlineStr">
@@ -28926,7 +29031,7 @@
     <row r="577">
       <c r="A577" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B577" s="9" t="inlineStr">
@@ -28968,7 +29073,7 @@
     <row r="578">
       <c r="A578" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B578" s="9" t="inlineStr">
@@ -29010,7 +29115,7 @@
     <row r="579">
       <c r="A579" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B579" s="9" t="inlineStr">
@@ -29052,7 +29157,7 @@
     <row r="580">
       <c r="A580" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B580" s="9" t="inlineStr">
@@ -29094,7 +29199,7 @@
     <row r="581">
       <c r="A581" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B581" s="9" t="inlineStr">
@@ -29136,7 +29241,7 @@
     <row r="582">
       <c r="A582" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B582" s="9" t="inlineStr">
@@ -29178,7 +29283,7 @@
     <row r="583">
       <c r="A583" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B583" s="9" t="inlineStr">
@@ -29198,17 +29303,17 @@
       </c>
       <c r="E583" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F583" s="9" t="inlineStr">
         <is>
-          <t>Elevated</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G583" s="9" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="H583" s="9" t="inlineStr">
@@ -29220,7 +29325,7 @@
     <row r="584">
       <c r="A584" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B584" s="9" t="inlineStr">
@@ -29262,7 +29367,7 @@
     <row r="585">
       <c r="A585" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B585" s="9" t="inlineStr">
@@ -29304,7 +29409,7 @@
     <row r="586">
       <c r="A586" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B586" s="9" t="inlineStr">
@@ -29346,7 +29451,7 @@
     <row r="587">
       <c r="A587" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B587" s="9" t="inlineStr">
@@ -29388,7 +29493,7 @@
     <row r="588">
       <c r="A588" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B588" s="9" t="inlineStr">
@@ -29430,7 +29535,7 @@
     <row r="589">
       <c r="A589" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B589" s="9" t="inlineStr">
@@ -29472,7 +29577,7 @@
     <row r="590">
       <c r="A590" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B590" s="9" t="inlineStr">
@@ -29514,7 +29619,7 @@
     <row r="591">
       <c r="A591" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B591" s="9" t="inlineStr">
@@ -29556,7 +29661,7 @@
     <row r="592">
       <c r="A592" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B592" s="9" t="inlineStr">
@@ -29598,7 +29703,7 @@
     <row r="593">
       <c r="A593" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B593" s="9" t="inlineStr">
@@ -29640,7 +29745,7 @@
     <row r="594">
       <c r="A594" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B594" s="9" t="inlineStr">
@@ -29682,7 +29787,7 @@
     <row r="595">
       <c r="A595" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B595" s="9" t="inlineStr">
@@ -29724,7 +29829,7 @@
     <row r="596">
       <c r="A596" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B596" s="9" t="inlineStr">
@@ -29766,7 +29871,7 @@
     <row r="597">
       <c r="A597" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B597" s="9" t="inlineStr">
@@ -29808,7 +29913,7 @@
     <row r="598">
       <c r="A598" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B598" s="9" t="inlineStr">
@@ -29850,7 +29955,7 @@
     <row r="599">
       <c r="A599" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B599" s="9" t="inlineStr">
@@ -29892,7 +29997,7 @@
     <row r="600">
       <c r="A600" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B600" s="9" t="inlineStr">
@@ -29934,7 +30039,7 @@
     <row r="601">
       <c r="A601" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B601" s="9" t="inlineStr">
@@ -29976,7 +30081,7 @@
     <row r="602">
       <c r="A602" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B602" s="9" t="inlineStr">
@@ -30018,7 +30123,7 @@
     <row r="603">
       <c r="A603" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B603" s="9" t="inlineStr">
@@ -30060,7 +30165,7 @@
     <row r="604">
       <c r="A604" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B604" s="9" t="inlineStr">
@@ -30102,7 +30207,7 @@
     <row r="605">
       <c r="A605" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B605" s="9" t="inlineStr">
@@ -30144,7 +30249,7 @@
     <row r="606">
       <c r="A606" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B606" s="9" t="inlineStr">
@@ -30186,7 +30291,7 @@
     <row r="607">
       <c r="A607" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B607" s="9" t="inlineStr">
@@ -30228,7 +30333,7 @@
     <row r="608">
       <c r="A608" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B608" s="9" t="inlineStr">
@@ -30270,7 +30375,7 @@
     <row r="609">
       <c r="A609" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B609" s="9" t="inlineStr">
@@ -30312,7 +30417,7 @@
     <row r="610">
       <c r="A610" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B610" s="9" t="inlineStr">
@@ -30354,7 +30459,7 @@
     <row r="611">
       <c r="A611" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B611" s="9" t="inlineStr">
@@ -30396,7 +30501,7 @@
     <row r="612">
       <c r="A612" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B612" s="9" t="inlineStr">
@@ -30438,7 +30543,7 @@
     <row r="613">
       <c r="A613" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B613" s="9" t="inlineStr">
@@ -30480,7 +30585,7 @@
     <row r="614">
       <c r="A614" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B614" s="9" t="inlineStr">
@@ -30522,7 +30627,7 @@
     <row r="615">
       <c r="A615" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B615" s="9" t="inlineStr">
@@ -30564,7 +30669,7 @@
     <row r="616">
       <c r="A616" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B616" s="9" t="inlineStr">
@@ -30606,7 +30711,7 @@
     <row r="617">
       <c r="A617" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B617" s="9" t="inlineStr">
@@ -30648,7 +30753,7 @@
     <row r="618">
       <c r="A618" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B618" s="9" t="inlineStr">
@@ -30690,7 +30795,7 @@
     <row r="619">
       <c r="A619" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B619" s="9" t="inlineStr">
@@ -30732,7 +30837,7 @@
     <row r="620">
       <c r="A620" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B620" s="9" t="inlineStr">
@@ -30774,7 +30879,7 @@
     <row r="621">
       <c r="A621" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B621" s="9" t="inlineStr">
@@ -30816,7 +30921,7 @@
     <row r="622">
       <c r="A622" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B622" s="9" t="inlineStr">
@@ -30858,7 +30963,7 @@
     <row r="623">
       <c r="A623" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B623" s="9" t="inlineStr">
@@ -30900,7 +31005,7 @@
     <row r="624">
       <c r="A624" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B624" s="9" t="inlineStr">
@@ -30942,7 +31047,7 @@
     <row r="625">
       <c r="A625" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B625" s="9" t="inlineStr">
@@ -30984,7 +31089,7 @@
     <row r="626">
       <c r="A626" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B626" s="9" t="inlineStr">
@@ -31026,7 +31131,7 @@
     <row r="627">
       <c r="A627" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B627" s="9" t="inlineStr">
@@ -31068,7 +31173,7 @@
     <row r="628">
       <c r="A628" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B628" s="9" t="inlineStr">
@@ -31110,7 +31215,7 @@
     <row r="629">
       <c r="A629" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B629" s="9" t="inlineStr">
@@ -31152,7 +31257,7 @@
     <row r="630">
       <c r="A630" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B630" s="9" t="inlineStr">
@@ -31194,7 +31299,7 @@
     <row r="631">
       <c r="A631" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B631" s="9" t="inlineStr">
@@ -31236,7 +31341,7 @@
     <row r="632">
       <c r="A632" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B632" s="9" t="inlineStr">
@@ -31278,7 +31383,7 @@
     <row r="633">
       <c r="A633" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B633" s="9" t="inlineStr">
@@ -31320,7 +31425,7 @@
     <row r="634">
       <c r="A634" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B634" s="9" t="inlineStr">
@@ -31362,7 +31467,7 @@
     <row r="635">
       <c r="A635" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B635" s="9" t="inlineStr">
@@ -31404,7 +31509,7 @@
     <row r="636">
       <c r="A636" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B636" s="9" t="inlineStr">
@@ -31446,7 +31551,7 @@
     <row r="637">
       <c r="A637" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B637" s="9" t="inlineStr">
@@ -31488,7 +31593,7 @@
     <row r="638">
       <c r="A638" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B638" s="9" t="inlineStr">
@@ -31530,7 +31635,7 @@
     <row r="639">
       <c r="A639" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B639" s="9" t="inlineStr">
@@ -31572,7 +31677,7 @@
     <row r="640">
       <c r="A640" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B640" s="9" t="inlineStr">
@@ -31614,7 +31719,7 @@
     <row r="641">
       <c r="A641" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B641" s="9" t="inlineStr">
@@ -31656,7 +31761,7 @@
     <row r="642">
       <c r="A642" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B642" s="9" t="inlineStr">
@@ -31698,7 +31803,7 @@
     <row r="643">
       <c r="A643" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B643" s="9" t="inlineStr">
@@ -31740,7 +31845,7 @@
     <row r="644">
       <c r="A644" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B644" s="9" t="inlineStr">
@@ -31782,7 +31887,7 @@
     <row r="645">
       <c r="A645" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B645" s="9" t="inlineStr">
@@ -31824,7 +31929,7 @@
     <row r="646">
       <c r="A646" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B646" s="9" t="inlineStr">
@@ -31866,7 +31971,7 @@
     <row r="647">
       <c r="A647" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B647" s="9" t="inlineStr">
@@ -31908,7 +32013,7 @@
     <row r="648">
       <c r="A648" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B648" s="9" t="inlineStr">
@@ -31928,7 +32033,7 @@
       </c>
       <c r="E648" s="9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F648" s="9" t="inlineStr">
@@ -31938,7 +32043,7 @@
       </c>
       <c r="G648" s="9" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="H648" s="9" t="inlineStr">
@@ -31950,7 +32055,7 @@
     <row r="649">
       <c r="A649" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B649" s="9" t="inlineStr">
@@ -31992,7 +32097,7 @@
     <row r="650">
       <c r="A650" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B650" s="9" t="inlineStr">
@@ -32034,7 +32139,7 @@
     <row r="651">
       <c r="A651" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B651" s="9" t="inlineStr">
@@ -32076,7 +32181,7 @@
     <row r="652">
       <c r="A652" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B652" s="9" t="inlineStr">
@@ -32118,7 +32223,7 @@
     <row r="653">
       <c r="A653" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B653" s="9" t="inlineStr">
@@ -32160,7 +32265,7 @@
     <row r="654">
       <c r="A654" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B654" s="9" t="inlineStr">
@@ -32202,7 +32307,7 @@
     <row r="655">
       <c r="A655" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B655" s="9" t="inlineStr">
@@ -32222,7 +32327,7 @@
       </c>
       <c r="E655" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F655" s="9" t="inlineStr">
@@ -32232,7 +32337,7 @@
       </c>
       <c r="G655" s="9" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="H655" s="9" t="inlineStr">
@@ -32244,7 +32349,7 @@
     <row r="656">
       <c r="A656" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B656" s="9" t="inlineStr">
@@ -32286,7 +32391,7 @@
     <row r="657">
       <c r="A657" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B657" s="9" t="inlineStr">
@@ -32328,7 +32433,7 @@
     <row r="658">
       <c r="A658" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B658" s="9" t="inlineStr">
@@ -32370,7 +32475,7 @@
     <row r="659">
       <c r="A659" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B659" s="9" t="inlineStr">
@@ -32412,7 +32517,7 @@
     <row r="660">
       <c r="A660" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B660" s="9" t="inlineStr">
@@ -32454,7 +32559,7 @@
     <row r="661">
       <c r="A661" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B661" s="9" t="inlineStr">
@@ -32496,7 +32601,7 @@
     <row r="662">
       <c r="A662" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B662" s="9" t="inlineStr">
@@ -32516,17 +32621,17 @@
       </c>
       <c r="E662" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F662" s="9" t="inlineStr">
         <is>
-          <t>Elevated</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G662" s="9" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="H662" s="9" t="inlineStr">
@@ -32538,7 +32643,7 @@
     <row r="663">
       <c r="A663" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B663" s="9" t="inlineStr">
@@ -32580,7 +32685,7 @@
     <row r="664">
       <c r="A664" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B664" s="9" t="inlineStr">
@@ -32622,7 +32727,7 @@
     <row r="665">
       <c r="A665" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B665" s="9" t="inlineStr">
@@ -32664,7 +32769,7 @@
     <row r="666">
       <c r="A666" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B666" s="9" t="inlineStr">
@@ -32706,7 +32811,7 @@
     <row r="667">
       <c r="A667" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B667" s="9" t="inlineStr">
@@ -32748,7 +32853,7 @@
     <row r="668">
       <c r="A668" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B668" s="9" t="inlineStr">
@@ -32790,7 +32895,7 @@
     <row r="669">
       <c r="A669" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B669" s="9" t="inlineStr">
@@ -32832,7 +32937,7 @@
     <row r="670">
       <c r="A670" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B670" s="9" t="inlineStr">
@@ -32874,7 +32979,7 @@
     <row r="671">
       <c r="A671" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B671" s="9" t="inlineStr">
@@ -32916,7 +33021,7 @@
     <row r="672">
       <c r="A672" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B672" s="9" t="inlineStr">
@@ -32958,7 +33063,7 @@
     <row r="673">
       <c r="A673" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B673" s="9" t="inlineStr">
@@ -33000,7 +33105,7 @@
     <row r="674">
       <c r="A674" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B674" s="9" t="inlineStr">
@@ -33042,7 +33147,7 @@
     <row r="675">
       <c r="A675" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B675" s="9" t="inlineStr">
@@ -33084,7 +33189,7 @@
     <row r="676">
       <c r="A676" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B676" s="9" t="inlineStr">
@@ -33126,7 +33231,7 @@
     <row r="677">
       <c r="A677" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B677" s="9" t="inlineStr">
@@ -33168,7 +33273,7 @@
     <row r="678">
       <c r="A678" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B678" s="9" t="inlineStr">
@@ -33210,7 +33315,7 @@
     <row r="679">
       <c r="A679" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B679" s="9" t="inlineStr">
@@ -33252,7 +33357,7 @@
     <row r="680">
       <c r="A680" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B680" s="9" t="inlineStr">
@@ -33294,7 +33399,7 @@
     <row r="681">
       <c r="A681" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B681" s="9" t="inlineStr">
@@ -33336,7 +33441,7 @@
     <row r="682">
       <c r="A682" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B682" s="9" t="inlineStr">
@@ -33378,7 +33483,7 @@
     <row r="683">
       <c r="A683" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B683" s="9" t="inlineStr">
@@ -33420,7 +33525,7 @@
     <row r="684">
       <c r="A684" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B684" s="9" t="inlineStr">
@@ -33462,7 +33567,7 @@
     <row r="685">
       <c r="A685" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B685" s="9" t="inlineStr">
@@ -33504,7 +33609,7 @@
     <row r="686">
       <c r="A686" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B686" s="9" t="inlineStr">
@@ -33546,7 +33651,7 @@
     <row r="687">
       <c r="A687" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B687" s="9" t="inlineStr">
@@ -33588,7 +33693,7 @@
     <row r="688">
       <c r="A688" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B688" s="9" t="inlineStr">
@@ -33630,7 +33735,7 @@
     <row r="689">
       <c r="A689" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B689" s="9" t="inlineStr">
@@ -33672,7 +33777,7 @@
     <row r="690">
       <c r="A690" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B690" s="9" t="inlineStr">
@@ -33714,7 +33819,7 @@
     <row r="691">
       <c r="A691" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B691" s="9" t="inlineStr">
@@ -33756,7 +33861,7 @@
     <row r="692">
       <c r="A692" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B692" s="9" t="inlineStr">
@@ -33798,7 +33903,7 @@
     <row r="693">
       <c r="A693" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B693" s="9" t="inlineStr">
@@ -33840,7 +33945,7 @@
     <row r="694">
       <c r="A694" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B694" s="9" t="inlineStr">
@@ -33882,7 +33987,7 @@
     <row r="695">
       <c r="A695" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B695" s="9" t="inlineStr">
@@ -33924,7 +34029,7 @@
     <row r="696">
       <c r="A696" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B696" s="9" t="inlineStr">
@@ -33966,7 +34071,7 @@
     <row r="697">
       <c r="A697" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B697" s="9" t="inlineStr">
@@ -34008,7 +34113,7 @@
     <row r="698">
       <c r="A698" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B698" s="9" t="inlineStr">
@@ -34050,7 +34155,7 @@
     <row r="699">
       <c r="A699" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B699" s="9" t="inlineStr">
@@ -34092,7 +34197,7 @@
     <row r="700">
       <c r="A700" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B700" s="9" t="inlineStr">
@@ -34134,7 +34239,7 @@
     <row r="701">
       <c r="A701" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B701" s="9" t="inlineStr">
@@ -34176,7 +34281,7 @@
     <row r="702">
       <c r="A702" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B702" s="9" t="inlineStr">
@@ -34218,7 +34323,7 @@
     <row r="703">
       <c r="A703" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B703" s="9" t="inlineStr">
@@ -34260,7 +34365,7 @@
     <row r="704">
       <c r="A704" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B704" s="9" t="inlineStr">
@@ -34302,7 +34407,7 @@
     <row r="705">
       <c r="A705" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B705" s="9" t="inlineStr">
@@ -34344,7 +34449,7 @@
     <row r="706">
       <c r="A706" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B706" s="9" t="inlineStr">
@@ -34386,7 +34491,7 @@
     <row r="707">
       <c r="A707" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B707" s="9" t="inlineStr">
@@ -34428,7 +34533,7 @@
     <row r="708">
       <c r="A708" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B708" s="9" t="inlineStr">
@@ -34470,7 +34575,7 @@
     <row r="709">
       <c r="A709" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B709" s="9" t="inlineStr">
@@ -34512,7 +34617,7 @@
     <row r="710">
       <c r="A710" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B710" s="9" t="inlineStr">
@@ -34554,7 +34659,7 @@
     <row r="711">
       <c r="A711" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B711" s="9" t="inlineStr">
@@ -34596,7 +34701,7 @@
     <row r="712">
       <c r="A712" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B712" s="9" t="inlineStr">
@@ -34638,7 +34743,7 @@
     <row r="713">
       <c r="A713" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B713" s="9" t="inlineStr">
@@ -34680,7 +34785,7 @@
     <row r="714">
       <c r="A714" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B714" s="9" t="inlineStr">
@@ -34722,7 +34827,7 @@
     <row r="715">
       <c r="A715" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B715" s="9" t="inlineStr">
@@ -34764,7 +34869,7 @@
     <row r="716">
       <c r="A716" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B716" s="9" t="inlineStr">
@@ -34806,7 +34911,7 @@
     <row r="717">
       <c r="A717" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B717" s="9" t="inlineStr">
@@ -34848,7 +34953,7 @@
     <row r="718">
       <c r="A718" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B718" s="9" t="inlineStr">
@@ -34890,7 +34995,7 @@
     <row r="719">
       <c r="A719" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B719" s="9" t="inlineStr">
@@ -34932,7 +35037,7 @@
     <row r="720">
       <c r="A720" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B720" s="9" t="inlineStr">
@@ -34974,7 +35079,7 @@
     <row r="721">
       <c r="A721" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B721" s="9" t="inlineStr">
@@ -35016,7 +35121,7 @@
     <row r="722">
       <c r="A722" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B722" s="9" t="inlineStr">
@@ -35058,7 +35163,7 @@
     <row r="723">
       <c r="A723" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B723" s="9" t="inlineStr">
@@ -35100,7 +35205,7 @@
     <row r="724">
       <c r="A724" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B724" s="9" t="inlineStr">
@@ -35142,7 +35247,7 @@
     <row r="725">
       <c r="A725" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B725" s="9" t="inlineStr">
@@ -35184,7 +35289,7 @@
     <row r="726">
       <c r="A726" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B726" s="9" t="inlineStr">
@@ -35226,7 +35331,7 @@
     <row r="727">
       <c r="A727" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B727" s="9" t="inlineStr">
@@ -35268,7 +35373,7 @@
     <row r="728">
       <c r="